--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -628,12 +628,12 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Hall of Fame</t>
+          <t>Packs from several sets</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mark Yes on the rips you want in the gold section at the top of the home page. Use Rank to order them, 1 first. Leave Rank blank and the site orders by rarity, then by views. Anything marked Yes also belongs in the Greatest Hits playlist on YouTube.</t>
+          <t>A tin with two packs, or an ex box with ten packs from four sets, belongs to every set it contains. Put the set the video is really about in Set, and the rest in Set 2 to Set 4. The rip then shows up under every one of those sets, and the first one picks which wrapper the tile shows. More than four is rare: type the extras into More Sets, separated by commas.</t>
         </is>
       </c>
     </row>
@@ -641,23 +641,36 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Hall of Fame</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Mark Yes on the rips you want in the gold section at the top of the home page. Use Rank to order them, 1 first. Leave Rank blank and the site orders by rarity, then by views. Anything marked Yes also belongs in the Greatest Hits playlist on YouTube.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Set Notes tab</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Two facts the card database does not carry: whether a set is still in print, and what a pack costs. The set guides leave both out until you fill them in.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Careful</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Rebuilding this file overwrites it. Import your latest export first, then rebuild.</t>
         </is>
@@ -1062,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W309"/>
+  <dimension ref="A1:Y309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1074,20 +1087,22 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="46" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1138,70 +1153,80 @@
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
+          <t>Set 4</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>More Sets</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
           <t>Box / Series</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Opening Type</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Has Hit</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Hit Card</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Hit Rarity</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Hall of Fame</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>HoF Rank</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>Playlist To Add</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="T1" s="8" t="inlineStr">
         <is>
           <t>Affiliate Link</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="U1" s="8" t="inlineStr">
         <is>
           <t>Site Title</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="V1" s="8" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="W1" s="8" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="X1" s="8" t="inlineStr">
         <is>
           <t>Hide</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="Y1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1243,13 +1268,13 @@
       <c r="H2" s="14" t="n"/>
       <c r="I2" s="14" t="n"/>
       <c r="J2" s="14" t="n"/>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L2" s="14" t="n"/>
-      <c r="M2" s="14" t="n"/>
       <c r="N2" s="14" t="n"/>
       <c r="O2" s="14" t="n"/>
       <c r="P2" s="14" t="n"/>
@@ -1260,6 +1285,8 @@
       <c r="U2" s="14" t="n"/>
       <c r="V2" s="14" t="n"/>
       <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1297,13 +1324,13 @@
       <c r="H3" s="14" t="n"/>
       <c r="I3" s="14" t="n"/>
       <c r="J3" s="14" t="n"/>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L3" s="14" t="n"/>
-      <c r="M3" s="14" t="n"/>
       <c r="N3" s="14" t="n"/>
       <c r="O3" s="14" t="n"/>
       <c r="P3" s="14" t="n"/>
@@ -1314,6 +1341,8 @@
       <c r="U3" s="14" t="n"/>
       <c r="V3" s="14" t="n"/>
       <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1351,24 +1380,24 @@
       <c r="H4" s="14" t="n"/>
       <c r="I4" s="14" t="n"/>
       <c r="J4" s="14" t="n"/>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O4" s="14" t="n"/>
-      <c r="P4" s="14" t="n"/>
       <c r="Q4" s="14" t="n"/>
       <c r="R4" s="14" t="n"/>
       <c r="S4" s="14" t="n"/>
@@ -1376,6 +1405,8 @@
       <c r="U4" s="14" t="n"/>
       <c r="V4" s="14" t="n"/>
       <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1414,19 +1445,19 @@
       <c r="I5" s="14" t="n"/>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="L5" s="14" t="n"/>
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="13" t="inlineStr">
+        <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="14" t="n"/>
       <c r="Q5" s="14" t="n"/>
       <c r="R5" s="14" t="n"/>
       <c r="S5" s="14" t="n"/>
@@ -1434,6 +1465,8 @@
       <c r="U5" s="14" t="n"/>
       <c r="V5" s="14" t="n"/>
       <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1471,13 +1504,13 @@
       <c r="H6" s="14" t="n"/>
       <c r="I6" s="14" t="n"/>
       <c r="J6" s="14" t="n"/>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
       <c r="P6" s="14" t="n"/>
@@ -1488,6 +1521,8 @@
       <c r="U6" s="14" t="n"/>
       <c r="V6" s="14" t="n"/>
       <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1525,24 +1560,24 @@
       <c r="H7" s="14" t="n"/>
       <c r="I7" s="14" t="n"/>
       <c r="J7" s="14" t="n"/>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M7" s="14" t="n"/>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="O7" s="14" t="n"/>
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O7" s="14" t="n"/>
-      <c r="P7" s="14" t="n"/>
       <c r="Q7" s="14" t="n"/>
       <c r="R7" s="14" t="n"/>
       <c r="S7" s="14" t="n"/>
@@ -1550,6 +1585,8 @@
       <c r="U7" s="14" t="n"/>
       <c r="V7" s="14" t="n"/>
       <c r="W7" s="14" t="n"/>
+      <c r="X7" s="14" t="n"/>
+      <c r="Y7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1587,24 +1624,24 @@
       <c r="H8" s="14" t="n"/>
       <c r="I8" s="14" t="n"/>
       <c r="J8" s="14" t="n"/>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="14" t="n"/>
       <c r="Q8" s="14" t="n"/>
       <c r="R8" s="14" t="n"/>
       <c r="S8" s="14" t="n"/>
@@ -1612,6 +1649,8 @@
       <c r="U8" s="14" t="n"/>
       <c r="V8" s="14" t="n"/>
       <c r="W8" s="14" t="n"/>
+      <c r="X8" s="14" t="n"/>
+      <c r="Y8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1649,24 +1688,24 @@
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="14" t="n"/>
       <c r="J9" s="14" t="n"/>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="O9" s="14" t="n"/>
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
       <c r="Q9" s="14" t="n"/>
       <c r="R9" s="14" t="n"/>
       <c r="S9" s="14" t="n"/>
@@ -1674,6 +1713,8 @@
       <c r="U9" s="14" t="n"/>
       <c r="V9" s="14" t="n"/>
       <c r="W9" s="14" t="n"/>
+      <c r="X9" s="14" t="n"/>
+      <c r="Y9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1711,24 +1752,24 @@
       <c r="H10" s="14" t="n"/>
       <c r="I10" s="14" t="n"/>
       <c r="J10" s="14" t="n"/>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="O10" s="14" t="n"/>
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t>Double Rare (2 black stars)</t>
         </is>
       </c>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14" t="n"/>
       <c r="Q10" s="14" t="n"/>
       <c r="R10" s="14" t="n"/>
       <c r="S10" s="14" t="n"/>
@@ -1736,6 +1777,8 @@
       <c r="U10" s="14" t="n"/>
       <c r="V10" s="14" t="n"/>
       <c r="W10" s="14" t="n"/>
+      <c r="X10" s="14" t="n"/>
+      <c r="Y10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1773,24 +1816,24 @@
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="14" t="n"/>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="13" t="inlineStr">
+      <c r="O11" s="14" t="n"/>
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
       <c r="Q11" s="14" t="n"/>
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="14" t="n"/>
@@ -1798,6 +1841,8 @@
       <c r="U11" s="14" t="n"/>
       <c r="V11" s="14" t="n"/>
       <c r="W11" s="14" t="n"/>
+      <c r="X11" s="14" t="n"/>
+      <c r="Y11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1835,13 +1880,13 @@
       <c r="H12" s="14" t="n"/>
       <c r="I12" s="14" t="n"/>
       <c r="J12" s="14" t="n"/>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
       <c r="P12" s="14" t="n"/>
@@ -1852,6 +1897,8 @@
       <c r="U12" s="14" t="n"/>
       <c r="V12" s="14" t="n"/>
       <c r="W12" s="14" t="n"/>
+      <c r="X12" s="14" t="n"/>
+      <c r="Y12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1890,19 +1937,19 @@
       <c r="I13" s="14" t="n"/>
       <c r="J13" s="14" t="n"/>
       <c r="K13" s="14" t="n"/>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="13" t="inlineStr">
+        <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="14" t="n"/>
       <c r="Q13" s="14" t="n"/>
       <c r="R13" s="14" t="n"/>
       <c r="S13" s="14" t="n"/>
@@ -1910,6 +1957,8 @@
       <c r="U13" s="14" t="n"/>
       <c r="V13" s="14" t="n"/>
       <c r="W13" s="14" t="n"/>
+      <c r="X13" s="14" t="n"/>
+      <c r="Y13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1947,24 +1996,24 @@
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="14" t="n"/>
       <c r="J14" s="14" t="n"/>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="N14" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M14" s="14" t="n"/>
-      <c r="N14" s="13" t="inlineStr">
+      <c r="O14" s="14" t="n"/>
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="14" t="n"/>
       <c r="Q14" s="14" t="n"/>
       <c r="R14" s="14" t="n"/>
       <c r="S14" s="14" t="n"/>
@@ -1972,6 +2021,8 @@
       <c r="U14" s="14" t="n"/>
       <c r="V14" s="14" t="n"/>
       <c r="W14" s="14" t="n"/>
+      <c r="X14" s="14" t="n"/>
+      <c r="Y14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -2009,24 +2060,24 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="14" t="n"/>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="13" t="inlineStr">
+      <c r="O15" s="14" t="n"/>
+      <c r="P15" s="13" t="inlineStr">
         <is>
           <t>Double Rare (2 black stars)</t>
         </is>
       </c>
-      <c r="O15" s="14" t="n"/>
-      <c r="P15" s="14" t="n"/>
       <c r="Q15" s="14" t="n"/>
       <c r="R15" s="14" t="n"/>
       <c r="S15" s="14" t="n"/>
@@ -2034,6 +2085,8 @@
       <c r="U15" s="14" t="n"/>
       <c r="V15" s="14" t="n"/>
       <c r="W15" s="14" t="n"/>
+      <c r="X15" s="14" t="n"/>
+      <c r="Y15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -2071,13 +2124,13 @@
       <c r="H16" s="14" t="n"/>
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="n"/>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
       <c r="P16" s="14" t="n"/>
@@ -2088,6 +2141,8 @@
       <c r="U16" s="14" t="n"/>
       <c r="V16" s="14" t="n"/>
       <c r="W16" s="14" t="n"/>
+      <c r="X16" s="14" t="n"/>
+      <c r="Y16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -2125,24 +2180,24 @@
       <c r="H17" s="14" t="n"/>
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="13" t="inlineStr">
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
       <c r="Q17" s="14" t="n"/>
       <c r="R17" s="14" t="n"/>
       <c r="S17" s="14" t="n"/>
@@ -2150,6 +2205,8 @@
       <c r="U17" s="14" t="n"/>
       <c r="V17" s="14" t="n"/>
       <c r="W17" s="14" t="n"/>
+      <c r="X17" s="14" t="n"/>
+      <c r="Y17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2187,13 +2244,13 @@
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="14" t="n"/>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
       <c r="P18" s="14" t="n"/>
@@ -2204,6 +2261,8 @@
       <c r="U18" s="14" t="n"/>
       <c r="V18" s="14" t="n"/>
       <c r="W18" s="14" t="n"/>
+      <c r="X18" s="14" t="n"/>
+      <c r="Y18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2242,19 +2301,19 @@
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="14" t="n"/>
       <c r="K19" s="14" t="n"/>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="13" t="inlineStr">
+        <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
       <c r="Q19" s="14" t="n"/>
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="n"/>
@@ -2262,6 +2321,8 @@
       <c r="U19" s="14" t="n"/>
       <c r="V19" s="14" t="n"/>
       <c r="W19" s="14" t="n"/>
+      <c r="X19" s="14" t="n"/>
+      <c r="Y19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2299,24 +2360,24 @@
       <c r="H20" s="14" t="n"/>
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="14" t="n"/>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="13" t="inlineStr">
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="n"/>
@@ -2324,6 +2385,8 @@
       <c r="U20" s="14" t="n"/>
       <c r="V20" s="14" t="n"/>
       <c r="W20" s="14" t="n"/>
+      <c r="X20" s="14" t="n"/>
+      <c r="Y20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2365,13 +2428,13 @@
       </c>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="14" t="n"/>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n"/>
       <c r="P21" s="14" t="n"/>
@@ -2382,6 +2445,8 @@
       <c r="U21" s="14" t="n"/>
       <c r="V21" s="14" t="n"/>
       <c r="W21" s="14" t="n"/>
+      <c r="X21" s="14" t="n"/>
+      <c r="Y21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2419,13 +2484,13 @@
       <c r="H22" s="14" t="n"/>
       <c r="I22" s="14" t="n"/>
       <c r="J22" s="14" t="n"/>
-      <c r="K22" s="13" t="inlineStr">
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
       <c r="P22" s="14" t="n"/>
@@ -2436,6 +2501,8 @@
       <c r="U22" s="14" t="n"/>
       <c r="V22" s="14" t="n"/>
       <c r="W22" s="14" t="n"/>
+      <c r="X22" s="14" t="n"/>
+      <c r="Y22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2473,24 +2540,24 @@
       <c r="H23" s="14" t="n"/>
       <c r="I23" s="14" t="n"/>
       <c r="J23" s="14" t="n"/>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="N23" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="13" t="inlineStr">
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="14" t="n"/>
       <c r="S23" s="14" t="n"/>
@@ -2498,6 +2565,8 @@
       <c r="U23" s="14" t="n"/>
       <c r="V23" s="14" t="n"/>
       <c r="W23" s="14" t="n"/>
+      <c r="X23" s="14" t="n"/>
+      <c r="Y23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2535,13 +2604,13 @@
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="14" t="n"/>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
       <c r="P24" s="14" t="n"/>
@@ -2552,6 +2621,8 @@
       <c r="U24" s="14" t="n"/>
       <c r="V24" s="14" t="n"/>
       <c r="W24" s="14" t="n"/>
+      <c r="X24" s="14" t="n"/>
+      <c r="Y24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2589,13 +2660,13 @@
       <c r="H25" s="14" t="n"/>
       <c r="I25" s="14" t="n"/>
       <c r="J25" s="14" t="n"/>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="14" t="n"/>
       <c r="N25" s="14" t="n"/>
       <c r="O25" s="14" t="n"/>
       <c r="P25" s="14" t="n"/>
@@ -2606,6 +2677,8 @@
       <c r="U25" s="14" t="n"/>
       <c r="V25" s="14" t="n"/>
       <c r="W25" s="14" t="n"/>
+      <c r="X25" s="14" t="n"/>
+      <c r="Y25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2647,24 +2720,24 @@
       </c>
       <c r="I26" s="14" t="n"/>
       <c r="J26" s="14" t="n"/>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="N26" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M26" s="14" t="n"/>
-      <c r="N26" s="13" t="inlineStr">
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O26" s="14" t="n"/>
-      <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="14" t="n"/>
@@ -2672,6 +2745,8 @@
       <c r="U26" s="14" t="n"/>
       <c r="V26" s="14" t="n"/>
       <c r="W26" s="14" t="n"/>
+      <c r="X26" s="14" t="n"/>
+      <c r="Y26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2709,13 +2784,13 @@
       <c r="H27" s="14" t="n"/>
       <c r="I27" s="14" t="n"/>
       <c r="J27" s="14" t="n"/>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L27" s="14" t="n"/>
-      <c r="M27" s="14" t="n"/>
       <c r="N27" s="14" t="n"/>
       <c r="O27" s="14" t="n"/>
       <c r="P27" s="14" t="n"/>
@@ -2726,6 +2801,8 @@
       <c r="U27" s="14" t="n"/>
       <c r="V27" s="14" t="n"/>
       <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14" t="n"/>
+      <c r="Y27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2763,13 +2840,13 @@
       <c r="H28" s="14" t="n"/>
       <c r="I28" s="14" t="n"/>
       <c r="J28" s="14" t="n"/>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L28" s="14" t="n"/>
-      <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
       <c r="P28" s="14" t="n"/>
@@ -2780,6 +2857,8 @@
       <c r="U28" s="14" t="n"/>
       <c r="V28" s="14" t="n"/>
       <c r="W28" s="14" t="n"/>
+      <c r="X28" s="14" t="n"/>
+      <c r="Y28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2817,24 +2896,24 @@
       <c r="H29" s="14" t="n"/>
       <c r="I29" s="14" t="n"/>
       <c r="J29" s="14" t="n"/>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L29" s="13" t="inlineStr">
+      <c r="N29" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="13" t="inlineStr">
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
       <c r="Q29" s="14" t="n"/>
       <c r="R29" s="14" t="n"/>
       <c r="S29" s="14" t="n"/>
@@ -2842,6 +2921,8 @@
       <c r="U29" s="14" t="n"/>
       <c r="V29" s="14" t="n"/>
       <c r="W29" s="14" t="n"/>
+      <c r="X29" s="14" t="n"/>
+      <c r="Y29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -2879,13 +2960,13 @@
       <c r="H30" s="14" t="n"/>
       <c r="I30" s="14" t="n"/>
       <c r="J30" s="14" t="n"/>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L30" s="14" t="n"/>
-      <c r="M30" s="14" t="n"/>
       <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
       <c r="P30" s="14" t="n"/>
@@ -2896,6 +2977,8 @@
       <c r="U30" s="14" t="n"/>
       <c r="V30" s="14" t="n"/>
       <c r="W30" s="14" t="n"/>
+      <c r="X30" s="14" t="n"/>
+      <c r="Y30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -2933,24 +3016,24 @@
       <c r="H31" s="14" t="n"/>
       <c r="I31" s="14" t="n"/>
       <c r="J31" s="14" t="n"/>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L31" s="13" t="inlineStr">
+      <c r="N31" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M31" s="14" t="n"/>
-      <c r="N31" s="13" t="inlineStr">
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="14" t="n"/>
       <c r="Q31" s="14" t="n"/>
       <c r="R31" s="14" t="n"/>
       <c r="S31" s="14" t="n"/>
@@ -2958,6 +3041,8 @@
       <c r="U31" s="14" t="n"/>
       <c r="V31" s="14" t="n"/>
       <c r="W31" s="14" t="n"/>
+      <c r="X31" s="14" t="n"/>
+      <c r="Y31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -2995,24 +3080,24 @@
       <c r="H32" s="14" t="n"/>
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="14" t="n"/>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="N32" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M32" s="14" t="n"/>
-      <c r="N32" s="13" t="inlineStr">
+      <c r="O32" s="14" t="n"/>
+      <c r="P32" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14" t="n"/>
       <c r="S32" s="14" t="n"/>
@@ -3020,6 +3105,8 @@
       <c r="U32" s="14" t="n"/>
       <c r="V32" s="14" t="n"/>
       <c r="W32" s="14" t="n"/>
+      <c r="X32" s="14" t="n"/>
+      <c r="Y32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -3061,13 +3148,13 @@
       </c>
       <c r="I33" s="14" t="n"/>
       <c r="J33" s="14" t="n"/>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="14" t="n"/>
       <c r="N33" s="14" t="n"/>
       <c r="O33" s="14" t="n"/>
       <c r="P33" s="14" t="n"/>
@@ -3078,6 +3165,8 @@
       <c r="U33" s="14" t="n"/>
       <c r="V33" s="14" t="n"/>
       <c r="W33" s="14" t="n"/>
+      <c r="X33" s="14" t="n"/>
+      <c r="Y33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3115,24 +3204,24 @@
       <c r="H34" s="14" t="n"/>
       <c r="I34" s="14" t="n"/>
       <c r="J34" s="14" t="n"/>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L34" s="13" t="inlineStr">
+      <c r="N34" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M34" s="14" t="n"/>
-      <c r="N34" s="13" t="inlineStr">
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O34" s="14" t="n"/>
-      <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14" t="n"/>
       <c r="S34" s="14" t="n"/>
@@ -3140,6 +3229,8 @@
       <c r="U34" s="14" t="n"/>
       <c r="V34" s="14" t="n"/>
       <c r="W34" s="14" t="n"/>
+      <c r="X34" s="14" t="n"/>
+      <c r="Y34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3177,24 +3268,24 @@
       <c r="H35" s="14" t="n"/>
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="14" t="n"/>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr">
+      <c r="N35" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M35" s="14" t="n"/>
-      <c r="N35" s="13" t="inlineStr">
+      <c r="O35" s="14" t="n"/>
+      <c r="P35" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14" t="n"/>
       <c r="S35" s="14" t="n"/>
@@ -3202,6 +3293,8 @@
       <c r="U35" s="14" t="n"/>
       <c r="V35" s="14" t="n"/>
       <c r="W35" s="14" t="n"/>
+      <c r="X35" s="14" t="n"/>
+      <c r="Y35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3239,13 +3332,13 @@
       <c r="H36" s="14" t="n"/>
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="n"/>
-      <c r="K36" s="13" t="inlineStr">
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
@@ -3256,6 +3349,8 @@
       <c r="U36" s="14" t="n"/>
       <c r="V36" s="14" t="n"/>
       <c r="W36" s="14" t="n"/>
+      <c r="X36" s="14" t="n"/>
+      <c r="Y36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3293,24 +3388,24 @@
       <c r="H37" s="14" t="n"/>
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="14" t="n"/>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L37" s="13" t="inlineStr">
+      <c r="N37" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M37" s="14" t="n"/>
-      <c r="N37" s="13" t="inlineStr">
+      <c r="O37" s="14" t="n"/>
+      <c r="P37" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O37" s="14" t="n"/>
-      <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14" t="n"/>
       <c r="S37" s="14" t="n"/>
@@ -3318,6 +3413,8 @@
       <c r="U37" s="14" t="n"/>
       <c r="V37" s="14" t="n"/>
       <c r="W37" s="14" t="n"/>
+      <c r="X37" s="14" t="n"/>
+      <c r="Y37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3355,13 +3452,13 @@
       <c r="H38" s="14" t="n"/>
       <c r="I38" s="14" t="n"/>
       <c r="J38" s="14" t="n"/>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
@@ -3372,6 +3469,8 @@
       <c r="U38" s="14" t="n"/>
       <c r="V38" s="14" t="n"/>
       <c r="W38" s="14" t="n"/>
+      <c r="X38" s="14" t="n"/>
+      <c r="Y38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3409,13 +3508,13 @@
       <c r="H39" s="14" t="n"/>
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="14" t="n"/>
-      <c r="K39" s="13" t="inlineStr">
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L39" s="14" t="n"/>
-      <c r="M39" s="14" t="n"/>
       <c r="N39" s="14" t="n"/>
       <c r="O39" s="14" t="n"/>
       <c r="P39" s="14" t="n"/>
@@ -3426,6 +3525,8 @@
       <c r="U39" s="14" t="n"/>
       <c r="V39" s="14" t="n"/>
       <c r="W39" s="14" t="n"/>
+      <c r="X39" s="14" t="n"/>
+      <c r="Y39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3463,24 +3564,24 @@
       <c r="H40" s="14" t="n"/>
       <c r="I40" s="14" t="n"/>
       <c r="J40" s="14" t="n"/>
-      <c r="K40" s="13" t="inlineStr">
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L40" s="13" t="inlineStr">
+      <c r="N40" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M40" s="14" t="n"/>
-      <c r="N40" s="13" t="inlineStr">
+      <c r="O40" s="14" t="n"/>
+      <c r="P40" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14" t="n"/>
       <c r="S40" s="14" t="n"/>
@@ -3488,6 +3589,8 @@
       <c r="U40" s="14" t="n"/>
       <c r="V40" s="14" t="n"/>
       <c r="W40" s="14" t="n"/>
+      <c r="X40" s="14" t="n"/>
+      <c r="Y40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3525,13 +3628,13 @@
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="n"/>
       <c r="J41" s="14" t="n"/>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L41" s="14" t="n"/>
-      <c r="M41" s="14" t="n"/>
       <c r="N41" s="14" t="n"/>
       <c r="O41" s="14" t="n"/>
       <c r="P41" s="14" t="n"/>
@@ -3542,6 +3645,8 @@
       <c r="U41" s="14" t="n"/>
       <c r="V41" s="14" t="n"/>
       <c r="W41" s="14" t="n"/>
+      <c r="X41" s="14" t="n"/>
+      <c r="Y41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3575,24 +3680,24 @@
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="14" t="n"/>
-      <c r="K42" s="13" t="inlineStr">
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L42" s="13" t="inlineStr">
+      <c r="N42" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M42" s="14" t="n"/>
-      <c r="N42" s="13" t="inlineStr">
+      <c r="O42" s="14" t="n"/>
+      <c r="P42" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14" t="n"/>
       <c r="S42" s="14" t="n"/>
@@ -3600,6 +3705,8 @@
       <c r="U42" s="14" t="n"/>
       <c r="V42" s="14" t="n"/>
       <c r="W42" s="14" t="n"/>
+      <c r="X42" s="14" t="n"/>
+      <c r="Y42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -3633,13 +3740,13 @@
       <c r="H43" s="14" t="n"/>
       <c r="I43" s="14" t="n"/>
       <c r="J43" s="14" t="n"/>
-      <c r="K43" s="13" t="inlineStr">
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L43" s="14" t="n"/>
-      <c r="M43" s="14" t="n"/>
       <c r="N43" s="14" t="n"/>
       <c r="O43" s="14" t="n"/>
       <c r="P43" s="14" t="n"/>
@@ -3650,6 +3757,8 @@
       <c r="U43" s="14" t="n"/>
       <c r="V43" s="14" t="n"/>
       <c r="W43" s="14" t="n"/>
+      <c r="X43" s="14" t="n"/>
+      <c r="Y43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -3691,24 +3800,24 @@
       </c>
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="14" t="n"/>
-      <c r="K44" s="13" t="inlineStr">
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L44" s="13" t="inlineStr">
+      <c r="N44" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M44" s="14" t="n"/>
-      <c r="N44" s="13" t="inlineStr">
+      <c r="O44" s="14" t="n"/>
+      <c r="P44" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O44" s="14" t="n"/>
-      <c r="P44" s="14" t="n"/>
       <c r="Q44" s="14" t="n"/>
       <c r="R44" s="14" t="n"/>
       <c r="S44" s="14" t="n"/>
@@ -3716,6 +3825,8 @@
       <c r="U44" s="14" t="n"/>
       <c r="V44" s="14" t="n"/>
       <c r="W44" s="14" t="n"/>
+      <c r="X44" s="14" t="n"/>
+      <c r="Y44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -3753,13 +3864,13 @@
       <c r="H45" s="14" t="n"/>
       <c r="I45" s="14" t="n"/>
       <c r="J45" s="14" t="n"/>
-      <c r="K45" s="13" t="inlineStr">
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L45" s="14" t="n"/>
-      <c r="M45" s="14" t="n"/>
       <c r="N45" s="14" t="n"/>
       <c r="O45" s="14" t="n"/>
       <c r="P45" s="14" t="n"/>
@@ -3770,6 +3881,8 @@
       <c r="U45" s="14" t="n"/>
       <c r="V45" s="14" t="n"/>
       <c r="W45" s="14" t="n"/>
+      <c r="X45" s="14" t="n"/>
+      <c r="Y45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -3807,24 +3920,24 @@
       <c r="H46" s="14" t="n"/>
       <c r="I46" s="14" t="n"/>
       <c r="J46" s="14" t="n"/>
-      <c r="K46" s="13" t="inlineStr">
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L46" s="13" t="inlineStr">
+      <c r="N46" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M46" s="14" t="n"/>
-      <c r="N46" s="13" t="inlineStr">
+      <c r="O46" s="14" t="n"/>
+      <c r="P46" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O46" s="14" t="n"/>
-      <c r="P46" s="14" t="n"/>
       <c r="Q46" s="14" t="n"/>
       <c r="R46" s="14" t="n"/>
       <c r="S46" s="14" t="n"/>
@@ -3832,6 +3945,8 @@
       <c r="U46" s="14" t="n"/>
       <c r="V46" s="14" t="n"/>
       <c r="W46" s="14" t="n"/>
+      <c r="X46" s="14" t="n"/>
+      <c r="Y46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -3869,13 +3984,13 @@
       <c r="H47" s="14" t="n"/>
       <c r="I47" s="14" t="n"/>
       <c r="J47" s="14" t="n"/>
-      <c r="K47" s="13" t="inlineStr">
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n"/>
+      <c r="M47" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L47" s="14" t="n"/>
-      <c r="M47" s="14" t="n"/>
       <c r="N47" s="14" t="n"/>
       <c r="O47" s="14" t="n"/>
       <c r="P47" s="14" t="n"/>
@@ -3886,6 +4001,8 @@
       <c r="U47" s="14" t="n"/>
       <c r="V47" s="14" t="n"/>
       <c r="W47" s="14" t="n"/>
+      <c r="X47" s="14" t="n"/>
+      <c r="Y47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -3923,24 +4040,24 @@
       <c r="H48" s="14" t="n"/>
       <c r="I48" s="14" t="n"/>
       <c r="J48" s="14" t="n"/>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L48" s="13" t="inlineStr">
+      <c r="N48" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M48" s="14" t="n"/>
-      <c r="N48" s="13" t="inlineStr">
+      <c r="O48" s="14" t="n"/>
+      <c r="P48" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O48" s="14" t="n"/>
-      <c r="P48" s="14" t="n"/>
       <c r="Q48" s="14" t="n"/>
       <c r="R48" s="14" t="n"/>
       <c r="S48" s="14" t="n"/>
@@ -3948,6 +4065,8 @@
       <c r="U48" s="14" t="n"/>
       <c r="V48" s="14" t="n"/>
       <c r="W48" s="14" t="n"/>
+      <c r="X48" s="14" t="n"/>
+      <c r="Y48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -3985,13 +4104,13 @@
       <c r="H49" s="14" t="n"/>
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="14" t="n"/>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="14" t="n"/>
+      <c r="M49" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L49" s="14" t="n"/>
-      <c r="M49" s="14" t="n"/>
       <c r="N49" s="14" t="n"/>
       <c r="O49" s="14" t="n"/>
       <c r="P49" s="14" t="n"/>
@@ -4002,6 +4121,8 @@
       <c r="U49" s="14" t="n"/>
       <c r="V49" s="14" t="n"/>
       <c r="W49" s="14" t="n"/>
+      <c r="X49" s="14" t="n"/>
+      <c r="Y49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -4039,13 +4160,13 @@
       <c r="H50" s="14" t="n"/>
       <c r="I50" s="14" t="n"/>
       <c r="J50" s="14" t="n"/>
-      <c r="K50" s="13" t="inlineStr">
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="14" t="n"/>
+      <c r="M50" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L50" s="14" t="n"/>
-      <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
       <c r="P50" s="14" t="n"/>
@@ -4056,6 +4177,8 @@
       <c r="U50" s="14" t="n"/>
       <c r="V50" s="14" t="n"/>
       <c r="W50" s="14" t="n"/>
+      <c r="X50" s="14" t="n"/>
+      <c r="Y50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4093,13 +4216,13 @@
       <c r="H51" s="14" t="n"/>
       <c r="I51" s="14" t="n"/>
       <c r="J51" s="14" t="n"/>
-      <c r="K51" s="13" t="inlineStr">
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L51" s="14" t="n"/>
-      <c r="M51" s="14" t="n"/>
       <c r="N51" s="14" t="n"/>
       <c r="O51" s="14" t="n"/>
       <c r="P51" s="14" t="n"/>
@@ -4110,6 +4233,8 @@
       <c r="U51" s="14" t="n"/>
       <c r="V51" s="14" t="n"/>
       <c r="W51" s="14" t="n"/>
+      <c r="X51" s="14" t="n"/>
+      <c r="Y51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -4143,13 +4268,13 @@
       <c r="H52" s="14" t="n"/>
       <c r="I52" s="14" t="n"/>
       <c r="J52" s="14" t="n"/>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="K52" s="14" t="n"/>
+      <c r="L52" s="14" t="n"/>
+      <c r="M52" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L52" s="14" t="n"/>
-      <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
       <c r="P52" s="14" t="n"/>
@@ -4160,6 +4285,8 @@
       <c r="U52" s="14" t="n"/>
       <c r="V52" s="14" t="n"/>
       <c r="W52" s="14" t="n"/>
+      <c r="X52" s="14" t="n"/>
+      <c r="Y52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4197,13 +4324,13 @@
       <c r="H53" s="14" t="n"/>
       <c r="I53" s="14" t="n"/>
       <c r="J53" s="14" t="n"/>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="K53" s="14" t="n"/>
+      <c r="L53" s="14" t="n"/>
+      <c r="M53" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L53" s="14" t="n"/>
-      <c r="M53" s="14" t="n"/>
       <c r="N53" s="14" t="n"/>
       <c r="O53" s="14" t="n"/>
       <c r="P53" s="14" t="n"/>
@@ -4214,6 +4341,8 @@
       <c r="U53" s="14" t="n"/>
       <c r="V53" s="14" t="n"/>
       <c r="W53" s="14" t="n"/>
+      <c r="X53" s="14" t="n"/>
+      <c r="Y53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -4251,13 +4380,13 @@
       <c r="H54" s="14" t="n"/>
       <c r="I54" s="14" t="n"/>
       <c r="J54" s="14" t="n"/>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K54" s="14" t="n"/>
+      <c r="L54" s="14" t="n"/>
+      <c r="M54" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L54" s="14" t="n"/>
-      <c r="M54" s="14" t="n"/>
       <c r="N54" s="14" t="n"/>
       <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
@@ -4268,6 +4397,8 @@
       <c r="U54" s="14" t="n"/>
       <c r="V54" s="14" t="n"/>
       <c r="W54" s="14" t="n"/>
+      <c r="X54" s="14" t="n"/>
+      <c r="Y54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -4305,24 +4436,24 @@
       <c r="H55" s="14" t="n"/>
       <c r="I55" s="14" t="n"/>
       <c r="J55" s="14" t="n"/>
-      <c r="K55" s="13" t="inlineStr">
+      <c r="K55" s="14" t="n"/>
+      <c r="L55" s="14" t="n"/>
+      <c r="M55" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L55" s="13" t="inlineStr">
+      <c r="N55" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M55" s="14" t="n"/>
-      <c r="N55" s="13" t="inlineStr">
+      <c r="O55" s="14" t="n"/>
+      <c r="P55" s="13" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
       </c>
-      <c r="O55" s="14" t="n"/>
-      <c r="P55" s="14" t="n"/>
       <c r="Q55" s="14" t="n"/>
       <c r="R55" s="14" t="n"/>
       <c r="S55" s="14" t="n"/>
@@ -4330,6 +4461,8 @@
       <c r="U55" s="14" t="n"/>
       <c r="V55" s="14" t="n"/>
       <c r="W55" s="14" t="n"/>
+      <c r="X55" s="14" t="n"/>
+      <c r="Y55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -4367,13 +4500,13 @@
       <c r="H56" s="14" t="n"/>
       <c r="I56" s="14" t="n"/>
       <c r="J56" s="14" t="n"/>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="K56" s="14" t="n"/>
+      <c r="L56" s="14" t="n"/>
+      <c r="M56" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L56" s="14" t="n"/>
-      <c r="M56" s="14" t="n"/>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
@@ -4384,6 +4517,8 @@
       <c r="U56" s="14" t="n"/>
       <c r="V56" s="14" t="n"/>
       <c r="W56" s="14" t="n"/>
+      <c r="X56" s="14" t="n"/>
+      <c r="Y56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -4434,6 +4569,8 @@
       <c r="U57" s="14" t="n"/>
       <c r="V57" s="14" t="n"/>
       <c r="W57" s="14" t="n"/>
+      <c r="X57" s="14" t="n"/>
+      <c r="Y57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -4471,13 +4608,13 @@
       <c r="H58" s="14" t="n"/>
       <c r="I58" s="14" t="n"/>
       <c r="J58" s="14" t="n"/>
-      <c r="K58" s="13" t="inlineStr">
+      <c r="K58" s="14" t="n"/>
+      <c r="L58" s="14" t="n"/>
+      <c r="M58" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L58" s="14" t="n"/>
-      <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
@@ -4488,6 +4625,8 @@
       <c r="U58" s="14" t="n"/>
       <c r="V58" s="14" t="n"/>
       <c r="W58" s="14" t="n"/>
+      <c r="X58" s="14" t="n"/>
+      <c r="Y58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -4525,13 +4664,13 @@
       <c r="H59" s="14" t="n"/>
       <c r="I59" s="14" t="n"/>
       <c r="J59" s="14" t="n"/>
-      <c r="K59" s="13" t="inlineStr">
+      <c r="K59" s="14" t="n"/>
+      <c r="L59" s="14" t="n"/>
+      <c r="M59" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L59" s="14" t="n"/>
-      <c r="M59" s="14" t="n"/>
       <c r="N59" s="14" t="n"/>
       <c r="O59" s="14" t="n"/>
       <c r="P59" s="14" t="n"/>
@@ -4542,6 +4681,8 @@
       <c r="U59" s="14" t="n"/>
       <c r="V59" s="14" t="n"/>
       <c r="W59" s="14" t="n"/>
+      <c r="X59" s="14" t="n"/>
+      <c r="Y59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -4579,13 +4720,13 @@
       <c r="H60" s="14" t="n"/>
       <c r="I60" s="14" t="n"/>
       <c r="J60" s="14" t="n"/>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="K60" s="14" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L60" s="14" t="n"/>
-      <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
@@ -4596,6 +4737,8 @@
       <c r="U60" s="14" t="n"/>
       <c r="V60" s="14" t="n"/>
       <c r="W60" s="14" t="n"/>
+      <c r="X60" s="14" t="n"/>
+      <c r="Y60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -4633,13 +4776,13 @@
       <c r="H61" s="14" t="n"/>
       <c r="I61" s="14" t="n"/>
       <c r="J61" s="14" t="n"/>
-      <c r="K61" s="13" t="inlineStr">
+      <c r="K61" s="14" t="n"/>
+      <c r="L61" s="14" t="n"/>
+      <c r="M61" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L61" s="14" t="n"/>
-      <c r="M61" s="14" t="n"/>
       <c r="N61" s="14" t="n"/>
       <c r="O61" s="14" t="n"/>
       <c r="P61" s="14" t="n"/>
@@ -4650,6 +4793,8 @@
       <c r="U61" s="14" t="n"/>
       <c r="V61" s="14" t="n"/>
       <c r="W61" s="14" t="n"/>
+      <c r="X61" s="14" t="n"/>
+      <c r="Y61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -4700,6 +4845,8 @@
       <c r="U62" s="14" t="n"/>
       <c r="V62" s="14" t="n"/>
       <c r="W62" s="14" t="n"/>
+      <c r="X62" s="14" t="n"/>
+      <c r="Y62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -4737,13 +4884,13 @@
       <c r="H63" s="14" t="n"/>
       <c r="I63" s="14" t="n"/>
       <c r="J63" s="14" t="n"/>
-      <c r="K63" s="13" t="inlineStr">
+      <c r="K63" s="14" t="n"/>
+      <c r="L63" s="14" t="n"/>
+      <c r="M63" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="n"/>
       <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n"/>
       <c r="P63" s="14" t="n"/>
@@ -4754,6 +4901,8 @@
       <c r="U63" s="14" t="n"/>
       <c r="V63" s="14" t="n"/>
       <c r="W63" s="14" t="n"/>
+      <c r="X63" s="14" t="n"/>
+      <c r="Y63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -4791,13 +4940,13 @@
       <c r="H64" s="14" t="n"/>
       <c r="I64" s="14" t="n"/>
       <c r="J64" s="14" t="n"/>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="K64" s="14" t="n"/>
+      <c r="L64" s="14" t="n"/>
+      <c r="M64" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L64" s="14" t="n"/>
-      <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
       <c r="O64" s="14" t="n"/>
       <c r="P64" s="14" t="n"/>
@@ -4808,6 +4957,8 @@
       <c r="U64" s="14" t="n"/>
       <c r="V64" s="14" t="n"/>
       <c r="W64" s="14" t="n"/>
+      <c r="X64" s="14" t="n"/>
+      <c r="Y64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -4845,13 +4996,13 @@
       <c r="H65" s="14" t="n"/>
       <c r="I65" s="14" t="n"/>
       <c r="J65" s="14" t="n"/>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="K65" s="14" t="n"/>
+      <c r="L65" s="14" t="n"/>
+      <c r="M65" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L65" s="14" t="n"/>
-      <c r="M65" s="14" t="n"/>
       <c r="N65" s="14" t="n"/>
       <c r="O65" s="14" t="n"/>
       <c r="P65" s="14" t="n"/>
@@ -4862,6 +5013,8 @@
       <c r="U65" s="14" t="n"/>
       <c r="V65" s="14" t="n"/>
       <c r="W65" s="14" t="n"/>
+      <c r="X65" s="14" t="n"/>
+      <c r="Y65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -4899,13 +5052,13 @@
       <c r="H66" s="14" t="n"/>
       <c r="I66" s="14" t="n"/>
       <c r="J66" s="14" t="n"/>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L66" s="14" t="n"/>
-      <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
@@ -4916,6 +5069,8 @@
       <c r="U66" s="14" t="n"/>
       <c r="V66" s="14" t="n"/>
       <c r="W66" s="14" t="n"/>
+      <c r="X66" s="14" t="n"/>
+      <c r="Y66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -4953,13 +5108,13 @@
       <c r="H67" s="14" t="n"/>
       <c r="I67" s="14" t="n"/>
       <c r="J67" s="14" t="n"/>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K67" s="14" t="n"/>
+      <c r="L67" s="14" t="n"/>
+      <c r="M67" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L67" s="14" t="n"/>
-      <c r="M67" s="14" t="n"/>
       <c r="N67" s="14" t="n"/>
       <c r="O67" s="14" t="n"/>
       <c r="P67" s="14" t="n"/>
@@ -4970,6 +5125,8 @@
       <c r="U67" s="14" t="n"/>
       <c r="V67" s="14" t="n"/>
       <c r="W67" s="14" t="n"/>
+      <c r="X67" s="14" t="n"/>
+      <c r="Y67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -5007,13 +5164,13 @@
       <c r="H68" s="14" t="n"/>
       <c r="I68" s="14" t="n"/>
       <c r="J68" s="14" t="n"/>
-      <c r="K68" s="13" t="inlineStr">
+      <c r="K68" s="14" t="n"/>
+      <c r="L68" s="14" t="n"/>
+      <c r="M68" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L68" s="14" t="n"/>
-      <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
       <c r="P68" s="14" t="n"/>
@@ -5024,6 +5181,8 @@
       <c r="U68" s="14" t="n"/>
       <c r="V68" s="14" t="n"/>
       <c r="W68" s="14" t="n"/>
+      <c r="X68" s="14" t="n"/>
+      <c r="Y68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -5061,13 +5220,13 @@
       <c r="H69" s="14" t="n"/>
       <c r="I69" s="14" t="n"/>
       <c r="J69" s="14" t="n"/>
-      <c r="K69" s="13" t="inlineStr">
+      <c r="K69" s="14" t="n"/>
+      <c r="L69" s="14" t="n"/>
+      <c r="M69" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L69" s="14" t="n"/>
-      <c r="M69" s="14" t="n"/>
       <c r="N69" s="14" t="n"/>
       <c r="O69" s="14" t="n"/>
       <c r="P69" s="14" t="n"/>
@@ -5078,6 +5237,8 @@
       <c r="U69" s="14" t="n"/>
       <c r="V69" s="14" t="n"/>
       <c r="W69" s="14" t="n"/>
+      <c r="X69" s="14" t="n"/>
+      <c r="Y69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -5115,13 +5276,13 @@
       <c r="H70" s="14" t="n"/>
       <c r="I70" s="14" t="n"/>
       <c r="J70" s="14" t="n"/>
-      <c r="K70" s="13" t="inlineStr">
+      <c r="K70" s="14" t="n"/>
+      <c r="L70" s="14" t="n"/>
+      <c r="M70" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L70" s="14" t="n"/>
-      <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
@@ -5132,6 +5293,8 @@
       <c r="U70" s="14" t="n"/>
       <c r="V70" s="14" t="n"/>
       <c r="W70" s="14" t="n"/>
+      <c r="X70" s="14" t="n"/>
+      <c r="Y70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -5182,6 +5345,8 @@
       <c r="U71" s="14" t="n"/>
       <c r="V71" s="14" t="n"/>
       <c r="W71" s="14" t="n"/>
+      <c r="X71" s="14" t="n"/>
+      <c r="Y71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -5219,13 +5384,13 @@
       <c r="H72" s="14" t="n"/>
       <c r="I72" s="14" t="n"/>
       <c r="J72" s="14" t="n"/>
-      <c r="K72" s="13" t="inlineStr">
+      <c r="K72" s="14" t="n"/>
+      <c r="L72" s="14" t="n"/>
+      <c r="M72" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L72" s="14" t="n"/>
-      <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
       <c r="O72" s="14" t="n"/>
       <c r="P72" s="14" t="n"/>
@@ -5236,6 +5401,8 @@
       <c r="U72" s="14" t="n"/>
       <c r="V72" s="14" t="n"/>
       <c r="W72" s="14" t="n"/>
+      <c r="X72" s="14" t="n"/>
+      <c r="Y72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -5273,13 +5440,13 @@
       <c r="H73" s="14" t="n"/>
       <c r="I73" s="14" t="n"/>
       <c r="J73" s="14" t="n"/>
-      <c r="K73" s="13" t="inlineStr">
+      <c r="K73" s="14" t="n"/>
+      <c r="L73" s="14" t="n"/>
+      <c r="M73" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L73" s="14" t="n"/>
-      <c r="M73" s="14" t="n"/>
       <c r="N73" s="14" t="n"/>
       <c r="O73" s="14" t="n"/>
       <c r="P73" s="14" t="n"/>
@@ -5290,6 +5457,8 @@
       <c r="U73" s="14" t="n"/>
       <c r="V73" s="14" t="n"/>
       <c r="W73" s="14" t="n"/>
+      <c r="X73" s="14" t="n"/>
+      <c r="Y73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -5327,24 +5496,24 @@
       <c r="H74" s="14" t="n"/>
       <c r="I74" s="14" t="n"/>
       <c r="J74" s="14" t="n"/>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K74" s="14" t="n"/>
+      <c r="L74" s="14" t="n"/>
+      <c r="M74" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L74" s="13" t="inlineStr">
+      <c r="N74" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M74" s="14" t="n"/>
-      <c r="N74" s="13" t="inlineStr">
+      <c r="O74" s="14" t="n"/>
+      <c r="P74" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O74" s="14" t="n"/>
-      <c r="P74" s="14" t="n"/>
       <c r="Q74" s="14" t="n"/>
       <c r="R74" s="14" t="n"/>
       <c r="S74" s="14" t="n"/>
@@ -5352,6 +5521,8 @@
       <c r="U74" s="14" t="n"/>
       <c r="V74" s="14" t="n"/>
       <c r="W74" s="14" t="n"/>
+      <c r="X74" s="14" t="n"/>
+      <c r="Y74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -5385,24 +5556,24 @@
       <c r="H75" s="14" t="n"/>
       <c r="I75" s="14" t="n"/>
       <c r="J75" s="14" t="n"/>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K75" s="14" t="n"/>
+      <c r="L75" s="14" t="n"/>
+      <c r="M75" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L75" s="13" t="inlineStr">
+      <c r="N75" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M75" s="14" t="n"/>
-      <c r="N75" s="13" t="inlineStr">
+      <c r="O75" s="14" t="n"/>
+      <c r="P75" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O75" s="14" t="n"/>
-      <c r="P75" s="14" t="n"/>
       <c r="Q75" s="14" t="n"/>
       <c r="R75" s="14" t="n"/>
       <c r="S75" s="14" t="n"/>
@@ -5410,6 +5581,8 @@
       <c r="U75" s="14" t="n"/>
       <c r="V75" s="14" t="n"/>
       <c r="W75" s="14" t="n"/>
+      <c r="X75" s="14" t="n"/>
+      <c r="Y75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -5447,24 +5620,24 @@
       <c r="H76" s="14" t="n"/>
       <c r="I76" s="14" t="n"/>
       <c r="J76" s="14" t="n"/>
-      <c r="K76" s="13" t="inlineStr">
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L76" s="13" t="inlineStr">
+      <c r="N76" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M76" s="14" t="n"/>
-      <c r="N76" s="13" t="inlineStr">
+      <c r="O76" s="14" t="n"/>
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O76" s="14" t="n"/>
-      <c r="P76" s="14" t="n"/>
       <c r="Q76" s="14" t="n"/>
       <c r="R76" s="14" t="n"/>
       <c r="S76" s="14" t="n"/>
@@ -5472,6 +5645,8 @@
       <c r="U76" s="14" t="n"/>
       <c r="V76" s="14" t="n"/>
       <c r="W76" s="14" t="n"/>
+      <c r="X76" s="14" t="n"/>
+      <c r="Y76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -5505,24 +5680,24 @@
       <c r="H77" s="14" t="n"/>
       <c r="I77" s="14" t="n"/>
       <c r="J77" s="14" t="n"/>
-      <c r="K77" s="13" t="inlineStr">
+      <c r="K77" s="14" t="n"/>
+      <c r="L77" s="14" t="n"/>
+      <c r="M77" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L77" s="13" t="inlineStr">
+      <c r="N77" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M77" s="14" t="n"/>
-      <c r="N77" s="13" t="inlineStr">
+      <c r="O77" s="14" t="n"/>
+      <c r="P77" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O77" s="14" t="n"/>
-      <c r="P77" s="14" t="n"/>
       <c r="Q77" s="14" t="n"/>
       <c r="R77" s="14" t="n"/>
       <c r="S77" s="14" t="n"/>
@@ -5530,6 +5705,8 @@
       <c r="U77" s="14" t="n"/>
       <c r="V77" s="14" t="n"/>
       <c r="W77" s="14" t="n"/>
+      <c r="X77" s="14" t="n"/>
+      <c r="Y77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -5567,13 +5744,13 @@
       <c r="H78" s="14" t="n"/>
       <c r="I78" s="14" t="n"/>
       <c r="J78" s="14" t="n"/>
-      <c r="K78" s="13" t="inlineStr">
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L78" s="14" t="n"/>
-      <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
       <c r="P78" s="14" t="n"/>
@@ -5584,6 +5761,8 @@
       <c r="U78" s="14" t="n"/>
       <c r="V78" s="14" t="n"/>
       <c r="W78" s="14" t="n"/>
+      <c r="X78" s="14" t="n"/>
+      <c r="Y78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -5621,13 +5800,13 @@
       <c r="H79" s="14" t="n"/>
       <c r="I79" s="14" t="n"/>
       <c r="J79" s="14" t="n"/>
-      <c r="K79" s="13" t="inlineStr">
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L79" s="14" t="n"/>
-      <c r="M79" s="14" t="n"/>
       <c r="N79" s="14" t="n"/>
       <c r="O79" s="14" t="n"/>
       <c r="P79" s="14" t="n"/>
@@ -5638,6 +5817,8 @@
       <c r="U79" s="14" t="n"/>
       <c r="V79" s="14" t="n"/>
       <c r="W79" s="14" t="n"/>
+      <c r="X79" s="14" t="n"/>
+      <c r="Y79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -5671,24 +5852,24 @@
       <c r="H80" s="14" t="n"/>
       <c r="I80" s="14" t="n"/>
       <c r="J80" s="14" t="n"/>
-      <c r="K80" s="13" t="inlineStr">
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L80" s="13" t="inlineStr">
+      <c r="N80" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M80" s="14" t="n"/>
-      <c r="N80" s="13" t="inlineStr">
+      <c r="O80" s="14" t="n"/>
+      <c r="P80" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O80" s="14" t="n"/>
-      <c r="P80" s="14" t="n"/>
       <c r="Q80" s="14" t="n"/>
       <c r="R80" s="14" t="n"/>
       <c r="S80" s="14" t="n"/>
@@ -5696,6 +5877,8 @@
       <c r="U80" s="14" t="n"/>
       <c r="V80" s="14" t="n"/>
       <c r="W80" s="14" t="n"/>
+      <c r="X80" s="14" t="n"/>
+      <c r="Y80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -5733,24 +5916,24 @@
       <c r="H81" s="14" t="n"/>
       <c r="I81" s="14" t="n"/>
       <c r="J81" s="14" t="n"/>
-      <c r="K81" s="13" t="inlineStr">
+      <c r="K81" s="14" t="n"/>
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L81" s="13" t="inlineStr">
+      <c r="N81" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M81" s="14" t="n"/>
-      <c r="N81" s="13" t="inlineStr">
+      <c r="O81" s="14" t="n"/>
+      <c r="P81" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O81" s="14" t="n"/>
-      <c r="P81" s="14" t="n"/>
       <c r="Q81" s="14" t="n"/>
       <c r="R81" s="14" t="n"/>
       <c r="S81" s="14" t="n"/>
@@ -5758,6 +5941,8 @@
       <c r="U81" s="14" t="n"/>
       <c r="V81" s="14" t="n"/>
       <c r="W81" s="14" t="n"/>
+      <c r="X81" s="14" t="n"/>
+      <c r="Y81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -5791,24 +5976,24 @@
       <c r="H82" s="14" t="n"/>
       <c r="I82" s="14" t="n"/>
       <c r="J82" s="14" t="n"/>
-      <c r="K82" s="13" t="inlineStr">
+      <c r="K82" s="14" t="n"/>
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L82" s="13" t="inlineStr">
+      <c r="N82" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M82" s="14" t="n"/>
-      <c r="N82" s="13" t="inlineStr">
+      <c r="O82" s="14" t="n"/>
+      <c r="P82" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O82" s="14" t="n"/>
-      <c r="P82" s="14" t="n"/>
       <c r="Q82" s="14" t="n"/>
       <c r="R82" s="14" t="n"/>
       <c r="S82" s="14" t="n"/>
@@ -5816,6 +6001,8 @@
       <c r="U82" s="14" t="n"/>
       <c r="V82" s="14" t="n"/>
       <c r="W82" s="14" t="n"/>
+      <c r="X82" s="14" t="n"/>
+      <c r="Y82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -5853,24 +6040,24 @@
       <c r="H83" s="14" t="n"/>
       <c r="I83" s="14" t="n"/>
       <c r="J83" s="14" t="n"/>
-      <c r="K83" s="13" t="inlineStr">
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L83" s="13" t="inlineStr">
+      <c r="N83" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M83" s="14" t="n"/>
-      <c r="N83" s="13" t="inlineStr">
+      <c r="O83" s="14" t="n"/>
+      <c r="P83" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O83" s="14" t="n"/>
-      <c r="P83" s="14" t="n"/>
       <c r="Q83" s="14" t="n"/>
       <c r="R83" s="14" t="n"/>
       <c r="S83" s="14" t="n"/>
@@ -5878,6 +6065,8 @@
       <c r="U83" s="14" t="n"/>
       <c r="V83" s="14" t="n"/>
       <c r="W83" s="14" t="n"/>
+      <c r="X83" s="14" t="n"/>
+      <c r="Y83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -5915,13 +6104,13 @@
       <c r="H84" s="14" t="n"/>
       <c r="I84" s="14" t="n"/>
       <c r="J84" s="14" t="n"/>
-      <c r="K84" s="13" t="inlineStr">
+      <c r="K84" s="14" t="n"/>
+      <c r="L84" s="14" t="n"/>
+      <c r="M84" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L84" s="14" t="n"/>
-      <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
       <c r="P84" s="14" t="n"/>
@@ -5932,6 +6121,8 @@
       <c r="U84" s="14" t="n"/>
       <c r="V84" s="14" t="n"/>
       <c r="W84" s="14" t="n"/>
+      <c r="X84" s="14" t="n"/>
+      <c r="Y84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -5969,13 +6160,13 @@
       <c r="H85" s="14" t="n"/>
       <c r="I85" s="14" t="n"/>
       <c r="J85" s="14" t="n"/>
-      <c r="K85" s="13" t="inlineStr">
+      <c r="K85" s="14" t="n"/>
+      <c r="L85" s="14" t="n"/>
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L85" s="14" t="n"/>
-      <c r="M85" s="14" t="n"/>
       <c r="N85" s="14" t="n"/>
       <c r="O85" s="14" t="n"/>
       <c r="P85" s="14" t="n"/>
@@ -5986,6 +6177,8 @@
       <c r="U85" s="14" t="n"/>
       <c r="V85" s="14" t="n"/>
       <c r="W85" s="14" t="n"/>
+      <c r="X85" s="14" t="n"/>
+      <c r="Y85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -6023,13 +6216,13 @@
       <c r="H86" s="14" t="n"/>
       <c r="I86" s="14" t="n"/>
       <c r="J86" s="14" t="n"/>
-      <c r="K86" s="13" t="inlineStr">
+      <c r="K86" s="14" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L86" s="14" t="n"/>
-      <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
       <c r="O86" s="14" t="n"/>
       <c r="P86" s="14" t="n"/>
@@ -6040,6 +6233,8 @@
       <c r="U86" s="14" t="n"/>
       <c r="V86" s="14" t="n"/>
       <c r="W86" s="14" t="n"/>
+      <c r="X86" s="14" t="n"/>
+      <c r="Y86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -6073,13 +6268,13 @@
       <c r="H87" s="14" t="n"/>
       <c r="I87" s="14" t="n"/>
       <c r="J87" s="14" t="n"/>
-      <c r="K87" s="13" t="inlineStr">
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L87" s="14" t="n"/>
-      <c r="M87" s="14" t="n"/>
       <c r="N87" s="14" t="n"/>
       <c r="O87" s="14" t="n"/>
       <c r="P87" s="14" t="n"/>
@@ -6090,6 +6285,8 @@
       <c r="U87" s="14" t="n"/>
       <c r="V87" s="14" t="n"/>
       <c r="W87" s="14" t="n"/>
+      <c r="X87" s="14" t="n"/>
+      <c r="Y87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -6127,13 +6324,13 @@
       <c r="H88" s="14" t="n"/>
       <c r="I88" s="14" t="n"/>
       <c r="J88" s="14" t="n"/>
-      <c r="K88" s="13" t="inlineStr">
+      <c r="K88" s="14" t="n"/>
+      <c r="L88" s="14" t="n"/>
+      <c r="M88" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L88" s="14" t="n"/>
-      <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
       <c r="O88" s="14" t="n"/>
       <c r="P88" s="14" t="n"/>
@@ -6144,6 +6341,8 @@
       <c r="U88" s="14" t="n"/>
       <c r="V88" s="14" t="n"/>
       <c r="W88" s="14" t="n"/>
+      <c r="X88" s="14" t="n"/>
+      <c r="Y88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -6177,13 +6376,13 @@
       <c r="H89" s="14" t="n"/>
       <c r="I89" s="14" t="n"/>
       <c r="J89" s="14" t="n"/>
-      <c r="K89" s="13" t="inlineStr">
+      <c r="K89" s="14" t="n"/>
+      <c r="L89" s="14" t="n"/>
+      <c r="M89" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L89" s="14" t="n"/>
-      <c r="M89" s="14" t="n"/>
       <c r="N89" s="14" t="n"/>
       <c r="O89" s="14" t="n"/>
       <c r="P89" s="14" t="n"/>
@@ -6194,6 +6393,8 @@
       <c r="U89" s="14" t="n"/>
       <c r="V89" s="14" t="n"/>
       <c r="W89" s="14" t="n"/>
+      <c r="X89" s="14" t="n"/>
+      <c r="Y89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -6231,13 +6432,13 @@
       <c r="H90" s="14" t="n"/>
       <c r="I90" s="14" t="n"/>
       <c r="J90" s="14" t="n"/>
-      <c r="K90" s="13" t="inlineStr">
+      <c r="K90" s="14" t="n"/>
+      <c r="L90" s="14" t="n"/>
+      <c r="M90" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L90" s="14" t="n"/>
-      <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n"/>
       <c r="P90" s="14" t="n"/>
@@ -6248,6 +6449,8 @@
       <c r="U90" s="14" t="n"/>
       <c r="V90" s="14" t="n"/>
       <c r="W90" s="14" t="n"/>
+      <c r="X90" s="14" t="n"/>
+      <c r="Y90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -6285,13 +6488,13 @@
       <c r="H91" s="14" t="n"/>
       <c r="I91" s="14" t="n"/>
       <c r="J91" s="14" t="n"/>
-      <c r="K91" s="13" t="inlineStr">
+      <c r="K91" s="14" t="n"/>
+      <c r="L91" s="14" t="n"/>
+      <c r="M91" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L91" s="14" t="n"/>
-      <c r="M91" s="14" t="n"/>
       <c r="N91" s="14" t="n"/>
       <c r="O91" s="14" t="n"/>
       <c r="P91" s="14" t="n"/>
@@ -6302,6 +6505,8 @@
       <c r="U91" s="14" t="n"/>
       <c r="V91" s="14" t="n"/>
       <c r="W91" s="14" t="n"/>
+      <c r="X91" s="14" t="n"/>
+      <c r="Y91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -6339,13 +6544,13 @@
       <c r="H92" s="14" t="n"/>
       <c r="I92" s="14" t="n"/>
       <c r="J92" s="14" t="n"/>
-      <c r="K92" s="13" t="inlineStr">
+      <c r="K92" s="14" t="n"/>
+      <c r="L92" s="14" t="n"/>
+      <c r="M92" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L92" s="14" t="n"/>
-      <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
       <c r="O92" s="14" t="n"/>
       <c r="P92" s="14" t="n"/>
@@ -6356,6 +6561,8 @@
       <c r="U92" s="14" t="n"/>
       <c r="V92" s="14" t="n"/>
       <c r="W92" s="14" t="n"/>
+      <c r="X92" s="14" t="n"/>
+      <c r="Y92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -6393,13 +6600,13 @@
       <c r="H93" s="14" t="n"/>
       <c r="I93" s="14" t="n"/>
       <c r="J93" s="14" t="n"/>
-      <c r="K93" s="13" t="inlineStr">
+      <c r="K93" s="14" t="n"/>
+      <c r="L93" s="14" t="n"/>
+      <c r="M93" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L93" s="14" t="n"/>
-      <c r="M93" s="14" t="n"/>
       <c r="N93" s="14" t="n"/>
       <c r="O93" s="14" t="n"/>
       <c r="P93" s="14" t="n"/>
@@ -6410,6 +6617,8 @@
       <c r="U93" s="14" t="n"/>
       <c r="V93" s="14" t="n"/>
       <c r="W93" s="14" t="n"/>
+      <c r="X93" s="14" t="n"/>
+      <c r="Y93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -6447,24 +6656,24 @@
       <c r="H94" s="14" t="n"/>
       <c r="I94" s="14" t="n"/>
       <c r="J94" s="14" t="n"/>
-      <c r="K94" s="13" t="inlineStr">
+      <c r="K94" s="14" t="n"/>
+      <c r="L94" s="14" t="n"/>
+      <c r="M94" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L94" s="13" t="inlineStr">
+      <c r="N94" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M94" s="14" t="n"/>
-      <c r="N94" s="13" t="inlineStr">
+      <c r="O94" s="14" t="n"/>
+      <c r="P94" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O94" s="14" t="n"/>
-      <c r="P94" s="14" t="n"/>
       <c r="Q94" s="14" t="n"/>
       <c r="R94" s="14" t="n"/>
       <c r="S94" s="14" t="n"/>
@@ -6472,6 +6681,8 @@
       <c r="U94" s="14" t="n"/>
       <c r="V94" s="14" t="n"/>
       <c r="W94" s="14" t="n"/>
+      <c r="X94" s="14" t="n"/>
+      <c r="Y94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -6518,6 +6729,8 @@
       <c r="U95" s="14" t="n"/>
       <c r="V95" s="14" t="n"/>
       <c r="W95" s="14" t="n"/>
+      <c r="X95" s="14" t="n"/>
+      <c r="Y95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -6559,24 +6772,24 @@
       </c>
       <c r="I96" s="14" t="n"/>
       <c r="J96" s="14" t="n"/>
-      <c r="K96" s="13" t="inlineStr">
+      <c r="K96" s="14" t="n"/>
+      <c r="L96" s="14" t="n"/>
+      <c r="M96" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L96" s="13" t="inlineStr">
+      <c r="N96" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M96" s="14" t="n"/>
-      <c r="N96" s="13" t="inlineStr">
+      <c r="O96" s="14" t="n"/>
+      <c r="P96" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O96" s="14" t="n"/>
-      <c r="P96" s="14" t="n"/>
       <c r="Q96" s="14" t="n"/>
       <c r="R96" s="14" t="n"/>
       <c r="S96" s="14" t="n"/>
@@ -6584,6 +6797,8 @@
       <c r="U96" s="14" t="n"/>
       <c r="V96" s="14" t="n"/>
       <c r="W96" s="14" t="n"/>
+      <c r="X96" s="14" t="n"/>
+      <c r="Y96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -6621,13 +6836,13 @@
       <c r="H97" s="14" t="n"/>
       <c r="I97" s="14" t="n"/>
       <c r="J97" s="14" t="n"/>
-      <c r="K97" s="13" t="inlineStr">
+      <c r="K97" s="14" t="n"/>
+      <c r="L97" s="14" t="n"/>
+      <c r="M97" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L97" s="14" t="n"/>
-      <c r="M97" s="14" t="n"/>
       <c r="N97" s="14" t="n"/>
       <c r="O97" s="14" t="n"/>
       <c r="P97" s="14" t="n"/>
@@ -6638,6 +6853,8 @@
       <c r="U97" s="14" t="n"/>
       <c r="V97" s="14" t="n"/>
       <c r="W97" s="14" t="n"/>
+      <c r="X97" s="14" t="n"/>
+      <c r="Y97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -6679,13 +6896,13 @@
       </c>
       <c r="I98" s="14" t="n"/>
       <c r="J98" s="14" t="n"/>
-      <c r="K98" s="13" t="inlineStr">
+      <c r="K98" s="14" t="n"/>
+      <c r="L98" s="14" t="n"/>
+      <c r="M98" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L98" s="14" t="n"/>
-      <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
       <c r="O98" s="14" t="n"/>
       <c r="P98" s="14" t="n"/>
@@ -6696,6 +6913,8 @@
       <c r="U98" s="14" t="n"/>
       <c r="V98" s="14" t="n"/>
       <c r="W98" s="14" t="n"/>
+      <c r="X98" s="14" t="n"/>
+      <c r="Y98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -6729,13 +6948,13 @@
       <c r="H99" s="14" t="n"/>
       <c r="I99" s="14" t="n"/>
       <c r="J99" s="14" t="n"/>
-      <c r="K99" s="13" t="inlineStr">
+      <c r="K99" s="14" t="n"/>
+      <c r="L99" s="14" t="n"/>
+      <c r="M99" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L99" s="14" t="n"/>
-      <c r="M99" s="14" t="n"/>
       <c r="N99" s="14" t="n"/>
       <c r="O99" s="14" t="n"/>
       <c r="P99" s="14" t="n"/>
@@ -6746,6 +6965,8 @@
       <c r="U99" s="14" t="n"/>
       <c r="V99" s="14" t="n"/>
       <c r="W99" s="14" t="n"/>
+      <c r="X99" s="14" t="n"/>
+      <c r="Y99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -6792,6 +7013,8 @@
       <c r="U100" s="14" t="n"/>
       <c r="V100" s="14" t="n"/>
       <c r="W100" s="14" t="n"/>
+      <c r="X100" s="14" t="n"/>
+      <c r="Y100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -6838,6 +7061,8 @@
       <c r="U101" s="14" t="n"/>
       <c r="V101" s="14" t="n"/>
       <c r="W101" s="14" t="n"/>
+      <c r="X101" s="14" t="n"/>
+      <c r="Y101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -6875,13 +7100,13 @@
       <c r="H102" s="14" t="n"/>
       <c r="I102" s="14" t="n"/>
       <c r="J102" s="14" t="n"/>
-      <c r="K102" s="13" t="inlineStr">
+      <c r="K102" s="14" t="n"/>
+      <c r="L102" s="14" t="n"/>
+      <c r="M102" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L102" s="14" t="n"/>
-      <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
       <c r="O102" s="14" t="n"/>
       <c r="P102" s="14" t="n"/>
@@ -6892,6 +7117,8 @@
       <c r="U102" s="14" t="n"/>
       <c r="V102" s="14" t="n"/>
       <c r="W102" s="14" t="n"/>
+      <c r="X102" s="14" t="n"/>
+      <c r="Y102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -6929,13 +7156,13 @@
       <c r="H103" s="14" t="n"/>
       <c r="I103" s="14" t="n"/>
       <c r="J103" s="14" t="n"/>
-      <c r="K103" s="13" t="inlineStr">
+      <c r="K103" s="14" t="n"/>
+      <c r="L103" s="14" t="n"/>
+      <c r="M103" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L103" s="14" t="n"/>
-      <c r="M103" s="14" t="n"/>
       <c r="N103" s="14" t="n"/>
       <c r="O103" s="14" t="n"/>
       <c r="P103" s="14" t="n"/>
@@ -6946,6 +7173,8 @@
       <c r="U103" s="14" t="n"/>
       <c r="V103" s="14" t="n"/>
       <c r="W103" s="14" t="n"/>
+      <c r="X103" s="14" t="n"/>
+      <c r="Y103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -6979,13 +7208,13 @@
       <c r="H104" s="14" t="n"/>
       <c r="I104" s="14" t="n"/>
       <c r="J104" s="14" t="n"/>
-      <c r="K104" s="13" t="inlineStr">
+      <c r="K104" s="14" t="n"/>
+      <c r="L104" s="14" t="n"/>
+      <c r="M104" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L104" s="14" t="n"/>
-      <c r="M104" s="14" t="n"/>
       <c r="N104" s="14" t="n"/>
       <c r="O104" s="14" t="n"/>
       <c r="P104" s="14" t="n"/>
@@ -6996,6 +7225,8 @@
       <c r="U104" s="14" t="n"/>
       <c r="V104" s="14" t="n"/>
       <c r="W104" s="14" t="n"/>
+      <c r="X104" s="14" t="n"/>
+      <c r="Y104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -7029,13 +7260,13 @@
       <c r="H105" s="14" t="n"/>
       <c r="I105" s="14" t="n"/>
       <c r="J105" s="14" t="n"/>
-      <c r="K105" s="13" t="inlineStr">
+      <c r="K105" s="14" t="n"/>
+      <c r="L105" s="14" t="n"/>
+      <c r="M105" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L105" s="14" t="n"/>
-      <c r="M105" s="14" t="n"/>
       <c r="N105" s="14" t="n"/>
       <c r="O105" s="14" t="n"/>
       <c r="P105" s="14" t="n"/>
@@ -7046,6 +7277,8 @@
       <c r="U105" s="14" t="n"/>
       <c r="V105" s="14" t="n"/>
       <c r="W105" s="14" t="n"/>
+      <c r="X105" s="14" t="n"/>
+      <c r="Y105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -7092,6 +7325,8 @@
       <c r="U106" s="14" t="n"/>
       <c r="V106" s="14" t="n"/>
       <c r="W106" s="14" t="n"/>
+      <c r="X106" s="14" t="n"/>
+      <c r="Y106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -7125,13 +7360,13 @@
       <c r="H107" s="14" t="n"/>
       <c r="I107" s="14" t="n"/>
       <c r="J107" s="14" t="n"/>
-      <c r="K107" s="13" t="inlineStr">
+      <c r="K107" s="14" t="n"/>
+      <c r="L107" s="14" t="n"/>
+      <c r="M107" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L107" s="14" t="n"/>
-      <c r="M107" s="14" t="n"/>
       <c r="N107" s="14" t="n"/>
       <c r="O107" s="14" t="n"/>
       <c r="P107" s="14" t="n"/>
@@ -7142,6 +7377,8 @@
       <c r="U107" s="14" t="n"/>
       <c r="V107" s="14" t="n"/>
       <c r="W107" s="14" t="n"/>
+      <c r="X107" s="14" t="n"/>
+      <c r="Y107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -7179,13 +7416,13 @@
       <c r="H108" s="14" t="n"/>
       <c r="I108" s="14" t="n"/>
       <c r="J108" s="14" t="n"/>
-      <c r="K108" s="13" t="inlineStr">
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L108" s="14" t="n"/>
-      <c r="M108" s="14" t="n"/>
       <c r="N108" s="14" t="n"/>
       <c r="O108" s="14" t="n"/>
       <c r="P108" s="14" t="n"/>
@@ -7196,6 +7433,8 @@
       <c r="U108" s="14" t="n"/>
       <c r="V108" s="14" t="n"/>
       <c r="W108" s="14" t="n"/>
+      <c r="X108" s="14" t="n"/>
+      <c r="Y108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -7233,13 +7472,13 @@
       <c r="H109" s="14" t="n"/>
       <c r="I109" s="14" t="n"/>
       <c r="J109" s="14" t="n"/>
-      <c r="K109" s="13" t="inlineStr">
+      <c r="K109" s="14" t="n"/>
+      <c r="L109" s="14" t="n"/>
+      <c r="M109" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L109" s="14" t="n"/>
-      <c r="M109" s="14" t="n"/>
       <c r="N109" s="14" t="n"/>
       <c r="O109" s="14" t="n"/>
       <c r="P109" s="14" t="n"/>
@@ -7250,6 +7489,8 @@
       <c r="U109" s="14" t="n"/>
       <c r="V109" s="14" t="n"/>
       <c r="W109" s="14" t="n"/>
+      <c r="X109" s="14" t="n"/>
+      <c r="Y109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -7283,13 +7524,13 @@
       <c r="H110" s="14" t="n"/>
       <c r="I110" s="14" t="n"/>
       <c r="J110" s="14" t="n"/>
-      <c r="K110" s="13" t="inlineStr">
+      <c r="K110" s="14" t="n"/>
+      <c r="L110" s="14" t="n"/>
+      <c r="M110" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L110" s="14" t="n"/>
-      <c r="M110" s="14" t="n"/>
       <c r="N110" s="14" t="n"/>
       <c r="O110" s="14" t="n"/>
       <c r="P110" s="14" t="n"/>
@@ -7300,6 +7541,8 @@
       <c r="U110" s="14" t="n"/>
       <c r="V110" s="14" t="n"/>
       <c r="W110" s="14" t="n"/>
+      <c r="X110" s="14" t="n"/>
+      <c r="Y110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -7337,13 +7580,13 @@
       <c r="H111" s="14" t="n"/>
       <c r="I111" s="14" t="n"/>
       <c r="J111" s="14" t="n"/>
-      <c r="K111" s="13" t="inlineStr">
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L111" s="14" t="n"/>
-      <c r="M111" s="14" t="n"/>
       <c r="N111" s="14" t="n"/>
       <c r="O111" s="14" t="n"/>
       <c r="P111" s="14" t="n"/>
@@ -7354,6 +7597,8 @@
       <c r="U111" s="14" t="n"/>
       <c r="V111" s="14" t="n"/>
       <c r="W111" s="14" t="n"/>
+      <c r="X111" s="14" t="n"/>
+      <c r="Y111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -7387,13 +7632,13 @@
       <c r="H112" s="14" t="n"/>
       <c r="I112" s="14" t="n"/>
       <c r="J112" s="14" t="n"/>
-      <c r="K112" s="13" t="inlineStr">
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
+      <c r="M112" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L112" s="14" t="n"/>
-      <c r="M112" s="14" t="n"/>
       <c r="N112" s="14" t="n"/>
       <c r="O112" s="14" t="n"/>
       <c r="P112" s="14" t="n"/>
@@ -7404,6 +7649,8 @@
       <c r="U112" s="14" t="n"/>
       <c r="V112" s="14" t="n"/>
       <c r="W112" s="14" t="n"/>
+      <c r="X112" s="14" t="n"/>
+      <c r="Y112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -7441,13 +7688,13 @@
       <c r="H113" s="14" t="n"/>
       <c r="I113" s="14" t="n"/>
       <c r="J113" s="14" t="n"/>
-      <c r="K113" s="13" t="inlineStr">
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
+      <c r="M113" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L113" s="14" t="n"/>
-      <c r="M113" s="14" t="n"/>
       <c r="N113" s="14" t="n"/>
       <c r="O113" s="14" t="n"/>
       <c r="P113" s="14" t="n"/>
@@ -7458,6 +7705,8 @@
       <c r="U113" s="14" t="n"/>
       <c r="V113" s="14" t="n"/>
       <c r="W113" s="14" t="n"/>
+      <c r="X113" s="14" t="n"/>
+      <c r="Y113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -7495,13 +7744,13 @@
       <c r="H114" s="14" t="n"/>
       <c r="I114" s="14" t="n"/>
       <c r="J114" s="14" t="n"/>
-      <c r="K114" s="13" t="inlineStr">
+      <c r="K114" s="14" t="n"/>
+      <c r="L114" s="14" t="n"/>
+      <c r="M114" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L114" s="14" t="n"/>
-      <c r="M114" s="14" t="n"/>
       <c r="N114" s="14" t="n"/>
       <c r="O114" s="14" t="n"/>
       <c r="P114" s="14" t="n"/>
@@ -7512,6 +7761,8 @@
       <c r="U114" s="14" t="n"/>
       <c r="V114" s="14" t="n"/>
       <c r="W114" s="14" t="n"/>
+      <c r="X114" s="14" t="n"/>
+      <c r="Y114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -7549,13 +7800,13 @@
       <c r="H115" s="14" t="n"/>
       <c r="I115" s="14" t="n"/>
       <c r="J115" s="14" t="n"/>
-      <c r="K115" s="13" t="inlineStr">
+      <c r="K115" s="14" t="n"/>
+      <c r="L115" s="14" t="n"/>
+      <c r="M115" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L115" s="14" t="n"/>
-      <c r="M115" s="14" t="n"/>
       <c r="N115" s="14" t="n"/>
       <c r="O115" s="14" t="n"/>
       <c r="P115" s="14" t="n"/>
@@ -7566,6 +7817,8 @@
       <c r="U115" s="14" t="n"/>
       <c r="V115" s="14" t="n"/>
       <c r="W115" s="14" t="n"/>
+      <c r="X115" s="14" t="n"/>
+      <c r="Y115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -7603,13 +7856,13 @@
       <c r="H116" s="14" t="n"/>
       <c r="I116" s="14" t="n"/>
       <c r="J116" s="14" t="n"/>
-      <c r="K116" s="13" t="inlineStr">
+      <c r="K116" s="14" t="n"/>
+      <c r="L116" s="14" t="n"/>
+      <c r="M116" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L116" s="14" t="n"/>
-      <c r="M116" s="14" t="n"/>
       <c r="N116" s="14" t="n"/>
       <c r="O116" s="14" t="n"/>
       <c r="P116" s="14" t="n"/>
@@ -7620,6 +7873,8 @@
       <c r="U116" s="14" t="n"/>
       <c r="V116" s="14" t="n"/>
       <c r="W116" s="14" t="n"/>
+      <c r="X116" s="14" t="n"/>
+      <c r="Y116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -7657,13 +7912,13 @@
       <c r="H117" s="14" t="n"/>
       <c r="I117" s="14" t="n"/>
       <c r="J117" s="14" t="n"/>
-      <c r="K117" s="13" t="inlineStr">
+      <c r="K117" s="14" t="n"/>
+      <c r="L117" s="14" t="n"/>
+      <c r="M117" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L117" s="14" t="n"/>
-      <c r="M117" s="14" t="n"/>
       <c r="N117" s="14" t="n"/>
       <c r="O117" s="14" t="n"/>
       <c r="P117" s="14" t="n"/>
@@ -7674,6 +7929,8 @@
       <c r="U117" s="14" t="n"/>
       <c r="V117" s="14" t="n"/>
       <c r="W117" s="14" t="n"/>
+      <c r="X117" s="14" t="n"/>
+      <c r="Y117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -7711,13 +7968,13 @@
       <c r="H118" s="14" t="n"/>
       <c r="I118" s="14" t="n"/>
       <c r="J118" s="14" t="n"/>
-      <c r="K118" s="13" t="inlineStr">
+      <c r="K118" s="14" t="n"/>
+      <c r="L118" s="14" t="n"/>
+      <c r="M118" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L118" s="14" t="n"/>
-      <c r="M118" s="14" t="n"/>
       <c r="N118" s="14" t="n"/>
       <c r="O118" s="14" t="n"/>
       <c r="P118" s="14" t="n"/>
@@ -7728,6 +7985,8 @@
       <c r="U118" s="14" t="n"/>
       <c r="V118" s="14" t="n"/>
       <c r="W118" s="14" t="n"/>
+      <c r="X118" s="14" t="n"/>
+      <c r="Y118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -7765,13 +8024,13 @@
       <c r="H119" s="14" t="n"/>
       <c r="I119" s="14" t="n"/>
       <c r="J119" s="14" t="n"/>
-      <c r="K119" s="13" t="inlineStr">
+      <c r="K119" s="14" t="n"/>
+      <c r="L119" s="14" t="n"/>
+      <c r="M119" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L119" s="14" t="n"/>
-      <c r="M119" s="14" t="n"/>
       <c r="N119" s="14" t="n"/>
       <c r="O119" s="14" t="n"/>
       <c r="P119" s="14" t="n"/>
@@ -7782,6 +8041,8 @@
       <c r="U119" s="14" t="n"/>
       <c r="V119" s="14" t="n"/>
       <c r="W119" s="14" t="n"/>
+      <c r="X119" s="14" t="n"/>
+      <c r="Y119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -7819,13 +8080,13 @@
       <c r="H120" s="14" t="n"/>
       <c r="I120" s="14" t="n"/>
       <c r="J120" s="14" t="n"/>
-      <c r="K120" s="13" t="inlineStr">
+      <c r="K120" s="14" t="n"/>
+      <c r="L120" s="14" t="n"/>
+      <c r="M120" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L120" s="14" t="n"/>
-      <c r="M120" s="14" t="n"/>
       <c r="N120" s="14" t="n"/>
       <c r="O120" s="14" t="n"/>
       <c r="P120" s="14" t="n"/>
@@ -7836,6 +8097,8 @@
       <c r="U120" s="14" t="n"/>
       <c r="V120" s="14" t="n"/>
       <c r="W120" s="14" t="n"/>
+      <c r="X120" s="14" t="n"/>
+      <c r="Y120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -7873,13 +8136,13 @@
       <c r="H121" s="14" t="n"/>
       <c r="I121" s="14" t="n"/>
       <c r="J121" s="14" t="n"/>
-      <c r="K121" s="13" t="inlineStr">
+      <c r="K121" s="14" t="n"/>
+      <c r="L121" s="14" t="n"/>
+      <c r="M121" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L121" s="14" t="n"/>
-      <c r="M121" s="14" t="n"/>
       <c r="N121" s="14" t="n"/>
       <c r="O121" s="14" t="n"/>
       <c r="P121" s="14" t="n"/>
@@ -7890,6 +8153,8 @@
       <c r="U121" s="14" t="n"/>
       <c r="V121" s="14" t="n"/>
       <c r="W121" s="14" t="n"/>
+      <c r="X121" s="14" t="n"/>
+      <c r="Y121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -7927,13 +8192,13 @@
       <c r="H122" s="14" t="n"/>
       <c r="I122" s="14" t="n"/>
       <c r="J122" s="14" t="n"/>
-      <c r="K122" s="13" t="inlineStr">
+      <c r="K122" s="14" t="n"/>
+      <c r="L122" s="14" t="n"/>
+      <c r="M122" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L122" s="14" t="n"/>
-      <c r="M122" s="14" t="n"/>
       <c r="N122" s="14" t="n"/>
       <c r="O122" s="14" t="n"/>
       <c r="P122" s="14" t="n"/>
@@ -7944,6 +8209,8 @@
       <c r="U122" s="14" t="n"/>
       <c r="V122" s="14" t="n"/>
       <c r="W122" s="14" t="n"/>
+      <c r="X122" s="14" t="n"/>
+      <c r="Y122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -7981,13 +8248,13 @@
       <c r="H123" s="14" t="n"/>
       <c r="I123" s="14" t="n"/>
       <c r="J123" s="14" t="n"/>
-      <c r="K123" s="13" t="inlineStr">
+      <c r="K123" s="14" t="n"/>
+      <c r="L123" s="14" t="n"/>
+      <c r="M123" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L123" s="14" t="n"/>
-      <c r="M123" s="14" t="n"/>
       <c r="N123" s="14" t="n"/>
       <c r="O123" s="14" t="n"/>
       <c r="P123" s="14" t="n"/>
@@ -7998,6 +8265,8 @@
       <c r="U123" s="14" t="n"/>
       <c r="V123" s="14" t="n"/>
       <c r="W123" s="14" t="n"/>
+      <c r="X123" s="14" t="n"/>
+      <c r="Y123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -8035,13 +8304,13 @@
       <c r="H124" s="14" t="n"/>
       <c r="I124" s="14" t="n"/>
       <c r="J124" s="14" t="n"/>
-      <c r="K124" s="13" t="inlineStr">
+      <c r="K124" s="14" t="n"/>
+      <c r="L124" s="14" t="n"/>
+      <c r="M124" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L124" s="14" t="n"/>
-      <c r="M124" s="14" t="n"/>
       <c r="N124" s="14" t="n"/>
       <c r="O124" s="14" t="n"/>
       <c r="P124" s="14" t="n"/>
@@ -8052,6 +8321,8 @@
       <c r="U124" s="14" t="n"/>
       <c r="V124" s="14" t="n"/>
       <c r="W124" s="14" t="n"/>
+      <c r="X124" s="14" t="n"/>
+      <c r="Y124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -8089,13 +8360,13 @@
       <c r="H125" s="14" t="n"/>
       <c r="I125" s="14" t="n"/>
       <c r="J125" s="14" t="n"/>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K125" s="14" t="n"/>
+      <c r="L125" s="14" t="n"/>
+      <c r="M125" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L125" s="14" t="n"/>
-      <c r="M125" s="14" t="n"/>
       <c r="N125" s="14" t="n"/>
       <c r="O125" s="14" t="n"/>
       <c r="P125" s="14" t="n"/>
@@ -8106,6 +8377,8 @@
       <c r="U125" s="14" t="n"/>
       <c r="V125" s="14" t="n"/>
       <c r="W125" s="14" t="n"/>
+      <c r="X125" s="14" t="n"/>
+      <c r="Y125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -8143,13 +8416,13 @@
       <c r="H126" s="14" t="n"/>
       <c r="I126" s="14" t="n"/>
       <c r="J126" s="14" t="n"/>
-      <c r="K126" s="13" t="inlineStr">
+      <c r="K126" s="14" t="n"/>
+      <c r="L126" s="14" t="n"/>
+      <c r="M126" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L126" s="14" t="n"/>
-      <c r="M126" s="14" t="n"/>
       <c r="N126" s="14" t="n"/>
       <c r="O126" s="14" t="n"/>
       <c r="P126" s="14" t="n"/>
@@ -8160,6 +8433,8 @@
       <c r="U126" s="14" t="n"/>
       <c r="V126" s="14" t="n"/>
       <c r="W126" s="14" t="n"/>
+      <c r="X126" s="14" t="n"/>
+      <c r="Y126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -8197,13 +8472,13 @@
       <c r="H127" s="14" t="n"/>
       <c r="I127" s="14" t="n"/>
       <c r="J127" s="14" t="n"/>
-      <c r="K127" s="13" t="inlineStr">
+      <c r="K127" s="14" t="n"/>
+      <c r="L127" s="14" t="n"/>
+      <c r="M127" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L127" s="14" t="n"/>
-      <c r="M127" s="14" t="n"/>
       <c r="N127" s="14" t="n"/>
       <c r="O127" s="14" t="n"/>
       <c r="P127" s="14" t="n"/>
@@ -8214,6 +8489,8 @@
       <c r="U127" s="14" t="n"/>
       <c r="V127" s="14" t="n"/>
       <c r="W127" s="14" t="n"/>
+      <c r="X127" s="14" t="n"/>
+      <c r="Y127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -8251,13 +8528,13 @@
       <c r="H128" s="14" t="n"/>
       <c r="I128" s="14" t="n"/>
       <c r="J128" s="14" t="n"/>
-      <c r="K128" s="13" t="inlineStr">
+      <c r="K128" s="14" t="n"/>
+      <c r="L128" s="14" t="n"/>
+      <c r="M128" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L128" s="14" t="n"/>
-      <c r="M128" s="14" t="n"/>
       <c r="N128" s="14" t="n"/>
       <c r="O128" s="14" t="n"/>
       <c r="P128" s="14" t="n"/>
@@ -8268,6 +8545,8 @@
       <c r="U128" s="14" t="n"/>
       <c r="V128" s="14" t="n"/>
       <c r="W128" s="14" t="n"/>
+      <c r="X128" s="14" t="n"/>
+      <c r="Y128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -8305,13 +8584,13 @@
       <c r="H129" s="14" t="n"/>
       <c r="I129" s="14" t="n"/>
       <c r="J129" s="14" t="n"/>
-      <c r="K129" s="13" t="inlineStr">
+      <c r="K129" s="14" t="n"/>
+      <c r="L129" s="14" t="n"/>
+      <c r="M129" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L129" s="14" t="n"/>
-      <c r="M129" s="14" t="n"/>
       <c r="N129" s="14" t="n"/>
       <c r="O129" s="14" t="n"/>
       <c r="P129" s="14" t="n"/>
@@ -8322,6 +8601,8 @@
       <c r="U129" s="14" t="n"/>
       <c r="V129" s="14" t="n"/>
       <c r="W129" s="14" t="n"/>
+      <c r="X129" s="14" t="n"/>
+      <c r="Y129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -8359,24 +8640,24 @@
       <c r="H130" s="14" t="n"/>
       <c r="I130" s="14" t="n"/>
       <c r="J130" s="14" t="n"/>
-      <c r="K130" s="13" t="inlineStr">
+      <c r="K130" s="14" t="n"/>
+      <c r="L130" s="14" t="n"/>
+      <c r="M130" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L130" s="13" t="inlineStr">
+      <c r="N130" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M130" s="14" t="n"/>
-      <c r="N130" s="13" t="inlineStr">
+      <c r="O130" s="14" t="n"/>
+      <c r="P130" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O130" s="14" t="n"/>
-      <c r="P130" s="14" t="n"/>
       <c r="Q130" s="14" t="n"/>
       <c r="R130" s="14" t="n"/>
       <c r="S130" s="14" t="n"/>
@@ -8384,6 +8665,8 @@
       <c r="U130" s="14" t="n"/>
       <c r="V130" s="14" t="n"/>
       <c r="W130" s="14" t="n"/>
+      <c r="X130" s="14" t="n"/>
+      <c r="Y130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -8421,13 +8704,13 @@
       <c r="H131" s="14" t="n"/>
       <c r="I131" s="14" t="n"/>
       <c r="J131" s="14" t="n"/>
-      <c r="K131" s="13" t="inlineStr">
+      <c r="K131" s="14" t="n"/>
+      <c r="L131" s="14" t="n"/>
+      <c r="M131" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L131" s="14" t="n"/>
-      <c r="M131" s="14" t="n"/>
       <c r="N131" s="14" t="n"/>
       <c r="O131" s="14" t="n"/>
       <c r="P131" s="14" t="n"/>
@@ -8438,6 +8721,8 @@
       <c r="U131" s="14" t="n"/>
       <c r="V131" s="14" t="n"/>
       <c r="W131" s="14" t="n"/>
+      <c r="X131" s="14" t="n"/>
+      <c r="Y131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
@@ -8475,24 +8760,24 @@
       <c r="H132" s="14" t="n"/>
       <c r="I132" s="14" t="n"/>
       <c r="J132" s="14" t="n"/>
-      <c r="K132" s="13" t="inlineStr">
+      <c r="K132" s="14" t="n"/>
+      <c r="L132" s="14" t="n"/>
+      <c r="M132" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L132" s="13" t="inlineStr">
+      <c r="N132" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M132" s="14" t="n"/>
-      <c r="N132" s="13" t="inlineStr">
+      <c r="O132" s="14" t="n"/>
+      <c r="P132" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O132" s="14" t="n"/>
-      <c r="P132" s="14" t="n"/>
       <c r="Q132" s="14" t="n"/>
       <c r="R132" s="14" t="n"/>
       <c r="S132" s="14" t="n"/>
@@ -8500,6 +8785,8 @@
       <c r="U132" s="14" t="n"/>
       <c r="V132" s="14" t="n"/>
       <c r="W132" s="14" t="n"/>
+      <c r="X132" s="14" t="n"/>
+      <c r="Y132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -8537,24 +8824,24 @@
       <c r="H133" s="14" t="n"/>
       <c r="I133" s="14" t="n"/>
       <c r="J133" s="14" t="n"/>
-      <c r="K133" s="13" t="inlineStr">
+      <c r="K133" s="14" t="n"/>
+      <c r="L133" s="14" t="n"/>
+      <c r="M133" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L133" s="13" t="inlineStr">
+      <c r="N133" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M133" s="14" t="n"/>
-      <c r="N133" s="13" t="inlineStr">
+      <c r="O133" s="14" t="n"/>
+      <c r="P133" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O133" s="14" t="n"/>
-      <c r="P133" s="14" t="n"/>
       <c r="Q133" s="14" t="n"/>
       <c r="R133" s="14" t="n"/>
       <c r="S133" s="14" t="n"/>
@@ -8562,6 +8849,8 @@
       <c r="U133" s="14" t="n"/>
       <c r="V133" s="14" t="n"/>
       <c r="W133" s="14" t="n"/>
+      <c r="X133" s="14" t="n"/>
+      <c r="Y133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -8599,24 +8888,24 @@
       <c r="H134" s="14" t="n"/>
       <c r="I134" s="14" t="n"/>
       <c r="J134" s="14" t="n"/>
-      <c r="K134" s="13" t="inlineStr">
+      <c r="K134" s="14" t="n"/>
+      <c r="L134" s="14" t="n"/>
+      <c r="M134" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L134" s="13" t="inlineStr">
+      <c r="N134" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M134" s="14" t="n"/>
-      <c r="N134" s="13" t="inlineStr">
+      <c r="O134" s="14" t="n"/>
+      <c r="P134" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O134" s="14" t="n"/>
-      <c r="P134" s="14" t="n"/>
       <c r="Q134" s="14" t="n"/>
       <c r="R134" s="14" t="n"/>
       <c r="S134" s="14" t="n"/>
@@ -8624,6 +8913,8 @@
       <c r="U134" s="14" t="n"/>
       <c r="V134" s="14" t="n"/>
       <c r="W134" s="14" t="n"/>
+      <c r="X134" s="14" t="n"/>
+      <c r="Y134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
@@ -8661,24 +8952,24 @@
       <c r="H135" s="14" t="n"/>
       <c r="I135" s="14" t="n"/>
       <c r="J135" s="14" t="n"/>
-      <c r="K135" s="13" t="inlineStr">
+      <c r="K135" s="14" t="n"/>
+      <c r="L135" s="14" t="n"/>
+      <c r="M135" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L135" s="13" t="inlineStr">
+      <c r="N135" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M135" s="14" t="n"/>
-      <c r="N135" s="13" t="inlineStr">
+      <c r="O135" s="14" t="n"/>
+      <c r="P135" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O135" s="14" t="n"/>
-      <c r="P135" s="14" t="n"/>
       <c r="Q135" s="14" t="n"/>
       <c r="R135" s="14" t="n"/>
       <c r="S135" s="14" t="n"/>
@@ -8686,6 +8977,8 @@
       <c r="U135" s="14" t="n"/>
       <c r="V135" s="14" t="n"/>
       <c r="W135" s="14" t="n"/>
+      <c r="X135" s="14" t="n"/>
+      <c r="Y135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
@@ -8723,13 +9016,13 @@
       <c r="H136" s="14" t="n"/>
       <c r="I136" s="14" t="n"/>
       <c r="J136" s="14" t="n"/>
-      <c r="K136" s="13" t="inlineStr">
+      <c r="K136" s="14" t="n"/>
+      <c r="L136" s="14" t="n"/>
+      <c r="M136" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L136" s="14" t="n"/>
-      <c r="M136" s="14" t="n"/>
       <c r="N136" s="14" t="n"/>
       <c r="O136" s="14" t="n"/>
       <c r="P136" s="14" t="n"/>
@@ -8740,6 +9033,8 @@
       <c r="U136" s="14" t="n"/>
       <c r="V136" s="14" t="n"/>
       <c r="W136" s="14" t="n"/>
+      <c r="X136" s="14" t="n"/>
+      <c r="Y136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
@@ -8777,13 +9072,13 @@
       <c r="H137" s="14" t="n"/>
       <c r="I137" s="14" t="n"/>
       <c r="J137" s="14" t="n"/>
-      <c r="K137" s="13" t="inlineStr">
+      <c r="K137" s="14" t="n"/>
+      <c r="L137" s="14" t="n"/>
+      <c r="M137" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L137" s="14" t="n"/>
-      <c r="M137" s="14" t="n"/>
       <c r="N137" s="14" t="n"/>
       <c r="O137" s="14" t="n"/>
       <c r="P137" s="14" t="n"/>
@@ -8794,6 +9089,8 @@
       <c r="U137" s="14" t="n"/>
       <c r="V137" s="14" t="n"/>
       <c r="W137" s="14" t="n"/>
+      <c r="X137" s="14" t="n"/>
+      <c r="Y137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
@@ -8831,24 +9128,24 @@
       <c r="H138" s="14" t="n"/>
       <c r="I138" s="14" t="n"/>
       <c r="J138" s="14" t="n"/>
-      <c r="K138" s="13" t="inlineStr">
+      <c r="K138" s="14" t="n"/>
+      <c r="L138" s="14" t="n"/>
+      <c r="M138" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L138" s="13" t="inlineStr">
+      <c r="N138" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M138" s="14" t="n"/>
-      <c r="N138" s="13" t="inlineStr">
+      <c r="O138" s="14" t="n"/>
+      <c r="P138" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O138" s="14" t="n"/>
-      <c r="P138" s="14" t="n"/>
       <c r="Q138" s="14" t="n"/>
       <c r="R138" s="14" t="n"/>
       <c r="S138" s="14" t="n"/>
@@ -8856,6 +9153,8 @@
       <c r="U138" s="14" t="n"/>
       <c r="V138" s="14" t="n"/>
       <c r="W138" s="14" t="n"/>
+      <c r="X138" s="14" t="n"/>
+      <c r="Y138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -8893,13 +9192,13 @@
       <c r="H139" s="14" t="n"/>
       <c r="I139" s="14" t="n"/>
       <c r="J139" s="14" t="n"/>
-      <c r="K139" s="13" t="inlineStr">
+      <c r="K139" s="14" t="n"/>
+      <c r="L139" s="14" t="n"/>
+      <c r="M139" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L139" s="14" t="n"/>
-      <c r="M139" s="14" t="n"/>
       <c r="N139" s="14" t="n"/>
       <c r="O139" s="14" t="n"/>
       <c r="P139" s="14" t="n"/>
@@ -8910,6 +9209,8 @@
       <c r="U139" s="14" t="n"/>
       <c r="V139" s="14" t="n"/>
       <c r="W139" s="14" t="n"/>
+      <c r="X139" s="14" t="n"/>
+      <c r="Y139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -8947,13 +9248,13 @@
       <c r="H140" s="14" t="n"/>
       <c r="I140" s="14" t="n"/>
       <c r="J140" s="14" t="n"/>
-      <c r="K140" s="13" t="inlineStr">
+      <c r="K140" s="14" t="n"/>
+      <c r="L140" s="14" t="n"/>
+      <c r="M140" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L140" s="14" t="n"/>
-      <c r="M140" s="14" t="n"/>
       <c r="N140" s="14" t="n"/>
       <c r="O140" s="14" t="n"/>
       <c r="P140" s="14" t="n"/>
@@ -8964,6 +9265,8 @@
       <c r="U140" s="14" t="n"/>
       <c r="V140" s="14" t="n"/>
       <c r="W140" s="14" t="n"/>
+      <c r="X140" s="14" t="n"/>
+      <c r="Y140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -9001,13 +9304,13 @@
       <c r="H141" s="14" t="n"/>
       <c r="I141" s="14" t="n"/>
       <c r="J141" s="14" t="n"/>
-      <c r="K141" s="13" t="inlineStr">
+      <c r="K141" s="14" t="n"/>
+      <c r="L141" s="14" t="n"/>
+      <c r="M141" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L141" s="14" t="n"/>
-      <c r="M141" s="14" t="n"/>
       <c r="N141" s="14" t="n"/>
       <c r="O141" s="14" t="n"/>
       <c r="P141" s="14" t="n"/>
@@ -9018,6 +9321,8 @@
       <c r="U141" s="14" t="n"/>
       <c r="V141" s="14" t="n"/>
       <c r="W141" s="14" t="n"/>
+      <c r="X141" s="14" t="n"/>
+      <c r="Y141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -9055,13 +9360,13 @@
       <c r="H142" s="14" t="n"/>
       <c r="I142" s="14" t="n"/>
       <c r="J142" s="14" t="n"/>
-      <c r="K142" s="13" t="inlineStr">
+      <c r="K142" s="14" t="n"/>
+      <c r="L142" s="14" t="n"/>
+      <c r="M142" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L142" s="14" t="n"/>
-      <c r="M142" s="14" t="n"/>
       <c r="N142" s="14" t="n"/>
       <c r="O142" s="14" t="n"/>
       <c r="P142" s="14" t="n"/>
@@ -9072,6 +9377,8 @@
       <c r="U142" s="14" t="n"/>
       <c r="V142" s="14" t="n"/>
       <c r="W142" s="14" t="n"/>
+      <c r="X142" s="14" t="n"/>
+      <c r="Y142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -9109,13 +9416,13 @@
       <c r="H143" s="14" t="n"/>
       <c r="I143" s="14" t="n"/>
       <c r="J143" s="14" t="n"/>
-      <c r="K143" s="13" t="inlineStr">
+      <c r="K143" s="14" t="n"/>
+      <c r="L143" s="14" t="n"/>
+      <c r="M143" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L143" s="14" t="n"/>
-      <c r="M143" s="14" t="n"/>
       <c r="N143" s="14" t="n"/>
       <c r="O143" s="14" t="n"/>
       <c r="P143" s="14" t="n"/>
@@ -9126,6 +9433,8 @@
       <c r="U143" s="14" t="n"/>
       <c r="V143" s="14" t="n"/>
       <c r="W143" s="14" t="n"/>
+      <c r="X143" s="14" t="n"/>
+      <c r="Y143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -9163,13 +9472,13 @@
       <c r="H144" s="14" t="n"/>
       <c r="I144" s="14" t="n"/>
       <c r="J144" s="14" t="n"/>
-      <c r="K144" s="13" t="inlineStr">
+      <c r="K144" s="14" t="n"/>
+      <c r="L144" s="14" t="n"/>
+      <c r="M144" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L144" s="14" t="n"/>
-      <c r="M144" s="14" t="n"/>
       <c r="N144" s="14" t="n"/>
       <c r="O144" s="14" t="n"/>
       <c r="P144" s="14" t="n"/>
@@ -9180,6 +9489,8 @@
       <c r="U144" s="14" t="n"/>
       <c r="V144" s="14" t="n"/>
       <c r="W144" s="14" t="n"/>
+      <c r="X144" s="14" t="n"/>
+      <c r="Y144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -9217,24 +9528,24 @@
       <c r="H145" s="14" t="n"/>
       <c r="I145" s="14" t="n"/>
       <c r="J145" s="14" t="n"/>
-      <c r="K145" s="13" t="inlineStr">
+      <c r="K145" s="14" t="n"/>
+      <c r="L145" s="14" t="n"/>
+      <c r="M145" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L145" s="13" t="inlineStr">
+      <c r="N145" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M145" s="14" t="n"/>
-      <c r="N145" s="13" t="inlineStr">
+      <c r="O145" s="14" t="n"/>
+      <c r="P145" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O145" s="14" t="n"/>
-      <c r="P145" s="14" t="n"/>
       <c r="Q145" s="14" t="n"/>
       <c r="R145" s="14" t="n"/>
       <c r="S145" s="14" t="n"/>
@@ -9242,6 +9553,8 @@
       <c r="U145" s="14" t="n"/>
       <c r="V145" s="14" t="n"/>
       <c r="W145" s="14" t="n"/>
+      <c r="X145" s="14" t="n"/>
+      <c r="Y145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -9279,13 +9592,13 @@
       <c r="H146" s="14" t="n"/>
       <c r="I146" s="14" t="n"/>
       <c r="J146" s="14" t="n"/>
-      <c r="K146" s="13" t="inlineStr">
+      <c r="K146" s="14" t="n"/>
+      <c r="L146" s="14" t="n"/>
+      <c r="M146" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L146" s="14" t="n"/>
-      <c r="M146" s="14" t="n"/>
       <c r="N146" s="14" t="n"/>
       <c r="O146" s="14" t="n"/>
       <c r="P146" s="14" t="n"/>
@@ -9296,6 +9609,8 @@
       <c r="U146" s="14" t="n"/>
       <c r="V146" s="14" t="n"/>
       <c r="W146" s="14" t="n"/>
+      <c r="X146" s="14" t="n"/>
+      <c r="Y146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -9333,13 +9648,13 @@
       <c r="H147" s="14" t="n"/>
       <c r="I147" s="14" t="n"/>
       <c r="J147" s="14" t="n"/>
-      <c r="K147" s="13" t="inlineStr">
+      <c r="K147" s="14" t="n"/>
+      <c r="L147" s="14" t="n"/>
+      <c r="M147" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L147" s="14" t="n"/>
-      <c r="M147" s="14" t="n"/>
       <c r="N147" s="14" t="n"/>
       <c r="O147" s="14" t="n"/>
       <c r="P147" s="14" t="n"/>
@@ -9350,6 +9665,8 @@
       <c r="U147" s="14" t="n"/>
       <c r="V147" s="14" t="n"/>
       <c r="W147" s="14" t="n"/>
+      <c r="X147" s="14" t="n"/>
+      <c r="Y147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
@@ -9387,24 +9704,24 @@
       <c r="H148" s="14" t="n"/>
       <c r="I148" s="14" t="n"/>
       <c r="J148" s="14" t="n"/>
-      <c r="K148" s="13" t="inlineStr">
+      <c r="K148" s="14" t="n"/>
+      <c r="L148" s="14" t="n"/>
+      <c r="M148" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L148" s="13" t="inlineStr">
+      <c r="N148" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M148" s="14" t="n"/>
-      <c r="N148" s="13" t="inlineStr">
+      <c r="O148" s="14" t="n"/>
+      <c r="P148" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O148" s="14" t="n"/>
-      <c r="P148" s="14" t="n"/>
       <c r="Q148" s="14" t="n"/>
       <c r="R148" s="14" t="n"/>
       <c r="S148" s="14" t="n"/>
@@ -9412,6 +9729,8 @@
       <c r="U148" s="14" t="n"/>
       <c r="V148" s="14" t="n"/>
       <c r="W148" s="14" t="n"/>
+      <c r="X148" s="14" t="n"/>
+      <c r="Y148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
@@ -9458,6 +9777,8 @@
       <c r="U149" s="14" t="n"/>
       <c r="V149" s="14" t="n"/>
       <c r="W149" s="14" t="n"/>
+      <c r="X149" s="14" t="n"/>
+      <c r="Y149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
@@ -9495,13 +9816,13 @@
       <c r="H150" s="14" t="n"/>
       <c r="I150" s="14" t="n"/>
       <c r="J150" s="14" t="n"/>
-      <c r="K150" s="13" t="inlineStr">
+      <c r="K150" s="14" t="n"/>
+      <c r="L150" s="14" t="n"/>
+      <c r="M150" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L150" s="14" t="n"/>
-      <c r="M150" s="14" t="n"/>
       <c r="N150" s="14" t="n"/>
       <c r="O150" s="14" t="n"/>
       <c r="P150" s="14" t="n"/>
@@ -9512,6 +9833,8 @@
       <c r="U150" s="14" t="n"/>
       <c r="V150" s="14" t="n"/>
       <c r="W150" s="14" t="n"/>
+      <c r="X150" s="14" t="n"/>
+      <c r="Y150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
@@ -9549,24 +9872,24 @@
       <c r="H151" s="14" t="n"/>
       <c r="I151" s="14" t="n"/>
       <c r="J151" s="14" t="n"/>
-      <c r="K151" s="13" t="inlineStr">
+      <c r="K151" s="14" t="n"/>
+      <c r="L151" s="14" t="n"/>
+      <c r="M151" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L151" s="13" t="inlineStr">
+      <c r="N151" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M151" s="14" t="n"/>
-      <c r="N151" s="13" t="inlineStr">
+      <c r="O151" s="14" t="n"/>
+      <c r="P151" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O151" s="14" t="n"/>
-      <c r="P151" s="14" t="n"/>
       <c r="Q151" s="14" t="n"/>
       <c r="R151" s="14" t="n"/>
       <c r="S151" s="14" t="n"/>
@@ -9574,6 +9897,8 @@
       <c r="U151" s="14" t="n"/>
       <c r="V151" s="14" t="n"/>
       <c r="W151" s="14" t="n"/>
+      <c r="X151" s="14" t="n"/>
+      <c r="Y151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
@@ -9611,24 +9936,24 @@
       <c r="H152" s="14" t="n"/>
       <c r="I152" s="14" t="n"/>
       <c r="J152" s="14" t="n"/>
-      <c r="K152" s="13" t="inlineStr">
+      <c r="K152" s="14" t="n"/>
+      <c r="L152" s="14" t="n"/>
+      <c r="M152" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L152" s="13" t="inlineStr">
+      <c r="N152" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M152" s="14" t="n"/>
-      <c r="N152" s="13" t="inlineStr">
+      <c r="O152" s="14" t="n"/>
+      <c r="P152" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O152" s="14" t="n"/>
-      <c r="P152" s="14" t="n"/>
       <c r="Q152" s="14" t="n"/>
       <c r="R152" s="14" t="n"/>
       <c r="S152" s="14" t="n"/>
@@ -9636,6 +9961,8 @@
       <c r="U152" s="14" t="n"/>
       <c r="V152" s="14" t="n"/>
       <c r="W152" s="14" t="n"/>
+      <c r="X152" s="14" t="n"/>
+      <c r="Y152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
@@ -9673,13 +10000,13 @@
       <c r="H153" s="14" t="n"/>
       <c r="I153" s="14" t="n"/>
       <c r="J153" s="14" t="n"/>
-      <c r="K153" s="13" t="inlineStr">
+      <c r="K153" s="14" t="n"/>
+      <c r="L153" s="14" t="n"/>
+      <c r="M153" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L153" s="14" t="n"/>
-      <c r="M153" s="14" t="n"/>
       <c r="N153" s="14" t="n"/>
       <c r="O153" s="14" t="n"/>
       <c r="P153" s="14" t="n"/>
@@ -9690,6 +10017,8 @@
       <c r="U153" s="14" t="n"/>
       <c r="V153" s="14" t="n"/>
       <c r="W153" s="14" t="n"/>
+      <c r="X153" s="14" t="n"/>
+      <c r="Y153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
@@ -9727,13 +10056,13 @@
       <c r="H154" s="14" t="n"/>
       <c r="I154" s="14" t="n"/>
       <c r="J154" s="14" t="n"/>
-      <c r="K154" s="13" t="inlineStr">
+      <c r="K154" s="14" t="n"/>
+      <c r="L154" s="14" t="n"/>
+      <c r="M154" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L154" s="14" t="n"/>
-      <c r="M154" s="14" t="n"/>
       <c r="N154" s="14" t="n"/>
       <c r="O154" s="14" t="n"/>
       <c r="P154" s="14" t="n"/>
@@ -9744,6 +10073,8 @@
       <c r="U154" s="14" t="n"/>
       <c r="V154" s="14" t="n"/>
       <c r="W154" s="14" t="n"/>
+      <c r="X154" s="14" t="n"/>
+      <c r="Y154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
@@ -9781,24 +10112,24 @@
       <c r="H155" s="14" t="n"/>
       <c r="I155" s="14" t="n"/>
       <c r="J155" s="14" t="n"/>
-      <c r="K155" s="13" t="inlineStr">
+      <c r="K155" s="14" t="n"/>
+      <c r="L155" s="14" t="n"/>
+      <c r="M155" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L155" s="13" t="inlineStr">
+      <c r="N155" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M155" s="14" t="n"/>
-      <c r="N155" s="13" t="inlineStr">
+      <c r="O155" s="14" t="n"/>
+      <c r="P155" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O155" s="14" t="n"/>
-      <c r="P155" s="14" t="n"/>
       <c r="Q155" s="14" t="n"/>
       <c r="R155" s="14" t="n"/>
       <c r="S155" s="14" t="n"/>
@@ -9806,6 +10137,8 @@
       <c r="U155" s="14" t="n"/>
       <c r="V155" s="14" t="n"/>
       <c r="W155" s="14" t="n"/>
+      <c r="X155" s="14" t="n"/>
+      <c r="Y155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
@@ -9852,6 +10185,8 @@
       <c r="U156" s="14" t="n"/>
       <c r="V156" s="14" t="n"/>
       <c r="W156" s="14" t="n"/>
+      <c r="X156" s="14" t="n"/>
+      <c r="Y156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
@@ -9889,13 +10224,13 @@
       <c r="H157" s="14" t="n"/>
       <c r="I157" s="14" t="n"/>
       <c r="J157" s="14" t="n"/>
-      <c r="K157" s="13" t="inlineStr">
+      <c r="K157" s="14" t="n"/>
+      <c r="L157" s="14" t="n"/>
+      <c r="M157" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L157" s="14" t="n"/>
-      <c r="M157" s="14" t="n"/>
       <c r="N157" s="14" t="n"/>
       <c r="O157" s="14" t="n"/>
       <c r="P157" s="14" t="n"/>
@@ -9906,6 +10241,8 @@
       <c r="U157" s="14" t="n"/>
       <c r="V157" s="14" t="n"/>
       <c r="W157" s="14" t="n"/>
+      <c r="X157" s="14" t="n"/>
+      <c r="Y157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
@@ -9943,24 +10280,24 @@
       <c r="H158" s="14" t="n"/>
       <c r="I158" s="14" t="n"/>
       <c r="J158" s="14" t="n"/>
-      <c r="K158" s="13" t="inlineStr">
+      <c r="K158" s="14" t="n"/>
+      <c r="L158" s="14" t="n"/>
+      <c r="M158" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L158" s="13" t="inlineStr">
+      <c r="N158" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M158" s="14" t="n"/>
-      <c r="N158" s="13" t="inlineStr">
+      <c r="O158" s="14" t="n"/>
+      <c r="P158" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O158" s="14" t="n"/>
-      <c r="P158" s="14" t="n"/>
       <c r="Q158" s="14" t="n"/>
       <c r="R158" s="14" t="n"/>
       <c r="S158" s="14" t="n"/>
@@ -9968,6 +10305,8 @@
       <c r="U158" s="14" t="n"/>
       <c r="V158" s="14" t="n"/>
       <c r="W158" s="14" t="n"/>
+      <c r="X158" s="14" t="n"/>
+      <c r="Y158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
@@ -10005,13 +10344,13 @@
       <c r="H159" s="14" t="n"/>
       <c r="I159" s="14" t="n"/>
       <c r="J159" s="14" t="n"/>
-      <c r="K159" s="13" t="inlineStr">
+      <c r="K159" s="14" t="n"/>
+      <c r="L159" s="14" t="n"/>
+      <c r="M159" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L159" s="14" t="n"/>
-      <c r="M159" s="14" t="n"/>
       <c r="N159" s="14" t="n"/>
       <c r="O159" s="14" t="n"/>
       <c r="P159" s="14" t="n"/>
@@ -10022,6 +10361,8 @@
       <c r="U159" s="14" t="n"/>
       <c r="V159" s="14" t="n"/>
       <c r="W159" s="14" t="n"/>
+      <c r="X159" s="14" t="n"/>
+      <c r="Y159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
@@ -10059,13 +10400,13 @@
       <c r="H160" s="14" t="n"/>
       <c r="I160" s="14" t="n"/>
       <c r="J160" s="14" t="n"/>
-      <c r="K160" s="13" t="inlineStr">
+      <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
+      <c r="M160" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L160" s="14" t="n"/>
-      <c r="M160" s="14" t="n"/>
       <c r="N160" s="14" t="n"/>
       <c r="O160" s="14" t="n"/>
       <c r="P160" s="14" t="n"/>
@@ -10076,6 +10417,8 @@
       <c r="U160" s="14" t="n"/>
       <c r="V160" s="14" t="n"/>
       <c r="W160" s="14" t="n"/>
+      <c r="X160" s="14" t="n"/>
+      <c r="Y160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
@@ -10113,24 +10456,24 @@
       <c r="H161" s="14" t="n"/>
       <c r="I161" s="14" t="n"/>
       <c r="J161" s="14" t="n"/>
-      <c r="K161" s="13" t="inlineStr">
+      <c r="K161" s="14" t="n"/>
+      <c r="L161" s="14" t="n"/>
+      <c r="M161" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L161" s="13" t="inlineStr">
+      <c r="N161" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M161" s="14" t="n"/>
-      <c r="N161" s="13" t="inlineStr">
+      <c r="O161" s="14" t="n"/>
+      <c r="P161" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O161" s="14" t="n"/>
-      <c r="P161" s="14" t="n"/>
       <c r="Q161" s="14" t="n"/>
       <c r="R161" s="14" t="n"/>
       <c r="S161" s="14" t="n"/>
@@ -10138,6 +10481,8 @@
       <c r="U161" s="14" t="n"/>
       <c r="V161" s="14" t="n"/>
       <c r="W161" s="14" t="n"/>
+      <c r="X161" s="14" t="n"/>
+      <c r="Y161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
@@ -10184,6 +10529,8 @@
       <c r="U162" s="14" t="n"/>
       <c r="V162" s="14" t="n"/>
       <c r="W162" s="14" t="n"/>
+      <c r="X162" s="14" t="n"/>
+      <c r="Y162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
@@ -10221,13 +10568,13 @@
       <c r="H163" s="14" t="n"/>
       <c r="I163" s="14" t="n"/>
       <c r="J163" s="14" t="n"/>
-      <c r="K163" s="13" t="inlineStr">
+      <c r="K163" s="14" t="n"/>
+      <c r="L163" s="14" t="n"/>
+      <c r="M163" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L163" s="14" t="n"/>
-      <c r="M163" s="14" t="n"/>
       <c r="N163" s="14" t="n"/>
       <c r="O163" s="14" t="n"/>
       <c r="P163" s="14" t="n"/>
@@ -10238,6 +10585,8 @@
       <c r="U163" s="14" t="n"/>
       <c r="V163" s="14" t="n"/>
       <c r="W163" s="14" t="n"/>
+      <c r="X163" s="14" t="n"/>
+      <c r="Y163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
@@ -10275,24 +10624,24 @@
       <c r="H164" s="14" t="n"/>
       <c r="I164" s="14" t="n"/>
       <c r="J164" s="14" t="n"/>
-      <c r="K164" s="13" t="inlineStr">
+      <c r="K164" s="14" t="n"/>
+      <c r="L164" s="14" t="n"/>
+      <c r="M164" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L164" s="13" t="inlineStr">
+      <c r="N164" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M164" s="14" t="n"/>
-      <c r="N164" s="13" t="inlineStr">
+      <c r="O164" s="14" t="n"/>
+      <c r="P164" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O164" s="14" t="n"/>
-      <c r="P164" s="14" t="n"/>
       <c r="Q164" s="14" t="n"/>
       <c r="R164" s="14" t="n"/>
       <c r="S164" s="14" t="n"/>
@@ -10300,6 +10649,8 @@
       <c r="U164" s="14" t="n"/>
       <c r="V164" s="14" t="n"/>
       <c r="W164" s="14" t="n"/>
+      <c r="X164" s="14" t="n"/>
+      <c r="Y164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
@@ -10337,13 +10688,13 @@
       <c r="H165" s="14" t="n"/>
       <c r="I165" s="14" t="n"/>
       <c r="J165" s="14" t="n"/>
-      <c r="K165" s="13" t="inlineStr">
+      <c r="K165" s="14" t="n"/>
+      <c r="L165" s="14" t="n"/>
+      <c r="M165" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L165" s="14" t="n"/>
-      <c r="M165" s="14" t="n"/>
       <c r="N165" s="14" t="n"/>
       <c r="O165" s="14" t="n"/>
       <c r="P165" s="14" t="n"/>
@@ -10354,6 +10705,8 @@
       <c r="U165" s="14" t="n"/>
       <c r="V165" s="14" t="n"/>
       <c r="W165" s="14" t="n"/>
+      <c r="X165" s="14" t="n"/>
+      <c r="Y165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
@@ -10400,6 +10753,8 @@
       <c r="U166" s="14" t="n"/>
       <c r="V166" s="14" t="n"/>
       <c r="W166" s="14" t="n"/>
+      <c r="X166" s="14" t="n"/>
+      <c r="Y166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
@@ -10437,13 +10792,13 @@
       <c r="H167" s="14" t="n"/>
       <c r="I167" s="14" t="n"/>
       <c r="J167" s="14" t="n"/>
-      <c r="K167" s="13" t="inlineStr">
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+      <c r="M167" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L167" s="14" t="n"/>
-      <c r="M167" s="14" t="n"/>
       <c r="N167" s="14" t="n"/>
       <c r="O167" s="14" t="n"/>
       <c r="P167" s="14" t="n"/>
@@ -10454,6 +10809,8 @@
       <c r="U167" s="14" t="n"/>
       <c r="V167" s="14" t="n"/>
       <c r="W167" s="14" t="n"/>
+      <c r="X167" s="14" t="n"/>
+      <c r="Y167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
@@ -10491,24 +10848,24 @@
       <c r="H168" s="14" t="n"/>
       <c r="I168" s="14" t="n"/>
       <c r="J168" s="14" t="n"/>
-      <c r="K168" s="13" t="inlineStr">
+      <c r="K168" s="14" t="n"/>
+      <c r="L168" s="14" t="n"/>
+      <c r="M168" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L168" s="13" t="inlineStr">
+      <c r="N168" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M168" s="14" t="n"/>
-      <c r="N168" s="13" t="inlineStr">
+      <c r="O168" s="14" t="n"/>
+      <c r="P168" s="13" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
       </c>
-      <c r="O168" s="14" t="n"/>
-      <c r="P168" s="14" t="n"/>
       <c r="Q168" s="14" t="n"/>
       <c r="R168" s="14" t="n"/>
       <c r="S168" s="14" t="n"/>
@@ -10516,6 +10873,8 @@
       <c r="U168" s="14" t="n"/>
       <c r="V168" s="14" t="n"/>
       <c r="W168" s="14" t="n"/>
+      <c r="X168" s="14" t="n"/>
+      <c r="Y168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
@@ -10553,24 +10912,24 @@
       <c r="H169" s="14" t="n"/>
       <c r="I169" s="14" t="n"/>
       <c r="J169" s="14" t="n"/>
-      <c r="K169" s="13" t="inlineStr">
+      <c r="K169" s="14" t="n"/>
+      <c r="L169" s="14" t="n"/>
+      <c r="M169" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L169" s="13" t="inlineStr">
+      <c r="N169" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M169" s="14" t="n"/>
-      <c r="N169" s="13" t="inlineStr">
+      <c r="O169" s="14" t="n"/>
+      <c r="P169" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O169" s="14" t="n"/>
-      <c r="P169" s="14" t="n"/>
       <c r="Q169" s="14" t="n"/>
       <c r="R169" s="14" t="n"/>
       <c r="S169" s="14" t="n"/>
@@ -10578,6 +10937,8 @@
       <c r="U169" s="14" t="n"/>
       <c r="V169" s="14" t="n"/>
       <c r="W169" s="14" t="n"/>
+      <c r="X169" s="14" t="n"/>
+      <c r="Y169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
@@ -10615,13 +10976,13 @@
       <c r="H170" s="14" t="n"/>
       <c r="I170" s="14" t="n"/>
       <c r="J170" s="14" t="n"/>
-      <c r="K170" s="13" t="inlineStr">
+      <c r="K170" s="14" t="n"/>
+      <c r="L170" s="14" t="n"/>
+      <c r="M170" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L170" s="14" t="n"/>
-      <c r="M170" s="14" t="n"/>
       <c r="N170" s="14" t="n"/>
       <c r="O170" s="14" t="n"/>
       <c r="P170" s="14" t="n"/>
@@ -10632,6 +10993,8 @@
       <c r="U170" s="14" t="n"/>
       <c r="V170" s="14" t="n"/>
       <c r="W170" s="14" t="n"/>
+      <c r="X170" s="14" t="n"/>
+      <c r="Y170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
@@ -10669,13 +11032,13 @@
       <c r="H171" s="14" t="n"/>
       <c r="I171" s="14" t="n"/>
       <c r="J171" s="14" t="n"/>
-      <c r="K171" s="13" t="inlineStr">
+      <c r="K171" s="14" t="n"/>
+      <c r="L171" s="14" t="n"/>
+      <c r="M171" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L171" s="14" t="n"/>
-      <c r="M171" s="14" t="n"/>
       <c r="N171" s="14" t="n"/>
       <c r="O171" s="14" t="n"/>
       <c r="P171" s="14" t="n"/>
@@ -10686,6 +11049,8 @@
       <c r="U171" s="14" t="n"/>
       <c r="V171" s="14" t="n"/>
       <c r="W171" s="14" t="n"/>
+      <c r="X171" s="14" t="n"/>
+      <c r="Y171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
@@ -10723,13 +11088,13 @@
       <c r="H172" s="14" t="n"/>
       <c r="I172" s="14" t="n"/>
       <c r="J172" s="14" t="n"/>
-      <c r="K172" s="13" t="inlineStr">
+      <c r="K172" s="14" t="n"/>
+      <c r="L172" s="14" t="n"/>
+      <c r="M172" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L172" s="14" t="n"/>
-      <c r="M172" s="14" t="n"/>
       <c r="N172" s="14" t="n"/>
       <c r="O172" s="14" t="n"/>
       <c r="P172" s="14" t="n"/>
@@ -10740,6 +11105,8 @@
       <c r="U172" s="14" t="n"/>
       <c r="V172" s="14" t="n"/>
       <c r="W172" s="14" t="n"/>
+      <c r="X172" s="14" t="n"/>
+      <c r="Y172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
@@ -10777,13 +11144,13 @@
       <c r="H173" s="14" t="n"/>
       <c r="I173" s="14" t="n"/>
       <c r="J173" s="14" t="n"/>
-      <c r="K173" s="13" t="inlineStr">
+      <c r="K173" s="14" t="n"/>
+      <c r="L173" s="14" t="n"/>
+      <c r="M173" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L173" s="14" t="n"/>
-      <c r="M173" s="14" t="n"/>
       <c r="N173" s="14" t="n"/>
       <c r="O173" s="14" t="n"/>
       <c r="P173" s="14" t="n"/>
@@ -10794,6 +11161,8 @@
       <c r="U173" s="14" t="n"/>
       <c r="V173" s="14" t="n"/>
       <c r="W173" s="14" t="n"/>
+      <c r="X173" s="14" t="n"/>
+      <c r="Y173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
@@ -10831,13 +11200,13 @@
       <c r="H174" s="14" t="n"/>
       <c r="I174" s="14" t="n"/>
       <c r="J174" s="14" t="n"/>
-      <c r="K174" s="13" t="inlineStr">
+      <c r="K174" s="14" t="n"/>
+      <c r="L174" s="14" t="n"/>
+      <c r="M174" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L174" s="14" t="n"/>
-      <c r="M174" s="14" t="n"/>
       <c r="N174" s="14" t="n"/>
       <c r="O174" s="14" t="n"/>
       <c r="P174" s="14" t="n"/>
@@ -10848,6 +11217,8 @@
       <c r="U174" s="14" t="n"/>
       <c r="V174" s="14" t="n"/>
       <c r="W174" s="14" t="n"/>
+      <c r="X174" s="14" t="n"/>
+      <c r="Y174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
@@ -10885,13 +11256,13 @@
       <c r="H175" s="14" t="n"/>
       <c r="I175" s="14" t="n"/>
       <c r="J175" s="14" t="n"/>
-      <c r="K175" s="13" t="inlineStr">
+      <c r="K175" s="14" t="n"/>
+      <c r="L175" s="14" t="n"/>
+      <c r="M175" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L175" s="14" t="n"/>
-      <c r="M175" s="14" t="n"/>
       <c r="N175" s="14" t="n"/>
       <c r="O175" s="14" t="n"/>
       <c r="P175" s="14" t="n"/>
@@ -10902,6 +11273,8 @@
       <c r="U175" s="14" t="n"/>
       <c r="V175" s="14" t="n"/>
       <c r="W175" s="14" t="n"/>
+      <c r="X175" s="14" t="n"/>
+      <c r="Y175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="10" t="inlineStr">
@@ -10939,13 +11312,13 @@
       <c r="H176" s="14" t="n"/>
       <c r="I176" s="14" t="n"/>
       <c r="J176" s="14" t="n"/>
-      <c r="K176" s="13" t="inlineStr">
+      <c r="K176" s="14" t="n"/>
+      <c r="L176" s="14" t="n"/>
+      <c r="M176" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L176" s="14" t="n"/>
-      <c r="M176" s="14" t="n"/>
       <c r="N176" s="14" t="n"/>
       <c r="O176" s="14" t="n"/>
       <c r="P176" s="14" t="n"/>
@@ -10956,6 +11329,8 @@
       <c r="U176" s="14" t="n"/>
       <c r="V176" s="14" t="n"/>
       <c r="W176" s="14" t="n"/>
+      <c r="X176" s="14" t="n"/>
+      <c r="Y176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="10" t="inlineStr">
@@ -10993,13 +11368,13 @@
       <c r="H177" s="14" t="n"/>
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="14" t="n"/>
-      <c r="K177" s="13" t="inlineStr">
+      <c r="K177" s="14" t="n"/>
+      <c r="L177" s="14" t="n"/>
+      <c r="M177" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L177" s="14" t="n"/>
-      <c r="M177" s="14" t="n"/>
       <c r="N177" s="14" t="n"/>
       <c r="O177" s="14" t="n"/>
       <c r="P177" s="14" t="n"/>
@@ -11010,6 +11385,8 @@
       <c r="U177" s="14" t="n"/>
       <c r="V177" s="14" t="n"/>
       <c r="W177" s="14" t="n"/>
+      <c r="X177" s="14" t="n"/>
+      <c r="Y177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="10" t="inlineStr">
@@ -11047,13 +11424,13 @@
       <c r="H178" s="14" t="n"/>
       <c r="I178" s="14" t="n"/>
       <c r="J178" s="14" t="n"/>
-      <c r="K178" s="13" t="inlineStr">
+      <c r="K178" s="14" t="n"/>
+      <c r="L178" s="14" t="n"/>
+      <c r="M178" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L178" s="14" t="n"/>
-      <c r="M178" s="14" t="n"/>
       <c r="N178" s="14" t="n"/>
       <c r="O178" s="14" t="n"/>
       <c r="P178" s="14" t="n"/>
@@ -11064,6 +11441,8 @@
       <c r="U178" s="14" t="n"/>
       <c r="V178" s="14" t="n"/>
       <c r="W178" s="14" t="n"/>
+      <c r="X178" s="14" t="n"/>
+      <c r="Y178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
@@ -11101,13 +11480,13 @@
       <c r="H179" s="14" t="n"/>
       <c r="I179" s="14" t="n"/>
       <c r="J179" s="14" t="n"/>
-      <c r="K179" s="13" t="inlineStr">
+      <c r="K179" s="14" t="n"/>
+      <c r="L179" s="14" t="n"/>
+      <c r="M179" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L179" s="14" t="n"/>
-      <c r="M179" s="14" t="n"/>
       <c r="N179" s="14" t="n"/>
       <c r="O179" s="14" t="n"/>
       <c r="P179" s="14" t="n"/>
@@ -11118,6 +11497,8 @@
       <c r="U179" s="14" t="n"/>
       <c r="V179" s="14" t="n"/>
       <c r="W179" s="14" t="n"/>
+      <c r="X179" s="14" t="n"/>
+      <c r="Y179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="10" t="inlineStr">
@@ -11155,24 +11536,24 @@
       <c r="H180" s="14" t="n"/>
       <c r="I180" s="14" t="n"/>
       <c r="J180" s="14" t="n"/>
-      <c r="K180" s="13" t="inlineStr">
+      <c r="K180" s="14" t="n"/>
+      <c r="L180" s="14" t="n"/>
+      <c r="M180" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L180" s="13" t="inlineStr">
+      <c r="N180" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M180" s="14" t="n"/>
-      <c r="N180" s="13" t="inlineStr">
+      <c r="O180" s="14" t="n"/>
+      <c r="P180" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O180" s="14" t="n"/>
-      <c r="P180" s="14" t="n"/>
       <c r="Q180" s="14" t="n"/>
       <c r="R180" s="14" t="n"/>
       <c r="S180" s="14" t="n"/>
@@ -11180,6 +11561,8 @@
       <c r="U180" s="14" t="n"/>
       <c r="V180" s="14" t="n"/>
       <c r="W180" s="14" t="n"/>
+      <c r="X180" s="14" t="n"/>
+      <c r="Y180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="10" t="inlineStr">
@@ -11217,13 +11600,13 @@
       <c r="H181" s="14" t="n"/>
       <c r="I181" s="14" t="n"/>
       <c r="J181" s="14" t="n"/>
-      <c r="K181" s="13" t="inlineStr">
+      <c r="K181" s="14" t="n"/>
+      <c r="L181" s="14" t="n"/>
+      <c r="M181" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L181" s="14" t="n"/>
-      <c r="M181" s="14" t="n"/>
       <c r="N181" s="14" t="n"/>
       <c r="O181" s="14" t="n"/>
       <c r="P181" s="14" t="n"/>
@@ -11234,6 +11617,8 @@
       <c r="U181" s="14" t="n"/>
       <c r="V181" s="14" t="n"/>
       <c r="W181" s="14" t="n"/>
+      <c r="X181" s="14" t="n"/>
+      <c r="Y181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="10" t="inlineStr">
@@ -11271,13 +11656,13 @@
       <c r="H182" s="14" t="n"/>
       <c r="I182" s="14" t="n"/>
       <c r="J182" s="14" t="n"/>
-      <c r="K182" s="13" t="inlineStr">
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n"/>
+      <c r="M182" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L182" s="14" t="n"/>
-      <c r="M182" s="14" t="n"/>
       <c r="N182" s="14" t="n"/>
       <c r="O182" s="14" t="n"/>
       <c r="P182" s="14" t="n"/>
@@ -11288,6 +11673,8 @@
       <c r="U182" s="14" t="n"/>
       <c r="V182" s="14" t="n"/>
       <c r="W182" s="14" t="n"/>
+      <c r="X182" s="14" t="n"/>
+      <c r="Y182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="10" t="inlineStr">
@@ -11325,13 +11712,13 @@
       <c r="H183" s="14" t="n"/>
       <c r="I183" s="14" t="n"/>
       <c r="J183" s="14" t="n"/>
-      <c r="K183" s="13" t="inlineStr">
+      <c r="K183" s="14" t="n"/>
+      <c r="L183" s="14" t="n"/>
+      <c r="M183" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L183" s="14" t="n"/>
-      <c r="M183" s="14" t="n"/>
       <c r="N183" s="14" t="n"/>
       <c r="O183" s="14" t="n"/>
       <c r="P183" s="14" t="n"/>
@@ -11342,6 +11729,8 @@
       <c r="U183" s="14" t="n"/>
       <c r="V183" s="14" t="n"/>
       <c r="W183" s="14" t="n"/>
+      <c r="X183" s="14" t="n"/>
+      <c r="Y183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
@@ -11379,24 +11768,24 @@
       <c r="H184" s="14" t="n"/>
       <c r="I184" s="14" t="n"/>
       <c r="J184" s="14" t="n"/>
-      <c r="K184" s="13" t="inlineStr">
+      <c r="K184" s="14" t="n"/>
+      <c r="L184" s="14" t="n"/>
+      <c r="M184" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L184" s="13" t="inlineStr">
+      <c r="N184" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M184" s="14" t="n"/>
-      <c r="N184" s="13" t="inlineStr">
+      <c r="O184" s="14" t="n"/>
+      <c r="P184" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O184" s="14" t="n"/>
-      <c r="P184" s="14" t="n"/>
       <c r="Q184" s="14" t="n"/>
       <c r="R184" s="14" t="n"/>
       <c r="S184" s="14" t="n"/>
@@ -11404,6 +11793,8 @@
       <c r="U184" s="14" t="n"/>
       <c r="V184" s="14" t="n"/>
       <c r="W184" s="14" t="n"/>
+      <c r="X184" s="14" t="n"/>
+      <c r="Y184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
@@ -11441,13 +11832,13 @@
       <c r="H185" s="14" t="n"/>
       <c r="I185" s="14" t="n"/>
       <c r="J185" s="14" t="n"/>
-      <c r="K185" s="13" t="inlineStr">
+      <c r="K185" s="14" t="n"/>
+      <c r="L185" s="14" t="n"/>
+      <c r="M185" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L185" s="14" t="n"/>
-      <c r="M185" s="14" t="n"/>
       <c r="N185" s="14" t="n"/>
       <c r="O185" s="14" t="n"/>
       <c r="P185" s="14" t="n"/>
@@ -11458,6 +11849,8 @@
       <c r="U185" s="14" t="n"/>
       <c r="V185" s="14" t="n"/>
       <c r="W185" s="14" t="n"/>
+      <c r="X185" s="14" t="n"/>
+      <c r="Y185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
@@ -11495,13 +11888,13 @@
       <c r="H186" s="14" t="n"/>
       <c r="I186" s="14" t="n"/>
       <c r="J186" s="14" t="n"/>
-      <c r="K186" s="13" t="inlineStr">
+      <c r="K186" s="14" t="n"/>
+      <c r="L186" s="14" t="n"/>
+      <c r="M186" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L186" s="14" t="n"/>
-      <c r="M186" s="14" t="n"/>
       <c r="N186" s="14" t="n"/>
       <c r="O186" s="14" t="n"/>
       <c r="P186" s="14" t="n"/>
@@ -11512,6 +11905,8 @@
       <c r="U186" s="14" t="n"/>
       <c r="V186" s="14" t="n"/>
       <c r="W186" s="14" t="n"/>
+      <c r="X186" s="14" t="n"/>
+      <c r="Y186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
@@ -11549,13 +11944,13 @@
       <c r="H187" s="14" t="n"/>
       <c r="I187" s="14" t="n"/>
       <c r="J187" s="14" t="n"/>
-      <c r="K187" s="13" t="inlineStr">
+      <c r="K187" s="14" t="n"/>
+      <c r="L187" s="14" t="n"/>
+      <c r="M187" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L187" s="14" t="n"/>
-      <c r="M187" s="14" t="n"/>
       <c r="N187" s="14" t="n"/>
       <c r="O187" s="14" t="n"/>
       <c r="P187" s="14" t="n"/>
@@ -11566,6 +11961,8 @@
       <c r="U187" s="14" t="n"/>
       <c r="V187" s="14" t="n"/>
       <c r="W187" s="14" t="n"/>
+      <c r="X187" s="14" t="n"/>
+      <c r="Y187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
@@ -11603,24 +12000,24 @@
       <c r="H188" s="14" t="n"/>
       <c r="I188" s="14" t="n"/>
       <c r="J188" s="14" t="n"/>
-      <c r="K188" s="13" t="inlineStr">
+      <c r="K188" s="14" t="n"/>
+      <c r="L188" s="14" t="n"/>
+      <c r="M188" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L188" s="13" t="inlineStr">
+      <c r="N188" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M188" s="14" t="n"/>
-      <c r="N188" s="13" t="inlineStr">
+      <c r="O188" s="14" t="n"/>
+      <c r="P188" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O188" s="14" t="n"/>
-      <c r="P188" s="14" t="n"/>
       <c r="Q188" s="14" t="n"/>
       <c r="R188" s="14" t="n"/>
       <c r="S188" s="14" t="n"/>
@@ -11628,6 +12025,8 @@
       <c r="U188" s="14" t="n"/>
       <c r="V188" s="14" t="n"/>
       <c r="W188" s="14" t="n"/>
+      <c r="X188" s="14" t="n"/>
+      <c r="Y188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="10" t="inlineStr">
@@ -11665,24 +12064,24 @@
       <c r="H189" s="14" t="n"/>
       <c r="I189" s="14" t="n"/>
       <c r="J189" s="14" t="n"/>
-      <c r="K189" s="13" t="inlineStr">
+      <c r="K189" s="14" t="n"/>
+      <c r="L189" s="14" t="n"/>
+      <c r="M189" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L189" s="13" t="inlineStr">
+      <c r="N189" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M189" s="14" t="n"/>
-      <c r="N189" s="13" t="inlineStr">
+      <c r="O189" s="14" t="n"/>
+      <c r="P189" s="13" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
       </c>
-      <c r="O189" s="14" t="n"/>
-      <c r="P189" s="14" t="n"/>
       <c r="Q189" s="14" t="n"/>
       <c r="R189" s="14" t="n"/>
       <c r="S189" s="14" t="n"/>
@@ -11690,6 +12089,8 @@
       <c r="U189" s="14" t="n"/>
       <c r="V189" s="14" t="n"/>
       <c r="W189" s="14" t="n"/>
+      <c r="X189" s="14" t="n"/>
+      <c r="Y189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -11727,13 +12128,13 @@
       <c r="H190" s="14" t="n"/>
       <c r="I190" s="14" t="n"/>
       <c r="J190" s="14" t="n"/>
-      <c r="K190" s="13" t="inlineStr">
+      <c r="K190" s="14" t="n"/>
+      <c r="L190" s="14" t="n"/>
+      <c r="M190" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L190" s="14" t="n"/>
-      <c r="M190" s="14" t="n"/>
       <c r="N190" s="14" t="n"/>
       <c r="O190" s="14" t="n"/>
       <c r="P190" s="14" t="n"/>
@@ -11744,6 +12145,8 @@
       <c r="U190" s="14" t="n"/>
       <c r="V190" s="14" t="n"/>
       <c r="W190" s="14" t="n"/>
+      <c r="X190" s="14" t="n"/>
+      <c r="Y190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
@@ -11781,13 +12184,13 @@
       <c r="H191" s="14" t="n"/>
       <c r="I191" s="14" t="n"/>
       <c r="J191" s="14" t="n"/>
-      <c r="K191" s="13" t="inlineStr">
+      <c r="K191" s="14" t="n"/>
+      <c r="L191" s="14" t="n"/>
+      <c r="M191" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L191" s="14" t="n"/>
-      <c r="M191" s="14" t="n"/>
       <c r="N191" s="14" t="n"/>
       <c r="O191" s="14" t="n"/>
       <c r="P191" s="14" t="n"/>
@@ -11798,6 +12201,8 @@
       <c r="U191" s="14" t="n"/>
       <c r="V191" s="14" t="n"/>
       <c r="W191" s="14" t="n"/>
+      <c r="X191" s="14" t="n"/>
+      <c r="Y191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
@@ -11844,6 +12249,8 @@
       <c r="U192" s="14" t="n"/>
       <c r="V192" s="14" t="n"/>
       <c r="W192" s="14" t="n"/>
+      <c r="X192" s="14" t="n"/>
+      <c r="Y192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -11877,13 +12284,13 @@
       <c r="H193" s="14" t="n"/>
       <c r="I193" s="14" t="n"/>
       <c r="J193" s="14" t="n"/>
-      <c r="K193" s="13" t="inlineStr">
+      <c r="K193" s="14" t="n"/>
+      <c r="L193" s="14" t="n"/>
+      <c r="M193" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L193" s="14" t="n"/>
-      <c r="M193" s="14" t="n"/>
       <c r="N193" s="14" t="n"/>
       <c r="O193" s="14" t="n"/>
       <c r="P193" s="14" t="n"/>
@@ -11894,6 +12301,8 @@
       <c r="U193" s="14" t="n"/>
       <c r="V193" s="14" t="n"/>
       <c r="W193" s="14" t="n"/>
+      <c r="X193" s="14" t="n"/>
+      <c r="Y193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
@@ -11931,13 +12340,13 @@
       <c r="H194" s="14" t="n"/>
       <c r="I194" s="14" t="n"/>
       <c r="J194" s="14" t="n"/>
-      <c r="K194" s="13" t="inlineStr">
+      <c r="K194" s="14" t="n"/>
+      <c r="L194" s="14" t="n"/>
+      <c r="M194" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L194" s="14" t="n"/>
-      <c r="M194" s="14" t="n"/>
       <c r="N194" s="14" t="n"/>
       <c r="O194" s="14" t="n"/>
       <c r="P194" s="14" t="n"/>
@@ -11948,6 +12357,8 @@
       <c r="U194" s="14" t="n"/>
       <c r="V194" s="14" t="n"/>
       <c r="W194" s="14" t="n"/>
+      <c r="X194" s="14" t="n"/>
+      <c r="Y194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -11985,13 +12396,13 @@
       <c r="H195" s="14" t="n"/>
       <c r="I195" s="14" t="n"/>
       <c r="J195" s="14" t="n"/>
-      <c r="K195" s="13" t="inlineStr">
+      <c r="K195" s="14" t="n"/>
+      <c r="L195" s="14" t="n"/>
+      <c r="M195" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L195" s="14" t="n"/>
-      <c r="M195" s="14" t="n"/>
       <c r="N195" s="14" t="n"/>
       <c r="O195" s="14" t="n"/>
       <c r="P195" s="14" t="n"/>
@@ -12002,6 +12413,8 @@
       <c r="U195" s="14" t="n"/>
       <c r="V195" s="14" t="n"/>
       <c r="W195" s="14" t="n"/>
+      <c r="X195" s="14" t="n"/>
+      <c r="Y195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
@@ -12039,13 +12452,13 @@
       <c r="H196" s="14" t="n"/>
       <c r="I196" s="14" t="n"/>
       <c r="J196" s="14" t="n"/>
-      <c r="K196" s="13" t="inlineStr">
+      <c r="K196" s="14" t="n"/>
+      <c r="L196" s="14" t="n"/>
+      <c r="M196" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L196" s="14" t="n"/>
-      <c r="M196" s="14" t="n"/>
       <c r="N196" s="14" t="n"/>
       <c r="O196" s="14" t="n"/>
       <c r="P196" s="14" t="n"/>
@@ -12056,6 +12469,8 @@
       <c r="U196" s="14" t="n"/>
       <c r="V196" s="14" t="n"/>
       <c r="W196" s="14" t="n"/>
+      <c r="X196" s="14" t="n"/>
+      <c r="Y196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="10" t="inlineStr">
@@ -12093,13 +12508,13 @@
       <c r="H197" s="14" t="n"/>
       <c r="I197" s="14" t="n"/>
       <c r="J197" s="14" t="n"/>
-      <c r="K197" s="13" t="inlineStr">
+      <c r="K197" s="14" t="n"/>
+      <c r="L197" s="14" t="n"/>
+      <c r="M197" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L197" s="14" t="n"/>
-      <c r="M197" s="14" t="n"/>
       <c r="N197" s="14" t="n"/>
       <c r="O197" s="14" t="n"/>
       <c r="P197" s="14" t="n"/>
@@ -12110,6 +12525,8 @@
       <c r="U197" s="14" t="n"/>
       <c r="V197" s="14" t="n"/>
       <c r="W197" s="14" t="n"/>
+      <c r="X197" s="14" t="n"/>
+      <c r="Y197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
@@ -12147,13 +12564,13 @@
       <c r="H198" s="14" t="n"/>
       <c r="I198" s="14" t="n"/>
       <c r="J198" s="14" t="n"/>
-      <c r="K198" s="13" t="inlineStr">
+      <c r="K198" s="14" t="n"/>
+      <c r="L198" s="14" t="n"/>
+      <c r="M198" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L198" s="14" t="n"/>
-      <c r="M198" s="14" t="n"/>
       <c r="N198" s="14" t="n"/>
       <c r="O198" s="14" t="n"/>
       <c r="P198" s="14" t="n"/>
@@ -12164,6 +12581,8 @@
       <c r="U198" s="14" t="n"/>
       <c r="V198" s="14" t="n"/>
       <c r="W198" s="14" t="n"/>
+      <c r="X198" s="14" t="n"/>
+      <c r="Y198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
@@ -12197,13 +12616,13 @@
       <c r="H199" s="14" t="n"/>
       <c r="I199" s="14" t="n"/>
       <c r="J199" s="14" t="n"/>
-      <c r="K199" s="13" t="inlineStr">
+      <c r="K199" s="14" t="n"/>
+      <c r="L199" s="14" t="n"/>
+      <c r="M199" s="13" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="L199" s="14" t="n"/>
-      <c r="M199" s="14" t="n"/>
       <c r="N199" s="14" t="n"/>
       <c r="O199" s="14" t="n"/>
       <c r="P199" s="14" t="n"/>
@@ -12214,6 +12633,8 @@
       <c r="U199" s="14" t="n"/>
       <c r="V199" s="14" t="n"/>
       <c r="W199" s="14" t="n"/>
+      <c r="X199" s="14" t="n"/>
+      <c r="Y199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="10" t="inlineStr">
@@ -12251,13 +12672,13 @@
       <c r="H200" s="14" t="n"/>
       <c r="I200" s="14" t="n"/>
       <c r="J200" s="14" t="n"/>
-      <c r="K200" s="13" t="inlineStr">
+      <c r="K200" s="14" t="n"/>
+      <c r="L200" s="14" t="n"/>
+      <c r="M200" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L200" s="14" t="n"/>
-      <c r="M200" s="14" t="n"/>
       <c r="N200" s="14" t="n"/>
       <c r="O200" s="14" t="n"/>
       <c r="P200" s="14" t="n"/>
@@ -12268,6 +12689,8 @@
       <c r="U200" s="14" t="n"/>
       <c r="V200" s="14" t="n"/>
       <c r="W200" s="14" t="n"/>
+      <c r="X200" s="14" t="n"/>
+      <c r="Y200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="10" t="inlineStr">
@@ -12318,6 +12741,8 @@
       <c r="U201" s="14" t="n"/>
       <c r="V201" s="14" t="n"/>
       <c r="W201" s="14" t="n"/>
+      <c r="X201" s="14" t="n"/>
+      <c r="Y201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="10" t="inlineStr">
@@ -12351,13 +12776,13 @@
       <c r="H202" s="14" t="n"/>
       <c r="I202" s="14" t="n"/>
       <c r="J202" s="14" t="n"/>
-      <c r="K202" s="13" t="inlineStr">
+      <c r="K202" s="14" t="n"/>
+      <c r="L202" s="14" t="n"/>
+      <c r="M202" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L202" s="14" t="n"/>
-      <c r="M202" s="14" t="n"/>
       <c r="N202" s="14" t="n"/>
       <c r="O202" s="14" t="n"/>
       <c r="P202" s="14" t="n"/>
@@ -12368,6 +12793,8 @@
       <c r="U202" s="14" t="n"/>
       <c r="V202" s="14" t="n"/>
       <c r="W202" s="14" t="n"/>
+      <c r="X202" s="14" t="n"/>
+      <c r="Y202" s="14" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
@@ -12405,13 +12832,13 @@
       <c r="H203" s="14" t="n"/>
       <c r="I203" s="14" t="n"/>
       <c r="J203" s="14" t="n"/>
-      <c r="K203" s="13" t="inlineStr">
+      <c r="K203" s="14" t="n"/>
+      <c r="L203" s="14" t="n"/>
+      <c r="M203" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L203" s="14" t="n"/>
-      <c r="M203" s="14" t="n"/>
       <c r="N203" s="14" t="n"/>
       <c r="O203" s="14" t="n"/>
       <c r="P203" s="14" t="n"/>
@@ -12422,6 +12849,8 @@
       <c r="U203" s="14" t="n"/>
       <c r="V203" s="14" t="n"/>
       <c r="W203" s="14" t="n"/>
+      <c r="X203" s="14" t="n"/>
+      <c r="Y203" s="14" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
@@ -12468,6 +12897,8 @@
       <c r="U204" s="14" t="n"/>
       <c r="V204" s="14" t="n"/>
       <c r="W204" s="14" t="n"/>
+      <c r="X204" s="14" t="n"/>
+      <c r="Y204" s="14" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
@@ -12505,13 +12936,13 @@
       <c r="H205" s="14" t="n"/>
       <c r="I205" s="14" t="n"/>
       <c r="J205" s="14" t="n"/>
-      <c r="K205" s="13" t="inlineStr">
+      <c r="K205" s="14" t="n"/>
+      <c r="L205" s="14" t="n"/>
+      <c r="M205" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L205" s="14" t="n"/>
-      <c r="M205" s="14" t="n"/>
       <c r="N205" s="14" t="n"/>
       <c r="O205" s="14" t="n"/>
       <c r="P205" s="14" t="n"/>
@@ -12522,6 +12953,8 @@
       <c r="U205" s="14" t="n"/>
       <c r="V205" s="14" t="n"/>
       <c r="W205" s="14" t="n"/>
+      <c r="X205" s="14" t="n"/>
+      <c r="Y205" s="14" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="10" t="inlineStr">
@@ -12559,13 +12992,13 @@
       <c r="H206" s="14" t="n"/>
       <c r="I206" s="14" t="n"/>
       <c r="J206" s="14" t="n"/>
-      <c r="K206" s="13" t="inlineStr">
+      <c r="K206" s="14" t="n"/>
+      <c r="L206" s="14" t="n"/>
+      <c r="M206" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L206" s="14" t="n"/>
-      <c r="M206" s="14" t="n"/>
       <c r="N206" s="14" t="n"/>
       <c r="O206" s="14" t="n"/>
       <c r="P206" s="14" t="n"/>
@@ -12576,6 +13009,8 @@
       <c r="U206" s="14" t="n"/>
       <c r="V206" s="14" t="n"/>
       <c r="W206" s="14" t="n"/>
+      <c r="X206" s="14" t="n"/>
+      <c r="Y206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="10" t="inlineStr">
@@ -12613,13 +13048,13 @@
       <c r="H207" s="14" t="n"/>
       <c r="I207" s="14" t="n"/>
       <c r="J207" s="14" t="n"/>
-      <c r="K207" s="13" t="inlineStr">
+      <c r="K207" s="14" t="n"/>
+      <c r="L207" s="14" t="n"/>
+      <c r="M207" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L207" s="14" t="n"/>
-      <c r="M207" s="14" t="n"/>
       <c r="N207" s="14" t="n"/>
       <c r="O207" s="14" t="n"/>
       <c r="P207" s="14" t="n"/>
@@ -12630,6 +13065,8 @@
       <c r="U207" s="14" t="n"/>
       <c r="V207" s="14" t="n"/>
       <c r="W207" s="14" t="n"/>
+      <c r="X207" s="14" t="n"/>
+      <c r="Y207" s="14" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
@@ -12667,13 +13104,13 @@
       <c r="H208" s="14" t="n"/>
       <c r="I208" s="14" t="n"/>
       <c r="J208" s="14" t="n"/>
-      <c r="K208" s="13" t="inlineStr">
+      <c r="K208" s="14" t="n"/>
+      <c r="L208" s="14" t="n"/>
+      <c r="M208" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L208" s="14" t="n"/>
-      <c r="M208" s="14" t="n"/>
       <c r="N208" s="14" t="n"/>
       <c r="O208" s="14" t="n"/>
       <c r="P208" s="14" t="n"/>
@@ -12684,6 +13121,8 @@
       <c r="U208" s="14" t="n"/>
       <c r="V208" s="14" t="n"/>
       <c r="W208" s="14" t="n"/>
+      <c r="X208" s="14" t="n"/>
+      <c r="Y208" s="14" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
@@ -12717,13 +13156,13 @@
       <c r="H209" s="14" t="n"/>
       <c r="I209" s="14" t="n"/>
       <c r="J209" s="14" t="n"/>
-      <c r="K209" s="13" t="inlineStr">
+      <c r="K209" s="14" t="n"/>
+      <c r="L209" s="14" t="n"/>
+      <c r="M209" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L209" s="14" t="n"/>
-      <c r="M209" s="14" t="n"/>
       <c r="N209" s="14" t="n"/>
       <c r="O209" s="14" t="n"/>
       <c r="P209" s="14" t="n"/>
@@ -12734,6 +13173,8 @@
       <c r="U209" s="14" t="n"/>
       <c r="V209" s="14" t="n"/>
       <c r="W209" s="14" t="n"/>
+      <c r="X209" s="14" t="n"/>
+      <c r="Y209" s="14" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
@@ -12771,13 +13212,13 @@
       <c r="H210" s="14" t="n"/>
       <c r="I210" s="14" t="n"/>
       <c r="J210" s="14" t="n"/>
-      <c r="K210" s="13" t="inlineStr">
+      <c r="K210" s="14" t="n"/>
+      <c r="L210" s="14" t="n"/>
+      <c r="M210" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L210" s="14" t="n"/>
-      <c r="M210" s="14" t="n"/>
       <c r="N210" s="14" t="n"/>
       <c r="O210" s="14" t="n"/>
       <c r="P210" s="14" t="n"/>
@@ -12788,6 +13229,8 @@
       <c r="U210" s="14" t="n"/>
       <c r="V210" s="14" t="n"/>
       <c r="W210" s="14" t="n"/>
+      <c r="X210" s="14" t="n"/>
+      <c r="Y210" s="14" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
@@ -12821,13 +13264,13 @@
       <c r="H211" s="14" t="n"/>
       <c r="I211" s="14" t="n"/>
       <c r="J211" s="14" t="n"/>
-      <c r="K211" s="13" t="inlineStr">
+      <c r="K211" s="14" t="n"/>
+      <c r="L211" s="14" t="n"/>
+      <c r="M211" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L211" s="14" t="n"/>
-      <c r="M211" s="14" t="n"/>
       <c r="N211" s="14" t="n"/>
       <c r="O211" s="14" t="n"/>
       <c r="P211" s="14" t="n"/>
@@ -12838,6 +13281,8 @@
       <c r="U211" s="14" t="n"/>
       <c r="V211" s="14" t="n"/>
       <c r="W211" s="14" t="n"/>
+      <c r="X211" s="14" t="n"/>
+      <c r="Y211" s="14" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
@@ -12875,13 +13320,13 @@
       <c r="H212" s="14" t="n"/>
       <c r="I212" s="14" t="n"/>
       <c r="J212" s="14" t="n"/>
-      <c r="K212" s="13" t="inlineStr">
+      <c r="K212" s="14" t="n"/>
+      <c r="L212" s="14" t="n"/>
+      <c r="M212" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L212" s="14" t="n"/>
-      <c r="M212" s="14" t="n"/>
       <c r="N212" s="14" t="n"/>
       <c r="O212" s="14" t="n"/>
       <c r="P212" s="14" t="n"/>
@@ -12892,6 +13337,8 @@
       <c r="U212" s="14" t="n"/>
       <c r="V212" s="14" t="n"/>
       <c r="W212" s="14" t="n"/>
+      <c r="X212" s="14" t="n"/>
+      <c r="Y212" s="14" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
@@ -12929,13 +13376,13 @@
       <c r="H213" s="14" t="n"/>
       <c r="I213" s="14" t="n"/>
       <c r="J213" s="14" t="n"/>
-      <c r="K213" s="13" t="inlineStr">
+      <c r="K213" s="14" t="n"/>
+      <c r="L213" s="14" t="n"/>
+      <c r="M213" s="13" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="L213" s="14" t="n"/>
-      <c r="M213" s="14" t="n"/>
       <c r="N213" s="14" t="n"/>
       <c r="O213" s="14" t="n"/>
       <c r="P213" s="14" t="n"/>
@@ -12946,6 +13393,8 @@
       <c r="U213" s="14" t="n"/>
       <c r="V213" s="14" t="n"/>
       <c r="W213" s="14" t="n"/>
+      <c r="X213" s="14" t="n"/>
+      <c r="Y213" s="14" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
@@ -12983,13 +13432,13 @@
       <c r="H214" s="14" t="n"/>
       <c r="I214" s="14" t="n"/>
       <c r="J214" s="14" t="n"/>
-      <c r="K214" s="13" t="inlineStr">
+      <c r="K214" s="14" t="n"/>
+      <c r="L214" s="14" t="n"/>
+      <c r="M214" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L214" s="14" t="n"/>
-      <c r="M214" s="14" t="n"/>
       <c r="N214" s="14" t="n"/>
       <c r="O214" s="14" t="n"/>
       <c r="P214" s="14" t="n"/>
@@ -13000,6 +13449,8 @@
       <c r="U214" s="14" t="n"/>
       <c r="V214" s="14" t="n"/>
       <c r="W214" s="14" t="n"/>
+      <c r="X214" s="14" t="n"/>
+      <c r="Y214" s="14" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
@@ -13037,13 +13488,13 @@
       <c r="H215" s="14" t="n"/>
       <c r="I215" s="14" t="n"/>
       <c r="J215" s="14" t="n"/>
-      <c r="K215" s="13" t="inlineStr">
+      <c r="K215" s="14" t="n"/>
+      <c r="L215" s="14" t="n"/>
+      <c r="M215" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L215" s="14" t="n"/>
-      <c r="M215" s="14" t="n"/>
       <c r="N215" s="14" t="n"/>
       <c r="O215" s="14" t="n"/>
       <c r="P215" s="14" t="n"/>
@@ -13054,6 +13505,8 @@
       <c r="U215" s="14" t="n"/>
       <c r="V215" s="14" t="n"/>
       <c r="W215" s="14" t="n"/>
+      <c r="X215" s="14" t="n"/>
+      <c r="Y215" s="14" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
@@ -13100,6 +13553,8 @@
       <c r="U216" s="14" t="n"/>
       <c r="V216" s="14" t="n"/>
       <c r="W216" s="14" t="n"/>
+      <c r="X216" s="14" t="n"/>
+      <c r="Y216" s="14" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
@@ -13137,13 +13592,13 @@
       <c r="H217" s="14" t="n"/>
       <c r="I217" s="14" t="n"/>
       <c r="J217" s="14" t="n"/>
-      <c r="K217" s="13" t="inlineStr">
+      <c r="K217" s="14" t="n"/>
+      <c r="L217" s="14" t="n"/>
+      <c r="M217" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L217" s="14" t="n"/>
-      <c r="M217" s="14" t="n"/>
       <c r="N217" s="14" t="n"/>
       <c r="O217" s="14" t="n"/>
       <c r="P217" s="14" t="n"/>
@@ -13154,6 +13609,8 @@
       <c r="U217" s="14" t="n"/>
       <c r="V217" s="14" t="n"/>
       <c r="W217" s="14" t="n"/>
+      <c r="X217" s="14" t="n"/>
+      <c r="Y217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
@@ -13187,13 +13644,13 @@
       <c r="H218" s="14" t="n"/>
       <c r="I218" s="14" t="n"/>
       <c r="J218" s="14" t="n"/>
-      <c r="K218" s="13" t="inlineStr">
+      <c r="K218" s="14" t="n"/>
+      <c r="L218" s="14" t="n"/>
+      <c r="M218" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L218" s="14" t="n"/>
-      <c r="M218" s="14" t="n"/>
       <c r="N218" s="14" t="n"/>
       <c r="O218" s="14" t="n"/>
       <c r="P218" s="14" t="n"/>
@@ -13204,6 +13661,8 @@
       <c r="U218" s="14" t="n"/>
       <c r="V218" s="14" t="n"/>
       <c r="W218" s="14" t="n"/>
+      <c r="X218" s="14" t="n"/>
+      <c r="Y218" s="14" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="10" t="inlineStr">
@@ -13241,13 +13700,13 @@
       <c r="H219" s="14" t="n"/>
       <c r="I219" s="14" t="n"/>
       <c r="J219" s="14" t="n"/>
-      <c r="K219" s="13" t="inlineStr">
+      <c r="K219" s="14" t="n"/>
+      <c r="L219" s="14" t="n"/>
+      <c r="M219" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L219" s="14" t="n"/>
-      <c r="M219" s="14" t="n"/>
       <c r="N219" s="14" t="n"/>
       <c r="O219" s="14" t="n"/>
       <c r="P219" s="14" t="n"/>
@@ -13258,6 +13717,8 @@
       <c r="U219" s="14" t="n"/>
       <c r="V219" s="14" t="n"/>
       <c r="W219" s="14" t="n"/>
+      <c r="X219" s="14" t="n"/>
+      <c r="Y219" s="14" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
@@ -13295,13 +13756,13 @@
       <c r="H220" s="14" t="n"/>
       <c r="I220" s="14" t="n"/>
       <c r="J220" s="14" t="n"/>
-      <c r="K220" s="13" t="inlineStr">
+      <c r="K220" s="14" t="n"/>
+      <c r="L220" s="14" t="n"/>
+      <c r="M220" s="13" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="L220" s="14" t="n"/>
-      <c r="M220" s="14" t="n"/>
       <c r="N220" s="14" t="n"/>
       <c r="O220" s="14" t="n"/>
       <c r="P220" s="14" t="n"/>
@@ -13312,6 +13773,8 @@
       <c r="U220" s="14" t="n"/>
       <c r="V220" s="14" t="n"/>
       <c r="W220" s="14" t="n"/>
+      <c r="X220" s="14" t="n"/>
+      <c r="Y220" s="14" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="10" t="inlineStr">
@@ -13349,13 +13812,13 @@
       <c r="H221" s="14" t="n"/>
       <c r="I221" s="14" t="n"/>
       <c r="J221" s="14" t="n"/>
-      <c r="K221" s="13" t="inlineStr">
+      <c r="K221" s="14" t="n"/>
+      <c r="L221" s="14" t="n"/>
+      <c r="M221" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L221" s="14" t="n"/>
-      <c r="M221" s="14" t="n"/>
       <c r="N221" s="14" t="n"/>
       <c r="O221" s="14" t="n"/>
       <c r="P221" s="14" t="n"/>
@@ -13366,6 +13829,8 @@
       <c r="U221" s="14" t="n"/>
       <c r="V221" s="14" t="n"/>
       <c r="W221" s="14" t="n"/>
+      <c r="X221" s="14" t="n"/>
+      <c r="Y221" s="14" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="10" t="inlineStr">
@@ -13403,13 +13868,13 @@
       <c r="H222" s="14" t="n"/>
       <c r="I222" s="14" t="n"/>
       <c r="J222" s="14" t="n"/>
-      <c r="K222" s="13" t="inlineStr">
+      <c r="K222" s="14" t="n"/>
+      <c r="L222" s="14" t="n"/>
+      <c r="M222" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L222" s="14" t="n"/>
-      <c r="M222" s="14" t="n"/>
       <c r="N222" s="14" t="n"/>
       <c r="O222" s="14" t="n"/>
       <c r="P222" s="14" t="n"/>
@@ -13420,6 +13885,8 @@
       <c r="U222" s="14" t="n"/>
       <c r="V222" s="14" t="n"/>
       <c r="W222" s="14" t="n"/>
+      <c r="X222" s="14" t="n"/>
+      <c r="Y222" s="14" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
@@ -13457,13 +13924,13 @@
       <c r="H223" s="14" t="n"/>
       <c r="I223" s="14" t="n"/>
       <c r="J223" s="14" t="n"/>
-      <c r="K223" s="13" t="inlineStr">
+      <c r="K223" s="14" t="n"/>
+      <c r="L223" s="14" t="n"/>
+      <c r="M223" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L223" s="14" t="n"/>
-      <c r="M223" s="14" t="n"/>
       <c r="N223" s="14" t="n"/>
       <c r="O223" s="14" t="n"/>
       <c r="P223" s="14" t="n"/>
@@ -13474,6 +13941,8 @@
       <c r="U223" s="14" t="n"/>
       <c r="V223" s="14" t="n"/>
       <c r="W223" s="14" t="n"/>
+      <c r="X223" s="14" t="n"/>
+      <c r="Y223" s="14" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="10" t="inlineStr">
@@ -13507,13 +13976,13 @@
       <c r="H224" s="14" t="n"/>
       <c r="I224" s="14" t="n"/>
       <c r="J224" s="14" t="n"/>
-      <c r="K224" s="13" t="inlineStr">
+      <c r="K224" s="14" t="n"/>
+      <c r="L224" s="14" t="n"/>
+      <c r="M224" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L224" s="14" t="n"/>
-      <c r="M224" s="14" t="n"/>
       <c r="N224" s="14" t="n"/>
       <c r="O224" s="14" t="n"/>
       <c r="P224" s="14" t="n"/>
@@ -13524,6 +13993,8 @@
       <c r="U224" s="14" t="n"/>
       <c r="V224" s="14" t="n"/>
       <c r="W224" s="14" t="n"/>
+      <c r="X224" s="14" t="n"/>
+      <c r="Y224" s="14" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
@@ -13557,13 +14028,13 @@
       <c r="H225" s="14" t="n"/>
       <c r="I225" s="14" t="n"/>
       <c r="J225" s="14" t="n"/>
-      <c r="K225" s="13" t="inlineStr">
+      <c r="K225" s="14" t="n"/>
+      <c r="L225" s="14" t="n"/>
+      <c r="M225" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L225" s="14" t="n"/>
-      <c r="M225" s="14" t="n"/>
       <c r="N225" s="14" t="n"/>
       <c r="O225" s="14" t="n"/>
       <c r="P225" s="14" t="n"/>
@@ -13574,6 +14045,8 @@
       <c r="U225" s="14" t="n"/>
       <c r="V225" s="14" t="n"/>
       <c r="W225" s="14" t="n"/>
+      <c r="X225" s="14" t="n"/>
+      <c r="Y225" s="14" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="10" t="inlineStr">
@@ -13611,13 +14084,13 @@
       <c r="H226" s="14" t="n"/>
       <c r="I226" s="14" t="n"/>
       <c r="J226" s="14" t="n"/>
-      <c r="K226" s="13" t="inlineStr">
+      <c r="K226" s="14" t="n"/>
+      <c r="L226" s="14" t="n"/>
+      <c r="M226" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L226" s="14" t="n"/>
-      <c r="M226" s="14" t="n"/>
       <c r="N226" s="14" t="n"/>
       <c r="O226" s="14" t="n"/>
       <c r="P226" s="14" t="n"/>
@@ -13628,6 +14101,8 @@
       <c r="U226" s="14" t="n"/>
       <c r="V226" s="14" t="n"/>
       <c r="W226" s="14" t="n"/>
+      <c r="X226" s="14" t="n"/>
+      <c r="Y226" s="14" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="10" t="inlineStr">
@@ -13665,13 +14140,13 @@
       <c r="H227" s="14" t="n"/>
       <c r="I227" s="14" t="n"/>
       <c r="J227" s="14" t="n"/>
-      <c r="K227" s="13" t="inlineStr">
+      <c r="K227" s="14" t="n"/>
+      <c r="L227" s="14" t="n"/>
+      <c r="M227" s="13" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="L227" s="14" t="n"/>
-      <c r="M227" s="14" t="n"/>
       <c r="N227" s="14" t="n"/>
       <c r="O227" s="14" t="n"/>
       <c r="P227" s="14" t="n"/>
@@ -13682,6 +14157,8 @@
       <c r="U227" s="14" t="n"/>
       <c r="V227" s="14" t="n"/>
       <c r="W227" s="14" t="n"/>
+      <c r="X227" s="14" t="n"/>
+      <c r="Y227" s="14" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
@@ -13719,13 +14196,13 @@
       <c r="H228" s="14" t="n"/>
       <c r="I228" s="14" t="n"/>
       <c r="J228" s="14" t="n"/>
-      <c r="K228" s="13" t="inlineStr">
+      <c r="K228" s="14" t="n"/>
+      <c r="L228" s="14" t="n"/>
+      <c r="M228" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L228" s="14" t="n"/>
-      <c r="M228" s="14" t="n"/>
       <c r="N228" s="14" t="n"/>
       <c r="O228" s="14" t="n"/>
       <c r="P228" s="14" t="n"/>
@@ -13736,6 +14213,8 @@
       <c r="U228" s="14" t="n"/>
       <c r="V228" s="14" t="n"/>
       <c r="W228" s="14" t="n"/>
+      <c r="X228" s="14" t="n"/>
+      <c r="Y228" s="14" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
@@ -13769,13 +14248,13 @@
       <c r="H229" s="14" t="n"/>
       <c r="I229" s="14" t="n"/>
       <c r="J229" s="14" t="n"/>
-      <c r="K229" s="13" t="inlineStr">
+      <c r="K229" s="14" t="n"/>
+      <c r="L229" s="14" t="n"/>
+      <c r="M229" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L229" s="14" t="n"/>
-      <c r="M229" s="14" t="n"/>
       <c r="N229" s="14" t="n"/>
       <c r="O229" s="14" t="n"/>
       <c r="P229" s="14" t="n"/>
@@ -13786,6 +14265,8 @@
       <c r="U229" s="14" t="n"/>
       <c r="V229" s="14" t="n"/>
       <c r="W229" s="14" t="n"/>
+      <c r="X229" s="14" t="n"/>
+      <c r="Y229" s="14" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
@@ -13823,13 +14304,13 @@
       <c r="H230" s="14" t="n"/>
       <c r="I230" s="14" t="n"/>
       <c r="J230" s="14" t="n"/>
-      <c r="K230" s="13" t="inlineStr">
+      <c r="K230" s="14" t="n"/>
+      <c r="L230" s="14" t="n"/>
+      <c r="M230" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L230" s="14" t="n"/>
-      <c r="M230" s="14" t="n"/>
       <c r="N230" s="14" t="n"/>
       <c r="O230" s="14" t="n"/>
       <c r="P230" s="14" t="n"/>
@@ -13840,6 +14321,8 @@
       <c r="U230" s="14" t="n"/>
       <c r="V230" s="14" t="n"/>
       <c r="W230" s="14" t="n"/>
+      <c r="X230" s="14" t="n"/>
+      <c r="Y230" s="14" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
@@ -13877,13 +14360,13 @@
       <c r="H231" s="14" t="n"/>
       <c r="I231" s="14" t="n"/>
       <c r="J231" s="14" t="n"/>
-      <c r="K231" s="13" t="inlineStr">
+      <c r="K231" s="14" t="n"/>
+      <c r="L231" s="14" t="n"/>
+      <c r="M231" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L231" s="14" t="n"/>
-      <c r="M231" s="14" t="n"/>
       <c r="N231" s="14" t="n"/>
       <c r="O231" s="14" t="n"/>
       <c r="P231" s="14" t="n"/>
@@ -13894,6 +14377,8 @@
       <c r="U231" s="14" t="n"/>
       <c r="V231" s="14" t="n"/>
       <c r="W231" s="14" t="n"/>
+      <c r="X231" s="14" t="n"/>
+      <c r="Y231" s="14" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
@@ -13931,13 +14416,13 @@
       <c r="H232" s="14" t="n"/>
       <c r="I232" s="14" t="n"/>
       <c r="J232" s="14" t="n"/>
-      <c r="K232" s="13" t="inlineStr">
+      <c r="K232" s="14" t="n"/>
+      <c r="L232" s="14" t="n"/>
+      <c r="M232" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L232" s="14" t="n"/>
-      <c r="M232" s="14" t="n"/>
       <c r="N232" s="14" t="n"/>
       <c r="O232" s="14" t="n"/>
       <c r="P232" s="14" t="n"/>
@@ -13948,6 +14433,8 @@
       <c r="U232" s="14" t="n"/>
       <c r="V232" s="14" t="n"/>
       <c r="W232" s="14" t="n"/>
+      <c r="X232" s="14" t="n"/>
+      <c r="Y232" s="14" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
@@ -13998,6 +14485,8 @@
       <c r="U233" s="14" t="n"/>
       <c r="V233" s="14" t="n"/>
       <c r="W233" s="14" t="n"/>
+      <c r="X233" s="14" t="n"/>
+      <c r="Y233" s="14" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="10" t="inlineStr">
@@ -14035,13 +14524,13 @@
       <c r="H234" s="14" t="n"/>
       <c r="I234" s="14" t="n"/>
       <c r="J234" s="14" t="n"/>
-      <c r="K234" s="13" t="inlineStr">
+      <c r="K234" s="14" t="n"/>
+      <c r="L234" s="14" t="n"/>
+      <c r="M234" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L234" s="14" t="n"/>
-      <c r="M234" s="14" t="n"/>
       <c r="N234" s="14" t="n"/>
       <c r="O234" s="14" t="n"/>
       <c r="P234" s="14" t="n"/>
@@ -14052,6 +14541,8 @@
       <c r="U234" s="14" t="n"/>
       <c r="V234" s="14" t="n"/>
       <c r="W234" s="14" t="n"/>
+      <c r="X234" s="14" t="n"/>
+      <c r="Y234" s="14" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="10" t="inlineStr">
@@ -14089,13 +14580,13 @@
       <c r="H235" s="14" t="n"/>
       <c r="I235" s="14" t="n"/>
       <c r="J235" s="14" t="n"/>
-      <c r="K235" s="13" t="inlineStr">
+      <c r="K235" s="14" t="n"/>
+      <c r="L235" s="14" t="n"/>
+      <c r="M235" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L235" s="14" t="n"/>
-      <c r="M235" s="14" t="n"/>
       <c r="N235" s="14" t="n"/>
       <c r="O235" s="14" t="n"/>
       <c r="P235" s="14" t="n"/>
@@ -14106,6 +14597,8 @@
       <c r="U235" s="14" t="n"/>
       <c r="V235" s="14" t="n"/>
       <c r="W235" s="14" t="n"/>
+      <c r="X235" s="14" t="n"/>
+      <c r="Y235" s="14" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="10" t="inlineStr">
@@ -14139,13 +14632,13 @@
       <c r="H236" s="14" t="n"/>
       <c r="I236" s="14" t="n"/>
       <c r="J236" s="14" t="n"/>
-      <c r="K236" s="13" t="inlineStr">
+      <c r="K236" s="14" t="n"/>
+      <c r="L236" s="14" t="n"/>
+      <c r="M236" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L236" s="14" t="n"/>
-      <c r="M236" s="14" t="n"/>
       <c r="N236" s="14" t="n"/>
       <c r="O236" s="14" t="n"/>
       <c r="P236" s="14" t="n"/>
@@ -14156,6 +14649,8 @@
       <c r="U236" s="14" t="n"/>
       <c r="V236" s="14" t="n"/>
       <c r="W236" s="14" t="n"/>
+      <c r="X236" s="14" t="n"/>
+      <c r="Y236" s="14" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="10" t="inlineStr">
@@ -14189,24 +14684,24 @@
       <c r="H237" s="14" t="n"/>
       <c r="I237" s="14" t="n"/>
       <c r="J237" s="14" t="n"/>
-      <c r="K237" s="13" t="inlineStr">
+      <c r="K237" s="14" t="n"/>
+      <c r="L237" s="14" t="n"/>
+      <c r="M237" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L237" s="13" t="inlineStr">
+      <c r="N237" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M237" s="14" t="n"/>
-      <c r="N237" s="13" t="inlineStr">
+      <c r="O237" s="14" t="n"/>
+      <c r="P237" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O237" s="14" t="n"/>
-      <c r="P237" s="14" t="n"/>
       <c r="Q237" s="14" t="n"/>
       <c r="R237" s="14" t="n"/>
       <c r="S237" s="14" t="n"/>
@@ -14214,6 +14709,8 @@
       <c r="U237" s="14" t="n"/>
       <c r="V237" s="14" t="n"/>
       <c r="W237" s="14" t="n"/>
+      <c r="X237" s="14" t="n"/>
+      <c r="Y237" s="14" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="10" t="inlineStr">
@@ -14247,13 +14744,13 @@
       <c r="H238" s="14" t="n"/>
       <c r="I238" s="14" t="n"/>
       <c r="J238" s="14" t="n"/>
-      <c r="K238" s="13" t="inlineStr">
+      <c r="K238" s="14" t="n"/>
+      <c r="L238" s="14" t="n"/>
+      <c r="M238" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L238" s="14" t="n"/>
-      <c r="M238" s="14" t="n"/>
       <c r="N238" s="14" t="n"/>
       <c r="O238" s="14" t="n"/>
       <c r="P238" s="14" t="n"/>
@@ -14264,6 +14761,8 @@
       <c r="U238" s="14" t="n"/>
       <c r="V238" s="14" t="n"/>
       <c r="W238" s="14" t="n"/>
+      <c r="X238" s="14" t="n"/>
+      <c r="Y238" s="14" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="10" t="inlineStr">
@@ -14310,6 +14809,8 @@
       <c r="U239" s="14" t="n"/>
       <c r="V239" s="14" t="n"/>
       <c r="W239" s="14" t="n"/>
+      <c r="X239" s="14" t="n"/>
+      <c r="Y239" s="14" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="10" t="inlineStr">
@@ -14347,13 +14848,13 @@
       <c r="H240" s="14" t="n"/>
       <c r="I240" s="14" t="n"/>
       <c r="J240" s="14" t="n"/>
-      <c r="K240" s="13" t="inlineStr">
+      <c r="K240" s="14" t="n"/>
+      <c r="L240" s="14" t="n"/>
+      <c r="M240" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L240" s="14" t="n"/>
-      <c r="M240" s="14" t="n"/>
       <c r="N240" s="14" t="n"/>
       <c r="O240" s="14" t="n"/>
       <c r="P240" s="14" t="n"/>
@@ -14364,6 +14865,8 @@
       <c r="U240" s="14" t="n"/>
       <c r="V240" s="14" t="n"/>
       <c r="W240" s="14" t="n"/>
+      <c r="X240" s="14" t="n"/>
+      <c r="Y240" s="14" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
@@ -14401,13 +14904,13 @@
       <c r="H241" s="14" t="n"/>
       <c r="I241" s="14" t="n"/>
       <c r="J241" s="14" t="n"/>
-      <c r="K241" s="13" t="inlineStr">
+      <c r="K241" s="14" t="n"/>
+      <c r="L241" s="14" t="n"/>
+      <c r="M241" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L241" s="14" t="n"/>
-      <c r="M241" s="14" t="n"/>
       <c r="N241" s="14" t="n"/>
       <c r="O241" s="14" t="n"/>
       <c r="P241" s="14" t="n"/>
@@ -14418,6 +14921,8 @@
       <c r="U241" s="14" t="n"/>
       <c r="V241" s="14" t="n"/>
       <c r="W241" s="14" t="n"/>
+      <c r="X241" s="14" t="n"/>
+      <c r="Y241" s="14" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
@@ -14455,13 +14960,13 @@
       <c r="H242" s="14" t="n"/>
       <c r="I242" s="14" t="n"/>
       <c r="J242" s="14" t="n"/>
-      <c r="K242" s="13" t="inlineStr">
+      <c r="K242" s="14" t="n"/>
+      <c r="L242" s="14" t="n"/>
+      <c r="M242" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L242" s="14" t="n"/>
-      <c r="M242" s="14" t="n"/>
       <c r="N242" s="14" t="n"/>
       <c r="O242" s="14" t="n"/>
       <c r="P242" s="14" t="n"/>
@@ -14472,6 +14977,8 @@
       <c r="U242" s="14" t="n"/>
       <c r="V242" s="14" t="n"/>
       <c r="W242" s="14" t="n"/>
+      <c r="X242" s="14" t="n"/>
+      <c r="Y242" s="14" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
@@ -14509,13 +15016,13 @@
       <c r="H243" s="14" t="n"/>
       <c r="I243" s="14" t="n"/>
       <c r="J243" s="14" t="n"/>
-      <c r="K243" s="13" t="inlineStr">
+      <c r="K243" s="14" t="n"/>
+      <c r="L243" s="14" t="n"/>
+      <c r="M243" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L243" s="14" t="n"/>
-      <c r="M243" s="14" t="n"/>
       <c r="N243" s="14" t="n"/>
       <c r="O243" s="14" t="n"/>
       <c r="P243" s="14" t="n"/>
@@ -14526,6 +15033,8 @@
       <c r="U243" s="14" t="n"/>
       <c r="V243" s="14" t="n"/>
       <c r="W243" s="14" t="n"/>
+      <c r="X243" s="14" t="n"/>
+      <c r="Y243" s="14" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="10" t="inlineStr">
@@ -14563,13 +15072,13 @@
       <c r="H244" s="14" t="n"/>
       <c r="I244" s="14" t="n"/>
       <c r="J244" s="14" t="n"/>
-      <c r="K244" s="13" t="inlineStr">
+      <c r="K244" s="14" t="n"/>
+      <c r="L244" s="14" t="n"/>
+      <c r="M244" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L244" s="14" t="n"/>
-      <c r="M244" s="14" t="n"/>
       <c r="N244" s="14" t="n"/>
       <c r="O244" s="14" t="n"/>
       <c r="P244" s="14" t="n"/>
@@ -14580,6 +15089,8 @@
       <c r="U244" s="14" t="n"/>
       <c r="V244" s="14" t="n"/>
       <c r="W244" s="14" t="n"/>
+      <c r="X244" s="14" t="n"/>
+      <c r="Y244" s="14" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="10" t="inlineStr">
@@ -14626,6 +15137,8 @@
       <c r="U245" s="14" t="n"/>
       <c r="V245" s="14" t="n"/>
       <c r="W245" s="14" t="n"/>
+      <c r="X245" s="14" t="n"/>
+      <c r="Y245" s="14" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="10" t="inlineStr">
@@ -14663,13 +15176,13 @@
       <c r="H246" s="14" t="n"/>
       <c r="I246" s="14" t="n"/>
       <c r="J246" s="14" t="n"/>
-      <c r="K246" s="13" t="inlineStr">
+      <c r="K246" s="14" t="n"/>
+      <c r="L246" s="14" t="n"/>
+      <c r="M246" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L246" s="14" t="n"/>
-      <c r="M246" s="14" t="n"/>
       <c r="N246" s="14" t="n"/>
       <c r="O246" s="14" t="n"/>
       <c r="P246" s="14" t="n"/>
@@ -14680,6 +15193,8 @@
       <c r="U246" s="14" t="n"/>
       <c r="V246" s="14" t="n"/>
       <c r="W246" s="14" t="n"/>
+      <c r="X246" s="14" t="n"/>
+      <c r="Y246" s="14" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
@@ -14717,13 +15232,13 @@
       <c r="H247" s="14" t="n"/>
       <c r="I247" s="14" t="n"/>
       <c r="J247" s="14" t="n"/>
-      <c r="K247" s="13" t="inlineStr">
+      <c r="K247" s="14" t="n"/>
+      <c r="L247" s="14" t="n"/>
+      <c r="M247" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L247" s="14" t="n"/>
-      <c r="M247" s="14" t="n"/>
       <c r="N247" s="14" t="n"/>
       <c r="O247" s="14" t="n"/>
       <c r="P247" s="14" t="n"/>
@@ -14734,6 +15249,8 @@
       <c r="U247" s="14" t="n"/>
       <c r="V247" s="14" t="n"/>
       <c r="W247" s="14" t="n"/>
+      <c r="X247" s="14" t="n"/>
+      <c r="Y247" s="14" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="10" t="inlineStr">
@@ -14780,6 +15297,8 @@
       <c r="U248" s="14" t="n"/>
       <c r="V248" s="14" t="n"/>
       <c r="W248" s="14" t="n"/>
+      <c r="X248" s="14" t="n"/>
+      <c r="Y248" s="14" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
@@ -14813,13 +15332,13 @@
       <c r="H249" s="14" t="n"/>
       <c r="I249" s="14" t="n"/>
       <c r="J249" s="14" t="n"/>
-      <c r="K249" s="13" t="inlineStr">
+      <c r="K249" s="14" t="n"/>
+      <c r="L249" s="14" t="n"/>
+      <c r="M249" s="13" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="L249" s="14" t="n"/>
-      <c r="M249" s="14" t="n"/>
       <c r="N249" s="14" t="n"/>
       <c r="O249" s="14" t="n"/>
       <c r="P249" s="14" t="n"/>
@@ -14830,6 +15349,8 @@
       <c r="U249" s="14" t="n"/>
       <c r="V249" s="14" t="n"/>
       <c r="W249" s="14" t="n"/>
+      <c r="X249" s="14" t="n"/>
+      <c r="Y249" s="14" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
@@ -14863,13 +15384,13 @@
       <c r="H250" s="14" t="n"/>
       <c r="I250" s="14" t="n"/>
       <c r="J250" s="14" t="n"/>
-      <c r="K250" s="13" t="inlineStr">
+      <c r="K250" s="14" t="n"/>
+      <c r="L250" s="14" t="n"/>
+      <c r="M250" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L250" s="14" t="n"/>
-      <c r="M250" s="14" t="n"/>
       <c r="N250" s="14" t="n"/>
       <c r="O250" s="14" t="n"/>
       <c r="P250" s="14" t="n"/>
@@ -14880,6 +15401,8 @@
       <c r="U250" s="14" t="n"/>
       <c r="V250" s="14" t="n"/>
       <c r="W250" s="14" t="n"/>
+      <c r="X250" s="14" t="n"/>
+      <c r="Y250" s="14" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="10" t="inlineStr">
@@ -14917,13 +15440,13 @@
       <c r="H251" s="14" t="n"/>
       <c r="I251" s="14" t="n"/>
       <c r="J251" s="14" t="n"/>
-      <c r="K251" s="13" t="inlineStr">
+      <c r="K251" s="14" t="n"/>
+      <c r="L251" s="14" t="n"/>
+      <c r="M251" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L251" s="14" t="n"/>
-      <c r="M251" s="14" t="n"/>
       <c r="N251" s="14" t="n"/>
       <c r="O251" s="14" t="n"/>
       <c r="P251" s="14" t="n"/>
@@ -14934,6 +15457,8 @@
       <c r="U251" s="14" t="n"/>
       <c r="V251" s="14" t="n"/>
       <c r="W251" s="14" t="n"/>
+      <c r="X251" s="14" t="n"/>
+      <c r="Y251" s="14" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="10" t="inlineStr">
@@ -14980,6 +15505,8 @@
       <c r="U252" s="14" t="n"/>
       <c r="V252" s="14" t="n"/>
       <c r="W252" s="14" t="n"/>
+      <c r="X252" s="14" t="n"/>
+      <c r="Y252" s="14" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="10" t="inlineStr">
@@ -15017,13 +15544,13 @@
       <c r="H253" s="14" t="n"/>
       <c r="I253" s="14" t="n"/>
       <c r="J253" s="14" t="n"/>
-      <c r="K253" s="13" t="inlineStr">
+      <c r="K253" s="14" t="n"/>
+      <c r="L253" s="14" t="n"/>
+      <c r="M253" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L253" s="14" t="n"/>
-      <c r="M253" s="14" t="n"/>
       <c r="N253" s="14" t="n"/>
       <c r="O253" s="14" t="n"/>
       <c r="P253" s="14" t="n"/>
@@ -15034,6 +15561,8 @@
       <c r="U253" s="14" t="n"/>
       <c r="V253" s="14" t="n"/>
       <c r="W253" s="14" t="n"/>
+      <c r="X253" s="14" t="n"/>
+      <c r="Y253" s="14" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="10" t="inlineStr">
@@ -15071,13 +15600,13 @@
       <c r="H254" s="14" t="n"/>
       <c r="I254" s="14" t="n"/>
       <c r="J254" s="14" t="n"/>
-      <c r="K254" s="13" t="inlineStr">
+      <c r="K254" s="14" t="n"/>
+      <c r="L254" s="14" t="n"/>
+      <c r="M254" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L254" s="14" t="n"/>
-      <c r="M254" s="14" t="n"/>
       <c r="N254" s="14" t="n"/>
       <c r="O254" s="14" t="n"/>
       <c r="P254" s="14" t="n"/>
@@ -15088,6 +15617,8 @@
       <c r="U254" s="14" t="n"/>
       <c r="V254" s="14" t="n"/>
       <c r="W254" s="14" t="n"/>
+      <c r="X254" s="14" t="n"/>
+      <c r="Y254" s="14" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="10" t="inlineStr">
@@ -15125,13 +15656,13 @@
       <c r="H255" s="14" t="n"/>
       <c r="I255" s="14" t="n"/>
       <c r="J255" s="14" t="n"/>
-      <c r="K255" s="13" t="inlineStr">
+      <c r="K255" s="14" t="n"/>
+      <c r="L255" s="14" t="n"/>
+      <c r="M255" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L255" s="14" t="n"/>
-      <c r="M255" s="14" t="n"/>
       <c r="N255" s="14" t="n"/>
       <c r="O255" s="14" t="n"/>
       <c r="P255" s="14" t="n"/>
@@ -15142,6 +15673,8 @@
       <c r="U255" s="14" t="n"/>
       <c r="V255" s="14" t="n"/>
       <c r="W255" s="14" t="n"/>
+      <c r="X255" s="14" t="n"/>
+      <c r="Y255" s="14" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="10" t="inlineStr">
@@ -15179,13 +15712,13 @@
       <c r="H256" s="14" t="n"/>
       <c r="I256" s="14" t="n"/>
       <c r="J256" s="14" t="n"/>
-      <c r="K256" s="13" t="inlineStr">
+      <c r="K256" s="14" t="n"/>
+      <c r="L256" s="14" t="n"/>
+      <c r="M256" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L256" s="14" t="n"/>
-      <c r="M256" s="14" t="n"/>
       <c r="N256" s="14" t="n"/>
       <c r="O256" s="14" t="n"/>
       <c r="P256" s="14" t="n"/>
@@ -15196,6 +15729,8 @@
       <c r="U256" s="14" t="n"/>
       <c r="V256" s="14" t="n"/>
       <c r="W256" s="14" t="n"/>
+      <c r="X256" s="14" t="n"/>
+      <c r="Y256" s="14" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="10" t="inlineStr">
@@ -15233,13 +15768,13 @@
       <c r="H257" s="14" t="n"/>
       <c r="I257" s="14" t="n"/>
       <c r="J257" s="14" t="n"/>
-      <c r="K257" s="13" t="inlineStr">
+      <c r="K257" s="14" t="n"/>
+      <c r="L257" s="14" t="n"/>
+      <c r="M257" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L257" s="14" t="n"/>
-      <c r="M257" s="14" t="n"/>
       <c r="N257" s="14" t="n"/>
       <c r="O257" s="14" t="n"/>
       <c r="P257" s="14" t="n"/>
@@ -15250,6 +15785,8 @@
       <c r="U257" s="14" t="n"/>
       <c r="V257" s="14" t="n"/>
       <c r="W257" s="14" t="n"/>
+      <c r="X257" s="14" t="n"/>
+      <c r="Y257" s="14" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="10" t="inlineStr">
@@ -15287,13 +15824,13 @@
       <c r="H258" s="14" t="n"/>
       <c r="I258" s="14" t="n"/>
       <c r="J258" s="14" t="n"/>
-      <c r="K258" s="13" t="inlineStr">
+      <c r="K258" s="14" t="n"/>
+      <c r="L258" s="14" t="n"/>
+      <c r="M258" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L258" s="14" t="n"/>
-      <c r="M258" s="14" t="n"/>
       <c r="N258" s="14" t="n"/>
       <c r="O258" s="14" t="n"/>
       <c r="P258" s="14" t="n"/>
@@ -15304,6 +15841,8 @@
       <c r="U258" s="14" t="n"/>
       <c r="V258" s="14" t="n"/>
       <c r="W258" s="14" t="n"/>
+      <c r="X258" s="14" t="n"/>
+      <c r="Y258" s="14" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="10" t="inlineStr">
@@ -15341,13 +15880,13 @@
       <c r="H259" s="14" t="n"/>
       <c r="I259" s="14" t="n"/>
       <c r="J259" s="14" t="n"/>
-      <c r="K259" s="13" t="inlineStr">
+      <c r="K259" s="14" t="n"/>
+      <c r="L259" s="14" t="n"/>
+      <c r="M259" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L259" s="14" t="n"/>
-      <c r="M259" s="14" t="n"/>
       <c r="N259" s="14" t="n"/>
       <c r="O259" s="14" t="n"/>
       <c r="P259" s="14" t="n"/>
@@ -15358,6 +15897,8 @@
       <c r="U259" s="14" t="n"/>
       <c r="V259" s="14" t="n"/>
       <c r="W259" s="14" t="n"/>
+      <c r="X259" s="14" t="n"/>
+      <c r="Y259" s="14" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="10" t="inlineStr">
@@ -15395,13 +15936,13 @@
       <c r="H260" s="14" t="n"/>
       <c r="I260" s="14" t="n"/>
       <c r="J260" s="14" t="n"/>
-      <c r="K260" s="13" t="inlineStr">
+      <c r="K260" s="14" t="n"/>
+      <c r="L260" s="14" t="n"/>
+      <c r="M260" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L260" s="14" t="n"/>
-      <c r="M260" s="14" t="n"/>
       <c r="N260" s="14" t="n"/>
       <c r="O260" s="14" t="n"/>
       <c r="P260" s="14" t="n"/>
@@ -15412,6 +15953,8 @@
       <c r="U260" s="14" t="n"/>
       <c r="V260" s="14" t="n"/>
       <c r="W260" s="14" t="n"/>
+      <c r="X260" s="14" t="n"/>
+      <c r="Y260" s="14" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="10" t="inlineStr">
@@ -15449,13 +15992,13 @@
       <c r="H261" s="14" t="n"/>
       <c r="I261" s="14" t="n"/>
       <c r="J261" s="14" t="n"/>
-      <c r="K261" s="13" t="inlineStr">
+      <c r="K261" s="14" t="n"/>
+      <c r="L261" s="14" t="n"/>
+      <c r="M261" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L261" s="14" t="n"/>
-      <c r="M261" s="14" t="n"/>
       <c r="N261" s="14" t="n"/>
       <c r="O261" s="14" t="n"/>
       <c r="P261" s="14" t="n"/>
@@ -15466,6 +16009,8 @@
       <c r="U261" s="14" t="n"/>
       <c r="V261" s="14" t="n"/>
       <c r="W261" s="14" t="n"/>
+      <c r="X261" s="14" t="n"/>
+      <c r="Y261" s="14" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="10" t="inlineStr">
@@ -15503,13 +16048,13 @@
       <c r="H262" s="14" t="n"/>
       <c r="I262" s="14" t="n"/>
       <c r="J262" s="14" t="n"/>
-      <c r="K262" s="13" t="inlineStr">
+      <c r="K262" s="14" t="n"/>
+      <c r="L262" s="14" t="n"/>
+      <c r="M262" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L262" s="14" t="n"/>
-      <c r="M262" s="14" t="n"/>
       <c r="N262" s="14" t="n"/>
       <c r="O262" s="14" t="n"/>
       <c r="P262" s="14" t="n"/>
@@ -15520,6 +16065,8 @@
       <c r="U262" s="14" t="n"/>
       <c r="V262" s="14" t="n"/>
       <c r="W262" s="14" t="n"/>
+      <c r="X262" s="14" t="n"/>
+      <c r="Y262" s="14" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="10" t="inlineStr">
@@ -15553,13 +16100,13 @@
       <c r="H263" s="14" t="n"/>
       <c r="I263" s="14" t="n"/>
       <c r="J263" s="14" t="n"/>
-      <c r="K263" s="13" t="inlineStr">
+      <c r="K263" s="14" t="n"/>
+      <c r="L263" s="14" t="n"/>
+      <c r="M263" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L263" s="14" t="n"/>
-      <c r="M263" s="14" t="n"/>
       <c r="N263" s="14" t="n"/>
       <c r="O263" s="14" t="n"/>
       <c r="P263" s="14" t="n"/>
@@ -15570,6 +16117,8 @@
       <c r="U263" s="14" t="n"/>
       <c r="V263" s="14" t="n"/>
       <c r="W263" s="14" t="n"/>
+      <c r="X263" s="14" t="n"/>
+      <c r="Y263" s="14" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="10" t="inlineStr">
@@ -15607,13 +16156,13 @@
       <c r="H264" s="14" t="n"/>
       <c r="I264" s="14" t="n"/>
       <c r="J264" s="14" t="n"/>
-      <c r="K264" s="13" t="inlineStr">
+      <c r="K264" s="14" t="n"/>
+      <c r="L264" s="14" t="n"/>
+      <c r="M264" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L264" s="14" t="n"/>
-      <c r="M264" s="14" t="n"/>
       <c r="N264" s="14" t="n"/>
       <c r="O264" s="14" t="n"/>
       <c r="P264" s="14" t="n"/>
@@ -15624,6 +16173,8 @@
       <c r="U264" s="14" t="n"/>
       <c r="V264" s="14" t="n"/>
       <c r="W264" s="14" t="n"/>
+      <c r="X264" s="14" t="n"/>
+      <c r="Y264" s="14" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="10" t="inlineStr">
@@ -15657,13 +16208,13 @@
       <c r="H265" s="14" t="n"/>
       <c r="I265" s="14" t="n"/>
       <c r="J265" s="14" t="n"/>
-      <c r="K265" s="13" t="inlineStr">
+      <c r="K265" s="14" t="n"/>
+      <c r="L265" s="14" t="n"/>
+      <c r="M265" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L265" s="14" t="n"/>
-      <c r="M265" s="14" t="n"/>
       <c r="N265" s="14" t="n"/>
       <c r="O265" s="14" t="n"/>
       <c r="P265" s="14" t="n"/>
@@ -15674,6 +16225,8 @@
       <c r="U265" s="14" t="n"/>
       <c r="V265" s="14" t="n"/>
       <c r="W265" s="14" t="n"/>
+      <c r="X265" s="14" t="n"/>
+      <c r="Y265" s="14" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="10" t="inlineStr">
@@ -15711,13 +16264,13 @@
       <c r="H266" s="14" t="n"/>
       <c r="I266" s="14" t="n"/>
       <c r="J266" s="14" t="n"/>
-      <c r="K266" s="13" t="inlineStr">
+      <c r="K266" s="14" t="n"/>
+      <c r="L266" s="14" t="n"/>
+      <c r="M266" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L266" s="14" t="n"/>
-      <c r="M266" s="14" t="n"/>
       <c r="N266" s="14" t="n"/>
       <c r="O266" s="14" t="n"/>
       <c r="P266" s="14" t="n"/>
@@ -15728,6 +16281,8 @@
       <c r="U266" s="14" t="n"/>
       <c r="V266" s="14" t="n"/>
       <c r="W266" s="14" t="n"/>
+      <c r="X266" s="14" t="n"/>
+      <c r="Y266" s="14" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="10" t="inlineStr">
@@ -15765,13 +16320,13 @@
       <c r="H267" s="14" t="n"/>
       <c r="I267" s="14" t="n"/>
       <c r="J267" s="14" t="n"/>
-      <c r="K267" s="13" t="inlineStr">
+      <c r="K267" s="14" t="n"/>
+      <c r="L267" s="14" t="n"/>
+      <c r="M267" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L267" s="14" t="n"/>
-      <c r="M267" s="14" t="n"/>
       <c r="N267" s="14" t="n"/>
       <c r="O267" s="14" t="n"/>
       <c r="P267" s="14" t="n"/>
@@ -15782,6 +16337,8 @@
       <c r="U267" s="14" t="n"/>
       <c r="V267" s="14" t="n"/>
       <c r="W267" s="14" t="n"/>
+      <c r="X267" s="14" t="n"/>
+      <c r="Y267" s="14" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="10" t="inlineStr">
@@ -15819,13 +16376,13 @@
       <c r="H268" s="14" t="n"/>
       <c r="I268" s="14" t="n"/>
       <c r="J268" s="14" t="n"/>
-      <c r="K268" s="13" t="inlineStr">
+      <c r="K268" s="14" t="n"/>
+      <c r="L268" s="14" t="n"/>
+      <c r="M268" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L268" s="14" t="n"/>
-      <c r="M268" s="14" t="n"/>
       <c r="N268" s="14" t="n"/>
       <c r="O268" s="14" t="n"/>
       <c r="P268" s="14" t="n"/>
@@ -15836,6 +16393,8 @@
       <c r="U268" s="14" t="n"/>
       <c r="V268" s="14" t="n"/>
       <c r="W268" s="14" t="n"/>
+      <c r="X268" s="14" t="n"/>
+      <c r="Y268" s="14" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="10" t="inlineStr">
@@ -15873,13 +16432,13 @@
       <c r="H269" s="14" t="n"/>
       <c r="I269" s="14" t="n"/>
       <c r="J269" s="14" t="n"/>
-      <c r="K269" s="13" t="inlineStr">
+      <c r="K269" s="14" t="n"/>
+      <c r="L269" s="14" t="n"/>
+      <c r="M269" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L269" s="14" t="n"/>
-      <c r="M269" s="14" t="n"/>
       <c r="N269" s="14" t="n"/>
       <c r="O269" s="14" t="n"/>
       <c r="P269" s="14" t="n"/>
@@ -15890,6 +16449,8 @@
       <c r="U269" s="14" t="n"/>
       <c r="V269" s="14" t="n"/>
       <c r="W269" s="14" t="n"/>
+      <c r="X269" s="14" t="n"/>
+      <c r="Y269" s="14" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="10" t="inlineStr">
@@ -15927,13 +16488,13 @@
       <c r="H270" s="14" t="n"/>
       <c r="I270" s="14" t="n"/>
       <c r="J270" s="14" t="n"/>
-      <c r="K270" s="13" t="inlineStr">
+      <c r="K270" s="14" t="n"/>
+      <c r="L270" s="14" t="n"/>
+      <c r="M270" s="13" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="L270" s="14" t="n"/>
-      <c r="M270" s="14" t="n"/>
       <c r="N270" s="14" t="n"/>
       <c r="O270" s="14" t="n"/>
       <c r="P270" s="14" t="n"/>
@@ -15944,6 +16505,8 @@
       <c r="U270" s="14" t="n"/>
       <c r="V270" s="14" t="n"/>
       <c r="W270" s="14" t="n"/>
+      <c r="X270" s="14" t="n"/>
+      <c r="Y270" s="14" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="10" t="inlineStr">
@@ -15977,13 +16540,13 @@
       <c r="H271" s="14" t="n"/>
       <c r="I271" s="14" t="n"/>
       <c r="J271" s="14" t="n"/>
-      <c r="K271" s="13" t="inlineStr">
+      <c r="K271" s="14" t="n"/>
+      <c r="L271" s="14" t="n"/>
+      <c r="M271" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L271" s="14" t="n"/>
-      <c r="M271" s="14" t="n"/>
       <c r="N271" s="14" t="n"/>
       <c r="O271" s="14" t="n"/>
       <c r="P271" s="14" t="n"/>
@@ -15994,6 +16557,8 @@
       <c r="U271" s="14" t="n"/>
       <c r="V271" s="14" t="n"/>
       <c r="W271" s="14" t="n"/>
+      <c r="X271" s="14" t="n"/>
+      <c r="Y271" s="14" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="10" t="inlineStr">
@@ -16031,13 +16596,13 @@
       <c r="H272" s="14" t="n"/>
       <c r="I272" s="14" t="n"/>
       <c r="J272" s="14" t="n"/>
-      <c r="K272" s="13" t="inlineStr">
+      <c r="K272" s="14" t="n"/>
+      <c r="L272" s="14" t="n"/>
+      <c r="M272" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L272" s="14" t="n"/>
-      <c r="M272" s="14" t="n"/>
       <c r="N272" s="14" t="n"/>
       <c r="O272" s="14" t="n"/>
       <c r="P272" s="14" t="n"/>
@@ -16048,6 +16613,8 @@
       <c r="U272" s="14" t="n"/>
       <c r="V272" s="14" t="n"/>
       <c r="W272" s="14" t="n"/>
+      <c r="X272" s="14" t="n"/>
+      <c r="Y272" s="14" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="10" t="inlineStr">
@@ -16085,13 +16652,13 @@
       <c r="H273" s="14" t="n"/>
       <c r="I273" s="14" t="n"/>
       <c r="J273" s="14" t="n"/>
-      <c r="K273" s="13" t="inlineStr">
+      <c r="K273" s="14" t="n"/>
+      <c r="L273" s="14" t="n"/>
+      <c r="M273" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L273" s="14" t="n"/>
-      <c r="M273" s="14" t="n"/>
       <c r="N273" s="14" t="n"/>
       <c r="O273" s="14" t="n"/>
       <c r="P273" s="14" t="n"/>
@@ -16102,6 +16669,8 @@
       <c r="U273" s="14" t="n"/>
       <c r="V273" s="14" t="n"/>
       <c r="W273" s="14" t="n"/>
+      <c r="X273" s="14" t="n"/>
+      <c r="Y273" s="14" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="10" t="inlineStr">
@@ -16139,13 +16708,13 @@
       <c r="H274" s="14" t="n"/>
       <c r="I274" s="14" t="n"/>
       <c r="J274" s="14" t="n"/>
-      <c r="K274" s="13" t="inlineStr">
+      <c r="K274" s="14" t="n"/>
+      <c r="L274" s="14" t="n"/>
+      <c r="M274" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L274" s="14" t="n"/>
-      <c r="M274" s="14" t="n"/>
       <c r="N274" s="14" t="n"/>
       <c r="O274" s="14" t="n"/>
       <c r="P274" s="14" t="n"/>
@@ -16156,6 +16725,8 @@
       <c r="U274" s="14" t="n"/>
       <c r="V274" s="14" t="n"/>
       <c r="W274" s="14" t="n"/>
+      <c r="X274" s="14" t="n"/>
+      <c r="Y274" s="14" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="10" t="inlineStr">
@@ -16202,6 +16773,8 @@
       <c r="U275" s="14" t="n"/>
       <c r="V275" s="14" t="n"/>
       <c r="W275" s="14" t="n"/>
+      <c r="X275" s="14" t="n"/>
+      <c r="Y275" s="14" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="10" t="inlineStr">
@@ -16239,13 +16812,13 @@
       <c r="H276" s="14" t="n"/>
       <c r="I276" s="14" t="n"/>
       <c r="J276" s="14" t="n"/>
-      <c r="K276" s="13" t="inlineStr">
+      <c r="K276" s="14" t="n"/>
+      <c r="L276" s="14" t="n"/>
+      <c r="M276" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L276" s="14" t="n"/>
-      <c r="M276" s="14" t="n"/>
       <c r="N276" s="14" t="n"/>
       <c r="O276" s="14" t="n"/>
       <c r="P276" s="14" t="n"/>
@@ -16256,6 +16829,8 @@
       <c r="U276" s="14" t="n"/>
       <c r="V276" s="14" t="n"/>
       <c r="W276" s="14" t="n"/>
+      <c r="X276" s="14" t="n"/>
+      <c r="Y276" s="14" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="10" t="inlineStr">
@@ -16302,6 +16877,8 @@
       <c r="U277" s="14" t="n"/>
       <c r="V277" s="14" t="n"/>
       <c r="W277" s="14" t="n"/>
+      <c r="X277" s="14" t="n"/>
+      <c r="Y277" s="14" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="10" t="inlineStr">
@@ -16339,13 +16916,13 @@
       <c r="H278" s="14" t="n"/>
       <c r="I278" s="14" t="n"/>
       <c r="J278" s="14" t="n"/>
-      <c r="K278" s="13" t="inlineStr">
+      <c r="K278" s="14" t="n"/>
+      <c r="L278" s="14" t="n"/>
+      <c r="M278" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L278" s="14" t="n"/>
-      <c r="M278" s="14" t="n"/>
       <c r="N278" s="14" t="n"/>
       <c r="O278" s="14" t="n"/>
       <c r="P278" s="14" t="n"/>
@@ -16356,6 +16933,8 @@
       <c r="U278" s="14" t="n"/>
       <c r="V278" s="14" t="n"/>
       <c r="W278" s="14" t="n"/>
+      <c r="X278" s="14" t="n"/>
+      <c r="Y278" s="14" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="10" t="inlineStr">
@@ -16393,13 +16972,13 @@
       <c r="H279" s="14" t="n"/>
       <c r="I279" s="14" t="n"/>
       <c r="J279" s="14" t="n"/>
-      <c r="K279" s="13" t="inlineStr">
+      <c r="K279" s="14" t="n"/>
+      <c r="L279" s="14" t="n"/>
+      <c r="M279" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L279" s="14" t="n"/>
-      <c r="M279" s="14" t="n"/>
       <c r="N279" s="14" t="n"/>
       <c r="O279" s="14" t="n"/>
       <c r="P279" s="14" t="n"/>
@@ -16410,6 +16989,8 @@
       <c r="U279" s="14" t="n"/>
       <c r="V279" s="14" t="n"/>
       <c r="W279" s="14" t="n"/>
+      <c r="X279" s="14" t="n"/>
+      <c r="Y279" s="14" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="10" t="inlineStr">
@@ -16443,24 +17024,24 @@
       <c r="H280" s="14" t="n"/>
       <c r="I280" s="14" t="n"/>
       <c r="J280" s="14" t="n"/>
-      <c r="K280" s="13" t="inlineStr">
+      <c r="K280" s="14" t="n"/>
+      <c r="L280" s="14" t="n"/>
+      <c r="M280" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L280" s="13" t="inlineStr">
+      <c r="N280" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M280" s="14" t="n"/>
-      <c r="N280" s="13" t="inlineStr">
+      <c r="O280" s="14" t="n"/>
+      <c r="P280" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O280" s="14" t="n"/>
-      <c r="P280" s="14" t="n"/>
       <c r="Q280" s="14" t="n"/>
       <c r="R280" s="14" t="n"/>
       <c r="S280" s="14" t="n"/>
@@ -16468,6 +17049,8 @@
       <c r="U280" s="14" t="n"/>
       <c r="V280" s="14" t="n"/>
       <c r="W280" s="14" t="n"/>
+      <c r="X280" s="14" t="n"/>
+      <c r="Y280" s="14" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="10" t="inlineStr">
@@ -16518,6 +17101,8 @@
       <c r="U281" s="14" t="n"/>
       <c r="V281" s="14" t="n"/>
       <c r="W281" s="14" t="n"/>
+      <c r="X281" s="14" t="n"/>
+      <c r="Y281" s="14" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="10" t="inlineStr">
@@ -16551,13 +17136,13 @@
       <c r="H282" s="14" t="n"/>
       <c r="I282" s="14" t="n"/>
       <c r="J282" s="14" t="n"/>
-      <c r="K282" s="13" t="inlineStr">
+      <c r="K282" s="14" t="n"/>
+      <c r="L282" s="14" t="n"/>
+      <c r="M282" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L282" s="14" t="n"/>
-      <c r="M282" s="14" t="n"/>
       <c r="N282" s="14" t="n"/>
       <c r="O282" s="14" t="n"/>
       <c r="P282" s="14" t="n"/>
@@ -16568,6 +17153,8 @@
       <c r="U282" s="14" t="n"/>
       <c r="V282" s="14" t="n"/>
       <c r="W282" s="14" t="n"/>
+      <c r="X282" s="14" t="n"/>
+      <c r="Y282" s="14" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="10" t="inlineStr">
@@ -16618,6 +17205,8 @@
       <c r="U283" s="14" t="n"/>
       <c r="V283" s="14" t="n"/>
       <c r="W283" s="14" t="n"/>
+      <c r="X283" s="14" t="n"/>
+      <c r="Y283" s="14" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="10" t="inlineStr">
@@ -16659,13 +17248,13 @@
       </c>
       <c r="I284" s="14" t="n"/>
       <c r="J284" s="14" t="n"/>
-      <c r="K284" s="13" t="inlineStr">
+      <c r="K284" s="14" t="n"/>
+      <c r="L284" s="14" t="n"/>
+      <c r="M284" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L284" s="14" t="n"/>
-      <c r="M284" s="14" t="n"/>
       <c r="N284" s="14" t="n"/>
       <c r="O284" s="14" t="n"/>
       <c r="P284" s="14" t="n"/>
@@ -16676,6 +17265,8 @@
       <c r="U284" s="14" t="n"/>
       <c r="V284" s="14" t="n"/>
       <c r="W284" s="14" t="n"/>
+      <c r="X284" s="14" t="n"/>
+      <c r="Y284" s="14" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="10" t="inlineStr">
@@ -16713,13 +17304,13 @@
       <c r="H285" s="14" t="n"/>
       <c r="I285" s="14" t="n"/>
       <c r="J285" s="14" t="n"/>
-      <c r="K285" s="13" t="inlineStr">
+      <c r="K285" s="14" t="n"/>
+      <c r="L285" s="14" t="n"/>
+      <c r="M285" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L285" s="14" t="n"/>
-      <c r="M285" s="14" t="n"/>
       <c r="N285" s="14" t="n"/>
       <c r="O285" s="14" t="n"/>
       <c r="P285" s="14" t="n"/>
@@ -16730,6 +17321,8 @@
       <c r="U285" s="14" t="n"/>
       <c r="V285" s="14" t="n"/>
       <c r="W285" s="14" t="n"/>
+      <c r="X285" s="14" t="n"/>
+      <c r="Y285" s="14" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="10" t="inlineStr">
@@ -16767,13 +17360,13 @@
       <c r="H286" s="14" t="n"/>
       <c r="I286" s="14" t="n"/>
       <c r="J286" s="14" t="n"/>
-      <c r="K286" s="13" t="inlineStr">
+      <c r="K286" s="14" t="n"/>
+      <c r="L286" s="14" t="n"/>
+      <c r="M286" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L286" s="14" t="n"/>
-      <c r="M286" s="14" t="n"/>
       <c r="N286" s="14" t="n"/>
       <c r="O286" s="14" t="n"/>
       <c r="P286" s="14" t="n"/>
@@ -16784,6 +17377,8 @@
       <c r="U286" s="14" t="n"/>
       <c r="V286" s="14" t="n"/>
       <c r="W286" s="14" t="n"/>
+      <c r="X286" s="14" t="n"/>
+      <c r="Y286" s="14" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="10" t="inlineStr">
@@ -16825,13 +17420,13 @@
       </c>
       <c r="I287" s="14" t="n"/>
       <c r="J287" s="14" t="n"/>
-      <c r="K287" s="13" t="inlineStr">
+      <c r="K287" s="14" t="n"/>
+      <c r="L287" s="14" t="n"/>
+      <c r="M287" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L287" s="14" t="n"/>
-      <c r="M287" s="14" t="n"/>
       <c r="N287" s="14" t="n"/>
       <c r="O287" s="14" t="n"/>
       <c r="P287" s="14" t="n"/>
@@ -16842,6 +17437,8 @@
       <c r="U287" s="14" t="n"/>
       <c r="V287" s="14" t="n"/>
       <c r="W287" s="14" t="n"/>
+      <c r="X287" s="14" t="n"/>
+      <c r="Y287" s="14" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="10" t="inlineStr">
@@ -16879,13 +17476,13 @@
       <c r="H288" s="14" t="n"/>
       <c r="I288" s="14" t="n"/>
       <c r="J288" s="14" t="n"/>
-      <c r="K288" s="13" t="inlineStr">
+      <c r="K288" s="14" t="n"/>
+      <c r="L288" s="14" t="n"/>
+      <c r="M288" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L288" s="14" t="n"/>
-      <c r="M288" s="14" t="n"/>
       <c r="N288" s="14" t="n"/>
       <c r="O288" s="14" t="n"/>
       <c r="P288" s="14" t="n"/>
@@ -16896,6 +17493,8 @@
       <c r="U288" s="14" t="n"/>
       <c r="V288" s="14" t="n"/>
       <c r="W288" s="14" t="n"/>
+      <c r="X288" s="14" t="n"/>
+      <c r="Y288" s="14" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="10" t="inlineStr">
@@ -16933,13 +17532,13 @@
       <c r="H289" s="14" t="n"/>
       <c r="I289" s="14" t="n"/>
       <c r="J289" s="14" t="n"/>
-      <c r="K289" s="13" t="inlineStr">
+      <c r="K289" s="14" t="n"/>
+      <c r="L289" s="14" t="n"/>
+      <c r="M289" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L289" s="14" t="n"/>
-      <c r="M289" s="14" t="n"/>
       <c r="N289" s="14" t="n"/>
       <c r="O289" s="14" t="n"/>
       <c r="P289" s="14" t="n"/>
@@ -16950,6 +17549,8 @@
       <c r="U289" s="14" t="n"/>
       <c r="V289" s="14" t="n"/>
       <c r="W289" s="14" t="n"/>
+      <c r="X289" s="14" t="n"/>
+      <c r="Y289" s="14" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="10" t="inlineStr">
@@ -16987,13 +17588,13 @@
       <c r="H290" s="14" t="n"/>
       <c r="I290" s="14" t="n"/>
       <c r="J290" s="14" t="n"/>
-      <c r="K290" s="13" t="inlineStr">
+      <c r="K290" s="14" t="n"/>
+      <c r="L290" s="14" t="n"/>
+      <c r="M290" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L290" s="14" t="n"/>
-      <c r="M290" s="14" t="n"/>
       <c r="N290" s="14" t="n"/>
       <c r="O290" s="14" t="n"/>
       <c r="P290" s="14" t="n"/>
@@ -17004,6 +17605,8 @@
       <c r="U290" s="14" t="n"/>
       <c r="V290" s="14" t="n"/>
       <c r="W290" s="14" t="n"/>
+      <c r="X290" s="14" t="n"/>
+      <c r="Y290" s="14" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="10" t="inlineStr">
@@ -17037,13 +17640,13 @@
       <c r="H291" s="14" t="n"/>
       <c r="I291" s="14" t="n"/>
       <c r="J291" s="14" t="n"/>
-      <c r="K291" s="13" t="inlineStr">
+      <c r="K291" s="14" t="n"/>
+      <c r="L291" s="14" t="n"/>
+      <c r="M291" s="13" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
       </c>
-      <c r="L291" s="14" t="n"/>
-      <c r="M291" s="14" t="n"/>
       <c r="N291" s="14" t="n"/>
       <c r="O291" s="14" t="n"/>
       <c r="P291" s="14" t="n"/>
@@ -17054,6 +17657,8 @@
       <c r="U291" s="14" t="n"/>
       <c r="V291" s="14" t="n"/>
       <c r="W291" s="14" t="n"/>
+      <c r="X291" s="14" t="n"/>
+      <c r="Y291" s="14" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="10" t="inlineStr">
@@ -17091,13 +17696,13 @@
       <c r="H292" s="14" t="n"/>
       <c r="I292" s="14" t="n"/>
       <c r="J292" s="14" t="n"/>
-      <c r="K292" s="13" t="inlineStr">
+      <c r="K292" s="14" t="n"/>
+      <c r="L292" s="14" t="n"/>
+      <c r="M292" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L292" s="14" t="n"/>
-      <c r="M292" s="14" t="n"/>
       <c r="N292" s="14" t="n"/>
       <c r="O292" s="14" t="n"/>
       <c r="P292" s="14" t="n"/>
@@ -17108,6 +17713,8 @@
       <c r="U292" s="14" t="n"/>
       <c r="V292" s="14" t="n"/>
       <c r="W292" s="14" t="n"/>
+      <c r="X292" s="14" t="n"/>
+      <c r="Y292" s="14" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="10" t="inlineStr">
@@ -17154,6 +17761,8 @@
       <c r="U293" s="14" t="n"/>
       <c r="V293" s="14" t="n"/>
       <c r="W293" s="14" t="n"/>
+      <c r="X293" s="14" t="n"/>
+      <c r="Y293" s="14" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="10" t="inlineStr">
@@ -17187,13 +17796,13 @@
       <c r="H294" s="14" t="n"/>
       <c r="I294" s="14" t="n"/>
       <c r="J294" s="14" t="n"/>
-      <c r="K294" s="13" t="inlineStr">
+      <c r="K294" s="14" t="n"/>
+      <c r="L294" s="14" t="n"/>
+      <c r="M294" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L294" s="14" t="n"/>
-      <c r="M294" s="14" t="n"/>
       <c r="N294" s="14" t="n"/>
       <c r="O294" s="14" t="n"/>
       <c r="P294" s="14" t="n"/>
@@ -17204,6 +17813,8 @@
       <c r="U294" s="14" t="n"/>
       <c r="V294" s="14" t="n"/>
       <c r="W294" s="14" t="n"/>
+      <c r="X294" s="14" t="n"/>
+      <c r="Y294" s="14" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="10" t="inlineStr">
@@ -17241,13 +17852,13 @@
       <c r="H295" s="14" t="n"/>
       <c r="I295" s="14" t="n"/>
       <c r="J295" s="14" t="n"/>
-      <c r="K295" s="13" t="inlineStr">
+      <c r="K295" s="14" t="n"/>
+      <c r="L295" s="14" t="n"/>
+      <c r="M295" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L295" s="14" t="n"/>
-      <c r="M295" s="14" t="n"/>
       <c r="N295" s="14" t="n"/>
       <c r="O295" s="14" t="n"/>
       <c r="P295" s="14" t="n"/>
@@ -17258,6 +17869,8 @@
       <c r="U295" s="14" t="n"/>
       <c r="V295" s="14" t="n"/>
       <c r="W295" s="14" t="n"/>
+      <c r="X295" s="14" t="n"/>
+      <c r="Y295" s="14" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="10" t="inlineStr">
@@ -17291,13 +17904,13 @@
       <c r="H296" s="14" t="n"/>
       <c r="I296" s="14" t="n"/>
       <c r="J296" s="14" t="n"/>
-      <c r="K296" s="13" t="inlineStr">
+      <c r="K296" s="14" t="n"/>
+      <c r="L296" s="14" t="n"/>
+      <c r="M296" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L296" s="14" t="n"/>
-      <c r="M296" s="14" t="n"/>
       <c r="N296" s="14" t="n"/>
       <c r="O296" s="14" t="n"/>
       <c r="P296" s="14" t="n"/>
@@ -17308,6 +17921,8 @@
       <c r="U296" s="14" t="n"/>
       <c r="V296" s="14" t="n"/>
       <c r="W296" s="14" t="n"/>
+      <c r="X296" s="14" t="n"/>
+      <c r="Y296" s="14" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="10" t="inlineStr">
@@ -17349,13 +17964,13 @@
       </c>
       <c r="I297" s="14" t="n"/>
       <c r="J297" s="14" t="n"/>
-      <c r="K297" s="13" t="inlineStr">
+      <c r="K297" s="14" t="n"/>
+      <c r="L297" s="14" t="n"/>
+      <c r="M297" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L297" s="14" t="n"/>
-      <c r="M297" s="14" t="n"/>
       <c r="N297" s="14" t="n"/>
       <c r="O297" s="14" t="n"/>
       <c r="P297" s="14" t="n"/>
@@ -17366,6 +17981,8 @@
       <c r="U297" s="14" t="n"/>
       <c r="V297" s="14" t="n"/>
       <c r="W297" s="14" t="n"/>
+      <c r="X297" s="14" t="n"/>
+      <c r="Y297" s="14" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="10" t="inlineStr">
@@ -17403,13 +18020,13 @@
       <c r="H298" s="14" t="n"/>
       <c r="I298" s="14" t="n"/>
       <c r="J298" s="14" t="n"/>
-      <c r="K298" s="13" t="inlineStr">
+      <c r="K298" s="14" t="n"/>
+      <c r="L298" s="14" t="n"/>
+      <c r="M298" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L298" s="14" t="n"/>
-      <c r="M298" s="14" t="n"/>
       <c r="N298" s="14" t="n"/>
       <c r="O298" s="14" t="n"/>
       <c r="P298" s="14" t="n"/>
@@ -17420,6 +18037,8 @@
       <c r="U298" s="14" t="n"/>
       <c r="V298" s="14" t="n"/>
       <c r="W298" s="14" t="n"/>
+      <c r="X298" s="14" t="n"/>
+      <c r="Y298" s="14" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="10" t="inlineStr">
@@ -17461,13 +18080,13 @@
       </c>
       <c r="I299" s="14" t="n"/>
       <c r="J299" s="14" t="n"/>
-      <c r="K299" s="13" t="inlineStr">
+      <c r="K299" s="14" t="n"/>
+      <c r="L299" s="14" t="n"/>
+      <c r="M299" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L299" s="14" t="n"/>
-      <c r="M299" s="14" t="n"/>
       <c r="N299" s="14" t="n"/>
       <c r="O299" s="14" t="n"/>
       <c r="P299" s="14" t="n"/>
@@ -17478,6 +18097,8 @@
       <c r="U299" s="14" t="n"/>
       <c r="V299" s="14" t="n"/>
       <c r="W299" s="14" t="n"/>
+      <c r="X299" s="14" t="n"/>
+      <c r="Y299" s="14" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="10" t="inlineStr">
@@ -17515,13 +18136,13 @@
       <c r="H300" s="14" t="n"/>
       <c r="I300" s="14" t="n"/>
       <c r="J300" s="14" t="n"/>
-      <c r="K300" s="13" t="inlineStr">
+      <c r="K300" s="14" t="n"/>
+      <c r="L300" s="14" t="n"/>
+      <c r="M300" s="13" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="L300" s="14" t="n"/>
-      <c r="M300" s="14" t="n"/>
       <c r="N300" s="14" t="n"/>
       <c r="O300" s="14" t="n"/>
       <c r="P300" s="14" t="n"/>
@@ -17532,6 +18153,8 @@
       <c r="U300" s="14" t="n"/>
       <c r="V300" s="14" t="n"/>
       <c r="W300" s="14" t="n"/>
+      <c r="X300" s="14" t="n"/>
+      <c r="Y300" s="14" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="10" t="inlineStr">
@@ -17578,6 +18201,8 @@
       <c r="U301" s="14" t="n"/>
       <c r="V301" s="14" t="n"/>
       <c r="W301" s="14" t="n"/>
+      <c r="X301" s="14" t="n"/>
+      <c r="Y301" s="14" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="10" t="inlineStr">
@@ -17615,13 +18240,13 @@
       <c r="H302" s="14" t="n"/>
       <c r="I302" s="14" t="n"/>
       <c r="J302" s="14" t="n"/>
-      <c r="K302" s="13" t="inlineStr">
+      <c r="K302" s="14" t="n"/>
+      <c r="L302" s="14" t="n"/>
+      <c r="M302" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L302" s="14" t="n"/>
-      <c r="M302" s="14" t="n"/>
       <c r="N302" s="14" t="n"/>
       <c r="O302" s="14" t="n"/>
       <c r="P302" s="14" t="n"/>
@@ -17632,6 +18257,8 @@
       <c r="U302" s="14" t="n"/>
       <c r="V302" s="14" t="n"/>
       <c r="W302" s="14" t="n"/>
+      <c r="X302" s="14" t="n"/>
+      <c r="Y302" s="14" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="10" t="inlineStr">
@@ -17669,13 +18296,13 @@
       <c r="H303" s="14" t="n"/>
       <c r="I303" s="14" t="n"/>
       <c r="J303" s="14" t="n"/>
-      <c r="K303" s="13" t="inlineStr">
+      <c r="K303" s="14" t="n"/>
+      <c r="L303" s="14" t="n"/>
+      <c r="M303" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L303" s="14" t="n"/>
-      <c r="M303" s="14" t="n"/>
       <c r="N303" s="14" t="n"/>
       <c r="O303" s="14" t="n"/>
       <c r="P303" s="14" t="n"/>
@@ -17686,6 +18313,8 @@
       <c r="U303" s="14" t="n"/>
       <c r="V303" s="14" t="n"/>
       <c r="W303" s="14" t="n"/>
+      <c r="X303" s="14" t="n"/>
+      <c r="Y303" s="14" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="10" t="inlineStr">
@@ -17732,6 +18361,8 @@
       <c r="U304" s="14" t="n"/>
       <c r="V304" s="14" t="n"/>
       <c r="W304" s="14" t="n"/>
+      <c r="X304" s="14" t="n"/>
+      <c r="Y304" s="14" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="10" t="inlineStr">
@@ -17778,6 +18409,8 @@
       <c r="U305" s="14" t="n"/>
       <c r="V305" s="14" t="n"/>
       <c r="W305" s="14" t="n"/>
+      <c r="X305" s="14" t="n"/>
+      <c r="Y305" s="14" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="10" t="inlineStr">
@@ -17815,13 +18448,13 @@
       <c r="H306" s="14" t="n"/>
       <c r="I306" s="14" t="n"/>
       <c r="J306" s="14" t="n"/>
-      <c r="K306" s="13" t="inlineStr">
+      <c r="K306" s="14" t="n"/>
+      <c r="L306" s="14" t="n"/>
+      <c r="M306" s="13" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="L306" s="14" t="n"/>
-      <c r="M306" s="14" t="n"/>
       <c r="N306" s="14" t="n"/>
       <c r="O306" s="14" t="n"/>
       <c r="P306" s="14" t="n"/>
@@ -17832,6 +18465,8 @@
       <c r="U306" s="14" t="n"/>
       <c r="V306" s="14" t="n"/>
       <c r="W306" s="14" t="n"/>
+      <c r="X306" s="14" t="n"/>
+      <c r="Y306" s="14" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="10" t="inlineStr">
@@ -17865,13 +18500,13 @@
       <c r="H307" s="14" t="n"/>
       <c r="I307" s="14" t="n"/>
       <c r="J307" s="14" t="n"/>
-      <c r="K307" s="13" t="inlineStr">
+      <c r="K307" s="14" t="n"/>
+      <c r="L307" s="14" t="n"/>
+      <c r="M307" s="13" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="L307" s="14" t="n"/>
-      <c r="M307" s="14" t="n"/>
       <c r="N307" s="14" t="n"/>
       <c r="O307" s="14" t="n"/>
       <c r="P307" s="14" t="n"/>
@@ -17882,6 +18517,8 @@
       <c r="U307" s="14" t="n"/>
       <c r="V307" s="14" t="n"/>
       <c r="W307" s="14" t="n"/>
+      <c r="X307" s="14" t="n"/>
+      <c r="Y307" s="14" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="10" t="inlineStr">
@@ -17915,24 +18552,24 @@
       <c r="H308" s="14" t="n"/>
       <c r="I308" s="14" t="n"/>
       <c r="J308" s="14" t="n"/>
-      <c r="K308" s="13" t="inlineStr">
+      <c r="K308" s="14" t="n"/>
+      <c r="L308" s="14" t="n"/>
+      <c r="M308" s="13" t="inlineStr">
         <is>
           <t>UPC (Ultra Premium Collection)</t>
         </is>
       </c>
-      <c r="L308" s="13" t="inlineStr">
+      <c r="N308" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M308" s="14" t="n"/>
-      <c r="N308" s="13" t="inlineStr">
+      <c r="O308" s="14" t="n"/>
+      <c r="P308" s="13" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
       </c>
-      <c r="O308" s="14" t="n"/>
-      <c r="P308" s="14" t="n"/>
       <c r="Q308" s="14" t="n"/>
       <c r="R308" s="14" t="n"/>
       <c r="S308" s="14" t="n"/>
@@ -17940,6 +18577,8 @@
       <c r="U308" s="14" t="n"/>
       <c r="V308" s="14" t="n"/>
       <c r="W308" s="14" t="n"/>
+      <c r="X308" s="14" t="n"/>
+      <c r="Y308" s="14" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="10" t="inlineStr">
@@ -17986,22 +18625,24 @@
       <c r="U309" s="14" t="n"/>
       <c r="V309" s="14" t="n"/>
       <c r="W309" s="14" t="n"/>
+      <c r="X309" s="14" t="n"/>
+      <c r="Y309" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="G2:G309 H2:H309 I2:I309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G309 H2:H309 I2:I309 J2:J309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$26</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$17</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$10</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L309 O2:O309 U2:U309 V2:V309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N309 Q2:Q309 W2:W309 X2:X309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S309" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$E$2:$E$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -18749,7 +19390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18810,62 +19451,62 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Opening type filled in</t>
+          <t>Videos with 4 sets</t>
         </is>
       </c>
       <c r="B7" s="17">
-        <f>COUNTA('Video Log'!K2:K309)</f>
+        <f>COUNTA('Video Log'!J2:J309)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Marked as a hit</t>
+          <t>Opening type filled in</t>
         </is>
       </c>
       <c r="B8" s="17">
-        <f>COUNTIF('Video Log'!L2:L309,"Yes")</f>
+        <f>COUNTA('Video Log'!M2:M309)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Hit card named</t>
+          <t>Marked as a hit</t>
         </is>
       </c>
       <c r="B9" s="17">
-        <f>COUNTA('Video Log'!M2:M309)</f>
+        <f>COUNTIF('Video Log'!N2:N309,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>In the Hall of Fame</t>
+          <t>Hit card named</t>
         </is>
       </c>
       <c r="B10" s="17">
-        <f>COUNTIF('Video Log'!O2:O309,"Yes")</f>
+        <f>COUNTA('Video Log'!O2:O309)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Given a HoF rank</t>
+          <t>In the Hall of Fame</t>
         </is>
       </c>
       <c r="B11" s="17">
-        <f>COUNTA('Video Log'!P2:P309)</f>
+        <f>COUNTIF('Video Log'!Q2:Q309,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Affiliate links added</t>
+          <t>Given a HoF rank</t>
         </is>
       </c>
       <c r="B12" s="17">
@@ -18876,16 +19517,27 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Affiliate links added</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
+        <f>COUNTA('Video Log'!T2:T309)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>Hidden from the site</t>
         </is>
       </c>
-      <c r="B13" s="17">
-        <f>COUNTIF('Video Log'!V2:V309,"Yes")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B14" s="17">
+        <f>COUNTIF('Video Log'!X2:X309,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Counts update as you type. Blank cells are skipped by the import, so a half-filled sheet is fine.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -776,12 +776,12 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Hall of Fame</t>
+          <t>Greatest Hits</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Mark Yes on the rips you want in the gold section at the top of the home page. Rank orders them, 1 first. Leave Rank blank and the site orders by rarity then views.</t>
+          <t>Mark Yes on the RIPS you want in the gold section at the top of the home page. Rank orders them, 1 first. Leave Rank blank and the site orders by rarity then views. These are videos.</t>
         </is>
       </c>
     </row>
@@ -789,23 +789,36 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PSA 10 prices</t>
+          <t>Card Hall of Fame</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Put in a number you have actually seen, set PSA 10 Checked to the date you checked it (2026-08-11 format), and name the source. A graded price with no date is not a fact about anything, and a blank shows nothing rather than a guess.</t>
+          <t>On the Chase Cards tab. Mark Yes on the CARDS you have actually pulled. They get their own page, ranked by value, with the card image, the set, the raw near mint price and the PSA 10 price. These are cards, not videos, which is the whole difference between the two.</t>
         </is>
       </c>
     </row>
     <row r="32"/>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PSA 10 prices</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Put in a number you have actually seen, set PSA 10 Checked to the date you checked it (2026-08-11 format), and name the source. A graded price with no date is not a fact about anything, and a blank shows nothing rather than a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Careful</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Rebuilding this file overwrites it. Import your latest export FIRST, then rebuild. Anything already imported is carried back in; anything not is lost.</t>
         </is>
@@ -2514,8 +2527,8 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="40" customWidth="1" min="21" max="21"/>
@@ -2608,12 +2621,12 @@
       </c>
       <c r="Q1" s="10" t="inlineStr">
         <is>
-          <t>Hall of Fame</t>
+          <t>Greatest Hits</t>
         </is>
       </c>
       <c r="R1" s="10" t="inlineStr">
         <is>
-          <t>HoF Rank</t>
+          <t>Greatest Hits Rank</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
@@ -20924,7 +20937,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>In the Hall of Fame</t>
+          <t>In Greatest Hits</t>
         </is>
       </c>
       <c r="B11" s="18">
@@ -20935,7 +20948,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Given a HoF rank</t>
+          <t>Given a rank</t>
         </is>
       </c>
       <c r="B12" s="18">
@@ -20983,7 +20996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20996,8 +21009,10 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -21053,10 +21068,20 @@
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>Got It</t>
+          <t>Card Hall of Fame</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Pulled On</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Pulled In Video</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Why I Want It</t>
         </is>
@@ -21097,6 +21122,8 @@
       <c r="J2" s="15" t="n"/>
       <c r="K2" s="15" t="n"/>
       <c r="L2" s="15" t="n"/>
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -21133,6 +21160,8 @@
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
+      <c r="M3" s="15" t="n"/>
+      <c r="N3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -21169,6 +21198,8 @@
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="n"/>
+      <c r="N4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -21205,6 +21236,8 @@
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -21241,6 +21274,8 @@
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -21277,6 +21312,8 @@
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -21313,6 +21350,8 @@
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -21349,6 +21388,8 @@
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -21385,6 +21426,8 @@
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="n"/>
+      <c r="N10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -21421,6 +21464,8 @@
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -21457,6 +21502,8 @@
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -21493,6 +21540,8 @@
       <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
+      <c r="M13" s="15" t="n"/>
+      <c r="N13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -21529,6 +21578,8 @@
       <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -21565,6 +21616,8 @@
       <c r="J15" s="15" t="n"/>
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
+      <c r="M15" s="15" t="n"/>
+      <c r="N15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -21601,6 +21654,8 @@
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -21637,6 +21692,8 @@
       <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -21673,6 +21730,8 @@
       <c r="J18" s="15" t="n"/>
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -21709,6 +21768,8 @@
       <c r="J19" s="15" t="n"/>
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -21745,6 +21806,8 @@
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -21781,6 +21844,8 @@
       <c r="J21" s="15" t="n"/>
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -21817,6 +21882,8 @@
       <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -21853,6 +21920,8 @@
       <c r="J23" s="15" t="n"/>
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -21889,6 +21958,8 @@
       <c r="J24" s="15" t="n"/>
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -21925,6 +21996,8 @@
       <c r="J25" s="15" t="n"/>
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
+      <c r="M25" s="15" t="n"/>
+      <c r="N25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -21961,6 +22034,8 @@
       <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
+      <c r="M26" s="15" t="n"/>
+      <c r="N26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -21997,6 +22072,8 @@
       <c r="J27" s="15" t="n"/>
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
+      <c r="M27" s="15" t="n"/>
+      <c r="N27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -22033,6 +22110,8 @@
       <c r="J28" s="15" t="n"/>
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="n"/>
+      <c r="N28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -22069,6 +22148,8 @@
       <c r="J29" s="15" t="n"/>
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
+      <c r="M29" s="15" t="n"/>
+      <c r="N29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -22105,6 +22186,8 @@
       <c r="J30" s="15" t="n"/>
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
+      <c r="M30" s="15" t="n"/>
+      <c r="N30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -22141,6 +22224,8 @@
       <c r="J31" s="15" t="n"/>
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
+      <c r="M31" s="15" t="n"/>
+      <c r="N31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -22177,6 +22262,8 @@
       <c r="J32" s="15" t="n"/>
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -22213,6 +22300,8 @@
       <c r="J33" s="15" t="n"/>
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -22249,6 +22338,8 @@
       <c r="J34" s="15" t="n"/>
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -22285,6 +22376,8 @@
       <c r="J35" s="15" t="n"/>
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
+      <c r="M35" s="15" t="n"/>
+      <c r="N35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -22321,6 +22414,8 @@
       <c r="J36" s="15" t="n"/>
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -22357,6 +22452,8 @@
       <c r="J37" s="15" t="n"/>
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -22393,6 +22490,8 @@
       <c r="J38" s="15" t="n"/>
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
+      <c r="M38" s="15" t="n"/>
+      <c r="N38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -22429,6 +22528,8 @@
       <c r="J39" s="15" t="n"/>
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
+      <c r="M39" s="15" t="n"/>
+      <c r="N39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -22465,6 +22566,8 @@
       <c r="J40" s="15" t="n"/>
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
+      <c r="M40" s="15" t="n"/>
+      <c r="N40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -22501,6 +22604,8 @@
       <c r="J41" s="15" t="n"/>
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
+      <c r="M41" s="15" t="n"/>
+      <c r="N41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -22537,6 +22642,8 @@
       <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
+      <c r="M42" s="15" t="n"/>
+      <c r="N42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -22573,6 +22680,8 @@
       <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
+      <c r="M43" s="15" t="n"/>
+      <c r="N43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -22609,6 +22718,8 @@
       <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
+      <c r="M44" s="15" t="n"/>
+      <c r="N44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -22645,6 +22756,8 @@
       <c r="J45" s="15" t="n"/>
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
+      <c r="M45" s="15" t="n"/>
+      <c r="N45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -22681,6 +22794,8 @@
       <c r="J46" s="15" t="n"/>
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -22717,6 +22832,8 @@
       <c r="J47" s="15" t="n"/>
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
+      <c r="M47" s="15" t="n"/>
+      <c r="N47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -22753,6 +22870,8 @@
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
+      <c r="M48" s="15" t="n"/>
+      <c r="N48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -22789,6 +22908,8 @@
       <c r="J49" s="15" t="n"/>
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
+      <c r="M49" s="15" t="n"/>
+      <c r="N49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -22825,6 +22946,8 @@
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
+      <c r="M50" s="15" t="n"/>
+      <c r="N50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -22861,6 +22984,8 @@
       <c r="J51" s="15" t="n"/>
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
+      <c r="M51" s="15" t="n"/>
+      <c r="N51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -22897,6 +23022,8 @@
       <c r="J52" s="15" t="n"/>
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
+      <c r="M52" s="15" t="n"/>
+      <c r="N52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -22933,6 +23060,8 @@
       <c r="J53" s="15" t="n"/>
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
+      <c r="M53" s="15" t="n"/>
+      <c r="N53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -22969,6 +23098,8 @@
       <c r="J54" s="15" t="n"/>
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
+      <c r="M54" s="15" t="n"/>
+      <c r="N54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -23005,6 +23136,8 @@
       <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
+      <c r="M55" s="15" t="n"/>
+      <c r="N55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -23041,6 +23174,8 @@
       <c r="J56" s="15" t="n"/>
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
+      <c r="M56" s="15" t="n"/>
+      <c r="N56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -23077,6 +23212,8 @@
       <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
+      <c r="M57" s="15" t="n"/>
+      <c r="N57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -23113,6 +23250,8 @@
       <c r="J58" s="15" t="n"/>
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
+      <c r="M58" s="15" t="n"/>
+      <c r="N58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -23149,6 +23288,8 @@
       <c r="J59" s="15" t="n"/>
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
+      <c r="M59" s="15" t="n"/>
+      <c r="N59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -23185,6 +23326,8 @@
       <c r="J60" s="15" t="n"/>
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
+      <c r="M60" s="15" t="n"/>
+      <c r="N60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -23221,6 +23364,8 @@
       <c r="J61" s="15" t="n"/>
       <c r="K61" s="15" t="n"/>
       <c r="L61" s="15" t="n"/>
+      <c r="M61" s="15" t="n"/>
+      <c r="N61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -23257,6 +23402,8 @@
       <c r="J62" s="15" t="n"/>
       <c r="K62" s="15" t="n"/>
       <c r="L62" s="15" t="n"/>
+      <c r="M62" s="15" t="n"/>
+      <c r="N62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -23293,6 +23440,8 @@
       <c r="J63" s="15" t="n"/>
       <c r="K63" s="15" t="n"/>
       <c r="L63" s="15" t="n"/>
+      <c r="M63" s="15" t="n"/>
+      <c r="N63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -23329,6 +23478,8 @@
       <c r="J64" s="15" t="n"/>
       <c r="K64" s="15" t="n"/>
       <c r="L64" s="15" t="n"/>
+      <c r="M64" s="15" t="n"/>
+      <c r="N64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -23365,6 +23516,8 @@
       <c r="J65" s="15" t="n"/>
       <c r="K65" s="15" t="n"/>
       <c r="L65" s="15" t="n"/>
+      <c r="M65" s="15" t="n"/>
+      <c r="N65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -23401,6 +23554,8 @@
       <c r="J66" s="15" t="n"/>
       <c r="K66" s="15" t="n"/>
       <c r="L66" s="15" t="n"/>
+      <c r="M66" s="15" t="n"/>
+      <c r="N66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -23437,6 +23592,8 @@
       <c r="J67" s="15" t="n"/>
       <c r="K67" s="15" t="n"/>
       <c r="L67" s="15" t="n"/>
+      <c r="M67" s="15" t="n"/>
+      <c r="N67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -23473,6 +23630,8 @@
       <c r="J68" s="15" t="n"/>
       <c r="K68" s="15" t="n"/>
       <c r="L68" s="15" t="n"/>
+      <c r="M68" s="15" t="n"/>
+      <c r="N68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -23509,6 +23668,8 @@
       <c r="J69" s="15" t="n"/>
       <c r="K69" s="15" t="n"/>
       <c r="L69" s="15" t="n"/>
+      <c r="M69" s="15" t="n"/>
+      <c r="N69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -23545,6 +23706,8 @@
       <c r="J70" s="15" t="n"/>
       <c r="K70" s="15" t="n"/>
       <c r="L70" s="15" t="n"/>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -23581,6 +23744,8 @@
       <c r="J71" s="15" t="n"/>
       <c r="K71" s="15" t="n"/>
       <c r="L71" s="15" t="n"/>
+      <c r="M71" s="15" t="n"/>
+      <c r="N71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -23617,6 +23782,8 @@
       <c r="J72" s="15" t="n"/>
       <c r="K72" s="15" t="n"/>
       <c r="L72" s="15" t="n"/>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -23653,6 +23820,8 @@
       <c r="J73" s="15" t="n"/>
       <c r="K73" s="15" t="n"/>
       <c r="L73" s="15" t="n"/>
+      <c r="M73" s="15" t="n"/>
+      <c r="N73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -23689,6 +23858,8 @@
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n"/>
       <c r="L74" s="15" t="n"/>
+      <c r="M74" s="15" t="n"/>
+      <c r="N74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -23725,6 +23896,8 @@
       <c r="J75" s="15" t="n"/>
       <c r="K75" s="15" t="n"/>
       <c r="L75" s="15" t="n"/>
+      <c r="M75" s="15" t="n"/>
+      <c r="N75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -23761,6 +23934,8 @@
       <c r="J76" s="15" t="n"/>
       <c r="K76" s="15" t="n"/>
       <c r="L76" s="15" t="n"/>
+      <c r="M76" s="15" t="n"/>
+      <c r="N76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -23797,6 +23972,8 @@
       <c r="J77" s="15" t="n"/>
       <c r="K77" s="15" t="n"/>
       <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -23833,6 +24010,8 @@
       <c r="J78" s="15" t="n"/>
       <c r="K78" s="15" t="n"/>
       <c r="L78" s="15" t="n"/>
+      <c r="M78" s="15" t="n"/>
+      <c r="N78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -23869,6 +24048,8 @@
       <c r="J79" s="15" t="n"/>
       <c r="K79" s="15" t="n"/>
       <c r="L79" s="15" t="n"/>
+      <c r="M79" s="15" t="n"/>
+      <c r="N79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -23905,6 +24086,8 @@
       <c r="J80" s="15" t="n"/>
       <c r="K80" s="15" t="n"/>
       <c r="L80" s="15" t="n"/>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -23941,6 +24124,8 @@
       <c r="J81" s="15" t="n"/>
       <c r="K81" s="15" t="n"/>
       <c r="L81" s="15" t="n"/>
+      <c r="M81" s="15" t="n"/>
+      <c r="N81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -23977,6 +24162,8 @@
       <c r="J82" s="15" t="n"/>
       <c r="K82" s="15" t="n"/>
       <c r="L82" s="15" t="n"/>
+      <c r="M82" s="15" t="n"/>
+      <c r="N82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -24013,6 +24200,8 @@
       <c r="J83" s="15" t="n"/>
       <c r="K83" s="15" t="n"/>
       <c r="L83" s="15" t="n"/>
+      <c r="M83" s="15" t="n"/>
+      <c r="N83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -24049,6 +24238,8 @@
       <c r="J84" s="15" t="n"/>
       <c r="K84" s="15" t="n"/>
       <c r="L84" s="15" t="n"/>
+      <c r="M84" s="15" t="n"/>
+      <c r="N84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -24085,6 +24276,8 @@
       <c r="J85" s="15" t="n"/>
       <c r="K85" s="15" t="n"/>
       <c r="L85" s="15" t="n"/>
+      <c r="M85" s="15" t="n"/>
+      <c r="N85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -24121,6 +24314,8 @@
       <c r="J86" s="15" t="n"/>
       <c r="K86" s="15" t="n"/>
       <c r="L86" s="15" t="n"/>
+      <c r="M86" s="15" t="n"/>
+      <c r="N86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -24157,6 +24352,8 @@
       <c r="J87" s="15" t="n"/>
       <c r="K87" s="15" t="n"/>
       <c r="L87" s="15" t="n"/>
+      <c r="M87" s="15" t="n"/>
+      <c r="N87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -24193,6 +24390,8 @@
       <c r="J88" s="15" t="n"/>
       <c r="K88" s="15" t="n"/>
       <c r="L88" s="15" t="n"/>
+      <c r="M88" s="15" t="n"/>
+      <c r="N88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
@@ -24229,6 +24428,8 @@
       <c r="J89" s="15" t="n"/>
       <c r="K89" s="15" t="n"/>
       <c r="L89" s="15" t="n"/>
+      <c r="M89" s="15" t="n"/>
+      <c r="N89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -24265,6 +24466,8 @@
       <c r="J90" s="15" t="n"/>
       <c r="K90" s="15" t="n"/>
       <c r="L90" s="15" t="n"/>
+      <c r="M90" s="15" t="n"/>
+      <c r="N90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -24301,6 +24504,8 @@
       <c r="J91" s="15" t="n"/>
       <c r="K91" s="15" t="n"/>
       <c r="L91" s="15" t="n"/>
+      <c r="M91" s="15" t="n"/>
+      <c r="N91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
@@ -24337,6 +24542,8 @@
       <c r="J92" s="15" t="n"/>
       <c r="K92" s="15" t="n"/>
       <c r="L92" s="15" t="n"/>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -24373,6 +24580,8 @@
       <c r="J93" s="15" t="n"/>
       <c r="K93" s="15" t="n"/>
       <c r="L93" s="15" t="n"/>
+      <c r="M93" s="15" t="n"/>
+      <c r="N93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -24409,6 +24618,8 @@
       <c r="J94" s="15" t="n"/>
       <c r="K94" s="15" t="n"/>
       <c r="L94" s="15" t="n"/>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -24445,6 +24656,8 @@
       <c r="J95" s="15" t="n"/>
       <c r="K95" s="15" t="n"/>
       <c r="L95" s="15" t="n"/>
+      <c r="M95" s="15" t="n"/>
+      <c r="N95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -24481,6 +24694,8 @@
       <c r="J96" s="15" t="n"/>
       <c r="K96" s="15" t="n"/>
       <c r="L96" s="15" t="n"/>
+      <c r="M96" s="15" t="n"/>
+      <c r="N96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -24517,6 +24732,8 @@
       <c r="J97" s="15" t="n"/>
       <c r="K97" s="15" t="n"/>
       <c r="L97" s="15" t="n"/>
+      <c r="M97" s="15" t="n"/>
+      <c r="N97" s="15" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -24553,6 +24770,8 @@
       <c r="J98" s="15" t="n"/>
       <c r="K98" s="15" t="n"/>
       <c r="L98" s="15" t="n"/>
+      <c r="M98" s="15" t="n"/>
+      <c r="N98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -24589,6 +24808,8 @@
       <c r="J99" s="15" t="n"/>
       <c r="K99" s="15" t="n"/>
       <c r="L99" s="15" t="n"/>
+      <c r="M99" s="15" t="n"/>
+      <c r="N99" s="15" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -24625,6 +24846,8 @@
       <c r="J100" s="15" t="n"/>
       <c r="K100" s="15" t="n"/>
       <c r="L100" s="15" t="n"/>
+      <c r="M100" s="15" t="n"/>
+      <c r="N100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
@@ -24661,6 +24884,8 @@
       <c r="J101" s="15" t="n"/>
       <c r="K101" s="15" t="n"/>
       <c r="L101" s="15" t="n"/>
+      <c r="M101" s="15" t="n"/>
+      <c r="N101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -24697,6 +24922,8 @@
       <c r="J102" s="15" t="n"/>
       <c r="K102" s="15" t="n"/>
       <c r="L102" s="15" t="n"/>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -24733,6 +24960,8 @@
       <c r="J103" s="15" t="n"/>
       <c r="K103" s="15" t="n"/>
       <c r="L103" s="15" t="n"/>
+      <c r="M103" s="15" t="n"/>
+      <c r="N103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -24769,6 +24998,8 @@
       <c r="J104" s="15" t="n"/>
       <c r="K104" s="15" t="n"/>
       <c r="L104" s="15" t="n"/>
+      <c r="M104" s="15" t="n"/>
+      <c r="N104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -24805,6 +25036,8 @@
       <c r="J105" s="15" t="n"/>
       <c r="K105" s="15" t="n"/>
       <c r="L105" s="15" t="n"/>
+      <c r="M105" s="15" t="n"/>
+      <c r="N105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -24841,6 +25074,8 @@
       <c r="J106" s="15" t="n"/>
       <c r="K106" s="15" t="n"/>
       <c r="L106" s="15" t="n"/>
+      <c r="M106" s="15" t="n"/>
+      <c r="N106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -24877,6 +25112,8 @@
       <c r="J107" s="15" t="n"/>
       <c r="K107" s="15" t="n"/>
       <c r="L107" s="15" t="n"/>
+      <c r="M107" s="15" t="n"/>
+      <c r="N107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -24913,6 +25150,8 @@
       <c r="J108" s="15" t="n"/>
       <c r="K108" s="15" t="n"/>
       <c r="L108" s="15" t="n"/>
+      <c r="M108" s="15" t="n"/>
+      <c r="N108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -24949,6 +25188,8 @@
       <c r="J109" s="15" t="n"/>
       <c r="K109" s="15" t="n"/>
       <c r="L109" s="15" t="n"/>
+      <c r="M109" s="15" t="n"/>
+      <c r="N109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -24985,6 +25226,8 @@
       <c r="J110" s="15" t="n"/>
       <c r="K110" s="15" t="n"/>
       <c r="L110" s="15" t="n"/>
+      <c r="M110" s="15" t="n"/>
+      <c r="N110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -25021,6 +25264,8 @@
       <c r="J111" s="15" t="n"/>
       <c r="K111" s="15" t="n"/>
       <c r="L111" s="15" t="n"/>
+      <c r="M111" s="15" t="n"/>
+      <c r="N111" s="15" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -25057,6 +25302,8 @@
       <c r="J112" s="15" t="n"/>
       <c r="K112" s="15" t="n"/>
       <c r="L112" s="15" t="n"/>
+      <c r="M112" s="15" t="n"/>
+      <c r="N112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -25093,6 +25340,8 @@
       <c r="J113" s="15" t="n"/>
       <c r="K113" s="15" t="n"/>
       <c r="L113" s="15" t="n"/>
+      <c r="M113" s="15" t="n"/>
+      <c r="N113" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
@@ -25129,6 +25378,8 @@
       <c r="J114" s="15" t="n"/>
       <c r="K114" s="15" t="n"/>
       <c r="L114" s="15" t="n"/>
+      <c r="M114" s="15" t="n"/>
+      <c r="N114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -25165,6 +25416,8 @@
       <c r="J115" s="15" t="n"/>
       <c r="K115" s="15" t="n"/>
       <c r="L115" s="15" t="n"/>
+      <c r="M115" s="15" t="n"/>
+      <c r="N115" s="15" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
@@ -25201,6 +25454,8 @@
       <c r="J116" s="15" t="n"/>
       <c r="K116" s="15" t="n"/>
       <c r="L116" s="15" t="n"/>
+      <c r="M116" s="15" t="n"/>
+      <c r="N116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -25237,6 +25492,8 @@
       <c r="J117" s="15" t="n"/>
       <c r="K117" s="15" t="n"/>
       <c r="L117" s="15" t="n"/>
+      <c r="M117" s="15" t="n"/>
+      <c r="N117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
@@ -25273,6 +25530,8 @@
       <c r="J118" s="15" t="n"/>
       <c r="K118" s="15" t="n"/>
       <c r="L118" s="15" t="n"/>
+      <c r="M118" s="15" t="n"/>
+      <c r="N118" s="15" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
@@ -25309,6 +25568,8 @@
       <c r="J119" s="15" t="n"/>
       <c r="K119" s="15" t="n"/>
       <c r="L119" s="15" t="n"/>
+      <c r="M119" s="15" t="n"/>
+      <c r="N119" s="15" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -25345,6 +25606,8 @@
       <c r="J120" s="15" t="n"/>
       <c r="K120" s="15" t="n"/>
       <c r="L120" s="15" t="n"/>
+      <c r="M120" s="15" t="n"/>
+      <c r="N120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -25381,6 +25644,8 @@
       <c r="J121" s="15" t="n"/>
       <c r="K121" s="15" t="n"/>
       <c r="L121" s="15" t="n"/>
+      <c r="M121" s="15" t="n"/>
+      <c r="N121" s="15" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -25417,6 +25682,8 @@
       <c r="J122" s="15" t="n"/>
       <c r="K122" s="15" t="n"/>
       <c r="L122" s="15" t="n"/>
+      <c r="M122" s="15" t="n"/>
+      <c r="N122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -25453,6 +25720,8 @@
       <c r="J123" s="15" t="n"/>
       <c r="K123" s="15" t="n"/>
       <c r="L123" s="15" t="n"/>
+      <c r="M123" s="15" t="n"/>
+      <c r="N123" s="15" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -25489,6 +25758,8 @@
       <c r="J124" s="15" t="n"/>
       <c r="K124" s="15" t="n"/>
       <c r="L124" s="15" t="n"/>
+      <c r="M124" s="15" t="n"/>
+      <c r="N124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -25525,6 +25796,8 @@
       <c r="J125" s="15" t="n"/>
       <c r="K125" s="15" t="n"/>
       <c r="L125" s="15" t="n"/>
+      <c r="M125" s="15" t="n"/>
+      <c r="N125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -25561,6 +25834,8 @@
       <c r="J126" s="15" t="n"/>
       <c r="K126" s="15" t="n"/>
       <c r="L126" s="15" t="n"/>
+      <c r="M126" s="15" t="n"/>
+      <c r="N126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -25597,6 +25872,8 @@
       <c r="J127" s="15" t="n"/>
       <c r="K127" s="15" t="n"/>
       <c r="L127" s="15" t="n"/>
+      <c r="M127" s="15" t="n"/>
+      <c r="N127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -25633,6 +25910,8 @@
       <c r="J128" s="15" t="n"/>
       <c r="K128" s="15" t="n"/>
       <c r="L128" s="15" t="n"/>
+      <c r="M128" s="15" t="n"/>
+      <c r="N128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -25669,6 +25948,8 @@
       <c r="J129" s="15" t="n"/>
       <c r="K129" s="15" t="n"/>
       <c r="L129" s="15" t="n"/>
+      <c r="M129" s="15" t="n"/>
+      <c r="N129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
@@ -25705,6 +25986,8 @@
       <c r="J130" s="15" t="n"/>
       <c r="K130" s="15" t="n"/>
       <c r="L130" s="15" t="n"/>
+      <c r="M130" s="15" t="n"/>
+      <c r="N130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -25741,6 +26024,8 @@
       <c r="J131" s="15" t="n"/>
       <c r="K131" s="15" t="n"/>
       <c r="L131" s="15" t="n"/>
+      <c r="M131" s="15" t="n"/>
+      <c r="N131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -25777,6 +26062,8 @@
       <c r="J132" s="15" t="n"/>
       <c r="K132" s="15" t="n"/>
       <c r="L132" s="15" t="n"/>
+      <c r="M132" s="15" t="n"/>
+      <c r="N132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -25813,6 +26100,8 @@
       <c r="J133" s="15" t="n"/>
       <c r="K133" s="15" t="n"/>
       <c r="L133" s="15" t="n"/>
+      <c r="M133" s="15" t="n"/>
+      <c r="N133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -25849,6 +26138,8 @@
       <c r="J134" s="15" t="n"/>
       <c r="K134" s="15" t="n"/>
       <c r="L134" s="15" t="n"/>
+      <c r="M134" s="15" t="n"/>
+      <c r="N134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -25885,6 +26176,8 @@
       <c r="J135" s="15" t="n"/>
       <c r="K135" s="15" t="n"/>
       <c r="L135" s="15" t="n"/>
+      <c r="M135" s="15" t="n"/>
+      <c r="N135" s="15" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
@@ -25921,6 +26214,8 @@
       <c r="J136" s="15" t="n"/>
       <c r="K136" s="15" t="n"/>
       <c r="L136" s="15" t="n"/>
+      <c r="M136" s="15" t="n"/>
+      <c r="N136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -25957,6 +26252,8 @@
       <c r="J137" s="15" t="n"/>
       <c r="K137" s="15" t="n"/>
       <c r="L137" s="15" t="n"/>
+      <c r="M137" s="15" t="n"/>
+      <c r="N137" s="15" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -25993,6 +26290,8 @@
       <c r="J138" s="15" t="n"/>
       <c r="K138" s="15" t="n"/>
       <c r="L138" s="15" t="n"/>
+      <c r="M138" s="15" t="n"/>
+      <c r="N138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -26029,6 +26328,8 @@
       <c r="J139" s="15" t="n"/>
       <c r="K139" s="15" t="n"/>
       <c r="L139" s="15" t="n"/>
+      <c r="M139" s="15" t="n"/>
+      <c r="N139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -26065,6 +26366,8 @@
       <c r="J140" s="15" t="n"/>
       <c r="K140" s="15" t="n"/>
       <c r="L140" s="15" t="n"/>
+      <c r="M140" s="15" t="n"/>
+      <c r="N140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
@@ -26101,6 +26404,8 @@
       <c r="J141" s="15" t="n"/>
       <c r="K141" s="15" t="n"/>
       <c r="L141" s="15" t="n"/>
+      <c r="M141" s="15" t="n"/>
+      <c r="N141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
@@ -26137,6 +26442,8 @@
       <c r="J142" s="15" t="n"/>
       <c r="K142" s="15" t="n"/>
       <c r="L142" s="15" t="n"/>
+      <c r="M142" s="15" t="n"/>
+      <c r="N142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -26173,6 +26480,8 @@
       <c r="J143" s="15" t="n"/>
       <c r="K143" s="15" t="n"/>
       <c r="L143" s="15" t="n"/>
+      <c r="M143" s="15" t="n"/>
+      <c r="N143" s="15" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -26209,6 +26518,8 @@
       <c r="J144" s="15" t="n"/>
       <c r="K144" s="15" t="n"/>
       <c r="L144" s="15" t="n"/>
+      <c r="M144" s="15" t="n"/>
+      <c r="N144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -26245,6 +26556,8 @@
       <c r="J145" s="15" t="n"/>
       <c r="K145" s="15" t="n"/>
       <c r="L145" s="15" t="n"/>
+      <c r="M145" s="15" t="n"/>
+      <c r="N145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
@@ -26281,6 +26594,8 @@
       <c r="J146" s="15" t="n"/>
       <c r="K146" s="15" t="n"/>
       <c r="L146" s="15" t="n"/>
+      <c r="M146" s="15" t="n"/>
+      <c r="N146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -26317,6 +26632,8 @@
       <c r="J147" s="15" t="n"/>
       <c r="K147" s="15" t="n"/>
       <c r="L147" s="15" t="n"/>
+      <c r="M147" s="15" t="n"/>
+      <c r="N147" s="15" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -26353,6 +26670,8 @@
       <c r="J148" s="15" t="n"/>
       <c r="K148" s="15" t="n"/>
       <c r="L148" s="15" t="n"/>
+      <c r="M148" s="15" t="n"/>
+      <c r="N148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -26389,6 +26708,8 @@
       <c r="J149" s="15" t="n"/>
       <c r="K149" s="15" t="n"/>
       <c r="L149" s="15" t="n"/>
+      <c r="M149" s="15" t="n"/>
+      <c r="N149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
@@ -26425,6 +26746,8 @@
       <c r="J150" s="15" t="n"/>
       <c r="K150" s="15" t="n"/>
       <c r="L150" s="15" t="n"/>
+      <c r="M150" s="15" t="n"/>
+      <c r="N150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -26461,6 +26784,8 @@
       <c r="J151" s="15" t="n"/>
       <c r="K151" s="15" t="n"/>
       <c r="L151" s="15" t="n"/>
+      <c r="M151" s="15" t="n"/>
+      <c r="N151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -26497,6 +26822,8 @@
       <c r="J152" s="15" t="n"/>
       <c r="K152" s="15" t="n"/>
       <c r="L152" s="15" t="n"/>
+      <c r="M152" s="15" t="n"/>
+      <c r="N152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -26533,6 +26860,8 @@
       <c r="J153" s="15" t="n"/>
       <c r="K153" s="15" t="n"/>
       <c r="L153" s="15" t="n"/>
+      <c r="M153" s="15" t="n"/>
+      <c r="N153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -26574,7 +26903,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L154" s="14" t="inlineStr">
+      <c r="L154" s="15" t="n"/>
+      <c r="M154" s="15" t="n"/>
+      <c r="N154" s="14" t="inlineStr">
         <is>
           <t>The one. Pitch Black's chase, and the reason the box keeps getting opened.</t>
         </is>
@@ -26620,7 +26951,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L155" s="14" t="inlineStr">
+      <c r="L155" s="15" t="n"/>
+      <c r="M155" s="15" t="n"/>
+      <c r="N155" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising's best art, and still hiding.</t>
         </is>
@@ -26666,7 +26999,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L156" s="14" t="inlineStr">
+      <c r="L156" s="15" t="n"/>
+      <c r="M156" s="15" t="n"/>
+      <c r="N156" s="14" t="inlineStr">
         <is>
           <t>Perfect Order's SIR. Pulled everything else in the set except this.</t>
         </is>
@@ -26675,7 +27010,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Key is what links a row back to a card and must not be edited. PSA 10 Checked is a date like 2026-08-11: a graded price with no date is not a fact about anything.</t>
+          <t>Most Wanted is a card you are still chasing. Card Hall of Fame is one you have actually pulled, and it appears on /hall.html ranked by value, PSA 10 first and raw where there is no graded price. A card can be both while you chase a second copy. Key is what links a row back to a card and must not be edited. PSA 10 Checked is a date like 2026-08-11: a graded price with no date is not a fact about anything.</t>
         </is>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -20962,7 +20962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20971,10 +20971,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21010,20 +21008,10 @@
       </c>
       <c r="G1" s="17" t="inlineStr">
         <is>
-          <t>Pack Price USD</t>
+          <t>Fun Fact 1</t>
         </is>
       </c>
       <c r="H1" s="17" t="inlineStr">
-        <is>
-          <t>Booster Box Price USD</t>
-        </is>
-      </c>
-      <c r="I1" s="17" t="inlineStr">
-        <is>
-          <t>Fun Fact 1</t>
-        </is>
-      </c>
-      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Fun Fact 2</t>
         </is>
@@ -21054,8 +21042,6 @@
       <c r="F2" s="15" t="n"/>
       <c r="G2" s="15" t="n"/>
       <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -21082,8 +21068,6 @@
       <c r="F3" s="15" t="n"/>
       <c r="G3" s="15" t="n"/>
       <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -21110,8 +21094,6 @@
       <c r="F4" s="15" t="n"/>
       <c r="G4" s="15" t="n"/>
       <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
-      <c r="J4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -21138,8 +21120,6 @@
       <c r="F5" s="15" t="n"/>
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -21166,8 +21146,6 @@
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -21194,8 +21172,6 @@
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -21222,8 +21198,6 @@
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -21250,8 +21224,6 @@
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -21278,8 +21250,6 @@
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -21306,8 +21276,6 @@
       <c r="F11" s="15" t="n"/>
       <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -21334,8 +21302,6 @@
       <c r="F12" s="15" t="n"/>
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -21362,8 +21328,6 @@
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -21390,8 +21354,6 @@
       <c r="F14" s="15" t="n"/>
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -21418,8 +21380,6 @@
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -21446,8 +21406,6 @@
       <c r="F16" s="15" t="n"/>
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -21474,8 +21432,6 @@
       <c r="F17" s="15" t="n"/>
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -21502,8 +21458,6 @@
       <c r="F18" s="15" t="n"/>
       <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -21530,8 +21484,6 @@
       <c r="F19" s="15" t="n"/>
       <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -21558,8 +21510,6 @@
       <c r="F20" s="15" t="n"/>
       <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -21586,8 +21536,6 @@
       <c r="F21" s="15" t="n"/>
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -21614,8 +21562,6 @@
       <c r="F22" s="15" t="n"/>
       <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -21642,8 +21588,6 @@
       <c r="F23" s="15" t="n"/>
       <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -21670,8 +21614,6 @@
       <c r="F24" s="15" t="n"/>
       <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Set Notes" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Chase Cards" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Shops" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="My Hits" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Shops" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -119,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +159,7 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27959,6 +27962,4495 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I403"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Video ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Rarity</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Raw NM USD</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>PSA 10 USD</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Hall of Fame</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="15" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="15" t="n"/>
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="15" t="n"/>
+      <c r="I49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="15" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="15" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="15" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="15" t="n"/>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="15" t="n"/>
+      <c r="I57" s="15" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="15" t="n"/>
+      <c r="E59" s="15" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="15" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="15" t="n"/>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="15" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="15" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n"/>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="15" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n"/>
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="15" t="n"/>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="15" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="15" t="n"/>
+      <c r="D65" s="15" t="n"/>
+      <c r="E65" s="15" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="15" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="15" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="15" t="n"/>
+      <c r="D67" s="15" t="n"/>
+      <c r="E67" s="15" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="15" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="15" t="n"/>
+      <c r="D68" s="15" t="n"/>
+      <c r="E68" s="15" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="15" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="15" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="15" t="n"/>
+      <c r="E70" s="15" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="15" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n"/>
+      <c r="B71" s="15" t="n"/>
+      <c r="C71" s="15" t="n"/>
+      <c r="D71" s="15" t="n"/>
+      <c r="E71" s="15" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="15" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="15" t="n"/>
+      <c r="D72" s="15" t="n"/>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="15" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="21" t="n"/>
+      <c r="G73" s="21" t="n"/>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="15" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n"/>
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="15" t="n"/>
+      <c r="D74" s="15" t="n"/>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="15" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n"/>
+      <c r="B75" s="15" t="n"/>
+      <c r="C75" s="15" t="n"/>
+      <c r="D75" s="15" t="n"/>
+      <c r="E75" s="15" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="15" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n"/>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="21" t="n"/>
+      <c r="G76" s="21" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="15" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n"/>
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="15" t="n"/>
+      <c r="D77" s="15" t="n"/>
+      <c r="E77" s="15" t="n"/>
+      <c r="F77" s="21" t="n"/>
+      <c r="G77" s="21" t="n"/>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="15" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n"/>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="15" t="n"/>
+      <c r="E78" s="15" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="15" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="15" t="n"/>
+      <c r="D79" s="15" t="n"/>
+      <c r="E79" s="15" t="n"/>
+      <c r="F79" s="21" t="n"/>
+      <c r="G79" s="21" t="n"/>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="15" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n"/>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="15" t="n"/>
+      <c r="D80" s="15" t="n"/>
+      <c r="E80" s="15" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="21" t="n"/>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="15" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n"/>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="15" t="n"/>
+      <c r="D81" s="15" t="n"/>
+      <c r="E81" s="15" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="15" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="15" t="n"/>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="15" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n"/>
+      <c r="B83" s="15" t="n"/>
+      <c r="C83" s="15" t="n"/>
+      <c r="D83" s="15" t="n"/>
+      <c r="E83" s="15" t="n"/>
+      <c r="F83" s="21" t="n"/>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="15" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n"/>
+      <c r="B84" s="15" t="n"/>
+      <c r="C84" s="15" t="n"/>
+      <c r="D84" s="15" t="n"/>
+      <c r="E84" s="15" t="n"/>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="15" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n"/>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="15" t="n"/>
+      <c r="D85" s="15" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="21" t="n"/>
+      <c r="G85" s="21" t="n"/>
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="15" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n"/>
+      <c r="B86" s="15" t="n"/>
+      <c r="C86" s="15" t="n"/>
+      <c r="D86" s="15" t="n"/>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="21" t="n"/>
+      <c r="G86" s="21" t="n"/>
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="15" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n"/>
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="15" t="n"/>
+      <c r="D87" s="15" t="n"/>
+      <c r="E87" s="15" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="15" t="n"/>
+      <c r="I87" s="15" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n"/>
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="15" t="n"/>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="21" t="n"/>
+      <c r="G88" s="21" t="n"/>
+      <c r="H88" s="15" t="n"/>
+      <c r="I88" s="15" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n"/>
+      <c r="B89" s="15" t="n"/>
+      <c r="C89" s="15" t="n"/>
+      <c r="D89" s="15" t="n"/>
+      <c r="E89" s="15" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="15" t="n"/>
+      <c r="I89" s="15" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n"/>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="15" t="n"/>
+      <c r="D90" s="15" t="n"/>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="15" t="n"/>
+      <c r="I90" s="15" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n"/>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="15" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n"/>
+      <c r="B92" s="15" t="n"/>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="15" t="n"/>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="15" t="n"/>
+      <c r="I92" s="15" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n"/>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="15" t="n"/>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="15" t="n"/>
+      <c r="I93" s="15" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n"/>
+      <c r="B94" s="15" t="n"/>
+      <c r="C94" s="15" t="n"/>
+      <c r="D94" s="15" t="n"/>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="21" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="15" t="n"/>
+      <c r="I94" s="15" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n"/>
+      <c r="B95" s="15" t="n"/>
+      <c r="C95" s="15" t="n"/>
+      <c r="D95" s="15" t="n"/>
+      <c r="E95" s="15" t="n"/>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="15" t="n"/>
+      <c r="I95" s="15" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="n"/>
+      <c r="B96" s="15" t="n"/>
+      <c r="C96" s="15" t="n"/>
+      <c r="D96" s="15" t="n"/>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="15" t="n"/>
+      <c r="I96" s="15" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n"/>
+      <c r="B97" s="15" t="n"/>
+      <c r="C97" s="15" t="n"/>
+      <c r="D97" s="15" t="n"/>
+      <c r="E97" s="15" t="n"/>
+      <c r="F97" s="21" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="15" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n"/>
+      <c r="B98" s="15" t="n"/>
+      <c r="C98" s="15" t="n"/>
+      <c r="D98" s="15" t="n"/>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="15" t="n"/>
+      <c r="I98" s="15" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n"/>
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="15" t="n"/>
+      <c r="D99" s="15" t="n"/>
+      <c r="E99" s="15" t="n"/>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="15" t="n"/>
+      <c r="I99" s="15" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n"/>
+      <c r="B100" s="15" t="n"/>
+      <c r="C100" s="15" t="n"/>
+      <c r="D100" s="15" t="n"/>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="21" t="n"/>
+      <c r="G100" s="21" t="n"/>
+      <c r="H100" s="15" t="n"/>
+      <c r="I100" s="15" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="15" t="n"/>
+      <c r="C101" s="15" t="n"/>
+      <c r="D101" s="15" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="15" t="n"/>
+      <c r="I101" s="15" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n"/>
+      <c r="B102" s="15" t="n"/>
+      <c r="C102" s="15" t="n"/>
+      <c r="D102" s="15" t="n"/>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="15" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n"/>
+      <c r="B103" s="15" t="n"/>
+      <c r="C103" s="15" t="n"/>
+      <c r="D103" s="15" t="n"/>
+      <c r="E103" s="15" t="n"/>
+      <c r="F103" s="21" t="n"/>
+      <c r="G103" s="21" t="n"/>
+      <c r="H103" s="15" t="n"/>
+      <c r="I103" s="15" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n"/>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="15" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="15" t="n"/>
+      <c r="I104" s="15" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n"/>
+      <c r="B105" s="15" t="n"/>
+      <c r="C105" s="15" t="n"/>
+      <c r="D105" s="15" t="n"/>
+      <c r="E105" s="15" t="n"/>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="15" t="n"/>
+      <c r="I105" s="15" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n"/>
+      <c r="B106" s="15" t="n"/>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="21" t="n"/>
+      <c r="G106" s="21" t="n"/>
+      <c r="H106" s="15" t="n"/>
+      <c r="I106" s="15" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n"/>
+      <c r="B107" s="15" t="n"/>
+      <c r="C107" s="15" t="n"/>
+      <c r="D107" s="15" t="n"/>
+      <c r="E107" s="15" t="n"/>
+      <c r="F107" s="21" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="15" t="n"/>
+      <c r="I107" s="15" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n"/>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="21" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="15" t="n"/>
+      <c r="I108" s="15" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n"/>
+      <c r="B109" s="15" t="n"/>
+      <c r="C109" s="15" t="n"/>
+      <c r="D109" s="15" t="n"/>
+      <c r="E109" s="15" t="n"/>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="15" t="n"/>
+      <c r="I109" s="15" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n"/>
+      <c r="B110" s="15" t="n"/>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="15" t="n"/>
+      <c r="E110" s="15" t="n"/>
+      <c r="F110" s="21" t="n"/>
+      <c r="G110" s="21" t="n"/>
+      <c r="H110" s="15" t="n"/>
+      <c r="I110" s="15" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n"/>
+      <c r="B111" s="15" t="n"/>
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="21" t="n"/>
+      <c r="G111" s="21" t="n"/>
+      <c r="H111" s="15" t="n"/>
+      <c r="I111" s="15" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n"/>
+      <c r="B112" s="15" t="n"/>
+      <c r="C112" s="15" t="n"/>
+      <c r="D112" s="15" t="n"/>
+      <c r="E112" s="15" t="n"/>
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="15" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n"/>
+      <c r="B113" s="15" t="n"/>
+      <c r="C113" s="15" t="n"/>
+      <c r="D113" s="15" t="n"/>
+      <c r="E113" s="15" t="n"/>
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="15" t="n"/>
+      <c r="I113" s="15" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n"/>
+      <c r="B114" s="15" t="n"/>
+      <c r="C114" s="15" t="n"/>
+      <c r="D114" s="15" t="n"/>
+      <c r="E114" s="15" t="n"/>
+      <c r="F114" s="21" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="15" t="n"/>
+      <c r="I114" s="15" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n"/>
+      <c r="B115" s="15" t="n"/>
+      <c r="C115" s="15" t="n"/>
+      <c r="D115" s="15" t="n"/>
+      <c r="E115" s="15" t="n"/>
+      <c r="F115" s="21" t="n"/>
+      <c r="G115" s="21" t="n"/>
+      <c r="H115" s="15" t="n"/>
+      <c r="I115" s="15" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="n"/>
+      <c r="B116" s="15" t="n"/>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="21" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="15" t="n"/>
+      <c r="I116" s="15" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="n"/>
+      <c r="B117" s="15" t="n"/>
+      <c r="C117" s="15" t="n"/>
+      <c r="D117" s="15" t="n"/>
+      <c r="E117" s="15" t="n"/>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="15" t="n"/>
+      <c r="I117" s="15" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="n"/>
+      <c r="B118" s="15" t="n"/>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="21" t="n"/>
+      <c r="G118" s="21" t="n"/>
+      <c r="H118" s="15" t="n"/>
+      <c r="I118" s="15" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="n"/>
+      <c r="B119" s="15" t="n"/>
+      <c r="C119" s="15" t="n"/>
+      <c r="D119" s="15" t="n"/>
+      <c r="E119" s="15" t="n"/>
+      <c r="F119" s="21" t="n"/>
+      <c r="G119" s="21" t="n"/>
+      <c r="H119" s="15" t="n"/>
+      <c r="I119" s="15" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="n"/>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="15" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="21" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="15" t="n"/>
+      <c r="I120" s="15" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="n"/>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+      <c r="F121" s="21" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="15" t="n"/>
+      <c r="I121" s="15" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="n"/>
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="21" t="n"/>
+      <c r="G122" s="21" t="n"/>
+      <c r="H122" s="15" t="n"/>
+      <c r="I122" s="15" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="n"/>
+      <c r="B123" s="15" t="n"/>
+      <c r="C123" s="15" t="n"/>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="n"/>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="15" t="n"/>
+      <c r="I123" s="15" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="n"/>
+      <c r="B124" s="15" t="n"/>
+      <c r="C124" s="15" t="n"/>
+      <c r="D124" s="15" t="n"/>
+      <c r="E124" s="15" t="n"/>
+      <c r="F124" s="21" t="n"/>
+      <c r="G124" s="21" t="n"/>
+      <c r="H124" s="15" t="n"/>
+      <c r="I124" s="15" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="n"/>
+      <c r="B125" s="15" t="n"/>
+      <c r="C125" s="15" t="n"/>
+      <c r="D125" s="15" t="n"/>
+      <c r="E125" s="15" t="n"/>
+      <c r="F125" s="21" t="n"/>
+      <c r="G125" s="21" t="n"/>
+      <c r="H125" s="15" t="n"/>
+      <c r="I125" s="15" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="n"/>
+      <c r="B126" s="15" t="n"/>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="15" t="n"/>
+      <c r="E126" s="15" t="n"/>
+      <c r="F126" s="21" t="n"/>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="15" t="n"/>
+      <c r="I126" s="15" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="n"/>
+      <c r="B127" s="15" t="n"/>
+      <c r="C127" s="15" t="n"/>
+      <c r="D127" s="15" t="n"/>
+      <c r="E127" s="15" t="n"/>
+      <c r="F127" s="21" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="15" t="n"/>
+      <c r="I127" s="15" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="n"/>
+      <c r="B128" s="15" t="n"/>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="15" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="n"/>
+      <c r="B129" s="15" t="n"/>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15" t="n"/>
+      <c r="E129" s="15" t="n"/>
+      <c r="F129" s="21" t="n"/>
+      <c r="G129" s="21" t="n"/>
+      <c r="H129" s="15" t="n"/>
+      <c r="I129" s="15" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="n"/>
+      <c r="B130" s="15" t="n"/>
+      <c r="C130" s="15" t="n"/>
+      <c r="D130" s="15" t="n"/>
+      <c r="E130" s="15" t="n"/>
+      <c r="F130" s="21" t="n"/>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="15" t="n"/>
+      <c r="I130" s="15" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="n"/>
+      <c r="B131" s="15" t="n"/>
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15" t="n"/>
+      <c r="E131" s="15" t="n"/>
+      <c r="F131" s="21" t="n"/>
+      <c r="G131" s="21" t="n"/>
+      <c r="H131" s="15" t="n"/>
+      <c r="I131" s="15" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="n"/>
+      <c r="B132" s="15" t="n"/>
+      <c r="C132" s="15" t="n"/>
+      <c r="D132" s="15" t="n"/>
+      <c r="E132" s="15" t="n"/>
+      <c r="F132" s="21" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="15" t="n"/>
+      <c r="I132" s="15" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="n"/>
+      <c r="B133" s="15" t="n"/>
+      <c r="C133" s="15" t="n"/>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
+      <c r="F133" s="21" t="n"/>
+      <c r="G133" s="21" t="n"/>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="15" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="n"/>
+      <c r="B134" s="15" t="n"/>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="21" t="n"/>
+      <c r="G134" s="21" t="n"/>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="15" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="n"/>
+      <c r="B135" s="15" t="n"/>
+      <c r="C135" s="15" t="n"/>
+      <c r="D135" s="15" t="n"/>
+      <c r="E135" s="15" t="n"/>
+      <c r="F135" s="21" t="n"/>
+      <c r="G135" s="21" t="n"/>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="15" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="n"/>
+      <c r="B136" s="15" t="n"/>
+      <c r="C136" s="15" t="n"/>
+      <c r="D136" s="15" t="n"/>
+      <c r="E136" s="15" t="n"/>
+      <c r="F136" s="21" t="n"/>
+      <c r="G136" s="21" t="n"/>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="15" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="n"/>
+      <c r="B137" s="15" t="n"/>
+      <c r="C137" s="15" t="n"/>
+      <c r="D137" s="15" t="n"/>
+      <c r="E137" s="15" t="n"/>
+      <c r="F137" s="21" t="n"/>
+      <c r="G137" s="21" t="n"/>
+      <c r="H137" s="15" t="n"/>
+      <c r="I137" s="15" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="n"/>
+      <c r="B138" s="15" t="n"/>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="21" t="n"/>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="15" t="n"/>
+      <c r="I138" s="15" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="n"/>
+      <c r="B139" s="15" t="n"/>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="21" t="n"/>
+      <c r="G139" s="21" t="n"/>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="15" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="n"/>
+      <c r="B140" s="15" t="n"/>
+      <c r="C140" s="15" t="n"/>
+      <c r="D140" s="15" t="n"/>
+      <c r="E140" s="15" t="n"/>
+      <c r="F140" s="21" t="n"/>
+      <c r="G140" s="21" t="n"/>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="15" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="n"/>
+      <c r="B141" s="15" t="n"/>
+      <c r="C141" s="15" t="n"/>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+      <c r="F141" s="21" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="15" t="n"/>
+      <c r="I141" s="15" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="n"/>
+      <c r="B142" s="15" t="n"/>
+      <c r="C142" s="15" t="n"/>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="n"/>
+      <c r="F142" s="21" t="n"/>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="15" t="n"/>
+      <c r="I142" s="15" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="n"/>
+      <c r="B143" s="15" t="n"/>
+      <c r="C143" s="15" t="n"/>
+      <c r="D143" s="15" t="n"/>
+      <c r="E143" s="15" t="n"/>
+      <c r="F143" s="21" t="n"/>
+      <c r="G143" s="21" t="n"/>
+      <c r="H143" s="15" t="n"/>
+      <c r="I143" s="15" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="n"/>
+      <c r="B144" s="15" t="n"/>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="21" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="15" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="n"/>
+      <c r="B145" s="15" t="n"/>
+      <c r="C145" s="15" t="n"/>
+      <c r="D145" s="15" t="n"/>
+      <c r="E145" s="15" t="n"/>
+      <c r="F145" s="21" t="n"/>
+      <c r="G145" s="21" t="n"/>
+      <c r="H145" s="15" t="n"/>
+      <c r="I145" s="15" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="n"/>
+      <c r="B146" s="15" t="n"/>
+      <c r="C146" s="15" t="n"/>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="21" t="n"/>
+      <c r="G146" s="21" t="n"/>
+      <c r="H146" s="15" t="n"/>
+      <c r="I146" s="15" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="n"/>
+      <c r="B147" s="15" t="n"/>
+      <c r="C147" s="15" t="n"/>
+      <c r="D147" s="15" t="n"/>
+      <c r="E147" s="15" t="n"/>
+      <c r="F147" s="21" t="n"/>
+      <c r="G147" s="21" t="n"/>
+      <c r="H147" s="15" t="n"/>
+      <c r="I147" s="15" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="n"/>
+      <c r="B148" s="15" t="n"/>
+      <c r="C148" s="15" t="n"/>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
+      <c r="F148" s="21" t="n"/>
+      <c r="G148" s="21" t="n"/>
+      <c r="H148" s="15" t="n"/>
+      <c r="I148" s="15" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="n"/>
+      <c r="B149" s="15" t="n"/>
+      <c r="C149" s="15" t="n"/>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
+      <c r="F149" s="21" t="n"/>
+      <c r="G149" s="21" t="n"/>
+      <c r="H149" s="15" t="n"/>
+      <c r="I149" s="15" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="n"/>
+      <c r="B150" s="15" t="n"/>
+      <c r="C150" s="15" t="n"/>
+      <c r="D150" s="15" t="n"/>
+      <c r="E150" s="15" t="n"/>
+      <c r="F150" s="21" t="n"/>
+      <c r="G150" s="21" t="n"/>
+      <c r="H150" s="15" t="n"/>
+      <c r="I150" s="15" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="n"/>
+      <c r="B151" s="15" t="n"/>
+      <c r="C151" s="15" t="n"/>
+      <c r="D151" s="15" t="n"/>
+      <c r="E151" s="15" t="n"/>
+      <c r="F151" s="21" t="n"/>
+      <c r="G151" s="21" t="n"/>
+      <c r="H151" s="15" t="n"/>
+      <c r="I151" s="15" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="n"/>
+      <c r="B152" s="15" t="n"/>
+      <c r="C152" s="15" t="n"/>
+      <c r="D152" s="15" t="n"/>
+      <c r="E152" s="15" t="n"/>
+      <c r="F152" s="21" t="n"/>
+      <c r="G152" s="21" t="n"/>
+      <c r="H152" s="15" t="n"/>
+      <c r="I152" s="15" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="n"/>
+      <c r="B153" s="15" t="n"/>
+      <c r="C153" s="15" t="n"/>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n"/>
+      <c r="F153" s="21" t="n"/>
+      <c r="G153" s="21" t="n"/>
+      <c r="H153" s="15" t="n"/>
+      <c r="I153" s="15" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="n"/>
+      <c r="B154" s="15" t="n"/>
+      <c r="C154" s="15" t="n"/>
+      <c r="D154" s="15" t="n"/>
+      <c r="E154" s="15" t="n"/>
+      <c r="F154" s="21" t="n"/>
+      <c r="G154" s="21" t="n"/>
+      <c r="H154" s="15" t="n"/>
+      <c r="I154" s="15" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="n"/>
+      <c r="B155" s="15" t="n"/>
+      <c r="C155" s="15" t="n"/>
+      <c r="D155" s="15" t="n"/>
+      <c r="E155" s="15" t="n"/>
+      <c r="F155" s="21" t="n"/>
+      <c r="G155" s="21" t="n"/>
+      <c r="H155" s="15" t="n"/>
+      <c r="I155" s="15" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="n"/>
+      <c r="B156" s="15" t="n"/>
+      <c r="C156" s="15" t="n"/>
+      <c r="D156" s="15" t="n"/>
+      <c r="E156" s="15" t="n"/>
+      <c r="F156" s="21" t="n"/>
+      <c r="G156" s="21" t="n"/>
+      <c r="H156" s="15" t="n"/>
+      <c r="I156" s="15" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="n"/>
+      <c r="B157" s="15" t="n"/>
+      <c r="C157" s="15" t="n"/>
+      <c r="D157" s="15" t="n"/>
+      <c r="E157" s="15" t="n"/>
+      <c r="F157" s="21" t="n"/>
+      <c r="G157" s="21" t="n"/>
+      <c r="H157" s="15" t="n"/>
+      <c r="I157" s="15" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="15" t="n"/>
+      <c r="B158" s="15" t="n"/>
+      <c r="C158" s="15" t="n"/>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
+      <c r="F158" s="21" t="n"/>
+      <c r="G158" s="21" t="n"/>
+      <c r="H158" s="15" t="n"/>
+      <c r="I158" s="15" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="n"/>
+      <c r="B159" s="15" t="n"/>
+      <c r="C159" s="15" t="n"/>
+      <c r="D159" s="15" t="n"/>
+      <c r="E159" s="15" t="n"/>
+      <c r="F159" s="21" t="n"/>
+      <c r="G159" s="21" t="n"/>
+      <c r="H159" s="15" t="n"/>
+      <c r="I159" s="15" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="n"/>
+      <c r="B160" s="15" t="n"/>
+      <c r="C160" s="15" t="n"/>
+      <c r="D160" s="15" t="n"/>
+      <c r="E160" s="15" t="n"/>
+      <c r="F160" s="21" t="n"/>
+      <c r="G160" s="21" t="n"/>
+      <c r="H160" s="15" t="n"/>
+      <c r="I160" s="15" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="n"/>
+      <c r="B161" s="15" t="n"/>
+      <c r="C161" s="15" t="n"/>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="15" t="n"/>
+      <c r="F161" s="21" t="n"/>
+      <c r="G161" s="21" t="n"/>
+      <c r="H161" s="15" t="n"/>
+      <c r="I161" s="15" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="n"/>
+      <c r="B162" s="15" t="n"/>
+      <c r="C162" s="15" t="n"/>
+      <c r="D162" s="15" t="n"/>
+      <c r="E162" s="15" t="n"/>
+      <c r="F162" s="21" t="n"/>
+      <c r="G162" s="21" t="n"/>
+      <c r="H162" s="15" t="n"/>
+      <c r="I162" s="15" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="n"/>
+      <c r="B163" s="15" t="n"/>
+      <c r="C163" s="15" t="n"/>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="15" t="n"/>
+      <c r="F163" s="21" t="n"/>
+      <c r="G163" s="21" t="n"/>
+      <c r="H163" s="15" t="n"/>
+      <c r="I163" s="15" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="n"/>
+      <c r="B164" s="15" t="n"/>
+      <c r="C164" s="15" t="n"/>
+      <c r="D164" s="15" t="n"/>
+      <c r="E164" s="15" t="n"/>
+      <c r="F164" s="21" t="n"/>
+      <c r="G164" s="21" t="n"/>
+      <c r="H164" s="15" t="n"/>
+      <c r="I164" s="15" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="n"/>
+      <c r="B165" s="15" t="n"/>
+      <c r="C165" s="15" t="n"/>
+      <c r="D165" s="15" t="n"/>
+      <c r="E165" s="15" t="n"/>
+      <c r="F165" s="21" t="n"/>
+      <c r="G165" s="21" t="n"/>
+      <c r="H165" s="15" t="n"/>
+      <c r="I165" s="15" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="n"/>
+      <c r="B166" s="15" t="n"/>
+      <c r="C166" s="15" t="n"/>
+      <c r="D166" s="15" t="n"/>
+      <c r="E166" s="15" t="n"/>
+      <c r="F166" s="21" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="15" t="n"/>
+      <c r="I166" s="15" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="n"/>
+      <c r="B167" s="15" t="n"/>
+      <c r="C167" s="15" t="n"/>
+      <c r="D167" s="15" t="n"/>
+      <c r="E167" s="15" t="n"/>
+      <c r="F167" s="21" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="15" t="n"/>
+      <c r="I167" s="15" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="n"/>
+      <c r="B168" s="15" t="n"/>
+      <c r="C168" s="15" t="n"/>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="15" t="n"/>
+      <c r="F168" s="21" t="n"/>
+      <c r="G168" s="21" t="n"/>
+      <c r="H168" s="15" t="n"/>
+      <c r="I168" s="15" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="n"/>
+      <c r="B169" s="15" t="n"/>
+      <c r="C169" s="15" t="n"/>
+      <c r="D169" s="15" t="n"/>
+      <c r="E169" s="15" t="n"/>
+      <c r="F169" s="21" t="n"/>
+      <c r="G169" s="21" t="n"/>
+      <c r="H169" s="15" t="n"/>
+      <c r="I169" s="15" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="n"/>
+      <c r="B170" s="15" t="n"/>
+      <c r="C170" s="15" t="n"/>
+      <c r="D170" s="15" t="n"/>
+      <c r="E170" s="15" t="n"/>
+      <c r="F170" s="21" t="n"/>
+      <c r="G170" s="21" t="n"/>
+      <c r="H170" s="15" t="n"/>
+      <c r="I170" s="15" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="n"/>
+      <c r="B171" s="15" t="n"/>
+      <c r="C171" s="15" t="n"/>
+      <c r="D171" s="15" t="n"/>
+      <c r="E171" s="15" t="n"/>
+      <c r="F171" s="21" t="n"/>
+      <c r="G171" s="21" t="n"/>
+      <c r="H171" s="15" t="n"/>
+      <c r="I171" s="15" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="n"/>
+      <c r="B172" s="15" t="n"/>
+      <c r="C172" s="15" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="15" t="n"/>
+      <c r="F172" s="21" t="n"/>
+      <c r="G172" s="21" t="n"/>
+      <c r="H172" s="15" t="n"/>
+      <c r="I172" s="15" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="n"/>
+      <c r="B173" s="15" t="n"/>
+      <c r="C173" s="15" t="n"/>
+      <c r="D173" s="15" t="n"/>
+      <c r="E173" s="15" t="n"/>
+      <c r="F173" s="21" t="n"/>
+      <c r="G173" s="21" t="n"/>
+      <c r="H173" s="15" t="n"/>
+      <c r="I173" s="15" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="n"/>
+      <c r="B174" s="15" t="n"/>
+      <c r="C174" s="15" t="n"/>
+      <c r="D174" s="15" t="n"/>
+      <c r="E174" s="15" t="n"/>
+      <c r="F174" s="21" t="n"/>
+      <c r="G174" s="21" t="n"/>
+      <c r="H174" s="15" t="n"/>
+      <c r="I174" s="15" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="n"/>
+      <c r="B175" s="15" t="n"/>
+      <c r="C175" s="15" t="n"/>
+      <c r="D175" s="15" t="n"/>
+      <c r="E175" s="15" t="n"/>
+      <c r="F175" s="21" t="n"/>
+      <c r="G175" s="21" t="n"/>
+      <c r="H175" s="15" t="n"/>
+      <c r="I175" s="15" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="n"/>
+      <c r="B176" s="15" t="n"/>
+      <c r="C176" s="15" t="n"/>
+      <c r="D176" s="15" t="n"/>
+      <c r="E176" s="15" t="n"/>
+      <c r="F176" s="21" t="n"/>
+      <c r="G176" s="21" t="n"/>
+      <c r="H176" s="15" t="n"/>
+      <c r="I176" s="15" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="n"/>
+      <c r="B177" s="15" t="n"/>
+      <c r="C177" s="15" t="n"/>
+      <c r="D177" s="15" t="n"/>
+      <c r="E177" s="15" t="n"/>
+      <c r="F177" s="21" t="n"/>
+      <c r="G177" s="21" t="n"/>
+      <c r="H177" s="15" t="n"/>
+      <c r="I177" s="15" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="n"/>
+      <c r="B178" s="15" t="n"/>
+      <c r="C178" s="15" t="n"/>
+      <c r="D178" s="15" t="n"/>
+      <c r="E178" s="15" t="n"/>
+      <c r="F178" s="21" t="n"/>
+      <c r="G178" s="21" t="n"/>
+      <c r="H178" s="15" t="n"/>
+      <c r="I178" s="15" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="n"/>
+      <c r="B179" s="15" t="n"/>
+      <c r="C179" s="15" t="n"/>
+      <c r="D179" s="15" t="n"/>
+      <c r="E179" s="15" t="n"/>
+      <c r="F179" s="21" t="n"/>
+      <c r="G179" s="21" t="n"/>
+      <c r="H179" s="15" t="n"/>
+      <c r="I179" s="15" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="n"/>
+      <c r="B180" s="15" t="n"/>
+      <c r="C180" s="15" t="n"/>
+      <c r="D180" s="15" t="n"/>
+      <c r="E180" s="15" t="n"/>
+      <c r="F180" s="21" t="n"/>
+      <c r="G180" s="21" t="n"/>
+      <c r="H180" s="15" t="n"/>
+      <c r="I180" s="15" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="n"/>
+      <c r="B181" s="15" t="n"/>
+      <c r="C181" s="15" t="n"/>
+      <c r="D181" s="15" t="n"/>
+      <c r="E181" s="15" t="n"/>
+      <c r="F181" s="21" t="n"/>
+      <c r="G181" s="21" t="n"/>
+      <c r="H181" s="15" t="n"/>
+      <c r="I181" s="15" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="n"/>
+      <c r="B182" s="15" t="n"/>
+      <c r="C182" s="15" t="n"/>
+      <c r="D182" s="15" t="n"/>
+      <c r="E182" s="15" t="n"/>
+      <c r="F182" s="21" t="n"/>
+      <c r="G182" s="21" t="n"/>
+      <c r="H182" s="15" t="n"/>
+      <c r="I182" s="15" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="n"/>
+      <c r="B183" s="15" t="n"/>
+      <c r="C183" s="15" t="n"/>
+      <c r="D183" s="15" t="n"/>
+      <c r="E183" s="15" t="n"/>
+      <c r="F183" s="21" t="n"/>
+      <c r="G183" s="21" t="n"/>
+      <c r="H183" s="15" t="n"/>
+      <c r="I183" s="15" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="n"/>
+      <c r="B184" s="15" t="n"/>
+      <c r="C184" s="15" t="n"/>
+      <c r="D184" s="15" t="n"/>
+      <c r="E184" s="15" t="n"/>
+      <c r="F184" s="21" t="n"/>
+      <c r="G184" s="21" t="n"/>
+      <c r="H184" s="15" t="n"/>
+      <c r="I184" s="15" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="n"/>
+      <c r="B185" s="15" t="n"/>
+      <c r="C185" s="15" t="n"/>
+      <c r="D185" s="15" t="n"/>
+      <c r="E185" s="15" t="n"/>
+      <c r="F185" s="21" t="n"/>
+      <c r="G185" s="21" t="n"/>
+      <c r="H185" s="15" t="n"/>
+      <c r="I185" s="15" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="n"/>
+      <c r="B186" s="15" t="n"/>
+      <c r="C186" s="15" t="n"/>
+      <c r="D186" s="15" t="n"/>
+      <c r="E186" s="15" t="n"/>
+      <c r="F186" s="21" t="n"/>
+      <c r="G186" s="21" t="n"/>
+      <c r="H186" s="15" t="n"/>
+      <c r="I186" s="15" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="n"/>
+      <c r="B187" s="15" t="n"/>
+      <c r="C187" s="15" t="n"/>
+      <c r="D187" s="15" t="n"/>
+      <c r="E187" s="15" t="n"/>
+      <c r="F187" s="21" t="n"/>
+      <c r="G187" s="21" t="n"/>
+      <c r="H187" s="15" t="n"/>
+      <c r="I187" s="15" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="n"/>
+      <c r="B188" s="15" t="n"/>
+      <c r="C188" s="15" t="n"/>
+      <c r="D188" s="15" t="n"/>
+      <c r="E188" s="15" t="n"/>
+      <c r="F188" s="21" t="n"/>
+      <c r="G188" s="21" t="n"/>
+      <c r="H188" s="15" t="n"/>
+      <c r="I188" s="15" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="n"/>
+      <c r="B189" s="15" t="n"/>
+      <c r="C189" s="15" t="n"/>
+      <c r="D189" s="15" t="n"/>
+      <c r="E189" s="15" t="n"/>
+      <c r="F189" s="21" t="n"/>
+      <c r="G189" s="21" t="n"/>
+      <c r="H189" s="15" t="n"/>
+      <c r="I189" s="15" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="n"/>
+      <c r="B190" s="15" t="n"/>
+      <c r="C190" s="15" t="n"/>
+      <c r="D190" s="15" t="n"/>
+      <c r="E190" s="15" t="n"/>
+      <c r="F190" s="21" t="n"/>
+      <c r="G190" s="21" t="n"/>
+      <c r="H190" s="15" t="n"/>
+      <c r="I190" s="15" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="n"/>
+      <c r="B191" s="15" t="n"/>
+      <c r="C191" s="15" t="n"/>
+      <c r="D191" s="15" t="n"/>
+      <c r="E191" s="15" t="n"/>
+      <c r="F191" s="21" t="n"/>
+      <c r="G191" s="21" t="n"/>
+      <c r="H191" s="15" t="n"/>
+      <c r="I191" s="15" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="n"/>
+      <c r="B192" s="15" t="n"/>
+      <c r="C192" s="15" t="n"/>
+      <c r="D192" s="15" t="n"/>
+      <c r="E192" s="15" t="n"/>
+      <c r="F192" s="21" t="n"/>
+      <c r="G192" s="21" t="n"/>
+      <c r="H192" s="15" t="n"/>
+      <c r="I192" s="15" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="n"/>
+      <c r="B193" s="15" t="n"/>
+      <c r="C193" s="15" t="n"/>
+      <c r="D193" s="15" t="n"/>
+      <c r="E193" s="15" t="n"/>
+      <c r="F193" s="21" t="n"/>
+      <c r="G193" s="21" t="n"/>
+      <c r="H193" s="15" t="n"/>
+      <c r="I193" s="15" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="n"/>
+      <c r="B194" s="15" t="n"/>
+      <c r="C194" s="15" t="n"/>
+      <c r="D194" s="15" t="n"/>
+      <c r="E194" s="15" t="n"/>
+      <c r="F194" s="21" t="n"/>
+      <c r="G194" s="21" t="n"/>
+      <c r="H194" s="15" t="n"/>
+      <c r="I194" s="15" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="n"/>
+      <c r="B195" s="15" t="n"/>
+      <c r="C195" s="15" t="n"/>
+      <c r="D195" s="15" t="n"/>
+      <c r="E195" s="15" t="n"/>
+      <c r="F195" s="21" t="n"/>
+      <c r="G195" s="21" t="n"/>
+      <c r="H195" s="15" t="n"/>
+      <c r="I195" s="15" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="n"/>
+      <c r="B196" s="15" t="n"/>
+      <c r="C196" s="15" t="n"/>
+      <c r="D196" s="15" t="n"/>
+      <c r="E196" s="15" t="n"/>
+      <c r="F196" s="21" t="n"/>
+      <c r="G196" s="21" t="n"/>
+      <c r="H196" s="15" t="n"/>
+      <c r="I196" s="15" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="n"/>
+      <c r="B197" s="15" t="n"/>
+      <c r="C197" s="15" t="n"/>
+      <c r="D197" s="15" t="n"/>
+      <c r="E197" s="15" t="n"/>
+      <c r="F197" s="21" t="n"/>
+      <c r="G197" s="21" t="n"/>
+      <c r="H197" s="15" t="n"/>
+      <c r="I197" s="15" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="n"/>
+      <c r="B198" s="15" t="n"/>
+      <c r="C198" s="15" t="n"/>
+      <c r="D198" s="15" t="n"/>
+      <c r="E198" s="15" t="n"/>
+      <c r="F198" s="21" t="n"/>
+      <c r="G198" s="21" t="n"/>
+      <c r="H198" s="15" t="n"/>
+      <c r="I198" s="15" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="n"/>
+      <c r="B199" s="15" t="n"/>
+      <c r="C199" s="15" t="n"/>
+      <c r="D199" s="15" t="n"/>
+      <c r="E199" s="15" t="n"/>
+      <c r="F199" s="21" t="n"/>
+      <c r="G199" s="21" t="n"/>
+      <c r="H199" s="15" t="n"/>
+      <c r="I199" s="15" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="n"/>
+      <c r="B200" s="15" t="n"/>
+      <c r="C200" s="15" t="n"/>
+      <c r="D200" s="15" t="n"/>
+      <c r="E200" s="15" t="n"/>
+      <c r="F200" s="21" t="n"/>
+      <c r="G200" s="21" t="n"/>
+      <c r="H200" s="15" t="n"/>
+      <c r="I200" s="15" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="n"/>
+      <c r="B201" s="15" t="n"/>
+      <c r="C201" s="15" t="n"/>
+      <c r="D201" s="15" t="n"/>
+      <c r="E201" s="15" t="n"/>
+      <c r="F201" s="21" t="n"/>
+      <c r="G201" s="21" t="n"/>
+      <c r="H201" s="15" t="n"/>
+      <c r="I201" s="15" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="n"/>
+      <c r="B202" s="15" t="n"/>
+      <c r="C202" s="15" t="n"/>
+      <c r="D202" s="15" t="n"/>
+      <c r="E202" s="15" t="n"/>
+      <c r="F202" s="21" t="n"/>
+      <c r="G202" s="21" t="n"/>
+      <c r="H202" s="15" t="n"/>
+      <c r="I202" s="15" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="n"/>
+      <c r="B203" s="15" t="n"/>
+      <c r="C203" s="15" t="n"/>
+      <c r="D203" s="15" t="n"/>
+      <c r="E203" s="15" t="n"/>
+      <c r="F203" s="21" t="n"/>
+      <c r="G203" s="21" t="n"/>
+      <c r="H203" s="15" t="n"/>
+      <c r="I203" s="15" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="n"/>
+      <c r="B204" s="15" t="n"/>
+      <c r="C204" s="15" t="n"/>
+      <c r="D204" s="15" t="n"/>
+      <c r="E204" s="15" t="n"/>
+      <c r="F204" s="21" t="n"/>
+      <c r="G204" s="21" t="n"/>
+      <c r="H204" s="15" t="n"/>
+      <c r="I204" s="15" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="n"/>
+      <c r="B205" s="15" t="n"/>
+      <c r="C205" s="15" t="n"/>
+      <c r="D205" s="15" t="n"/>
+      <c r="E205" s="15" t="n"/>
+      <c r="F205" s="21" t="n"/>
+      <c r="G205" s="21" t="n"/>
+      <c r="H205" s="15" t="n"/>
+      <c r="I205" s="15" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="n"/>
+      <c r="B206" s="15" t="n"/>
+      <c r="C206" s="15" t="n"/>
+      <c r="D206" s="15" t="n"/>
+      <c r="E206" s="15" t="n"/>
+      <c r="F206" s="21" t="n"/>
+      <c r="G206" s="21" t="n"/>
+      <c r="H206" s="15" t="n"/>
+      <c r="I206" s="15" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="n"/>
+      <c r="B207" s="15" t="n"/>
+      <c r="C207" s="15" t="n"/>
+      <c r="D207" s="15" t="n"/>
+      <c r="E207" s="15" t="n"/>
+      <c r="F207" s="21" t="n"/>
+      <c r="G207" s="21" t="n"/>
+      <c r="H207" s="15" t="n"/>
+      <c r="I207" s="15" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="n"/>
+      <c r="B208" s="15" t="n"/>
+      <c r="C208" s="15" t="n"/>
+      <c r="D208" s="15" t="n"/>
+      <c r="E208" s="15" t="n"/>
+      <c r="F208" s="21" t="n"/>
+      <c r="G208" s="21" t="n"/>
+      <c r="H208" s="15" t="n"/>
+      <c r="I208" s="15" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="n"/>
+      <c r="B209" s="15" t="n"/>
+      <c r="C209" s="15" t="n"/>
+      <c r="D209" s="15" t="n"/>
+      <c r="E209" s="15" t="n"/>
+      <c r="F209" s="21" t="n"/>
+      <c r="G209" s="21" t="n"/>
+      <c r="H209" s="15" t="n"/>
+      <c r="I209" s="15" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="n"/>
+      <c r="B210" s="15" t="n"/>
+      <c r="C210" s="15" t="n"/>
+      <c r="D210" s="15" t="n"/>
+      <c r="E210" s="15" t="n"/>
+      <c r="F210" s="21" t="n"/>
+      <c r="G210" s="21" t="n"/>
+      <c r="H210" s="15" t="n"/>
+      <c r="I210" s="15" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="n"/>
+      <c r="B211" s="15" t="n"/>
+      <c r="C211" s="15" t="n"/>
+      <c r="D211" s="15" t="n"/>
+      <c r="E211" s="15" t="n"/>
+      <c r="F211" s="21" t="n"/>
+      <c r="G211" s="21" t="n"/>
+      <c r="H211" s="15" t="n"/>
+      <c r="I211" s="15" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="n"/>
+      <c r="B212" s="15" t="n"/>
+      <c r="C212" s="15" t="n"/>
+      <c r="D212" s="15" t="n"/>
+      <c r="E212" s="15" t="n"/>
+      <c r="F212" s="21" t="n"/>
+      <c r="G212" s="21" t="n"/>
+      <c r="H212" s="15" t="n"/>
+      <c r="I212" s="15" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="n"/>
+      <c r="B213" s="15" t="n"/>
+      <c r="C213" s="15" t="n"/>
+      <c r="D213" s="15" t="n"/>
+      <c r="E213" s="15" t="n"/>
+      <c r="F213" s="21" t="n"/>
+      <c r="G213" s="21" t="n"/>
+      <c r="H213" s="15" t="n"/>
+      <c r="I213" s="15" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="n"/>
+      <c r="B214" s="15" t="n"/>
+      <c r="C214" s="15" t="n"/>
+      <c r="D214" s="15" t="n"/>
+      <c r="E214" s="15" t="n"/>
+      <c r="F214" s="21" t="n"/>
+      <c r="G214" s="21" t="n"/>
+      <c r="H214" s="15" t="n"/>
+      <c r="I214" s="15" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="n"/>
+      <c r="B215" s="15" t="n"/>
+      <c r="C215" s="15" t="n"/>
+      <c r="D215" s="15" t="n"/>
+      <c r="E215" s="15" t="n"/>
+      <c r="F215" s="21" t="n"/>
+      <c r="G215" s="21" t="n"/>
+      <c r="H215" s="15" t="n"/>
+      <c r="I215" s="15" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="n"/>
+      <c r="B216" s="15" t="n"/>
+      <c r="C216" s="15" t="n"/>
+      <c r="D216" s="15" t="n"/>
+      <c r="E216" s="15" t="n"/>
+      <c r="F216" s="21" t="n"/>
+      <c r="G216" s="21" t="n"/>
+      <c r="H216" s="15" t="n"/>
+      <c r="I216" s="15" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="n"/>
+      <c r="B217" s="15" t="n"/>
+      <c r="C217" s="15" t="n"/>
+      <c r="D217" s="15" t="n"/>
+      <c r="E217" s="15" t="n"/>
+      <c r="F217" s="21" t="n"/>
+      <c r="G217" s="21" t="n"/>
+      <c r="H217" s="15" t="n"/>
+      <c r="I217" s="15" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="n"/>
+      <c r="B218" s="15" t="n"/>
+      <c r="C218" s="15" t="n"/>
+      <c r="D218" s="15" t="n"/>
+      <c r="E218" s="15" t="n"/>
+      <c r="F218" s="21" t="n"/>
+      <c r="G218" s="21" t="n"/>
+      <c r="H218" s="15" t="n"/>
+      <c r="I218" s="15" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="n"/>
+      <c r="B219" s="15" t="n"/>
+      <c r="C219" s="15" t="n"/>
+      <c r="D219" s="15" t="n"/>
+      <c r="E219" s="15" t="n"/>
+      <c r="F219" s="21" t="n"/>
+      <c r="G219" s="21" t="n"/>
+      <c r="H219" s="15" t="n"/>
+      <c r="I219" s="15" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="n"/>
+      <c r="B220" s="15" t="n"/>
+      <c r="C220" s="15" t="n"/>
+      <c r="D220" s="15" t="n"/>
+      <c r="E220" s="15" t="n"/>
+      <c r="F220" s="21" t="n"/>
+      <c r="G220" s="21" t="n"/>
+      <c r="H220" s="15" t="n"/>
+      <c r="I220" s="15" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="15" t="n"/>
+      <c r="B221" s="15" t="n"/>
+      <c r="C221" s="15" t="n"/>
+      <c r="D221" s="15" t="n"/>
+      <c r="E221" s="15" t="n"/>
+      <c r="F221" s="21" t="n"/>
+      <c r="G221" s="21" t="n"/>
+      <c r="H221" s="15" t="n"/>
+      <c r="I221" s="15" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="n"/>
+      <c r="B222" s="15" t="n"/>
+      <c r="C222" s="15" t="n"/>
+      <c r="D222" s="15" t="n"/>
+      <c r="E222" s="15" t="n"/>
+      <c r="F222" s="21" t="n"/>
+      <c r="G222" s="21" t="n"/>
+      <c r="H222" s="15" t="n"/>
+      <c r="I222" s="15" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="15" t="n"/>
+      <c r="B223" s="15" t="n"/>
+      <c r="C223" s="15" t="n"/>
+      <c r="D223" s="15" t="n"/>
+      <c r="E223" s="15" t="n"/>
+      <c r="F223" s="21" t="n"/>
+      <c r="G223" s="21" t="n"/>
+      <c r="H223" s="15" t="n"/>
+      <c r="I223" s="15" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="n"/>
+      <c r="B224" s="15" t="n"/>
+      <c r="C224" s="15" t="n"/>
+      <c r="D224" s="15" t="n"/>
+      <c r="E224" s="15" t="n"/>
+      <c r="F224" s="21" t="n"/>
+      <c r="G224" s="21" t="n"/>
+      <c r="H224" s="15" t="n"/>
+      <c r="I224" s="15" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="n"/>
+      <c r="B225" s="15" t="n"/>
+      <c r="C225" s="15" t="n"/>
+      <c r="D225" s="15" t="n"/>
+      <c r="E225" s="15" t="n"/>
+      <c r="F225" s="21" t="n"/>
+      <c r="G225" s="21" t="n"/>
+      <c r="H225" s="15" t="n"/>
+      <c r="I225" s="15" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="n"/>
+      <c r="B226" s="15" t="n"/>
+      <c r="C226" s="15" t="n"/>
+      <c r="D226" s="15" t="n"/>
+      <c r="E226" s="15" t="n"/>
+      <c r="F226" s="21" t="n"/>
+      <c r="G226" s="21" t="n"/>
+      <c r="H226" s="15" t="n"/>
+      <c r="I226" s="15" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="n"/>
+      <c r="B227" s="15" t="n"/>
+      <c r="C227" s="15" t="n"/>
+      <c r="D227" s="15" t="n"/>
+      <c r="E227" s="15" t="n"/>
+      <c r="F227" s="21" t="n"/>
+      <c r="G227" s="21" t="n"/>
+      <c r="H227" s="15" t="n"/>
+      <c r="I227" s="15" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="15" t="n"/>
+      <c r="B228" s="15" t="n"/>
+      <c r="C228" s="15" t="n"/>
+      <c r="D228" s="15" t="n"/>
+      <c r="E228" s="15" t="n"/>
+      <c r="F228" s="21" t="n"/>
+      <c r="G228" s="21" t="n"/>
+      <c r="H228" s="15" t="n"/>
+      <c r="I228" s="15" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="15" t="n"/>
+      <c r="B229" s="15" t="n"/>
+      <c r="C229" s="15" t="n"/>
+      <c r="D229" s="15" t="n"/>
+      <c r="E229" s="15" t="n"/>
+      <c r="F229" s="21" t="n"/>
+      <c r="G229" s="21" t="n"/>
+      <c r="H229" s="15" t="n"/>
+      <c r="I229" s="15" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="n"/>
+      <c r="B230" s="15" t="n"/>
+      <c r="C230" s="15" t="n"/>
+      <c r="D230" s="15" t="n"/>
+      <c r="E230" s="15" t="n"/>
+      <c r="F230" s="21" t="n"/>
+      <c r="G230" s="21" t="n"/>
+      <c r="H230" s="15" t="n"/>
+      <c r="I230" s="15" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="n"/>
+      <c r="B231" s="15" t="n"/>
+      <c r="C231" s="15" t="n"/>
+      <c r="D231" s="15" t="n"/>
+      <c r="E231" s="15" t="n"/>
+      <c r="F231" s="21" t="n"/>
+      <c r="G231" s="21" t="n"/>
+      <c r="H231" s="15" t="n"/>
+      <c r="I231" s="15" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="15" t="n"/>
+      <c r="B232" s="15" t="n"/>
+      <c r="C232" s="15" t="n"/>
+      <c r="D232" s="15" t="n"/>
+      <c r="E232" s="15" t="n"/>
+      <c r="F232" s="21" t="n"/>
+      <c r="G232" s="21" t="n"/>
+      <c r="H232" s="15" t="n"/>
+      <c r="I232" s="15" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="n"/>
+      <c r="B233" s="15" t="n"/>
+      <c r="C233" s="15" t="n"/>
+      <c r="D233" s="15" t="n"/>
+      <c r="E233" s="15" t="n"/>
+      <c r="F233" s="21" t="n"/>
+      <c r="G233" s="21" t="n"/>
+      <c r="H233" s="15" t="n"/>
+      <c r="I233" s="15" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="n"/>
+      <c r="B234" s="15" t="n"/>
+      <c r="C234" s="15" t="n"/>
+      <c r="D234" s="15" t="n"/>
+      <c r="E234" s="15" t="n"/>
+      <c r="F234" s="21" t="n"/>
+      <c r="G234" s="21" t="n"/>
+      <c r="H234" s="15" t="n"/>
+      <c r="I234" s="15" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="n"/>
+      <c r="B235" s="15" t="n"/>
+      <c r="C235" s="15" t="n"/>
+      <c r="D235" s="15" t="n"/>
+      <c r="E235" s="15" t="n"/>
+      <c r="F235" s="21" t="n"/>
+      <c r="G235" s="21" t="n"/>
+      <c r="H235" s="15" t="n"/>
+      <c r="I235" s="15" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="n"/>
+      <c r="B236" s="15" t="n"/>
+      <c r="C236" s="15" t="n"/>
+      <c r="D236" s="15" t="n"/>
+      <c r="E236" s="15" t="n"/>
+      <c r="F236" s="21" t="n"/>
+      <c r="G236" s="21" t="n"/>
+      <c r="H236" s="15" t="n"/>
+      <c r="I236" s="15" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="n"/>
+      <c r="B237" s="15" t="n"/>
+      <c r="C237" s="15" t="n"/>
+      <c r="D237" s="15" t="n"/>
+      <c r="E237" s="15" t="n"/>
+      <c r="F237" s="21" t="n"/>
+      <c r="G237" s="21" t="n"/>
+      <c r="H237" s="15" t="n"/>
+      <c r="I237" s="15" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="15" t="n"/>
+      <c r="B238" s="15" t="n"/>
+      <c r="C238" s="15" t="n"/>
+      <c r="D238" s="15" t="n"/>
+      <c r="E238" s="15" t="n"/>
+      <c r="F238" s="21" t="n"/>
+      <c r="G238" s="21" t="n"/>
+      <c r="H238" s="15" t="n"/>
+      <c r="I238" s="15" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="n"/>
+      <c r="B239" s="15" t="n"/>
+      <c r="C239" s="15" t="n"/>
+      <c r="D239" s="15" t="n"/>
+      <c r="E239" s="15" t="n"/>
+      <c r="F239" s="21" t="n"/>
+      <c r="G239" s="21" t="n"/>
+      <c r="H239" s="15" t="n"/>
+      <c r="I239" s="15" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="15" t="n"/>
+      <c r="B240" s="15" t="n"/>
+      <c r="C240" s="15" t="n"/>
+      <c r="D240" s="15" t="n"/>
+      <c r="E240" s="15" t="n"/>
+      <c r="F240" s="21" t="n"/>
+      <c r="G240" s="21" t="n"/>
+      <c r="H240" s="15" t="n"/>
+      <c r="I240" s="15" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="n"/>
+      <c r="B241" s="15" t="n"/>
+      <c r="C241" s="15" t="n"/>
+      <c r="D241" s="15" t="n"/>
+      <c r="E241" s="15" t="n"/>
+      <c r="F241" s="21" t="n"/>
+      <c r="G241" s="21" t="n"/>
+      <c r="H241" s="15" t="n"/>
+      <c r="I241" s="15" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="15" t="n"/>
+      <c r="B242" s="15" t="n"/>
+      <c r="C242" s="15" t="n"/>
+      <c r="D242" s="15" t="n"/>
+      <c r="E242" s="15" t="n"/>
+      <c r="F242" s="21" t="n"/>
+      <c r="G242" s="21" t="n"/>
+      <c r="H242" s="15" t="n"/>
+      <c r="I242" s="15" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="15" t="n"/>
+      <c r="B243" s="15" t="n"/>
+      <c r="C243" s="15" t="n"/>
+      <c r="D243" s="15" t="n"/>
+      <c r="E243" s="15" t="n"/>
+      <c r="F243" s="21" t="n"/>
+      <c r="G243" s="21" t="n"/>
+      <c r="H243" s="15" t="n"/>
+      <c r="I243" s="15" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="15" t="n"/>
+      <c r="B244" s="15" t="n"/>
+      <c r="C244" s="15" t="n"/>
+      <c r="D244" s="15" t="n"/>
+      <c r="E244" s="15" t="n"/>
+      <c r="F244" s="21" t="n"/>
+      <c r="G244" s="21" t="n"/>
+      <c r="H244" s="15" t="n"/>
+      <c r="I244" s="15" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="15" t="n"/>
+      <c r="B245" s="15" t="n"/>
+      <c r="C245" s="15" t="n"/>
+      <c r="D245" s="15" t="n"/>
+      <c r="E245" s="15" t="n"/>
+      <c r="F245" s="21" t="n"/>
+      <c r="G245" s="21" t="n"/>
+      <c r="H245" s="15" t="n"/>
+      <c r="I245" s="15" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="n"/>
+      <c r="B246" s="15" t="n"/>
+      <c r="C246" s="15" t="n"/>
+      <c r="D246" s="15" t="n"/>
+      <c r="E246" s="15" t="n"/>
+      <c r="F246" s="21" t="n"/>
+      <c r="G246" s="21" t="n"/>
+      <c r="H246" s="15" t="n"/>
+      <c r="I246" s="15" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="15" t="n"/>
+      <c r="B247" s="15" t="n"/>
+      <c r="C247" s="15" t="n"/>
+      <c r="D247" s="15" t="n"/>
+      <c r="E247" s="15" t="n"/>
+      <c r="F247" s="21" t="n"/>
+      <c r="G247" s="21" t="n"/>
+      <c r="H247" s="15" t="n"/>
+      <c r="I247" s="15" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="15" t="n"/>
+      <c r="B248" s="15" t="n"/>
+      <c r="C248" s="15" t="n"/>
+      <c r="D248" s="15" t="n"/>
+      <c r="E248" s="15" t="n"/>
+      <c r="F248" s="21" t="n"/>
+      <c r="G248" s="21" t="n"/>
+      <c r="H248" s="15" t="n"/>
+      <c r="I248" s="15" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="15" t="n"/>
+      <c r="B249" s="15" t="n"/>
+      <c r="C249" s="15" t="n"/>
+      <c r="D249" s="15" t="n"/>
+      <c r="E249" s="15" t="n"/>
+      <c r="F249" s="21" t="n"/>
+      <c r="G249" s="21" t="n"/>
+      <c r="H249" s="15" t="n"/>
+      <c r="I249" s="15" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="15" t="n"/>
+      <c r="B250" s="15" t="n"/>
+      <c r="C250" s="15" t="n"/>
+      <c r="D250" s="15" t="n"/>
+      <c r="E250" s="15" t="n"/>
+      <c r="F250" s="21" t="n"/>
+      <c r="G250" s="21" t="n"/>
+      <c r="H250" s="15" t="n"/>
+      <c r="I250" s="15" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="15" t="n"/>
+      <c r="B251" s="15" t="n"/>
+      <c r="C251" s="15" t="n"/>
+      <c r="D251" s="15" t="n"/>
+      <c r="E251" s="15" t="n"/>
+      <c r="F251" s="21" t="n"/>
+      <c r="G251" s="21" t="n"/>
+      <c r="H251" s="15" t="n"/>
+      <c r="I251" s="15" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="15" t="n"/>
+      <c r="B252" s="15" t="n"/>
+      <c r="C252" s="15" t="n"/>
+      <c r="D252" s="15" t="n"/>
+      <c r="E252" s="15" t="n"/>
+      <c r="F252" s="21" t="n"/>
+      <c r="G252" s="21" t="n"/>
+      <c r="H252" s="15" t="n"/>
+      <c r="I252" s="15" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="15" t="n"/>
+      <c r="B253" s="15" t="n"/>
+      <c r="C253" s="15" t="n"/>
+      <c r="D253" s="15" t="n"/>
+      <c r="E253" s="15" t="n"/>
+      <c r="F253" s="21" t="n"/>
+      <c r="G253" s="21" t="n"/>
+      <c r="H253" s="15" t="n"/>
+      <c r="I253" s="15" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="15" t="n"/>
+      <c r="B254" s="15" t="n"/>
+      <c r="C254" s="15" t="n"/>
+      <c r="D254" s="15" t="n"/>
+      <c r="E254" s="15" t="n"/>
+      <c r="F254" s="21" t="n"/>
+      <c r="G254" s="21" t="n"/>
+      <c r="H254" s="15" t="n"/>
+      <c r="I254" s="15" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="15" t="n"/>
+      <c r="B255" s="15" t="n"/>
+      <c r="C255" s="15" t="n"/>
+      <c r="D255" s="15" t="n"/>
+      <c r="E255" s="15" t="n"/>
+      <c r="F255" s="21" t="n"/>
+      <c r="G255" s="21" t="n"/>
+      <c r="H255" s="15" t="n"/>
+      <c r="I255" s="15" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="n"/>
+      <c r="B256" s="15" t="n"/>
+      <c r="C256" s="15" t="n"/>
+      <c r="D256" s="15" t="n"/>
+      <c r="E256" s="15" t="n"/>
+      <c r="F256" s="21" t="n"/>
+      <c r="G256" s="21" t="n"/>
+      <c r="H256" s="15" t="n"/>
+      <c r="I256" s="15" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="15" t="n"/>
+      <c r="B257" s="15" t="n"/>
+      <c r="C257" s="15" t="n"/>
+      <c r="D257" s="15" t="n"/>
+      <c r="E257" s="15" t="n"/>
+      <c r="F257" s="21" t="n"/>
+      <c r="G257" s="21" t="n"/>
+      <c r="H257" s="15" t="n"/>
+      <c r="I257" s="15" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="15" t="n"/>
+      <c r="B258" s="15" t="n"/>
+      <c r="C258" s="15" t="n"/>
+      <c r="D258" s="15" t="n"/>
+      <c r="E258" s="15" t="n"/>
+      <c r="F258" s="21" t="n"/>
+      <c r="G258" s="21" t="n"/>
+      <c r="H258" s="15" t="n"/>
+      <c r="I258" s="15" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="n"/>
+      <c r="B259" s="15" t="n"/>
+      <c r="C259" s="15" t="n"/>
+      <c r="D259" s="15" t="n"/>
+      <c r="E259" s="15" t="n"/>
+      <c r="F259" s="21" t="n"/>
+      <c r="G259" s="21" t="n"/>
+      <c r="H259" s="15" t="n"/>
+      <c r="I259" s="15" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="15" t="n"/>
+      <c r="B260" s="15" t="n"/>
+      <c r="C260" s="15" t="n"/>
+      <c r="D260" s="15" t="n"/>
+      <c r="E260" s="15" t="n"/>
+      <c r="F260" s="21" t="n"/>
+      <c r="G260" s="21" t="n"/>
+      <c r="H260" s="15" t="n"/>
+      <c r="I260" s="15" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="15" t="n"/>
+      <c r="B261" s="15" t="n"/>
+      <c r="C261" s="15" t="n"/>
+      <c r="D261" s="15" t="n"/>
+      <c r="E261" s="15" t="n"/>
+      <c r="F261" s="21" t="n"/>
+      <c r="G261" s="21" t="n"/>
+      <c r="H261" s="15" t="n"/>
+      <c r="I261" s="15" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="15" t="n"/>
+      <c r="B262" s="15" t="n"/>
+      <c r="C262" s="15" t="n"/>
+      <c r="D262" s="15" t="n"/>
+      <c r="E262" s="15" t="n"/>
+      <c r="F262" s="21" t="n"/>
+      <c r="G262" s="21" t="n"/>
+      <c r="H262" s="15" t="n"/>
+      <c r="I262" s="15" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="15" t="n"/>
+      <c r="B263" s="15" t="n"/>
+      <c r="C263" s="15" t="n"/>
+      <c r="D263" s="15" t="n"/>
+      <c r="E263" s="15" t="n"/>
+      <c r="F263" s="21" t="n"/>
+      <c r="G263" s="21" t="n"/>
+      <c r="H263" s="15" t="n"/>
+      <c r="I263" s="15" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="15" t="n"/>
+      <c r="B264" s="15" t="n"/>
+      <c r="C264" s="15" t="n"/>
+      <c r="D264" s="15" t="n"/>
+      <c r="E264" s="15" t="n"/>
+      <c r="F264" s="21" t="n"/>
+      <c r="G264" s="21" t="n"/>
+      <c r="H264" s="15" t="n"/>
+      <c r="I264" s="15" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="n"/>
+      <c r="B265" s="15" t="n"/>
+      <c r="C265" s="15" t="n"/>
+      <c r="D265" s="15" t="n"/>
+      <c r="E265" s="15" t="n"/>
+      <c r="F265" s="21" t="n"/>
+      <c r="G265" s="21" t="n"/>
+      <c r="H265" s="15" t="n"/>
+      <c r="I265" s="15" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="n"/>
+      <c r="B266" s="15" t="n"/>
+      <c r="C266" s="15" t="n"/>
+      <c r="D266" s="15" t="n"/>
+      <c r="E266" s="15" t="n"/>
+      <c r="F266" s="21" t="n"/>
+      <c r="G266" s="21" t="n"/>
+      <c r="H266" s="15" t="n"/>
+      <c r="I266" s="15" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="n"/>
+      <c r="B267" s="15" t="n"/>
+      <c r="C267" s="15" t="n"/>
+      <c r="D267" s="15" t="n"/>
+      <c r="E267" s="15" t="n"/>
+      <c r="F267" s="21" t="n"/>
+      <c r="G267" s="21" t="n"/>
+      <c r="H267" s="15" t="n"/>
+      <c r="I267" s="15" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="15" t="n"/>
+      <c r="B268" s="15" t="n"/>
+      <c r="C268" s="15" t="n"/>
+      <c r="D268" s="15" t="n"/>
+      <c r="E268" s="15" t="n"/>
+      <c r="F268" s="21" t="n"/>
+      <c r="G268" s="21" t="n"/>
+      <c r="H268" s="15" t="n"/>
+      <c r="I268" s="15" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="15" t="n"/>
+      <c r="B269" s="15" t="n"/>
+      <c r="C269" s="15" t="n"/>
+      <c r="D269" s="15" t="n"/>
+      <c r="E269" s="15" t="n"/>
+      <c r="F269" s="21" t="n"/>
+      <c r="G269" s="21" t="n"/>
+      <c r="H269" s="15" t="n"/>
+      <c r="I269" s="15" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="15" t="n"/>
+      <c r="B270" s="15" t="n"/>
+      <c r="C270" s="15" t="n"/>
+      <c r="D270" s="15" t="n"/>
+      <c r="E270" s="15" t="n"/>
+      <c r="F270" s="21" t="n"/>
+      <c r="G270" s="21" t="n"/>
+      <c r="H270" s="15" t="n"/>
+      <c r="I270" s="15" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="15" t="n"/>
+      <c r="B271" s="15" t="n"/>
+      <c r="C271" s="15" t="n"/>
+      <c r="D271" s="15" t="n"/>
+      <c r="E271" s="15" t="n"/>
+      <c r="F271" s="21" t="n"/>
+      <c r="G271" s="21" t="n"/>
+      <c r="H271" s="15" t="n"/>
+      <c r="I271" s="15" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="n"/>
+      <c r="B272" s="15" t="n"/>
+      <c r="C272" s="15" t="n"/>
+      <c r="D272" s="15" t="n"/>
+      <c r="E272" s="15" t="n"/>
+      <c r="F272" s="21" t="n"/>
+      <c r="G272" s="21" t="n"/>
+      <c r="H272" s="15" t="n"/>
+      <c r="I272" s="15" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="15" t="n"/>
+      <c r="B273" s="15" t="n"/>
+      <c r="C273" s="15" t="n"/>
+      <c r="D273" s="15" t="n"/>
+      <c r="E273" s="15" t="n"/>
+      <c r="F273" s="21" t="n"/>
+      <c r="G273" s="21" t="n"/>
+      <c r="H273" s="15" t="n"/>
+      <c r="I273" s="15" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="15" t="n"/>
+      <c r="B274" s="15" t="n"/>
+      <c r="C274" s="15" t="n"/>
+      <c r="D274" s="15" t="n"/>
+      <c r="E274" s="15" t="n"/>
+      <c r="F274" s="21" t="n"/>
+      <c r="G274" s="21" t="n"/>
+      <c r="H274" s="15" t="n"/>
+      <c r="I274" s="15" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="15" t="n"/>
+      <c r="B275" s="15" t="n"/>
+      <c r="C275" s="15" t="n"/>
+      <c r="D275" s="15" t="n"/>
+      <c r="E275" s="15" t="n"/>
+      <c r="F275" s="21" t="n"/>
+      <c r="G275" s="21" t="n"/>
+      <c r="H275" s="15" t="n"/>
+      <c r="I275" s="15" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="15" t="n"/>
+      <c r="B276" s="15" t="n"/>
+      <c r="C276" s="15" t="n"/>
+      <c r="D276" s="15" t="n"/>
+      <c r="E276" s="15" t="n"/>
+      <c r="F276" s="21" t="n"/>
+      <c r="G276" s="21" t="n"/>
+      <c r="H276" s="15" t="n"/>
+      <c r="I276" s="15" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="15" t="n"/>
+      <c r="B277" s="15" t="n"/>
+      <c r="C277" s="15" t="n"/>
+      <c r="D277" s="15" t="n"/>
+      <c r="E277" s="15" t="n"/>
+      <c r="F277" s="21" t="n"/>
+      <c r="G277" s="21" t="n"/>
+      <c r="H277" s="15" t="n"/>
+      <c r="I277" s="15" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="15" t="n"/>
+      <c r="B278" s="15" t="n"/>
+      <c r="C278" s="15" t="n"/>
+      <c r="D278" s="15" t="n"/>
+      <c r="E278" s="15" t="n"/>
+      <c r="F278" s="21" t="n"/>
+      <c r="G278" s="21" t="n"/>
+      <c r="H278" s="15" t="n"/>
+      <c r="I278" s="15" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="15" t="n"/>
+      <c r="B279" s="15" t="n"/>
+      <c r="C279" s="15" t="n"/>
+      <c r="D279" s="15" t="n"/>
+      <c r="E279" s="15" t="n"/>
+      <c r="F279" s="21" t="n"/>
+      <c r="G279" s="21" t="n"/>
+      <c r="H279" s="15" t="n"/>
+      <c r="I279" s="15" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="15" t="n"/>
+      <c r="B280" s="15" t="n"/>
+      <c r="C280" s="15" t="n"/>
+      <c r="D280" s="15" t="n"/>
+      <c r="E280" s="15" t="n"/>
+      <c r="F280" s="21" t="n"/>
+      <c r="G280" s="21" t="n"/>
+      <c r="H280" s="15" t="n"/>
+      <c r="I280" s="15" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="15" t="n"/>
+      <c r="B281" s="15" t="n"/>
+      <c r="C281" s="15" t="n"/>
+      <c r="D281" s="15" t="n"/>
+      <c r="E281" s="15" t="n"/>
+      <c r="F281" s="21" t="n"/>
+      <c r="G281" s="21" t="n"/>
+      <c r="H281" s="15" t="n"/>
+      <c r="I281" s="15" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="15" t="n"/>
+      <c r="B282" s="15" t="n"/>
+      <c r="C282" s="15" t="n"/>
+      <c r="D282" s="15" t="n"/>
+      <c r="E282" s="15" t="n"/>
+      <c r="F282" s="21" t="n"/>
+      <c r="G282" s="21" t="n"/>
+      <c r="H282" s="15" t="n"/>
+      <c r="I282" s="15" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="15" t="n"/>
+      <c r="B283" s="15" t="n"/>
+      <c r="C283" s="15" t="n"/>
+      <c r="D283" s="15" t="n"/>
+      <c r="E283" s="15" t="n"/>
+      <c r="F283" s="21" t="n"/>
+      <c r="G283" s="21" t="n"/>
+      <c r="H283" s="15" t="n"/>
+      <c r="I283" s="15" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="15" t="n"/>
+      <c r="B284" s="15" t="n"/>
+      <c r="C284" s="15" t="n"/>
+      <c r="D284" s="15" t="n"/>
+      <c r="E284" s="15" t="n"/>
+      <c r="F284" s="21" t="n"/>
+      <c r="G284" s="21" t="n"/>
+      <c r="H284" s="15" t="n"/>
+      <c r="I284" s="15" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="n"/>
+      <c r="B285" s="15" t="n"/>
+      <c r="C285" s="15" t="n"/>
+      <c r="D285" s="15" t="n"/>
+      <c r="E285" s="15" t="n"/>
+      <c r="F285" s="21" t="n"/>
+      <c r="G285" s="21" t="n"/>
+      <c r="H285" s="15" t="n"/>
+      <c r="I285" s="15" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="15" t="n"/>
+      <c r="B286" s="15" t="n"/>
+      <c r="C286" s="15" t="n"/>
+      <c r="D286" s="15" t="n"/>
+      <c r="E286" s="15" t="n"/>
+      <c r="F286" s="21" t="n"/>
+      <c r="G286" s="21" t="n"/>
+      <c r="H286" s="15" t="n"/>
+      <c r="I286" s="15" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="n"/>
+      <c r="B287" s="15" t="n"/>
+      <c r="C287" s="15" t="n"/>
+      <c r="D287" s="15" t="n"/>
+      <c r="E287" s="15" t="n"/>
+      <c r="F287" s="21" t="n"/>
+      <c r="G287" s="21" t="n"/>
+      <c r="H287" s="15" t="n"/>
+      <c r="I287" s="15" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="n"/>
+      <c r="B288" s="15" t="n"/>
+      <c r="C288" s="15" t="n"/>
+      <c r="D288" s="15" t="n"/>
+      <c r="E288" s="15" t="n"/>
+      <c r="F288" s="21" t="n"/>
+      <c r="G288" s="21" t="n"/>
+      <c r="H288" s="15" t="n"/>
+      <c r="I288" s="15" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="15" t="n"/>
+      <c r="B289" s="15" t="n"/>
+      <c r="C289" s="15" t="n"/>
+      <c r="D289" s="15" t="n"/>
+      <c r="E289" s="15" t="n"/>
+      <c r="F289" s="21" t="n"/>
+      <c r="G289" s="21" t="n"/>
+      <c r="H289" s="15" t="n"/>
+      <c r="I289" s="15" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="n"/>
+      <c r="B290" s="15" t="n"/>
+      <c r="C290" s="15" t="n"/>
+      <c r="D290" s="15" t="n"/>
+      <c r="E290" s="15" t="n"/>
+      <c r="F290" s="21" t="n"/>
+      <c r="G290" s="21" t="n"/>
+      <c r="H290" s="15" t="n"/>
+      <c r="I290" s="15" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="15" t="n"/>
+      <c r="B291" s="15" t="n"/>
+      <c r="C291" s="15" t="n"/>
+      <c r="D291" s="15" t="n"/>
+      <c r="E291" s="15" t="n"/>
+      <c r="F291" s="21" t="n"/>
+      <c r="G291" s="21" t="n"/>
+      <c r="H291" s="15" t="n"/>
+      <c r="I291" s="15" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="n"/>
+      <c r="B292" s="15" t="n"/>
+      <c r="C292" s="15" t="n"/>
+      <c r="D292" s="15" t="n"/>
+      <c r="E292" s="15" t="n"/>
+      <c r="F292" s="21" t="n"/>
+      <c r="G292" s="21" t="n"/>
+      <c r="H292" s="15" t="n"/>
+      <c r="I292" s="15" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="15" t="n"/>
+      <c r="B293" s="15" t="n"/>
+      <c r="C293" s="15" t="n"/>
+      <c r="D293" s="15" t="n"/>
+      <c r="E293" s="15" t="n"/>
+      <c r="F293" s="21" t="n"/>
+      <c r="G293" s="21" t="n"/>
+      <c r="H293" s="15" t="n"/>
+      <c r="I293" s="15" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="15" t="n"/>
+      <c r="B294" s="15" t="n"/>
+      <c r="C294" s="15" t="n"/>
+      <c r="D294" s="15" t="n"/>
+      <c r="E294" s="15" t="n"/>
+      <c r="F294" s="21" t="n"/>
+      <c r="G294" s="21" t="n"/>
+      <c r="H294" s="15" t="n"/>
+      <c r="I294" s="15" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="15" t="n"/>
+      <c r="B295" s="15" t="n"/>
+      <c r="C295" s="15" t="n"/>
+      <c r="D295" s="15" t="n"/>
+      <c r="E295" s="15" t="n"/>
+      <c r="F295" s="21" t="n"/>
+      <c r="G295" s="21" t="n"/>
+      <c r="H295" s="15" t="n"/>
+      <c r="I295" s="15" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="15" t="n"/>
+      <c r="B296" s="15" t="n"/>
+      <c r="C296" s="15" t="n"/>
+      <c r="D296" s="15" t="n"/>
+      <c r="E296" s="15" t="n"/>
+      <c r="F296" s="21" t="n"/>
+      <c r="G296" s="21" t="n"/>
+      <c r="H296" s="15" t="n"/>
+      <c r="I296" s="15" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="15" t="n"/>
+      <c r="B297" s="15" t="n"/>
+      <c r="C297" s="15" t="n"/>
+      <c r="D297" s="15" t="n"/>
+      <c r="E297" s="15" t="n"/>
+      <c r="F297" s="21" t="n"/>
+      <c r="G297" s="21" t="n"/>
+      <c r="H297" s="15" t="n"/>
+      <c r="I297" s="15" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="n"/>
+      <c r="B298" s="15" t="n"/>
+      <c r="C298" s="15" t="n"/>
+      <c r="D298" s="15" t="n"/>
+      <c r="E298" s="15" t="n"/>
+      <c r="F298" s="21" t="n"/>
+      <c r="G298" s="21" t="n"/>
+      <c r="H298" s="15" t="n"/>
+      <c r="I298" s="15" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="15" t="n"/>
+      <c r="B299" s="15" t="n"/>
+      <c r="C299" s="15" t="n"/>
+      <c r="D299" s="15" t="n"/>
+      <c r="E299" s="15" t="n"/>
+      <c r="F299" s="21" t="n"/>
+      <c r="G299" s="21" t="n"/>
+      <c r="H299" s="15" t="n"/>
+      <c r="I299" s="15" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="15" t="n"/>
+      <c r="B300" s="15" t="n"/>
+      <c r="C300" s="15" t="n"/>
+      <c r="D300" s="15" t="n"/>
+      <c r="E300" s="15" t="n"/>
+      <c r="F300" s="21" t="n"/>
+      <c r="G300" s="21" t="n"/>
+      <c r="H300" s="15" t="n"/>
+      <c r="I300" s="15" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="15" t="n"/>
+      <c r="B301" s="15" t="n"/>
+      <c r="C301" s="15" t="n"/>
+      <c r="D301" s="15" t="n"/>
+      <c r="E301" s="15" t="n"/>
+      <c r="F301" s="21" t="n"/>
+      <c r="G301" s="21" t="n"/>
+      <c r="H301" s="15" t="n"/>
+      <c r="I301" s="15" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="15" t="n"/>
+      <c r="B302" s="15" t="n"/>
+      <c r="C302" s="15" t="n"/>
+      <c r="D302" s="15" t="n"/>
+      <c r="E302" s="15" t="n"/>
+      <c r="F302" s="21" t="n"/>
+      <c r="G302" s="21" t="n"/>
+      <c r="H302" s="15" t="n"/>
+      <c r="I302" s="15" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="15" t="n"/>
+      <c r="B303" s="15" t="n"/>
+      <c r="C303" s="15" t="n"/>
+      <c r="D303" s="15" t="n"/>
+      <c r="E303" s="15" t="n"/>
+      <c r="F303" s="21" t="n"/>
+      <c r="G303" s="21" t="n"/>
+      <c r="H303" s="15" t="n"/>
+      <c r="I303" s="15" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="15" t="n"/>
+      <c r="B304" s="15" t="n"/>
+      <c r="C304" s="15" t="n"/>
+      <c r="D304" s="15" t="n"/>
+      <c r="E304" s="15" t="n"/>
+      <c r="F304" s="21" t="n"/>
+      <c r="G304" s="21" t="n"/>
+      <c r="H304" s="15" t="n"/>
+      <c r="I304" s="15" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="15" t="n"/>
+      <c r="B305" s="15" t="n"/>
+      <c r="C305" s="15" t="n"/>
+      <c r="D305" s="15" t="n"/>
+      <c r="E305" s="15" t="n"/>
+      <c r="F305" s="21" t="n"/>
+      <c r="G305" s="21" t="n"/>
+      <c r="H305" s="15" t="n"/>
+      <c r="I305" s="15" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="15" t="n"/>
+      <c r="B306" s="15" t="n"/>
+      <c r="C306" s="15" t="n"/>
+      <c r="D306" s="15" t="n"/>
+      <c r="E306" s="15" t="n"/>
+      <c r="F306" s="21" t="n"/>
+      <c r="G306" s="21" t="n"/>
+      <c r="H306" s="15" t="n"/>
+      <c r="I306" s="15" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="15" t="n"/>
+      <c r="B307" s="15" t="n"/>
+      <c r="C307" s="15" t="n"/>
+      <c r="D307" s="15" t="n"/>
+      <c r="E307" s="15" t="n"/>
+      <c r="F307" s="21" t="n"/>
+      <c r="G307" s="21" t="n"/>
+      <c r="H307" s="15" t="n"/>
+      <c r="I307" s="15" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="15" t="n"/>
+      <c r="B308" s="15" t="n"/>
+      <c r="C308" s="15" t="n"/>
+      <c r="D308" s="15" t="n"/>
+      <c r="E308" s="15" t="n"/>
+      <c r="F308" s="21" t="n"/>
+      <c r="G308" s="21" t="n"/>
+      <c r="H308" s="15" t="n"/>
+      <c r="I308" s="15" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="15" t="n"/>
+      <c r="B309" s="15" t="n"/>
+      <c r="C309" s="15" t="n"/>
+      <c r="D309" s="15" t="n"/>
+      <c r="E309" s="15" t="n"/>
+      <c r="F309" s="21" t="n"/>
+      <c r="G309" s="21" t="n"/>
+      <c r="H309" s="15" t="n"/>
+      <c r="I309" s="15" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="15" t="n"/>
+      <c r="B310" s="15" t="n"/>
+      <c r="C310" s="15" t="n"/>
+      <c r="D310" s="15" t="n"/>
+      <c r="E310" s="15" t="n"/>
+      <c r="F310" s="21" t="n"/>
+      <c r="G310" s="21" t="n"/>
+      <c r="H310" s="15" t="n"/>
+      <c r="I310" s="15" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="15" t="n"/>
+      <c r="B311" s="15" t="n"/>
+      <c r="C311" s="15" t="n"/>
+      <c r="D311" s="15" t="n"/>
+      <c r="E311" s="15" t="n"/>
+      <c r="F311" s="21" t="n"/>
+      <c r="G311" s="21" t="n"/>
+      <c r="H311" s="15" t="n"/>
+      <c r="I311" s="15" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="15" t="n"/>
+      <c r="B312" s="15" t="n"/>
+      <c r="C312" s="15" t="n"/>
+      <c r="D312" s="15" t="n"/>
+      <c r="E312" s="15" t="n"/>
+      <c r="F312" s="21" t="n"/>
+      <c r="G312" s="21" t="n"/>
+      <c r="H312" s="15" t="n"/>
+      <c r="I312" s="15" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="15" t="n"/>
+      <c r="B313" s="15" t="n"/>
+      <c r="C313" s="15" t="n"/>
+      <c r="D313" s="15" t="n"/>
+      <c r="E313" s="15" t="n"/>
+      <c r="F313" s="21" t="n"/>
+      <c r="G313" s="21" t="n"/>
+      <c r="H313" s="15" t="n"/>
+      <c r="I313" s="15" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="15" t="n"/>
+      <c r="B314" s="15" t="n"/>
+      <c r="C314" s="15" t="n"/>
+      <c r="D314" s="15" t="n"/>
+      <c r="E314" s="15" t="n"/>
+      <c r="F314" s="21" t="n"/>
+      <c r="G314" s="21" t="n"/>
+      <c r="H314" s="15" t="n"/>
+      <c r="I314" s="15" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="n"/>
+      <c r="B315" s="15" t="n"/>
+      <c r="C315" s="15" t="n"/>
+      <c r="D315" s="15" t="n"/>
+      <c r="E315" s="15" t="n"/>
+      <c r="F315" s="21" t="n"/>
+      <c r="G315" s="21" t="n"/>
+      <c r="H315" s="15" t="n"/>
+      <c r="I315" s="15" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="15" t="n"/>
+      <c r="B316" s="15" t="n"/>
+      <c r="C316" s="15" t="n"/>
+      <c r="D316" s="15" t="n"/>
+      <c r="E316" s="15" t="n"/>
+      <c r="F316" s="21" t="n"/>
+      <c r="G316" s="21" t="n"/>
+      <c r="H316" s="15" t="n"/>
+      <c r="I316" s="15" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="15" t="n"/>
+      <c r="B317" s="15" t="n"/>
+      <c r="C317" s="15" t="n"/>
+      <c r="D317" s="15" t="n"/>
+      <c r="E317" s="15" t="n"/>
+      <c r="F317" s="21" t="n"/>
+      <c r="G317" s="21" t="n"/>
+      <c r="H317" s="15" t="n"/>
+      <c r="I317" s="15" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="15" t="n"/>
+      <c r="B318" s="15" t="n"/>
+      <c r="C318" s="15" t="n"/>
+      <c r="D318" s="15" t="n"/>
+      <c r="E318" s="15" t="n"/>
+      <c r="F318" s="21" t="n"/>
+      <c r="G318" s="21" t="n"/>
+      <c r="H318" s="15" t="n"/>
+      <c r="I318" s="15" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="15" t="n"/>
+      <c r="B319" s="15" t="n"/>
+      <c r="C319" s="15" t="n"/>
+      <c r="D319" s="15" t="n"/>
+      <c r="E319" s="15" t="n"/>
+      <c r="F319" s="21" t="n"/>
+      <c r="G319" s="21" t="n"/>
+      <c r="H319" s="15" t="n"/>
+      <c r="I319" s="15" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="15" t="n"/>
+      <c r="B320" s="15" t="n"/>
+      <c r="C320" s="15" t="n"/>
+      <c r="D320" s="15" t="n"/>
+      <c r="E320" s="15" t="n"/>
+      <c r="F320" s="21" t="n"/>
+      <c r="G320" s="21" t="n"/>
+      <c r="H320" s="15" t="n"/>
+      <c r="I320" s="15" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="15" t="n"/>
+      <c r="B321" s="15" t="n"/>
+      <c r="C321" s="15" t="n"/>
+      <c r="D321" s="15" t="n"/>
+      <c r="E321" s="15" t="n"/>
+      <c r="F321" s="21" t="n"/>
+      <c r="G321" s="21" t="n"/>
+      <c r="H321" s="15" t="n"/>
+      <c r="I321" s="15" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="15" t="n"/>
+      <c r="B322" s="15" t="n"/>
+      <c r="C322" s="15" t="n"/>
+      <c r="D322" s="15" t="n"/>
+      <c r="E322" s="15" t="n"/>
+      <c r="F322" s="21" t="n"/>
+      <c r="G322" s="21" t="n"/>
+      <c r="H322" s="15" t="n"/>
+      <c r="I322" s="15" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="15" t="n"/>
+      <c r="B323" s="15" t="n"/>
+      <c r="C323" s="15" t="n"/>
+      <c r="D323" s="15" t="n"/>
+      <c r="E323" s="15" t="n"/>
+      <c r="F323" s="21" t="n"/>
+      <c r="G323" s="21" t="n"/>
+      <c r="H323" s="15" t="n"/>
+      <c r="I323" s="15" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="15" t="n"/>
+      <c r="B324" s="15" t="n"/>
+      <c r="C324" s="15" t="n"/>
+      <c r="D324" s="15" t="n"/>
+      <c r="E324" s="15" t="n"/>
+      <c r="F324" s="21" t="n"/>
+      <c r="G324" s="21" t="n"/>
+      <c r="H324" s="15" t="n"/>
+      <c r="I324" s="15" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="15" t="n"/>
+      <c r="B325" s="15" t="n"/>
+      <c r="C325" s="15" t="n"/>
+      <c r="D325" s="15" t="n"/>
+      <c r="E325" s="15" t="n"/>
+      <c r="F325" s="21" t="n"/>
+      <c r="G325" s="21" t="n"/>
+      <c r="H325" s="15" t="n"/>
+      <c r="I325" s="15" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="15" t="n"/>
+      <c r="B326" s="15" t="n"/>
+      <c r="C326" s="15" t="n"/>
+      <c r="D326" s="15" t="n"/>
+      <c r="E326" s="15" t="n"/>
+      <c r="F326" s="21" t="n"/>
+      <c r="G326" s="21" t="n"/>
+      <c r="H326" s="15" t="n"/>
+      <c r="I326" s="15" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="n"/>
+      <c r="B327" s="15" t="n"/>
+      <c r="C327" s="15" t="n"/>
+      <c r="D327" s="15" t="n"/>
+      <c r="E327" s="15" t="n"/>
+      <c r="F327" s="21" t="n"/>
+      <c r="G327" s="21" t="n"/>
+      <c r="H327" s="15" t="n"/>
+      <c r="I327" s="15" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="15" t="n"/>
+      <c r="B328" s="15" t="n"/>
+      <c r="C328" s="15" t="n"/>
+      <c r="D328" s="15" t="n"/>
+      <c r="E328" s="15" t="n"/>
+      <c r="F328" s="21" t="n"/>
+      <c r="G328" s="21" t="n"/>
+      <c r="H328" s="15" t="n"/>
+      <c r="I328" s="15" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="15" t="n"/>
+      <c r="B329" s="15" t="n"/>
+      <c r="C329" s="15" t="n"/>
+      <c r="D329" s="15" t="n"/>
+      <c r="E329" s="15" t="n"/>
+      <c r="F329" s="21" t="n"/>
+      <c r="G329" s="21" t="n"/>
+      <c r="H329" s="15" t="n"/>
+      <c r="I329" s="15" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="15" t="n"/>
+      <c r="B330" s="15" t="n"/>
+      <c r="C330" s="15" t="n"/>
+      <c r="D330" s="15" t="n"/>
+      <c r="E330" s="15" t="n"/>
+      <c r="F330" s="21" t="n"/>
+      <c r="G330" s="21" t="n"/>
+      <c r="H330" s="15" t="n"/>
+      <c r="I330" s="15" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="15" t="n"/>
+      <c r="B331" s="15" t="n"/>
+      <c r="C331" s="15" t="n"/>
+      <c r="D331" s="15" t="n"/>
+      <c r="E331" s="15" t="n"/>
+      <c r="F331" s="21" t="n"/>
+      <c r="G331" s="21" t="n"/>
+      <c r="H331" s="15" t="n"/>
+      <c r="I331" s="15" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="15" t="n"/>
+      <c r="B332" s="15" t="n"/>
+      <c r="C332" s="15" t="n"/>
+      <c r="D332" s="15" t="n"/>
+      <c r="E332" s="15" t="n"/>
+      <c r="F332" s="21" t="n"/>
+      <c r="G332" s="21" t="n"/>
+      <c r="H332" s="15" t="n"/>
+      <c r="I332" s="15" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="n"/>
+      <c r="B333" s="15" t="n"/>
+      <c r="C333" s="15" t="n"/>
+      <c r="D333" s="15" t="n"/>
+      <c r="E333" s="15" t="n"/>
+      <c r="F333" s="21" t="n"/>
+      <c r="G333" s="21" t="n"/>
+      <c r="H333" s="15" t="n"/>
+      <c r="I333" s="15" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="15" t="n"/>
+      <c r="B334" s="15" t="n"/>
+      <c r="C334" s="15" t="n"/>
+      <c r="D334" s="15" t="n"/>
+      <c r="E334" s="15" t="n"/>
+      <c r="F334" s="21" t="n"/>
+      <c r="G334" s="21" t="n"/>
+      <c r="H334" s="15" t="n"/>
+      <c r="I334" s="15" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="15" t="n"/>
+      <c r="B335" s="15" t="n"/>
+      <c r="C335" s="15" t="n"/>
+      <c r="D335" s="15" t="n"/>
+      <c r="E335" s="15" t="n"/>
+      <c r="F335" s="21" t="n"/>
+      <c r="G335" s="21" t="n"/>
+      <c r="H335" s="15" t="n"/>
+      <c r="I335" s="15" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="15" t="n"/>
+      <c r="B336" s="15" t="n"/>
+      <c r="C336" s="15" t="n"/>
+      <c r="D336" s="15" t="n"/>
+      <c r="E336" s="15" t="n"/>
+      <c r="F336" s="21" t="n"/>
+      <c r="G336" s="21" t="n"/>
+      <c r="H336" s="15" t="n"/>
+      <c r="I336" s="15" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="15" t="n"/>
+      <c r="B337" s="15" t="n"/>
+      <c r="C337" s="15" t="n"/>
+      <c r="D337" s="15" t="n"/>
+      <c r="E337" s="15" t="n"/>
+      <c r="F337" s="21" t="n"/>
+      <c r="G337" s="21" t="n"/>
+      <c r="H337" s="15" t="n"/>
+      <c r="I337" s="15" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="15" t="n"/>
+      <c r="B338" s="15" t="n"/>
+      <c r="C338" s="15" t="n"/>
+      <c r="D338" s="15" t="n"/>
+      <c r="E338" s="15" t="n"/>
+      <c r="F338" s="21" t="n"/>
+      <c r="G338" s="21" t="n"/>
+      <c r="H338" s="15" t="n"/>
+      <c r="I338" s="15" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="15" t="n"/>
+      <c r="B339" s="15" t="n"/>
+      <c r="C339" s="15" t="n"/>
+      <c r="D339" s="15" t="n"/>
+      <c r="E339" s="15" t="n"/>
+      <c r="F339" s="21" t="n"/>
+      <c r="G339" s="21" t="n"/>
+      <c r="H339" s="15" t="n"/>
+      <c r="I339" s="15" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="n"/>
+      <c r="B340" s="15" t="n"/>
+      <c r="C340" s="15" t="n"/>
+      <c r="D340" s="15" t="n"/>
+      <c r="E340" s="15" t="n"/>
+      <c r="F340" s="21" t="n"/>
+      <c r="G340" s="21" t="n"/>
+      <c r="H340" s="15" t="n"/>
+      <c r="I340" s="15" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="15" t="n"/>
+      <c r="B341" s="15" t="n"/>
+      <c r="C341" s="15" t="n"/>
+      <c r="D341" s="15" t="n"/>
+      <c r="E341" s="15" t="n"/>
+      <c r="F341" s="21" t="n"/>
+      <c r="G341" s="21" t="n"/>
+      <c r="H341" s="15" t="n"/>
+      <c r="I341" s="15" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="15" t="n"/>
+      <c r="B342" s="15" t="n"/>
+      <c r="C342" s="15" t="n"/>
+      <c r="D342" s="15" t="n"/>
+      <c r="E342" s="15" t="n"/>
+      <c r="F342" s="21" t="n"/>
+      <c r="G342" s="21" t="n"/>
+      <c r="H342" s="15" t="n"/>
+      <c r="I342" s="15" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="15" t="n"/>
+      <c r="B343" s="15" t="n"/>
+      <c r="C343" s="15" t="n"/>
+      <c r="D343" s="15" t="n"/>
+      <c r="E343" s="15" t="n"/>
+      <c r="F343" s="21" t="n"/>
+      <c r="G343" s="21" t="n"/>
+      <c r="H343" s="15" t="n"/>
+      <c r="I343" s="15" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="15" t="n"/>
+      <c r="B344" s="15" t="n"/>
+      <c r="C344" s="15" t="n"/>
+      <c r="D344" s="15" t="n"/>
+      <c r="E344" s="15" t="n"/>
+      <c r="F344" s="21" t="n"/>
+      <c r="G344" s="21" t="n"/>
+      <c r="H344" s="15" t="n"/>
+      <c r="I344" s="15" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="15" t="n"/>
+      <c r="B345" s="15" t="n"/>
+      <c r="C345" s="15" t="n"/>
+      <c r="D345" s="15" t="n"/>
+      <c r="E345" s="15" t="n"/>
+      <c r="F345" s="21" t="n"/>
+      <c r="G345" s="21" t="n"/>
+      <c r="H345" s="15" t="n"/>
+      <c r="I345" s="15" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="n"/>
+      <c r="B346" s="15" t="n"/>
+      <c r="C346" s="15" t="n"/>
+      <c r="D346" s="15" t="n"/>
+      <c r="E346" s="15" t="n"/>
+      <c r="F346" s="21" t="n"/>
+      <c r="G346" s="21" t="n"/>
+      <c r="H346" s="15" t="n"/>
+      <c r="I346" s="15" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="15" t="n"/>
+      <c r="B347" s="15" t="n"/>
+      <c r="C347" s="15" t="n"/>
+      <c r="D347" s="15" t="n"/>
+      <c r="E347" s="15" t="n"/>
+      <c r="F347" s="21" t="n"/>
+      <c r="G347" s="21" t="n"/>
+      <c r="H347" s="15" t="n"/>
+      <c r="I347" s="15" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="15" t="n"/>
+      <c r="B348" s="15" t="n"/>
+      <c r="C348" s="15" t="n"/>
+      <c r="D348" s="15" t="n"/>
+      <c r="E348" s="15" t="n"/>
+      <c r="F348" s="21" t="n"/>
+      <c r="G348" s="21" t="n"/>
+      <c r="H348" s="15" t="n"/>
+      <c r="I348" s="15" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="15" t="n"/>
+      <c r="B349" s="15" t="n"/>
+      <c r="C349" s="15" t="n"/>
+      <c r="D349" s="15" t="n"/>
+      <c r="E349" s="15" t="n"/>
+      <c r="F349" s="21" t="n"/>
+      <c r="G349" s="21" t="n"/>
+      <c r="H349" s="15" t="n"/>
+      <c r="I349" s="15" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="15" t="n"/>
+      <c r="B350" s="15" t="n"/>
+      <c r="C350" s="15" t="n"/>
+      <c r="D350" s="15" t="n"/>
+      <c r="E350" s="15" t="n"/>
+      <c r="F350" s="21" t="n"/>
+      <c r="G350" s="21" t="n"/>
+      <c r="H350" s="15" t="n"/>
+      <c r="I350" s="15" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="15" t="n"/>
+      <c r="B351" s="15" t="n"/>
+      <c r="C351" s="15" t="n"/>
+      <c r="D351" s="15" t="n"/>
+      <c r="E351" s="15" t="n"/>
+      <c r="F351" s="21" t="n"/>
+      <c r="G351" s="21" t="n"/>
+      <c r="H351" s="15" t="n"/>
+      <c r="I351" s="15" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="15" t="n"/>
+      <c r="B352" s="15" t="n"/>
+      <c r="C352" s="15" t="n"/>
+      <c r="D352" s="15" t="n"/>
+      <c r="E352" s="15" t="n"/>
+      <c r="F352" s="21" t="n"/>
+      <c r="G352" s="21" t="n"/>
+      <c r="H352" s="15" t="n"/>
+      <c r="I352" s="15" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="n"/>
+      <c r="B353" s="15" t="n"/>
+      <c r="C353" s="15" t="n"/>
+      <c r="D353" s="15" t="n"/>
+      <c r="E353" s="15" t="n"/>
+      <c r="F353" s="21" t="n"/>
+      <c r="G353" s="21" t="n"/>
+      <c r="H353" s="15" t="n"/>
+      <c r="I353" s="15" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="n"/>
+      <c r="B354" s="15" t="n"/>
+      <c r="C354" s="15" t="n"/>
+      <c r="D354" s="15" t="n"/>
+      <c r="E354" s="15" t="n"/>
+      <c r="F354" s="21" t="n"/>
+      <c r="G354" s="21" t="n"/>
+      <c r="H354" s="15" t="n"/>
+      <c r="I354" s="15" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="n"/>
+      <c r="B355" s="15" t="n"/>
+      <c r="C355" s="15" t="n"/>
+      <c r="D355" s="15" t="n"/>
+      <c r="E355" s="15" t="n"/>
+      <c r="F355" s="21" t="n"/>
+      <c r="G355" s="21" t="n"/>
+      <c r="H355" s="15" t="n"/>
+      <c r="I355" s="15" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="15" t="n"/>
+      <c r="B356" s="15" t="n"/>
+      <c r="C356" s="15" t="n"/>
+      <c r="D356" s="15" t="n"/>
+      <c r="E356" s="15" t="n"/>
+      <c r="F356" s="21" t="n"/>
+      <c r="G356" s="21" t="n"/>
+      <c r="H356" s="15" t="n"/>
+      <c r="I356" s="15" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="15" t="n"/>
+      <c r="B357" s="15" t="n"/>
+      <c r="C357" s="15" t="n"/>
+      <c r="D357" s="15" t="n"/>
+      <c r="E357" s="15" t="n"/>
+      <c r="F357" s="21" t="n"/>
+      <c r="G357" s="21" t="n"/>
+      <c r="H357" s="15" t="n"/>
+      <c r="I357" s="15" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="15" t="n"/>
+      <c r="B358" s="15" t="n"/>
+      <c r="C358" s="15" t="n"/>
+      <c r="D358" s="15" t="n"/>
+      <c r="E358" s="15" t="n"/>
+      <c r="F358" s="21" t="n"/>
+      <c r="G358" s="21" t="n"/>
+      <c r="H358" s="15" t="n"/>
+      <c r="I358" s="15" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="n"/>
+      <c r="B359" s="15" t="n"/>
+      <c r="C359" s="15" t="n"/>
+      <c r="D359" s="15" t="n"/>
+      <c r="E359" s="15" t="n"/>
+      <c r="F359" s="21" t="n"/>
+      <c r="G359" s="21" t="n"/>
+      <c r="H359" s="15" t="n"/>
+      <c r="I359" s="15" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="15" t="n"/>
+      <c r="B360" s="15" t="n"/>
+      <c r="C360" s="15" t="n"/>
+      <c r="D360" s="15" t="n"/>
+      <c r="E360" s="15" t="n"/>
+      <c r="F360" s="21" t="n"/>
+      <c r="G360" s="21" t="n"/>
+      <c r="H360" s="15" t="n"/>
+      <c r="I360" s="15" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="15" t="n"/>
+      <c r="B361" s="15" t="n"/>
+      <c r="C361" s="15" t="n"/>
+      <c r="D361" s="15" t="n"/>
+      <c r="E361" s="15" t="n"/>
+      <c r="F361" s="21" t="n"/>
+      <c r="G361" s="21" t="n"/>
+      <c r="H361" s="15" t="n"/>
+      <c r="I361" s="15" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="15" t="n"/>
+      <c r="B362" s="15" t="n"/>
+      <c r="C362" s="15" t="n"/>
+      <c r="D362" s="15" t="n"/>
+      <c r="E362" s="15" t="n"/>
+      <c r="F362" s="21" t="n"/>
+      <c r="G362" s="21" t="n"/>
+      <c r="H362" s="15" t="n"/>
+      <c r="I362" s="15" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="15" t="n"/>
+      <c r="B363" s="15" t="n"/>
+      <c r="C363" s="15" t="n"/>
+      <c r="D363" s="15" t="n"/>
+      <c r="E363" s="15" t="n"/>
+      <c r="F363" s="21" t="n"/>
+      <c r="G363" s="21" t="n"/>
+      <c r="H363" s="15" t="n"/>
+      <c r="I363" s="15" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="15" t="n"/>
+      <c r="B364" s="15" t="n"/>
+      <c r="C364" s="15" t="n"/>
+      <c r="D364" s="15" t="n"/>
+      <c r="E364" s="15" t="n"/>
+      <c r="F364" s="21" t="n"/>
+      <c r="G364" s="21" t="n"/>
+      <c r="H364" s="15" t="n"/>
+      <c r="I364" s="15" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="15" t="n"/>
+      <c r="B365" s="15" t="n"/>
+      <c r="C365" s="15" t="n"/>
+      <c r="D365" s="15" t="n"/>
+      <c r="E365" s="15" t="n"/>
+      <c r="F365" s="21" t="n"/>
+      <c r="G365" s="21" t="n"/>
+      <c r="H365" s="15" t="n"/>
+      <c r="I365" s="15" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="n"/>
+      <c r="B366" s="15" t="n"/>
+      <c r="C366" s="15" t="n"/>
+      <c r="D366" s="15" t="n"/>
+      <c r="E366" s="15" t="n"/>
+      <c r="F366" s="21" t="n"/>
+      <c r="G366" s="21" t="n"/>
+      <c r="H366" s="15" t="n"/>
+      <c r="I366" s="15" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="15" t="n"/>
+      <c r="B367" s="15" t="n"/>
+      <c r="C367" s="15" t="n"/>
+      <c r="D367" s="15" t="n"/>
+      <c r="E367" s="15" t="n"/>
+      <c r="F367" s="21" t="n"/>
+      <c r="G367" s="21" t="n"/>
+      <c r="H367" s="15" t="n"/>
+      <c r="I367" s="15" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="15" t="n"/>
+      <c r="B368" s="15" t="n"/>
+      <c r="C368" s="15" t="n"/>
+      <c r="D368" s="15" t="n"/>
+      <c r="E368" s="15" t="n"/>
+      <c r="F368" s="21" t="n"/>
+      <c r="G368" s="21" t="n"/>
+      <c r="H368" s="15" t="n"/>
+      <c r="I368" s="15" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="15" t="n"/>
+      <c r="B369" s="15" t="n"/>
+      <c r="C369" s="15" t="n"/>
+      <c r="D369" s="15" t="n"/>
+      <c r="E369" s="15" t="n"/>
+      <c r="F369" s="21" t="n"/>
+      <c r="G369" s="21" t="n"/>
+      <c r="H369" s="15" t="n"/>
+      <c r="I369" s="15" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="15" t="n"/>
+      <c r="B370" s="15" t="n"/>
+      <c r="C370" s="15" t="n"/>
+      <c r="D370" s="15" t="n"/>
+      <c r="E370" s="15" t="n"/>
+      <c r="F370" s="21" t="n"/>
+      <c r="G370" s="21" t="n"/>
+      <c r="H370" s="15" t="n"/>
+      <c r="I370" s="15" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="15" t="n"/>
+      <c r="B371" s="15" t="n"/>
+      <c r="C371" s="15" t="n"/>
+      <c r="D371" s="15" t="n"/>
+      <c r="E371" s="15" t="n"/>
+      <c r="F371" s="21" t="n"/>
+      <c r="G371" s="21" t="n"/>
+      <c r="H371" s="15" t="n"/>
+      <c r="I371" s="15" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="n"/>
+      <c r="B372" s="15" t="n"/>
+      <c r="C372" s="15" t="n"/>
+      <c r="D372" s="15" t="n"/>
+      <c r="E372" s="15" t="n"/>
+      <c r="F372" s="21" t="n"/>
+      <c r="G372" s="21" t="n"/>
+      <c r="H372" s="15" t="n"/>
+      <c r="I372" s="15" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="15" t="n"/>
+      <c r="B373" s="15" t="n"/>
+      <c r="C373" s="15" t="n"/>
+      <c r="D373" s="15" t="n"/>
+      <c r="E373" s="15" t="n"/>
+      <c r="F373" s="21" t="n"/>
+      <c r="G373" s="21" t="n"/>
+      <c r="H373" s="15" t="n"/>
+      <c r="I373" s="15" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="15" t="n"/>
+      <c r="B374" s="15" t="n"/>
+      <c r="C374" s="15" t="n"/>
+      <c r="D374" s="15" t="n"/>
+      <c r="E374" s="15" t="n"/>
+      <c r="F374" s="21" t="n"/>
+      <c r="G374" s="21" t="n"/>
+      <c r="H374" s="15" t="n"/>
+      <c r="I374" s="15" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="15" t="n"/>
+      <c r="B375" s="15" t="n"/>
+      <c r="C375" s="15" t="n"/>
+      <c r="D375" s="15" t="n"/>
+      <c r="E375" s="15" t="n"/>
+      <c r="F375" s="21" t="n"/>
+      <c r="G375" s="21" t="n"/>
+      <c r="H375" s="15" t="n"/>
+      <c r="I375" s="15" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="15" t="n"/>
+      <c r="B376" s="15" t="n"/>
+      <c r="C376" s="15" t="n"/>
+      <c r="D376" s="15" t="n"/>
+      <c r="E376" s="15" t="n"/>
+      <c r="F376" s="21" t="n"/>
+      <c r="G376" s="21" t="n"/>
+      <c r="H376" s="15" t="n"/>
+      <c r="I376" s="15" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="15" t="n"/>
+      <c r="B377" s="15" t="n"/>
+      <c r="C377" s="15" t="n"/>
+      <c r="D377" s="15" t="n"/>
+      <c r="E377" s="15" t="n"/>
+      <c r="F377" s="21" t="n"/>
+      <c r="G377" s="21" t="n"/>
+      <c r="H377" s="15" t="n"/>
+      <c r="I377" s="15" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="15" t="n"/>
+      <c r="B378" s="15" t="n"/>
+      <c r="C378" s="15" t="n"/>
+      <c r="D378" s="15" t="n"/>
+      <c r="E378" s="15" t="n"/>
+      <c r="F378" s="21" t="n"/>
+      <c r="G378" s="21" t="n"/>
+      <c r="H378" s="15" t="n"/>
+      <c r="I378" s="15" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="n"/>
+      <c r="B379" s="15" t="n"/>
+      <c r="C379" s="15" t="n"/>
+      <c r="D379" s="15" t="n"/>
+      <c r="E379" s="15" t="n"/>
+      <c r="F379" s="21" t="n"/>
+      <c r="G379" s="21" t="n"/>
+      <c r="H379" s="15" t="n"/>
+      <c r="I379" s="15" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="15" t="n"/>
+      <c r="B380" s="15" t="n"/>
+      <c r="C380" s="15" t="n"/>
+      <c r="D380" s="15" t="n"/>
+      <c r="E380" s="15" t="n"/>
+      <c r="F380" s="21" t="n"/>
+      <c r="G380" s="21" t="n"/>
+      <c r="H380" s="15" t="n"/>
+      <c r="I380" s="15" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="n"/>
+      <c r="B381" s="15" t="n"/>
+      <c r="C381" s="15" t="n"/>
+      <c r="D381" s="15" t="n"/>
+      <c r="E381" s="15" t="n"/>
+      <c r="F381" s="21" t="n"/>
+      <c r="G381" s="21" t="n"/>
+      <c r="H381" s="15" t="n"/>
+      <c r="I381" s="15" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="15" t="n"/>
+      <c r="B382" s="15" t="n"/>
+      <c r="C382" s="15" t="n"/>
+      <c r="D382" s="15" t="n"/>
+      <c r="E382" s="15" t="n"/>
+      <c r="F382" s="21" t="n"/>
+      <c r="G382" s="21" t="n"/>
+      <c r="H382" s="15" t="n"/>
+      <c r="I382" s="15" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="15" t="n"/>
+      <c r="B383" s="15" t="n"/>
+      <c r="C383" s="15" t="n"/>
+      <c r="D383" s="15" t="n"/>
+      <c r="E383" s="15" t="n"/>
+      <c r="F383" s="21" t="n"/>
+      <c r="G383" s="21" t="n"/>
+      <c r="H383" s="15" t="n"/>
+      <c r="I383" s="15" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="15" t="n"/>
+      <c r="B384" s="15" t="n"/>
+      <c r="C384" s="15" t="n"/>
+      <c r="D384" s="15" t="n"/>
+      <c r="E384" s="15" t="n"/>
+      <c r="F384" s="21" t="n"/>
+      <c r="G384" s="21" t="n"/>
+      <c r="H384" s="15" t="n"/>
+      <c r="I384" s="15" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="15" t="n"/>
+      <c r="B385" s="15" t="n"/>
+      <c r="C385" s="15" t="n"/>
+      <c r="D385" s="15" t="n"/>
+      <c r="E385" s="15" t="n"/>
+      <c r="F385" s="21" t="n"/>
+      <c r="G385" s="21" t="n"/>
+      <c r="H385" s="15" t="n"/>
+      <c r="I385" s="15" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="15" t="n"/>
+      <c r="B386" s="15" t="n"/>
+      <c r="C386" s="15" t="n"/>
+      <c r="D386" s="15" t="n"/>
+      <c r="E386" s="15" t="n"/>
+      <c r="F386" s="21" t="n"/>
+      <c r="G386" s="21" t="n"/>
+      <c r="H386" s="15" t="n"/>
+      <c r="I386" s="15" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="15" t="n"/>
+      <c r="B387" s="15" t="n"/>
+      <c r="C387" s="15" t="n"/>
+      <c r="D387" s="15" t="n"/>
+      <c r="E387" s="15" t="n"/>
+      <c r="F387" s="21" t="n"/>
+      <c r="G387" s="21" t="n"/>
+      <c r="H387" s="15" t="n"/>
+      <c r="I387" s="15" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="15" t="n"/>
+      <c r="B388" s="15" t="n"/>
+      <c r="C388" s="15" t="n"/>
+      <c r="D388" s="15" t="n"/>
+      <c r="E388" s="15" t="n"/>
+      <c r="F388" s="21" t="n"/>
+      <c r="G388" s="21" t="n"/>
+      <c r="H388" s="15" t="n"/>
+      <c r="I388" s="15" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="15" t="n"/>
+      <c r="B389" s="15" t="n"/>
+      <c r="C389" s="15" t="n"/>
+      <c r="D389" s="15" t="n"/>
+      <c r="E389" s="15" t="n"/>
+      <c r="F389" s="21" t="n"/>
+      <c r="G389" s="21" t="n"/>
+      <c r="H389" s="15" t="n"/>
+      <c r="I389" s="15" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="15" t="n"/>
+      <c r="B390" s="15" t="n"/>
+      <c r="C390" s="15" t="n"/>
+      <c r="D390" s="15" t="n"/>
+      <c r="E390" s="15" t="n"/>
+      <c r="F390" s="21" t="n"/>
+      <c r="G390" s="21" t="n"/>
+      <c r="H390" s="15" t="n"/>
+      <c r="I390" s="15" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="15" t="n"/>
+      <c r="B391" s="15" t="n"/>
+      <c r="C391" s="15" t="n"/>
+      <c r="D391" s="15" t="n"/>
+      <c r="E391" s="15" t="n"/>
+      <c r="F391" s="21" t="n"/>
+      <c r="G391" s="21" t="n"/>
+      <c r="H391" s="15" t="n"/>
+      <c r="I391" s="15" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="n"/>
+      <c r="B392" s="15" t="n"/>
+      <c r="C392" s="15" t="n"/>
+      <c r="D392" s="15" t="n"/>
+      <c r="E392" s="15" t="n"/>
+      <c r="F392" s="21" t="n"/>
+      <c r="G392" s="21" t="n"/>
+      <c r="H392" s="15" t="n"/>
+      <c r="I392" s="15" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="15" t="n"/>
+      <c r="B393" s="15" t="n"/>
+      <c r="C393" s="15" t="n"/>
+      <c r="D393" s="15" t="n"/>
+      <c r="E393" s="15" t="n"/>
+      <c r="F393" s="21" t="n"/>
+      <c r="G393" s="21" t="n"/>
+      <c r="H393" s="15" t="n"/>
+      <c r="I393" s="15" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="15" t="n"/>
+      <c r="B394" s="15" t="n"/>
+      <c r="C394" s="15" t="n"/>
+      <c r="D394" s="15" t="n"/>
+      <c r="E394" s="15" t="n"/>
+      <c r="F394" s="21" t="n"/>
+      <c r="G394" s="21" t="n"/>
+      <c r="H394" s="15" t="n"/>
+      <c r="I394" s="15" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="15" t="n"/>
+      <c r="B395" s="15" t="n"/>
+      <c r="C395" s="15" t="n"/>
+      <c r="D395" s="15" t="n"/>
+      <c r="E395" s="15" t="n"/>
+      <c r="F395" s="21" t="n"/>
+      <c r="G395" s="21" t="n"/>
+      <c r="H395" s="15" t="n"/>
+      <c r="I395" s="15" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="15" t="n"/>
+      <c r="B396" s="15" t="n"/>
+      <c r="C396" s="15" t="n"/>
+      <c r="D396" s="15" t="n"/>
+      <c r="E396" s="15" t="n"/>
+      <c r="F396" s="21" t="n"/>
+      <c r="G396" s="21" t="n"/>
+      <c r="H396" s="15" t="n"/>
+      <c r="I396" s="15" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="15" t="n"/>
+      <c r="B397" s="15" t="n"/>
+      <c r="C397" s="15" t="n"/>
+      <c r="D397" s="15" t="n"/>
+      <c r="E397" s="15" t="n"/>
+      <c r="F397" s="21" t="n"/>
+      <c r="G397" s="21" t="n"/>
+      <c r="H397" s="15" t="n"/>
+      <c r="I397" s="15" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="15" t="n"/>
+      <c r="B398" s="15" t="n"/>
+      <c r="C398" s="15" t="n"/>
+      <c r="D398" s="15" t="n"/>
+      <c r="E398" s="15" t="n"/>
+      <c r="F398" s="21" t="n"/>
+      <c r="G398" s="21" t="n"/>
+      <c r="H398" s="15" t="n"/>
+      <c r="I398" s="15" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="15" t="n"/>
+      <c r="B399" s="15" t="n"/>
+      <c r="C399" s="15" t="n"/>
+      <c r="D399" s="15" t="n"/>
+      <c r="E399" s="15" t="n"/>
+      <c r="F399" s="21" t="n"/>
+      <c r="G399" s="21" t="n"/>
+      <c r="H399" s="15" t="n"/>
+      <c r="I399" s="15" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="15" t="n"/>
+      <c r="B400" s="15" t="n"/>
+      <c r="C400" s="15" t="n"/>
+      <c r="D400" s="15" t="n"/>
+      <c r="E400" s="15" t="n"/>
+      <c r="F400" s="21" t="n"/>
+      <c r="G400" s="21" t="n"/>
+      <c r="H400" s="15" t="n"/>
+      <c r="I400" s="15" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="inlineStr">
+        <is>
+          <t>One row per card pulled. Several rows can share a Video ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t>Hall of Fame = Yes marks the all-time best, which get their own page.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>='Video Log'!$A$2:$A$311</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$A$2:$A$26</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$C$2:$C$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -838,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -847,7 +847,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Alolan Exeggutor ex</t>
+          <t>AZ's Tranquility</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Altaria ex</t>
+          <t>Abra</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Articuno</t>
+          <t>Accelgor</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Basic Darkness Energy</t>
+          <t>Acerola's Mischief</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Blastoise ex</t>
+          <t>Aegislash</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Bloodmoon Ursaluna ex</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Bulbasaur</t>
+          <t>Alakazam ex</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Carmine</t>
+          <t>Alolan Exeggutor ex</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Cassiopeia</t>
+          <t>Alomomola</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Chandelure</t>
+          <t>Altaria ex</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Amarys</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Charizard ex</t>
+          <t>Amoonguss</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Charmander</t>
+          <t>Applin</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Arbok</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Cynthia's Garchomp ex</t>
+          <t>Arcanine ex</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Dachsbun ex</t>
+          <t>Archaludon ex</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Archen</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Ditto</t>
+          <t>Archeops</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Dragonite V</t>
+          <t>Arctibax</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Dragonite VSTAR</t>
+          <t>Armarouge</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Drowzee</t>
+          <t>Articuno</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Durant ex</t>
+          <t>Arven</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1703,14 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Arven's Mabosstiff ex</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Multiple sets</t>
+          <t>Abyss Eye (JP)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1720,783 +1720,3424 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Audino</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>Battle Partners (KR)</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Prismatic Evolutions Mini Tin</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Axew</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Clay Burst (KR)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Prismatic Evolutions Poster Collection</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Banette</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Crimson Haze (KR)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Prismatic Evolutions Tech Sticker Collection</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Basculin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Cyber Judge (JP)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Basic Darkness Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Gem Pack Vol. 2 (CN)</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Basic Grass Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Mask of Change (KR)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Basic Metal Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Mega Brave (JP)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Basic Water Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Mega Symphonia (JP)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Baxcalibur</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Nihil Zero (JP)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Beartic</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Ninja Spinner (JP)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Bewear</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Stellar Miracle (JP)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Bianca's Devotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Violet ex (JP)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Bisharp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Multiple sets</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Blastoise ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t>Not a set (sealed/other)</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Prismatic Evolutions Mini Tin</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Eevee</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Prismatic Evolutions Poster Collection</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Espeon ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Prismatic Evolutions Tech Sticker Collection</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Ethan's Ho-Oh ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Fezandipiti ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Fidough</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Flareon ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Fuecoco</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Galvantula ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Garchomp ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Gardevoir ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Gastly</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Gengar ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Glaceon ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Gloom</t>
+          <t>Blaziken</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Gouging Fire ex</t>
+          <t>Blitzle</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Greninja ex</t>
+          <t>Bloodmoon Ursaluna ex</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Groudon</t>
+          <t>Boss's Orders</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Haxorus</t>
+          <t>Bouffalant ex</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Hop's Zacian ex</t>
+          <t>Bramblin</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Horsea</t>
+          <t>Braviary</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Houndoom</t>
+          <t>Briar</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Hydrapple ex</t>
+          <t>Brute Bonnet</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Hydreigon ex</t>
+          <t>Buddy-Buddy Poffin</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Iono</t>
+          <t>Bulbasaur</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Iono's Bellibolt ex</t>
+          <t>Canari</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Iron Crown ex</t>
+          <t>Carmine</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Jolteon ex</t>
+          <t>Carracosta</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Keldeo ex</t>
+          <t>Cassiopeia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Caterpie</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Kyurem ex</t>
+          <t>Ceruledge</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Lacey</t>
+          <t>Ceruledge ex</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Lana's Aid</t>
+          <t>Chandelure</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Latias ex</t>
+          <t>Chansey</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Latios</t>
+          <t>Charizard ex</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Leafeon ex</t>
+          <t>Charmander</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Lillie's Clefairy ex</t>
+          <t>Charmeleon</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Lillie's Determination</t>
+          <t>Chatot</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Chi-Yu ex</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Maushold</t>
+          <t>Chien-Pao ex</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Mega Absol ex</t>
+          <t>Cinccino</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Mega Charizard X ex</t>
+          <t>Cinccino ex</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>Mega Gardevoir ex</t>
+          <t>Clefairy</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Mega Latias ex</t>
+          <t>Cleffa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Mega Lopunny ex</t>
+          <t>Clive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Mega Lucario ex</t>
+          <t>Cobalion</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Mega Sharpedo ex</t>
+          <t>Cofagrigus</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
+          <t>Conkeldurr</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Melmetal VMAX</t>
+          <t>Cornerstone Mask Ogerpon ex</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>Meowth</t>
+          <t>Cottonee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>Mew ex</t>
+          <t>Cresselia</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Mewtwo V</t>
+          <t>Crispin</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Mewtwo VSTAR</t>
+          <t>Crocalor</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>Milcery</t>
+          <t>Cubchoo</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>Milotic ex</t>
+          <t>Cufant</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Mimikyu</t>
+          <t>Cynthia's Garchomp ex</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>Minun</t>
+          <t>Cynthia's Roserade</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Misty's Psyduck</t>
+          <t>Cynthia's Spiritomb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>Morpeko</t>
+          <t>Dachsbun</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>Morty's Conviction</t>
+          <t>Dachsbun ex</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>N's Plan</t>
+          <t>Darmanitan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>N's Reshiram</t>
+          <t>Darumaka</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>N's Zoroark ex</t>
+          <t>Dawn</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Dedenne ex</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Deerling</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>Perrin</t>
+          <t>Deino</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Dendra</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>Pidgeot ex</t>
+          <t>Dewott</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Dipplin</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Pikachu ex</t>
+          <t>Ditto</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Plusle</t>
+          <t>Dondozo</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Radiant Blastoise</t>
+          <t>Dragapult ex</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Radiant Charizard</t>
+          <t>Dragonair</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Raging Bolt ex</t>
+          <t>Dragonite V</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Raichu</t>
+          <t>Dragonite VSTAR</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Drampa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Reshiram ex</t>
+          <t>Drayton</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>Riolu</t>
+          <t>Drowzee</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Roaring Moon ex</t>
+          <t>Druddigon</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Rotom ex</t>
+          <t>Ducklett</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Salamence ex</t>
+          <t>Dudunsparce</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Sawsbuck</t>
+          <t>Duosion</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Scizor</t>
+          <t>Durant</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Seismitoad</t>
+          <t>Durant ex</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Sinistcha ex</t>
+          <t>Dusclops</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Slowpoke</t>
+          <t>Dusknoir</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Snorlax</t>
+          <t>Duskull</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Sprigatito</t>
+          <t>Dwebble</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Squirtle</t>
+          <t>Earthen Vessel</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Eelektrik</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Sylveon ex</t>
+          <t>Eelektross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Team Rocket's Crobat ex</t>
+          <t>Eevee</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Team Rocket's Mewtwo ex</t>
+          <t>Eevee ex</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Team Rocket's Moltres ex</t>
+          <t>Eiscue</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Team Rocket's Nidoking ex</t>
+          <t>Elgyem</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Terapagos ex</t>
+          <t>Emboar</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Tinkaton ex</t>
+          <t>Emolga</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Tyranitar</t>
+          <t>Entei</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Umbreon ex</t>
+          <t>Eri</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Vaporeon ex</t>
+          <t>Erika's Invitation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Venusaur ex</t>
+          <t>Erika's Tangela</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Victini</t>
+          <t>Escavalier</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Volcanion ex</t>
+          <t>Espeon ex</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Volcarona</t>
+          <t>Ethan's Adventure</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Walking Wake ex</t>
+          <t>Ethan's Ho-Oh ex</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Wiglett</t>
+          <t>Ethan's Typhlosion</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Zapdos ex</t>
+          <t>Excadrill</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Zekrom ex</t>
+          <t>Excadrill ex</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="G133" s="7" t="inlineStr">
         <is>
+          <t>Farigiraf</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Feebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Ferrothorn</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Fezandipiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>Fezandipiti ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>Fidough</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Flamigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>Flareon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Fletchinder</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>Floragato</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Foongus</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>Fraxure</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>Frigibax</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Frillish</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Froakie</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>Fuecoco</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Galvantula</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Galvantula ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>Garbodor</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>Garchomp ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Gardevoir ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>Gastly</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Genesect ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>Gengar ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>Gholdengo ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Gigalith</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Gimmighoul</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>Giovanni's Charisma</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Glaceon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>Gladion's Final Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>Gloom</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>Golett</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Golisopod ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>Golurk</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>Gothita</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Gothorita</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Gouging Fire ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>Gravity Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>Great Tusk ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Greavard</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>Greninja ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>Grotle</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Groudon</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>Grusha</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Gulpin</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Gurdurr</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Gwynn</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>Haxorus</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Hearthflame Mask Ogerpon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>Heracross</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>Herdier</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Hero's Cape</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Hilda</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Hisuian Growlithe</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Hop's Zacian ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Horsea</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>Houndoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Houndour</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Hydrapple ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Hydreigon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>Infernape</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Iono</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Iono's Bellibolt ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>Iris's Fighting Spirit</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Iron Boulder ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>Iron Crown ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>Iron Hands ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>Iron Jugulis</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>Iron Leaves ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>Iron Valiant ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>Ivysaur</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>Jacinthe</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>Janine's Secret Art</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>Jasmine's Gaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>Jellicent ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>Jigglypuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>Jolteon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>Joltik</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>Kangaskhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>Karrablast</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>Keldeo ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>Kieran</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>Kingambit</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>Kirlia</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>Klinklang</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>Koraidon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>Krokorok</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>Krookodile</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>Kyurem ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>Lacey</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>Lampent</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>Lana's Aid</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>Landorus</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>Larvesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>Latias ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>Latios</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>Leafeon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>Leavanny</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>Lechonk</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>Lickitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>Liepard</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>Lillie's Clefairy ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>Lillie's Determination</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>Lilligant</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>Lillipup</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>Lisia's Appeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>Litten</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>Litwick</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="G241" s="7" t="inlineStr">
+        <is>
+          <t>Loudred</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>Lt. Surge's Bargain</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="G243" s="7" t="inlineStr">
+        <is>
+          <t>Lucario</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>Luxray</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>Machoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>Magby</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>Magikarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>Mandibuzz</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>Mantyke</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="G250" s="7" t="inlineStr">
+        <is>
+          <t>Marill</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>Marnie's Grimmsnarl ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>Marshadow</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>Maushold</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>Maushold ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>Mega Absol ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="G256" s="7" t="inlineStr">
+        <is>
+          <t>Mega Chandelure ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="G257" s="7" t="inlineStr">
+        <is>
+          <t>Mega Charizard X ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>Mega Charizard Y ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>Mega Clefable ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>Mega Darkrai ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="G261" s="7" t="inlineStr">
+        <is>
+          <t>Mega Diancie ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="G262" s="7" t="inlineStr">
+        <is>
+          <t>Mega Dragalge ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="G263" s="7" t="inlineStr">
+        <is>
+          <t>Mega Dragonite ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="G264" s="7" t="inlineStr">
+        <is>
+          <t>Mega Eelektross ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="G265" s="7" t="inlineStr">
+        <is>
+          <t>Mega Emboar ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="G266" s="7" t="inlineStr">
+        <is>
+          <t>Mega Excadrill ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="G267" s="7" t="inlineStr">
+        <is>
+          <t>Mega Feraligatr ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="G268" s="7" t="inlineStr">
+        <is>
+          <t>Mega Floette ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="G269" s="7" t="inlineStr">
+        <is>
+          <t>Mega Froslass ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="G270" s="7" t="inlineStr">
+        <is>
+          <t>Mega Gardevoir ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="G271" s="7" t="inlineStr">
+        <is>
+          <t>Mega Gengar ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="G272" s="7" t="inlineStr">
+        <is>
+          <t>Mega Greninja ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="G273" s="7" t="inlineStr">
+        <is>
+          <t>Mega Hawlucha ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="G274" s="7" t="inlineStr">
+        <is>
+          <t>Mega Kangaskhan ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="G275" s="7" t="inlineStr">
+        <is>
+          <t>Mega Latias ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="G276" s="7" t="inlineStr">
+        <is>
+          <t>Mega Lopunny ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="G277" s="7" t="inlineStr">
+        <is>
+          <t>Mega Lucario ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="G278" s="7" t="inlineStr">
+        <is>
+          <t>Mega Meganium ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="G279" s="7" t="inlineStr">
+        <is>
+          <t>Mega Scrafty ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="G280" s="7" t="inlineStr">
+        <is>
+          <t>Mega Sharpedo ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="G281" s="7" t="inlineStr">
+        <is>
+          <t>Mega Starmie ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="G282" s="7" t="inlineStr">
+        <is>
+          <t>Mega Venusaur ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="G283" s="7" t="inlineStr">
+        <is>
+          <t>Mega Zeraora ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="G284" s="7" t="inlineStr">
+        <is>
+          <t>Mega Zygarde ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="G285" s="7" t="inlineStr">
+        <is>
+          <t>Melmetal VMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="G286" s="7" t="inlineStr">
+        <is>
+          <t>Meloetta ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="G287" s="7" t="inlineStr">
+        <is>
+          <t>Meowscarada ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="G288" s="7" t="inlineStr">
+        <is>
+          <t>Meowth</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="G289" s="7" t="inlineStr">
+        <is>
+          <t>Meowth ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="G290" s="7" t="inlineStr">
+        <is>
+          <t>Mesprit</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="G291" s="7" t="inlineStr">
+        <is>
+          <t>Metagross</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="G292" s="7" t="inlineStr">
+        <is>
+          <t>Mew ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="G293" s="7" t="inlineStr">
+        <is>
+          <t>Mewtwo V</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="G294" s="7" t="inlineStr">
+        <is>
+          <t>Mewtwo VSTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="G295" s="7" t="inlineStr">
+        <is>
+          <t>Mienfoo</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="G296" s="7" t="inlineStr">
+        <is>
+          <t>Mienshao</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="G297" s="7" t="inlineStr">
+        <is>
+          <t>Milcery</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="G298" s="7" t="inlineStr">
+        <is>
+          <t>Milotic ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="G299" s="7" t="inlineStr">
+        <is>
+          <t>Mimikyu</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="G300" s="7" t="inlineStr">
+        <is>
+          <t>Minccino</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="G301" s="7" t="inlineStr">
+        <is>
+          <t>Minior</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="G302" s="7" t="inlineStr">
+        <is>
+          <t>Minun</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="G303" s="7" t="inlineStr">
+        <is>
+          <t>Miraidon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="G304" s="7" t="inlineStr">
+        <is>
+          <t>Miriam</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="G305" s="7" t="inlineStr">
+        <is>
+          <t>Mismagius</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="G306" s="7" t="inlineStr">
+        <is>
+          <t>Misty's Lapras</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="G307" s="7" t="inlineStr">
+        <is>
+          <t>Misty's Psyduck</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="G308" s="7" t="inlineStr">
+        <is>
+          <t>Misty's Vitality</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="G309" s="7" t="inlineStr">
+        <is>
+          <t>Morpeko</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="G310" s="7" t="inlineStr">
+        <is>
+          <t>Morpeko ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="G311" s="7" t="inlineStr">
+        <is>
+          <t>Morty's Conviction</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="G312" s="7" t="inlineStr">
+        <is>
+          <t>Mr. Mime</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="G313" s="7" t="inlineStr">
+        <is>
+          <t>Mudsdale</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="G314" s="7" t="inlineStr">
+        <is>
+          <t>Munkidori</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="G315" s="7" t="inlineStr">
+        <is>
+          <t>Munkidori ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="G316" s="7" t="inlineStr">
+        <is>
+          <t>Munna</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="G317" s="7" t="inlineStr">
+        <is>
+          <t>Musharna</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="G318" s="7" t="inlineStr">
+        <is>
+          <t>N's Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="G319" s="7" t="inlineStr">
+        <is>
+          <t>N's Reshiram</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="G320" s="7" t="inlineStr">
+        <is>
+          <t>N's Zoroark ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="G321" s="7" t="inlineStr">
+        <is>
+          <t>Neo Upper Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="G322" s="7" t="inlineStr">
+        <is>
+          <t>Nidoking</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="G323" s="7" t="inlineStr">
+        <is>
+          <t>Ninetales</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="G324" s="7" t="inlineStr">
+        <is>
+          <t>Ninetales ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="G325" s="7" t="inlineStr">
+        <is>
+          <t>Oddish</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="G326" s="7" t="inlineStr">
+        <is>
+          <t>Okidogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="G327" s="7" t="inlineStr">
+        <is>
+          <t>Okidogi ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="G328" s="7" t="inlineStr">
+        <is>
+          <t>Omanyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="G329" s="7" t="inlineStr">
+        <is>
+          <t>Oshawott</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="G330" s="7" t="inlineStr">
+        <is>
+          <t>Pachirisu</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="G331" s="7" t="inlineStr">
+        <is>
+          <t>Palafin ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="G332" s="7" t="inlineStr">
+        <is>
+          <t>Paldean Tauros</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="G333" s="7" t="inlineStr">
+        <is>
+          <t>Paldean Wooper</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="G334" s="7" t="inlineStr">
+        <is>
+          <t>Palpitoad</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="G335" s="7" t="inlineStr">
+        <is>
+          <t>Panpour</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t>Pansage</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="G337" s="7" t="inlineStr">
+        <is>
+          <t>Pansear</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="G338" s="7" t="inlineStr">
+        <is>
+          <t>Parasol Lady</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="G339" s="7" t="inlineStr">
+        <is>
+          <t>Patrat</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="G340" s="7" t="inlineStr">
+        <is>
+          <t>Pawmot</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="G341" s="7" t="inlineStr">
+        <is>
+          <t>Pecharunt ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="G342" s="7" t="inlineStr">
+        <is>
+          <t>Penny</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="G343" s="7" t="inlineStr">
+        <is>
+          <t>Perrin</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="G344" s="7" t="inlineStr">
+        <is>
+          <t>Persian</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="G345" s="7" t="inlineStr">
+        <is>
+          <t>Petilil</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="G346" s="7" t="inlineStr">
+        <is>
+          <t>Phione</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="G347" s="7" t="inlineStr">
+        <is>
+          <t>Pidgeot ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="G348" s="7" t="inlineStr">
+        <is>
+          <t>Pidgeotto</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="G349" s="7" t="inlineStr">
+        <is>
+          <t>Pidgey</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="G350" s="7" t="inlineStr">
+        <is>
+          <t>Pidove</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="G351" s="7" t="inlineStr">
+        <is>
+          <t>Pignite</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="G352" s="7" t="inlineStr">
+        <is>
+          <t>Pikachu</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="G353" s="7" t="inlineStr">
+        <is>
+          <t>Pikachu ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="G354" s="7" t="inlineStr">
+        <is>
+          <t>Pinsir</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="G355" s="7" t="inlineStr">
+        <is>
+          <t>Piplup</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="G356" s="7" t="inlineStr">
+        <is>
+          <t>Plusle</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="G357" s="7" t="inlineStr">
+        <is>
+          <t>Poké Pad</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="G358" s="7" t="inlineStr">
+        <is>
+          <t>Poliwhirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="G359" s="7" t="inlineStr">
+        <is>
+          <t>Porygon-Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="G360" s="7" t="inlineStr">
+        <is>
+          <t>Powerglass</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="G361" s="7" t="inlineStr">
+        <is>
+          <t>Psyduck</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="G362" s="7" t="inlineStr">
+        <is>
+          <t>Purrloin</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="G363" s="7" t="inlineStr">
+        <is>
+          <t>Pyroar</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="G364" s="7" t="inlineStr">
+        <is>
+          <t>Quaquaval ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="G365" s="7" t="inlineStr">
+        <is>
+          <t>Quaxly</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="G366" s="7" t="inlineStr">
+        <is>
+          <t>Quaxwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="G367" s="7" t="inlineStr">
+        <is>
+          <t>Radiant Blastoise</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="G368" s="7" t="inlineStr">
+        <is>
+          <t>Radiant Charizard</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="G369" s="7" t="inlineStr">
+        <is>
+          <t>Raging Bolt ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="G370" s="7" t="inlineStr">
+        <is>
+          <t>Raichu</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="G371" s="7" t="inlineStr">
+        <is>
+          <t>Ralts</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="G372" s="7" t="inlineStr">
+        <is>
+          <t>Relicanth</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="G373" s="7" t="inlineStr">
+        <is>
+          <t>Reshiram ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="G374" s="7" t="inlineStr">
+        <is>
+          <t>Reuniclus</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="G375" s="7" t="inlineStr">
+        <is>
+          <t>Riolu</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="G376" s="7" t="inlineStr">
+        <is>
+          <t>Roaring Moon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="G377" s="7" t="inlineStr">
+        <is>
+          <t>Roggenrola</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="G378" s="7" t="inlineStr">
+        <is>
+          <t>Rookidee</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="G379" s="7" t="inlineStr">
+        <is>
+          <t>Rosa's Encouragement</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="G380" s="7" t="inlineStr">
+        <is>
+          <t>Rotom ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="G381" s="7" t="inlineStr">
+        <is>
+          <t>Roxie's Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="G382" s="7" t="inlineStr">
+        <is>
+          <t>Saguaro</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="G383" s="7" t="inlineStr">
+        <is>
+          <t>Salamence ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="G384" s="7" t="inlineStr">
+        <is>
+          <t>Salvatore</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="G385" s="7" t="inlineStr">
+        <is>
+          <t>Samurott</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="G386" s="7" t="inlineStr">
+        <is>
+          <t>Sandile</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="G387" s="7" t="inlineStr">
+        <is>
+          <t>Sandy Shocks ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="G388" s="7" t="inlineStr">
+        <is>
+          <t>Sandygast</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="G389" s="7" t="inlineStr">
+        <is>
+          <t>Sawk</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="G390" s="7" t="inlineStr">
+        <is>
+          <t>Sawsbuck</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="G391" s="7" t="inlineStr">
+        <is>
+          <t>Scizor</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="G392" s="7" t="inlineStr">
+        <is>
+          <t>Scolipede</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="G393" s="7" t="inlineStr">
+        <is>
+          <t>Scrafty</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="G394" s="7" t="inlineStr">
+        <is>
+          <t>Scraggy</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="G395" s="7" t="inlineStr">
+        <is>
+          <t>Scyther</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="G396" s="7" t="inlineStr">
+        <is>
+          <t>Seismitoad</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="G397" s="7" t="inlineStr">
+        <is>
+          <t>Serperior ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="G398" s="7" t="inlineStr">
+        <is>
+          <t>Servine</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="G399" s="7" t="inlineStr">
+        <is>
+          <t>Sewaddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="G400" s="7" t="inlineStr">
+        <is>
+          <t>Shaymin</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="G401" s="7" t="inlineStr">
+        <is>
+          <t>Shiftry</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="G402" s="7" t="inlineStr">
+        <is>
+          <t>Shinx</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="G403" s="7" t="inlineStr">
+        <is>
+          <t>Sigilyph</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="G404" s="7" t="inlineStr">
+        <is>
+          <t>Simipour</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="G405" s="7" t="inlineStr">
+        <is>
+          <t>Simisage</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="G406" s="7" t="inlineStr">
+        <is>
+          <t>Simisear</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="G407" s="7" t="inlineStr">
+        <is>
+          <t>Sinistcha ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="G408" s="7" t="inlineStr">
+        <is>
+          <t>Skarmory</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="G409" s="7" t="inlineStr">
+        <is>
+          <t>Skeledirge ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="G410" s="7" t="inlineStr">
+        <is>
+          <t>Slakoth</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="G411" s="7" t="inlineStr">
+        <is>
+          <t>Slowbro</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="G412" s="7" t="inlineStr">
+        <is>
+          <t>Slowpoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="G413" s="7" t="inlineStr">
+        <is>
+          <t>Snivy</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="G414" s="7" t="inlineStr">
+        <is>
+          <t>Snom</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="G415" s="7" t="inlineStr">
+        <is>
+          <t>Snorlax</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="G416" s="7" t="inlineStr">
+        <is>
+          <t>Snorunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="G417" s="7" t="inlineStr">
+        <is>
+          <t>Solosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="G418" s="7" t="inlineStr">
+        <is>
+          <t>Spheal</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="G419" s="7" t="inlineStr">
+        <is>
+          <t>Sprigatito</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="G420" s="7" t="inlineStr">
+        <is>
+          <t>Squawkabilly ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="G421" s="7" t="inlineStr">
+        <is>
+          <t>Squirtle</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="G422" s="7" t="inlineStr">
+        <is>
+          <t>Starly</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="G423" s="7" t="inlineStr">
+        <is>
+          <t>Steelix</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="G424" s="7" t="inlineStr">
+        <is>
+          <t>Steven's Metagross ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="G425" s="7" t="inlineStr">
+        <is>
+          <t>Stoutland</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="G426" s="7" t="inlineStr">
+        <is>
+          <t>Sudowoodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="G427" s="7" t="inlineStr">
+        <is>
+          <t>Surfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="G428" s="7" t="inlineStr">
+        <is>
+          <t>Swablu</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="G429" s="7" t="inlineStr">
+        <is>
+          <t>Swadloon</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="G430" s="7" t="inlineStr">
+        <is>
+          <t>Swanna</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="G431" s="7" t="inlineStr">
+        <is>
+          <t>Swoobat</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="G432" s="7" t="inlineStr">
+        <is>
+          <t>Sylveon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="G433" s="7" t="inlineStr">
+        <is>
+          <t>Tandemaus</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="G434" s="7" t="inlineStr">
+        <is>
+          <t>Tangela</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="G435" s="7" t="inlineStr">
+        <is>
+          <t>Tapu Bulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="G436" s="7" t="inlineStr">
+        <is>
+          <t>Tapu Koko ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="G437" s="7" t="inlineStr">
+        <is>
+          <t>Tarountula</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="G438" s="7" t="inlineStr">
+        <is>
+          <t>Tatsugiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="G439" s="7" t="inlineStr">
+        <is>
+          <t>Teal Mask Ogerpon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="G440" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Ariana</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="G441" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Crobat ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="G442" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Giovanni</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="G443" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Houndoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="G444" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Meowth</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="G445" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Mewtwo ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="G446" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Mimikyu</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="G447" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Moltres ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="G448" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Nidoking ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="G449" s="7" t="inlineStr">
+        <is>
+          <t>Team Rocket's Petrel</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="G450" s="7" t="inlineStr">
+        <is>
+          <t>Tepig</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="G451" s="7" t="inlineStr">
+        <is>
+          <t>Terapagos ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="G452" s="7" t="inlineStr">
+        <is>
+          <t>Terrakion</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="G453" s="7" t="inlineStr">
+        <is>
+          <t>Throh</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="G454" s="7" t="inlineStr">
+        <is>
+          <t>Timburr</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="G455" s="7" t="inlineStr">
+        <is>
+          <t>Ting-Lu ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="G456" s="7" t="inlineStr">
+        <is>
+          <t>Tinkatink</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="G457" s="7" t="inlineStr">
+        <is>
+          <t>Tinkaton</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="G458" s="7" t="inlineStr">
+        <is>
+          <t>Tinkaton ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="G459" s="7" t="inlineStr">
+        <is>
+          <t>Tinkatuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="G460" s="7" t="inlineStr">
+        <is>
+          <t>Tirtouga</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="G461" s="7" t="inlineStr">
+        <is>
+          <t>Tropius</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="G462" s="7" t="inlineStr">
+        <is>
+          <t>Trubbish</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="G463" s="7" t="inlineStr">
+        <is>
+          <t>Tympole</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="G464" s="7" t="inlineStr">
+        <is>
+          <t>Tynamo</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="G465" s="7" t="inlineStr">
+        <is>
+          <t>Tyranitar</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="G466" s="7" t="inlineStr">
+        <is>
+          <t>Umbreon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="G467" s="7" t="inlineStr">
+        <is>
+          <t>Unfair Stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="G468" s="7" t="inlineStr">
+        <is>
+          <t>Unfezant</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="G469" s="7" t="inlineStr">
+        <is>
+          <t>Vanillish</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="G470" s="7" t="inlineStr">
+        <is>
+          <t>Vanillite</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="G471" s="7" t="inlineStr">
+        <is>
+          <t>Vanilluxe</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="G472" s="7" t="inlineStr">
+        <is>
+          <t>Vaporeon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="G473" s="7" t="inlineStr">
+        <is>
+          <t>Veluza</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="G474" s="7" t="inlineStr">
+        <is>
+          <t>Venusaur ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="G475" s="7" t="inlineStr">
+        <is>
+          <t>Victini</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="G476" s="7" t="inlineStr">
+        <is>
+          <t>Virizion</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="G477" s="7" t="inlineStr">
+        <is>
+          <t>Volcanion ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="G478" s="7" t="inlineStr">
+        <is>
+          <t>Volcarona</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="G479" s="7" t="inlineStr">
+        <is>
+          <t>Vullaby</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="G480" s="7" t="inlineStr">
+        <is>
+          <t>Vulpix</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="G481" s="7" t="inlineStr">
+        <is>
+          <t>Wailord</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="G482" s="7" t="inlineStr">
+        <is>
+          <t>Walking Wake ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="G483" s="7" t="inlineStr">
+        <is>
+          <t>Wally's Compassion</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="G484" s="7" t="inlineStr">
+        <is>
+          <t>Wartortle</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="G485" s="7" t="inlineStr">
+        <is>
+          <t>Watchog</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="G486" s="7" t="inlineStr">
+        <is>
+          <t>Wellspring Mask Ogerpon ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="G487" s="7" t="inlineStr">
+        <is>
+          <t>Whimsicott ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="G488" s="7" t="inlineStr">
+        <is>
+          <t>Wiglett</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="G489" s="7" t="inlineStr">
+        <is>
+          <t>Wimpod</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="G490" s="7" t="inlineStr">
+        <is>
+          <t>Wo-Chien ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="G491" s="7" t="inlineStr">
+        <is>
+          <t>Woobat</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="G492" s="7" t="inlineStr">
+        <is>
+          <t>Yamask</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="G493" s="7" t="inlineStr">
+        <is>
+          <t>Yanmega ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="G494" s="7" t="inlineStr">
+        <is>
+          <t>Yveltal</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="G495" s="7" t="inlineStr">
+        <is>
+          <t>Zapdos ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="G496" s="7" t="inlineStr">
+        <is>
+          <t>Zebstrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="G497" s="7" t="inlineStr">
+        <is>
+          <t>Zekrom ex</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="G498" s="7" t="inlineStr">
+        <is>
+          <t>Zeraora</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="G499" s="7" t="inlineStr">
+        <is>
           <t>Zoroark</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="G500" s="7" t="inlineStr">
+        <is>
+          <t>Zorua</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="G501" s="7" t="inlineStr">
+        <is>
+          <t>Zweilous</t>
         </is>
       </c>
     </row>
@@ -2691,7 +5332,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>430</v>
+        <v>593</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -2750,7 +5391,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -2811,7 +5452,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
@@ -2870,7 +5511,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -5413,7 +8054,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
@@ -8451,14 +11092,24 @@
         <f>HYPERLINK("https://youtu.be/tuX1t8p29Ik","watch")</f>
         <v/>
       </c>
-      <c r="G97" s="15" t="n"/>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>Abyss Eye (JP)</t>
+        </is>
+      </c>
       <c r="H97" s="15" t="n"/>
       <c r="I97" s="15" t="n"/>
       <c r="J97" s="15" t="n"/>
       <c r="K97" s="15" t="n"/>
       <c r="L97" s="15" t="n"/>
-      <c r="M97" s="15" t="n"/>
-      <c r="N97" s="15" t="n"/>
+      <c r="M97" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N97" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O97" s="15" t="n"/>
       <c r="P97" s="15" t="n"/>
       <c r="Q97" s="15" t="n"/>
@@ -8742,14 +11393,24 @@
         <f>HYPERLINK("https://youtu.be/XjM6y2L7v1c","watch")</f>
         <v/>
       </c>
-      <c r="G102" s="15" t="n"/>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>Abyss Eye (JP)</t>
+        </is>
+      </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="15" t="n"/>
       <c r="J102" s="15" t="n"/>
       <c r="K102" s="15" t="n"/>
       <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="n"/>
-      <c r="N102" s="15" t="n"/>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N102" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O102" s="15" t="n"/>
       <c r="P102" s="15" t="n"/>
       <c r="Q102" s="15" t="n"/>
@@ -8791,14 +11452,24 @@
         <f>HYPERLINK("https://youtu.be/0vpWimyqJIE","watch")</f>
         <v/>
       </c>
-      <c r="G103" s="15" t="n"/>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>Abyss Eye (JP)</t>
+        </is>
+      </c>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="15" t="n"/>
       <c r="J103" s="15" t="n"/>
       <c r="K103" s="15" t="n"/>
       <c r="L103" s="15" t="n"/>
-      <c r="M103" s="15" t="n"/>
-      <c r="N103" s="15" t="n"/>
+      <c r="M103" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N103" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O103" s="15" t="n"/>
       <c r="P103" s="15" t="n"/>
       <c r="Q103" s="15" t="n"/>
@@ -9064,14 +11735,24 @@
         <f>HYPERLINK("https://youtu.be/EKTgIGCiET4","watch")</f>
         <v/>
       </c>
-      <c r="G108" s="15" t="n"/>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>Abyss Eye (JP)</t>
+        </is>
+      </c>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="15" t="n"/>
       <c r="J108" s="15" t="n"/>
       <c r="K108" s="15" t="n"/>
       <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
-      <c r="N108" s="15" t="n"/>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N108" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O108" s="15" t="n"/>
       <c r="P108" s="15" t="n"/>
       <c r="Q108" s="15" t="n"/>
@@ -9113,7 +11794,11 @@
         <f>HYPERLINK("https://youtu.be/-eQ-tG_cj_0","watch")</f>
         <v/>
       </c>
-      <c r="G109" s="15" t="n"/>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>Abyss Eye (JP)</t>
+        </is>
+      </c>
       <c r="H109" s="15" t="n"/>
       <c r="I109" s="15" t="n"/>
       <c r="J109" s="15" t="n"/>
@@ -11639,14 +14324,24 @@
         <f>HYPERLINK("https://youtu.be/yJujjKbIVFg","watch")</f>
         <v/>
       </c>
-      <c r="G151" s="15" t="n"/>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>Stellar Miracle (JP)</t>
+        </is>
+      </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="15" t="n"/>
       <c r="J151" s="15" t="n"/>
       <c r="K151" s="15" t="n"/>
       <c r="L151" s="15" t="n"/>
-      <c r="M151" s="15" t="n"/>
-      <c r="N151" s="15" t="n"/>
+      <c r="M151" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N151" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O151" s="15" t="n"/>
       <c r="P151" s="15" t="n"/>
       <c r="Q151" s="15" t="n"/>
@@ -12066,14 +14761,24 @@
         <f>HYPERLINK("https://youtu.be/auKzs0g2LL8","watch")</f>
         <v/>
       </c>
-      <c r="G158" s="15" t="n"/>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>Mega Symphonia (JP)</t>
+        </is>
+      </c>
       <c r="H158" s="15" t="n"/>
       <c r="I158" s="15" t="n"/>
       <c r="J158" s="15" t="n"/>
       <c r="K158" s="15" t="n"/>
       <c r="L158" s="15" t="n"/>
-      <c r="M158" s="15" t="n"/>
-      <c r="N158" s="15" t="n"/>
+      <c r="M158" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N158" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O158" s="15" t="n"/>
       <c r="P158" s="15" t="n"/>
       <c r="Q158" s="15" t="n"/>
@@ -12426,14 +15131,24 @@
         <f>HYPERLINK("https://youtu.be/bh8OGK_jE2Y","watch")</f>
         <v/>
       </c>
-      <c r="G164" s="15" t="n"/>
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t>Stellar Miracle (JP)</t>
+        </is>
+      </c>
       <c r="H164" s="15" t="n"/>
       <c r="I164" s="15" t="n"/>
       <c r="J164" s="15" t="n"/>
       <c r="K164" s="15" t="n"/>
       <c r="L164" s="15" t="n"/>
-      <c r="M164" s="15" t="n"/>
-      <c r="N164" s="15" t="n"/>
+      <c r="M164" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N164" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O164" s="15" t="n"/>
       <c r="P164" s="15" t="n"/>
       <c r="Q164" s="15" t="n"/>
@@ -12660,14 +15375,24 @@
         <f>HYPERLINK("https://youtu.be/OMpbKBu38rk","watch")</f>
         <v/>
       </c>
-      <c r="G168" s="15" t="n"/>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>Mega Symphonia (JP)</t>
+        </is>
+      </c>
       <c r="H168" s="15" t="n"/>
       <c r="I168" s="15" t="n"/>
       <c r="J168" s="15" t="n"/>
       <c r="K168" s="15" t="n"/>
       <c r="L168" s="15" t="n"/>
-      <c r="M168" s="15" t="n"/>
-      <c r="N168" s="15" t="n"/>
+      <c r="M168" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N168" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O168" s="15" t="n"/>
       <c r="P168" s="15" t="n"/>
       <c r="Q168" s="15" t="n"/>
@@ -14230,14 +16955,24 @@
         <f>HYPERLINK("https://youtu.be/EPqUqzrAc30","watch")</f>
         <v/>
       </c>
-      <c r="G194" s="15" t="n"/>
+      <c r="G194" s="14" t="inlineStr">
+        <is>
+          <t>Nihil Zero (JP)</t>
+        </is>
+      </c>
       <c r="H194" s="15" t="n"/>
       <c r="I194" s="15" t="n"/>
       <c r="J194" s="15" t="n"/>
       <c r="K194" s="15" t="n"/>
       <c r="L194" s="15" t="n"/>
-      <c r="M194" s="15" t="n"/>
-      <c r="N194" s="15" t="n"/>
+      <c r="M194" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N194" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O194" s="15" t="n"/>
       <c r="P194" s="15" t="n"/>
       <c r="Q194" s="15" t="n"/>
@@ -14745,8 +17480,14 @@
       <c r="J203" s="15" t="n"/>
       <c r="K203" s="15" t="n"/>
       <c r="L203" s="15" t="n"/>
-      <c r="M203" s="15" t="n"/>
-      <c r="N203" s="15" t="n"/>
+      <c r="M203" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="N203" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O203" s="15" t="n"/>
       <c r="P203" s="15" t="n"/>
       <c r="Q203" s="15" t="n"/>
@@ -14898,14 +17639,24 @@
         <f>HYPERLINK("https://youtu.be/NzWUDxXwnPI","watch")</f>
         <v/>
       </c>
-      <c r="G206" s="15" t="n"/>
+      <c r="G206" s="14" t="inlineStr">
+        <is>
+          <t>Nihil Zero (JP)</t>
+        </is>
+      </c>
       <c r="H206" s="15" t="n"/>
       <c r="I206" s="15" t="n"/>
       <c r="J206" s="15" t="n"/>
       <c r="K206" s="15" t="n"/>
       <c r="L206" s="15" t="n"/>
-      <c r="M206" s="15" t="n"/>
-      <c r="N206" s="15" t="n"/>
+      <c r="M206" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N206" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O206" s="15" t="n"/>
       <c r="P206" s="15" t="n"/>
       <c r="Q206" s="15" t="n"/>
@@ -15586,14 +18337,24 @@
         <f>HYPERLINK("https://youtu.be/K5RKQlNhvl8","watch")</f>
         <v/>
       </c>
-      <c r="G218" s="15" t="n"/>
+      <c r="G218" s="14" t="inlineStr">
+        <is>
+          <t>Mega Brave (JP)</t>
+        </is>
+      </c>
       <c r="H218" s="15" t="n"/>
       <c r="I218" s="15" t="n"/>
       <c r="J218" s="15" t="n"/>
       <c r="K218" s="15" t="n"/>
       <c r="L218" s="15" t="n"/>
-      <c r="M218" s="15" t="n"/>
-      <c r="N218" s="15" t="n"/>
+      <c r="M218" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N218" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O218" s="15" t="n"/>
       <c r="P218" s="15" t="n"/>
       <c r="Q218" s="15" t="n"/>
@@ -16569,8 +19330,14 @@
       <c r="J235" s="15" t="n"/>
       <c r="K235" s="15" t="n"/>
       <c r="L235" s="15" t="n"/>
-      <c r="M235" s="15" t="n"/>
-      <c r="N235" s="15" t="n"/>
+      <c r="M235" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="N235" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O235" s="15" t="n"/>
       <c r="P235" s="15" t="n"/>
       <c r="Q235" s="15" t="n"/>
@@ -16899,14 +19666,24 @@
         <f>HYPERLINK("https://youtu.be/N3bs0HjmrKY","watch")</f>
         <v/>
       </c>
-      <c r="G241" s="15" t="n"/>
+      <c r="G241" s="14" t="inlineStr">
+        <is>
+          <t>Stellar Miracle (JP)</t>
+        </is>
+      </c>
       <c r="H241" s="15" t="n"/>
       <c r="I241" s="15" t="n"/>
       <c r="J241" s="15" t="n"/>
       <c r="K241" s="15" t="n"/>
       <c r="L241" s="15" t="n"/>
-      <c r="M241" s="15" t="n"/>
-      <c r="N241" s="15" t="n"/>
+      <c r="M241" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N241" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O241" s="15" t="n"/>
       <c r="P241" s="15" t="n"/>
       <c r="Q241" s="15" t="n"/>
@@ -17241,14 +20018,24 @@
         <f>HYPERLINK("https://youtu.be/_ccErXVzURs","watch")</f>
         <v/>
       </c>
-      <c r="G247" s="15" t="n"/>
+      <c r="G247" s="14" t="inlineStr">
+        <is>
+          <t>Ninja Spinner (JP)</t>
+        </is>
+      </c>
       <c r="H247" s="15" t="n"/>
       <c r="I247" s="15" t="n"/>
       <c r="J247" s="15" t="n"/>
       <c r="K247" s="15" t="n"/>
       <c r="L247" s="15" t="n"/>
-      <c r="M247" s="15" t="n"/>
-      <c r="N247" s="15" t="n"/>
+      <c r="M247" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N247" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O247" s="15" t="n"/>
       <c r="P247" s="15" t="n"/>
       <c r="Q247" s="15" t="n"/>
@@ -17408,7 +20195,11 @@
         <f>HYPERLINK("https://youtu.be/PnbibBm1E64","watch")</f>
         <v/>
       </c>
-      <c r="G250" s="15" t="n"/>
+      <c r="G250" s="14" t="inlineStr">
+        <is>
+          <t>Clay Burst (KR)</t>
+        </is>
+      </c>
       <c r="H250" s="15" t="n"/>
       <c r="I250" s="15" t="n"/>
       <c r="J250" s="15" t="n"/>
@@ -18963,7 +21754,11 @@
         <f>HYPERLINK("https://youtu.be/pof6Ph34E6w","watch")</f>
         <v/>
       </c>
-      <c r="G277" s="15" t="n"/>
+      <c r="G277" s="14" t="inlineStr">
+        <is>
+          <t>Battle Partners (KR)</t>
+        </is>
+      </c>
       <c r="H277" s="15" t="n"/>
       <c r="I277" s="15" t="n"/>
       <c r="J277" s="15" t="n"/>
@@ -19077,7 +21872,11 @@
         <f>HYPERLINK("https://youtu.be/mbzWBfNI-Qs","watch")</f>
         <v/>
       </c>
-      <c r="G279" s="15" t="n"/>
+      <c r="G279" s="14" t="inlineStr">
+        <is>
+          <t>Crimson Haze (KR)</t>
+        </is>
+      </c>
       <c r="H279" s="15" t="n"/>
       <c r="I279" s="15" t="n"/>
       <c r="J279" s="15" t="n"/>
@@ -19321,8 +22120,14 @@
       <c r="J283" s="15" t="n"/>
       <c r="K283" s="15" t="n"/>
       <c r="L283" s="15" t="n"/>
-      <c r="M283" s="15" t="n"/>
-      <c r="N283" s="15" t="n"/>
+      <c r="M283" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="N283" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O283" s="15" t="n"/>
       <c r="P283" s="15" t="n"/>
       <c r="Q283" s="15" t="n"/>
@@ -19429,8 +22234,14 @@
       <c r="J285" s="15" t="n"/>
       <c r="K285" s="15" t="n"/>
       <c r="L285" s="15" t="n"/>
-      <c r="M285" s="15" t="n"/>
-      <c r="N285" s="15" t="n"/>
+      <c r="M285" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="N285" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O285" s="15" t="n"/>
       <c r="P285" s="15" t="n"/>
       <c r="Q285" s="15" t="n"/>
@@ -20011,8 +22822,14 @@
       <c r="J295" s="15" t="n"/>
       <c r="K295" s="15" t="n"/>
       <c r="L295" s="15" t="n"/>
-      <c r="M295" s="15" t="n"/>
-      <c r="N295" s="15" t="n"/>
+      <c r="M295" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="N295" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O295" s="15" t="n"/>
       <c r="P295" s="15" t="n"/>
       <c r="Q295" s="15" t="n"/>
@@ -20054,7 +22871,11 @@
         <f>HYPERLINK("https://youtu.be/QADrkuqf9pg","watch")</f>
         <v/>
       </c>
-      <c r="G296" s="15" t="n"/>
+      <c r="G296" s="14" t="inlineStr">
+        <is>
+          <t>Mask of Change (KR)</t>
+        </is>
+      </c>
       <c r="H296" s="15" t="n"/>
       <c r="I296" s="15" t="n"/>
       <c r="J296" s="15" t="n"/>
@@ -20114,7 +22935,11 @@
           <t>Scarlet &amp; Violet</t>
         </is>
       </c>
-      <c r="H297" s="15" t="n"/>
+      <c r="H297" s="14" t="inlineStr">
+        <is>
+          <t>Violet ex (JP)</t>
+        </is>
+      </c>
       <c r="I297" s="15" t="n"/>
       <c r="J297" s="15" t="n"/>
       <c r="K297" s="15" t="n"/>
@@ -20168,7 +22993,11 @@
         <f>HYPERLINK("https://youtu.be/8jKHh-P7P7M","watch")</f>
         <v/>
       </c>
-      <c r="G298" s="15" t="n"/>
+      <c r="G298" s="14" t="inlineStr">
+        <is>
+          <t>Gem Pack Vol. 2 (CN)</t>
+        </is>
+      </c>
       <c r="H298" s="15" t="n"/>
       <c r="I298" s="15" t="n"/>
       <c r="J298" s="15" t="n"/>
@@ -20467,14 +23296,24 @@
         <f>HYPERLINK("https://youtu.be/-1fhlQB1okI","watch")</f>
         <v/>
       </c>
-      <c r="G303" s="15" t="n"/>
+      <c r="G303" s="14" t="inlineStr">
+        <is>
+          <t>Cyber Judge (JP)</t>
+        </is>
+      </c>
       <c r="H303" s="15" t="n"/>
       <c r="I303" s="15" t="n"/>
       <c r="J303" s="15" t="n"/>
       <c r="K303" s="15" t="n"/>
       <c r="L303" s="15" t="n"/>
-      <c r="M303" s="15" t="n"/>
-      <c r="N303" s="15" t="n"/>
+      <c r="M303" s="14" t="inlineStr">
+        <is>
+          <t>Japanese Booster Pack</t>
+        </is>
+      </c>
+      <c r="N303" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="O303" s="15" t="n"/>
       <c r="P303" s="15" t="n"/>
       <c r="Q303" s="15" t="n"/>
@@ -20931,7 +23770,7 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation sqref="G2:G311 H2:H311 I2:I311 J2:J311" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$26</formula1>
+      <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M311" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$17</formula1>
@@ -20952,7 +23791,7 @@
       <formula1>=Lists!$F$2:$F$28</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$G$2:$G$133</formula1>
+      <formula1>=Lists!$G$2:$G$501</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21923,7 +24762,7 @@
         </is>
       </c>
       <c r="F2" s="19" t="n">
-        <v>716.8</v>
+        <v>715.98</v>
       </c>
       <c r="G2" s="20" t="n"/>
       <c r="H2" s="15" t="n"/>
@@ -21973,7 +24812,7 @@
         </is>
       </c>
       <c r="F3" s="19" t="n">
-        <v>312.08</v>
+        <v>309.71</v>
       </c>
       <c r="G3" s="20" t="n"/>
       <c r="H3" s="15" t="n"/>
@@ -22011,7 +24850,7 @@
         </is>
       </c>
       <c r="F4" s="19" t="n">
-        <v>28.61</v>
+        <v>29.21</v>
       </c>
       <c r="G4" s="20" t="n"/>
       <c r="H4" s="15" t="n"/>
@@ -22049,7 +24888,7 @@
         </is>
       </c>
       <c r="F5" s="19" t="n">
-        <v>23.35</v>
+        <v>22.66</v>
       </c>
       <c r="G5" s="20" t="n"/>
       <c r="H5" s="15" t="n"/>
@@ -22087,7 +24926,7 @@
         </is>
       </c>
       <c r="F6" s="19" t="n">
-        <v>20.85</v>
+        <v>21.11</v>
       </c>
       <c r="G6" s="20" t="n"/>
       <c r="H6" s="15" t="n"/>
@@ -22125,7 +24964,7 @@
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>20.3</v>
+        <v>20.06</v>
       </c>
       <c r="G7" s="20" t="n"/>
       <c r="H7" s="15" t="n"/>
@@ -22163,7 +25002,7 @@
         </is>
       </c>
       <c r="F8" s="19" t="n">
-        <v>19.17</v>
+        <v>18.87</v>
       </c>
       <c r="G8" s="20" t="n"/>
       <c r="H8" s="15" t="n"/>
@@ -22239,7 +25078,7 @@
         </is>
       </c>
       <c r="F10" s="19" t="n">
-        <v>271.92</v>
+        <v>271.82</v>
       </c>
       <c r="G10" s="20" t="n"/>
       <c r="H10" s="15" t="n"/>
@@ -22365,7 +25204,7 @@
         </is>
       </c>
       <c r="F13" s="19" t="n">
-        <v>195.22</v>
+        <v>194.46</v>
       </c>
       <c r="G13" s="20" t="n"/>
       <c r="H13" s="15" t="n"/>
@@ -22403,7 +25242,7 @@
         </is>
       </c>
       <c r="F14" s="19" t="n">
-        <v>156.64</v>
+        <v>156.39</v>
       </c>
       <c r="G14" s="20" t="n"/>
       <c r="H14" s="15" t="n"/>
@@ -22441,7 +25280,7 @@
         </is>
       </c>
       <c r="F15" s="19" t="n">
-        <v>86.98999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G15" s="20" t="n"/>
       <c r="H15" s="15" t="n"/>
@@ -22479,7 +25318,7 @@
         </is>
       </c>
       <c r="F16" s="19" t="n">
-        <v>65.43000000000001</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="G16" s="20" t="n"/>
       <c r="H16" s="15" t="n"/>
@@ -22517,7 +25356,7 @@
         </is>
       </c>
       <c r="F17" s="19" t="n">
-        <v>60.63</v>
+        <v>59.86</v>
       </c>
       <c r="G17" s="20" t="n"/>
       <c r="H17" s="15" t="n"/>
@@ -22693,7 +25532,7 @@
         </is>
       </c>
       <c r="F21" s="19" t="n">
-        <v>93.95999999999999</v>
+        <v>93.84</v>
       </c>
       <c r="G21" s="20" t="n"/>
       <c r="H21" s="15" t="n"/>
@@ -22807,7 +25646,7 @@
         </is>
       </c>
       <c r="F24" s="19" t="n">
-        <v>75.84</v>
+        <v>76.16</v>
       </c>
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="15" t="n"/>
@@ -22845,7 +25684,7 @@
         </is>
       </c>
       <c r="F25" s="19" t="n">
-        <v>72.54000000000001</v>
+        <v>72.34</v>
       </c>
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="15" t="n"/>
@@ -22883,7 +25722,7 @@
         </is>
       </c>
       <c r="F26" s="19" t="n">
-        <v>607.2</v>
+        <v>602</v>
       </c>
       <c r="G26" s="20" t="n"/>
       <c r="H26" s="15" t="n"/>
@@ -22959,7 +25798,7 @@
         </is>
       </c>
       <c r="F28" s="19" t="n">
-        <v>288.09</v>
+        <v>287.93</v>
       </c>
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="15" t="n"/>
@@ -22997,7 +25836,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>235.67</v>
+        <v>235.15</v>
       </c>
       <c r="G29" s="20" t="n"/>
       <c r="H29" s="15" t="n"/>
@@ -23047,7 +25886,7 @@
         </is>
       </c>
       <c r="F30" s="19" t="n">
-        <v>80.84</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="G30" s="20" t="n"/>
       <c r="H30" s="15" t="n"/>
@@ -23085,7 +25924,7 @@
         </is>
       </c>
       <c r="F31" s="19" t="n">
-        <v>75.39</v>
+        <v>75.31</v>
       </c>
       <c r="G31" s="20" t="n"/>
       <c r="H31" s="15" t="n"/>
@@ -23123,7 +25962,7 @@
         </is>
       </c>
       <c r="F32" s="19" t="n">
-        <v>72.17</v>
+        <v>72.11</v>
       </c>
       <c r="G32" s="20" t="n"/>
       <c r="H32" s="15" t="n"/>
@@ -23199,7 +26038,7 @@
         </is>
       </c>
       <c r="F34" s="19" t="n">
-        <v>514.15</v>
+        <v>508.18</v>
       </c>
       <c r="G34" s="20" t="n"/>
       <c r="H34" s="15" t="n"/>
@@ -23249,7 +26088,7 @@
         </is>
       </c>
       <c r="F35" s="19" t="n">
-        <v>252.88</v>
+        <v>249.57</v>
       </c>
       <c r="G35" s="20" t="n"/>
       <c r="H35" s="15" t="n"/>
@@ -23287,7 +26126,7 @@
         </is>
       </c>
       <c r="F36" s="19" t="n">
-        <v>168.52</v>
+        <v>168.15</v>
       </c>
       <c r="G36" s="20" t="n"/>
       <c r="H36" s="15" t="n"/>
@@ -23325,7 +26164,7 @@
         </is>
       </c>
       <c r="F37" s="19" t="n">
-        <v>107.15</v>
+        <v>106.83</v>
       </c>
       <c r="G37" s="20" t="n"/>
       <c r="H37" s="15" t="n"/>
@@ -23363,7 +26202,7 @@
         </is>
       </c>
       <c r="F38" s="19" t="n">
-        <v>105.93</v>
+        <v>105.2</v>
       </c>
       <c r="G38" s="20" t="n"/>
       <c r="H38" s="15" t="n"/>
@@ -23401,7 +26240,7 @@
         </is>
       </c>
       <c r="F39" s="19" t="n">
-        <v>67.81</v>
+        <v>66.97</v>
       </c>
       <c r="G39" s="20" t="n"/>
       <c r="H39" s="15" t="n"/>
@@ -23439,7 +26278,7 @@
         </is>
       </c>
       <c r="F40" s="19" t="n">
-        <v>66.55</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G40" s="20" t="n"/>
       <c r="H40" s="15" t="n"/>
@@ -23477,7 +26316,7 @@
         </is>
       </c>
       <c r="F41" s="19" t="n">
-        <v>61.66</v>
+        <v>61.27</v>
       </c>
       <c r="G41" s="20" t="n"/>
       <c r="H41" s="15" t="n"/>
@@ -23515,7 +26354,7 @@
         </is>
       </c>
       <c r="F42" s="19" t="n">
-        <v>111.31</v>
+        <v>111.35</v>
       </c>
       <c r="G42" s="20" t="n"/>
       <c r="H42" s="15" t="n"/>
@@ -23553,7 +26392,7 @@
         </is>
       </c>
       <c r="F43" s="19" t="n">
-        <v>59</v>
+        <v>59.47</v>
       </c>
       <c r="G43" s="20" t="n"/>
       <c r="H43" s="15" t="n"/>
@@ -23591,7 +26430,7 @@
         </is>
       </c>
       <c r="F44" s="19" t="n">
-        <v>48.89</v>
+        <v>48.48</v>
       </c>
       <c r="G44" s="20" t="n"/>
       <c r="H44" s="15" t="n"/>
@@ -23629,7 +26468,7 @@
         </is>
       </c>
       <c r="F45" s="19" t="n">
-        <v>40.7</v>
+        <v>40.66</v>
       </c>
       <c r="G45" s="20" t="n"/>
       <c r="H45" s="15" t="n"/>
@@ -23667,7 +26506,7 @@
         </is>
       </c>
       <c r="F46" s="19" t="n">
-        <v>35.03</v>
+        <v>34.86</v>
       </c>
       <c r="G46" s="20" t="n"/>
       <c r="H46" s="15" t="n"/>
@@ -23705,7 +26544,7 @@
         </is>
       </c>
       <c r="F47" s="19" t="n">
-        <v>20.93</v>
+        <v>21.35</v>
       </c>
       <c r="G47" s="20" t="n"/>
       <c r="H47" s="15" t="n"/>
@@ -23743,7 +26582,7 @@
         </is>
       </c>
       <c r="F48" s="19" t="n">
-        <v>20.69</v>
+        <v>17.96</v>
       </c>
       <c r="G48" s="20" t="n"/>
       <c r="H48" s="15" t="n"/>
@@ -23781,7 +26620,7 @@
         </is>
       </c>
       <c r="F49" s="19" t="n">
-        <v>20.31</v>
+        <v>20.06</v>
       </c>
       <c r="G49" s="20" t="n"/>
       <c r="H49" s="15" t="n"/>
@@ -23819,7 +26658,7 @@
         </is>
       </c>
       <c r="F50" s="19" t="n">
-        <v>1480.32</v>
+        <v>1470.58</v>
       </c>
       <c r="G50" s="20" t="n"/>
       <c r="H50" s="15" t="n"/>
@@ -23857,7 +26696,7 @@
         </is>
       </c>
       <c r="F51" s="19" t="n">
-        <v>520.04</v>
+        <v>518.08</v>
       </c>
       <c r="G51" s="20" t="n"/>
       <c r="H51" s="15" t="n"/>
@@ -23971,7 +26810,7 @@
         </is>
       </c>
       <c r="F54" s="19" t="n">
-        <v>300.88</v>
+        <v>300.38</v>
       </c>
       <c r="G54" s="20" t="n"/>
       <c r="H54" s="15" t="n"/>
@@ -24047,7 +26886,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>226.64</v>
+        <v>225.44</v>
       </c>
       <c r="G56" s="20" t="n"/>
       <c r="H56" s="15" t="n"/>
@@ -24085,7 +26924,7 @@
         </is>
       </c>
       <c r="F57" s="19" t="n">
-        <v>203.33</v>
+        <v>203.18</v>
       </c>
       <c r="G57" s="20" t="n"/>
       <c r="H57" s="15" t="n"/>
@@ -24123,7 +26962,7 @@
         </is>
       </c>
       <c r="F58" s="19" t="n">
-        <v>295.8</v>
+        <v>296.13</v>
       </c>
       <c r="G58" s="20" t="n"/>
       <c r="H58" s="15" t="n"/>
@@ -24161,7 +27000,7 @@
         </is>
       </c>
       <c r="F59" s="19" t="n">
-        <v>173.76</v>
+        <v>175.38</v>
       </c>
       <c r="G59" s="20" t="n"/>
       <c r="H59" s="15" t="n"/>
@@ -24199,7 +27038,7 @@
         </is>
       </c>
       <c r="F60" s="19" t="n">
-        <v>129.22</v>
+        <v>129.21</v>
       </c>
       <c r="G60" s="20" t="n"/>
       <c r="H60" s="15" t="n"/>
@@ -24237,7 +27076,7 @@
         </is>
       </c>
       <c r="F61" s="19" t="n">
-        <v>97.28</v>
+        <v>97.14</v>
       </c>
       <c r="G61" s="20" t="n"/>
       <c r="H61" s="15" t="n"/>
@@ -24275,7 +27114,7 @@
         </is>
       </c>
       <c r="F62" s="19" t="n">
-        <v>36.36</v>
+        <v>36.59</v>
       </c>
       <c r="G62" s="20" t="n"/>
       <c r="H62" s="15" t="n"/>
@@ -24313,7 +27152,7 @@
         </is>
       </c>
       <c r="F63" s="19" t="n">
-        <v>36.32</v>
+        <v>36.55</v>
       </c>
       <c r="G63" s="20" t="n"/>
       <c r="H63" s="15" t="n"/>
@@ -24351,7 +27190,7 @@
         </is>
       </c>
       <c r="F64" s="19" t="n">
-        <v>34</v>
+        <v>34.32</v>
       </c>
       <c r="G64" s="20" t="n"/>
       <c r="H64" s="15" t="n"/>
@@ -24389,7 +27228,7 @@
         </is>
       </c>
       <c r="F65" s="19" t="n">
-        <v>32.77</v>
+        <v>32.81</v>
       </c>
       <c r="G65" s="20" t="n"/>
       <c r="H65" s="15" t="n"/>
@@ -24427,7 +27266,7 @@
         </is>
       </c>
       <c r="F66" s="19" t="n">
-        <v>118.79</v>
+        <v>118.81</v>
       </c>
       <c r="G66" s="20" t="n"/>
       <c r="H66" s="15" t="n"/>
@@ -24465,7 +27304,7 @@
         </is>
       </c>
       <c r="F67" s="19" t="n">
-        <v>104.89</v>
+        <v>105.26</v>
       </c>
       <c r="G67" s="20" t="n"/>
       <c r="H67" s="15" t="n"/>
@@ -24503,7 +27342,7 @@
         </is>
       </c>
       <c r="F68" s="19" t="n">
-        <v>64.59999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="G68" s="20" t="n"/>
       <c r="H68" s="15" t="n"/>
@@ -24541,7 +27380,7 @@
         </is>
       </c>
       <c r="F69" s="19" t="n">
-        <v>39.29</v>
+        <v>39.27</v>
       </c>
       <c r="G69" s="20" t="n"/>
       <c r="H69" s="15" t="n"/>
@@ -24579,7 +27418,7 @@
         </is>
       </c>
       <c r="F70" s="19" t="n">
-        <v>38</v>
+        <v>38.07</v>
       </c>
       <c r="G70" s="20" t="n"/>
       <c r="H70" s="15" t="n"/>
@@ -24655,7 +27494,7 @@
         </is>
       </c>
       <c r="F72" s="19" t="n">
-        <v>19.54</v>
+        <v>19.41</v>
       </c>
       <c r="G72" s="20" t="n"/>
       <c r="H72" s="15" t="n"/>
@@ -24693,7 +27532,7 @@
         </is>
       </c>
       <c r="F73" s="19" t="n">
-        <v>17.4</v>
+        <v>17.21</v>
       </c>
       <c r="G73" s="20" t="n"/>
       <c r="H73" s="15" t="n"/>
@@ -24731,7 +27570,7 @@
         </is>
       </c>
       <c r="F74" s="19" t="n">
-        <v>72.94</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="G74" s="20" t="n"/>
       <c r="H74" s="15" t="n"/>
@@ -24769,7 +27608,7 @@
         </is>
       </c>
       <c r="F75" s="19" t="n">
-        <v>62.94</v>
+        <v>62.9</v>
       </c>
       <c r="G75" s="20" t="n"/>
       <c r="H75" s="15" t="n"/>
@@ -24807,7 +27646,7 @@
         </is>
       </c>
       <c r="F76" s="19" t="n">
-        <v>58.14</v>
+        <v>56.99</v>
       </c>
       <c r="G76" s="20" t="n"/>
       <c r="H76" s="15" t="n"/>
@@ -24845,7 +27684,7 @@
         </is>
       </c>
       <c r="F77" s="19" t="n">
-        <v>53.89</v>
+        <v>53.45</v>
       </c>
       <c r="G77" s="20" t="n"/>
       <c r="H77" s="15" t="n"/>
@@ -24883,7 +27722,7 @@
         </is>
       </c>
       <c r="F78" s="19" t="n">
-        <v>48.3</v>
+        <v>49.01</v>
       </c>
       <c r="G78" s="20" t="n"/>
       <c r="H78" s="15" t="n"/>
@@ -24921,7 +27760,7 @@
         </is>
       </c>
       <c r="F79" s="19" t="n">
-        <v>42.79</v>
+        <v>43.44</v>
       </c>
       <c r="G79" s="20" t="n"/>
       <c r="H79" s="15" t="n"/>
@@ -24959,7 +27798,7 @@
         </is>
       </c>
       <c r="F80" s="19" t="n">
-        <v>41.23</v>
+        <v>41.22</v>
       </c>
       <c r="G80" s="20" t="n"/>
       <c r="H80" s="15" t="n"/>
@@ -24997,7 +27836,7 @@
         </is>
       </c>
       <c r="F81" s="19" t="n">
-        <v>38.37</v>
+        <v>37.45</v>
       </c>
       <c r="G81" s="20" t="n"/>
       <c r="H81" s="15" t="n"/>
@@ -25035,7 +27874,7 @@
         </is>
       </c>
       <c r="F82" s="19" t="n">
-        <v>376.5</v>
+        <v>375.54</v>
       </c>
       <c r="G82" s="20" t="n"/>
       <c r="H82" s="15" t="n"/>
@@ -25073,7 +27912,7 @@
         </is>
       </c>
       <c r="F83" s="19" t="n">
-        <v>174.82</v>
+        <v>173.84</v>
       </c>
       <c r="G83" s="20" t="n"/>
       <c r="H83" s="15" t="n"/>
@@ -25111,7 +27950,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>97.42</v>
+        <v>98.28</v>
       </c>
       <c r="G84" s="20" t="n"/>
       <c r="H84" s="15" t="n"/>
@@ -25149,7 +27988,7 @@
         </is>
       </c>
       <c r="F85" s="19" t="n">
-        <v>56.43</v>
+        <v>56.32</v>
       </c>
       <c r="G85" s="20" t="n"/>
       <c r="H85" s="15" t="n"/>
@@ -25225,7 +28064,7 @@
         </is>
       </c>
       <c r="F87" s="19" t="n">
-        <v>48.09</v>
+        <v>48.67</v>
       </c>
       <c r="G87" s="20" t="n"/>
       <c r="H87" s="15" t="n"/>
@@ -25301,7 +28140,7 @@
         </is>
       </c>
       <c r="F89" s="19" t="n">
-        <v>34.5</v>
+        <v>34.77</v>
       </c>
       <c r="G89" s="20" t="n"/>
       <c r="H89" s="15" t="n"/>
@@ -25339,7 +28178,7 @@
         </is>
       </c>
       <c r="F90" s="19" t="n">
-        <v>97.18000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="G90" s="20" t="n"/>
       <c r="H90" s="15" t="n"/>
@@ -25377,7 +28216,7 @@
         </is>
       </c>
       <c r="F91" s="19" t="n">
-        <v>71.16</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G91" s="20" t="n"/>
       <c r="H91" s="15" t="n"/>
@@ -25415,7 +28254,7 @@
         </is>
       </c>
       <c r="F92" s="19" t="n">
-        <v>67.79000000000001</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G92" s="20" t="n"/>
       <c r="H92" s="15" t="n"/>
@@ -25453,7 +28292,7 @@
         </is>
       </c>
       <c r="F93" s="19" t="n">
-        <v>61.42</v>
+        <v>61.2</v>
       </c>
       <c r="G93" s="20" t="n"/>
       <c r="H93" s="15" t="n"/>
@@ -25491,7 +28330,7 @@
         </is>
       </c>
       <c r="F94" s="19" t="n">
-        <v>59.81</v>
+        <v>59.46</v>
       </c>
       <c r="G94" s="20" t="n"/>
       <c r="H94" s="15" t="n"/>
@@ -25529,7 +28368,7 @@
         </is>
       </c>
       <c r="F95" s="19" t="n">
-        <v>56.86</v>
+        <v>56.24</v>
       </c>
       <c r="G95" s="20" t="n"/>
       <c r="H95" s="15" t="n"/>
@@ -25567,7 +28406,7 @@
         </is>
       </c>
       <c r="F96" s="19" t="n">
-        <v>56.41</v>
+        <v>56.22</v>
       </c>
       <c r="G96" s="20" t="n"/>
       <c r="H96" s="15" t="n"/>
@@ -25605,7 +28444,7 @@
         </is>
       </c>
       <c r="F97" s="19" t="n">
-        <v>53.21</v>
+        <v>53.22</v>
       </c>
       <c r="G97" s="20" t="n"/>
       <c r="H97" s="15" t="n"/>
@@ -25643,7 +28482,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>1017.1</v>
+        <v>1013.78</v>
       </c>
       <c r="G98" s="20" t="n"/>
       <c r="H98" s="15" t="n"/>
@@ -25719,7 +28558,7 @@
         </is>
       </c>
       <c r="F100" s="19" t="n">
-        <v>180.62</v>
+        <v>180.08</v>
       </c>
       <c r="G100" s="20" t="n"/>
       <c r="H100" s="15" t="n"/>
@@ -25871,7 +28710,7 @@
         </is>
       </c>
       <c r="F104" s="19" t="n">
-        <v>50.94</v>
+        <v>51.14</v>
       </c>
       <c r="G104" s="20" t="n"/>
       <c r="H104" s="15" t="n"/>
@@ -25909,7 +28748,7 @@
         </is>
       </c>
       <c r="F105" s="19" t="n">
-        <v>44.46</v>
+        <v>43.58</v>
       </c>
       <c r="G105" s="20" t="n"/>
       <c r="H105" s="15" t="n"/>
@@ -25947,7 +28786,7 @@
         </is>
       </c>
       <c r="F106" s="19" t="n">
-        <v>126.36</v>
+        <v>126.82</v>
       </c>
       <c r="G106" s="20" t="n"/>
       <c r="H106" s="15" t="n"/>
@@ -25985,7 +28824,7 @@
         </is>
       </c>
       <c r="F107" s="19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="G107" s="20" t="n"/>
       <c r="H107" s="15" t="n"/>
@@ -26023,7 +28862,7 @@
         </is>
       </c>
       <c r="F108" s="19" t="n">
-        <v>53.18</v>
+        <v>53.15</v>
       </c>
       <c r="G108" s="20" t="n"/>
       <c r="H108" s="15" t="n"/>
@@ -26061,7 +28900,7 @@
         </is>
       </c>
       <c r="F109" s="19" t="n">
-        <v>46.39</v>
+        <v>46.21</v>
       </c>
       <c r="G109" s="20" t="n"/>
       <c r="H109" s="15" t="n"/>
@@ -26099,7 +28938,7 @@
         </is>
       </c>
       <c r="F110" s="19" t="n">
-        <v>44.77</v>
+        <v>44.38</v>
       </c>
       <c r="G110" s="20" t="n"/>
       <c r="H110" s="15" t="n"/>
@@ -26175,7 +29014,7 @@
         </is>
       </c>
       <c r="F112" s="19" t="n">
-        <v>39.27</v>
+        <v>39.4</v>
       </c>
       <c r="G112" s="20" t="n"/>
       <c r="H112" s="15" t="n"/>
@@ -26213,7 +29052,7 @@
         </is>
       </c>
       <c r="F113" s="19" t="n">
-        <v>36.69</v>
+        <v>35.59</v>
       </c>
       <c r="G113" s="20" t="n"/>
       <c r="H113" s="15" t="n"/>
@@ -26251,7 +29090,7 @@
         </is>
       </c>
       <c r="F114" s="19" t="n">
-        <v>374.9</v>
+        <v>378.16</v>
       </c>
       <c r="G114" s="20" t="n"/>
       <c r="H114" s="15" t="n"/>
@@ -26289,7 +29128,7 @@
         </is>
       </c>
       <c r="F115" s="19" t="n">
-        <v>137.85</v>
+        <v>138.12</v>
       </c>
       <c r="G115" s="20" t="n"/>
       <c r="H115" s="15" t="n"/>
@@ -26327,7 +29166,7 @@
         </is>
       </c>
       <c r="F116" s="19" t="n">
-        <v>117.13</v>
+        <v>116.89</v>
       </c>
       <c r="G116" s="20" t="n"/>
       <c r="H116" s="15" t="n"/>
@@ -26365,7 +29204,7 @@
         </is>
       </c>
       <c r="F117" s="19" t="n">
-        <v>100.72</v>
+        <v>100.77</v>
       </c>
       <c r="G117" s="20" t="n"/>
       <c r="H117" s="15" t="n"/>
@@ -26403,7 +29242,7 @@
         </is>
       </c>
       <c r="F118" s="19" t="n">
-        <v>92.23</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="G118" s="20" t="n"/>
       <c r="H118" s="15" t="n"/>
@@ -26441,7 +29280,7 @@
         </is>
       </c>
       <c r="F119" s="19" t="n">
-        <v>92.09</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="G119" s="20" t="n"/>
       <c r="H119" s="15" t="n"/>
@@ -26479,7 +29318,7 @@
         </is>
       </c>
       <c r="F120" s="19" t="n">
-        <v>91.40000000000001</v>
+        <v>90.77</v>
       </c>
       <c r="G120" s="20" t="n"/>
       <c r="H120" s="15" t="n"/>
@@ -26517,7 +29356,7 @@
         </is>
       </c>
       <c r="F121" s="19" t="n">
-        <v>85.18000000000001</v>
+        <v>83.14</v>
       </c>
       <c r="G121" s="20" t="n"/>
       <c r="H121" s="15" t="n"/>
@@ -26555,7 +29394,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>109.79</v>
+        <v>109.88</v>
       </c>
       <c r="G122" s="20" t="n"/>
       <c r="H122" s="15" t="n"/>
@@ -26593,7 +29432,7 @@
         </is>
       </c>
       <c r="F123" s="19" t="n">
-        <v>42.87</v>
+        <v>45.69</v>
       </c>
       <c r="G123" s="20" t="n"/>
       <c r="H123" s="15" t="n"/>
@@ -26631,7 +29470,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>38.6</v>
+        <v>38.74</v>
       </c>
       <c r="G124" s="20" t="n"/>
       <c r="H124" s="15" t="n"/>
@@ -26669,7 +29508,7 @@
         </is>
       </c>
       <c r="F125" s="19" t="n">
-        <v>36.27</v>
+        <v>36.83</v>
       </c>
       <c r="G125" s="20" t="n"/>
       <c r="H125" s="15" t="n"/>
@@ -26707,7 +29546,7 @@
         </is>
       </c>
       <c r="F126" s="19" t="n">
-        <v>22.6</v>
+        <v>22.17</v>
       </c>
       <c r="G126" s="20" t="n"/>
       <c r="H126" s="15" t="n"/>
@@ -26745,7 +29584,7 @@
         </is>
       </c>
       <c r="F127" s="19" t="n">
-        <v>21.28</v>
+        <v>21.83</v>
       </c>
       <c r="G127" s="20" t="n"/>
       <c r="H127" s="15" t="n"/>
@@ -26783,7 +29622,7 @@
         </is>
       </c>
       <c r="F128" s="19" t="n">
-        <v>20.79</v>
+        <v>20.24</v>
       </c>
       <c r="G128" s="20" t="n"/>
       <c r="H128" s="15" t="n"/>
@@ -26821,7 +29660,7 @@
         </is>
       </c>
       <c r="F129" s="19" t="n">
-        <v>16.7</v>
+        <v>16.47</v>
       </c>
       <c r="G129" s="20" t="n"/>
       <c r="H129" s="15" t="n"/>
@@ -26897,7 +29736,7 @@
         </is>
       </c>
       <c r="F131" s="19" t="n">
-        <v>101.03</v>
+        <v>100.42</v>
       </c>
       <c r="G131" s="20" t="n"/>
       <c r="H131" s="15" t="n"/>
@@ -26935,7 +29774,7 @@
         </is>
       </c>
       <c r="F132" s="19" t="n">
-        <v>92.91</v>
+        <v>95.45</v>
       </c>
       <c r="G132" s="20" t="n"/>
       <c r="H132" s="15" t="n"/>
@@ -26973,7 +29812,7 @@
         </is>
       </c>
       <c r="F133" s="19" t="n">
-        <v>72.47</v>
+        <v>73.84</v>
       </c>
       <c r="G133" s="20" t="n"/>
       <c r="H133" s="15" t="n"/>
@@ -27049,7 +29888,7 @@
         </is>
       </c>
       <c r="F135" s="19" t="n">
-        <v>61.47</v>
+        <v>61.16</v>
       </c>
       <c r="G135" s="20" t="n"/>
       <c r="H135" s="15" t="n"/>
@@ -27087,7 +29926,7 @@
         </is>
       </c>
       <c r="F136" s="19" t="n">
-        <v>59.14</v>
+        <v>58.58</v>
       </c>
       <c r="G136" s="20" t="n"/>
       <c r="H136" s="15" t="n"/>
@@ -27125,7 +29964,7 @@
         </is>
       </c>
       <c r="F137" s="19" t="n">
-        <v>57.99</v>
+        <v>56.53</v>
       </c>
       <c r="G137" s="20" t="n"/>
       <c r="H137" s="15" t="n"/>
@@ -27163,7 +30002,7 @@
         </is>
       </c>
       <c r="F138" s="19" t="n">
-        <v>72.41</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="G138" s="20" t="n"/>
       <c r="H138" s="15" t="n"/>
@@ -27201,7 +30040,7 @@
         </is>
       </c>
       <c r="F139" s="19" t="n">
-        <v>58.7</v>
+        <v>58.25</v>
       </c>
       <c r="G139" s="20" t="n"/>
       <c r="H139" s="15" t="n"/>
@@ -27239,7 +30078,7 @@
         </is>
       </c>
       <c r="F140" s="19" t="n">
-        <v>44.66</v>
+        <v>44.04</v>
       </c>
       <c r="G140" s="20" t="n"/>
       <c r="H140" s="15" t="n"/>
@@ -27277,7 +30116,7 @@
         </is>
       </c>
       <c r="F141" s="19" t="n">
-        <v>44.1</v>
+        <v>43.82</v>
       </c>
       <c r="G141" s="20" t="n"/>
       <c r="H141" s="15" t="n"/>
@@ -27315,7 +30154,7 @@
         </is>
       </c>
       <c r="F142" s="19" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="G142" s="20" t="n"/>
       <c r="H142" s="15" t="n"/>
@@ -27353,7 +30192,7 @@
         </is>
       </c>
       <c r="F143" s="19" t="n">
-        <v>33.71</v>
+        <v>33.72</v>
       </c>
       <c r="G143" s="20" t="n"/>
       <c r="H143" s="15" t="n"/>
@@ -27391,7 +30230,7 @@
         </is>
       </c>
       <c r="F144" s="19" t="n">
-        <v>24.9</v>
+        <v>24.87</v>
       </c>
       <c r="G144" s="20" t="n"/>
       <c r="H144" s="15" t="n"/>
@@ -27429,7 +30268,7 @@
         </is>
       </c>
       <c r="F145" s="19" t="n">
-        <v>24.14</v>
+        <v>24.25</v>
       </c>
       <c r="G145" s="20" t="n"/>
       <c r="H145" s="15" t="n"/>
@@ -27505,7 +30344,7 @@
         </is>
       </c>
       <c r="F147" s="19" t="n">
-        <v>52.71</v>
+        <v>52.7</v>
       </c>
       <c r="G147" s="20" t="n"/>
       <c r="H147" s="15" t="n"/>
@@ -27619,7 +30458,7 @@
         </is>
       </c>
       <c r="F150" s="19" t="n">
-        <v>19.59</v>
+        <v>19.6</v>
       </c>
       <c r="G150" s="20" t="n"/>
       <c r="H150" s="15" t="n"/>
@@ -27657,7 +30496,7 @@
         </is>
       </c>
       <c r="F151" s="19" t="n">
-        <v>15.86</v>
+        <v>15.81</v>
       </c>
       <c r="G151" s="20" t="n"/>
       <c r="H151" s="15" t="n"/>
@@ -27695,7 +30534,7 @@
         </is>
       </c>
       <c r="F152" s="19" t="n">
-        <v>12.05</v>
+        <v>12.04</v>
       </c>
       <c r="G152" s="20" t="n"/>
       <c r="H152" s="15" t="n"/>
@@ -27992,17 +30831,17 @@
           <t>Set</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Raw NM USD</t>
         </is>
@@ -32432,7 +35271,7 @@
       <formula1>='Video Log'!$A$2:$A$311</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$26</formula1>
+      <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$10</formula1>
@@ -32451,7 +35290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -32497,27 +35336,27 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>LingSter Games</t>
+          <t>Just Games</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>https://lingstergames.com/collections/pokemon</t>
+          <t>https://www.justgamesrochester.com/category/pokemon/</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Panorama Plaza, Penfield</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Sealed product, Singles, New releases</t>
+          <t>Singles, Sealed product, Organised play, Prereleases</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Deep Pokemon singles and sealed, and the first stop when a set drops.</t>
+          <t>Rochester's flagship game store and the one with the busiest Pokemon calendar. Prereleases every set, a learn to play session for anyone starting out, and League Challenges and Cups through the year.</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
@@ -32539,27 +35378,59 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>Jefferson Road, Henrietta</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Sealed product, Singles, In store, Organised play</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>One of the biggest game stores in the area, with a Pokemon section to match and a sanctioned league of its own.</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>LingSter Games</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>https://lingstergames.com/collections/pokemon</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
           <t>Rochester, NY</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Sealed product, Singles, In store</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>One of the biggest game stores in the area, with a Pokemon section to match.</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Sealed product, Singles, New releases</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Deep Pokemon singles and sealed, and the first stop when a set drops.</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Add a row per shop. Paste the plain page URL: tracking and session parameters are stripped on build, but a clean link is easier to check.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -539,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -551,6 +552,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -611,6 +613,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -690,6 +693,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -745,6 +749,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -757,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -769,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -781,6 +788,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -793,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -805,6 +814,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
@@ -5363,12 +5373,14 @@
         <f>HYPERLINK("https://youtu.be/O5WscUY7qZI","watch")</f>
         <v/>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
+      <c r="H2" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="n"/>
       <c r="K2" s="15" t="n"/>
@@ -5378,18 +5390,22 @@
       <c r="O2" s="15" t="n"/>
       <c r="P2" s="15" t="n"/>
       <c r="Q2" s="15" t="n"/>
-      <c r="R2" s="15" t="n"/>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S2" s="15">
         <f>SUM(H2,J2,L2,N2,P2)</f>
         <v/>
       </c>
-      <c r="T2" s="15" t="inlineStr">
+      <c r="T2" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U2" s="15" t="n"/>
-      <c r="V2" s="15" t="inlineStr">
+      <c r="V2" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -5432,12 +5448,12 @@
         <f>HYPERLINK("https://youtu.be/IQMn3DNCzik","watch")</f>
         <v/>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n">
+      <c r="H3" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I3" s="15" t="n"/>
@@ -5449,7 +5465,7 @@
       <c r="O3" s="15" t="n"/>
       <c r="P3" s="15" t="n"/>
       <c r="Q3" s="15" t="n"/>
-      <c r="R3" s="15" t="inlineStr">
+      <c r="R3" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -5499,12 +5515,14 @@
         <f>HYPERLINK("https://youtu.be/2XdMKde79M8","watch")</f>
         <v/>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n"/>
+      <c r="H4" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
@@ -5514,18 +5532,22 @@
       <c r="O4" s="15" t="n"/>
       <c r="P4" s="15" t="n"/>
       <c r="Q4" s="15" t="n"/>
-      <c r="R4" s="15" t="n"/>
+      <c r="R4" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S4" s="15">
         <f>SUM(H4,J4,L4,N4,P4)</f>
         <v/>
       </c>
-      <c r="T4" s="15" t="inlineStr">
+      <c r="T4" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U4" s="15" t="n"/>
-      <c r="V4" s="15" t="inlineStr">
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -5568,12 +5590,12 @@
         <f>HYPERLINK("https://youtu.be/RZInASE6x1c","watch")</f>
         <v/>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I5" s="15" t="n"/>
@@ -5585,7 +5607,7 @@
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
       <c r="Q5" s="15" t="n"/>
-      <c r="R5" s="15" t="inlineStr">
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -5635,12 +5657,12 @@
         <f>HYPERLINK("https://youtu.be/oSPbl9reyIM","watch")</f>
         <v/>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I6" s="15" t="n"/>
@@ -5652,7 +5674,7 @@
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
       <c r="Q6" s="15" t="n"/>
-      <c r="R6" s="15" t="inlineStr">
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -5702,12 +5724,12 @@
         <f>HYPERLINK("https://youtu.be/inTMqcQmFhM","watch")</f>
         <v/>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I7" s="15" t="n"/>
@@ -5719,7 +5741,7 @@
       <c r="O7" s="15" t="n"/>
       <c r="P7" s="15" t="n"/>
       <c r="Q7" s="15" t="n"/>
-      <c r="R7" s="15" t="inlineStr">
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -5728,13 +5750,13 @@
         <f>SUM(H7,J7,L7,N7,P7)</f>
         <v/>
       </c>
-      <c r="T7" s="15" t="inlineStr">
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U7" s="15" t="n"/>
-      <c r="V7" s="15" t="inlineStr">
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -5777,12 +5799,14 @@
         <f>HYPERLINK("https://youtu.be/b8CfpcK7-h0","watch")</f>
         <v/>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n"/>
+      <c r="H8" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -5792,18 +5816,22 @@
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="15" t="n"/>
       <c r="Q8" s="15" t="n"/>
-      <c r="R8" s="15" t="n"/>
+      <c r="R8" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S8" s="15">
         <f>SUM(H8,J8,L8,N8,P8)</f>
         <v/>
       </c>
-      <c r="T8" s="15" t="inlineStr">
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U8" s="15" t="n"/>
-      <c r="V8" s="15" t="inlineStr">
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -5846,7 +5874,7 @@
         <f>HYPERLINK("https://youtu.be/aa9jzXRFtrg","watch")</f>
         <v/>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -5861,7 +5889,7 @@
       <c r="O9" s="15" t="n"/>
       <c r="P9" s="15" t="n"/>
       <c r="Q9" s="15" t="n"/>
-      <c r="R9" s="15" t="inlineStr">
+      <c r="R9" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -5911,12 +5939,12 @@
         <f>HYPERLINK("https://youtu.be/znsnYB6boh4","watch")</f>
         <v/>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I10" s="15" t="n"/>
@@ -5928,7 +5956,7 @@
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
       <c r="Q10" s="15" t="n"/>
-      <c r="R10" s="15" t="inlineStr">
+      <c r="R10" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -5937,13 +5965,13 @@
         <f>SUM(H10,J10,L10,N10,P10)</f>
         <v/>
       </c>
-      <c r="T10" s="15" t="inlineStr">
+      <c r="T10" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U10" s="15" t="n"/>
-      <c r="V10" s="15" t="inlineStr">
+      <c r="V10" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -5986,12 +6014,12 @@
         <f>HYPERLINK("https://youtu.be/16jOkWyE1Cs","watch")</f>
         <v/>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I11" s="15" t="n"/>
@@ -6003,7 +6031,7 @@
       <c r="O11" s="15" t="n"/>
       <c r="P11" s="15" t="n"/>
       <c r="Q11" s="15" t="n"/>
-      <c r="R11" s="15" t="inlineStr">
+      <c r="R11" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -6012,13 +6040,13 @@
         <f>SUM(H11,J11,L11,N11,P11)</f>
         <v/>
       </c>
-      <c r="T11" s="15" t="inlineStr">
+      <c r="T11" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U11" s="15" t="n"/>
-      <c r="V11" s="15" t="inlineStr">
+      <c r="V11" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -6061,12 +6089,12 @@
         <f>HYPERLINK("https://youtu.be/LmdyCAqDodM","watch")</f>
         <v/>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="15" t="n"/>
@@ -6078,7 +6106,7 @@
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="15" t="n"/>
-      <c r="R12" s="15" t="inlineStr">
+      <c r="R12" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -6087,13 +6115,13 @@
         <f>SUM(H12,J12,L12,N12,P12)</f>
         <v/>
       </c>
-      <c r="T12" s="15" t="inlineStr">
+      <c r="T12" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U12" s="15" t="n"/>
-      <c r="V12" s="15" t="inlineStr">
+      <c r="V12" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -6136,7 +6164,7 @@
         <f>HYPERLINK("https://youtu.be/k6p_6HEntYw","watch")</f>
         <v/>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -6151,7 +6179,7 @@
       <c r="O13" s="15" t="n"/>
       <c r="P13" s="15" t="n"/>
       <c r="Q13" s="15" t="n"/>
-      <c r="R13" s="15" t="inlineStr">
+      <c r="R13" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -6160,13 +6188,13 @@
         <f>SUM(H13,J13,L13,N13,P13)</f>
         <v/>
       </c>
-      <c r="T13" s="15" t="inlineStr">
+      <c r="T13" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U13" s="15" t="n"/>
-      <c r="V13" s="15" t="inlineStr">
+      <c r="V13" s="14" t="inlineStr">
         <is>
           <t>Double Rare (2 black stars)</t>
         </is>
@@ -6209,12 +6237,12 @@
         <f>HYPERLINK("https://youtu.be/ndzNjhARITQ","watch")</f>
         <v/>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="15" t="n"/>
@@ -6226,7 +6254,7 @@
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="15" t="n"/>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="R14" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -6235,13 +6263,13 @@
         <f>SUM(H14,J14,L14,N14,P14)</f>
         <v/>
       </c>
-      <c r="T14" s="15" t="inlineStr">
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U14" s="15" t="n"/>
-      <c r="V14" s="15" t="inlineStr">
+      <c r="V14" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -6284,12 +6312,12 @@
         <f>HYPERLINK("https://youtu.be/fY-u0pxphVo","watch")</f>
         <v/>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I15" s="15" t="n"/>
@@ -6301,7 +6329,7 @@
       <c r="O15" s="15" t="n"/>
       <c r="P15" s="15" t="n"/>
       <c r="Q15" s="15" t="n"/>
-      <c r="R15" s="15" t="inlineStr">
+      <c r="R15" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -6351,12 +6379,14 @@
         <f>HYPERLINK("https://youtu.be/76ziDoR2YJg","watch")</f>
         <v/>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n"/>
+      <c r="H16" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
@@ -6366,18 +6396,22 @@
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="15" t="n"/>
-      <c r="R16" s="15" t="n"/>
+      <c r="R16" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S16" s="15">
         <f>SUM(H16,J16,L16,N16,P16)</f>
         <v/>
       </c>
-      <c r="T16" s="15" t="inlineStr">
+      <c r="T16" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U16" s="15" t="n"/>
-      <c r="V16" s="15" t="inlineStr">
+      <c r="V16" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -6420,7 +6454,7 @@
         <f>HYPERLINK("https://youtu.be/3pUiN-8XkEk","watch")</f>
         <v/>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
@@ -6435,7 +6469,7 @@
       <c r="O17" s="15" t="n"/>
       <c r="P17" s="15" t="n"/>
       <c r="Q17" s="15" t="n"/>
-      <c r="R17" s="15" t="inlineStr">
+      <c r="R17" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -6444,13 +6478,13 @@
         <f>SUM(H17,J17,L17,N17,P17)</f>
         <v/>
       </c>
-      <c r="T17" s="15" t="inlineStr">
+      <c r="T17" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U17" s="15" t="n"/>
-      <c r="V17" s="15" t="inlineStr">
+      <c r="V17" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -6493,7 +6527,7 @@
         <f>HYPERLINK("https://youtu.be/019sIQP5PwA","watch")</f>
         <v/>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -6508,7 +6542,7 @@
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
-      <c r="R18" s="15" t="inlineStr">
+      <c r="R18" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -6517,13 +6551,13 @@
         <f>SUM(H18,J18,L18,N18,P18)</f>
         <v/>
       </c>
-      <c r="T18" s="15" t="inlineStr">
+      <c r="T18" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U18" s="15" t="n"/>
-      <c r="V18" s="15" t="inlineStr">
+      <c r="V18" s="14" t="inlineStr">
         <is>
           <t>Double Rare (2 black stars)</t>
         </is>
@@ -6566,7 +6600,7 @@
         <f>HYPERLINK("https://youtu.be/3dAQ-PS0fpU","watch")</f>
         <v/>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -6581,7 +6615,7 @@
       <c r="O19" s="15" t="n"/>
       <c r="P19" s="15" t="n"/>
       <c r="Q19" s="15" t="n"/>
-      <c r="R19" s="15" t="inlineStr">
+      <c r="R19" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -6631,12 +6665,12 @@
         <f>HYPERLINK("https://youtu.be/JfHlnrlX6S0","watch")</f>
         <v/>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I20" s="15" t="n"/>
@@ -6648,7 +6682,7 @@
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
-      <c r="R20" s="15" t="inlineStr">
+      <c r="R20" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -6657,13 +6691,13 @@
         <f>SUM(H20,J20,L20,N20,P20)</f>
         <v/>
       </c>
-      <c r="T20" s="15" t="inlineStr">
+      <c r="T20" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U20" s="15" t="n"/>
-      <c r="V20" s="15" t="inlineStr">
+      <c r="V20" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -6706,12 +6740,12 @@
         <f>HYPERLINK("https://youtu.be/vTy3MKGN73k","watch")</f>
         <v/>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I21" s="15" t="n"/>
@@ -6723,7 +6757,7 @@
       <c r="O21" s="15" t="n"/>
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
-      <c r="R21" s="15" t="inlineStr">
+      <c r="R21" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -6773,12 +6807,14 @@
         <f>HYPERLINK("https://youtu.be/1_ivvCs7Gp4","watch")</f>
         <v/>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n"/>
+      <c r="H22" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I22" s="15" t="n"/>
       <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
@@ -6788,18 +6824,22 @@
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
-      <c r="R22" s="15" t="n"/>
+      <c r="R22" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S22" s="15">
         <f>SUM(H22,J22,L22,N22,P22)</f>
         <v/>
       </c>
-      <c r="T22" s="15" t="inlineStr">
+      <c r="T22" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="inlineStr">
+      <c r="V22" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -6842,7 +6882,7 @@
         <f>HYPERLINK("https://youtu.be/R2VxbNMrlXQ","watch")</f>
         <v/>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
@@ -6857,7 +6897,7 @@
       <c r="O23" s="15" t="n"/>
       <c r="P23" s="15" t="n"/>
       <c r="Q23" s="15" t="n"/>
-      <c r="R23" s="15" t="inlineStr">
+      <c r="R23" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -6866,13 +6906,13 @@
         <f>SUM(H23,J23,L23,N23,P23)</f>
         <v/>
       </c>
-      <c r="T23" s="15" t="inlineStr">
+      <c r="T23" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U23" s="15" t="n"/>
-      <c r="V23" s="15" t="inlineStr">
+      <c r="V23" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -6915,13 +6955,13 @@
         <f>HYPERLINK("https://youtu.be/m41IeIUpqRI","watch")</f>
         <v/>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -6934,7 +6974,7 @@
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
-      <c r="R24" s="15" t="inlineStr">
+      <c r="R24" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -6984,7 +7024,7 @@
         <f>HYPERLINK("https://youtu.be/LGGJhVyJwDc","watch")</f>
         <v/>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -6999,7 +7039,7 @@
       <c r="O25" s="15" t="n"/>
       <c r="P25" s="15" t="n"/>
       <c r="Q25" s="15" t="n"/>
-      <c r="R25" s="15" t="inlineStr">
+      <c r="R25" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7049,12 +7089,12 @@
         <f>HYPERLINK("https://youtu.be/SQ-_tTDutFA","watch")</f>
         <v/>
       </c>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H26" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="15" t="n"/>
@@ -7066,7 +7106,7 @@
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
-      <c r="R26" s="15" t="inlineStr">
+      <c r="R26" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -7075,13 +7115,13 @@
         <f>SUM(H26,J26,L26,N26,P26)</f>
         <v/>
       </c>
-      <c r="T26" s="15" t="inlineStr">
+      <c r="T26" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U26" s="15" t="n"/>
-      <c r="V26" s="15" t="inlineStr">
+      <c r="V26" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -7124,12 +7164,12 @@
         <f>HYPERLINK("https://youtu.be/405aRLjbdmM","watch")</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I27" s="15" t="n"/>
@@ -7141,7 +7181,7 @@
       <c r="O27" s="15" t="n"/>
       <c r="P27" s="15" t="n"/>
       <c r="Q27" s="15" t="n"/>
-      <c r="R27" s="15" t="inlineStr">
+      <c r="R27" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -7191,12 +7231,12 @@
         <f>HYPERLINK("https://youtu.be/yrfwnJKXRgo","watch")</f>
         <v/>
       </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H28" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I28" s="15" t="n"/>
@@ -7208,7 +7248,7 @@
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="15" t="n"/>
       <c r="Q28" s="15" t="n"/>
-      <c r="R28" s="15" t="inlineStr">
+      <c r="R28" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -7258,13 +7298,13 @@
         <f>HYPERLINK("https://youtu.be/92-pjMEGpDI","watch")</f>
         <v/>
       </c>
-      <c r="G29" s="15" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -7277,7 +7317,7 @@
       <c r="O29" s="15" t="n"/>
       <c r="P29" s="15" t="n"/>
       <c r="Q29" s="15" t="n"/>
-      <c r="R29" s="15" t="inlineStr">
+      <c r="R29" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7286,13 +7326,13 @@
         <f>SUM(H29,J29,L29,N29,P29)</f>
         <v/>
       </c>
-      <c r="T29" s="15" t="inlineStr">
+      <c r="T29" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U29" s="15" t="n"/>
-      <c r="V29" s="15" t="inlineStr">
+      <c r="V29" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -7335,7 +7375,7 @@
         <f>HYPERLINK("https://youtu.be/2S4poqmGKWE","watch")</f>
         <v/>
       </c>
-      <c r="G30" s="15" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>Twilight Masquerade</t>
         </is>
@@ -7350,7 +7390,7 @@
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="15" t="n"/>
       <c r="Q30" s="15" t="n"/>
-      <c r="R30" s="15" t="inlineStr">
+      <c r="R30" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -7400,7 +7440,7 @@
         <f>HYPERLINK("https://youtu.be/XxYqEIFgWvg","watch")</f>
         <v/>
       </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -7415,7 +7455,7 @@
       <c r="O31" s="15" t="n"/>
       <c r="P31" s="15" t="n"/>
       <c r="Q31" s="15" t="n"/>
-      <c r="R31" s="15" t="inlineStr">
+      <c r="R31" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7465,12 +7505,12 @@
         <f>HYPERLINK("https://youtu.be/q1WTwiauv3w","watch")</f>
         <v/>
       </c>
-      <c r="G32" s="15" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H32" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I32" s="15" t="n"/>
@@ -7482,7 +7522,7 @@
       <c r="O32" s="15" t="n"/>
       <c r="P32" s="15" t="n"/>
       <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="inlineStr">
+      <c r="R32" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -7491,13 +7531,13 @@
         <f>SUM(H32,J32,L32,N32,P32)</f>
         <v/>
       </c>
-      <c r="T32" s="15" t="inlineStr">
+      <c r="T32" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U32" s="15" t="n"/>
-      <c r="V32" s="15" t="inlineStr">
+      <c r="V32" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -7540,12 +7580,12 @@
         <f>HYPERLINK("https://youtu.be/EtFK6nFW6IQ","watch")</f>
         <v/>
       </c>
-      <c r="G33" s="15" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H33" s="15" t="n">
+      <c r="H33" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I33" s="15" t="n"/>
@@ -7557,7 +7597,7 @@
       <c r="O33" s="15" t="n"/>
       <c r="P33" s="15" t="n"/>
       <c r="Q33" s="15" t="n"/>
-      <c r="R33" s="15" t="inlineStr">
+      <c r="R33" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -7607,7 +7647,7 @@
         <f>HYPERLINK("https://youtu.be/z9fpigSEZ3Y","watch")</f>
         <v/>
       </c>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -7622,7 +7662,7 @@
       <c r="O34" s="15" t="n"/>
       <c r="P34" s="15" t="n"/>
       <c r="Q34" s="15" t="n"/>
-      <c r="R34" s="15" t="inlineStr">
+      <c r="R34" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7631,13 +7671,13 @@
         <f>SUM(H34,J34,L34,N34,P34)</f>
         <v/>
       </c>
-      <c r="T34" s="15" t="inlineStr">
+      <c r="T34" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U34" s="15" t="n"/>
-      <c r="V34" s="15" t="inlineStr">
+      <c r="V34" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -7680,12 +7720,12 @@
         <f>HYPERLINK("https://youtu.be/GTC45Mri_gc","watch")</f>
         <v/>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="15" t="n"/>
@@ -7697,7 +7737,7 @@
       <c r="O35" s="15" t="n"/>
       <c r="P35" s="15" t="n"/>
       <c r="Q35" s="15" t="n"/>
-      <c r="R35" s="15" t="inlineStr">
+      <c r="R35" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -7706,13 +7746,13 @@
         <f>SUM(H35,J35,L35,N35,P35)</f>
         <v/>
       </c>
-      <c r="T35" s="15" t="inlineStr">
+      <c r="T35" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U35" s="15" t="n"/>
-      <c r="V35" s="15" t="inlineStr">
+      <c r="V35" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -7755,13 +7795,13 @@
         <f>HYPERLINK("https://youtu.be/RtJn1UOi2S8","watch")</f>
         <v/>
       </c>
-      <c r="G36" s="15" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Twilight Masquerade</t>
         </is>
@@ -7774,7 +7814,7 @@
       <c r="O36" s="15" t="n"/>
       <c r="P36" s="15" t="n"/>
       <c r="Q36" s="15" t="n"/>
-      <c r="R36" s="15" t="inlineStr">
+      <c r="R36" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -7824,7 +7864,7 @@
         <f>HYPERLINK("https://youtu.be/rUOMBBOjrXI","watch")</f>
         <v/>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -7839,7 +7879,7 @@
       <c r="O37" s="15" t="n"/>
       <c r="P37" s="15" t="n"/>
       <c r="Q37" s="15" t="n"/>
-      <c r="R37" s="15" t="inlineStr">
+      <c r="R37" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7848,13 +7888,13 @@
         <f>SUM(H37,J37,L37,N37,P37)</f>
         <v/>
       </c>
-      <c r="T37" s="15" t="inlineStr">
+      <c r="T37" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U37" s="15" t="n"/>
-      <c r="V37" s="15" t="inlineStr">
+      <c r="V37" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -7897,7 +7937,7 @@
         <f>HYPERLINK("https://youtu.be/pRkDVGXWufQ","watch")</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -7912,7 +7952,7 @@
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="15" t="n"/>
       <c r="Q38" s="15" t="n"/>
-      <c r="R38" s="15" t="inlineStr">
+      <c r="R38" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -7921,13 +7961,13 @@
         <f>SUM(H38,J38,L38,N38,P38)</f>
         <v/>
       </c>
-      <c r="T38" s="15" t="inlineStr">
+      <c r="T38" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U38" s="15" t="n"/>
-      <c r="V38" s="15" t="inlineStr">
+      <c r="V38" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -7970,7 +8010,7 @@
         <f>HYPERLINK("https://youtu.be/X0KK70SjzEM","watch")</f>
         <v/>
       </c>
-      <c r="G39" s="15" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -7985,7 +8025,7 @@
       <c r="O39" s="15" t="n"/>
       <c r="P39" s="15" t="n"/>
       <c r="Q39" s="15" t="n"/>
-      <c r="R39" s="15" t="inlineStr">
+      <c r="R39" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8035,7 +8075,7 @@
         <f>HYPERLINK("https://youtu.be/STMGjXcUAm4","watch")</f>
         <v/>
       </c>
-      <c r="G40" s="15" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -8050,7 +8090,7 @@
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="15" t="n"/>
       <c r="Q40" s="15" t="n"/>
-      <c r="R40" s="15" t="inlineStr">
+      <c r="R40" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8059,13 +8099,13 @@
         <f>SUM(H40,J40,L40,N40,P40)</f>
         <v/>
       </c>
-      <c r="T40" s="15" t="inlineStr">
+      <c r="T40" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U40" s="15" t="n"/>
-      <c r="V40" s="15" t="inlineStr">
+      <c r="V40" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -8108,7 +8148,7 @@
         <f>HYPERLINK("https://youtu.be/O1hNutypTR8","watch")</f>
         <v/>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -8123,7 +8163,7 @@
       <c r="O41" s="15" t="n"/>
       <c r="P41" s="15" t="n"/>
       <c r="Q41" s="15" t="n"/>
-      <c r="R41" s="15" t="inlineStr">
+      <c r="R41" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -8173,7 +8213,7 @@
         <f>HYPERLINK("https://youtu.be/xqV7AYXoVJs","watch")</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -8188,7 +8228,7 @@
       <c r="O42" s="15" t="n"/>
       <c r="P42" s="15" t="n"/>
       <c r="Q42" s="15" t="n"/>
-      <c r="R42" s="15" t="inlineStr">
+      <c r="R42" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8238,7 +8278,7 @@
         <f>HYPERLINK("https://youtu.be/RP08BTumj2U","watch")</f>
         <v/>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
@@ -8253,7 +8293,7 @@
       <c r="O43" s="15" t="n"/>
       <c r="P43" s="15" t="n"/>
       <c r="Q43" s="15" t="n"/>
-      <c r="R43" s="15" t="inlineStr">
+      <c r="R43" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8262,13 +8302,13 @@
         <f>SUM(H43,J43,L43,N43,P43)</f>
         <v/>
       </c>
-      <c r="T43" s="15" t="inlineStr">
+      <c r="T43" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U43" s="15" t="n"/>
-      <c r="V43" s="15" t="inlineStr">
+      <c r="V43" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -8311,7 +8351,7 @@
         <f>HYPERLINK("https://youtu.be/nBKJMnw9L2Y","watch")</f>
         <v/>
       </c>
-      <c r="G44" s="15" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -8326,7 +8366,7 @@
       <c r="O44" s="15" t="n"/>
       <c r="P44" s="15" t="n"/>
       <c r="Q44" s="15" t="n"/>
-      <c r="R44" s="15" t="inlineStr">
+      <c r="R44" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8387,7 +8427,7 @@
       <c r="O45" s="15" t="n"/>
       <c r="P45" s="15" t="n"/>
       <c r="Q45" s="15" t="n"/>
-      <c r="R45" s="15" t="inlineStr">
+      <c r="R45" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8396,13 +8436,13 @@
         <f>SUM(H45,J45,L45,N45,P45)</f>
         <v/>
       </c>
-      <c r="T45" s="15" t="inlineStr">
+      <c r="T45" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U45" s="15" t="n"/>
-      <c r="V45" s="15" t="inlineStr">
+      <c r="V45" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -8456,7 +8496,7 @@
       <c r="O46" s="15" t="n"/>
       <c r="P46" s="15" t="n"/>
       <c r="Q46" s="15" t="n"/>
-      <c r="R46" s="15" t="inlineStr">
+      <c r="R46" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8506,13 +8546,13 @@
         <f>HYPERLINK("https://youtu.be/DTBxGFtTOc8","watch")</f>
         <v/>
       </c>
-      <c r="G47" s="15" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -8525,7 +8565,7 @@
       <c r="O47" s="15" t="n"/>
       <c r="P47" s="15" t="n"/>
       <c r="Q47" s="15" t="n"/>
-      <c r="R47" s="15" t="inlineStr">
+      <c r="R47" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8534,13 +8574,13 @@
         <f>SUM(H47,J47,L47,N47,P47)</f>
         <v/>
       </c>
-      <c r="T47" s="15" t="inlineStr">
+      <c r="T47" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U47" s="15" t="n"/>
-      <c r="V47" s="15" t="inlineStr">
+      <c r="V47" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -8583,7 +8623,7 @@
         <f>HYPERLINK("https://youtu.be/uTGe-WswoVY","watch")</f>
         <v/>
       </c>
-      <c r="G48" s="15" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -8598,7 +8638,7 @@
       <c r="O48" s="15" t="n"/>
       <c r="P48" s="15" t="n"/>
       <c r="Q48" s="15" t="n"/>
-      <c r="R48" s="15" t="inlineStr">
+      <c r="R48" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8648,12 +8688,12 @@
         <f>HYPERLINK("https://youtu.be/xGmQaLcx-c8","watch")</f>
         <v/>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H49" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I49" s="15" t="n"/>
@@ -8665,7 +8705,7 @@
       <c r="O49" s="15" t="n"/>
       <c r="P49" s="15" t="n"/>
       <c r="Q49" s="15" t="n"/>
-      <c r="R49" s="15" t="inlineStr">
+      <c r="R49" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -8674,13 +8714,13 @@
         <f>SUM(H49,J49,L49,N49,P49)</f>
         <v/>
       </c>
-      <c r="T49" s="15" t="inlineStr">
+      <c r="T49" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U49" s="15" t="n"/>
-      <c r="V49" s="15" t="inlineStr">
+      <c r="V49" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -8723,12 +8763,12 @@
         <f>HYPERLINK("https://youtu.be/iV0h672wrGA","watch")</f>
         <v/>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H50" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I50" s="15" t="n"/>
@@ -8740,7 +8780,7 @@
       <c r="O50" s="15" t="n"/>
       <c r="P50" s="15" t="n"/>
       <c r="Q50" s="15" t="n"/>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="R50" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -8790,7 +8830,7 @@
         <f>HYPERLINK("https://youtu.be/u9zpVOVsWyg","watch")</f>
         <v/>
       </c>
-      <c r="G51" s="15" t="inlineStr">
+      <c r="G51" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -8805,7 +8845,7 @@
       <c r="O51" s="15" t="n"/>
       <c r="P51" s="15" t="n"/>
       <c r="Q51" s="15" t="n"/>
-      <c r="R51" s="15" t="inlineStr">
+      <c r="R51" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8814,13 +8854,13 @@
         <f>SUM(H51,J51,L51,N51,P51)</f>
         <v/>
       </c>
-      <c r="T51" s="15" t="inlineStr">
+      <c r="T51" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U51" s="15" t="n"/>
-      <c r="V51" s="15" t="inlineStr">
+      <c r="V51" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -8863,12 +8903,12 @@
         <f>HYPERLINK("https://youtu.be/MCe_0kpYnwE","watch")</f>
         <v/>
       </c>
-      <c r="G52" s="15" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I52" s="15" t="n"/>
@@ -8880,7 +8920,7 @@
       <c r="O52" s="15" t="n"/>
       <c r="P52" s="15" t="n"/>
       <c r="Q52" s="15" t="n"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="R52" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -8930,7 +8970,7 @@
         <f>HYPERLINK("https://youtu.be/WhfY82RrS4w","watch")</f>
         <v/>
       </c>
-      <c r="G53" s="15" t="inlineStr">
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -8945,7 +8985,7 @@
       <c r="O53" s="15" t="n"/>
       <c r="P53" s="15" t="n"/>
       <c r="Q53" s="15" t="n"/>
-      <c r="R53" s="15" t="inlineStr">
+      <c r="R53" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -8995,12 +9035,12 @@
         <f>HYPERLINK("https://youtu.be/x3gI4dEKNMs","watch")</f>
         <v/>
       </c>
-      <c r="G54" s="15" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H54" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I54" s="15" t="n"/>
@@ -9012,7 +9052,7 @@
       <c r="O54" s="15" t="n"/>
       <c r="P54" s="15" t="n"/>
       <c r="Q54" s="15" t="n"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="R54" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9073,7 +9113,7 @@
       <c r="O55" s="15" t="n"/>
       <c r="P55" s="15" t="n"/>
       <c r="Q55" s="15" t="n"/>
-      <c r="R55" s="15" t="inlineStr">
+      <c r="R55" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -9123,12 +9163,12 @@
         <f>HYPERLINK("https://youtu.be/LvWz0hfaQVE","watch")</f>
         <v/>
       </c>
-      <c r="G56" s="15" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n">
+      <c r="H56" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I56" s="15" t="n"/>
@@ -9140,7 +9180,7 @@
       <c r="O56" s="15" t="n"/>
       <c r="P56" s="15" t="n"/>
       <c r="Q56" s="15" t="n"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="R56" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9190,7 +9230,7 @@
         <f>HYPERLINK("https://youtu.be/blSCuSk5nb0","watch")</f>
         <v/>
       </c>
-      <c r="G57" s="15" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -9205,7 +9245,7 @@
       <c r="O57" s="15" t="n"/>
       <c r="P57" s="15" t="n"/>
       <c r="Q57" s="15" t="n"/>
-      <c r="R57" s="15" t="inlineStr">
+      <c r="R57" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -9255,12 +9295,12 @@
         <f>HYPERLINK("https://youtu.be/rlJDEb0q1d0","watch")</f>
         <v/>
       </c>
-      <c r="G58" s="15" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n">
+      <c r="H58" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I58" s="15" t="n"/>
@@ -9272,7 +9312,7 @@
       <c r="O58" s="15" t="n"/>
       <c r="P58" s="15" t="n"/>
       <c r="Q58" s="15" t="n"/>
-      <c r="R58" s="15" t="inlineStr">
+      <c r="R58" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9281,13 +9321,13 @@
         <f>SUM(H58,J58,L58,N58,P58)</f>
         <v/>
       </c>
-      <c r="T58" s="15" t="inlineStr">
+      <c r="T58" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U58" s="15" t="n"/>
-      <c r="V58" s="15" t="inlineStr">
+      <c r="V58" s="14" t="inlineStr">
         <is>
           <t>Illustration Rare (1 gold star)</t>
         </is>
@@ -9330,7 +9370,7 @@
         <f>HYPERLINK("https://youtu.be/UpdeUMc-6ys","watch")</f>
         <v/>
       </c>
-      <c r="G59" s="15" t="inlineStr">
+      <c r="G59" s="14" t="inlineStr">
         <is>
           <t>Twilight Masquerade</t>
         </is>
@@ -9345,7 +9385,7 @@
       <c r="O59" s="15" t="n"/>
       <c r="P59" s="15" t="n"/>
       <c r="Q59" s="15" t="n"/>
-      <c r="R59" s="15" t="inlineStr">
+      <c r="R59" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -9395,11 +9435,7 @@
         <f>HYPERLINK("https://youtu.be/M7NqqhR8V4M","watch")</f>
         <v/>
       </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+      <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="15" t="n"/>
       <c r="J60" s="15" t="n"/>
@@ -9456,7 +9492,7 @@
         <f>HYPERLINK("https://youtu.be/lrl5v4z317s","watch")</f>
         <v/>
       </c>
-      <c r="G61" s="15" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
@@ -9471,7 +9507,7 @@
       <c r="O61" s="15" t="n"/>
       <c r="P61" s="15" t="n"/>
       <c r="Q61" s="15" t="n"/>
-      <c r="R61" s="15" t="inlineStr">
+      <c r="R61" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -9521,7 +9557,7 @@
         <f>HYPERLINK("https://youtu.be/EJ0AKqX2a_Q","watch")</f>
         <v/>
       </c>
-      <c r="G62" s="15" t="inlineStr">
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -9536,7 +9572,7 @@
       <c r="O62" s="15" t="n"/>
       <c r="P62" s="15" t="n"/>
       <c r="Q62" s="15" t="n"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="R62" s="14" t="inlineStr">
         <is>
           <t>Poke Ball Tin</t>
         </is>
@@ -9586,12 +9622,12 @@
         <f>HYPERLINK("https://youtu.be/msETNgFSWD0","watch")</f>
         <v/>
       </c>
-      <c r="G63" s="15" t="inlineStr">
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H63" s="15" t="n">
+      <c r="H63" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I63" s="15" t="n"/>
@@ -9603,7 +9639,7 @@
       <c r="O63" s="15" t="n"/>
       <c r="P63" s="15" t="n"/>
       <c r="Q63" s="15" t="n"/>
-      <c r="R63" s="15" t="inlineStr">
+      <c r="R63" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9653,12 +9689,12 @@
         <f>HYPERLINK("https://youtu.be/Wwc1wVyI6CQ","watch")</f>
         <v/>
       </c>
-      <c r="G64" s="15" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H64" s="15" t="n">
+      <c r="H64" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I64" s="15" t="n"/>
@@ -9670,7 +9706,7 @@
       <c r="O64" s="15" t="n"/>
       <c r="P64" s="15" t="n"/>
       <c r="Q64" s="15" t="n"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="R64" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9720,11 +9756,7 @@
         <f>HYPERLINK("https://youtu.be/xNGxOuMpSiw","watch")</f>
         <v/>
       </c>
-      <c r="G65" s="15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+      <c r="G65" s="15" t="n"/>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="15" t="n"/>
       <c r="J65" s="15" t="n"/>
@@ -9781,12 +9813,12 @@
         <f>HYPERLINK("https://youtu.be/CbwSuTI8QKU","watch")</f>
         <v/>
       </c>
-      <c r="G66" s="15" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H66" s="15" t="n">
+      <c r="H66" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I66" s="15" t="n"/>
@@ -9798,7 +9830,7 @@
       <c r="O66" s="15" t="n"/>
       <c r="P66" s="15" t="n"/>
       <c r="Q66" s="15" t="n"/>
-      <c r="R66" s="15" t="inlineStr">
+      <c r="R66" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9848,12 +9880,12 @@
         <f>HYPERLINK("https://youtu.be/Ec_2Is8DmI8","watch")</f>
         <v/>
       </c>
-      <c r="G67" s="15" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H67" s="15" t="n">
+      <c r="H67" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="15" t="n"/>
@@ -9865,7 +9897,7 @@
       <c r="O67" s="15" t="n"/>
       <c r="P67" s="15" t="n"/>
       <c r="Q67" s="15" t="n"/>
-      <c r="R67" s="15" t="inlineStr">
+      <c r="R67" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -9915,12 +9947,12 @@
         <f>HYPERLINK("https://youtu.be/gLlqJvSuAek","watch")</f>
         <v/>
       </c>
-      <c r="G68" s="15" t="inlineStr">
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H68" s="15" t="n">
+      <c r="H68" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I68" s="15" t="n"/>
@@ -9932,7 +9964,7 @@
       <c r="O68" s="15" t="n"/>
       <c r="P68" s="15" t="n"/>
       <c r="Q68" s="15" t="n"/>
-      <c r="R68" s="15" t="inlineStr">
+      <c r="R68" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -9982,12 +10014,12 @@
         <f>HYPERLINK("https://youtu.be/I14rr28Qduw","watch")</f>
         <v/>
       </c>
-      <c r="G69" s="15" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H69" s="15" t="n">
+      <c r="H69" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I69" s="15" t="n"/>
@@ -9999,7 +10031,7 @@
       <c r="O69" s="15" t="n"/>
       <c r="P69" s="15" t="n"/>
       <c r="Q69" s="15" t="n"/>
-      <c r="R69" s="15" t="inlineStr">
+      <c r="R69" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10049,12 +10081,12 @@
         <f>HYPERLINK("https://youtu.be/NdXTKzUodpQ","watch")</f>
         <v/>
       </c>
-      <c r="G70" s="15" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H70" s="15" t="n">
+      <c r="H70" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I70" s="15" t="n"/>
@@ -10066,7 +10098,7 @@
       <c r="O70" s="15" t="n"/>
       <c r="P70" s="15" t="n"/>
       <c r="Q70" s="15" t="n"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="R70" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10116,12 +10148,12 @@
         <f>HYPERLINK("https://youtu.be/EifpW6bQhPE","watch")</f>
         <v/>
       </c>
-      <c r="G71" s="15" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n">
+      <c r="H71" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I71" s="15" t="n"/>
@@ -10133,7 +10165,7 @@
       <c r="O71" s="15" t="n"/>
       <c r="P71" s="15" t="n"/>
       <c r="Q71" s="15" t="n"/>
-      <c r="R71" s="15" t="inlineStr">
+      <c r="R71" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10183,12 +10215,12 @@
         <f>HYPERLINK("https://youtu.be/6bMl7VF_ov0","watch")</f>
         <v/>
       </c>
-      <c r="G72" s="15" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H72" s="15" t="n">
+      <c r="H72" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I72" s="15" t="n"/>
@@ -10200,7 +10232,7 @@
       <c r="O72" s="15" t="n"/>
       <c r="P72" s="15" t="n"/>
       <c r="Q72" s="15" t="n"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="R72" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10250,12 +10282,12 @@
         <f>HYPERLINK("https://youtu.be/HHjdWa5tfXY","watch")</f>
         <v/>
       </c>
-      <c r="G73" s="15" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H73" s="15" t="n">
+      <c r="H73" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I73" s="15" t="n"/>
@@ -10267,7 +10299,7 @@
       <c r="O73" s="15" t="n"/>
       <c r="P73" s="15" t="n"/>
       <c r="Q73" s="15" t="n"/>
-      <c r="R73" s="15" t="inlineStr">
+      <c r="R73" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10317,12 +10349,14 @@
         <f>HYPERLINK("https://youtu.be/JRMvkxmqFhQ","watch")</f>
         <v/>
       </c>
-      <c r="G74" s="15" t="inlineStr">
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n"/>
+      <c r="H74" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="I74" s="15" t="n"/>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n"/>
@@ -10332,7 +10366,11 @@
       <c r="O74" s="15" t="n"/>
       <c r="P74" s="15" t="n"/>
       <c r="Q74" s="15" t="n"/>
-      <c r="R74" s="15" t="n"/>
+      <c r="R74" s="14" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="S74" s="15">
         <f>SUM(H74,J74,L74,N74,P74)</f>
         <v/>
@@ -10378,12 +10416,12 @@
         <f>HYPERLINK("https://youtu.be/a4iR-qPthjY","watch")</f>
         <v/>
       </c>
-      <c r="G75" s="15" t="inlineStr">
+      <c r="G75" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H75" s="15" t="n">
+      <c r="H75" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I75" s="15" t="n"/>
@@ -10395,7 +10433,7 @@
       <c r="O75" s="15" t="n"/>
       <c r="P75" s="15" t="n"/>
       <c r="Q75" s="15" t="n"/>
-      <c r="R75" s="15" t="inlineStr">
+      <c r="R75" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10445,12 +10483,12 @@
         <f>HYPERLINK("https://youtu.be/cz75wI3fz7k","watch")</f>
         <v/>
       </c>
-      <c r="G76" s="15" t="inlineStr">
+      <c r="G76" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H76" s="15" t="n">
+      <c r="H76" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I76" s="15" t="n"/>
@@ -10462,7 +10500,7 @@
       <c r="O76" s="15" t="n"/>
       <c r="P76" s="15" t="n"/>
       <c r="Q76" s="15" t="n"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="R76" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10512,7 +10550,7 @@
         <f>HYPERLINK("https://youtu.be/czBVJAWDB8U","watch")</f>
         <v/>
       </c>
-      <c r="G77" s="15" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -10527,7 +10565,7 @@
       <c r="O77" s="15" t="n"/>
       <c r="P77" s="15" t="n"/>
       <c r="Q77" s="15" t="n"/>
-      <c r="R77" s="15" t="inlineStr">
+      <c r="R77" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -10536,13 +10574,13 @@
         <f>SUM(H77,J77,L77,N77,P77)</f>
         <v/>
       </c>
-      <c r="T77" s="15" t="inlineStr">
+      <c r="T77" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U77" s="15" t="n"/>
-      <c r="V77" s="15" t="inlineStr">
+      <c r="V77" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -10596,7 +10634,7 @@
       <c r="O78" s="15" t="n"/>
       <c r="P78" s="15" t="n"/>
       <c r="Q78" s="15" t="n"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="R78" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -10605,13 +10643,13 @@
         <f>SUM(H78,J78,L78,N78,P78)</f>
         <v/>
       </c>
-      <c r="T78" s="15" t="inlineStr">
+      <c r="T78" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U78" s="15" t="n"/>
-      <c r="V78" s="15" t="inlineStr">
+      <c r="V78" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -10654,7 +10692,7 @@
         <f>HYPERLINK("https://youtu.be/7nGg08wavGM","watch")</f>
         <v/>
       </c>
-      <c r="G79" s="15" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -10669,7 +10707,7 @@
       <c r="O79" s="15" t="n"/>
       <c r="P79" s="15" t="n"/>
       <c r="Q79" s="15" t="n"/>
-      <c r="R79" s="15" t="inlineStr">
+      <c r="R79" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -10678,13 +10716,13 @@
         <f>SUM(H79,J79,L79,N79,P79)</f>
         <v/>
       </c>
-      <c r="T79" s="15" t="inlineStr">
+      <c r="T79" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U79" s="15" t="n"/>
-      <c r="V79" s="15" t="inlineStr">
+      <c r="V79" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -10738,7 +10776,7 @@
       <c r="O80" s="15" t="n"/>
       <c r="P80" s="15" t="n"/>
       <c r="Q80" s="15" t="n"/>
-      <c r="R80" s="15" t="inlineStr">
+      <c r="R80" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -10747,13 +10785,13 @@
         <f>SUM(H80,J80,L80,N80,P80)</f>
         <v/>
       </c>
-      <c r="T80" s="15" t="inlineStr">
+      <c r="T80" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U80" s="15" t="n"/>
-      <c r="V80" s="15" t="inlineStr">
+      <c r="V80" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -10796,12 +10834,12 @@
         <f>HYPERLINK("https://youtu.be/Mhz1-_ppwJA","watch")</f>
         <v/>
       </c>
-      <c r="G81" s="15" t="inlineStr">
+      <c r="G81" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H81" s="15" t="n">
+      <c r="H81" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I81" s="15" t="n"/>
@@ -10813,7 +10851,7 @@
       <c r="O81" s="15" t="n"/>
       <c r="P81" s="15" t="n"/>
       <c r="Q81" s="15" t="n"/>
-      <c r="R81" s="15" t="inlineStr">
+      <c r="R81" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10863,12 +10901,12 @@
         <f>HYPERLINK("https://youtu.be/dqC9lAiWeaE","watch")</f>
         <v/>
       </c>
-      <c r="G82" s="15" t="inlineStr">
+      <c r="G82" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H82" s="15" t="n">
+      <c r="H82" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I82" s="15" t="n"/>
@@ -10880,7 +10918,7 @@
       <c r="O82" s="15" t="n"/>
       <c r="P82" s="15" t="n"/>
       <c r="Q82" s="15" t="n"/>
-      <c r="R82" s="15" t="inlineStr">
+      <c r="R82" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -10941,7 +10979,7 @@
       <c r="O83" s="15" t="n"/>
       <c r="P83" s="15" t="n"/>
       <c r="Q83" s="15" t="n"/>
-      <c r="R83" s="15" t="inlineStr">
+      <c r="R83" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -10950,13 +10988,13 @@
         <f>SUM(H83,J83,L83,N83,P83)</f>
         <v/>
       </c>
-      <c r="T83" s="15" t="inlineStr">
+      <c r="T83" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U83" s="15" t="n"/>
-      <c r="V83" s="15" t="inlineStr">
+      <c r="V83" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -10999,7 +11037,7 @@
         <f>HYPERLINK("https://youtu.be/r4WG2IWWyKc","watch")</f>
         <v/>
       </c>
-      <c r="G84" s="15" t="inlineStr">
+      <c r="G84" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -11014,7 +11052,7 @@
       <c r="O84" s="15" t="n"/>
       <c r="P84" s="15" t="n"/>
       <c r="Q84" s="15" t="n"/>
-      <c r="R84" s="15" t="inlineStr">
+      <c r="R84" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11023,13 +11061,13 @@
         <f>SUM(H84,J84,L84,N84,P84)</f>
         <v/>
       </c>
-      <c r="T84" s="15" t="inlineStr">
+      <c r="T84" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U84" s="15" t="n"/>
-      <c r="V84" s="15" t="inlineStr">
+      <c r="V84" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -11083,7 +11121,7 @@
       <c r="O85" s="15" t="n"/>
       <c r="P85" s="15" t="n"/>
       <c r="Q85" s="15" t="n"/>
-      <c r="R85" s="15" t="inlineStr">
+      <c r="R85" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11092,13 +11130,13 @@
         <f>SUM(H85,J85,L85,N85,P85)</f>
         <v/>
       </c>
-      <c r="T85" s="15" t="inlineStr">
+      <c r="T85" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U85" s="15" t="n"/>
-      <c r="V85" s="15" t="inlineStr">
+      <c r="V85" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -11141,7 +11179,7 @@
         <f>HYPERLINK("https://youtu.be/qKiLbaLhdp8","watch")</f>
         <v/>
       </c>
-      <c r="G86" s="15" t="inlineStr">
+      <c r="G86" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -11156,7 +11194,7 @@
       <c r="O86" s="15" t="n"/>
       <c r="P86" s="15" t="n"/>
       <c r="Q86" s="15" t="n"/>
-      <c r="R86" s="15" t="inlineStr">
+      <c r="R86" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11165,13 +11203,13 @@
         <f>SUM(H86,J86,L86,N86,P86)</f>
         <v/>
       </c>
-      <c r="T86" s="15" t="inlineStr">
+      <c r="T86" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U86" s="15" t="n"/>
-      <c r="V86" s="15" t="inlineStr">
+      <c r="V86" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -11214,12 +11252,12 @@
         <f>HYPERLINK("https://youtu.be/QKYrh9l8BYA","watch")</f>
         <v/>
       </c>
-      <c r="G87" s="15" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H87" s="15" t="n">
+      <c r="H87" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I87" s="15" t="n"/>
@@ -11231,7 +11269,7 @@
       <c r="O87" s="15" t="n"/>
       <c r="P87" s="15" t="n"/>
       <c r="Q87" s="15" t="n"/>
-      <c r="R87" s="15" t="inlineStr">
+      <c r="R87" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11281,7 +11319,7 @@
         <f>HYPERLINK("https://youtu.be/_Bu9zCfLI4c","watch")</f>
         <v/>
       </c>
-      <c r="G88" s="15" t="inlineStr">
+      <c r="G88" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -11296,7 +11334,7 @@
       <c r="O88" s="15" t="n"/>
       <c r="P88" s="15" t="n"/>
       <c r="Q88" s="15" t="n"/>
-      <c r="R88" s="15" t="inlineStr">
+      <c r="R88" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11346,12 +11384,12 @@
         <f>HYPERLINK("https://youtu.be/vqp2qrq1hls","watch")</f>
         <v/>
       </c>
-      <c r="G89" s="15" t="inlineStr">
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H89" s="15" t="n">
+      <c r="H89" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I89" s="15" t="n"/>
@@ -11363,7 +11401,7 @@
       <c r="O89" s="15" t="n"/>
       <c r="P89" s="15" t="n"/>
       <c r="Q89" s="15" t="n"/>
-      <c r="R89" s="15" t="inlineStr">
+      <c r="R89" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11424,7 +11462,7 @@
       <c r="O90" s="15" t="n"/>
       <c r="P90" s="15" t="n"/>
       <c r="Q90" s="15" t="n"/>
-      <c r="R90" s="15" t="inlineStr">
+      <c r="R90" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11474,12 +11512,12 @@
         <f>HYPERLINK("https://youtu.be/4gBo585VhEI","watch")</f>
         <v/>
       </c>
-      <c r="G91" s="15" t="inlineStr">
+      <c r="G91" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H91" s="15" t="n">
+      <c r="H91" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I91" s="15" t="n"/>
@@ -11491,7 +11529,7 @@
       <c r="O91" s="15" t="n"/>
       <c r="P91" s="15" t="n"/>
       <c r="Q91" s="15" t="n"/>
-      <c r="R91" s="15" t="inlineStr">
+      <c r="R91" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11552,7 +11590,7 @@
       <c r="O92" s="15" t="n"/>
       <c r="P92" s="15" t="n"/>
       <c r="Q92" s="15" t="n"/>
-      <c r="R92" s="15" t="inlineStr">
+      <c r="R92" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11602,12 +11640,12 @@
         <f>HYPERLINK("https://youtu.be/goGNPoBWQ-g","watch")</f>
         <v/>
       </c>
-      <c r="G93" s="15" t="inlineStr">
+      <c r="G93" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H93" s="15" t="n">
+      <c r="H93" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I93" s="15" t="n"/>
@@ -11619,7 +11657,7 @@
       <c r="O93" s="15" t="n"/>
       <c r="P93" s="15" t="n"/>
       <c r="Q93" s="15" t="n"/>
-      <c r="R93" s="15" t="inlineStr">
+      <c r="R93" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11669,7 +11707,7 @@
         <f>HYPERLINK("https://youtu.be/Fgj5afnnXVk","watch")</f>
         <v/>
       </c>
-      <c r="G94" s="15" t="inlineStr">
+      <c r="G94" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -11684,7 +11722,7 @@
       <c r="O94" s="15" t="n"/>
       <c r="P94" s="15" t="n"/>
       <c r="Q94" s="15" t="n"/>
-      <c r="R94" s="15" t="inlineStr">
+      <c r="R94" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11734,12 +11772,12 @@
         <f>HYPERLINK("https://youtu.be/u7xNNfIBEjg","watch")</f>
         <v/>
       </c>
-      <c r="G95" s="15" t="inlineStr">
+      <c r="G95" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H95" s="15" t="n">
+      <c r="H95" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I95" s="15" t="n"/>
@@ -11751,7 +11789,7 @@
       <c r="O95" s="15" t="n"/>
       <c r="P95" s="15" t="n"/>
       <c r="Q95" s="15" t="n"/>
-      <c r="R95" s="15" t="inlineStr">
+      <c r="R95" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11801,12 +11839,12 @@
         <f>HYPERLINK("https://youtu.be/bpm7cSVXNiM","watch")</f>
         <v/>
       </c>
-      <c r="G96" s="15" t="inlineStr">
+      <c r="G96" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H96" s="15" t="n">
+      <c r="H96" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I96" s="15" t="n"/>
@@ -11818,7 +11856,7 @@
       <c r="O96" s="15" t="n"/>
       <c r="P96" s="15" t="n"/>
       <c r="Q96" s="15" t="n"/>
-      <c r="R96" s="15" t="inlineStr">
+      <c r="R96" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -11868,7 +11906,7 @@
         <f>HYPERLINK("https://youtu.be/urvau7lIwC0","watch")</f>
         <v/>
       </c>
-      <c r="G97" s="15" t="inlineStr">
+      <c r="G97" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
@@ -11883,7 +11921,7 @@
       <c r="O97" s="15" t="n"/>
       <c r="P97" s="15" t="n"/>
       <c r="Q97" s="15" t="n"/>
-      <c r="R97" s="15" t="inlineStr">
+      <c r="R97" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -11892,13 +11930,13 @@
         <f>SUM(H97,J97,L97,N97,P97)</f>
         <v/>
       </c>
-      <c r="T97" s="15" t="inlineStr">
+      <c r="T97" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U97" s="15" t="n"/>
-      <c r="V97" s="15" t="inlineStr">
+      <c r="V97" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -11941,12 +11979,12 @@
         <f>HYPERLINK("https://youtu.be/tuX1t8p29Ik","watch")</f>
         <v/>
       </c>
-      <c r="G98" s="15" t="inlineStr">
+      <c r="G98" s="14" t="inlineStr">
         <is>
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H98" s="15" t="n">
+      <c r="H98" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I98" s="15" t="n"/>
@@ -11958,7 +11996,7 @@
       <c r="O98" s="15" t="n"/>
       <c r="P98" s="15" t="n"/>
       <c r="Q98" s="15" t="n"/>
-      <c r="R98" s="15" t="inlineStr">
+      <c r="R98" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -12008,13 +12046,13 @@
         <f>HYPERLINK("https://youtu.be/HGlF3-fpycc","watch")</f>
         <v/>
       </c>
-      <c r="G99" s="15" t="inlineStr">
+      <c r="G99" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="H99" s="15" t="n"/>
-      <c r="I99" s="15" t="inlineStr">
+      <c r="I99" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -12027,7 +12065,7 @@
       <c r="O99" s="15" t="n"/>
       <c r="P99" s="15" t="n"/>
       <c r="Q99" s="15" t="n"/>
-      <c r="R99" s="15" t="inlineStr">
+      <c r="R99" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -12036,13 +12074,13 @@
         <f>SUM(H99,J99,L99,N99,P99)</f>
         <v/>
       </c>
-      <c r="T99" s="15" t="inlineStr">
+      <c r="T99" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U99" s="15" t="n"/>
-      <c r="V99" s="15" t="inlineStr">
+      <c r="V99" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -12085,12 +12123,12 @@
         <f>HYPERLINK("https://youtu.be/R4TUGTf0Eb4","watch")</f>
         <v/>
       </c>
-      <c r="G100" s="15" t="inlineStr">
+      <c r="G100" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H100" s="15" t="n">
+      <c r="H100" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I100" s="15" t="n"/>
@@ -12102,7 +12140,7 @@
       <c r="O100" s="15" t="n"/>
       <c r="P100" s="15" t="n"/>
       <c r="Q100" s="15" t="n"/>
-      <c r="R100" s="15" t="inlineStr">
+      <c r="R100" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -12152,13 +12190,13 @@
         <f>HYPERLINK("https://youtu.be/sS0fvyss7IM","watch")</f>
         <v/>
       </c>
-      <c r="G101" s="15" t="inlineStr">
+      <c r="G101" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="H101" s="15" t="n"/>
-      <c r="I101" s="15" t="inlineStr">
+      <c r="I101" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
@@ -12171,7 +12209,7 @@
       <c r="O101" s="15" t="n"/>
       <c r="P101" s="15" t="n"/>
       <c r="Q101" s="15" t="n"/>
-      <c r="R101" s="15" t="inlineStr">
+      <c r="R101" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -12232,7 +12270,7 @@
       <c r="O102" s="15" t="n"/>
       <c r="P102" s="15" t="n"/>
       <c r="Q102" s="15" t="n"/>
-      <c r="R102" s="15" t="inlineStr">
+      <c r="R102" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -12282,12 +12320,12 @@
         <f>HYPERLINK("https://youtu.be/XjM6y2L7v1c","watch")</f>
         <v/>
       </c>
-      <c r="G103" s="15" t="inlineStr">
+      <c r="G103" s="14" t="inlineStr">
         <is>
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H103" s="15" t="n">
+      <c r="H103" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I103" s="15" t="n"/>
@@ -12299,7 +12337,7 @@
       <c r="O103" s="15" t="n"/>
       <c r="P103" s="15" t="n"/>
       <c r="Q103" s="15" t="n"/>
-      <c r="R103" s="15" t="inlineStr">
+      <c r="R103" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -12349,12 +12387,12 @@
         <f>HYPERLINK("https://youtu.be/0vpWimyqJIE","watch")</f>
         <v/>
       </c>
-      <c r="G104" s="15" t="inlineStr">
+      <c r="G104" s="14" t="inlineStr">
         <is>
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H104" s="15" t="n">
+      <c r="H104" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I104" s="15" t="n"/>
@@ -12366,7 +12404,7 @@
       <c r="O104" s="15" t="n"/>
       <c r="P104" s="15" t="n"/>
       <c r="Q104" s="15" t="n"/>
-      <c r="R104" s="15" t="inlineStr">
+      <c r="R104" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -12416,12 +12454,12 @@
         <f>HYPERLINK("https://youtu.be/udV4EBssAj0","watch")</f>
         <v/>
       </c>
-      <c r="G105" s="15" t="inlineStr">
+      <c r="G105" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H105" s="15" t="n">
+      <c r="H105" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I105" s="15" t="n"/>
@@ -12433,7 +12471,7 @@
       <c r="O105" s="15" t="n"/>
       <c r="P105" s="15" t="n"/>
       <c r="Q105" s="15" t="n"/>
-      <c r="R105" s="15" t="inlineStr">
+      <c r="R105" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -12483,12 +12521,12 @@
         <f>HYPERLINK("https://youtu.be/xCDigA8yq1Y","watch")</f>
         <v/>
       </c>
-      <c r="G106" s="15" t="inlineStr">
+      <c r="G106" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H106" s="15" t="n">
+      <c r="H106" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I106" s="15" t="n"/>
@@ -12500,7 +12538,7 @@
       <c r="O106" s="15" t="n"/>
       <c r="P106" s="15" t="n"/>
       <c r="Q106" s="15" t="n"/>
-      <c r="R106" s="15" t="inlineStr">
+      <c r="R106" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -12561,7 +12599,7 @@
       <c r="O107" s="15" t="n"/>
       <c r="P107" s="15" t="n"/>
       <c r="Q107" s="15" t="n"/>
-      <c r="R107" s="15" t="inlineStr">
+      <c r="R107" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -12622,7 +12660,7 @@
       <c r="O108" s="15" t="n"/>
       <c r="P108" s="15" t="n"/>
       <c r="Q108" s="15" t="n"/>
-      <c r="R108" s="15" t="inlineStr">
+      <c r="R108" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -12672,12 +12710,12 @@
         <f>HYPERLINK("https://youtu.be/EKTgIGCiET4","watch")</f>
         <v/>
       </c>
-      <c r="G109" s="15" t="inlineStr">
+      <c r="G109" s="14" t="inlineStr">
         <is>
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H109" s="15" t="n">
+      <c r="H109" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I109" s="15" t="n"/>
@@ -12689,7 +12727,7 @@
       <c r="O109" s="15" t="n"/>
       <c r="P109" s="15" t="n"/>
       <c r="Q109" s="15" t="n"/>
-      <c r="R109" s="15" t="inlineStr">
+      <c r="R109" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -12739,12 +12777,12 @@
         <f>HYPERLINK("https://youtu.be/-eQ-tG_cj_0","watch")</f>
         <v/>
       </c>
-      <c r="G110" s="15" t="inlineStr">
+      <c r="G110" s="14" t="inlineStr">
         <is>
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H110" s="15" t="n">
+      <c r="H110" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I110" s="15" t="n"/>
@@ -12756,7 +12794,7 @@
       <c r="O110" s="15" t="n"/>
       <c r="P110" s="15" t="n"/>
       <c r="Q110" s="15" t="n"/>
-      <c r="R110" s="15" t="inlineStr">
+      <c r="R110" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -12806,12 +12844,12 @@
         <f>HYPERLINK("https://youtu.be/-5rVYfdxRJw","watch")</f>
         <v/>
       </c>
-      <c r="G111" s="15" t="inlineStr">
+      <c r="G111" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H111" s="15" t="n">
+      <c r="H111" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I111" s="15" t="n"/>
@@ -12823,7 +12861,7 @@
       <c r="O111" s="15" t="n"/>
       <c r="P111" s="15" t="n"/>
       <c r="Q111" s="15" t="n"/>
-      <c r="R111" s="15" t="inlineStr">
+      <c r="R111" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -12873,12 +12911,12 @@
         <f>HYPERLINK("https://youtu.be/1Kd_E966_4k","watch")</f>
         <v/>
       </c>
-      <c r="G112" s="15" t="inlineStr">
+      <c r="G112" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H112" s="15" t="n">
+      <c r="H112" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I112" s="15" t="n"/>
@@ -12890,7 +12928,7 @@
       <c r="O112" s="15" t="n"/>
       <c r="P112" s="15" t="n"/>
       <c r="Q112" s="15" t="n"/>
-      <c r="R112" s="15" t="inlineStr">
+      <c r="R112" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -12951,7 +12989,7 @@
       <c r="O113" s="15" t="n"/>
       <c r="P113" s="15" t="n"/>
       <c r="Q113" s="15" t="n"/>
-      <c r="R113" s="15" t="inlineStr">
+      <c r="R113" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -13001,12 +13039,12 @@
         <f>HYPERLINK("https://youtu.be/BiBdyozoD_Q","watch")</f>
         <v/>
       </c>
-      <c r="G114" s="15" t="inlineStr">
+      <c r="G114" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H114" s="15" t="n">
+      <c r="H114" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I114" s="15" t="n"/>
@@ -13018,7 +13056,7 @@
       <c r="O114" s="15" t="n"/>
       <c r="P114" s="15" t="n"/>
       <c r="Q114" s="15" t="n"/>
-      <c r="R114" s="15" t="inlineStr">
+      <c r="R114" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13079,7 +13117,7 @@
       <c r="O115" s="15" t="n"/>
       <c r="P115" s="15" t="n"/>
       <c r="Q115" s="15" t="n"/>
-      <c r="R115" s="15" t="inlineStr">
+      <c r="R115" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -13129,12 +13167,12 @@
         <f>HYPERLINK("https://youtu.be/7qgnakc3__c","watch")</f>
         <v/>
       </c>
-      <c r="G116" s="15" t="inlineStr">
+      <c r="G116" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H116" s="15" t="n">
+      <c r="H116" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I116" s="15" t="n"/>
@@ -13146,7 +13184,7 @@
       <c r="O116" s="15" t="n"/>
       <c r="P116" s="15" t="n"/>
       <c r="Q116" s="15" t="n"/>
-      <c r="R116" s="15" t="inlineStr">
+      <c r="R116" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13196,12 +13234,12 @@
         <f>HYPERLINK("https://youtu.be/l_vpvsLXG50","watch")</f>
         <v/>
       </c>
-      <c r="G117" s="15" t="inlineStr">
+      <c r="G117" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H117" s="15" t="n">
+      <c r="H117" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I117" s="15" t="n"/>
@@ -13213,7 +13251,7 @@
       <c r="O117" s="15" t="n"/>
       <c r="P117" s="15" t="n"/>
       <c r="Q117" s="15" t="n"/>
-      <c r="R117" s="15" t="inlineStr">
+      <c r="R117" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13263,12 +13301,12 @@
         <f>HYPERLINK("https://youtu.be/23RED_g8uOE","watch")</f>
         <v/>
       </c>
-      <c r="G118" s="15" t="inlineStr">
+      <c r="G118" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H118" s="15" t="n">
+      <c r="H118" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I118" s="15" t="n"/>
@@ -13280,7 +13318,7 @@
       <c r="O118" s="15" t="n"/>
       <c r="P118" s="15" t="n"/>
       <c r="Q118" s="15" t="n"/>
-      <c r="R118" s="15" t="inlineStr">
+      <c r="R118" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13330,12 +13368,12 @@
         <f>HYPERLINK("https://youtu.be/qUzKnP4zmjM","watch")</f>
         <v/>
       </c>
-      <c r="G119" s="15" t="inlineStr">
+      <c r="G119" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H119" s="15" t="n">
+      <c r="H119" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I119" s="15" t="n"/>
@@ -13347,7 +13385,7 @@
       <c r="O119" s="15" t="n"/>
       <c r="P119" s="15" t="n"/>
       <c r="Q119" s="15" t="n"/>
-      <c r="R119" s="15" t="inlineStr">
+      <c r="R119" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13397,12 +13435,12 @@
         <f>HYPERLINK("https://youtu.be/vW8lkXEx3Ao","watch")</f>
         <v/>
       </c>
-      <c r="G120" s="15" t="inlineStr">
+      <c r="G120" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H120" s="15" t="n">
+      <c r="H120" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I120" s="15" t="n"/>
@@ -13414,7 +13452,7 @@
       <c r="O120" s="15" t="n"/>
       <c r="P120" s="15" t="n"/>
       <c r="Q120" s="15" t="n"/>
-      <c r="R120" s="15" t="inlineStr">
+      <c r="R120" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13464,12 +13502,12 @@
         <f>HYPERLINK("https://youtu.be/16GEn7wSyuk","watch")</f>
         <v/>
       </c>
-      <c r="G121" s="15" t="inlineStr">
+      <c r="G121" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H121" s="15" t="n">
+      <c r="H121" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I121" s="15" t="n"/>
@@ -13481,7 +13519,7 @@
       <c r="O121" s="15" t="n"/>
       <c r="P121" s="15" t="n"/>
       <c r="Q121" s="15" t="n"/>
-      <c r="R121" s="15" t="inlineStr">
+      <c r="R121" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13531,12 +13569,12 @@
         <f>HYPERLINK("https://youtu.be/i_YeXB489EY","watch")</f>
         <v/>
       </c>
-      <c r="G122" s="15" t="inlineStr">
+      <c r="G122" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H122" s="15" t="n">
+      <c r="H122" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I122" s="15" t="n"/>
@@ -13548,7 +13586,7 @@
       <c r="O122" s="15" t="n"/>
       <c r="P122" s="15" t="n"/>
       <c r="Q122" s="15" t="n"/>
-      <c r="R122" s="15" t="inlineStr">
+      <c r="R122" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13598,12 +13636,12 @@
         <f>HYPERLINK("https://youtu.be/wtUPdMnZ_S8","watch")</f>
         <v/>
       </c>
-      <c r="G123" s="15" t="inlineStr">
+      <c r="G123" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H123" s="15" t="n">
+      <c r="H123" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I123" s="15" t="n"/>
@@ -13615,7 +13653,7 @@
       <c r="O123" s="15" t="n"/>
       <c r="P123" s="15" t="n"/>
       <c r="Q123" s="15" t="n"/>
-      <c r="R123" s="15" t="inlineStr">
+      <c r="R123" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13665,12 +13703,12 @@
         <f>HYPERLINK("https://youtu.be/Y6rNMk6_kFs","watch")</f>
         <v/>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G124" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H124" s="15" t="n">
+      <c r="H124" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I124" s="15" t="n"/>
@@ -13682,7 +13720,7 @@
       <c r="O124" s="15" t="n"/>
       <c r="P124" s="15" t="n"/>
       <c r="Q124" s="15" t="n"/>
-      <c r="R124" s="15" t="inlineStr">
+      <c r="R124" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13732,12 +13770,12 @@
         <f>HYPERLINK("https://youtu.be/iPxD2pp1zHo","watch")</f>
         <v/>
       </c>
-      <c r="G125" s="15" t="inlineStr">
+      <c r="G125" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H125" s="15" t="n">
+      <c r="H125" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I125" s="15" t="n"/>
@@ -13749,7 +13787,7 @@
       <c r="O125" s="15" t="n"/>
       <c r="P125" s="15" t="n"/>
       <c r="Q125" s="15" t="n"/>
-      <c r="R125" s="15" t="inlineStr">
+      <c r="R125" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13799,12 +13837,12 @@
         <f>HYPERLINK("https://youtu.be/jAkffPVM-JA","watch")</f>
         <v/>
       </c>
-      <c r="G126" s="15" t="inlineStr">
+      <c r="G126" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H126" s="15" t="n">
+      <c r="H126" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I126" s="15" t="n"/>
@@ -13816,7 +13854,7 @@
       <c r="O126" s="15" t="n"/>
       <c r="P126" s="15" t="n"/>
       <c r="Q126" s="15" t="n"/>
-      <c r="R126" s="15" t="inlineStr">
+      <c r="R126" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13866,12 +13904,12 @@
         <f>HYPERLINK("https://youtu.be/c-5u5X8BT_Y","watch")</f>
         <v/>
       </c>
-      <c r="G127" s="15" t="inlineStr">
+      <c r="G127" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H127" s="15" t="n">
+      <c r="H127" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I127" s="15" t="n"/>
@@ -13883,7 +13921,7 @@
       <c r="O127" s="15" t="n"/>
       <c r="P127" s="15" t="n"/>
       <c r="Q127" s="15" t="n"/>
-      <c r="R127" s="15" t="inlineStr">
+      <c r="R127" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -13933,12 +13971,12 @@
         <f>HYPERLINK("https://youtu.be/JPzh3KWw084","watch")</f>
         <v/>
       </c>
-      <c r="G128" s="15" t="inlineStr">
+      <c r="G128" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H128" s="15" t="n">
+      <c r="H128" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I128" s="15" t="n"/>
@@ -13950,7 +13988,7 @@
       <c r="O128" s="15" t="n"/>
       <c r="P128" s="15" t="n"/>
       <c r="Q128" s="15" t="n"/>
-      <c r="R128" s="15" t="inlineStr">
+      <c r="R128" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14000,12 +14038,12 @@
         <f>HYPERLINK("https://youtu.be/xJyZLladJ0Q","watch")</f>
         <v/>
       </c>
-      <c r="G129" s="15" t="inlineStr">
+      <c r="G129" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H129" s="15" t="n">
+      <c r="H129" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I129" s="15" t="n"/>
@@ -14017,7 +14055,7 @@
       <c r="O129" s="15" t="n"/>
       <c r="P129" s="15" t="n"/>
       <c r="Q129" s="15" t="n"/>
-      <c r="R129" s="15" t="inlineStr">
+      <c r="R129" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14067,12 +14105,12 @@
         <f>HYPERLINK("https://youtu.be/APS_RnpORC8","watch")</f>
         <v/>
       </c>
-      <c r="G130" s="15" t="inlineStr">
+      <c r="G130" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H130" s="15" t="n">
+      <c r="H130" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I130" s="15" t="n"/>
@@ -14084,7 +14122,7 @@
       <c r="O130" s="15" t="n"/>
       <c r="P130" s="15" t="n"/>
       <c r="Q130" s="15" t="n"/>
-      <c r="R130" s="15" t="inlineStr">
+      <c r="R130" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14134,12 +14172,12 @@
         <f>HYPERLINK("https://youtu.be/kcmXPW6_Odo","watch")</f>
         <v/>
       </c>
-      <c r="G131" s="15" t="inlineStr">
+      <c r="G131" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H131" s="15" t="n">
+      <c r="H131" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I131" s="15" t="n"/>
@@ -14151,7 +14189,7 @@
       <c r="O131" s="15" t="n"/>
       <c r="P131" s="15" t="n"/>
       <c r="Q131" s="15" t="n"/>
-      <c r="R131" s="15" t="inlineStr">
+      <c r="R131" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14201,12 +14239,12 @@
         <f>HYPERLINK("https://youtu.be/xrJFDqGZjOs","watch")</f>
         <v/>
       </c>
-      <c r="G132" s="15" t="inlineStr">
+      <c r="G132" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H132" s="15" t="n">
+      <c r="H132" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I132" s="15" t="n"/>
@@ -14218,7 +14256,7 @@
       <c r="O132" s="15" t="n"/>
       <c r="P132" s="15" t="n"/>
       <c r="Q132" s="15" t="n"/>
-      <c r="R132" s="15" t="inlineStr">
+      <c r="R132" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14268,12 +14306,12 @@
         <f>HYPERLINK("https://youtu.be/CT5t8mKeZUw","watch")</f>
         <v/>
       </c>
-      <c r="G133" s="15" t="inlineStr">
+      <c r="G133" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H133" s="15" t="n">
+      <c r="H133" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I133" s="15" t="n"/>
@@ -14285,7 +14323,7 @@
       <c r="O133" s="15" t="n"/>
       <c r="P133" s="15" t="n"/>
       <c r="Q133" s="15" t="n"/>
-      <c r="R133" s="15" t="inlineStr">
+      <c r="R133" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -14294,13 +14332,13 @@
         <f>SUM(H133,J133,L133,N133,P133)</f>
         <v/>
       </c>
-      <c r="T133" s="15" t="inlineStr">
+      <c r="T133" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U133" s="15" t="n"/>
-      <c r="V133" s="15" t="inlineStr">
+      <c r="V133" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -14343,12 +14381,12 @@
         <f>HYPERLINK("https://youtu.be/W2eIV9tya84","watch")</f>
         <v/>
       </c>
-      <c r="G134" s="15" t="inlineStr">
+      <c r="G134" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H134" s="15" t="n">
+      <c r="H134" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I134" s="15" t="n"/>
@@ -14360,7 +14398,7 @@
       <c r="O134" s="15" t="n"/>
       <c r="P134" s="15" t="n"/>
       <c r="Q134" s="15" t="n"/>
-      <c r="R134" s="15" t="inlineStr">
+      <c r="R134" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14410,12 +14448,12 @@
         <f>HYPERLINK("https://youtu.be/2wZwMWDlxP0","watch")</f>
         <v/>
       </c>
-      <c r="G135" s="15" t="inlineStr">
+      <c r="G135" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H135" s="15" t="n">
+      <c r="H135" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I135" s="15" t="n"/>
@@ -14427,7 +14465,7 @@
       <c r="O135" s="15" t="n"/>
       <c r="P135" s="15" t="n"/>
       <c r="Q135" s="15" t="n"/>
-      <c r="R135" s="15" t="inlineStr">
+      <c r="R135" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -14436,13 +14474,13 @@
         <f>SUM(H135,J135,L135,N135,P135)</f>
         <v/>
       </c>
-      <c r="T135" s="15" t="inlineStr">
+      <c r="T135" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U135" s="15" t="n"/>
-      <c r="V135" s="15" t="inlineStr">
+      <c r="V135" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -14485,12 +14523,12 @@
         <f>HYPERLINK("https://youtu.be/hbUa4l-xono","watch")</f>
         <v/>
       </c>
-      <c r="G136" s="15" t="inlineStr">
+      <c r="G136" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H136" s="15" t="n">
+      <c r="H136" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I136" s="15" t="n"/>
@@ -14502,7 +14540,7 @@
       <c r="O136" s="15" t="n"/>
       <c r="P136" s="15" t="n"/>
       <c r="Q136" s="15" t="n"/>
-      <c r="R136" s="15" t="inlineStr">
+      <c r="R136" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -14511,13 +14549,13 @@
         <f>SUM(H136,J136,L136,N136,P136)</f>
         <v/>
       </c>
-      <c r="T136" s="15" t="inlineStr">
+      <c r="T136" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U136" s="15" t="n"/>
-      <c r="V136" s="15" t="inlineStr">
+      <c r="V136" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -14560,12 +14598,12 @@
         <f>HYPERLINK("https://youtu.be/Q26NJsmeVko","watch")</f>
         <v/>
       </c>
-      <c r="G137" s="15" t="inlineStr">
+      <c r="G137" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H137" s="15" t="n">
+      <c r="H137" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I137" s="15" t="n"/>
@@ -14577,7 +14615,7 @@
       <c r="O137" s="15" t="n"/>
       <c r="P137" s="15" t="n"/>
       <c r="Q137" s="15" t="n"/>
-      <c r="R137" s="15" t="inlineStr">
+      <c r="R137" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -14586,13 +14624,13 @@
         <f>SUM(H137,J137,L137,N137,P137)</f>
         <v/>
       </c>
-      <c r="T137" s="15" t="inlineStr">
+      <c r="T137" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U137" s="15" t="n"/>
-      <c r="V137" s="15" t="inlineStr">
+      <c r="V137" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -14635,12 +14673,12 @@
         <f>HYPERLINK("https://youtu.be/c7J6-dTu4jo","watch")</f>
         <v/>
       </c>
-      <c r="G138" s="15" t="inlineStr">
+      <c r="G138" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H138" s="15" t="n">
+      <c r="H138" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I138" s="15" t="n"/>
@@ -14652,7 +14690,7 @@
       <c r="O138" s="15" t="n"/>
       <c r="P138" s="15" t="n"/>
       <c r="Q138" s="15" t="n"/>
-      <c r="R138" s="15" t="inlineStr">
+      <c r="R138" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -14661,13 +14699,13 @@
         <f>SUM(H138,J138,L138,N138,P138)</f>
         <v/>
       </c>
-      <c r="T138" s="15" t="inlineStr">
+      <c r="T138" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U138" s="15" t="n"/>
-      <c r="V138" s="15" t="inlineStr">
+      <c r="V138" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -14710,12 +14748,12 @@
         <f>HYPERLINK("https://youtu.be/dFIdg1ZRxDM","watch")</f>
         <v/>
       </c>
-      <c r="G139" s="15" t="inlineStr">
+      <c r="G139" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H139" s="15" t="n">
+      <c r="H139" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I139" s="15" t="n"/>
@@ -14727,7 +14765,7 @@
       <c r="O139" s="15" t="n"/>
       <c r="P139" s="15" t="n"/>
       <c r="Q139" s="15" t="n"/>
-      <c r="R139" s="15" t="inlineStr">
+      <c r="R139" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -14777,12 +14815,12 @@
         <f>HYPERLINK("https://youtu.be/CP7sMGF3p3M","watch")</f>
         <v/>
       </c>
-      <c r="G140" s="15" t="inlineStr">
+      <c r="G140" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H140" s="15" t="n">
+      <c r="H140" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I140" s="15" t="n"/>
@@ -14794,7 +14832,7 @@
       <c r="O140" s="15" t="n"/>
       <c r="P140" s="15" t="n"/>
       <c r="Q140" s="15" t="n"/>
-      <c r="R140" s="15" t="inlineStr">
+      <c r="R140" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -14844,12 +14882,12 @@
         <f>HYPERLINK("https://youtu.be/25YT9cNRpqk","watch")</f>
         <v/>
       </c>
-      <c r="G141" s="15" t="inlineStr">
+      <c r="G141" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H141" s="15" t="n">
+      <c r="H141" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I141" s="15" t="n"/>
@@ -14861,7 +14899,7 @@
       <c r="O141" s="15" t="n"/>
       <c r="P141" s="15" t="n"/>
       <c r="Q141" s="15" t="n"/>
-      <c r="R141" s="15" t="inlineStr">
+      <c r="R141" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -14870,13 +14908,13 @@
         <f>SUM(H141,J141,L141,N141,P141)</f>
         <v/>
       </c>
-      <c r="T141" s="15" t="inlineStr">
+      <c r="T141" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U141" s="15" t="n"/>
-      <c r="V141" s="15" t="inlineStr">
+      <c r="V141" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -14919,12 +14957,12 @@
         <f>HYPERLINK("https://youtu.be/e6vbNj4YRJI","watch")</f>
         <v/>
       </c>
-      <c r="G142" s="15" t="inlineStr">
+      <c r="G142" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H142" s="15" t="n">
+      <c r="H142" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I142" s="15" t="n"/>
@@ -14936,7 +14974,7 @@
       <c r="O142" s="15" t="n"/>
       <c r="P142" s="15" t="n"/>
       <c r="Q142" s="15" t="n"/>
-      <c r="R142" s="15" t="inlineStr">
+      <c r="R142" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -14986,12 +15024,12 @@
         <f>HYPERLINK("https://youtu.be/HS0sPhhG3jo","watch")</f>
         <v/>
       </c>
-      <c r="G143" s="15" t="inlineStr">
+      <c r="G143" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H143" s="15" t="n">
+      <c r="H143" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I143" s="15" t="n"/>
@@ -15003,7 +15041,7 @@
       <c r="O143" s="15" t="n"/>
       <c r="P143" s="15" t="n"/>
       <c r="Q143" s="15" t="n"/>
-      <c r="R143" s="15" t="inlineStr">
+      <c r="R143" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15053,12 +15091,12 @@
         <f>HYPERLINK("https://youtu.be/-jstsp3DQNI","watch")</f>
         <v/>
       </c>
-      <c r="G144" s="15" t="inlineStr">
+      <c r="G144" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H144" s="15" t="n">
+      <c r="H144" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I144" s="15" t="n"/>
@@ -15070,7 +15108,7 @@
       <c r="O144" s="15" t="n"/>
       <c r="P144" s="15" t="n"/>
       <c r="Q144" s="15" t="n"/>
-      <c r="R144" s="15" t="inlineStr">
+      <c r="R144" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15120,12 +15158,12 @@
         <f>HYPERLINK("https://youtu.be/cdvEaKdmjeU","watch")</f>
         <v/>
       </c>
-      <c r="G145" s="15" t="inlineStr">
+      <c r="G145" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H145" s="15" t="n">
+      <c r="H145" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I145" s="15" t="n"/>
@@ -15137,7 +15175,7 @@
       <c r="O145" s="15" t="n"/>
       <c r="P145" s="15" t="n"/>
       <c r="Q145" s="15" t="n"/>
-      <c r="R145" s="15" t="inlineStr">
+      <c r="R145" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15187,12 +15225,12 @@
         <f>HYPERLINK("https://youtu.be/h1vqc-37k_8","watch")</f>
         <v/>
       </c>
-      <c r="G146" s="15" t="inlineStr">
+      <c r="G146" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H146" s="15" t="n">
+      <c r="H146" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I146" s="15" t="n"/>
@@ -15204,7 +15242,7 @@
       <c r="O146" s="15" t="n"/>
       <c r="P146" s="15" t="n"/>
       <c r="Q146" s="15" t="n"/>
-      <c r="R146" s="15" t="inlineStr">
+      <c r="R146" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15254,12 +15292,12 @@
         <f>HYPERLINK("https://youtu.be/JM8wHAH8FEw","watch")</f>
         <v/>
       </c>
-      <c r="G147" s="15" t="inlineStr">
+      <c r="G147" s="14" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H147" s="15" t="n">
+      <c r="H147" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I147" s="15" t="n"/>
@@ -15271,7 +15309,7 @@
       <c r="O147" s="15" t="n"/>
       <c r="P147" s="15" t="n"/>
       <c r="Q147" s="15" t="n"/>
-      <c r="R147" s="15" t="inlineStr">
+      <c r="R147" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15321,12 +15359,12 @@
         <f>HYPERLINK("https://youtu.be/t_okfWNQ4BQ","watch")</f>
         <v/>
       </c>
-      <c r="G148" s="15" t="inlineStr">
+      <c r="G148" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H148" s="15" t="n">
+      <c r="H148" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I148" s="15" t="n"/>
@@ -15338,7 +15376,7 @@
       <c r="O148" s="15" t="n"/>
       <c r="P148" s="15" t="n"/>
       <c r="Q148" s="15" t="n"/>
-      <c r="R148" s="15" t="inlineStr">
+      <c r="R148" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -15347,13 +15385,13 @@
         <f>SUM(H148,J148,L148,N148,P148)</f>
         <v/>
       </c>
-      <c r="T148" s="15" t="inlineStr">
+      <c r="T148" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U148" s="15" t="n"/>
-      <c r="V148" s="15" t="inlineStr">
+      <c r="V148" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -15396,12 +15434,12 @@
         <f>HYPERLINK("https://youtu.be/1dkor9FBy7s","watch")</f>
         <v/>
       </c>
-      <c r="G149" s="15" t="inlineStr">
+      <c r="G149" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H149" s="15" t="n">
+      <c r="H149" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I149" s="15" t="n"/>
@@ -15413,7 +15451,7 @@
       <c r="O149" s="15" t="n"/>
       <c r="P149" s="15" t="n"/>
       <c r="Q149" s="15" t="n"/>
-      <c r="R149" s="15" t="inlineStr">
+      <c r="R149" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -15463,12 +15501,12 @@
         <f>HYPERLINK("https://youtu.be/FlMsxjakWcs","watch")</f>
         <v/>
       </c>
-      <c r="G150" s="15" t="inlineStr">
+      <c r="G150" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H150" s="15" t="n">
+      <c r="H150" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I150" s="15" t="n"/>
@@ -15480,7 +15518,7 @@
       <c r="O150" s="15" t="n"/>
       <c r="P150" s="15" t="n"/>
       <c r="Q150" s="15" t="n"/>
-      <c r="R150" s="15" t="inlineStr">
+      <c r="R150" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -15530,12 +15568,12 @@
         <f>HYPERLINK("https://youtu.be/1zqH_hRYFvo","watch")</f>
         <v/>
       </c>
-      <c r="G151" s="15" t="inlineStr">
+      <c r="G151" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H151" s="15" t="n">
+      <c r="H151" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I151" s="15" t="n"/>
@@ -15547,7 +15585,7 @@
       <c r="O151" s="15" t="n"/>
       <c r="P151" s="15" t="n"/>
       <c r="Q151" s="15" t="n"/>
-      <c r="R151" s="15" t="inlineStr">
+      <c r="R151" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15556,13 +15594,13 @@
         <f>SUM(H151,J151,L151,N151,P151)</f>
         <v/>
       </c>
-      <c r="T151" s="15" t="inlineStr">
+      <c r="T151" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U151" s="15" t="n"/>
-      <c r="V151" s="15" t="inlineStr">
+      <c r="V151" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -15605,12 +15643,12 @@
         <f>HYPERLINK("https://youtu.be/yJujjKbIVFg","watch")</f>
         <v/>
       </c>
-      <c r="G152" s="15" t="inlineStr">
+      <c r="G152" s="14" t="inlineStr">
         <is>
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H152" s="15" t="n">
+      <c r="H152" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I152" s="15" t="n"/>
@@ -15622,7 +15660,7 @@
       <c r="O152" s="15" t="n"/>
       <c r="P152" s="15" t="n"/>
       <c r="Q152" s="15" t="n"/>
-      <c r="R152" s="15" t="inlineStr">
+      <c r="R152" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -15672,12 +15710,12 @@
         <f>HYPERLINK("https://youtu.be/vZT6BI7EcQM","watch")</f>
         <v/>
       </c>
-      <c r="G153" s="15" t="inlineStr">
+      <c r="G153" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H153" s="15" t="n">
+      <c r="H153" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I153" s="15" t="n"/>
@@ -15689,7 +15727,7 @@
       <c r="O153" s="15" t="n"/>
       <c r="P153" s="15" t="n"/>
       <c r="Q153" s="15" t="n"/>
-      <c r="R153" s="15" t="inlineStr">
+      <c r="R153" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -15739,12 +15777,12 @@
         <f>HYPERLINK("https://youtu.be/lo_VtHulsWc","watch")</f>
         <v/>
       </c>
-      <c r="G154" s="15" t="inlineStr">
+      <c r="G154" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H154" s="15" t="n">
+      <c r="H154" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I154" s="15" t="n"/>
@@ -15756,7 +15794,7 @@
       <c r="O154" s="15" t="n"/>
       <c r="P154" s="15" t="n"/>
       <c r="Q154" s="15" t="n"/>
-      <c r="R154" s="15" t="inlineStr">
+      <c r="R154" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -15765,13 +15803,13 @@
         <f>SUM(H154,J154,L154,N154,P154)</f>
         <v/>
       </c>
-      <c r="T154" s="15" t="inlineStr">
+      <c r="T154" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U154" s="15" t="n"/>
-      <c r="V154" s="15" t="inlineStr">
+      <c r="V154" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -15814,12 +15852,12 @@
         <f>HYPERLINK("https://youtu.be/VjhleCTxCDA","watch")</f>
         <v/>
       </c>
-      <c r="G155" s="15" t="inlineStr">
+      <c r="G155" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H155" s="15" t="n">
+      <c r="H155" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I155" s="15" t="n"/>
@@ -15831,7 +15869,7 @@
       <c r="O155" s="15" t="n"/>
       <c r="P155" s="15" t="n"/>
       <c r="Q155" s="15" t="n"/>
-      <c r="R155" s="15" t="inlineStr">
+      <c r="R155" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -15840,13 +15878,13 @@
         <f>SUM(H155,J155,L155,N155,P155)</f>
         <v/>
       </c>
-      <c r="T155" s="15" t="inlineStr">
+      <c r="T155" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U155" s="15" t="n"/>
-      <c r="V155" s="15" t="inlineStr">
+      <c r="V155" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -15889,12 +15927,12 @@
         <f>HYPERLINK("https://youtu.be/uIAcSD4quE8","watch")</f>
         <v/>
       </c>
-      <c r="G156" s="15" t="inlineStr">
+      <c r="G156" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H156" s="15" t="n">
+      <c r="H156" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I156" s="15" t="n"/>
@@ -15906,7 +15944,7 @@
       <c r="O156" s="15" t="n"/>
       <c r="P156" s="15" t="n"/>
       <c r="Q156" s="15" t="n"/>
-      <c r="R156" s="15" t="inlineStr">
+      <c r="R156" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -15956,12 +15994,12 @@
         <f>HYPERLINK("https://youtu.be/76YEF7mdqvk","watch")</f>
         <v/>
       </c>
-      <c r="G157" s="15" t="inlineStr">
+      <c r="G157" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H157" s="15" t="n">
+      <c r="H157" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I157" s="15" t="n"/>
@@ -15973,7 +16011,7 @@
       <c r="O157" s="15" t="n"/>
       <c r="P157" s="15" t="n"/>
       <c r="Q157" s="15" t="n"/>
-      <c r="R157" s="15" t="inlineStr">
+      <c r="R157" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -16023,12 +16061,12 @@
         <f>HYPERLINK("https://youtu.be/5FJZOamuxs8","watch")</f>
         <v/>
       </c>
-      <c r="G158" s="15" t="inlineStr">
+      <c r="G158" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H158" s="15" t="n">
+      <c r="H158" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I158" s="15" t="n"/>
@@ -16040,7 +16078,7 @@
       <c r="O158" s="15" t="n"/>
       <c r="P158" s="15" t="n"/>
       <c r="Q158" s="15" t="n"/>
-      <c r="R158" s="15" t="inlineStr">
+      <c r="R158" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -16049,13 +16087,13 @@
         <f>SUM(H158,J158,L158,N158,P158)</f>
         <v/>
       </c>
-      <c r="T158" s="15" t="inlineStr">
+      <c r="T158" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U158" s="15" t="n"/>
-      <c r="V158" s="15" t="inlineStr">
+      <c r="V158" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -16098,12 +16136,12 @@
         <f>HYPERLINK("https://youtu.be/auKzs0g2LL8","watch")</f>
         <v/>
       </c>
-      <c r="G159" s="15" t="inlineStr">
+      <c r="G159" s="14" t="inlineStr">
         <is>
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H159" s="15" t="n">
+      <c r="H159" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="15" t="n"/>
@@ -16115,7 +16153,7 @@
       <c r="O159" s="15" t="n"/>
       <c r="P159" s="15" t="n"/>
       <c r="Q159" s="15" t="n"/>
-      <c r="R159" s="15" t="inlineStr">
+      <c r="R159" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -16165,12 +16203,12 @@
         <f>HYPERLINK("https://youtu.be/8d2a5b_BmYQ","watch")</f>
         <v/>
       </c>
-      <c r="G160" s="15" t="inlineStr">
+      <c r="G160" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H160" s="15" t="n">
+      <c r="H160" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I160" s="15" t="n"/>
@@ -16182,7 +16220,7 @@
       <c r="O160" s="15" t="n"/>
       <c r="P160" s="15" t="n"/>
       <c r="Q160" s="15" t="n"/>
-      <c r="R160" s="15" t="inlineStr">
+      <c r="R160" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -16232,12 +16270,12 @@
         <f>HYPERLINK("https://youtu.be/484NOQA1r8Q","watch")</f>
         <v/>
       </c>
-      <c r="G161" s="15" t="inlineStr">
+      <c r="G161" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H161" s="15" t="n">
+      <c r="H161" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="15" t="n"/>
@@ -16249,7 +16287,7 @@
       <c r="O161" s="15" t="n"/>
       <c r="P161" s="15" t="n"/>
       <c r="Q161" s="15" t="n"/>
-      <c r="R161" s="15" t="inlineStr">
+      <c r="R161" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -16258,13 +16296,13 @@
         <f>SUM(H161,J161,L161,N161,P161)</f>
         <v/>
       </c>
-      <c r="T161" s="15" t="inlineStr">
+      <c r="T161" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U161" s="15" t="n"/>
-      <c r="V161" s="15" t="inlineStr">
+      <c r="V161" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -16307,12 +16345,12 @@
         <f>HYPERLINK("https://youtu.be/2OFpV33VzpU","watch")</f>
         <v/>
       </c>
-      <c r="G162" s="15" t="inlineStr">
+      <c r="G162" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H162" s="15" t="n">
+      <c r="H162" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I162" s="15" t="n"/>
@@ -16324,7 +16362,7 @@
       <c r="O162" s="15" t="n"/>
       <c r="P162" s="15" t="n"/>
       <c r="Q162" s="15" t="n"/>
-      <c r="R162" s="15" t="inlineStr">
+      <c r="R162" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -16374,12 +16412,12 @@
         <f>HYPERLINK("https://youtu.be/uGRqBM2AOag","watch")</f>
         <v/>
       </c>
-      <c r="G163" s="15" t="inlineStr">
+      <c r="G163" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H163" s="15" t="n">
+      <c r="H163" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I163" s="15" t="n"/>
@@ -16391,7 +16429,7 @@
       <c r="O163" s="15" t="n"/>
       <c r="P163" s="15" t="n"/>
       <c r="Q163" s="15" t="n"/>
-      <c r="R163" s="15" t="inlineStr">
+      <c r="R163" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -16441,12 +16479,12 @@
         <f>HYPERLINK("https://youtu.be/LFpa9K2DA6Q","watch")</f>
         <v/>
       </c>
-      <c r="G164" s="15" t="inlineStr">
+      <c r="G164" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H164" s="15" t="n">
+      <c r="H164" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I164" s="15" t="n"/>
@@ -16458,7 +16496,7 @@
       <c r="O164" s="15" t="n"/>
       <c r="P164" s="15" t="n"/>
       <c r="Q164" s="15" t="n"/>
-      <c r="R164" s="15" t="inlineStr">
+      <c r="R164" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -16467,13 +16505,13 @@
         <f>SUM(H164,J164,L164,N164,P164)</f>
         <v/>
       </c>
-      <c r="T164" s="15" t="inlineStr">
+      <c r="T164" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U164" s="15" t="n"/>
-      <c r="V164" s="15" t="inlineStr">
+      <c r="V164" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -16516,12 +16554,12 @@
         <f>HYPERLINK("https://youtu.be/bh8OGK_jE2Y","watch")</f>
         <v/>
       </c>
-      <c r="G165" s="15" t="inlineStr">
+      <c r="G165" s="14" t="inlineStr">
         <is>
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H165" s="15" t="n">
+      <c r="H165" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I165" s="15" t="n"/>
@@ -16533,7 +16571,7 @@
       <c r="O165" s="15" t="n"/>
       <c r="P165" s="15" t="n"/>
       <c r="Q165" s="15" t="n"/>
-      <c r="R165" s="15" t="inlineStr">
+      <c r="R165" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -16583,12 +16621,12 @@
         <f>HYPERLINK("https://youtu.be/PPEKxxW-s_g","watch")</f>
         <v/>
       </c>
-      <c r="G166" s="15" t="inlineStr">
+      <c r="G166" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H166" s="15" t="n">
+      <c r="H166" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I166" s="15" t="n"/>
@@ -16600,7 +16638,7 @@
       <c r="O166" s="15" t="n"/>
       <c r="P166" s="15" t="n"/>
       <c r="Q166" s="15" t="n"/>
-      <c r="R166" s="15" t="inlineStr">
+      <c r="R166" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -16650,12 +16688,12 @@
         <f>HYPERLINK("https://youtu.be/gq4wUMrTrB0","watch")</f>
         <v/>
       </c>
-      <c r="G167" s="15" t="inlineStr">
+      <c r="G167" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H167" s="15" t="n">
+      <c r="H167" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="15" t="n"/>
@@ -16667,7 +16705,7 @@
       <c r="O167" s="15" t="n"/>
       <c r="P167" s="15" t="n"/>
       <c r="Q167" s="15" t="n"/>
-      <c r="R167" s="15" t="inlineStr">
+      <c r="R167" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -16676,13 +16714,13 @@
         <f>SUM(H167,J167,L167,N167,P167)</f>
         <v/>
       </c>
-      <c r="T167" s="15" t="inlineStr">
+      <c r="T167" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U167" s="15" t="n"/>
-      <c r="V167" s="15" t="inlineStr">
+      <c r="V167" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -16725,12 +16763,12 @@
         <f>HYPERLINK("https://youtu.be/uyiszkVXiUQ","watch")</f>
         <v/>
       </c>
-      <c r="G168" s="15" t="inlineStr">
+      <c r="G168" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H168" s="15" t="n">
+      <c r="H168" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I168" s="15" t="n"/>
@@ -16742,7 +16780,7 @@
       <c r="O168" s="15" t="n"/>
       <c r="P168" s="15" t="n"/>
       <c r="Q168" s="15" t="n"/>
-      <c r="R168" s="15" t="inlineStr">
+      <c r="R168" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -16792,12 +16830,12 @@
         <f>HYPERLINK("https://youtu.be/OMpbKBu38rk","watch")</f>
         <v/>
       </c>
-      <c r="G169" s="15" t="inlineStr">
+      <c r="G169" s="14" t="inlineStr">
         <is>
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H169" s="15" t="n">
+      <c r="H169" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="15" t="n"/>
@@ -16809,7 +16847,7 @@
       <c r="O169" s="15" t="n"/>
       <c r="P169" s="15" t="n"/>
       <c r="Q169" s="15" t="n"/>
-      <c r="R169" s="15" t="inlineStr">
+      <c r="R169" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -16859,12 +16897,12 @@
         <f>HYPERLINK("https://youtu.be/YqaeisWumvQ","watch")</f>
         <v/>
       </c>
-      <c r="G170" s="15" t="inlineStr">
+      <c r="G170" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H170" s="15" t="n">
+      <c r="H170" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I170" s="15" t="n"/>
@@ -16876,7 +16914,7 @@
       <c r="O170" s="15" t="n"/>
       <c r="P170" s="15" t="n"/>
       <c r="Q170" s="15" t="n"/>
-      <c r="R170" s="15" t="inlineStr">
+      <c r="R170" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -16926,12 +16964,12 @@
         <f>HYPERLINK("https://youtu.be/GK_IadR7G1g","watch")</f>
         <v/>
       </c>
-      <c r="G171" s="15" t="inlineStr">
+      <c r="G171" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H171" s="15" t="n">
+      <c r="H171" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I171" s="15" t="n"/>
@@ -16943,7 +16981,7 @@
       <c r="O171" s="15" t="n"/>
       <c r="P171" s="15" t="n"/>
       <c r="Q171" s="15" t="n"/>
-      <c r="R171" s="15" t="inlineStr">
+      <c r="R171" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -16952,13 +16990,13 @@
         <f>SUM(H171,J171,L171,N171,P171)</f>
         <v/>
       </c>
-      <c r="T171" s="15" t="inlineStr">
+      <c r="T171" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U171" s="15" t="n"/>
-      <c r="V171" s="15" t="inlineStr">
+      <c r="V171" s="14" t="inlineStr">
         <is>
           <t>Hyper Rare (3 gold stars)</t>
         </is>
@@ -17001,12 +17039,12 @@
         <f>HYPERLINK("https://youtu.be/hCI0HSfly1c","watch")</f>
         <v/>
       </c>
-      <c r="G172" s="15" t="inlineStr">
+      <c r="G172" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H172" s="15" t="n">
+      <c r="H172" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I172" s="15" t="n"/>
@@ -17018,7 +17056,7 @@
       <c r="O172" s="15" t="n"/>
       <c r="P172" s="15" t="n"/>
       <c r="Q172" s="15" t="n"/>
-      <c r="R172" s="15" t="inlineStr">
+      <c r="R172" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -17027,13 +17065,13 @@
         <f>SUM(H172,J172,L172,N172,P172)</f>
         <v/>
       </c>
-      <c r="T172" s="15" t="inlineStr">
+      <c r="T172" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U172" s="15" t="n"/>
-      <c r="V172" s="15" t="inlineStr">
+      <c r="V172" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -17076,12 +17114,12 @@
         <f>HYPERLINK("https://youtu.be/UqZn1J9vVGc","watch")</f>
         <v/>
       </c>
-      <c r="G173" s="15" t="inlineStr">
+      <c r="G173" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H173" s="15" t="n">
+      <c r="H173" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I173" s="15" t="n"/>
@@ -17093,7 +17131,7 @@
       <c r="O173" s="15" t="n"/>
       <c r="P173" s="15" t="n"/>
       <c r="Q173" s="15" t="n"/>
-      <c r="R173" s="15" t="inlineStr">
+      <c r="R173" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -17143,12 +17181,12 @@
         <f>HYPERLINK("https://youtu.be/DMJYnQE8shY","watch")</f>
         <v/>
       </c>
-      <c r="G174" s="15" t="inlineStr">
+      <c r="G174" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H174" s="15" t="n">
+      <c r="H174" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I174" s="15" t="n"/>
@@ -17160,7 +17198,7 @@
       <c r="O174" s="15" t="n"/>
       <c r="P174" s="15" t="n"/>
       <c r="Q174" s="15" t="n"/>
-      <c r="R174" s="15" t="inlineStr">
+      <c r="R174" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -17210,12 +17248,12 @@
         <f>HYPERLINK("https://youtu.be/C4IPzbJZlHw","watch")</f>
         <v/>
       </c>
-      <c r="G175" s="15" t="inlineStr">
+      <c r="G175" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H175" s="15" t="n">
+      <c r="H175" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I175" s="15" t="n"/>
@@ -17227,7 +17265,7 @@
       <c r="O175" s="15" t="n"/>
       <c r="P175" s="15" t="n"/>
       <c r="Q175" s="15" t="n"/>
-      <c r="R175" s="15" t="inlineStr">
+      <c r="R175" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -17277,12 +17315,12 @@
         <f>HYPERLINK("https://youtu.be/d0ux4nsMixw","watch")</f>
         <v/>
       </c>
-      <c r="G176" s="15" t="inlineStr">
+      <c r="G176" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H176" s="15" t="n">
+      <c r="H176" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I176" s="15" t="n"/>
@@ -17294,7 +17332,7 @@
       <c r="O176" s="15" t="n"/>
       <c r="P176" s="15" t="n"/>
       <c r="Q176" s="15" t="n"/>
-      <c r="R176" s="15" t="inlineStr">
+      <c r="R176" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17344,12 +17382,12 @@
         <f>HYPERLINK("https://youtu.be/Z0s6mRdT_QE","watch")</f>
         <v/>
       </c>
-      <c r="G177" s="15" t="inlineStr">
+      <c r="G177" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H177" s="15" t="n">
+      <c r="H177" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I177" s="15" t="n"/>
@@ -17361,7 +17399,7 @@
       <c r="O177" s="15" t="n"/>
       <c r="P177" s="15" t="n"/>
       <c r="Q177" s="15" t="n"/>
-      <c r="R177" s="15" t="inlineStr">
+      <c r="R177" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17411,12 +17449,12 @@
         <f>HYPERLINK("https://youtu.be/A38u-diwmvw","watch")</f>
         <v/>
       </c>
-      <c r="G178" s="15" t="inlineStr">
+      <c r="G178" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H178" s="15" t="n">
+      <c r="H178" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I178" s="15" t="n"/>
@@ -17428,7 +17466,7 @@
       <c r="O178" s="15" t="n"/>
       <c r="P178" s="15" t="n"/>
       <c r="Q178" s="15" t="n"/>
-      <c r="R178" s="15" t="inlineStr">
+      <c r="R178" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17478,12 +17516,12 @@
         <f>HYPERLINK("https://youtu.be/PvitecaJjAc","watch")</f>
         <v/>
       </c>
-      <c r="G179" s="15" t="inlineStr">
+      <c r="G179" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H179" s="15" t="n">
+      <c r="H179" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I179" s="15" t="n"/>
@@ -17495,7 +17533,7 @@
       <c r="O179" s="15" t="n"/>
       <c r="P179" s="15" t="n"/>
       <c r="Q179" s="15" t="n"/>
-      <c r="R179" s="15" t="inlineStr">
+      <c r="R179" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -17545,12 +17583,12 @@
         <f>HYPERLINK("https://youtu.be/Q09fPPjWf8A","watch")</f>
         <v/>
       </c>
-      <c r="G180" s="15" t="inlineStr">
+      <c r="G180" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H180" s="15" t="n">
+      <c r="H180" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I180" s="15" t="n"/>
@@ -17562,7 +17600,7 @@
       <c r="O180" s="15" t="n"/>
       <c r="P180" s="15" t="n"/>
       <c r="Q180" s="15" t="n"/>
-      <c r="R180" s="15" t="inlineStr">
+      <c r="R180" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17612,12 +17650,12 @@
         <f>HYPERLINK("https://youtu.be/3gpbmrouFEw","watch")</f>
         <v/>
       </c>
-      <c r="G181" s="15" t="inlineStr">
+      <c r="G181" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H181" s="15" t="n">
+      <c r="H181" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I181" s="15" t="n"/>
@@ -17629,7 +17667,7 @@
       <c r="O181" s="15" t="n"/>
       <c r="P181" s="15" t="n"/>
       <c r="Q181" s="15" t="n"/>
-      <c r="R181" s="15" t="inlineStr">
+      <c r="R181" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -17679,12 +17717,12 @@
         <f>HYPERLINK("https://youtu.be/YQ2-iIhbOSY","watch")</f>
         <v/>
       </c>
-      <c r="G182" s="15" t="inlineStr">
+      <c r="G182" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H182" s="15" t="n">
+      <c r="H182" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I182" s="15" t="n"/>
@@ -17696,7 +17734,7 @@
       <c r="O182" s="15" t="n"/>
       <c r="P182" s="15" t="n"/>
       <c r="Q182" s="15" t="n"/>
-      <c r="R182" s="15" t="inlineStr">
+      <c r="R182" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -17746,12 +17784,12 @@
         <f>HYPERLINK("https://youtu.be/9UfyaoGCEZ8","watch")</f>
         <v/>
       </c>
-      <c r="G183" s="15" t="inlineStr">
+      <c r="G183" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H183" s="15" t="n">
+      <c r="H183" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="15" t="n"/>
@@ -17763,7 +17801,7 @@
       <c r="O183" s="15" t="n"/>
       <c r="P183" s="15" t="n"/>
       <c r="Q183" s="15" t="n"/>
-      <c r="R183" s="15" t="inlineStr">
+      <c r="R183" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17772,13 +17810,13 @@
         <f>SUM(H183,J183,L183,N183,P183)</f>
         <v/>
       </c>
-      <c r="T183" s="15" t="inlineStr">
+      <c r="T183" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U183" s="15" t="n"/>
-      <c r="V183" s="15" t="inlineStr">
+      <c r="V183" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -17821,12 +17859,12 @@
         <f>HYPERLINK("https://youtu.be/Vbqy14CESN4","watch")</f>
         <v/>
       </c>
-      <c r="G184" s="15" t="inlineStr">
+      <c r="G184" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H184" s="15" t="n">
+      <c r="H184" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I184" s="15" t="n"/>
@@ -17838,7 +17876,7 @@
       <c r="O184" s="15" t="n"/>
       <c r="P184" s="15" t="n"/>
       <c r="Q184" s="15" t="n"/>
-      <c r="R184" s="15" t="inlineStr">
+      <c r="R184" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -17888,12 +17926,12 @@
         <f>HYPERLINK("https://youtu.be/oAdG2xms9Ko","watch")</f>
         <v/>
       </c>
-      <c r="G185" s="15" t="inlineStr">
+      <c r="G185" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H185" s="15" t="n">
+      <c r="H185" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I185" s="15" t="n"/>
@@ -17905,7 +17943,7 @@
       <c r="O185" s="15" t="n"/>
       <c r="P185" s="15" t="n"/>
       <c r="Q185" s="15" t="n"/>
-      <c r="R185" s="15" t="inlineStr">
+      <c r="R185" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -17955,12 +17993,12 @@
         <f>HYPERLINK("https://youtu.be/Qf2PmYHL8Xw","watch")</f>
         <v/>
       </c>
-      <c r="G186" s="15" t="inlineStr">
+      <c r="G186" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H186" s="15" t="n">
+      <c r="H186" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I186" s="15" t="n"/>
@@ -17972,7 +18010,7 @@
       <c r="O186" s="15" t="n"/>
       <c r="P186" s="15" t="n"/>
       <c r="Q186" s="15" t="n"/>
-      <c r="R186" s="15" t="inlineStr">
+      <c r="R186" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -18022,12 +18060,12 @@
         <f>HYPERLINK("https://youtu.be/4qNvWCkNb9w","watch")</f>
         <v/>
       </c>
-      <c r="G187" s="15" t="inlineStr">
+      <c r="G187" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H187" s="15" t="n">
+      <c r="H187" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="15" t="n"/>
@@ -18039,7 +18077,7 @@
       <c r="O187" s="15" t="n"/>
       <c r="P187" s="15" t="n"/>
       <c r="Q187" s="15" t="n"/>
-      <c r="R187" s="15" t="inlineStr">
+      <c r="R187" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18048,13 +18086,13 @@
         <f>SUM(H187,J187,L187,N187,P187)</f>
         <v/>
       </c>
-      <c r="T187" s="15" t="inlineStr">
+      <c r="T187" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U187" s="15" t="n"/>
-      <c r="V187" s="15" t="inlineStr">
+      <c r="V187" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -18097,12 +18135,12 @@
         <f>HYPERLINK("https://youtu.be/Pvi54rMlLfQ","watch")</f>
         <v/>
       </c>
-      <c r="G188" s="15" t="inlineStr">
+      <c r="G188" s="14" t="inlineStr">
         <is>
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H188" s="15" t="n">
+      <c r="H188" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I188" s="15" t="n"/>
@@ -18114,7 +18152,7 @@
       <c r="O188" s="15" t="n"/>
       <c r="P188" s="15" t="n"/>
       <c r="Q188" s="15" t="n"/>
-      <c r="R188" s="15" t="inlineStr">
+      <c r="R188" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18164,12 +18202,12 @@
         <f>HYPERLINK("https://youtu.be/tTxItGrPfUw","watch")</f>
         <v/>
       </c>
-      <c r="G189" s="15" t="inlineStr">
+      <c r="G189" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H189" s="15" t="n">
+      <c r="H189" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="15" t="n"/>
@@ -18181,7 +18219,7 @@
       <c r="O189" s="15" t="n"/>
       <c r="P189" s="15" t="n"/>
       <c r="Q189" s="15" t="n"/>
-      <c r="R189" s="15" t="inlineStr">
+      <c r="R189" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18231,12 +18269,12 @@
         <f>HYPERLINK("https://youtu.be/6cwLQGIVpKU","watch")</f>
         <v/>
       </c>
-      <c r="G190" s="15" t="inlineStr">
+      <c r="G190" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H190" s="15" t="n">
+      <c r="H190" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="15" t="n"/>
@@ -18248,7 +18286,7 @@
       <c r="O190" s="15" t="n"/>
       <c r="P190" s="15" t="n"/>
       <c r="Q190" s="15" t="n"/>
-      <c r="R190" s="15" t="inlineStr">
+      <c r="R190" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18298,12 +18336,12 @@
         <f>HYPERLINK("https://youtu.be/RXKBcjWfqhE","watch")</f>
         <v/>
       </c>
-      <c r="G191" s="15" t="inlineStr">
+      <c r="G191" s="14" t="inlineStr">
         <is>
           <t>Obsidian Flames</t>
         </is>
       </c>
-      <c r="H191" s="15" t="n">
+      <c r="H191" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="15" t="n"/>
@@ -18315,7 +18353,7 @@
       <c r="O191" s="15" t="n"/>
       <c r="P191" s="15" t="n"/>
       <c r="Q191" s="15" t="n"/>
-      <c r="R191" s="15" t="inlineStr">
+      <c r="R191" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18324,13 +18362,13 @@
         <f>SUM(H191,J191,L191,N191,P191)</f>
         <v/>
       </c>
-      <c r="T191" s="15" t="inlineStr">
+      <c r="T191" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U191" s="15" t="n"/>
-      <c r="V191" s="15" t="inlineStr">
+      <c r="V191" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -18373,12 +18411,12 @@
         <f>HYPERLINK("https://youtu.be/yeX4naszsoo","watch")</f>
         <v/>
       </c>
-      <c r="G192" s="15" t="inlineStr">
+      <c r="G192" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H192" s="15" t="n">
+      <c r="H192" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="15" t="n"/>
@@ -18390,7 +18428,7 @@
       <c r="O192" s="15" t="n"/>
       <c r="P192" s="15" t="n"/>
       <c r="Q192" s="15" t="n"/>
-      <c r="R192" s="15" t="inlineStr">
+      <c r="R192" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18399,13 +18437,13 @@
         <f>SUM(H192,J192,L192,N192,P192)</f>
         <v/>
       </c>
-      <c r="T192" s="15" t="inlineStr">
+      <c r="T192" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U192" s="15" t="n"/>
-      <c r="V192" s="15" t="inlineStr">
+      <c r="V192" s="14" t="inlineStr">
         <is>
           <t>Special Illustration Rare (2 gold stars)</t>
         </is>
@@ -18448,12 +18486,12 @@
         <f>HYPERLINK("https://youtu.be/GroN9k8XsN0","watch")</f>
         <v/>
       </c>
-      <c r="G193" s="15" t="inlineStr">
+      <c r="G193" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H193" s="15" t="n">
+      <c r="H193" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="15" t="n"/>
@@ -18465,7 +18503,7 @@
       <c r="O193" s="15" t="n"/>
       <c r="P193" s="15" t="n"/>
       <c r="Q193" s="15" t="n"/>
-      <c r="R193" s="15" t="inlineStr">
+      <c r="R193" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18515,7 +18553,7 @@
         <f>HYPERLINK("https://youtu.be/rMMOuM8bsqE","watch")</f>
         <v/>
       </c>
-      <c r="G194" s="15" t="inlineStr">
+      <c r="G194" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -18530,7 +18568,7 @@
       <c r="O194" s="15" t="n"/>
       <c r="P194" s="15" t="n"/>
       <c r="Q194" s="15" t="n"/>
-      <c r="R194" s="15" t="inlineStr">
+      <c r="R194" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -18580,12 +18618,12 @@
         <f>HYPERLINK("https://youtu.be/EPqUqzrAc30","watch")</f>
         <v/>
       </c>
-      <c r="G195" s="15" t="inlineStr">
+      <c r="G195" s="14" t="inlineStr">
         <is>
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H195" s="15" t="n">
+      <c r="H195" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="15" t="n"/>
@@ -18597,7 +18635,7 @@
       <c r="O195" s="15" t="n"/>
       <c r="P195" s="15" t="n"/>
       <c r="Q195" s="15" t="n"/>
-      <c r="R195" s="15" t="inlineStr">
+      <c r="R195" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -18658,7 +18696,7 @@
       <c r="O196" s="15" t="n"/>
       <c r="P196" s="15" t="n"/>
       <c r="Q196" s="15" t="n"/>
-      <c r="R196" s="15" t="inlineStr">
+      <c r="R196" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -18708,12 +18746,12 @@
         <f>HYPERLINK("https://youtu.be/QXS1W_L2qbs","watch")</f>
         <v/>
       </c>
-      <c r="G197" s="15" t="inlineStr">
+      <c r="G197" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H197" s="15" t="n">
+      <c r="H197" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="15" t="n"/>
@@ -18725,7 +18763,7 @@
       <c r="O197" s="15" t="n"/>
       <c r="P197" s="15" t="n"/>
       <c r="Q197" s="15" t="n"/>
-      <c r="R197" s="15" t="inlineStr">
+      <c r="R197" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18775,7 +18813,7 @@
         <f>HYPERLINK("https://youtu.be/sdZx0lmq2mQ","watch")</f>
         <v/>
       </c>
-      <c r="G198" s="15" t="inlineStr">
+      <c r="G198" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -18790,7 +18828,7 @@
       <c r="O198" s="15" t="n"/>
       <c r="P198" s="15" t="n"/>
       <c r="Q198" s="15" t="n"/>
-      <c r="R198" s="15" t="inlineStr">
+      <c r="R198" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -18840,12 +18878,12 @@
         <f>HYPERLINK("https://youtu.be/KEK0q0PgN_I","watch")</f>
         <v/>
       </c>
-      <c r="G199" s="15" t="inlineStr">
+      <c r="G199" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H199" s="15" t="n">
+      <c r="H199" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="15" t="n"/>
@@ -18857,7 +18895,7 @@
       <c r="O199" s="15" t="n"/>
       <c r="P199" s="15" t="n"/>
       <c r="Q199" s="15" t="n"/>
-      <c r="R199" s="15" t="inlineStr">
+      <c r="R199" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -18907,7 +18945,7 @@
         <f>HYPERLINK("https://youtu.be/wBIeB-63sKw","watch")</f>
         <v/>
       </c>
-      <c r="G200" s="15" t="inlineStr">
+      <c r="G200" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
@@ -18922,7 +18960,7 @@
       <c r="O200" s="15" t="n"/>
       <c r="P200" s="15" t="n"/>
       <c r="Q200" s="15" t="n"/>
-      <c r="R200" s="15" t="inlineStr">
+      <c r="R200" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -18972,12 +19010,12 @@
         <f>HYPERLINK("https://youtu.be/-la8PgoBkCw","watch")</f>
         <v/>
       </c>
-      <c r="G201" s="15" t="inlineStr">
+      <c r="G201" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H201" s="15" t="n">
+      <c r="H201" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="15" t="n"/>
@@ -18989,7 +19027,7 @@
       <c r="O201" s="15" t="n"/>
       <c r="P201" s="15" t="n"/>
       <c r="Q201" s="15" t="n"/>
-      <c r="R201" s="15" t="inlineStr">
+      <c r="R201" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19050,7 +19088,7 @@
       <c r="O202" s="15" t="n"/>
       <c r="P202" s="15" t="n"/>
       <c r="Q202" s="15" t="n"/>
-      <c r="R202" s="15" t="inlineStr">
+      <c r="R202" s="14" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
@@ -19100,12 +19138,12 @@
         <f>HYPERLINK("https://youtu.be/LGzHC-k4vh0","watch")</f>
         <v/>
       </c>
-      <c r="G203" s="15" t="inlineStr">
+      <c r="G203" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H203" s="15" t="n">
+      <c r="H203" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I203" s="15" t="n"/>
@@ -19117,7 +19155,7 @@
       <c r="O203" s="15" t="n"/>
       <c r="P203" s="15" t="n"/>
       <c r="Q203" s="15" t="n"/>
-      <c r="R203" s="15" t="inlineStr">
+      <c r="R203" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -19167,12 +19205,12 @@
         <f>HYPERLINK("https://youtu.be/8SX0B-7WM8A","watch")</f>
         <v/>
       </c>
-      <c r="G204" s="15" t="inlineStr">
+      <c r="G204" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H204" s="15" t="n">
+      <c r="H204" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="15" t="n"/>
@@ -19184,7 +19222,7 @@
       <c r="O204" s="15" t="n"/>
       <c r="P204" s="15" t="n"/>
       <c r="Q204" s="15" t="n"/>
-      <c r="R204" s="15" t="inlineStr">
+      <c r="R204" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19245,7 +19283,7 @@
       <c r="O205" s="15" t="n"/>
       <c r="P205" s="15" t="n"/>
       <c r="Q205" s="15" t="n"/>
-      <c r="R205" s="15" t="inlineStr">
+      <c r="R205" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -19295,7 +19333,7 @@
         <f>HYPERLINK("https://youtu.be/HbSOpODafEw","watch")</f>
         <v/>
       </c>
-      <c r="G206" s="15" t="inlineStr">
+      <c r="G206" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -19310,7 +19348,7 @@
       <c r="O206" s="15" t="n"/>
       <c r="P206" s="15" t="n"/>
       <c r="Q206" s="15" t="n"/>
-      <c r="R206" s="15" t="inlineStr">
+      <c r="R206" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -19360,12 +19398,12 @@
         <f>HYPERLINK("https://youtu.be/NzWUDxXwnPI","watch")</f>
         <v/>
       </c>
-      <c r="G207" s="15" t="inlineStr">
+      <c r="G207" s="14" t="inlineStr">
         <is>
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H207" s="15" t="n">
+      <c r="H207" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="15" t="n"/>
@@ -19377,7 +19415,7 @@
       <c r="O207" s="15" t="n"/>
       <c r="P207" s="15" t="n"/>
       <c r="Q207" s="15" t="n"/>
-      <c r="R207" s="15" t="inlineStr">
+      <c r="R207" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -19427,12 +19465,12 @@
         <f>HYPERLINK("https://youtu.be/53yMHXauDnA","watch")</f>
         <v/>
       </c>
-      <c r="G208" s="15" t="inlineStr">
+      <c r="G208" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H208" s="15" t="n">
+      <c r="H208" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I208" s="15" t="n"/>
@@ -19444,7 +19482,7 @@
       <c r="O208" s="15" t="n"/>
       <c r="P208" s="15" t="n"/>
       <c r="Q208" s="15" t="n"/>
-      <c r="R208" s="15" t="inlineStr">
+      <c r="R208" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -19494,12 +19532,12 @@
         <f>HYPERLINK("https://youtu.be/dQaN_4yqS0w","watch")</f>
         <v/>
       </c>
-      <c r="G209" s="15" t="inlineStr">
+      <c r="G209" s="14" t="inlineStr">
         <is>
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H209" s="15" t="n">
+      <c r="H209" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="15" t="n"/>
@@ -19511,7 +19549,7 @@
       <c r="O209" s="15" t="n"/>
       <c r="P209" s="15" t="n"/>
       <c r="Q209" s="15" t="n"/>
-      <c r="R209" s="15" t="inlineStr">
+      <c r="R209" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19561,12 +19599,12 @@
         <f>HYPERLINK("https://youtu.be/7PBrXPgt9kU","watch")</f>
         <v/>
       </c>
-      <c r="G210" s="15" t="inlineStr">
+      <c r="G210" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H210" s="15" t="n">
+      <c r="H210" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I210" s="15" t="n"/>
@@ -19578,7 +19616,7 @@
       <c r="O210" s="15" t="n"/>
       <c r="P210" s="15" t="n"/>
       <c r="Q210" s="15" t="n"/>
-      <c r="R210" s="15" t="inlineStr">
+      <c r="R210" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -19628,12 +19666,12 @@
         <f>HYPERLINK("https://youtu.be/S_2SHhBqlH8","watch")</f>
         <v/>
       </c>
-      <c r="G211" s="15" t="inlineStr">
+      <c r="G211" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H211" s="15" t="n">
+      <c r="H211" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="15" t="n"/>
@@ -19645,7 +19683,7 @@
       <c r="O211" s="15" t="n"/>
       <c r="P211" s="15" t="n"/>
       <c r="Q211" s="15" t="n"/>
-      <c r="R211" s="15" t="inlineStr">
+      <c r="R211" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19696,7 +19734,7 @@
         <v/>
       </c>
       <c r="G212" s="15" t="n"/>
-      <c r="H212" s="15" t="n">
+      <c r="H212" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I212" s="15" t="n"/>
@@ -19708,7 +19746,7 @@
       <c r="O212" s="15" t="n"/>
       <c r="P212" s="15" t="n"/>
       <c r="Q212" s="15" t="n"/>
-      <c r="R212" s="15" t="inlineStr">
+      <c r="R212" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -19758,12 +19796,12 @@
         <f>HYPERLINK("https://youtu.be/hVS0VH-nfVM","watch")</f>
         <v/>
       </c>
-      <c r="G213" s="15" t="inlineStr">
+      <c r="G213" s="14" t="inlineStr">
         <is>
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H213" s="15" t="n">
+      <c r="H213" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I213" s="15" t="n"/>
@@ -19775,7 +19813,7 @@
       <c r="O213" s="15" t="n"/>
       <c r="P213" s="15" t="n"/>
       <c r="Q213" s="15" t="n"/>
-      <c r="R213" s="15" t="inlineStr">
+      <c r="R213" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19826,7 +19864,7 @@
         <v/>
       </c>
       <c r="G214" s="15" t="n"/>
-      <c r="H214" s="15" t="n">
+      <c r="H214" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I214" s="15" t="n"/>
@@ -19838,7 +19876,7 @@
       <c r="O214" s="15" t="n"/>
       <c r="P214" s="15" t="n"/>
       <c r="Q214" s="15" t="n"/>
-      <c r="R214" s="15" t="inlineStr">
+      <c r="R214" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -19888,12 +19926,12 @@
         <f>HYPERLINK("https://youtu.be/VP1UXW3MrGU","watch")</f>
         <v/>
       </c>
-      <c r="G215" s="15" t="inlineStr">
+      <c r="G215" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H215" s="15" t="n">
+      <c r="H215" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I215" s="15" t="n"/>
@@ -19905,7 +19943,7 @@
       <c r="O215" s="15" t="n"/>
       <c r="P215" s="15" t="n"/>
       <c r="Q215" s="15" t="n"/>
-      <c r="R215" s="15" t="inlineStr">
+      <c r="R215" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -19955,11 +19993,7 @@
         <f>HYPERLINK("https://youtu.be/JjTm-bYLhGE","watch")</f>
         <v/>
       </c>
-      <c r="G216" s="15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+      <c r="G216" s="15" t="n"/>
       <c r="H216" s="15" t="n"/>
       <c r="I216" s="15" t="n"/>
       <c r="J216" s="15" t="n"/>
@@ -19970,7 +20004,7 @@
       <c r="O216" s="15" t="n"/>
       <c r="P216" s="15" t="n"/>
       <c r="Q216" s="15" t="n"/>
-      <c r="R216" s="15" t="inlineStr">
+      <c r="R216" s="14" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
@@ -20020,12 +20054,12 @@
         <f>HYPERLINK("https://youtu.be/fFbWjWLD1N4","watch")</f>
         <v/>
       </c>
-      <c r="G217" s="15" t="inlineStr">
+      <c r="G217" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H217" s="15" t="n">
+      <c r="H217" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I217" s="15" t="n"/>
@@ -20037,7 +20071,7 @@
       <c r="O217" s="15" t="n"/>
       <c r="P217" s="15" t="n"/>
       <c r="Q217" s="15" t="n"/>
-      <c r="R217" s="15" t="inlineStr">
+      <c r="R217" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20087,12 +20121,12 @@
         <f>HYPERLINK("https://youtu.be/39Rh6NJPK9M","watch")</f>
         <v/>
       </c>
-      <c r="G218" s="15" t="inlineStr">
+      <c r="G218" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H218" s="15" t="n">
+      <c r="H218" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I218" s="15" t="n"/>
@@ -20104,7 +20138,7 @@
       <c r="O218" s="15" t="n"/>
       <c r="P218" s="15" t="n"/>
       <c r="Q218" s="15" t="n"/>
-      <c r="R218" s="15" t="inlineStr">
+      <c r="R218" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20154,12 +20188,12 @@
         <f>HYPERLINK("https://youtu.be/K5RKQlNhvl8","watch")</f>
         <v/>
       </c>
-      <c r="G219" s="15" t="inlineStr">
+      <c r="G219" s="14" t="inlineStr">
         <is>
           <t>Mega Brave (JP)</t>
         </is>
       </c>
-      <c r="H219" s="15" t="n">
+      <c r="H219" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I219" s="15" t="n"/>
@@ -20171,7 +20205,7 @@
       <c r="O219" s="15" t="n"/>
       <c r="P219" s="15" t="n"/>
       <c r="Q219" s="15" t="n"/>
-      <c r="R219" s="15" t="inlineStr">
+      <c r="R219" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -20221,12 +20255,12 @@
         <f>HYPERLINK("https://youtu.be/6sg185zTjM4","watch")</f>
         <v/>
       </c>
-      <c r="G220" s="15" t="inlineStr">
+      <c r="G220" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H220" s="15" t="n">
+      <c r="H220" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I220" s="15" t="n"/>
@@ -20238,7 +20272,7 @@
       <c r="O220" s="15" t="n"/>
       <c r="P220" s="15" t="n"/>
       <c r="Q220" s="15" t="n"/>
-      <c r="R220" s="15" t="inlineStr">
+      <c r="R220" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20289,7 +20323,7 @@
         <v/>
       </c>
       <c r="G221" s="15" t="n"/>
-      <c r="H221" s="15" t="n">
+      <c r="H221" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="15" t="n"/>
@@ -20301,7 +20335,7 @@
       <c r="O221" s="15" t="n"/>
       <c r="P221" s="15" t="n"/>
       <c r="Q221" s="15" t="n"/>
-      <c r="R221" s="15" t="inlineStr">
+      <c r="R221" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -20351,12 +20385,12 @@
         <f>HYPERLINK("https://youtu.be/yMTuhasZsZ4","watch")</f>
         <v/>
       </c>
-      <c r="G222" s="15" t="inlineStr">
+      <c r="G222" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H222" s="15" t="n">
+      <c r="H222" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I222" s="15" t="n"/>
@@ -20368,7 +20402,7 @@
       <c r="O222" s="15" t="n"/>
       <c r="P222" s="15" t="n"/>
       <c r="Q222" s="15" t="n"/>
-      <c r="R222" s="15" t="inlineStr">
+      <c r="R222" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20418,11 +20452,7 @@
         <f>HYPERLINK("https://youtu.be/4z82NZ7QCJY","watch")</f>
         <v/>
       </c>
-      <c r="G223" s="15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+      <c r="G223" s="15" t="n"/>
       <c r="H223" s="15" t="n"/>
       <c r="I223" s="15" t="n"/>
       <c r="J223" s="15" t="n"/>
@@ -20433,7 +20463,7 @@
       <c r="O223" s="15" t="n"/>
       <c r="P223" s="15" t="n"/>
       <c r="Q223" s="15" t="n"/>
-      <c r="R223" s="15" t="inlineStr">
+      <c r="R223" s="14" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
@@ -20483,12 +20513,12 @@
         <f>HYPERLINK("https://youtu.be/tlOeWpJhJ1E","watch")</f>
         <v/>
       </c>
-      <c r="G224" s="15" t="inlineStr">
+      <c r="G224" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H224" s="15" t="n">
+      <c r="H224" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I224" s="15" t="n"/>
@@ -20500,7 +20530,7 @@
       <c r="O224" s="15" t="n"/>
       <c r="P224" s="15" t="n"/>
       <c r="Q224" s="15" t="n"/>
-      <c r="R224" s="15" t="inlineStr">
+      <c r="R224" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20550,12 +20580,12 @@
         <f>HYPERLINK("https://youtu.be/IuNgQ6IWdVc","watch")</f>
         <v/>
       </c>
-      <c r="G225" s="15" t="inlineStr">
+      <c r="G225" s="14" t="inlineStr">
         <is>
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H225" s="15" t="n">
+      <c r="H225" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="15" t="n"/>
@@ -20567,7 +20597,7 @@
       <c r="O225" s="15" t="n"/>
       <c r="P225" s="15" t="n"/>
       <c r="Q225" s="15" t="n"/>
-      <c r="R225" s="15" t="inlineStr">
+      <c r="R225" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -20617,12 +20647,12 @@
         <f>HYPERLINK("https://youtu.be/DljCIsO2zkU","watch")</f>
         <v/>
       </c>
-      <c r="G226" s="15" t="inlineStr">
+      <c r="G226" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H226" s="15" t="n">
+      <c r="H226" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I226" s="15" t="n"/>
@@ -20634,7 +20664,7 @@
       <c r="O226" s="15" t="n"/>
       <c r="P226" s="15" t="n"/>
       <c r="Q226" s="15" t="n"/>
-      <c r="R226" s="15" t="inlineStr">
+      <c r="R226" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20685,7 +20715,7 @@
         <v/>
       </c>
       <c r="G227" s="15" t="n"/>
-      <c r="H227" s="15" t="n">
+      <c r="H227" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="15" t="n"/>
@@ -20697,7 +20727,7 @@
       <c r="O227" s="15" t="n"/>
       <c r="P227" s="15" t="n"/>
       <c r="Q227" s="15" t="n"/>
-      <c r="R227" s="15" t="inlineStr">
+      <c r="R227" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -20748,7 +20778,7 @@
         <v/>
       </c>
       <c r="G228" s="15" t="n"/>
-      <c r="H228" s="15" t="n">
+      <c r="H228" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I228" s="15" t="n"/>
@@ -20760,7 +20790,7 @@
       <c r="O228" s="15" t="n"/>
       <c r="P228" s="15" t="n"/>
       <c r="Q228" s="15" t="n"/>
-      <c r="R228" s="15" t="inlineStr">
+      <c r="R228" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -20810,12 +20840,12 @@
         <f>HYPERLINK("https://youtu.be/8Nbj7wLBgrc","watch")</f>
         <v/>
       </c>
-      <c r="G229" s="15" t="inlineStr">
+      <c r="G229" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H229" s="15" t="n">
+      <c r="H229" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I229" s="15" t="n"/>
@@ -20827,7 +20857,7 @@
       <c r="O229" s="15" t="n"/>
       <c r="P229" s="15" t="n"/>
       <c r="Q229" s="15" t="n"/>
-      <c r="R229" s="15" t="inlineStr">
+      <c r="R229" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20877,12 +20907,12 @@
         <f>HYPERLINK("https://youtu.be/OTKn4mNzQ7I","watch")</f>
         <v/>
       </c>
-      <c r="G230" s="15" t="inlineStr">
+      <c r="G230" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H230" s="15" t="n">
+      <c r="H230" s="14" t="n">
         <v>6</v>
       </c>
       <c r="I230" s="15" t="n"/>
@@ -20894,7 +20924,7 @@
       <c r="O230" s="15" t="n"/>
       <c r="P230" s="15" t="n"/>
       <c r="Q230" s="15" t="n"/>
-      <c r="R230" s="15" t="inlineStr">
+      <c r="R230" s="14" t="inlineStr">
         <is>
           <t>Booster Bundle</t>
         </is>
@@ -20944,12 +20974,12 @@
         <f>HYPERLINK("https://youtu.be/fZk7D5Wd0Eg","watch")</f>
         <v/>
       </c>
-      <c r="G231" s="15" t="inlineStr">
+      <c r="G231" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H231" s="15" t="n">
+      <c r="H231" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I231" s="15" t="n"/>
@@ -20961,7 +20991,7 @@
       <c r="O231" s="15" t="n"/>
       <c r="P231" s="15" t="n"/>
       <c r="Q231" s="15" t="n"/>
-      <c r="R231" s="15" t="inlineStr">
+      <c r="R231" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21022,7 +21052,7 @@
       <c r="O232" s="15" t="n"/>
       <c r="P232" s="15" t="n"/>
       <c r="Q232" s="15" t="n"/>
-      <c r="R232" s="15" t="inlineStr">
+      <c r="R232" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -21072,12 +21102,12 @@
         <f>HYPERLINK("https://youtu.be/i9htInhtbCw","watch")</f>
         <v/>
       </c>
-      <c r="G233" s="15" t="inlineStr">
+      <c r="G233" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H233" s="15" t="n">
+      <c r="H233" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I233" s="15" t="n"/>
@@ -21089,7 +21119,7 @@
       <c r="O233" s="15" t="n"/>
       <c r="P233" s="15" t="n"/>
       <c r="Q233" s="15" t="n"/>
-      <c r="R233" s="15" t="inlineStr">
+      <c r="R233" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21139,12 +21169,12 @@
         <f>HYPERLINK("https://youtu.be/MFBINfOTwZ8","watch")</f>
         <v/>
       </c>
-      <c r="G234" s="15" t="inlineStr">
+      <c r="G234" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H234" s="15" t="n">
+      <c r="H234" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I234" s="15" t="n"/>
@@ -21156,7 +21186,7 @@
       <c r="O234" s="15" t="n"/>
       <c r="P234" s="15" t="n"/>
       <c r="Q234" s="15" t="n"/>
-      <c r="R234" s="15" t="inlineStr">
+      <c r="R234" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21206,12 +21236,12 @@
         <f>HYPERLINK("https://youtu.be/-fOEh7wMmkE","watch")</f>
         <v/>
       </c>
-      <c r="G235" s="15" t="inlineStr">
+      <c r="G235" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H235" s="15" t="n">
+      <c r="H235" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I235" s="15" t="n"/>
@@ -21223,7 +21253,7 @@
       <c r="O235" s="15" t="n"/>
       <c r="P235" s="15" t="n"/>
       <c r="Q235" s="15" t="n"/>
-      <c r="R235" s="15" t="inlineStr">
+      <c r="R235" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21273,12 +21303,12 @@
         <f>HYPERLINK("https://youtu.be/f5fYeGx1neA","watch")</f>
         <v/>
       </c>
-      <c r="G236" s="15" t="inlineStr">
+      <c r="G236" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H236" s="15" t="n">
+      <c r="H236" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I236" s="15" t="n"/>
@@ -21290,7 +21320,7 @@
       <c r="O236" s="15" t="n"/>
       <c r="P236" s="15" t="n"/>
       <c r="Q236" s="15" t="n"/>
-      <c r="R236" s="15" t="inlineStr">
+      <c r="R236" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21340,12 +21370,12 @@
         <f>HYPERLINK("https://youtu.be/-Xu2ulrwynY","watch")</f>
         <v/>
       </c>
-      <c r="G237" s="15" t="inlineStr">
+      <c r="G237" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H237" s="15" t="n">
+      <c r="H237" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I237" s="15" t="n"/>
@@ -21357,7 +21387,7 @@
       <c r="O237" s="15" t="n"/>
       <c r="P237" s="15" t="n"/>
       <c r="Q237" s="15" t="n"/>
-      <c r="R237" s="15" t="inlineStr">
+      <c r="R237" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21407,12 +21437,12 @@
         <f>HYPERLINK("https://youtu.be/7culUDeVb5Y","watch")</f>
         <v/>
       </c>
-      <c r="G238" s="15" t="inlineStr">
+      <c r="G238" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H238" s="15" t="n">
+      <c r="H238" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I238" s="15" t="n"/>
@@ -21424,7 +21454,7 @@
       <c r="O238" s="15" t="n"/>
       <c r="P238" s="15" t="n"/>
       <c r="Q238" s="15" t="n"/>
-      <c r="R238" s="15" t="inlineStr">
+      <c r="R238" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21485,7 +21515,7 @@
       <c r="O239" s="15" t="n"/>
       <c r="P239" s="15" t="n"/>
       <c r="Q239" s="15" t="n"/>
-      <c r="R239" s="15" t="inlineStr">
+      <c r="R239" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -21546,7 +21576,7 @@
       <c r="O240" s="15" t="n"/>
       <c r="P240" s="15" t="n"/>
       <c r="Q240" s="15" t="n"/>
-      <c r="R240" s="15" t="inlineStr">
+      <c r="R240" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -21555,13 +21585,13 @@
         <f>SUM(H240,J240,L240,N240,P240)</f>
         <v/>
       </c>
-      <c r="T240" s="15" t="inlineStr">
+      <c r="T240" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U240" s="15" t="n"/>
-      <c r="V240" s="15" t="inlineStr">
+      <c r="V240" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -21605,7 +21635,7 @@
         <v/>
       </c>
       <c r="G241" s="15" t="n"/>
-      <c r="H241" s="15" t="n">
+      <c r="H241" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I241" s="15" t="n"/>
@@ -21617,7 +21647,7 @@
       <c r="O241" s="15" t="n"/>
       <c r="P241" s="15" t="n"/>
       <c r="Q241" s="15" t="n"/>
-      <c r="R241" s="15" t="inlineStr">
+      <c r="R241" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21667,12 +21697,12 @@
         <f>HYPERLINK("https://youtu.be/N3bs0HjmrKY","watch")</f>
         <v/>
       </c>
-      <c r="G242" s="15" t="inlineStr">
+      <c r="G242" s="14" t="inlineStr">
         <is>
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H242" s="15" t="n">
+      <c r="H242" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I242" s="15" t="n"/>
@@ -21684,7 +21714,7 @@
       <c r="O242" s="15" t="n"/>
       <c r="P242" s="15" t="n"/>
       <c r="Q242" s="15" t="n"/>
-      <c r="R242" s="15" t="inlineStr">
+      <c r="R242" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -21734,12 +21764,12 @@
         <f>HYPERLINK("https://youtu.be/LlGPrTKqIYg","watch")</f>
         <v/>
       </c>
-      <c r="G243" s="15" t="inlineStr">
+      <c r="G243" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H243" s="15" t="n">
+      <c r="H243" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I243" s="15" t="n"/>
@@ -21751,7 +21781,7 @@
       <c r="O243" s="15" t="n"/>
       <c r="P243" s="15" t="n"/>
       <c r="Q243" s="15" t="n"/>
-      <c r="R243" s="15" t="inlineStr">
+      <c r="R243" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21801,12 +21831,12 @@
         <f>HYPERLINK("https://youtu.be/VYyrgZDkOFY","watch")</f>
         <v/>
       </c>
-      <c r="G244" s="15" t="inlineStr">
+      <c r="G244" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H244" s="15" t="n">
+      <c r="H244" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I244" s="15" t="n"/>
@@ -21818,7 +21848,7 @@
       <c r="O244" s="15" t="n"/>
       <c r="P244" s="15" t="n"/>
       <c r="Q244" s="15" t="n"/>
-      <c r="R244" s="15" t="inlineStr">
+      <c r="R244" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -21868,7 +21898,7 @@
         <f>HYPERLINK("https://youtu.be/LKSHOUDN-i4","watch")</f>
         <v/>
       </c>
-      <c r="G245" s="15" t="inlineStr">
+      <c r="G245" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
@@ -21883,7 +21913,7 @@
       <c r="O245" s="15" t="n"/>
       <c r="P245" s="15" t="n"/>
       <c r="Q245" s="15" t="n"/>
-      <c r="R245" s="15" t="inlineStr">
+      <c r="R245" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -21933,12 +21963,12 @@
         <f>HYPERLINK("https://youtu.be/igNbRZX5e_0","watch")</f>
         <v/>
       </c>
-      <c r="G246" s="15" t="inlineStr">
+      <c r="G246" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H246" s="15" t="n">
+      <c r="H246" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I246" s="15" t="n"/>
@@ -21950,7 +21980,7 @@
       <c r="O246" s="15" t="n"/>
       <c r="P246" s="15" t="n"/>
       <c r="Q246" s="15" t="n"/>
-      <c r="R246" s="15" t="inlineStr">
+      <c r="R246" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -22000,12 +22030,12 @@
         <f>HYPERLINK("https://youtu.be/5BnjVE-BN70","watch")</f>
         <v/>
       </c>
-      <c r="G247" s="15" t="inlineStr">
+      <c r="G247" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H247" s="15" t="n">
+      <c r="H247" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I247" s="15" t="n"/>
@@ -22017,7 +22047,7 @@
       <c r="O247" s="15" t="n"/>
       <c r="P247" s="15" t="n"/>
       <c r="Q247" s="15" t="n"/>
-      <c r="R247" s="15" t="inlineStr">
+      <c r="R247" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22067,12 +22097,12 @@
         <f>HYPERLINK("https://youtu.be/_ccErXVzURs","watch")</f>
         <v/>
       </c>
-      <c r="G248" s="15" t="inlineStr">
+      <c r="G248" s="14" t="inlineStr">
         <is>
           <t>Ninja Spinner (JP)</t>
         </is>
       </c>
-      <c r="H248" s="15" t="n">
+      <c r="H248" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I248" s="15" t="n"/>
@@ -22084,7 +22114,7 @@
       <c r="O248" s="15" t="n"/>
       <c r="P248" s="15" t="n"/>
       <c r="Q248" s="15" t="n"/>
-      <c r="R248" s="15" t="inlineStr">
+      <c r="R248" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -22134,12 +22164,12 @@
         <f>HYPERLINK("https://youtu.be/gSygkzEehmU","watch")</f>
         <v/>
       </c>
-      <c r="G249" s="15" t="inlineStr">
+      <c r="G249" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H249" s="15" t="n">
+      <c r="H249" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I249" s="15" t="n"/>
@@ -22151,7 +22181,7 @@
       <c r="O249" s="15" t="n"/>
       <c r="P249" s="15" t="n"/>
       <c r="Q249" s="15" t="n"/>
-      <c r="R249" s="15" t="inlineStr">
+      <c r="R249" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22201,12 +22231,12 @@
         <f>HYPERLINK("https://youtu.be/4yxqzTeZMAo","watch")</f>
         <v/>
       </c>
-      <c r="G250" s="15" t="inlineStr">
+      <c r="G250" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H250" s="15" t="n">
+      <c r="H250" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I250" s="15" t="n"/>
@@ -22218,7 +22248,7 @@
       <c r="O250" s="15" t="n"/>
       <c r="P250" s="15" t="n"/>
       <c r="Q250" s="15" t="n"/>
-      <c r="R250" s="15" t="inlineStr">
+      <c r="R250" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22268,12 +22298,12 @@
         <f>HYPERLINK("https://youtu.be/PnbibBm1E64","watch")</f>
         <v/>
       </c>
-      <c r="G251" s="15" t="inlineStr">
+      <c r="G251" s="14" t="inlineStr">
         <is>
           <t>Clay Burst (KR)</t>
         </is>
       </c>
-      <c r="H251" s="15" t="n">
+      <c r="H251" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I251" s="15" t="n"/>
@@ -22285,7 +22315,7 @@
       <c r="O251" s="15" t="n"/>
       <c r="P251" s="15" t="n"/>
       <c r="Q251" s="15" t="n"/>
-      <c r="R251" s="15" t="inlineStr">
+      <c r="R251" s="14" t="inlineStr">
         <is>
           <t>Korean Booster Pack</t>
         </is>
@@ -22346,7 +22376,7 @@
       <c r="O252" s="15" t="n"/>
       <c r="P252" s="15" t="n"/>
       <c r="Q252" s="15" t="n"/>
-      <c r="R252" s="15" t="inlineStr">
+      <c r="R252" s="14" t="inlineStr">
         <is>
           <t>Collection Box</t>
         </is>
@@ -22397,7 +22427,7 @@
         <v/>
       </c>
       <c r="G253" s="15" t="n"/>
-      <c r="H253" s="15" t="n">
+      <c r="H253" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I253" s="15" t="n"/>
@@ -22409,7 +22439,7 @@
       <c r="O253" s="15" t="n"/>
       <c r="P253" s="15" t="n"/>
       <c r="Q253" s="15" t="n"/>
-      <c r="R253" s="15" t="inlineStr">
+      <c r="R253" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -22459,12 +22489,12 @@
         <f>HYPERLINK("https://youtu.be/mDDuc-YDvbw","watch")</f>
         <v/>
       </c>
-      <c r="G254" s="15" t="inlineStr">
+      <c r="G254" s="14" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H254" s="15" t="n">
+      <c r="H254" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I254" s="15" t="n"/>
@@ -22476,7 +22506,7 @@
       <c r="O254" s="15" t="n"/>
       <c r="P254" s="15" t="n"/>
       <c r="Q254" s="15" t="n"/>
-      <c r="R254" s="15" t="inlineStr">
+      <c r="R254" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22583,12 +22613,12 @@
         <f>HYPERLINK("https://youtu.be/wHaIoWhy7XE","watch")</f>
         <v/>
       </c>
-      <c r="G256" s="15" t="inlineStr">
+      <c r="G256" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H256" s="15" t="n">
+      <c r="H256" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I256" s="15" t="n"/>
@@ -22600,7 +22630,7 @@
       <c r="O256" s="15" t="n"/>
       <c r="P256" s="15" t="n"/>
       <c r="Q256" s="15" t="n"/>
-      <c r="R256" s="15" t="inlineStr">
+      <c r="R256" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22650,12 +22680,12 @@
         <f>HYPERLINK("https://youtu.be/O-vFg-5cx8E","watch")</f>
         <v/>
       </c>
-      <c r="G257" s="15" t="inlineStr">
+      <c r="G257" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H257" s="15" t="n">
+      <c r="H257" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I257" s="15" t="n"/>
@@ -22667,7 +22697,7 @@
       <c r="O257" s="15" t="n"/>
       <c r="P257" s="15" t="n"/>
       <c r="Q257" s="15" t="n"/>
-      <c r="R257" s="15" t="inlineStr">
+      <c r="R257" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -22717,12 +22747,12 @@
         <f>HYPERLINK("https://youtu.be/yjBNG5dvopc","watch")</f>
         <v/>
       </c>
-      <c r="G258" s="15" t="inlineStr">
+      <c r="G258" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H258" s="15" t="n">
+      <c r="H258" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I258" s="15" t="n"/>
@@ -22734,7 +22764,7 @@
       <c r="O258" s="15" t="n"/>
       <c r="P258" s="15" t="n"/>
       <c r="Q258" s="15" t="n"/>
-      <c r="R258" s="15" t="inlineStr">
+      <c r="R258" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22784,12 +22814,12 @@
         <f>HYPERLINK("https://youtu.be/9J16fnroBBM","watch")</f>
         <v/>
       </c>
-      <c r="G259" s="15" t="inlineStr">
+      <c r="G259" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H259" s="15" t="n">
+      <c r="H259" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I259" s="15" t="n"/>
@@ -22801,7 +22831,7 @@
       <c r="O259" s="15" t="n"/>
       <c r="P259" s="15" t="n"/>
       <c r="Q259" s="15" t="n"/>
-      <c r="R259" s="15" t="inlineStr">
+      <c r="R259" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -22851,12 +22881,12 @@
         <f>HYPERLINK("https://youtu.be/tKOXv-qSYTo","watch")</f>
         <v/>
       </c>
-      <c r="G260" s="15" t="inlineStr">
+      <c r="G260" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H260" s="15" t="n">
+      <c r="H260" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I260" s="15" t="n"/>
@@ -22868,7 +22898,7 @@
       <c r="O260" s="15" t="n"/>
       <c r="P260" s="15" t="n"/>
       <c r="Q260" s="15" t="n"/>
-      <c r="R260" s="15" t="inlineStr">
+      <c r="R260" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -22918,12 +22948,12 @@
         <f>HYPERLINK("https://youtu.be/h-KAo8SScL8","watch")</f>
         <v/>
       </c>
-      <c r="G261" s="15" t="inlineStr">
+      <c r="G261" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H261" s="15" t="n">
+      <c r="H261" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I261" s="15" t="n"/>
@@ -22935,7 +22965,7 @@
       <c r="O261" s="15" t="n"/>
       <c r="P261" s="15" t="n"/>
       <c r="Q261" s="15" t="n"/>
-      <c r="R261" s="15" t="inlineStr">
+      <c r="R261" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -22985,12 +23015,12 @@
         <f>HYPERLINK("https://youtu.be/lByjKSw3s-U","watch")</f>
         <v/>
       </c>
-      <c r="G262" s="15" t="inlineStr">
+      <c r="G262" s="14" t="inlineStr">
         <is>
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H262" s="15" t="n">
+      <c r="H262" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I262" s="15" t="n"/>
@@ -23002,7 +23032,7 @@
       <c r="O262" s="15" t="n"/>
       <c r="P262" s="15" t="n"/>
       <c r="Q262" s="15" t="n"/>
-      <c r="R262" s="15" t="inlineStr">
+      <c r="R262" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23052,12 +23082,12 @@
         <f>HYPERLINK("https://youtu.be/3WxpO0osReg","watch")</f>
         <v/>
       </c>
-      <c r="G263" s="15" t="inlineStr">
+      <c r="G263" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H263" s="15" t="n">
+      <c r="H263" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I263" s="15" t="n"/>
@@ -23069,7 +23099,7 @@
       <c r="O263" s="15" t="n"/>
       <c r="P263" s="15" t="n"/>
       <c r="Q263" s="15" t="n"/>
-      <c r="R263" s="15" t="inlineStr">
+      <c r="R263" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23119,12 +23149,12 @@
         <f>HYPERLINK("https://youtu.be/mxwjJ0oXyUQ","watch")</f>
         <v/>
       </c>
-      <c r="G264" s="15" t="inlineStr">
+      <c r="G264" s="14" t="inlineStr">
         <is>
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H264" s="15" t="n">
+      <c r="H264" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I264" s="15" t="n"/>
@@ -23136,7 +23166,7 @@
       <c r="O264" s="15" t="n"/>
       <c r="P264" s="15" t="n"/>
       <c r="Q264" s="15" t="n"/>
-      <c r="R264" s="15" t="inlineStr">
+      <c r="R264" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23186,12 +23216,12 @@
         <f>HYPERLINK("https://youtu.be/IcQFu0SaoH4","watch")</f>
         <v/>
       </c>
-      <c r="G265" s="15" t="inlineStr">
+      <c r="G265" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H265" s="15" t="n">
+      <c r="H265" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I265" s="15" t="n"/>
@@ -23203,7 +23233,7 @@
       <c r="O265" s="15" t="n"/>
       <c r="P265" s="15" t="n"/>
       <c r="Q265" s="15" t="n"/>
-      <c r="R265" s="15" t="inlineStr">
+      <c r="R265" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23254,7 +23284,7 @@
         <v/>
       </c>
       <c r="G266" s="15" t="n"/>
-      <c r="H266" s="15" t="n">
+      <c r="H266" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I266" s="15" t="n"/>
@@ -23266,7 +23296,7 @@
       <c r="O266" s="15" t="n"/>
       <c r="P266" s="15" t="n"/>
       <c r="Q266" s="15" t="n"/>
-      <c r="R266" s="15" t="inlineStr">
+      <c r="R266" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23316,12 +23346,12 @@
         <f>HYPERLINK("https://youtu.be/juzo0HheF1U","watch")</f>
         <v/>
       </c>
-      <c r="G267" s="15" t="inlineStr">
+      <c r="G267" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H267" s="15" t="n">
+      <c r="H267" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I267" s="15" t="n"/>
@@ -23333,7 +23363,7 @@
       <c r="O267" s="15" t="n"/>
       <c r="P267" s="15" t="n"/>
       <c r="Q267" s="15" t="n"/>
-      <c r="R267" s="15" t="inlineStr">
+      <c r="R267" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23384,7 +23414,7 @@
         <v/>
       </c>
       <c r="G268" s="15" t="n"/>
-      <c r="H268" s="15" t="n">
+      <c r="H268" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I268" s="15" t="n"/>
@@ -23396,7 +23426,7 @@
       <c r="O268" s="15" t="n"/>
       <c r="P268" s="15" t="n"/>
       <c r="Q268" s="15" t="n"/>
-      <c r="R268" s="15" t="inlineStr">
+      <c r="R268" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23446,12 +23476,12 @@
         <f>HYPERLINK("https://youtu.be/NmO2vrjJhg0","watch")</f>
         <v/>
       </c>
-      <c r="G269" s="15" t="inlineStr">
+      <c r="G269" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H269" s="15" t="n">
+      <c r="H269" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I269" s="15" t="n"/>
@@ -23463,7 +23493,7 @@
       <c r="O269" s="15" t="n"/>
       <c r="P269" s="15" t="n"/>
       <c r="Q269" s="15" t="n"/>
-      <c r="R269" s="15" t="inlineStr">
+      <c r="R269" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23513,12 +23543,12 @@
         <f>HYPERLINK("https://youtu.be/SJQCui3NGWw","watch")</f>
         <v/>
       </c>
-      <c r="G270" s="15" t="inlineStr">
+      <c r="G270" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H270" s="15" t="n">
+      <c r="H270" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I270" s="15" t="n"/>
@@ -23530,7 +23560,7 @@
       <c r="O270" s="15" t="n"/>
       <c r="P270" s="15" t="n"/>
       <c r="Q270" s="15" t="n"/>
-      <c r="R270" s="15" t="inlineStr">
+      <c r="R270" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23580,12 +23610,12 @@
         <f>HYPERLINK("https://youtu.be/F9S695pYxZ8","watch")</f>
         <v/>
       </c>
-      <c r="G271" s="15" t="inlineStr">
+      <c r="G271" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H271" s="15" t="n">
+      <c r="H271" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I271" s="15" t="n"/>
@@ -23597,7 +23627,7 @@
       <c r="O271" s="15" t="n"/>
       <c r="P271" s="15" t="n"/>
       <c r="Q271" s="15" t="n"/>
-      <c r="R271" s="15" t="inlineStr">
+      <c r="R271" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23647,12 +23677,12 @@
         <f>HYPERLINK("https://youtu.be/Jtqb7ZpQXos","watch")</f>
         <v/>
       </c>
-      <c r="G272" s="15" t="inlineStr">
+      <c r="G272" s="14" t="inlineStr">
         <is>
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H272" s="15" t="n">
+      <c r="H272" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I272" s="15" t="n"/>
@@ -23664,7 +23694,7 @@
       <c r="O272" s="15" t="n"/>
       <c r="P272" s="15" t="n"/>
       <c r="Q272" s="15" t="n"/>
-      <c r="R272" s="15" t="inlineStr">
+      <c r="R272" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23714,12 +23744,12 @@
         <f>HYPERLINK("https://youtu.be/-e9F0ufKpIQ","watch")</f>
         <v/>
       </c>
-      <c r="G273" s="15" t="inlineStr">
+      <c r="G273" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H273" s="15" t="n">
+      <c r="H273" s="14" t="n">
         <v>9</v>
       </c>
       <c r="I273" s="15" t="n"/>
@@ -23731,7 +23761,7 @@
       <c r="O273" s="15" t="n"/>
       <c r="P273" s="15" t="n"/>
       <c r="Q273" s="15" t="n"/>
-      <c r="R273" s="15" t="inlineStr">
+      <c r="R273" s="14" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -23792,7 +23822,7 @@
       <c r="O274" s="15" t="n"/>
       <c r="P274" s="15" t="n"/>
       <c r="Q274" s="15" t="n"/>
-      <c r="R274" s="15" t="inlineStr">
+      <c r="R274" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -23842,12 +23872,12 @@
         <f>HYPERLINK("https://youtu.be/NWaiWG7vknM","watch")</f>
         <v/>
       </c>
-      <c r="G275" s="15" t="inlineStr">
+      <c r="G275" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H275" s="15" t="n">
+      <c r="H275" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I275" s="15" t="n"/>
@@ -23859,7 +23889,7 @@
       <c r="O275" s="15" t="n"/>
       <c r="P275" s="15" t="n"/>
       <c r="Q275" s="15" t="n"/>
-      <c r="R275" s="15" t="inlineStr">
+      <c r="R275" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -23909,12 +23939,12 @@
         <f>HYPERLINK("https://youtu.be/SOQUDUMboVU","watch")</f>
         <v/>
       </c>
-      <c r="G276" s="15" t="inlineStr">
+      <c r="G276" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H276" s="15" t="n">
+      <c r="H276" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I276" s="15" t="n"/>
@@ -23926,7 +23956,7 @@
       <c r="O276" s="15" t="n"/>
       <c r="P276" s="15" t="n"/>
       <c r="Q276" s="15" t="n"/>
-      <c r="R276" s="15" t="inlineStr">
+      <c r="R276" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -23976,12 +24006,12 @@
         <f>HYPERLINK("https://youtu.be/XaXGDiOpGJs","watch")</f>
         <v/>
       </c>
-      <c r="G277" s="15" t="inlineStr">
+      <c r="G277" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H277" s="15" t="n">
+      <c r="H277" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I277" s="15" t="n"/>
@@ -23993,7 +24023,7 @@
       <c r="O277" s="15" t="n"/>
       <c r="P277" s="15" t="n"/>
       <c r="Q277" s="15" t="n"/>
-      <c r="R277" s="15" t="inlineStr">
+      <c r="R277" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24043,12 +24073,12 @@
         <f>HYPERLINK("https://youtu.be/pof6Ph34E6w","watch")</f>
         <v/>
       </c>
-      <c r="G278" s="15" t="inlineStr">
+      <c r="G278" s="14" t="inlineStr">
         <is>
           <t>Battle Partners (KR)</t>
         </is>
       </c>
-      <c r="H278" s="15" t="n">
+      <c r="H278" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I278" s="15" t="n"/>
@@ -24060,7 +24090,7 @@
       <c r="O278" s="15" t="n"/>
       <c r="P278" s="15" t="n"/>
       <c r="Q278" s="15" t="n"/>
-      <c r="R278" s="15" t="inlineStr">
+      <c r="R278" s="14" t="inlineStr">
         <is>
           <t>Korean Booster Pack</t>
         </is>
@@ -24110,12 +24140,12 @@
         <f>HYPERLINK("https://youtu.be/EvVnOpgwSmo","watch")</f>
         <v/>
       </c>
-      <c r="G279" s="15" t="inlineStr">
+      <c r="G279" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H279" s="15" t="n">
+      <c r="H279" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I279" s="15" t="n"/>
@@ -24127,7 +24157,7 @@
       <c r="O279" s="15" t="n"/>
       <c r="P279" s="15" t="n"/>
       <c r="Q279" s="15" t="n"/>
-      <c r="R279" s="15" t="inlineStr">
+      <c r="R279" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24177,12 +24207,12 @@
         <f>HYPERLINK("https://youtu.be/mbzWBfNI-Qs","watch")</f>
         <v/>
       </c>
-      <c r="G280" s="15" t="inlineStr">
+      <c r="G280" s="14" t="inlineStr">
         <is>
           <t>Crimson Haze (KR)</t>
         </is>
       </c>
-      <c r="H280" s="15" t="n">
+      <c r="H280" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I280" s="15" t="n"/>
@@ -24194,7 +24224,7 @@
       <c r="O280" s="15" t="n"/>
       <c r="P280" s="15" t="n"/>
       <c r="Q280" s="15" t="n"/>
-      <c r="R280" s="15" t="inlineStr">
+      <c r="R280" s="14" t="inlineStr">
         <is>
           <t>Korean Booster Pack</t>
         </is>
@@ -24244,12 +24274,12 @@
         <f>HYPERLINK("https://youtu.be/IuEb3qtjflI","watch")</f>
         <v/>
       </c>
-      <c r="G281" s="15" t="inlineStr">
+      <c r="G281" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H281" s="15" t="n">
+      <c r="H281" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I281" s="15" t="n"/>
@@ -24261,7 +24291,7 @@
       <c r="O281" s="15" t="n"/>
       <c r="P281" s="15" t="n"/>
       <c r="Q281" s="15" t="n"/>
-      <c r="R281" s="15" t="inlineStr">
+      <c r="R281" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24311,12 +24341,12 @@
         <f>HYPERLINK("https://youtu.be/8xqvY3OzugE","watch")</f>
         <v/>
       </c>
-      <c r="G282" s="15" t="inlineStr">
+      <c r="G282" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H282" s="15" t="n">
+      <c r="H282" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I282" s="15" t="n"/>
@@ -24328,7 +24358,7 @@
       <c r="O282" s="15" t="n"/>
       <c r="P282" s="15" t="n"/>
       <c r="Q282" s="15" t="n"/>
-      <c r="R282" s="15" t="inlineStr">
+      <c r="R282" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -24389,7 +24419,7 @@
       <c r="O283" s="15" t="n"/>
       <c r="P283" s="15" t="n"/>
       <c r="Q283" s="15" t="n"/>
-      <c r="R283" s="15" t="inlineStr">
+      <c r="R283" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -24398,13 +24428,13 @@
         <f>SUM(H283,J283,L283,N283,P283)</f>
         <v/>
       </c>
-      <c r="T283" s="15" t="inlineStr">
+      <c r="T283" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U283" s="15" t="n"/>
-      <c r="V283" s="15" t="inlineStr">
+      <c r="V283" s="14" t="inlineStr">
         <is>
           <t>Charizard (any rarity)</t>
         </is>
@@ -24447,12 +24477,12 @@
         <f>HYPERLINK("https://youtu.be/brj3GukGFAE","watch")</f>
         <v/>
       </c>
-      <c r="G284" s="15" t="inlineStr">
+      <c r="G284" s="14" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="H284" s="15" t="n">
+      <c r="H284" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I284" s="15" t="n"/>
@@ -24464,7 +24494,7 @@
       <c r="O284" s="15" t="n"/>
       <c r="P284" s="15" t="n"/>
       <c r="Q284" s="15" t="n"/>
-      <c r="R284" s="15" t="inlineStr">
+      <c r="R284" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24515,7 +24545,7 @@
         <v/>
       </c>
       <c r="G285" s="15" t="n"/>
-      <c r="H285" s="15" t="n">
+      <c r="H285" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I285" s="15" t="n"/>
@@ -24527,7 +24557,7 @@
       <c r="O285" s="15" t="n"/>
       <c r="P285" s="15" t="n"/>
       <c r="Q285" s="15" t="n"/>
-      <c r="R285" s="15" t="inlineStr">
+      <c r="R285" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -24577,12 +24607,12 @@
         <f>HYPERLINK("https://youtu.be/AqZBxDu2wkc","watch")</f>
         <v/>
       </c>
-      <c r="G286" s="15" t="inlineStr">
+      <c r="G286" s="14" t="inlineStr">
         <is>
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H286" s="15" t="n">
+      <c r="H286" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I286" s="15" t="n"/>
@@ -24594,7 +24624,7 @@
       <c r="O286" s="15" t="n"/>
       <c r="P286" s="15" t="n"/>
       <c r="Q286" s="15" t="n"/>
-      <c r="R286" s="15" t="inlineStr">
+      <c r="R286" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24644,19 +24674,15 @@
         <f>HYPERLINK("https://youtu.be/qdzDD_kM4Uk","watch")</f>
         <v/>
       </c>
-      <c r="G287" s="15" t="inlineStr">
+      <c r="G287" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H287" s="15" t="n">
+      <c r="H287" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I287" s="15" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Violet</t>
-        </is>
-      </c>
+      <c r="I287" s="15" t="n"/>
       <c r="J287" s="15" t="n"/>
       <c r="K287" s="15" t="n"/>
       <c r="L287" s="15" t="n"/>
@@ -24665,7 +24691,7 @@
       <c r="O287" s="15" t="n"/>
       <c r="P287" s="15" t="n"/>
       <c r="Q287" s="15" t="n"/>
-      <c r="R287" s="15" t="inlineStr">
+      <c r="R287" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24715,12 +24741,12 @@
         <f>HYPERLINK("https://youtu.be/SQLDjKwVPk4","watch")</f>
         <v/>
       </c>
-      <c r="G288" s="15" t="inlineStr">
+      <c r="G288" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H288" s="15" t="n">
+      <c r="H288" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I288" s="15" t="n"/>
@@ -24732,7 +24758,7 @@
       <c r="O288" s="15" t="n"/>
       <c r="P288" s="15" t="n"/>
       <c r="Q288" s="15" t="n"/>
-      <c r="R288" s="15" t="inlineStr">
+      <c r="R288" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -24782,12 +24808,12 @@
         <f>HYPERLINK("https://youtu.be/n_3lk9V4L64","watch")</f>
         <v/>
       </c>
-      <c r="G289" s="15" t="inlineStr">
+      <c r="G289" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H289" s="15" t="n">
+      <c r="H289" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I289" s="15" t="n"/>
@@ -24799,7 +24825,7 @@
       <c r="O289" s="15" t="n"/>
       <c r="P289" s="15" t="n"/>
       <c r="Q289" s="15" t="n"/>
-      <c r="R289" s="15" t="inlineStr">
+      <c r="R289" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24849,19 +24875,15 @@
         <f>HYPERLINK("https://youtu.be/f9qJ_M3ot3k","watch")</f>
         <v/>
       </c>
-      <c r="G290" s="15" t="inlineStr">
+      <c r="G290" s="14" t="inlineStr">
         <is>
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H290" s="15" t="n">
+      <c r="H290" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I290" s="15" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Violet</t>
-        </is>
-      </c>
+      <c r="I290" s="15" t="n"/>
       <c r="J290" s="15" t="n"/>
       <c r="K290" s="15" t="n"/>
       <c r="L290" s="15" t="n"/>
@@ -24870,7 +24892,7 @@
       <c r="O290" s="15" t="n"/>
       <c r="P290" s="15" t="n"/>
       <c r="Q290" s="15" t="n"/>
-      <c r="R290" s="15" t="inlineStr">
+      <c r="R290" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24920,12 +24942,12 @@
         <f>HYPERLINK("https://youtu.be/LROQ-vFl4Hs","watch")</f>
         <v/>
       </c>
-      <c r="G291" s="15" t="inlineStr">
+      <c r="G291" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H291" s="15" t="n">
+      <c r="H291" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I291" s="15" t="n"/>
@@ -24937,7 +24959,7 @@
       <c r="O291" s="15" t="n"/>
       <c r="P291" s="15" t="n"/>
       <c r="Q291" s="15" t="n"/>
-      <c r="R291" s="15" t="inlineStr">
+      <c r="R291" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -24987,12 +25009,12 @@
         <f>HYPERLINK("https://youtu.be/RMastm9Bosw","watch")</f>
         <v/>
       </c>
-      <c r="G292" s="15" t="inlineStr">
+      <c r="G292" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H292" s="15" t="n">
+      <c r="H292" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I292" s="15" t="n"/>
@@ -25004,7 +25026,7 @@
       <c r="O292" s="15" t="n"/>
       <c r="P292" s="15" t="n"/>
       <c r="Q292" s="15" t="n"/>
-      <c r="R292" s="15" t="inlineStr">
+      <c r="R292" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25054,12 +25076,12 @@
         <f>HYPERLINK("https://youtu.be/vzYuzHFbueo","watch")</f>
         <v/>
       </c>
-      <c r="G293" s="15" t="inlineStr">
+      <c r="G293" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H293" s="15" t="n">
+      <c r="H293" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I293" s="15" t="n"/>
@@ -25071,7 +25093,7 @@
       <c r="O293" s="15" t="n"/>
       <c r="P293" s="15" t="n"/>
       <c r="Q293" s="15" t="n"/>
-      <c r="R293" s="15" t="inlineStr">
+      <c r="R293" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25132,7 +25154,7 @@
       <c r="O294" s="15" t="n"/>
       <c r="P294" s="15" t="n"/>
       <c r="Q294" s="15" t="n"/>
-      <c r="R294" s="15" t="inlineStr">
+      <c r="R294" s="14" t="inlineStr">
         <is>
           <t>Tin</t>
         </is>
@@ -25182,12 +25204,12 @@
         <f>HYPERLINK("https://youtu.be/3dKWTVbCH3I","watch")</f>
         <v/>
       </c>
-      <c r="G295" s="15" t="inlineStr">
+      <c r="G295" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H295" s="15" t="n">
+      <c r="H295" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I295" s="15" t="n"/>
@@ -25199,7 +25221,7 @@
       <c r="O295" s="15" t="n"/>
       <c r="P295" s="15" t="n"/>
       <c r="Q295" s="15" t="n"/>
-      <c r="R295" s="15" t="inlineStr">
+      <c r="R295" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25250,7 +25272,7 @@
         <v/>
       </c>
       <c r="G296" s="15" t="n"/>
-      <c r="H296" s="15" t="n">
+      <c r="H296" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I296" s="15" t="n"/>
@@ -25262,7 +25284,7 @@
       <c r="O296" s="15" t="n"/>
       <c r="P296" s="15" t="n"/>
       <c r="Q296" s="15" t="n"/>
-      <c r="R296" s="15" t="inlineStr">
+      <c r="R296" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25312,12 +25334,12 @@
         <f>HYPERLINK("https://youtu.be/QADrkuqf9pg","watch")</f>
         <v/>
       </c>
-      <c r="G297" s="15" t="inlineStr">
+      <c r="G297" s="14" t="inlineStr">
         <is>
           <t>Mask of Change (KR)</t>
         </is>
       </c>
-      <c r="H297" s="15" t="n">
+      <c r="H297" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I297" s="15" t="n"/>
@@ -25329,7 +25351,7 @@
       <c r="O297" s="15" t="n"/>
       <c r="P297" s="15" t="n"/>
       <c r="Q297" s="15" t="n"/>
-      <c r="R297" s="15" t="inlineStr">
+      <c r="R297" s="14" t="inlineStr">
         <is>
           <t>Korean Booster Pack</t>
         </is>
@@ -25379,19 +25401,15 @@
         <f>HYPERLINK("https://youtu.be/jO7K2zX6Rlg","watch")</f>
         <v/>
       </c>
-      <c r="G298" s="15" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Violet</t>
-        </is>
-      </c>
-      <c r="H298" s="15" t="n">
+      <c r="G298" s="14" t="inlineStr">
+        <is>
+          <t>Violet ex (JP)</t>
+        </is>
+      </c>
+      <c r="H298" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I298" s="15" t="inlineStr">
-        <is>
-          <t>Violet ex (JP)</t>
-        </is>
-      </c>
+      <c r="I298" s="15" t="n"/>
       <c r="J298" s="15" t="n"/>
       <c r="K298" s="15" t="n"/>
       <c r="L298" s="15" t="n"/>
@@ -25400,7 +25418,7 @@
       <c r="O298" s="15" t="n"/>
       <c r="P298" s="15" t="n"/>
       <c r="Q298" s="15" t="n"/>
-      <c r="R298" s="15" t="inlineStr">
+      <c r="R298" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25450,12 +25468,12 @@
         <f>HYPERLINK("https://youtu.be/8jKHh-P7P7M","watch")</f>
         <v/>
       </c>
-      <c r="G299" s="15" t="inlineStr">
+      <c r="G299" s="14" t="inlineStr">
         <is>
           <t>Gem Pack Vol. 2 (CN)</t>
         </is>
       </c>
-      <c r="H299" s="15" t="n">
+      <c r="H299" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I299" s="15" t="n"/>
@@ -25467,7 +25485,7 @@
       <c r="O299" s="15" t="n"/>
       <c r="P299" s="15" t="n"/>
       <c r="Q299" s="15" t="n"/>
-      <c r="R299" s="15" t="inlineStr">
+      <c r="R299" s="14" t="inlineStr">
         <is>
           <t>Chinese Booster Pack</t>
         </is>
@@ -25517,19 +25535,15 @@
         <f>HYPERLINK("https://youtu.be/hLr5iThoO2k","watch")</f>
         <v/>
       </c>
-      <c r="G300" s="15" t="inlineStr">
+      <c r="G300" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H300" s="15" t="n">
+      <c r="H300" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I300" s="15" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Violet</t>
-        </is>
-      </c>
+      <c r="I300" s="15" t="n"/>
       <c r="J300" s="15" t="n"/>
       <c r="K300" s="15" t="n"/>
       <c r="L300" s="15" t="n"/>
@@ -25538,7 +25552,7 @@
       <c r="O300" s="15" t="n"/>
       <c r="P300" s="15" t="n"/>
       <c r="Q300" s="15" t="n"/>
-      <c r="R300" s="15" t="inlineStr">
+      <c r="R300" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -25588,12 +25602,12 @@
         <f>HYPERLINK("https://youtu.be/cmV6P3ssh2g","watch")</f>
         <v/>
       </c>
-      <c r="G301" s="15" t="inlineStr">
+      <c r="G301" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H301" s="15" t="n">
+      <c r="H301" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I301" s="15" t="n"/>
@@ -25605,7 +25619,7 @@
       <c r="O301" s="15" t="n"/>
       <c r="P301" s="15" t="n"/>
       <c r="Q301" s="15" t="n"/>
-      <c r="R301" s="15" t="inlineStr">
+      <c r="R301" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -25655,19 +25669,15 @@
         <f>HYPERLINK("https://youtu.be/SOCAXif6Mzs","watch")</f>
         <v/>
       </c>
-      <c r="G302" s="15" t="inlineStr">
+      <c r="G302" s="14" t="inlineStr">
         <is>
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H302" s="15" t="n">
+      <c r="H302" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I302" s="15" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Violet</t>
-        </is>
-      </c>
+      <c r="I302" s="15" t="n"/>
       <c r="J302" s="15" t="n"/>
       <c r="K302" s="15" t="n"/>
       <c r="L302" s="15" t="n"/>
@@ -25676,7 +25686,7 @@
       <c r="O302" s="15" t="n"/>
       <c r="P302" s="15" t="n"/>
       <c r="Q302" s="15" t="n"/>
-      <c r="R302" s="15" t="inlineStr">
+      <c r="R302" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -25726,12 +25736,12 @@
         <f>HYPERLINK("https://youtu.be/Prq7KI6j1Vk","watch")</f>
         <v/>
       </c>
-      <c r="G303" s="15" t="inlineStr">
+      <c r="G303" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H303" s="15" t="n">
+      <c r="H303" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I303" s="15" t="n"/>
@@ -25743,7 +25753,7 @@
       <c r="O303" s="15" t="n"/>
       <c r="P303" s="15" t="n"/>
       <c r="Q303" s="15" t="n"/>
-      <c r="R303" s="15" t="inlineStr">
+      <c r="R303" s="14" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25793,12 +25803,12 @@
         <f>HYPERLINK("https://youtu.be/-1fhlQB1okI","watch")</f>
         <v/>
       </c>
-      <c r="G304" s="15" t="inlineStr">
+      <c r="G304" s="14" t="inlineStr">
         <is>
           <t>Cyber Judge (JP)</t>
         </is>
       </c>
-      <c r="H304" s="15" t="n">
+      <c r="H304" s="14" t="n">
         <v>1</v>
       </c>
       <c r="I304" s="15" t="n"/>
@@ -25810,7 +25820,7 @@
       <c r="O304" s="15" t="n"/>
       <c r="P304" s="15" t="n"/>
       <c r="Q304" s="15" t="n"/>
-      <c r="R304" s="15" t="inlineStr">
+      <c r="R304" s="14" t="inlineStr">
         <is>
           <t>Japanese Booster Pack</t>
         </is>
@@ -25860,12 +25870,12 @@
         <f>HYPERLINK("https://youtu.be/evnMahizn0I","watch")</f>
         <v/>
       </c>
-      <c r="G305" s="15" t="inlineStr">
+      <c r="G305" s="14" t="inlineStr">
         <is>
           <t>Paldea Evolved</t>
         </is>
       </c>
-      <c r="H305" s="15" t="n">
+      <c r="H305" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I305" s="15" t="n"/>
@@ -25877,7 +25887,7 @@
       <c r="O305" s="15" t="n"/>
       <c r="P305" s="15" t="n"/>
       <c r="Q305" s="15" t="n"/>
-      <c r="R305" s="15" t="inlineStr">
+      <c r="R305" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -25927,12 +25937,12 @@
         <f>HYPERLINK("https://youtu.be/AXOYuKfoBXU","watch")</f>
         <v/>
       </c>
-      <c r="G306" s="15" t="inlineStr">
+      <c r="G306" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H306" s="15" t="n">
+      <c r="H306" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I306" s="15" t="n"/>
@@ -25944,7 +25954,7 @@
       <c r="O306" s="15" t="n"/>
       <c r="P306" s="15" t="n"/>
       <c r="Q306" s="15" t="n"/>
-      <c r="R306" s="15" t="inlineStr">
+      <c r="R306" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -26108,12 +26118,12 @@
         <f>HYPERLINK("https://youtu.be/EOFAhFwJKqw","watch")</f>
         <v/>
       </c>
-      <c r="G309" s="15" t="inlineStr">
+      <c r="G309" s="14" t="inlineStr">
         <is>
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H309" s="15" t="n">
+      <c r="H309" s="14" t="n">
         <v>3</v>
       </c>
       <c r="I309" s="15" t="n"/>
@@ -26125,7 +26135,7 @@
       <c r="O309" s="15" t="n"/>
       <c r="P309" s="15" t="n"/>
       <c r="Q309" s="15" t="n"/>
-      <c r="R309" s="15" t="inlineStr">
+      <c r="R309" s="14" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
@@ -26186,7 +26196,7 @@
       <c r="O310" s="15" t="n"/>
       <c r="P310" s="15" t="n"/>
       <c r="Q310" s="15" t="n"/>
-      <c r="R310" s="15" t="inlineStr">
+      <c r="R310" s="14" t="inlineStr">
         <is>
           <t>ex Premium Collection</t>
         </is>
@@ -26236,40 +26246,20 @@
         <f>HYPERLINK("https://youtu.be/kj7532tb0_I","watch")</f>
         <v/>
       </c>
-      <c r="G311" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="H311" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="I311" s="15" t="inlineStr">
-        <is>
-          <t>Destined Rivals</t>
-        </is>
-      </c>
+      <c r="G311" s="15" t="n"/>
+      <c r="H311" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I311" s="15" t="n"/>
       <c r="J311" s="15" t="n"/>
-      <c r="K311" s="15" t="inlineStr">
-        <is>
-          <t>Surging Sparks</t>
-        </is>
-      </c>
+      <c r="K311" s="15" t="n"/>
       <c r="L311" s="15" t="n"/>
-      <c r="M311" s="15" t="inlineStr">
-        <is>
-          <t>Mega Evolution</t>
-        </is>
-      </c>
+      <c r="M311" s="15" t="n"/>
       <c r="N311" s="15" t="n"/>
-      <c r="O311" s="15" t="inlineStr">
-        <is>
-          <t>Journey Together</t>
-        </is>
-      </c>
+      <c r="O311" s="15" t="n"/>
       <c r="P311" s="15" t="n"/>
       <c r="Q311" s="15" t="n"/>
-      <c r="R311" s="15" t="inlineStr">
+      <c r="R311" s="14" t="inlineStr">
         <is>
           <t>UPC (Ultra Premium Collection)</t>
         </is>
@@ -26278,22 +26268,18 @@
         <f>SUM(H311,J311,L311,N311,P311)</f>
         <v/>
       </c>
-      <c r="T311" s="15" t="inlineStr">
+      <c r="T311" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U311" s="15" t="n"/>
-      <c r="V311" s="15" t="inlineStr">
-        <is>
-          <t>More than one</t>
-        </is>
-      </c>
-      <c r="W311" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V311" s="14" t="inlineStr">
+        <is>
+          <t>Charizard (any rarity)</t>
+        </is>
+      </c>
+      <c r="W311" s="15" t="n"/>
       <c r="X311" s="15" t="n"/>
       <c r="Y311" s="15" t="n"/>
       <c r="Z311" s="15" t="n"/>
@@ -26331,66 +26317,28 @@
         <f>HYPERLINK("https://youtu.be/TN7_ZsuRQSI","watch")</f>
         <v/>
       </c>
-      <c r="G312" s="15" t="inlineStr">
-        <is>
-          <t>Mega Evolution</t>
-        </is>
-      </c>
-      <c r="H312" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I312" s="15" t="inlineStr">
-        <is>
-          <t>Destined Rivals</t>
-        </is>
-      </c>
+      <c r="G312" s="15" t="n"/>
+      <c r="H312" s="15" t="n"/>
+      <c r="I312" s="15" t="n"/>
       <c r="J312" s="15" t="n"/>
-      <c r="K312" s="15" t="inlineStr">
-        <is>
-          <t>Journey Together</t>
-        </is>
-      </c>
+      <c r="K312" s="15" t="n"/>
       <c r="L312" s="15" t="n"/>
       <c r="M312" s="15" t="n"/>
       <c r="N312" s="15" t="n"/>
       <c r="O312" s="15" t="n"/>
       <c r="P312" s="15" t="n"/>
-      <c r="Q312" s="15" t="inlineStr">
-        <is>
-          <t>Fall 2025 Collector Chest</t>
-        </is>
-      </c>
-      <c r="R312" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="Q312" s="15" t="n"/>
+      <c r="R312" s="15" t="n"/>
       <c r="S312" s="15">
         <f>SUM(H312,J312,L312,N312,P312)</f>
         <v/>
       </c>
-      <c r="T312" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="T312" s="15" t="n"/>
       <c r="U312" s="15" t="n"/>
-      <c r="V312" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More than one </t>
-        </is>
-      </c>
-      <c r="W312" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="V312" s="15" t="n"/>
+      <c r="W312" s="15" t="n"/>
       <c r="X312" s="15" t="n"/>
-      <c r="Y312" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Y312" s="15" t="n"/>
       <c r="Z312" s="15" t="n"/>
       <c r="AA312" s="15" t="n"/>
       <c r="AB312" s="15" t="n"/>
@@ -26978,7 +26926,7 @@
         <v>207</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" s="15" t="n"/>
       <c r="G20" s="15" t="n"/>
@@ -27056,7 +27004,7 @@
         <v>258</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15" t="n"/>
       <c r="G23" s="15" t="n"/>
@@ -34566,64 +34514,156 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Dawn</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="D2" s="15" t="n"/>
-      <c r="E2" s="15" t="n"/>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F2" s="21" t="n"/>
       <c r="G2" s="21" t="n"/>
       <c r="H2" s="15" t="n"/>
       <c r="I2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="15" t="n"/>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Mega Gengar ex</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="D3" s="15" t="n"/>
-      <c r="E3" s="15" t="n"/>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F3" s="21" t="n"/>
       <c r="G3" s="21" t="n"/>
       <c r="H3" s="15" t="n"/>
       <c r="I3" s="15" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Mega Gardevoir ex</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="n"/>
       <c r="G4" s="21" t="n"/>
       <c r="H4" s="15" t="n"/>
       <c r="I4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Mega Venusaur ex</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F5" s="21" t="n"/>
       <c r="G5" s="21" t="n"/>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Marshadow</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="21" t="n"/>
       <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Cetitan ex</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="D7" s="15" t="n"/>
       <c r="E7" s="15" t="n"/>
       <c r="F7" s="21" t="n"/>
@@ -34632,121 +34672,305 @@
       <c r="I7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Rotom</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="n"/>
       <c r="G8" s="21" t="n"/>
       <c r="H8" s="15" t="n"/>
       <c r="I8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Noibat</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="21" t="n"/>
       <c r="H9" s="15" t="n"/>
       <c r="I9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Brock's Scouting</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F10" s="21" t="n"/>
       <c r="G10" s="21" t="n"/>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Blaziken ex</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="21" t="n"/>
       <c r="H11" s="15" t="n"/>
       <c r="I11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Scramble Switch</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Surging Sparks</t>
+        </is>
+      </c>
       <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>ACE SPEC Rare</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Cyrano</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Surging Sparks</t>
+        </is>
+      </c>
       <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
       <c r="H13" s="15" t="n"/>
       <c r="I13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Mega Charizard X ex</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>MEP Black Star Promos</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>023</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Black Star Promo</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>kj7532tb0_I</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Oricorio ex</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>MEP Black Star Promos</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Black Star Promo</t>
+        </is>
+      </c>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="21" t="n"/>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>TN7_ZsuRQSI</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Stufful</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F16" s="21" t="n"/>
       <c r="G16" s="21" t="n"/>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>TN7_ZsuRQSI</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Marnie's Grimmsnarl ex</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F17" s="21" t="n"/>
       <c r="G17" s="21" t="n"/>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>TN7_ZsuRQSI</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Wailord</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F18" s="21" t="n"/>
       <c r="G18" s="21" t="n"/>
       <c r="H18" s="15" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -26347,8 +26347,20 @@
       <c r="AE312" s="15" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation sqref="G2:G312 I2:I312 K2:K312 M2:M312 O2:O312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="15">
+    <dataValidation sqref="G2:G312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$A$2:$A$39</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$A$2:$A$39</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$A$2:$A$39</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$A$2:$A$39</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -26357,7 +26369,16 @@
     <dataValidation sqref="V2:V312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$10</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T312 W2:W312 AC2:AC312 AD2:AD312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="W2:W312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD2:AD312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -34434,8 +34455,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="J2:J185 K2:K185" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="J2:J185" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K185" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Collection Box</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Blister</t>
+          <t>Collection Box</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Japanese Booster Pack</t>
+          <t>Blister</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Korean Booster Pack</t>
+          <t>Japanese Booster Pack</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Chinese Booster Pack</t>
+          <t>Korean Booster Pack</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Chinese Booster Pack</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1572,6 +1572,11 @@
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Paldean Fates</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -5399,15 +5404,15 @@
         <f>SUM(H2,J2,L2,N2,P2)</f>
         <v/>
       </c>
-      <c r="T2" s="14" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U2" s="15" t="n"/>
-      <c r="V2" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V2" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W2" s="15" t="n"/>
@@ -5453,7 +5458,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I3" s="15" t="n"/>
@@ -5541,15 +5546,15 @@
         <f>SUM(H4,J4,L4,N4,P4)</f>
         <v/>
       </c>
-      <c r="T4" s="14" t="inlineStr">
+      <c r="T4" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U4" s="15" t="n"/>
-      <c r="V4" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V4" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W4" s="15" t="n"/>
@@ -5595,7 +5600,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I5" s="15" t="n"/>
@@ -5662,7 +5667,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I6" s="15" t="n"/>
@@ -5729,7 +5734,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I7" s="15" t="n"/>
@@ -5750,15 +5755,15 @@
         <f>SUM(H7,J7,L7,N7,P7)</f>
         <v/>
       </c>
-      <c r="T7" s="14" t="inlineStr">
+      <c r="T7" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U7" s="15" t="n"/>
-      <c r="V7" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V7" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W7" s="15" t="n"/>
@@ -5825,15 +5830,15 @@
         <f>SUM(H8,J8,L8,N8,P8)</f>
         <v/>
       </c>
-      <c r="T8" s="14" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U8" s="15" t="n"/>
-      <c r="V8" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V8" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W8" s="15" t="n"/>
@@ -5944,7 +5949,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I10" s="15" t="n"/>
@@ -5965,15 +5970,15 @@
         <f>SUM(H10,J10,L10,N10,P10)</f>
         <v/>
       </c>
-      <c r="T10" s="14" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U10" s="15" t="n"/>
-      <c r="V10" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V10" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W10" s="15" t="n"/>
@@ -6019,7 +6024,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I11" s="15" t="n"/>
@@ -6040,15 +6045,15 @@
         <f>SUM(H11,J11,L11,N11,P11)</f>
         <v/>
       </c>
-      <c r="T11" s="14" t="inlineStr">
+      <c r="T11" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U11" s="15" t="n"/>
-      <c r="V11" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V11" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W11" s="15" t="n"/>
@@ -6094,7 +6099,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="15" t="n"/>
@@ -6115,15 +6120,15 @@
         <f>SUM(H12,J12,L12,N12,P12)</f>
         <v/>
       </c>
-      <c r="T12" s="14" t="inlineStr">
+      <c r="T12" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U12" s="15" t="n"/>
-      <c r="V12" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V12" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W12" s="15" t="n"/>
@@ -6188,15 +6193,15 @@
         <f>SUM(H13,J13,L13,N13,P13)</f>
         <v/>
       </c>
-      <c r="T13" s="14" t="inlineStr">
+      <c r="T13" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U13" s="15" t="n"/>
-      <c r="V13" s="14" t="inlineStr">
-        <is>
-          <t>Double Rare (2 black stars)</t>
+      <c r="V13" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="W13" s="15" t="n"/>
@@ -6242,7 +6247,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I14" s="15" t="n"/>
@@ -6263,15 +6268,15 @@
         <f>SUM(H14,J14,L14,N14,P14)</f>
         <v/>
       </c>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="T14" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U14" s="15" t="n"/>
-      <c r="V14" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V14" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W14" s="15" t="n"/>
@@ -6317,7 +6322,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I15" s="15" t="n"/>
@@ -6405,15 +6410,15 @@
         <f>SUM(H16,J16,L16,N16,P16)</f>
         <v/>
       </c>
-      <c r="T16" s="14" t="inlineStr">
+      <c r="T16" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U16" s="15" t="n"/>
-      <c r="V16" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V16" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W16" s="15" t="n"/>
@@ -6478,15 +6483,15 @@
         <f>SUM(H17,J17,L17,N17,P17)</f>
         <v/>
       </c>
-      <c r="T17" s="14" t="inlineStr">
+      <c r="T17" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U17" s="15" t="n"/>
-      <c r="V17" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V17" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W17" s="15" t="n"/>
@@ -6551,15 +6556,15 @@
         <f>SUM(H18,J18,L18,N18,P18)</f>
         <v/>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="T18" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U18" s="15" t="n"/>
-      <c r="V18" s="14" t="inlineStr">
-        <is>
-          <t>Double Rare (2 black stars)</t>
+      <c r="V18" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="W18" s="15" t="n"/>
@@ -6670,7 +6675,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I20" s="15" t="n"/>
@@ -6691,15 +6696,15 @@
         <f>SUM(H20,J20,L20,N20,P20)</f>
         <v/>
       </c>
-      <c r="T20" s="14" t="inlineStr">
+      <c r="T20" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U20" s="15" t="n"/>
-      <c r="V20" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V20" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W20" s="15" t="n"/>
@@ -6745,7 +6750,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I21" s="15" t="n"/>
@@ -6833,15 +6838,15 @@
         <f>SUM(H22,J22,L22,N22,P22)</f>
         <v/>
       </c>
-      <c r="T22" s="14" t="inlineStr">
+      <c r="T22" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U22" s="15" t="n"/>
-      <c r="V22" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V22" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W22" s="15" t="n"/>
@@ -6906,15 +6911,15 @@
         <f>SUM(H23,J23,L23,N23,P23)</f>
         <v/>
       </c>
-      <c r="T23" s="14" t="inlineStr">
+      <c r="T23" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U23" s="15" t="n"/>
-      <c r="V23" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V23" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W23" s="15" t="n"/>
@@ -7094,7 +7099,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="15" t="n"/>
@@ -7115,15 +7120,15 @@
         <f>SUM(H26,J26,L26,N26,P26)</f>
         <v/>
       </c>
-      <c r="T26" s="14" t="inlineStr">
+      <c r="T26" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U26" s="15" t="n"/>
-      <c r="V26" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V26" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W26" s="15" t="n"/>
@@ -7169,7 +7174,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H27" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I27" s="15" t="n"/>
@@ -7236,7 +7241,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I28" s="15" t="n"/>
@@ -7326,15 +7331,15 @@
         <f>SUM(H29,J29,L29,N29,P29)</f>
         <v/>
       </c>
-      <c r="T29" s="14" t="inlineStr">
+      <c r="T29" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U29" s="15" t="n"/>
-      <c r="V29" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V29" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W29" s="15" t="n"/>
@@ -7510,7 +7515,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H32" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I32" s="15" t="n"/>
@@ -7531,15 +7536,15 @@
         <f>SUM(H32,J32,L32,N32,P32)</f>
         <v/>
       </c>
-      <c r="T32" s="14" t="inlineStr">
+      <c r="T32" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U32" s="15" t="n"/>
-      <c r="V32" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V32" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W32" s="15" t="n"/>
@@ -7585,7 +7590,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H33" s="14" t="n">
+      <c r="H33" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I33" s="15" t="n"/>
@@ -7671,15 +7676,15 @@
         <f>SUM(H34,J34,L34,N34,P34)</f>
         <v/>
       </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="T34" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U34" s="15" t="n"/>
-      <c r="V34" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V34" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W34" s="15" t="n"/>
@@ -7725,7 +7730,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="15" t="n"/>
@@ -7746,15 +7751,15 @@
         <f>SUM(H35,J35,L35,N35,P35)</f>
         <v/>
       </c>
-      <c r="T35" s="14" t="inlineStr">
+      <c r="T35" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U35" s="15" t="n"/>
-      <c r="V35" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V35" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W35" s="15" t="n"/>
@@ -7881,22 +7886,22 @@
       <c r="Q37" s="15" t="n"/>
       <c r="R37" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S37" s="15">
         <f>SUM(H37,J37,L37,N37,P37)</f>
         <v/>
       </c>
-      <c r="T37" s="14" t="inlineStr">
+      <c r="T37" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U37" s="15" t="n"/>
-      <c r="V37" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V37" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W37" s="15" t="n"/>
@@ -7961,15 +7966,15 @@
         <f>SUM(H38,J38,L38,N38,P38)</f>
         <v/>
       </c>
-      <c r="T38" s="14" t="inlineStr">
+      <c r="T38" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U38" s="15" t="n"/>
-      <c r="V38" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V38" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W38" s="15" t="n"/>
@@ -8099,15 +8104,15 @@
         <f>SUM(H40,J40,L40,N40,P40)</f>
         <v/>
       </c>
-      <c r="T40" s="14" t="inlineStr">
+      <c r="T40" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U40" s="15" t="n"/>
-      <c r="V40" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V40" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W40" s="15" t="n"/>
@@ -8230,7 +8235,7 @@
       <c r="Q42" s="15" t="n"/>
       <c r="R42" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S42" s="15">
@@ -8302,15 +8307,15 @@
         <f>SUM(H43,J43,L43,N43,P43)</f>
         <v/>
       </c>
-      <c r="T43" s="14" t="inlineStr">
+      <c r="T43" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U43" s="15" t="n"/>
-      <c r="V43" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V43" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W43" s="15" t="n"/>
@@ -8368,7 +8373,7 @@
       <c r="Q44" s="15" t="n"/>
       <c r="R44" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S44" s="15">
@@ -8436,15 +8441,15 @@
         <f>SUM(H45,J45,L45,N45,P45)</f>
         <v/>
       </c>
-      <c r="T45" s="14" t="inlineStr">
+      <c r="T45" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U45" s="15" t="n"/>
-      <c r="V45" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V45" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W45" s="15" t="n"/>
@@ -8498,7 +8503,7 @@
       <c r="Q46" s="15" t="n"/>
       <c r="R46" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S46" s="15">
@@ -8574,15 +8579,15 @@
         <f>SUM(H47,J47,L47,N47,P47)</f>
         <v/>
       </c>
-      <c r="T47" s="14" t="inlineStr">
+      <c r="T47" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U47" s="15" t="n"/>
-      <c r="V47" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V47" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W47" s="15" t="n"/>
@@ -8640,7 +8645,7 @@
       <c r="Q48" s="15" t="n"/>
       <c r="R48" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S48" s="15">
@@ -8693,7 +8698,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H49" s="14" t="n">
+      <c r="H49" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I49" s="15" t="n"/>
@@ -8714,15 +8719,15 @@
         <f>SUM(H49,J49,L49,N49,P49)</f>
         <v/>
       </c>
-      <c r="T49" s="14" t="inlineStr">
+      <c r="T49" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U49" s="15" t="n"/>
-      <c r="V49" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V49" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W49" s="15" t="n"/>
@@ -8768,7 +8773,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H50" s="14" t="n">
+      <c r="H50" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I50" s="15" t="n"/>
@@ -8847,22 +8852,22 @@
       <c r="Q51" s="15" t="n"/>
       <c r="R51" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S51" s="15">
         <f>SUM(H51,J51,L51,N51,P51)</f>
         <v/>
       </c>
-      <c r="T51" s="14" t="inlineStr">
+      <c r="T51" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U51" s="15" t="n"/>
-      <c r="V51" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V51" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W51" s="15" t="n"/>
@@ -8908,7 +8913,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H52" s="14" t="n">
+      <c r="H52" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I52" s="15" t="n"/>
@@ -8987,7 +8992,7 @@
       <c r="Q53" s="15" t="n"/>
       <c r="R53" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S53" s="15">
@@ -9040,7 +9045,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H54" s="14" t="n">
+      <c r="H54" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I54" s="15" t="n"/>
@@ -9115,7 +9120,7 @@
       <c r="Q55" s="15" t="n"/>
       <c r="R55" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S55" s="15">
@@ -9168,7 +9173,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H56" s="14" t="n">
+      <c r="H56" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I56" s="15" t="n"/>
@@ -9247,7 +9252,7 @@
       <c r="Q57" s="15" t="n"/>
       <c r="R57" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S57" s="15">
@@ -9300,7 +9305,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H58" s="14" t="n">
+      <c r="H58" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I58" s="15" t="n"/>
@@ -9321,15 +9326,15 @@
         <f>SUM(H58,J58,L58,N58,P58)</f>
         <v/>
       </c>
-      <c r="T58" s="14" t="inlineStr">
+      <c r="T58" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U58" s="15" t="n"/>
-      <c r="V58" s="14" t="inlineStr">
-        <is>
-          <t>Illustration Rare (1 gold star)</t>
+      <c r="V58" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="W58" s="15" t="n"/>
@@ -9627,7 +9632,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H63" s="14" t="n">
+      <c r="H63" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I63" s="15" t="n"/>
@@ -9694,7 +9699,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H64" s="14" t="n">
+      <c r="H64" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I64" s="15" t="n"/>
@@ -9818,7 +9823,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H66" s="14" t="n">
+      <c r="H66" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I66" s="15" t="n"/>
@@ -9885,7 +9890,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H67" s="14" t="n">
+      <c r="H67" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="15" t="n"/>
@@ -9952,7 +9957,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H68" s="14" t="n">
+      <c r="H68" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I68" s="15" t="n"/>
@@ -10019,7 +10024,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H69" s="14" t="n">
+      <c r="H69" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I69" s="15" t="n"/>
@@ -10086,7 +10091,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H70" s="14" t="n">
+      <c r="H70" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I70" s="15" t="n"/>
@@ -10153,7 +10158,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H71" s="14" t="n">
+      <c r="H71" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I71" s="15" t="n"/>
@@ -10220,7 +10225,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H72" s="14" t="n">
+      <c r="H72" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I72" s="15" t="n"/>
@@ -10287,7 +10292,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H73" s="14" t="n">
+      <c r="H73" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I73" s="15" t="n"/>
@@ -10421,7 +10426,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H75" s="14" t="n">
+      <c r="H75" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I75" s="15" t="n"/>
@@ -10488,7 +10493,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H76" s="14" t="n">
+      <c r="H76" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I76" s="15" t="n"/>
@@ -10567,22 +10572,22 @@
       <c r="Q77" s="15" t="n"/>
       <c r="R77" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S77" s="15">
         <f>SUM(H77,J77,L77,N77,P77)</f>
         <v/>
       </c>
-      <c r="T77" s="14" t="inlineStr">
+      <c r="T77" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U77" s="15" t="n"/>
-      <c r="V77" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V77" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W77" s="15" t="n"/>
@@ -10636,22 +10641,22 @@
       <c r="Q78" s="15" t="n"/>
       <c r="R78" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S78" s="15">
         <f>SUM(H78,J78,L78,N78,P78)</f>
         <v/>
       </c>
-      <c r="T78" s="14" t="inlineStr">
+      <c r="T78" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U78" s="15" t="n"/>
-      <c r="V78" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V78" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W78" s="15" t="n"/>
@@ -10709,22 +10714,22 @@
       <c r="Q79" s="15" t="n"/>
       <c r="R79" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S79" s="15">
         <f>SUM(H79,J79,L79,N79,P79)</f>
         <v/>
       </c>
-      <c r="T79" s="14" t="inlineStr">
+      <c r="T79" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U79" s="15" t="n"/>
-      <c r="V79" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V79" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W79" s="15" t="n"/>
@@ -10778,22 +10783,22 @@
       <c r="Q80" s="15" t="n"/>
       <c r="R80" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S80" s="15">
         <f>SUM(H80,J80,L80,N80,P80)</f>
         <v/>
       </c>
-      <c r="T80" s="14" t="inlineStr">
+      <c r="T80" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U80" s="15" t="n"/>
-      <c r="V80" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V80" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W80" s="15" t="n"/>
@@ -10839,7 +10844,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H81" s="14" t="n">
+      <c r="H81" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I81" s="15" t="n"/>
@@ -10906,7 +10911,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H82" s="14" t="n">
+      <c r="H82" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I82" s="15" t="n"/>
@@ -10981,22 +10986,22 @@
       <c r="Q83" s="15" t="n"/>
       <c r="R83" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S83" s="15">
         <f>SUM(H83,J83,L83,N83,P83)</f>
         <v/>
       </c>
-      <c r="T83" s="14" t="inlineStr">
+      <c r="T83" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U83" s="15" t="n"/>
-      <c r="V83" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V83" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W83" s="15" t="n"/>
@@ -11054,22 +11059,22 @@
       <c r="Q84" s="15" t="n"/>
       <c r="R84" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S84" s="15">
         <f>SUM(H84,J84,L84,N84,P84)</f>
         <v/>
       </c>
-      <c r="T84" s="14" t="inlineStr">
+      <c r="T84" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U84" s="15" t="n"/>
-      <c r="V84" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V84" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W84" s="15" t="n"/>
@@ -11123,22 +11128,22 @@
       <c r="Q85" s="15" t="n"/>
       <c r="R85" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S85" s="15">
         <f>SUM(H85,J85,L85,N85,P85)</f>
         <v/>
       </c>
-      <c r="T85" s="14" t="inlineStr">
+      <c r="T85" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U85" s="15" t="n"/>
-      <c r="V85" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V85" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W85" s="15" t="n"/>
@@ -11196,22 +11201,22 @@
       <c r="Q86" s="15" t="n"/>
       <c r="R86" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S86" s="15">
         <f>SUM(H86,J86,L86,N86,P86)</f>
         <v/>
       </c>
-      <c r="T86" s="14" t="inlineStr">
+      <c r="T86" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U86" s="15" t="n"/>
-      <c r="V86" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V86" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W86" s="15" t="n"/>
@@ -11257,7 +11262,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H87" s="14" t="n">
+      <c r="H87" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I87" s="15" t="n"/>
@@ -11336,7 +11341,7 @@
       <c r="Q88" s="15" t="n"/>
       <c r="R88" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S88" s="15">
@@ -11389,7 +11394,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H89" s="14" t="n">
+      <c r="H89" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I89" s="15" t="n"/>
@@ -11464,7 +11469,7 @@
       <c r="Q90" s="15" t="n"/>
       <c r="R90" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S90" s="15">
@@ -11517,7 +11522,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H91" s="14" t="n">
+      <c r="H91" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I91" s="15" t="n"/>
@@ -11592,7 +11597,7 @@
       <c r="Q92" s="15" t="n"/>
       <c r="R92" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S92" s="15">
@@ -11645,7 +11650,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H93" s="14" t="n">
+      <c r="H93" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I93" s="15" t="n"/>
@@ -11724,7 +11729,7 @@
       <c r="Q94" s="15" t="n"/>
       <c r="R94" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S94" s="15">
@@ -11777,7 +11782,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H95" s="14" t="n">
+      <c r="H95" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I95" s="15" t="n"/>
@@ -11844,7 +11849,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H96" s="14" t="n">
+      <c r="H96" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I96" s="15" t="n"/>
@@ -11930,15 +11935,15 @@
         <f>SUM(H97,J97,L97,N97,P97)</f>
         <v/>
       </c>
-      <c r="T97" s="14" t="inlineStr">
+      <c r="T97" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U97" s="15" t="n"/>
-      <c r="V97" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V97" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W97" s="15" t="n"/>
@@ -11984,7 +11989,7 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H98" s="14" t="n">
+      <c r="H98" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I98" s="15" t="n"/>
@@ -12074,15 +12079,15 @@
         <f>SUM(H99,J99,L99,N99,P99)</f>
         <v/>
       </c>
-      <c r="T99" s="14" t="inlineStr">
+      <c r="T99" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U99" s="15" t="n"/>
-      <c r="V99" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V99" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W99" s="15" t="n"/>
@@ -12128,7 +12133,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H100" s="14" t="n">
+      <c r="H100" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I100" s="15" t="n"/>
@@ -12325,7 +12330,7 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H103" s="14" t="n">
+      <c r="H103" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I103" s="15" t="n"/>
@@ -12392,7 +12397,7 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H104" s="14" t="n">
+      <c r="H104" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I104" s="15" t="n"/>
@@ -12459,7 +12464,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H105" s="14" t="n">
+      <c r="H105" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I105" s="15" t="n"/>
@@ -12526,7 +12531,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H106" s="14" t="n">
+      <c r="H106" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I106" s="15" t="n"/>
@@ -12715,7 +12720,7 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H109" s="14" t="n">
+      <c r="H109" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I109" s="15" t="n"/>
@@ -12782,7 +12787,7 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H110" s="14" t="n">
+      <c r="H110" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I110" s="15" t="n"/>
@@ -12849,7 +12854,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H111" s="14" t="n">
+      <c r="H111" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I111" s="15" t="n"/>
@@ -12916,7 +12921,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H112" s="14" t="n">
+      <c r="H112" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I112" s="15" t="n"/>
@@ -13044,7 +13049,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H114" s="14" t="n">
+      <c r="H114" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I114" s="15" t="n"/>
@@ -13172,7 +13177,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H116" s="14" t="n">
+      <c r="H116" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I116" s="15" t="n"/>
@@ -13239,7 +13244,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H117" s="14" t="n">
+      <c r="H117" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I117" s="15" t="n"/>
@@ -13306,7 +13311,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H118" s="14" t="n">
+      <c r="H118" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I118" s="15" t="n"/>
@@ -13373,7 +13378,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H119" s="14" t="n">
+      <c r="H119" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I119" s="15" t="n"/>
@@ -13440,7 +13445,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H120" s="14" t="n">
+      <c r="H120" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I120" s="15" t="n"/>
@@ -13507,7 +13512,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H121" s="14" t="n">
+      <c r="H121" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I121" s="15" t="n"/>
@@ -13574,7 +13579,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H122" s="14" t="n">
+      <c r="H122" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I122" s="15" t="n"/>
@@ -13641,7 +13646,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H123" s="14" t="n">
+      <c r="H123" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I123" s="15" t="n"/>
@@ -13708,7 +13713,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H124" s="14" t="n">
+      <c r="H124" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I124" s="15" t="n"/>
@@ -13775,7 +13780,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H125" s="14" t="n">
+      <c r="H125" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I125" s="15" t="n"/>
@@ -13842,7 +13847,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H126" s="14" t="n">
+      <c r="H126" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I126" s="15" t="n"/>
@@ -13909,7 +13914,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H127" s="14" t="n">
+      <c r="H127" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I127" s="15" t="n"/>
@@ -13976,7 +13981,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H128" s="14" t="n">
+      <c r="H128" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I128" s="15" t="n"/>
@@ -14043,7 +14048,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H129" s="14" t="n">
+      <c r="H129" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I129" s="15" t="n"/>
@@ -14110,7 +14115,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H130" s="14" t="n">
+      <c r="H130" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I130" s="15" t="n"/>
@@ -14177,7 +14182,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H131" s="14" t="n">
+      <c r="H131" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I131" s="15" t="n"/>
@@ -14244,7 +14249,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H132" s="14" t="n">
+      <c r="H132" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I132" s="15" t="n"/>
@@ -14311,7 +14316,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H133" s="14" t="n">
+      <c r="H133" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I133" s="15" t="n"/>
@@ -14332,15 +14337,15 @@
         <f>SUM(H133,J133,L133,N133,P133)</f>
         <v/>
       </c>
-      <c r="T133" s="14" t="inlineStr">
+      <c r="T133" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U133" s="15" t="n"/>
-      <c r="V133" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V133" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W133" s="15" t="n"/>
@@ -14386,7 +14391,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H134" s="14" t="n">
+      <c r="H134" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I134" s="15" t="n"/>
@@ -14453,7 +14458,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H135" s="14" t="n">
+      <c r="H135" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I135" s="15" t="n"/>
@@ -14474,15 +14479,15 @@
         <f>SUM(H135,J135,L135,N135,P135)</f>
         <v/>
       </c>
-      <c r="T135" s="14" t="inlineStr">
+      <c r="T135" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U135" s="15" t="n"/>
-      <c r="V135" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V135" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W135" s="15" t="n"/>
@@ -14528,7 +14533,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H136" s="14" t="n">
+      <c r="H136" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I136" s="15" t="n"/>
@@ -14549,15 +14554,15 @@
         <f>SUM(H136,J136,L136,N136,P136)</f>
         <v/>
       </c>
-      <c r="T136" s="14" t="inlineStr">
+      <c r="T136" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U136" s="15" t="n"/>
-      <c r="V136" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V136" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W136" s="15" t="n"/>
@@ -14603,7 +14608,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H137" s="14" t="n">
+      <c r="H137" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I137" s="15" t="n"/>
@@ -14624,15 +14629,15 @@
         <f>SUM(H137,J137,L137,N137,P137)</f>
         <v/>
       </c>
-      <c r="T137" s="14" t="inlineStr">
+      <c r="T137" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U137" s="15" t="n"/>
-      <c r="V137" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V137" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W137" s="15" t="n"/>
@@ -14678,7 +14683,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H138" s="14" t="n">
+      <c r="H138" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I138" s="15" t="n"/>
@@ -14699,15 +14704,15 @@
         <f>SUM(H138,J138,L138,N138,P138)</f>
         <v/>
       </c>
-      <c r="T138" s="14" t="inlineStr">
+      <c r="T138" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U138" s="15" t="n"/>
-      <c r="V138" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V138" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W138" s="15" t="n"/>
@@ -14753,7 +14758,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H139" s="14" t="n">
+      <c r="H139" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I139" s="15" t="n"/>
@@ -14820,7 +14825,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H140" s="14" t="n">
+      <c r="H140" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I140" s="15" t="n"/>
@@ -14887,7 +14892,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H141" s="14" t="n">
+      <c r="H141" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I141" s="15" t="n"/>
@@ -14908,15 +14913,15 @@
         <f>SUM(H141,J141,L141,N141,P141)</f>
         <v/>
       </c>
-      <c r="T141" s="14" t="inlineStr">
+      <c r="T141" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U141" s="15" t="n"/>
-      <c r="V141" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V141" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W141" s="15" t="n"/>
@@ -14962,7 +14967,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H142" s="14" t="n">
+      <c r="H142" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I142" s="15" t="n"/>
@@ -15029,7 +15034,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H143" s="14" t="n">
+      <c r="H143" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I143" s="15" t="n"/>
@@ -15096,7 +15101,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H144" s="14" t="n">
+      <c r="H144" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I144" s="15" t="n"/>
@@ -15163,7 +15168,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H145" s="14" t="n">
+      <c r="H145" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I145" s="15" t="n"/>
@@ -15230,7 +15235,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H146" s="14" t="n">
+      <c r="H146" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I146" s="15" t="n"/>
@@ -15297,7 +15302,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H147" s="14" t="n">
+      <c r="H147" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I147" s="15" t="n"/>
@@ -15364,7 +15369,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H148" s="14" t="n">
+      <c r="H148" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I148" s="15" t="n"/>
@@ -15385,15 +15390,15 @@
         <f>SUM(H148,J148,L148,N148,P148)</f>
         <v/>
       </c>
-      <c r="T148" s="14" t="inlineStr">
+      <c r="T148" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U148" s="15" t="n"/>
-      <c r="V148" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V148" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W148" s="15" t="n"/>
@@ -15439,7 +15444,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H149" s="14" t="n">
+      <c r="H149" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I149" s="15" t="n"/>
@@ -15506,7 +15511,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H150" s="14" t="n">
+      <c r="H150" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I150" s="15" t="n"/>
@@ -15573,7 +15578,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H151" s="14" t="n">
+      <c r="H151" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I151" s="15" t="n"/>
@@ -15594,15 +15599,15 @@
         <f>SUM(H151,J151,L151,N151,P151)</f>
         <v/>
       </c>
-      <c r="T151" s="14" t="inlineStr">
+      <c r="T151" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U151" s="15" t="n"/>
-      <c r="V151" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V151" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W151" s="15" t="n"/>
@@ -15648,7 +15653,7 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H152" s="14" t="n">
+      <c r="H152" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I152" s="15" t="n"/>
@@ -15715,7 +15720,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H153" s="14" t="n">
+      <c r="H153" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I153" s="15" t="n"/>
@@ -15782,7 +15787,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H154" s="14" t="n">
+      <c r="H154" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I154" s="15" t="n"/>
@@ -15803,15 +15808,15 @@
         <f>SUM(H154,J154,L154,N154,P154)</f>
         <v/>
       </c>
-      <c r="T154" s="14" t="inlineStr">
+      <c r="T154" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U154" s="15" t="n"/>
-      <c r="V154" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V154" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W154" s="15" t="n"/>
@@ -15857,7 +15862,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H155" s="14" t="n">
+      <c r="H155" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I155" s="15" t="n"/>
@@ -15878,15 +15883,15 @@
         <f>SUM(H155,J155,L155,N155,P155)</f>
         <v/>
       </c>
-      <c r="T155" s="14" t="inlineStr">
+      <c r="T155" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U155" s="15" t="n"/>
-      <c r="V155" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V155" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W155" s="15" t="n"/>
@@ -15932,7 +15937,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H156" s="14" t="n">
+      <c r="H156" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I156" s="15" t="n"/>
@@ -15999,7 +16004,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H157" s="14" t="n">
+      <c r="H157" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I157" s="15" t="n"/>
@@ -16066,7 +16071,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H158" s="14" t="n">
+      <c r="H158" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I158" s="15" t="n"/>
@@ -16087,15 +16092,15 @@
         <f>SUM(H158,J158,L158,N158,P158)</f>
         <v/>
       </c>
-      <c r="T158" s="14" t="inlineStr">
+      <c r="T158" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U158" s="15" t="n"/>
-      <c r="V158" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V158" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W158" s="15" t="n"/>
@@ -16141,7 +16146,7 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H159" s="14" t="n">
+      <c r="H159" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="15" t="n"/>
@@ -16208,7 +16213,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H160" s="14" t="n">
+      <c r="H160" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I160" s="15" t="n"/>
@@ -16275,7 +16280,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H161" s="14" t="n">
+      <c r="H161" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I161" s="15" t="n"/>
@@ -16296,15 +16301,15 @@
         <f>SUM(H161,J161,L161,N161,P161)</f>
         <v/>
       </c>
-      <c r="T161" s="14" t="inlineStr">
+      <c r="T161" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U161" s="15" t="n"/>
-      <c r="V161" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V161" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W161" s="15" t="n"/>
@@ -16350,7 +16355,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H162" s="14" t="n">
+      <c r="H162" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I162" s="15" t="n"/>
@@ -16417,7 +16422,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H163" s="14" t="n">
+      <c r="H163" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I163" s="15" t="n"/>
@@ -16484,7 +16489,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H164" s="14" t="n">
+      <c r="H164" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I164" s="15" t="n"/>
@@ -16505,15 +16510,15 @@
         <f>SUM(H164,J164,L164,N164,P164)</f>
         <v/>
       </c>
-      <c r="T164" s="14" t="inlineStr">
+      <c r="T164" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U164" s="15" t="n"/>
-      <c r="V164" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V164" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W164" s="15" t="n"/>
@@ -16559,7 +16564,7 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H165" s="14" t="n">
+      <c r="H165" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I165" s="15" t="n"/>
@@ -16626,7 +16631,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H166" s="14" t="n">
+      <c r="H166" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I166" s="15" t="n"/>
@@ -16693,7 +16698,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H167" s="14" t="n">
+      <c r="H167" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I167" s="15" t="n"/>
@@ -16714,15 +16719,15 @@
         <f>SUM(H167,J167,L167,N167,P167)</f>
         <v/>
       </c>
-      <c r="T167" s="14" t="inlineStr">
+      <c r="T167" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U167" s="15" t="n"/>
-      <c r="V167" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V167" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W167" s="15" t="n"/>
@@ -16768,7 +16773,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H168" s="14" t="n">
+      <c r="H168" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I168" s="15" t="n"/>
@@ -16835,7 +16840,7 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H169" s="14" t="n">
+      <c r="H169" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="15" t="n"/>
@@ -16902,7 +16907,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H170" s="14" t="n">
+      <c r="H170" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I170" s="15" t="n"/>
@@ -16969,7 +16974,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H171" s="14" t="n">
+      <c r="H171" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I171" s="15" t="n"/>
@@ -16990,15 +16995,15 @@
         <f>SUM(H171,J171,L171,N171,P171)</f>
         <v/>
       </c>
-      <c r="T171" s="14" t="inlineStr">
+      <c r="T171" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U171" s="15" t="n"/>
-      <c r="V171" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V171" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W171" s="15" t="n"/>
@@ -17044,7 +17049,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H172" s="14" t="n">
+      <c r="H172" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I172" s="15" t="n"/>
@@ -17065,15 +17070,15 @@
         <f>SUM(H172,J172,L172,N172,P172)</f>
         <v/>
       </c>
-      <c r="T172" s="14" t="inlineStr">
+      <c r="T172" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U172" s="15" t="n"/>
-      <c r="V172" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V172" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W172" s="15" t="n"/>
@@ -17119,7 +17124,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H173" s="14" t="n">
+      <c r="H173" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I173" s="15" t="n"/>
@@ -17186,7 +17191,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H174" s="14" t="n">
+      <c r="H174" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I174" s="15" t="n"/>
@@ -17253,7 +17258,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H175" s="14" t="n">
+      <c r="H175" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I175" s="15" t="n"/>
@@ -17320,7 +17325,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H176" s="14" t="n">
+      <c r="H176" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I176" s="15" t="n"/>
@@ -17387,7 +17392,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H177" s="14" t="n">
+      <c r="H177" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I177" s="15" t="n"/>
@@ -17454,7 +17459,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H178" s="14" t="n">
+      <c r="H178" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I178" s="15" t="n"/>
@@ -17521,7 +17526,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H179" s="14" t="n">
+      <c r="H179" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I179" s="15" t="n"/>
@@ -17588,7 +17593,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H180" s="14" t="n">
+      <c r="H180" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I180" s="15" t="n"/>
@@ -17655,7 +17660,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H181" s="14" t="n">
+      <c r="H181" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I181" s="15" t="n"/>
@@ -17722,7 +17727,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H182" s="14" t="n">
+      <c r="H182" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I182" s="15" t="n"/>
@@ -17789,7 +17794,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H183" s="14" t="n">
+      <c r="H183" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="15" t="n"/>
@@ -17810,15 +17815,15 @@
         <f>SUM(H183,J183,L183,N183,P183)</f>
         <v/>
       </c>
-      <c r="T183" s="14" t="inlineStr">
+      <c r="T183" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U183" s="15" t="n"/>
-      <c r="V183" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V183" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W183" s="15" t="n"/>
@@ -17864,7 +17869,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H184" s="14" t="n">
+      <c r="H184" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I184" s="15" t="n"/>
@@ -17931,7 +17936,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H185" s="14" t="n">
+      <c r="H185" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I185" s="15" t="n"/>
@@ -17998,7 +18003,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H186" s="14" t="n">
+      <c r="H186" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I186" s="15" t="n"/>
@@ -18065,7 +18070,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H187" s="14" t="n">
+      <c r="H187" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="15" t="n"/>
@@ -18086,15 +18091,15 @@
         <f>SUM(H187,J187,L187,N187,P187)</f>
         <v/>
       </c>
-      <c r="T187" s="14" t="inlineStr">
+      <c r="T187" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U187" s="15" t="n"/>
-      <c r="V187" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V187" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W187" s="15" t="n"/>
@@ -18140,7 +18145,7 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H188" s="14" t="n">
+      <c r="H188" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I188" s="15" t="n"/>
@@ -18207,7 +18212,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H189" s="14" t="n">
+      <c r="H189" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I189" s="15" t="n"/>
@@ -18274,7 +18279,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H190" s="14" t="n">
+      <c r="H190" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="15" t="n"/>
@@ -18341,7 +18346,7 @@
           <t>Obsidian Flames</t>
         </is>
       </c>
-      <c r="H191" s="14" t="n">
+      <c r="H191" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I191" s="15" t="n"/>
@@ -18362,15 +18367,15 @@
         <f>SUM(H191,J191,L191,N191,P191)</f>
         <v/>
       </c>
-      <c r="T191" s="14" t="inlineStr">
+      <c r="T191" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U191" s="15" t="n"/>
-      <c r="V191" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V191" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W191" s="15" t="n"/>
@@ -18416,7 +18421,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H192" s="14" t="n">
+      <c r="H192" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I192" s="15" t="n"/>
@@ -18437,15 +18442,15 @@
         <f>SUM(H192,J192,L192,N192,P192)</f>
         <v/>
       </c>
-      <c r="T192" s="14" t="inlineStr">
+      <c r="T192" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U192" s="15" t="n"/>
-      <c r="V192" s="14" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+      <c r="V192" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="W192" s="15" t="n"/>
@@ -18491,7 +18496,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H193" s="14" t="n">
+      <c r="H193" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I193" s="15" t="n"/>
@@ -18623,7 +18628,7 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H195" s="14" t="n">
+      <c r="H195" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I195" s="15" t="n"/>
@@ -18751,7 +18756,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H197" s="14" t="n">
+      <c r="H197" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I197" s="15" t="n"/>
@@ -18883,7 +18888,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H199" s="14" t="n">
+      <c r="H199" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I199" s="15" t="n"/>
@@ -19015,7 +19020,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H201" s="14" t="n">
+      <c r="H201" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I201" s="15" t="n"/>
@@ -19143,7 +19148,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H203" s="14" t="n">
+      <c r="H203" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I203" s="15" t="n"/>
@@ -19210,7 +19215,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H204" s="14" t="n">
+      <c r="H204" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I204" s="15" t="n"/>
@@ -19403,7 +19408,7 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H207" s="14" t="n">
+      <c r="H207" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I207" s="15" t="n"/>
@@ -19470,7 +19475,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H208" s="14" t="n">
+      <c r="H208" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I208" s="15" t="n"/>
@@ -19537,7 +19542,7 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H209" s="14" t="n">
+      <c r="H209" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I209" s="15" t="n"/>
@@ -19604,7 +19609,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H210" s="14" t="n">
+      <c r="H210" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I210" s="15" t="n"/>
@@ -19671,7 +19676,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H211" s="14" t="n">
+      <c r="H211" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I211" s="15" t="n"/>
@@ -19734,7 +19739,7 @@
         <v/>
       </c>
       <c r="G212" s="15" t="n"/>
-      <c r="H212" s="14" t="n">
+      <c r="H212" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I212" s="15" t="n"/>
@@ -19801,7 +19806,7 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H213" s="14" t="n">
+      <c r="H213" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I213" s="15" t="n"/>
@@ -19864,7 +19869,7 @@
         <v/>
       </c>
       <c r="G214" s="15" t="n"/>
-      <c r="H214" s="14" t="n">
+      <c r="H214" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I214" s="15" t="n"/>
@@ -19931,7 +19936,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H215" s="14" t="n">
+      <c r="H215" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I215" s="15" t="n"/>
@@ -20059,7 +20064,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H217" s="14" t="n">
+      <c r="H217" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I217" s="15" t="n"/>
@@ -20126,7 +20131,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H218" s="14" t="n">
+      <c r="H218" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I218" s="15" t="n"/>
@@ -20193,7 +20198,7 @@
           <t>Mega Brave (JP)</t>
         </is>
       </c>
-      <c r="H219" s="14" t="n">
+      <c r="H219" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I219" s="15" t="n"/>
@@ -20260,7 +20265,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H220" s="14" t="n">
+      <c r="H220" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I220" s="15" t="n"/>
@@ -20323,7 +20328,7 @@
         <v/>
       </c>
       <c r="G221" s="15" t="n"/>
-      <c r="H221" s="14" t="n">
+      <c r="H221" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I221" s="15" t="n"/>
@@ -20390,7 +20395,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H222" s="14" t="n">
+      <c r="H222" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I222" s="15" t="n"/>
@@ -20518,7 +20523,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H224" s="14" t="n">
+      <c r="H224" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I224" s="15" t="n"/>
@@ -20585,7 +20590,7 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H225" s="14" t="n">
+      <c r="H225" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I225" s="15" t="n"/>
@@ -20652,7 +20657,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H226" s="14" t="n">
+      <c r="H226" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I226" s="15" t="n"/>
@@ -20715,7 +20720,7 @@
         <v/>
       </c>
       <c r="G227" s="15" t="n"/>
-      <c r="H227" s="14" t="n">
+      <c r="H227" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I227" s="15" t="n"/>
@@ -20778,7 +20783,7 @@
         <v/>
       </c>
       <c r="G228" s="15" t="n"/>
-      <c r="H228" s="14" t="n">
+      <c r="H228" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I228" s="15" t="n"/>
@@ -20845,7 +20850,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H229" s="14" t="n">
+      <c r="H229" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I229" s="15" t="n"/>
@@ -20912,7 +20917,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H230" s="14" t="n">
+      <c r="H230" s="15" t="n">
         <v>6</v>
       </c>
       <c r="I230" s="15" t="n"/>
@@ -20979,7 +20984,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H231" s="14" t="n">
+      <c r="H231" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I231" s="15" t="n"/>
@@ -21054,7 +21059,7 @@
       <c r="Q232" s="15" t="n"/>
       <c r="R232" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S232" s="15">
@@ -21107,7 +21112,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H233" s="14" t="n">
+      <c r="H233" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I233" s="15" t="n"/>
@@ -21174,7 +21179,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H234" s="14" t="n">
+      <c r="H234" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I234" s="15" t="n"/>
@@ -21241,7 +21246,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H235" s="14" t="n">
+      <c r="H235" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I235" s="15" t="n"/>
@@ -21308,7 +21313,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H236" s="14" t="n">
+      <c r="H236" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I236" s="15" t="n"/>
@@ -21375,7 +21380,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H237" s="14" t="n">
+      <c r="H237" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I237" s="15" t="n"/>
@@ -21442,7 +21447,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H238" s="14" t="n">
+      <c r="H238" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I238" s="15" t="n"/>
@@ -21517,7 +21522,7 @@
       <c r="Q239" s="15" t="n"/>
       <c r="R239" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S239" s="15">
@@ -21585,15 +21590,15 @@
         <f>SUM(H240,J240,L240,N240,P240)</f>
         <v/>
       </c>
-      <c r="T240" s="14" t="inlineStr">
+      <c r="T240" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U240" s="15" t="n"/>
-      <c r="V240" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V240" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W240" s="15" t="n"/>
@@ -21635,7 +21640,7 @@
         <v/>
       </c>
       <c r="G241" s="15" t="n"/>
-      <c r="H241" s="14" t="n">
+      <c r="H241" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I241" s="15" t="n"/>
@@ -21702,7 +21707,7 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H242" s="14" t="n">
+      <c r="H242" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I242" s="15" t="n"/>
@@ -21769,7 +21774,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H243" s="14" t="n">
+      <c r="H243" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I243" s="15" t="n"/>
@@ -21836,7 +21841,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H244" s="14" t="n">
+      <c r="H244" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I244" s="15" t="n"/>
@@ -21968,7 +21973,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H246" s="14" t="n">
+      <c r="H246" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I246" s="15" t="n"/>
@@ -22035,7 +22040,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H247" s="14" t="n">
+      <c r="H247" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I247" s="15" t="n"/>
@@ -22102,7 +22107,7 @@
           <t>Ninja Spinner (JP)</t>
         </is>
       </c>
-      <c r="H248" s="14" t="n">
+      <c r="H248" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I248" s="15" t="n"/>
@@ -22169,7 +22174,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H249" s="14" t="n">
+      <c r="H249" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I249" s="15" t="n"/>
@@ -22236,7 +22241,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H250" s="14" t="n">
+      <c r="H250" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I250" s="15" t="n"/>
@@ -22303,7 +22308,7 @@
           <t>Clay Burst (KR)</t>
         </is>
       </c>
-      <c r="H251" s="14" t="n">
+      <c r="H251" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I251" s="15" t="n"/>
@@ -22427,7 +22432,7 @@
         <v/>
       </c>
       <c r="G253" s="15" t="n"/>
-      <c r="H253" s="14" t="n">
+      <c r="H253" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I253" s="15" t="n"/>
@@ -22494,7 +22499,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H254" s="14" t="n">
+      <c r="H254" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I254" s="15" t="n"/>
@@ -22618,7 +22623,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H256" s="14" t="n">
+      <c r="H256" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I256" s="15" t="n"/>
@@ -22685,7 +22690,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H257" s="14" t="n">
+      <c r="H257" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I257" s="15" t="n"/>
@@ -22752,7 +22757,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H258" s="14" t="n">
+      <c r="H258" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I258" s="15" t="n"/>
@@ -22819,7 +22824,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H259" s="14" t="n">
+      <c r="H259" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I259" s="15" t="n"/>
@@ -22886,7 +22891,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H260" s="14" t="n">
+      <c r="H260" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I260" s="15" t="n"/>
@@ -22953,7 +22958,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H261" s="14" t="n">
+      <c r="H261" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I261" s="15" t="n"/>
@@ -23020,7 +23025,7 @@
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H262" s="14" t="n">
+      <c r="H262" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I262" s="15" t="n"/>
@@ -23087,7 +23092,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H263" s="14" t="n">
+      <c r="H263" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I263" s="15" t="n"/>
@@ -23154,7 +23159,7 @@
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H264" s="14" t="n">
+      <c r="H264" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I264" s="15" t="n"/>
@@ -23221,7 +23226,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H265" s="14" t="n">
+      <c r="H265" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I265" s="15" t="n"/>
@@ -23284,7 +23289,7 @@
         <v/>
       </c>
       <c r="G266" s="15" t="n"/>
-      <c r="H266" s="14" t="n">
+      <c r="H266" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I266" s="15" t="n"/>
@@ -23351,7 +23356,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H267" s="14" t="n">
+      <c r="H267" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I267" s="15" t="n"/>
@@ -23414,7 +23419,7 @@
         <v/>
       </c>
       <c r="G268" s="15" t="n"/>
-      <c r="H268" s="14" t="n">
+      <c r="H268" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I268" s="15" t="n"/>
@@ -23481,7 +23486,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H269" s="14" t="n">
+      <c r="H269" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I269" s="15" t="n"/>
@@ -23548,7 +23553,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H270" s="14" t="n">
+      <c r="H270" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I270" s="15" t="n"/>
@@ -23615,7 +23620,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H271" s="14" t="n">
+      <c r="H271" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I271" s="15" t="n"/>
@@ -23682,7 +23687,7 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H272" s="14" t="n">
+      <c r="H272" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I272" s="15" t="n"/>
@@ -23749,7 +23754,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H273" s="14" t="n">
+      <c r="H273" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I273" s="15" t="n"/>
@@ -23877,7 +23882,7 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H275" s="14" t="n">
+      <c r="H275" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I275" s="15" t="n"/>
@@ -23944,7 +23949,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H276" s="14" t="n">
+      <c r="H276" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I276" s="15" t="n"/>
@@ -24011,7 +24016,7 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H277" s="14" t="n">
+      <c r="H277" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I277" s="15" t="n"/>
@@ -24078,7 +24083,7 @@
           <t>Battle Partners (KR)</t>
         </is>
       </c>
-      <c r="H278" s="14" t="n">
+      <c r="H278" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I278" s="15" t="n"/>
@@ -24145,7 +24150,7 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H279" s="14" t="n">
+      <c r="H279" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I279" s="15" t="n"/>
@@ -24212,7 +24217,7 @@
           <t>Crimson Haze (KR)</t>
         </is>
       </c>
-      <c r="H280" s="14" t="n">
+      <c r="H280" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I280" s="15" t="n"/>
@@ -24279,7 +24284,7 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H281" s="14" t="n">
+      <c r="H281" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I281" s="15" t="n"/>
@@ -24346,7 +24351,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H282" s="14" t="n">
+      <c r="H282" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I282" s="15" t="n"/>
@@ -24428,15 +24433,15 @@
         <f>SUM(H283,J283,L283,N283,P283)</f>
         <v/>
       </c>
-      <c r="T283" s="14" t="inlineStr">
+      <c r="T283" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U283" s="15" t="n"/>
-      <c r="V283" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
+      <c r="V283" s="15" t="inlineStr">
+        <is>
+          <t>Charizard</t>
         </is>
       </c>
       <c r="W283" s="15" t="n"/>
@@ -24482,7 +24487,7 @@
           <t>151</t>
         </is>
       </c>
-      <c r="H284" s="14" t="n">
+      <c r="H284" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I284" s="15" t="n"/>
@@ -24545,7 +24550,7 @@
         <v/>
       </c>
       <c r="G285" s="15" t="n"/>
-      <c r="H285" s="14" t="n">
+      <c r="H285" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I285" s="15" t="n"/>
@@ -24612,7 +24617,7 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H286" s="14" t="n">
+      <c r="H286" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I286" s="15" t="n"/>
@@ -24679,7 +24684,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H287" s="14" t="n">
+      <c r="H287" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I287" s="15" t="n"/>
@@ -24746,7 +24751,7 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H288" s="14" t="n">
+      <c r="H288" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I288" s="15" t="n"/>
@@ -24813,7 +24818,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H289" s="14" t="n">
+      <c r="H289" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I289" s="15" t="n"/>
@@ -24880,7 +24885,7 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H290" s="14" t="n">
+      <c r="H290" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I290" s="15" t="n"/>
@@ -24947,7 +24952,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H291" s="14" t="n">
+      <c r="H291" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I291" s="15" t="n"/>
@@ -25014,7 +25019,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H292" s="14" t="n">
+      <c r="H292" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I292" s="15" t="n"/>
@@ -25081,7 +25086,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H293" s="14" t="n">
+      <c r="H293" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I293" s="15" t="n"/>
@@ -25209,7 +25214,7 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H295" s="14" t="n">
+      <c r="H295" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I295" s="15" t="n"/>
@@ -25272,7 +25277,7 @@
         <v/>
       </c>
       <c r="G296" s="15" t="n"/>
-      <c r="H296" s="14" t="n">
+      <c r="H296" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I296" s="15" t="n"/>
@@ -25339,7 +25344,7 @@
           <t>Mask of Change (KR)</t>
         </is>
       </c>
-      <c r="H297" s="14" t="n">
+      <c r="H297" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I297" s="15" t="n"/>
@@ -25406,7 +25411,7 @@
           <t>Violet ex (JP)</t>
         </is>
       </c>
-      <c r="H298" s="14" t="n">
+      <c r="H298" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I298" s="15" t="n"/>
@@ -25473,7 +25478,7 @@
           <t>Gem Pack Vol. 2 (CN)</t>
         </is>
       </c>
-      <c r="H299" s="14" t="n">
+      <c r="H299" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I299" s="15" t="n"/>
@@ -25540,7 +25545,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H300" s="14" t="n">
+      <c r="H300" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I300" s="15" t="n"/>
@@ -25607,7 +25612,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H301" s="14" t="n">
+      <c r="H301" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I301" s="15" t="n"/>
@@ -25674,7 +25679,7 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H302" s="14" t="n">
+      <c r="H302" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I302" s="15" t="n"/>
@@ -25741,7 +25746,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H303" s="14" t="n">
+      <c r="H303" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I303" s="15" t="n"/>
@@ -25808,7 +25813,7 @@
           <t>Cyber Judge (JP)</t>
         </is>
       </c>
-      <c r="H304" s="14" t="n">
+      <c r="H304" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I304" s="15" t="n"/>
@@ -25875,7 +25880,7 @@
           <t>Paldea Evolved</t>
         </is>
       </c>
-      <c r="H305" s="14" t="n">
+      <c r="H305" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I305" s="15" t="n"/>
@@ -25942,7 +25947,7 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H306" s="14" t="n">
+      <c r="H306" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I306" s="15" t="n"/>
@@ -26123,7 +26128,7 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H309" s="14" t="n">
+      <c r="H309" s="15" t="n">
         <v>3</v>
       </c>
       <c r="I309" s="15" t="n"/>
@@ -26198,7 +26203,7 @@
       <c r="Q310" s="15" t="n"/>
       <c r="R310" s="14" t="inlineStr">
         <is>
-          <t>ex Premium Collection</t>
+          <t>ex Box</t>
         </is>
       </c>
       <c r="S310" s="15">
@@ -26246,17 +26251,35 @@
         <f>HYPERLINK("https://youtu.be/kj7532tb0_I","watch")</f>
         <v/>
       </c>
-      <c r="G311" s="15" t="n"/>
-      <c r="H311" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="I311" s="15" t="n"/>
+      <c r="G311" s="14" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="H311" s="14" t="n"/>
+      <c r="I311" s="14" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="J311" s="15" t="n"/>
-      <c r="K311" s="15" t="n"/>
+      <c r="K311" s="14" t="inlineStr">
+        <is>
+          <t>Surging Sparks</t>
+        </is>
+      </c>
       <c r="L311" s="15" t="n"/>
-      <c r="M311" s="15" t="n"/>
+      <c r="M311" s="14" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="N311" s="15" t="n"/>
-      <c r="O311" s="15" t="n"/>
+      <c r="O311" s="14" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="P311" s="15" t="n"/>
       <c r="Q311" s="15" t="n"/>
       <c r="R311" s="14" t="inlineStr">
@@ -26268,18 +26291,26 @@
         <f>SUM(H311,J311,L311,N311,P311)</f>
         <v/>
       </c>
-      <c r="T311" s="14" t="inlineStr">
+      <c r="T311" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="U311" s="15" t="n"/>
-      <c r="V311" s="14" t="inlineStr">
-        <is>
-          <t>Charizard (any rarity)</t>
-        </is>
-      </c>
-      <c r="W311" s="15" t="n"/>
+      <c r="U311" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames - Trainer - Dawn - Double Silver Star - Ultra Rare, Phantasmal Flames - Mega Gengar ex - Double Black Star - Double Rare , Mega Evolution - Mega Gardevoir ex - Double Silver Star - Ultra Rare , Mega Evolution - Mega Venusaur ex - Double Black Star - Double Rare , Mega Evolution - Marshadow - Single Gold Star - Illustration Rare ,  Destined Rivals - Cetitan ex - Double Black Star , Destined Rivals - Rotom - Single Gold Star - Illustration Rare, Journey Together - Noibat - Single Gold Star - Illustration Rare, Journey Together - Trainer - Brock's Scouting - Double Silver Star - Ultra Rare , Journey Together - Blaziken ex - Double Black Star - Double Rare, Surging Sparks - Trainer - Scramble Switch - Single Pink Star -  ACE SPEC Rare , Surging Sparks - Trainer - Cyrano - Double Silver Star - Ultra Rare, Phantasmal Falmes - Charizard X ex - Black Star Promo Card , Phantasmal Flames - Oricorio ex - Black Star Promo Card</t>
+        </is>
+      </c>
+      <c r="V311" s="15" t="inlineStr">
+        <is>
+          <t>More than one</t>
+        </is>
+      </c>
+      <c r="W311" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X311" s="15" t="n"/>
       <c r="Y311" s="15" t="n"/>
       <c r="Z311" s="15" t="n"/>
@@ -26287,7 +26318,11 @@
       <c r="AB311" s="15" t="n"/>
       <c r="AC311" s="15" t="n"/>
       <c r="AD311" s="15" t="n"/>
-      <c r="AE311" s="15" t="n"/>
+      <c r="AE311" s="15" t="inlineStr">
+        <is>
+          <t>Previously logged 18 packs in total. Split it across the Packs columns.</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
@@ -26317,34 +26352,78 @@
         <f>HYPERLINK("https://youtu.be/TN7_ZsuRQSI","watch")</f>
         <v/>
       </c>
-      <c r="G312" s="15" t="n"/>
+      <c r="G312" s="14" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="H312" s="15" t="n"/>
-      <c r="I312" s="15" t="n"/>
+      <c r="I312" s="14" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="J312" s="15" t="n"/>
-      <c r="K312" s="15" t="n"/>
+      <c r="K312" s="14" t="inlineStr">
+        <is>
+          <t>Journey Together</t>
+        </is>
+      </c>
       <c r="L312" s="15" t="n"/>
       <c r="M312" s="15" t="n"/>
       <c r="N312" s="15" t="n"/>
       <c r="O312" s="15" t="n"/>
       <c r="P312" s="15" t="n"/>
-      <c r="Q312" s="15" t="n"/>
-      <c r="R312" s="15" t="n"/>
+      <c r="Q312" s="15" t="inlineStr">
+        <is>
+          <t>Fall 2025 Collector Chest</t>
+        </is>
+      </c>
+      <c r="R312" s="14" t="inlineStr">
+        <is>
+          <t>Tin</t>
+        </is>
+      </c>
       <c r="S312" s="15">
         <f>SUM(H312,J312,L312,N312,P312)</f>
         <v/>
       </c>
-      <c r="T312" s="15" t="n"/>
-      <c r="U312" s="15" t="n"/>
-      <c r="V312" s="15" t="n"/>
-      <c r="W312" s="15" t="n"/>
+      <c r="T312" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U312" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution - Stufful - Single Gold star - Illustration Rare , Destined Rivals - Marnie's Grimmsnarl ex , Double Black Star - Double Rare , Journey Together - Wailord - Single Gold Star - Illustration Rare</t>
+        </is>
+      </c>
+      <c r="V312" s="15" t="inlineStr">
+        <is>
+          <t>More than one</t>
+        </is>
+      </c>
+      <c r="W312" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X312" s="15" t="n"/>
-      <c r="Y312" s="15" t="n"/>
+      <c r="Y312" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="Z312" s="15" t="n"/>
       <c r="AA312" s="15" t="n"/>
       <c r="AB312" s="15" t="n"/>
       <c r="AC312" s="15" t="n"/>
       <c r="AD312" s="15" t="n"/>
-      <c r="AE312" s="15" t="n"/>
+      <c r="AE312" s="15" t="inlineStr">
+        <is>
+          <t>Previously logged 6 packs in total. Split it across the Packs columns.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="15">
@@ -26364,7 +26443,7 @@
       <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$B$2:$B$17</formula1>
+      <formula1>=Lists!$B$2:$B$18</formula1>
     </dataValidation>
     <dataValidation sqref="V2:V312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$10</formula1>
@@ -26583,7 +26662,7 @@
         <v>130</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="15" t="n"/>
       <c r="G6" s="15" t="n"/>
@@ -26609,7 +26688,7 @@
         <v>188</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
@@ -26687,7 +26766,7 @@
         <v>244</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
@@ -26713,7 +26792,7 @@
         <v>190</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" s="15" t="n"/>
       <c r="G11" s="15" t="n"/>
@@ -26765,7 +26844,7 @@
         <v>252</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -26256,7 +26256,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H311" s="14" t="n"/>
+      <c r="H311" s="15" t="n">
+        <v>18</v>
+      </c>
       <c r="I311" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
@@ -26320,7 +26322,7 @@
       <c r="AD311" s="15" t="n"/>
       <c r="AE311" s="15" t="inlineStr">
         <is>
-          <t>Previously logged 18 packs in total. Split it across the Packs columns.</t>
+          <t>All 18 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26359,9 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H312" s="15" t="n"/>
+      <c r="H312" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="I312" s="14" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
@@ -26421,7 +26425,7 @@
       <c r="AD312" s="15" t="n"/>
       <c r="AE312" s="15" t="inlineStr">
         <is>
-          <t>Previously logged 6 packs in total. Split it across the Packs columns.</t>
+          <t>All 6 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -26430,7 +26430,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="15">
+  <dataValidations count="14">
     <dataValidation sqref="G2:G312" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
@@ -26473,9 +26473,6 @@
     <dataValidation sqref="Q2:Q312" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$F$2:$F$28</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U312" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$G$2:$G$501</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -234,6 +234,64 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Garbage Rips</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Start typing and pick from the list. If a set is missing, tell Claude rather than typing it freehand.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>How many packs from the set in the Set column, not the whole rip.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>COMPUTED. Do not type here.
+It adds up Packs, Packs 2, Packs 3, Packs 4 and Packs 5.
+Put the count for each set in that set's own Packs column and this
+adds itself up. Typing over it deletes the sum for that row.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>The headline card, written however you like.
+If a rip produced SEVERAL cards worth naming, set Hit Rarity to
+"More than one" and list them one per row on the My Hits tab.
+One card per row there means the site can price them and link them.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Read the star row at the bottom of the card.
+Mega Hyper Rare: one big yellow star.
+Hyper Rare: three gold stars.
+Special Illustration Rare: two gold stars.
+Illustration Rare: one gold star.
+Ultra Rare: two silver stars.
+Double Rare: two black stars.
+Rare: one black star.
+ACE SPEC Rare: one pink star.
+Charizard: any rarity, it is its own category here.
+More than one: several notable cards, list them on My Hits.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>The Hall of Fame band on the home page.
+Separate from the Hits playlist: this is the shortlist, that is a
+YouTube playlist. A video can be in one, both or neither.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -843,7 +901,7 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
@@ -924,7 +982,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Mega Hyper Rare (big yellow star)</t>
+          <t>Mega Hyper Rare</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -981,7 +1039,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Hyper Rare (3 gold stars)</t>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1038,7 +1096,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Special Illustration Rare (2 gold stars)</t>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1090,7 +1148,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Illustration Rare (1 gold star)</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1142,7 +1200,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Ultra Rare (2 silver stars)</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1194,7 +1252,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Double Rare (2 black stars)</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1246,7 +1304,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Rare (1 black star)</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1293,7 +1351,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Charizard (any rarity)</t>
+          <t>ACE SPEC Rare</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1335,7 +1393,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>No hit</t>
+          <t>Super Rare</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1375,6 +1433,11 @@
           <t>ex Special Collection</t>
         </is>
       </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Charizard</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Chaos Rising ETB</t>
@@ -1412,6 +1475,11 @@
           <t>ex Box</t>
         </is>
       </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>More than one</t>
+        </is>
+      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Chaos Rising ETB : The First Pack Reality</t>
@@ -1444,6 +1512,11 @@
           <t>Collection Box</t>
         </is>
       </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>No hit</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Destined Rivals</t>
@@ -1468,7 +1541,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Blister</t>
+          <t>Knock Out Collection</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1495,7 +1568,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Japanese Booster Pack</t>
+          <t>Blister</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1522,7 +1595,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Korean Booster Pack</t>
+          <t>Japanese Booster Pack</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1549,7 +1622,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Chinese Booster Pack</t>
+          <t>Korean Booster Pack</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1576,7 +1649,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Chinese Booster Pack</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1599,6 +1672,11 @@
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Paradox Rift</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -5383,7 +5461,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="15" t="n"/>
@@ -5395,7 +5473,7 @@
       <c r="O2" s="15" t="n"/>
       <c r="P2" s="15" t="n"/>
       <c r="Q2" s="15" t="n"/>
-      <c r="R2" s="14" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -5404,15 +5482,15 @@
         <f>SUM(H2,J2,L2,N2,P2)</f>
         <v/>
       </c>
-      <c r="T2" s="14" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="U2" s="15" t="n"/>
-      <c r="V2" s="14" t="inlineStr">
-        <is>
-          <t>Hyper Rare (3 gold stars)</t>
+      <c r="V2" s="15" t="inlineStr">
+        <is>
+          <t>Hyper Rare</t>
         </is>
       </c>
       <c r="W2" s="15" t="n"/>
@@ -5458,7 +5536,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="15" t="n">
         <v>9</v>
       </c>
       <c r="I3" s="15" t="n"/>
@@ -5470,7 +5548,7 @@
       <c r="O3" s="15" t="n"/>
       <c r="P3" s="15" t="n"/>
       <c r="Q3" s="15" t="n"/>
-      <c r="R3" s="14" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr">
         <is>
           <t>ETB (Elite Trainer Box)</t>
         </is>
@@ -5525,7 +5603,7 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="15" t="n"/>
@@ -5537,7 +5615,7 @@
       <c r="O4" s="15" t="n"/>
       <c r="P4" s="15" t="n"/>
       <c r="Q4" s="15" t="n"/>
-      <c r="R4" s="14" t="inlineStr">
+      <c r="R4" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -5667,7 +5745,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="15" t="n"/>
@@ -5679,7 +5757,7 @@
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
       <c r="Q6" s="15" t="n"/>
-      <c r="R6" s="14" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -5951,7 +6029,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="15" t="n"/>
@@ -5963,7 +6041,7 @@
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
       <c r="Q10" s="15" t="n"/>
-      <c r="R10" s="14" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -6531,7 +6609,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="15" t="n"/>
@@ -6543,7 +6621,7 @@
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
-      <c r="R18" s="14" t="inlineStr">
+      <c r="R18" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -6959,7 +7037,7 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="15" t="n"/>
@@ -6971,7 +7049,7 @@
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
-      <c r="R24" s="14" t="inlineStr">
+      <c r="R24" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -10501,7 +10579,7 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H76" s="14" t="n">
+      <c r="H76" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I76" s="15" t="n"/>
@@ -10513,7 +10591,7 @@
       <c r="O76" s="15" t="n"/>
       <c r="P76" s="15" t="n"/>
       <c r="Q76" s="15" t="n"/>
-      <c r="R76" s="14" t="inlineStr">
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>Single Booster Pack</t>
         </is>
@@ -25842,8 +25920,16 @@
         <f>SUM(H304,J304,L304,N304,P304)</f>
         <v/>
       </c>
-      <c r="T304" s="15" t="n"/>
-      <c r="U304" s="15" t="n"/>
+      <c r="T304" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U304" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together - Trainer - Ruffian - Double Silver Star - Ultra Rare</t>
+        </is>
+      </c>
       <c r="V304" s="15" t="n"/>
       <c r="W304" s="15" t="n"/>
       <c r="X304" s="15" t="n"/>
@@ -25889,7 +25975,7 @@
         </is>
       </c>
       <c r="H305" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I305" s="15" t="n"/>
       <c r="J305" s="15" t="n"/>
@@ -25909,8 +25995,16 @@
         <f>SUM(H305,J305,L305,N305,P305)</f>
         <v/>
       </c>
-      <c r="T305" s="15" t="n"/>
-      <c r="U305" s="15" t="n"/>
+      <c r="T305" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U305" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames - Mismagius ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
       <c r="V305" s="15" t="n"/>
       <c r="W305" s="15" t="n"/>
       <c r="X305" s="15" t="n"/>
@@ -25956,7 +26050,7 @@
         </is>
       </c>
       <c r="H306" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I306" s="15" t="n"/>
       <c r="J306" s="15" t="n"/>
@@ -25976,8 +26070,16 @@
         <f>SUM(H306,J306,L306,N306,P306)</f>
         <v/>
       </c>
-      <c r="T306" s="15" t="n"/>
-      <c r="U306" s="15" t="n"/>
+      <c r="T306" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U306" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Judge - Incineroar ex - SR - Super Rare</t>
+        </is>
+      </c>
       <c r="V306" s="15" t="n"/>
       <c r="W306" s="15" t="n"/>
       <c r="X306" s="15" t="n"/>
@@ -26023,7 +26125,7 @@
         </is>
       </c>
       <c r="H307" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I307" s="15" t="n"/>
       <c r="J307" s="15" t="n"/>
@@ -26043,7 +26145,11 @@
         <f>SUM(H307,J307,L307,N307,P307)</f>
         <v/>
       </c>
-      <c r="T307" s="15" t="n"/>
+      <c r="T307" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U307" s="15" t="n"/>
       <c r="V307" s="15" t="n"/>
       <c r="W307" s="15" t="n"/>
@@ -26090,7 +26196,7 @@
         </is>
       </c>
       <c r="H308" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I308" s="15" t="n"/>
       <c r="J308" s="15" t="n"/>
@@ -26110,12 +26216,24 @@
         <f>SUM(H308,J308,L308,N308,P308)</f>
         <v/>
       </c>
-      <c r="T308" s="15" t="n"/>
-      <c r="U308" s="15" t="n"/>
+      <c r="T308" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U308" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames - Mega Lopunny ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
       <c r="V308" s="15" t="n"/>
       <c r="W308" s="15" t="n"/>
       <c r="X308" s="15" t="n"/>
-      <c r="Y308" s="15" t="n"/>
+      <c r="Y308" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="Z308" s="15" t="n"/>
       <c r="AA308" s="15" t="n"/>
       <c r="AB308" s="15" t="n"/>
@@ -26152,7 +26270,9 @@
         <v/>
       </c>
       <c r="G309" s="15" t="n"/>
-      <c r="H309" s="15" t="n"/>
+      <c r="H309" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="I309" s="15" t="n"/>
       <c r="J309" s="15" t="n"/>
       <c r="K309" s="15" t="n"/>
@@ -26162,13 +26282,25 @@
       <c r="O309" s="15" t="n"/>
       <c r="P309" s="15" t="n"/>
       <c r="Q309" s="15" t="n"/>
-      <c r="R309" s="15" t="n"/>
+      <c r="R309" s="15" t="inlineStr">
+        <is>
+          <t>Knock Out Collection</t>
+        </is>
+      </c>
       <c r="S309" s="15">
         <f>SUM(H309,J309,L309,N309,P309)</f>
         <v/>
       </c>
-      <c r="T309" s="15" t="n"/>
-      <c r="U309" s="15" t="n"/>
+      <c r="T309" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U309" s="15" t="inlineStr">
+        <is>
+          <t>Surging Sparks - Feebas - Single Gold Star - Illustration Rare</t>
+        </is>
+      </c>
       <c r="V309" s="15" t="n"/>
       <c r="W309" s="15" t="n"/>
       <c r="X309" s="15" t="n"/>
@@ -26209,7 +26341,9 @@
         <v/>
       </c>
       <c r="G310" s="15" t="n"/>
-      <c r="H310" s="15" t="n"/>
+      <c r="H310" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="I310" s="15" t="n"/>
       <c r="J310" s="15" t="n"/>
       <c r="K310" s="15" t="n"/>
@@ -26219,17 +26353,29 @@
       <c r="O310" s="15" t="n"/>
       <c r="P310" s="15" t="n"/>
       <c r="Q310" s="15" t="n"/>
-      <c r="R310" s="15" t="n"/>
+      <c r="R310" s="15" t="inlineStr">
+        <is>
+          <t>Knock Out Collection</t>
+        </is>
+      </c>
       <c r="S310" s="15">
         <f>SUM(H310,J310,L310,N310,P310)</f>
         <v/>
       </c>
-      <c r="T310" s="15" t="n"/>
+      <c r="T310" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U310" s="15" t="n"/>
       <c r="V310" s="15" t="n"/>
       <c r="W310" s="15" t="n"/>
       <c r="X310" s="15" t="n"/>
-      <c r="Y310" s="15" t="n"/>
+      <c r="Y310" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="Z310" s="15" t="n"/>
       <c r="AA310" s="15" t="n"/>
       <c r="AB310" s="15" t="n"/>
@@ -26271,7 +26417,7 @@
         </is>
       </c>
       <c r="H311" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I311" s="15" t="n"/>
       <c r="J311" s="15" t="n"/>
@@ -26291,8 +26437,16 @@
         <f>SUM(H311,J311,L311,N311,P311)</f>
         <v/>
       </c>
-      <c r="T311" s="15" t="n"/>
-      <c r="U311" s="15" t="n"/>
+      <c r="T311" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U311" s="15" t="inlineStr">
+        <is>
+          <t>Paradox Rift - Tsareena ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
       <c r="V311" s="15" t="n"/>
       <c r="W311" s="15" t="n"/>
       <c r="X311" s="15" t="n"/>
@@ -26333,7 +26487,9 @@
         <v/>
       </c>
       <c r="G312" s="15" t="n"/>
-      <c r="H312" s="15" t="n"/>
+      <c r="H312" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="I312" s="15" t="n"/>
       <c r="J312" s="15" t="n"/>
       <c r="K312" s="15" t="n"/>
@@ -26352,12 +26508,24 @@
         <f>SUM(H312,J312,L312,N312,P312)</f>
         <v/>
       </c>
-      <c r="T312" s="15" t="n"/>
-      <c r="U312" s="15" t="n"/>
+      <c r="T312" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U312" s="15" t="inlineStr">
+        <is>
+          <t>Mega Kangakhan ex - Black Star Promo , Mega Evolution - Spearow - Single Gold Star - Illustration Rare,</t>
+        </is>
+      </c>
       <c r="V312" s="15" t="n"/>
       <c r="W312" s="15" t="n"/>
       <c r="X312" s="15" t="n"/>
-      <c r="Y312" s="15" t="n"/>
+      <c r="Y312" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="Z312" s="15" t="n"/>
       <c r="AA312" s="15" t="n"/>
       <c r="AB312" s="15" t="n"/>
@@ -26450,13 +26618,13 @@
           <t>More than one</t>
         </is>
       </c>
-      <c r="W313" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W313" s="15" t="n"/>
       <c r="X313" s="15" t="n"/>
-      <c r="Y313" s="15" t="n"/>
+      <c r="Y313" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="Z313" s="15" t="n"/>
       <c r="AA313" s="15" t="n"/>
       <c r="AB313" s="15" t="n"/>
@@ -26464,7 +26632,7 @@
       <c r="AD313" s="15" t="n"/>
       <c r="AE313" s="15" t="inlineStr">
         <is>
-          <t>All 18 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 18 packs are on the first set. Move some across the Packs columns if they came from different sets. All 18 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26549,11 +26717,7 @@
           <t>More than one</t>
         </is>
       </c>
-      <c r="W314" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="W314" s="15" t="n"/>
       <c r="X314" s="15" t="n"/>
       <c r="Y314" s="15" t="inlineStr">
         <is>
@@ -26567,7 +26731,7 @@
       <c r="AD314" s="15" t="n"/>
       <c r="AE314" s="15" t="inlineStr">
         <is>
-          <t>All 6 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 6 packs are on the first set. Move some across the Packs columns if they came from different sets. All 6 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26589,10 +26753,10 @@
       <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$B$2:$B$18</formula1>
+      <formula1>=Lists!$B$2:$B$19</formula1>
     </dataValidation>
     <dataValidation sqref="V2:V314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$C$2:$C$10</formula1>
+      <formula1>=Lists!$C$2:$C$13</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
@@ -26617,6 +26781,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -39447,7 +39612,7 @@
       <formula1>=Lists!$A$2:$A$39</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$C$2:$C$10</formula1>
+      <formula1>=Lists!$C$2:$C$13</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -26269,11 +26269,19 @@
         <f>HYPERLINK("https://youtu.be/m9K7hpyjn04","watch")</f>
         <v/>
       </c>
-      <c r="G309" s="15" t="n"/>
+      <c r="G309" s="14" t="inlineStr">
+        <is>
+          <t>Twilight Masquerade</t>
+        </is>
+      </c>
       <c r="H309" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I309" s="15" t="n"/>
+      <c r="I309" s="14" t="inlineStr">
+        <is>
+          <t>Surging Sparks</t>
+        </is>
+      </c>
       <c r="J309" s="15" t="n"/>
       <c r="K309" s="15" t="n"/>
       <c r="L309" s="15" t="n"/>
@@ -26310,7 +26318,11 @@
       <c r="AB309" s="15" t="n"/>
       <c r="AC309" s="15" t="n"/>
       <c r="AD309" s="15" t="n"/>
-      <c r="AE309" s="15" t="n"/>
+      <c r="AE309" s="15" t="inlineStr">
+        <is>
+          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
@@ -26340,11 +26352,19 @@
         <f>HYPERLINK("https://youtu.be/41vJCIdzYkw","watch")</f>
         <v/>
       </c>
-      <c r="G310" s="15" t="n"/>
+      <c r="G310" s="14" t="inlineStr">
+        <is>
+          <t>Twilight Masquerade</t>
+        </is>
+      </c>
       <c r="H310" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I310" s="15" t="n"/>
+      <c r="I310" s="14" t="inlineStr">
+        <is>
+          <t>Surging Sparks</t>
+        </is>
+      </c>
       <c r="J310" s="15" t="n"/>
       <c r="K310" s="15" t="n"/>
       <c r="L310" s="15" t="n"/>
@@ -26381,7 +26401,11 @@
       <c r="AB310" s="15" t="n"/>
       <c r="AC310" s="15" t="n"/>
       <c r="AD310" s="15" t="n"/>
-      <c r="AE310" s="15" t="n"/>
+      <c r="AE310" s="15" t="inlineStr">
+        <is>
+          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
@@ -26486,11 +26510,19 @@
         <f>HYPERLINK("https://youtu.be/l6RPdGNs7uE","watch")</f>
         <v/>
       </c>
-      <c r="G312" s="15" t="n"/>
+      <c r="G312" s="14" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="H312" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I312" s="15" t="n"/>
+      <c r="I312" s="14" t="inlineStr">
+        <is>
+          <t>Destined Rivals</t>
+        </is>
+      </c>
       <c r="J312" s="15" t="n"/>
       <c r="K312" s="15" t="n"/>
       <c r="L312" s="15" t="n"/>
@@ -26531,7 +26563,11 @@
       <c r="AB312" s="15" t="n"/>
       <c r="AC312" s="15" t="n"/>
       <c r="AD312" s="15" t="n"/>
-      <c r="AE312" s="15" t="n"/>
+      <c r="AE312" s="15" t="inlineStr">
+        <is>
+          <t>All 4 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
@@ -26587,11 +26623,7 @@
         </is>
       </c>
       <c r="N313" s="15" t="n"/>
-      <c r="O313" s="14" t="inlineStr">
-        <is>
-          <t>Journey Together</t>
-        </is>
-      </c>
+      <c r="O313" s="15" t="n"/>
       <c r="P313" s="15" t="n"/>
       <c r="Q313" s="15" t="n"/>
       <c r="R313" s="15" t="inlineStr">
@@ -26996,7 +27028,7 @@
         <v>188</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
@@ -27074,7 +27106,7 @@
         <v>244</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
@@ -27100,7 +27132,7 @@
         <v>190</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="15" t="n"/>
       <c r="G11" s="15" t="n"/>
@@ -27152,7 +27184,7 @@
         <v>252</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>
@@ -27230,7 +27262,7 @@
         <v>226</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" s="15" t="n"/>
       <c r="G16" s="15" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -16,7 +16,9 @@
     <sheet name="My Hits" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Shops" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$AE$314</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26768,6 +26770,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AE314"/>
   <dataValidations count="14">
     <dataValidation sqref="G2:G314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$39</formula1>
@@ -27499,7 +27502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27571,82 +27574,115 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Opening type filled in</t>
+          <t>Hit rarity filled in</t>
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!R2:R314)</f>
+        <f>COUNTA('Video Log'!V2:V314)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Marked as a hit</t>
+          <t>Pack count filled in</t>
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!T2:T314,"Yes")</f>
+        <f>COUNTA('Video Log'!H2:H314)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Hit card named</t>
+          <t>Still missing a pack count</t>
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!U2:U314)</f>
+        <f>COUNTA('Video Log'!A2:A314)-COUNTA('Video Log'!H2:H314)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>In Greatest Hits</t>
+          <t>Opening type filled in</t>
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!W2:W314,"Yes")</f>
+        <f>COUNTA('Video Log'!R2:R314)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Given a rank</t>
+          <t>Marked as a hit</t>
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!X2:X314)</f>
+        <f>COUNTIF('Video Log'!T2:T314,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Affiliate links added</t>
+          <t>Hit card named</t>
         </is>
       </c>
       <c r="B13" s="18">
-        <f>COUNTA('Video Log'!Z2:Z314)</f>
+        <f>COUNTA('Video Log'!U2:U314)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>In Greatest Hits</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>COUNTIF('Video Log'!W2:W314,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Given a rank</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>COUNTA('Video Log'!X2:X314)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Affiliate links added</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>COUNTA('Video Log'!Z2:Z314)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>Hidden from the site</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B17" s="18">
         <f>COUNTIF('Video Log'!AD2:AD314,"Yes")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Counts update as you type. Blank cells are skipped by the import, so a half-filled sheet is fine.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -264,15 +264,29 @@
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>The headline card, written however you like.
-If a rip produced SEVERAL cards worth naming, set Hit Rarity to
-"More than one" and list them one per row on the My Hits tab.
-One card per row there means the site can price them and link them.</t>
+        <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
+One line per card, in this shape:
+   Set - Card name - Rarity
+For example:
+   Surging Sparks - Feebas - Illustration Rare
+Several cards from one rip go in the SAME cell, separated by commas,
+and they can be from different sets and different rarities:
+   Journey Together - Noibat - Illustration Rare,
+   Mega Evolution - Marshadow - Illustration Rare
+The site reads the rarity out of these words, so spell the rarity out.
+The star description is welcome and ignored: write it if it helps you.
+Leave it EMPTY when there was no hit. An empty cell means the video
+shows no rarity badge anywhere on the site, which is correct: we only
+claim a pull where you have said what the card was.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>Read the star row at the bottom of the card.
+        <t>OPTIONAL, and it does not drive anything on its own.
+The rarity the site uses is read out of the Hit Card column.
+This column is only kept when a card is named beside it, so filling it
+in on its own does nothing. Use it as a quick label if you like.
+Read the star row at the bottom of the card.
 Mega Hyper Rare: one big yellow star.
 Hyper Rare: three gold stars.
 Special Illustration Rare: two gold stars.
@@ -5447,7 +5461,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -5490,11 +5504,7 @@
         </is>
       </c>
       <c r="U2" s="15" t="n"/>
-      <c r="V2" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V2" s="15" t="n"/>
       <c r="W2" s="15" t="n"/>
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="15" t="n"/>
@@ -5522,7 +5532,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -5589,7 +5599,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
@@ -5632,11 +5642,7 @@
         </is>
       </c>
       <c r="U4" s="15" t="n"/>
-      <c r="V4" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V4" s="15" t="n"/>
       <c r="W4" s="15" t="n"/>
       <c r="X4" s="15" t="n"/>
       <c r="Y4" s="15" t="n"/>
@@ -5774,11 +5780,7 @@
         </is>
       </c>
       <c r="U6" s="15" t="n"/>
-      <c r="V6" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V6" s="15" t="n"/>
       <c r="W6" s="15" t="n"/>
       <c r="X6" s="15" t="n"/>
       <c r="Y6" s="15" t="n"/>
@@ -5983,11 +5985,7 @@
         </is>
       </c>
       <c r="U9" s="15" t="n"/>
-      <c r="V9" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V9" s="15" t="n"/>
       <c r="W9" s="15" t="n"/>
       <c r="X9" s="15" t="n"/>
       <c r="Y9" s="15" t="n"/>
@@ -6058,11 +6056,7 @@
         </is>
       </c>
       <c r="U10" s="15" t="n"/>
-      <c r="V10" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V10" s="15" t="n"/>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="15" t="n"/>
       <c r="Y10" s="15" t="n"/>
@@ -6198,11 +6192,7 @@
         </is>
       </c>
       <c r="U12" s="15" t="n"/>
-      <c r="V12" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V12" s="15" t="n"/>
       <c r="W12" s="15" t="n"/>
       <c r="X12" s="15" t="n"/>
       <c r="Y12" s="15" t="n"/>
@@ -6273,11 +6263,7 @@
         </is>
       </c>
       <c r="U13" s="15" t="n"/>
-      <c r="V13" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V13" s="15" t="n"/>
       <c r="W13" s="15" t="n"/>
       <c r="X13" s="15" t="n"/>
       <c r="Y13" s="15" t="n"/>
@@ -6348,11 +6334,7 @@
         </is>
       </c>
       <c r="U14" s="15" t="n"/>
-      <c r="V14" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V14" s="15" t="n"/>
       <c r="W14" s="15" t="n"/>
       <c r="X14" s="15" t="n"/>
       <c r="Y14" s="15" t="n"/>
@@ -6421,11 +6403,7 @@
         </is>
       </c>
       <c r="U15" s="15" t="n"/>
-      <c r="V15" s="15" t="inlineStr">
-        <is>
-          <t>Double Rare</t>
-        </is>
-      </c>
+      <c r="V15" s="15" t="n"/>
       <c r="W15" s="15" t="n"/>
       <c r="X15" s="15" t="n"/>
       <c r="Y15" s="15" t="n"/>
@@ -6496,11 +6474,7 @@
         </is>
       </c>
       <c r="U16" s="15" t="n"/>
-      <c r="V16" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V16" s="15" t="n"/>
       <c r="W16" s="15" t="n"/>
       <c r="X16" s="15" t="n"/>
       <c r="Y16" s="15" t="n"/>
@@ -6638,11 +6612,7 @@
         </is>
       </c>
       <c r="U18" s="15" t="n"/>
-      <c r="V18" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V18" s="15" t="n"/>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="15" t="n"/>
       <c r="Y18" s="15" t="n"/>
@@ -6711,11 +6681,7 @@
         </is>
       </c>
       <c r="U19" s="15" t="n"/>
-      <c r="V19" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V19" s="15" t="n"/>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="15" t="n"/>
       <c r="Y19" s="15" t="n"/>
@@ -6784,11 +6750,7 @@
         </is>
       </c>
       <c r="U20" s="15" t="n"/>
-      <c r="V20" s="15" t="inlineStr">
-        <is>
-          <t>Double Rare</t>
-        </is>
-      </c>
+      <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
@@ -6924,11 +6886,7 @@
         </is>
       </c>
       <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V22" s="15" t="n"/>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
       <c r="Y22" s="15" t="n"/>
@@ -7066,11 +7024,7 @@
         </is>
       </c>
       <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V24" s="15" t="n"/>
       <c r="W24" s="15" t="n"/>
       <c r="X24" s="15" t="n"/>
       <c r="Y24" s="15" t="n"/>
@@ -7139,11 +7093,7 @@
         </is>
       </c>
       <c r="U25" s="15" t="n"/>
-      <c r="V25" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V25" s="15" t="n"/>
       <c r="W25" s="15" t="n"/>
       <c r="X25" s="15" t="n"/>
       <c r="Y25" s="15" t="n"/>
@@ -7348,11 +7298,7 @@
         </is>
       </c>
       <c r="U28" s="15" t="n"/>
-      <c r="V28" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V28" s="15" t="n"/>
       <c r="W28" s="15" t="n"/>
       <c r="X28" s="15" t="n"/>
       <c r="Y28" s="15" t="n"/>
@@ -7559,11 +7505,7 @@
         </is>
       </c>
       <c r="U31" s="15" t="n"/>
-      <c r="V31" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V31" s="15" t="n"/>
       <c r="W31" s="15" t="n"/>
       <c r="X31" s="15" t="n"/>
       <c r="Y31" s="15" t="n"/>
@@ -7764,11 +7706,7 @@
         </is>
       </c>
       <c r="U34" s="15" t="n"/>
-      <c r="V34" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V34" s="15" t="n"/>
       <c r="W34" s="15" t="n"/>
       <c r="X34" s="15" t="n"/>
       <c r="Y34" s="15" t="n"/>
@@ -7904,11 +7842,7 @@
         </is>
       </c>
       <c r="U36" s="15" t="n"/>
-      <c r="V36" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V36" s="15" t="n"/>
       <c r="W36" s="15" t="n"/>
       <c r="X36" s="15" t="n"/>
       <c r="Y36" s="15" t="n"/>
@@ -7936,7 +7870,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
@@ -7979,11 +7913,7 @@
         </is>
       </c>
       <c r="U37" s="15" t="n"/>
-      <c r="V37" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V37" s="15" t="n"/>
       <c r="W37" s="15" t="n"/>
       <c r="X37" s="15" t="n"/>
       <c r="Y37" s="15" t="n"/>
@@ -8121,11 +8051,7 @@
         </is>
       </c>
       <c r="U39" s="15" t="n"/>
-      <c r="V39" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V39" s="15" t="n"/>
       <c r="W39" s="15" t="n"/>
       <c r="X39" s="15" t="n"/>
       <c r="Y39" s="15" t="n"/>
@@ -8194,11 +8120,7 @@
         </is>
       </c>
       <c r="U40" s="15" t="n"/>
-      <c r="V40" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V40" s="15" t="n"/>
       <c r="W40" s="15" t="n"/>
       <c r="X40" s="15" t="n"/>
       <c r="Y40" s="15" t="n"/>
@@ -8332,11 +8254,7 @@
         </is>
       </c>
       <c r="U42" s="15" t="n"/>
-      <c r="V42" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V42" s="15" t="n"/>
       <c r="W42" s="15" t="n"/>
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="15" t="n"/>
@@ -8535,11 +8453,7 @@
         </is>
       </c>
       <c r="U45" s="15" t="n"/>
-      <c r="V45" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V45" s="15" t="n"/>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="15" t="n"/>
       <c r="Y45" s="15" t="n"/>
@@ -8669,11 +8583,7 @@
         </is>
       </c>
       <c r="U47" s="15" t="n"/>
-      <c r="V47" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V47" s="15" t="n"/>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="15" t="n"/>
       <c r="Y47" s="15" t="n"/>
@@ -8807,11 +8717,7 @@
         </is>
       </c>
       <c r="U49" s="15" t="n"/>
-      <c r="V49" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V49" s="15" t="n"/>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="15" t="n"/>
       <c r="Y49" s="15" t="n"/>
@@ -8947,11 +8853,7 @@
         </is>
       </c>
       <c r="U51" s="15" t="n"/>
-      <c r="V51" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V51" s="15" t="n"/>
       <c r="W51" s="15" t="n"/>
       <c r="X51" s="15" t="n"/>
       <c r="Y51" s="15" t="n"/>
@@ -9087,11 +8989,7 @@
         </is>
       </c>
       <c r="U53" s="15" t="n"/>
-      <c r="V53" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V53" s="15" t="n"/>
       <c r="W53" s="15" t="n"/>
       <c r="X53" s="15" t="n"/>
       <c r="Y53" s="15" t="n"/>
@@ -9554,11 +9452,7 @@
         </is>
       </c>
       <c r="U60" s="15" t="n"/>
-      <c r="V60" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V60" s="15" t="n"/>
       <c r="W60" s="15" t="n"/>
       <c r="X60" s="15" t="n"/>
       <c r="Y60" s="15" t="n"/>
@@ -10807,11 +10701,7 @@
         </is>
       </c>
       <c r="U79" s="15" t="n"/>
-      <c r="V79" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V79" s="15" t="n"/>
       <c r="W79" s="15" t="n"/>
       <c r="X79" s="15" t="n"/>
       <c r="Y79" s="15" t="n"/>
@@ -10876,11 +10766,7 @@
         </is>
       </c>
       <c r="U80" s="15" t="n"/>
-      <c r="V80" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V80" s="15" t="n"/>
       <c r="W80" s="15" t="n"/>
       <c r="X80" s="15" t="n"/>
       <c r="Y80" s="15" t="n"/>
@@ -10949,11 +10835,7 @@
         </is>
       </c>
       <c r="U81" s="15" t="n"/>
-      <c r="V81" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V81" s="15" t="n"/>
       <c r="W81" s="15" t="n"/>
       <c r="X81" s="15" t="n"/>
       <c r="Y81" s="15" t="n"/>
@@ -11018,11 +10900,7 @@
         </is>
       </c>
       <c r="U82" s="15" t="n"/>
-      <c r="V82" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V82" s="15" t="n"/>
       <c r="W82" s="15" t="n"/>
       <c r="X82" s="15" t="n"/>
       <c r="Y82" s="15" t="n"/>
@@ -11221,11 +11099,7 @@
         </is>
       </c>
       <c r="U85" s="15" t="n"/>
-      <c r="V85" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V85" s="15" t="n"/>
       <c r="W85" s="15" t="n"/>
       <c r="X85" s="15" t="n"/>
       <c r="Y85" s="15" t="n"/>
@@ -11294,11 +11168,7 @@
         </is>
       </c>
       <c r="U86" s="15" t="n"/>
-      <c r="V86" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V86" s="15" t="n"/>
       <c r="W86" s="15" t="n"/>
       <c r="X86" s="15" t="n"/>
       <c r="Y86" s="15" t="n"/>
@@ -11363,11 +11233,7 @@
         </is>
       </c>
       <c r="U87" s="15" t="n"/>
-      <c r="V87" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V87" s="15" t="n"/>
       <c r="W87" s="15" t="n"/>
       <c r="X87" s="15" t="n"/>
       <c r="Y87" s="15" t="n"/>
@@ -11436,11 +11302,7 @@
         </is>
       </c>
       <c r="U88" s="15" t="n"/>
-      <c r="V88" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V88" s="15" t="n"/>
       <c r="W88" s="15" t="n"/>
       <c r="X88" s="15" t="n"/>
       <c r="Y88" s="15" t="n"/>
@@ -12163,11 +12025,7 @@
         </is>
       </c>
       <c r="U99" s="15" t="n"/>
-      <c r="V99" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V99" s="15" t="n"/>
       <c r="W99" s="15" t="n"/>
       <c r="X99" s="15" t="n"/>
       <c r="Y99" s="15" t="n"/>
@@ -12307,11 +12165,7 @@
         </is>
       </c>
       <c r="U101" s="15" t="n"/>
-      <c r="V101" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V101" s="15" t="n"/>
       <c r="W101" s="15" t="n"/>
       <c r="X101" s="15" t="n"/>
       <c r="Y101" s="15" t="n"/>
@@ -14565,11 +14419,7 @@
         </is>
       </c>
       <c r="U135" s="15" t="n"/>
-      <c r="V135" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V135" s="15" t="n"/>
       <c r="W135" s="15" t="n"/>
       <c r="X135" s="15" t="n"/>
       <c r="Y135" s="15" t="n"/>
@@ -14707,11 +14557,7 @@
         </is>
       </c>
       <c r="U137" s="15" t="n"/>
-      <c r="V137" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V137" s="15" t="n"/>
       <c r="W137" s="15" t="n"/>
       <c r="X137" s="15" t="n"/>
       <c r="Y137" s="15" t="n"/>
@@ -14782,11 +14628,7 @@
         </is>
       </c>
       <c r="U138" s="15" t="n"/>
-      <c r="V138" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V138" s="15" t="n"/>
       <c r="W138" s="15" t="n"/>
       <c r="X138" s="15" t="n"/>
       <c r="Y138" s="15" t="n"/>
@@ -14857,11 +14699,7 @@
         </is>
       </c>
       <c r="U139" s="15" t="n"/>
-      <c r="V139" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V139" s="15" t="n"/>
       <c r="W139" s="15" t="n"/>
       <c r="X139" s="15" t="n"/>
       <c r="Y139" s="15" t="n"/>
@@ -14932,11 +14770,7 @@
         </is>
       </c>
       <c r="U140" s="15" t="n"/>
-      <c r="V140" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V140" s="15" t="n"/>
       <c r="W140" s="15" t="n"/>
       <c r="X140" s="15" t="n"/>
       <c r="Y140" s="15" t="n"/>
@@ -15141,11 +14975,7 @@
         </is>
       </c>
       <c r="U143" s="15" t="n"/>
-      <c r="V143" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V143" s="15" t="n"/>
       <c r="W143" s="15" t="n"/>
       <c r="X143" s="15" t="n"/>
       <c r="Y143" s="15" t="n"/>
@@ -15618,11 +15448,7 @@
         </is>
       </c>
       <c r="U150" s="15" t="n"/>
-      <c r="V150" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V150" s="15" t="n"/>
       <c r="W150" s="15" t="n"/>
       <c r="X150" s="15" t="n"/>
       <c r="Y150" s="15" t="n"/>
@@ -15827,11 +15653,7 @@
         </is>
       </c>
       <c r="U153" s="15" t="n"/>
-      <c r="V153" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V153" s="15" t="n"/>
       <c r="W153" s="15" t="n"/>
       <c r="X153" s="15" t="n"/>
       <c r="Y153" s="15" t="n"/>
@@ -16036,11 +15858,7 @@
         </is>
       </c>
       <c r="U156" s="15" t="n"/>
-      <c r="V156" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V156" s="15" t="n"/>
       <c r="W156" s="15" t="n"/>
       <c r="X156" s="15" t="n"/>
       <c r="Y156" s="15" t="n"/>
@@ -16111,11 +15929,7 @@
         </is>
       </c>
       <c r="U157" s="15" t="n"/>
-      <c r="V157" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V157" s="15" t="n"/>
       <c r="W157" s="15" t="n"/>
       <c r="X157" s="15" t="n"/>
       <c r="Y157" s="15" t="n"/>
@@ -16320,11 +16134,7 @@
         </is>
       </c>
       <c r="U160" s="15" t="n"/>
-      <c r="V160" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V160" s="15" t="n"/>
       <c r="W160" s="15" t="n"/>
       <c r="X160" s="15" t="n"/>
       <c r="Y160" s="15" t="n"/>
@@ -16529,11 +16339,7 @@
         </is>
       </c>
       <c r="U163" s="15" t="n"/>
-      <c r="V163" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V163" s="15" t="n"/>
       <c r="W163" s="15" t="n"/>
       <c r="X163" s="15" t="n"/>
       <c r="Y163" s="15" t="n"/>
@@ -16738,11 +16544,7 @@
         </is>
       </c>
       <c r="U166" s="15" t="n"/>
-      <c r="V166" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V166" s="15" t="n"/>
       <c r="W166" s="15" t="n"/>
       <c r="X166" s="15" t="n"/>
       <c r="Y166" s="15" t="n"/>
@@ -16947,11 +16749,7 @@
         </is>
       </c>
       <c r="U169" s="15" t="n"/>
-      <c r="V169" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V169" s="15" t="n"/>
       <c r="W169" s="15" t="n"/>
       <c r="X169" s="15" t="n"/>
       <c r="Y169" s="15" t="n"/>
@@ -17223,11 +17021,7 @@
         </is>
       </c>
       <c r="U173" s="15" t="n"/>
-      <c r="V173" s="15" t="inlineStr">
-        <is>
-          <t>Hyper Rare</t>
-        </is>
-      </c>
+      <c r="V173" s="15" t="n"/>
       <c r="W173" s="15" t="n"/>
       <c r="X173" s="15" t="n"/>
       <c r="Y173" s="15" t="n"/>
@@ -17298,11 +17092,7 @@
         </is>
       </c>
       <c r="U174" s="15" t="n"/>
-      <c r="V174" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V174" s="15" t="n"/>
       <c r="W174" s="15" t="n"/>
       <c r="X174" s="15" t="n"/>
       <c r="Y174" s="15" t="n"/>
@@ -18043,11 +17833,7 @@
         </is>
       </c>
       <c r="U185" s="15" t="n"/>
-      <c r="V185" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V185" s="15" t="n"/>
       <c r="W185" s="15" t="n"/>
       <c r="X185" s="15" t="n"/>
       <c r="Y185" s="15" t="n"/>
@@ -18319,11 +18105,7 @@
         </is>
       </c>
       <c r="U189" s="15" t="n"/>
-      <c r="V189" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V189" s="15" t="n"/>
       <c r="W189" s="15" t="n"/>
       <c r="X189" s="15" t="n"/>
       <c r="Y189" s="15" t="n"/>
@@ -18595,11 +18377,7 @@
         </is>
       </c>
       <c r="U193" s="15" t="n"/>
-      <c r="V193" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V193" s="15" t="n"/>
       <c r="W193" s="15" t="n"/>
       <c r="X193" s="15" t="n"/>
       <c r="Y193" s="15" t="n"/>
@@ -18670,11 +18448,7 @@
         </is>
       </c>
       <c r="U194" s="15" t="n"/>
-      <c r="V194" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="V194" s="15" t="n"/>
       <c r="W194" s="15" t="n"/>
       <c r="X194" s="15" t="n"/>
       <c r="Y194" s="15" t="n"/>
@@ -21818,11 +21592,7 @@
         </is>
       </c>
       <c r="U242" s="15" t="n"/>
-      <c r="V242" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V242" s="15" t="n"/>
       <c r="W242" s="15" t="n"/>
       <c r="X242" s="15" t="n"/>
       <c r="Y242" s="15" t="n"/>
@@ -24661,11 +24431,7 @@
         </is>
       </c>
       <c r="U285" s="15" t="n"/>
-      <c r="V285" s="15" t="inlineStr">
-        <is>
-          <t>Charizard</t>
-        </is>
-      </c>
+      <c r="V285" s="15" t="n"/>
       <c r="W285" s="15" t="n"/>
       <c r="X285" s="15" t="n"/>
       <c r="Y285" s="15" t="n"/>
@@ -26322,7 +26088,7 @@
       <c r="AD309" s="15" t="n"/>
       <c r="AE309" s="15" t="inlineStr">
         <is>
-          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets. All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26405,7 +26171,7 @@
       <c r="AD310" s="15" t="n"/>
       <c r="AE310" s="15" t="inlineStr">
         <is>
-          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 2 packs are on the first set. Move some across the Packs columns if they came from different sets. All 2 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26426,7 +26192,7 @@
         </is>
       </c>
       <c r="D311" s="12" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E311" s="11" t="inlineStr">
         <is>
@@ -26567,7 +26333,7 @@
       <c r="AD312" s="15" t="n"/>
       <c r="AE312" s="15" t="inlineStr">
         <is>
-          <t>All 4 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 4 packs are on the first set. Move some across the Packs columns if they came from different sets. All 4 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26666,7 +26432,7 @@
       <c r="AD313" s="15" t="n"/>
       <c r="AE313" s="15" t="inlineStr">
         <is>
-          <t>All 18 packs are on the first set. Move some across the Packs columns if they came from different sets. All 18 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 18 packs are on the first set. Move some across the Packs columns if they came from different sets. All 18 packs are on the first set. Move some across the Packs columns if they came from different sets. All 18 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
@@ -26765,7 +26531,7 @@
       <c r="AD314" s="15" t="n"/>
       <c r="AE314" s="15" t="inlineStr">
         <is>
-          <t>All 6 packs are on the first set. Move some across the Packs columns if they came from different sets. All 6 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+          <t>All 6 packs are on the first set. Move some across the Packs columns if they came from different sets. All 6 packs are on the first set. Move some across the Packs columns if they came from different sets. All 6 packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -272,6 +272,10 @@
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
+FREE TEXT. There is no dropdown on this column and there should not be
+one. If Sheets offers to turn what you have typed into a dropdown, say
+no; if one appears, select the column and use Data, Data validation,
+Remove rule. A dropdown here means retyping a card you already wrote.
 One line per card, in this shape:
    Set - Card name - Rarity
 For example:
@@ -606,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -690,156 +694,167 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Most columns have one. Some are strict and only accept what is listed. Others (Box / Series, Hit Card, PSA 10 Source, shop Area and Good For) offer a list but still accept anything typed, because those lists can never be complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
+          <t>A shortcut, never a gate. Every one accepts anything you type, so a value missing from the list is never a reason you cannot record it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>If the list looks short</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Google Sheets does not keep a dropdown that points at another tab. When you export back to xlsx it rebuilds each one from the values already in that column, so options nobody has used yet disappear. The Lists tab is the real list. Read it there and type the value in; it will be accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Hit Card is free text</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>It has no dropdown here. If Sheets offers to make one out of what you have typed, decline it. If one appears anyway, select the column and use Data then Data validation then Remove rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>THE TABS</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Video Log</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Every video. Sets, opening type, the hit, the Hall of Fame, and per-video copy for the site.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Set Notes</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>The two facts the card database does not carry: whether a set is still in print, and what a pack costs. Set guides omit both until filled in.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Chase Cards</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Every chase card on the site. PSA 10 prices live ONLY here: nothing can fetch a graded price, so this tab is the only route onto the site. Most Wanted marks a card for the hunt page and the home page band.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Shops</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Local card shops for /shops.html.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Live counts of how much is filled in.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Shops</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Local card shops for /shops.html.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Live counts of how much is filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Lists</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>The source of every dropdown. Add a row here to add an option.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>HOW TO IMPORT</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Google Sheets exports the ACTIVE tab only, so open the tab you want first, then File &gt; Download &gt; Comma-separated values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Video Log</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>node scripts/import-sheet.mjs &lt;csv&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Chase Cards</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>node scripts/import-cards.mjs &lt;csv&gt;</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Video Log</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>node scripts/import-sheet.mjs &lt;csv&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Chase Cards</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>node scripts/import-cards.mjs &lt;csv&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Shops</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>node scripts/import-cards.mjs &lt;csv&gt;</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Either importer works out which tab it is from the header row, so the filename does not matter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>The one that matters most</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Set. 61 videos have no set tag. A video with no set cannot be filtered and cannot reach the Hall of Fame. Eight of those are graded hits locked out of the home page right now.</t>
         </is>
       </c>
     </row>
@@ -847,12 +862,12 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Packs from several sets</t>
+          <t>The one that matters most</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A tin with two packs, or a box with ten packs from four sets, belongs to every set it contains. Put the set the video is really about in Set and the rest in Set 2 to Set 5. Next to each one, put how many packs of THAT set were in the opening. Packs Opened adds them up for you, so a UPC reads 18 packs AND tells us six were Journey Together. That is what makes a per-set pack count possible.</t>
+          <t>Set. 61 videos have no set tag. A video with no set cannot be filtered and cannot reach the Hall of Fame. Eight of those are graded hits locked out of the home page right now.</t>
         </is>
       </c>
     </row>
@@ -860,12 +875,12 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Greatest Hits</t>
+          <t>Packs from several sets</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Mark Yes on the RIPS you want in the gold section at the top of the home page. Rank orders them, 1 first. Leave Rank blank and the site orders by rarity then views. These are videos.</t>
+          <t>A tin with two packs, or a box with ten packs from four sets, belongs to every set it contains. Put the set the video is really about in Set and the rest in Set 2 to Set 5. Next to each one, put how many packs of THAT set were in the opening. Packs Opened adds them up for you, so a UPC reads 18 packs AND tells us six were Journey Together. That is what makes a per-set pack count possible.</t>
         </is>
       </c>
     </row>
@@ -873,12 +888,12 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Card Hall of Fame</t>
+          <t>Greatest Hits</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>On the Chase Cards tab. Mark Yes on the CARDS you have actually pulled. They get their own page, ranked by value, with the card image, the set, the raw near mint price and the PSA 10 price. These are cards, not videos, which is the whole difference between the two.</t>
+          <t>Mark Yes on the RIPS you want in the gold section at the top of the home page. Rank orders them, 1 first. Leave Rank blank and the site orders by rarity then views. These are videos.</t>
         </is>
       </c>
     </row>
@@ -886,23 +901,36 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PSA 10 prices</t>
+          <t>Card Hall of Fame</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Put in a number you have actually seen, set PSA 10 Checked to the date you checked it (2026-08-11 format), and name the source. A graded price with no date is not a fact about anything, and a blank shows nothing rather than a guess.</t>
+          <t>On the Chase Cards tab. Mark Yes on the CARDS you have actually pulled. They get their own page, ranked by value, with the card image, the set, the raw near mint price and the PSA 10 price. These are cards, not videos, which is the whole difference between the two.</t>
         </is>
       </c>
     </row>
     <row r="34"/>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>PSA 10 prices</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Put in a number you have actually seen, set PSA 10 Checked to the date you checked it (2026-08-11 format), and name the source. A graded price with no date is not a fact about anything, and a blank shows nothing rather than a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Careful</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Rebuilding this file overwrites it. Import your latest export FIRST, then rebuild. Anything already imported is carried back in; anything not is lost.</t>
         </is>
@@ -25334,8 +25362,16 @@
         <f>SUM(H297,J297,L297,N297,P297)</f>
         <v/>
       </c>
-      <c r="T297" s="15" t="n"/>
-      <c r="U297" s="15" t="n"/>
+      <c r="T297" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U297" s="15" t="inlineStr">
+        <is>
+          <t>Ascended Heroes - Stunfisk ex - Double Silver Star - Ultra Rare</t>
+        </is>
+      </c>
       <c r="V297" s="15" t="n"/>
       <c r="W297" s="15" t="n"/>
       <c r="X297" s="15" t="n"/>
@@ -25377,7 +25413,7 @@
       </c>
       <c r="G298" s="15" t="n"/>
       <c r="H298" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I298" s="15" t="n"/>
       <c r="J298" s="15" t="n"/>
@@ -25397,7 +25433,11 @@
         <f>SUM(H298,J298,L298,N298,P298)</f>
         <v/>
       </c>
-      <c r="T298" s="15" t="n"/>
+      <c r="T298" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U298" s="15" t="n"/>
       <c r="V298" s="15" t="n"/>
       <c r="W298" s="15" t="n"/>
@@ -25464,7 +25504,11 @@
         <f>SUM(H299,J299,L299,N299,P299)</f>
         <v/>
       </c>
-      <c r="T299" s="15" t="n"/>
+      <c r="T299" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U299" s="15" t="n"/>
       <c r="V299" s="15" t="n"/>
       <c r="W299" s="15" t="n"/>
@@ -25531,7 +25575,11 @@
         <f>SUM(H300,J300,L300,N300,P300)</f>
         <v/>
       </c>
-      <c r="T300" s="15" t="n"/>
+      <c r="T300" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U300" s="15" t="n"/>
       <c r="V300" s="15" t="n"/>
       <c r="W300" s="15" t="n"/>
@@ -25598,7 +25646,11 @@
         <f>SUM(H301,J301,L301,N301,P301)</f>
         <v/>
       </c>
-      <c r="T301" s="15" t="n"/>
+      <c r="T301" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="U301" s="15" t="n"/>
       <c r="V301" s="15" t="n"/>
       <c r="W301" s="15" t="n"/>
@@ -25665,8 +25717,16 @@
         <f>SUM(H302,J302,L302,N302,P302)</f>
         <v/>
       </c>
-      <c r="T302" s="15" t="n"/>
-      <c r="U302" s="15" t="n"/>
+      <c r="T302" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U302" s="15" t="inlineStr">
+        <is>
+          <t>Journey Together - Volcanion ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
       <c r="V302" s="15" t="n"/>
       <c r="W302" s="15" t="n"/>
       <c r="X302" s="15" t="n"/>
@@ -25712,7 +25772,7 @@
         </is>
       </c>
       <c r="H303" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I303" s="14" t="inlineStr">
         <is>
@@ -25736,8 +25796,16 @@
         <f>SUM(H303,J303,L303,N303,P303)</f>
         <v/>
       </c>
-      <c r="T303" s="15" t="n"/>
-      <c r="U303" s="15" t="n"/>
+      <c r="T303" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U303" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames - Rotom ex - Double Black Star- Double Rare</t>
+        </is>
+      </c>
       <c r="V303" s="15" t="n"/>
       <c r="W303" s="15" t="n"/>
       <c r="X303" s="15" t="n"/>
@@ -26657,43 +26725,43 @@
   </sheetData>
   <autoFilter ref="A1:AE314"/>
   <dataValidations count="14">
-    <dataValidation sqref="G2:G314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$44</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$44</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$44</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$44</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$44</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$19</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$C$2:$C$13</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AC314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AD2:AD314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$E$2:$E$7</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X314" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="X2:X314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$K$2:$K$21</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -27503,7 +27571,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -36446,10 +36514,10 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -41479,7 +41547,7 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="F2:F40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -17,6 +17,17 @@
     <sheet name="Shops" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="gr_list_A">Lists!$A$2:$A$44</definedName>
+    <definedName name="gr_list_B">Lists!$B$2:$B$19</definedName>
+    <definedName name="gr_list_C">Lists!$C$2:$C$13</definedName>
+    <definedName name="gr_list_D">Lists!$D$2:$D$3</definedName>
+    <definedName name="gr_list_E">Lists!$E$2:$E$7</definedName>
+    <definedName name="gr_list_F">Lists!$F$2:$F$31</definedName>
+    <definedName name="gr_list_G">Lists!$G$2:$G$501</definedName>
+    <definedName name="gr_list_H">Lists!$H$2:$H$8</definedName>
+    <definedName name="gr_list_I">Lists!$I$2:$I$12</definedName>
+    <definedName name="gr_list_J">Lists!$J$2:$J$11</definedName>
+    <definedName name="gr_list_K">Lists!$K$2:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$AE$314</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26726,46 +26737,46 @@
   <autoFilter ref="A1:AE314"/>
   <dataValidations count="14">
     <dataValidation sqref="G2:G314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$B$2:$B$19</formula1>
+      <formula1>gr_list_B</formula1>
     </dataValidation>
     <dataValidation sqref="V2:V314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$C$2:$C$13</formula1>
+      <formula1>gr_list_C</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="AD2:AD314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$E$2:$E$7</formula1>
+      <formula1>gr_list_E</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$K$2:$K$21</formula1>
+      <formula1>gr_list_K</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q314" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$F$2:$F$31</formula1>
+      <formula1>gr_list_F</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27572,7 +27583,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36515,13 +36526,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="J2:J225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$H$2:$H$8</formula1>
+      <formula1>gr_list_H</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41284,13 +41295,13 @@
       <formula1>='Video Log'!$A$2:$A$314</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$44</formula1>
+      <formula1>gr_list_A</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$C$2:$C$13</formula1>
+      <formula1>gr_list_C</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41548,13 +41559,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="F2:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+      <formula1>gr_list_D</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$I$2:$I$12</formula1>
+      <formula1>gr_list_I</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$J$2:$J$11</formula1>
+      <formula1>gr_list_J</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6690,8 +6690,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n">
-        <v>9</v>
+      <c r="H2" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="inlineStr">
@@ -6775,7 +6775,9 @@
         </is>
       </c>
       <c r="K3" s="15" t="n"/>
-      <c r="L3" s="15" t="n"/>
+      <c r="L3" s="14" t="n">
+        <v>13</v>
+      </c>
       <c r="M3" s="15">
         <f>SUM(H3,R3,T3,V3,X3)</f>
         <v/>
@@ -6834,8 +6836,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n">
-        <v>9</v>
+      <c r="H4" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="inlineStr">
@@ -6844,7 +6846,9 @@
         </is>
       </c>
       <c r="K4" s="15" t="n"/>
-      <c r="L4" s="15" t="n"/>
+      <c r="L4" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M4" s="15">
         <f>SUM(H4,R4,T4,V4,X4)</f>
         <v/>
@@ -6913,7 +6917,9 @@
         </is>
       </c>
       <c r="K5" s="15" t="n"/>
-      <c r="L5" s="15" t="n"/>
+      <c r="L5" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M5" s="15">
         <f>SUM(H5,R5,T5,V5,X5)</f>
         <v/>
@@ -6976,8 +6982,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n">
-        <v>9</v>
+      <c r="H6" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="inlineStr">
@@ -6986,7 +6992,9 @@
         </is>
       </c>
       <c r="K6" s="15" t="n"/>
-      <c r="L6" s="15" t="n"/>
+      <c r="L6" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M6" s="15">
         <f>SUM(H6,R6,T6,V6,X6)</f>
         <v/>
@@ -7055,7 +7063,9 @@
         </is>
       </c>
       <c r="K7" s="15" t="n"/>
-      <c r="L7" s="15" t="n"/>
+      <c r="L7" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="M7" s="15">
         <f>SUM(H7,R7,T7,V7,X7)</f>
         <v/>
@@ -7118,8 +7128,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n">
-        <v>9</v>
+      <c r="H8" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="inlineStr">
@@ -7128,7 +7138,9 @@
         </is>
       </c>
       <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
+      <c r="L8" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M8" s="15">
         <f>SUM(H8,R8,T8,V8,X8)</f>
         <v/>
@@ -7197,7 +7209,9 @@
         </is>
       </c>
       <c r="K9" s="15" t="n"/>
-      <c r="L9" s="15" t="n"/>
+      <c r="L9" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M9" s="15">
         <f>SUM(H9,R9,T9,V9,X9)</f>
         <v/>
@@ -7260,8 +7274,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n">
-        <v>9</v>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="inlineStr">
@@ -7269,8 +7283,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K10" s="15" t="n"/>
-      <c r="L10" s="15" t="n"/>
+      <c r="K10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M10" s="15">
         <f>SUM(H10,R10,T10,V10,X10)</f>
         <v/>
@@ -7329,8 +7347,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H11" s="15" t="n">
-        <v>9</v>
+      <c r="H11" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="inlineStr">
@@ -7339,7 +7357,9 @@
         </is>
       </c>
       <c r="K11" s="15" t="n"/>
-      <c r="L11" s="15" t="n"/>
+      <c r="L11" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M11" s="15">
         <f>SUM(H11,R11,T11,V11,X11)</f>
         <v/>
@@ -7398,8 +7418,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
-        <v>6</v>
+      <c r="H12" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="inlineStr">
@@ -7408,7 +7428,9 @@
         </is>
       </c>
       <c r="K12" s="15" t="n"/>
-      <c r="L12" s="15" t="n"/>
+      <c r="L12" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M12" s="15">
         <f>SUM(H12,R12,T12,V12,X12)</f>
         <v/>
@@ -7481,7 +7503,9 @@
         </is>
       </c>
       <c r="K13" s="15" t="n"/>
-      <c r="L13" s="15" t="n"/>
+      <c r="L13" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M13" s="15">
         <f>SUM(H13,R13,T13,V13,X13)</f>
         <v/>
@@ -7552,7 +7576,9 @@
         </is>
       </c>
       <c r="K14" s="15" t="n"/>
-      <c r="L14" s="15" t="n"/>
+      <c r="L14" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M14" s="15">
         <f>SUM(H14,R14,T14,V14,X14)</f>
         <v/>
@@ -7611,8 +7637,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
-        <v>9</v>
+      <c r="H15" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="15" t="inlineStr">
@@ -7621,7 +7647,9 @@
         </is>
       </c>
       <c r="K15" s="15" t="n"/>
-      <c r="L15" s="15" t="n"/>
+      <c r="L15" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M15" s="15">
         <f>SUM(H15,R15,T15,V15,X15)</f>
         <v/>
@@ -7684,8 +7712,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
-        <v>6</v>
+      <c r="H16" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="15" t="inlineStr">
@@ -7694,7 +7722,9 @@
         </is>
       </c>
       <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
+      <c r="L16" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M16" s="15">
         <f>SUM(H16,R16,T16,V16,X16)</f>
         <v/>
@@ -7767,7 +7797,9 @@
         </is>
       </c>
       <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
+      <c r="L17" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M17" s="15">
         <f>SUM(H17,R17,T17,V17,X17)</f>
         <v/>
@@ -7838,7 +7870,9 @@
         </is>
       </c>
       <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
+      <c r="L18" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M18" s="15">
         <f>SUM(H18,R18,T18,V18,X18)</f>
         <v/>
@@ -7901,8 +7935,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>9</v>
+      <c r="H19" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I19" s="15" t="n"/>
       <c r="J19" s="15" t="inlineStr">
@@ -7911,7 +7945,9 @@
         </is>
       </c>
       <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
+      <c r="L19" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M19" s="15">
         <f>SUM(H19,R19,T19,V19,X19)</f>
         <v/>
@@ -7974,8 +8010,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
-        <v>6</v>
+      <c r="H20" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="inlineStr">
@@ -7984,7 +8020,9 @@
         </is>
       </c>
       <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
+      <c r="L20" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M20" s="15">
         <f>SUM(H20,R20,T20,V20,X20)</f>
         <v/>
@@ -8053,7 +8091,9 @@
         </is>
       </c>
       <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
+      <c r="L21" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M21" s="15">
         <f>SUM(H21,R21,T21,V21,X21)</f>
         <v/>
@@ -8195,7 +8235,9 @@
         </is>
       </c>
       <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
+      <c r="L23" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M23" s="15">
         <f>SUM(H23,R23,T23,V23,X23)</f>
         <v/>
@@ -8325,8 +8367,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
-        <v>6</v>
+      <c r="H25" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="15" t="n"/>
       <c r="J25" s="15" t="inlineStr">
@@ -8335,7 +8377,9 @@
         </is>
       </c>
       <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="n"/>
+      <c r="L25" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M25" s="15">
         <f>SUM(H25,R25,T25,V25,X25)</f>
         <v/>
@@ -8398,8 +8442,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n">
-        <v>9</v>
+      <c r="H26" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I26" s="15" t="n"/>
       <c r="J26" s="15" t="inlineStr">
@@ -8408,7 +8452,9 @@
         </is>
       </c>
       <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
+      <c r="L26" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M26" s="15">
         <f>SUM(H26,R26,T26,V26,X26)</f>
         <v/>
@@ -8477,7 +8523,9 @@
         </is>
       </c>
       <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
+      <c r="L27" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M27" s="15">
         <f>SUM(H27,R27,T27,V27,X27)</f>
         <v/>
@@ -8548,7 +8596,9 @@
         </is>
       </c>
       <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
+      <c r="L28" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M28" s="15">
         <f>SUM(H28,R28,T28,V28,X28)</f>
         <v/>
@@ -8690,7 +8740,9 @@
         </is>
       </c>
       <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
+      <c r="L30" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M30" s="15">
         <f>SUM(H30,R30,T30,V30,X30)</f>
         <v/>
@@ -8749,8 +8801,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
-        <v>9</v>
+      <c r="H31" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I31" s="15" t="n"/>
       <c r="J31" s="15" t="inlineStr">
@@ -8759,7 +8811,9 @@
         </is>
       </c>
       <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="n"/>
+      <c r="L31" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M31" s="15">
         <f>SUM(H31,R31,T31,V31,X31)</f>
         <v/>
@@ -8822,8 +8876,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
-        <v>9</v>
+      <c r="H32" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I32" s="15" t="n"/>
       <c r="J32" s="15" t="inlineStr">
@@ -8832,7 +8886,9 @@
         </is>
       </c>
       <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
+      <c r="L32" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M32" s="15">
         <f>SUM(H32,R32,T32,V32,X32)</f>
         <v/>
@@ -8968,7 +9024,9 @@
         </is>
       </c>
       <c r="K34" s="15" t="n"/>
-      <c r="L34" s="15" t="n"/>
+      <c r="L34" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M34" s="15">
         <f>SUM(H34,R34,T34,V34,X34)</f>
         <v/>
@@ -9110,7 +9168,9 @@
         </is>
       </c>
       <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
+      <c r="L36" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M36" s="15">
         <f>SUM(H36,R36,T36,V36,X36)</f>
         <v/>
@@ -9169,8 +9229,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
-        <v>9</v>
+      <c r="H37" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I37" s="15" t="n"/>
       <c r="J37" s="15" t="inlineStr">
@@ -9179,7 +9239,9 @@
         </is>
       </c>
       <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
+      <c r="L37" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M37" s="15">
         <f>SUM(H37,R37,T37,V37,X37)</f>
         <v/>
@@ -9318,8 +9380,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
+      <c r="K39" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M39" s="15">
         <f>SUM(H39,R39,T39,V39,X39)</f>
         <v/>
@@ -9463,7 +9529,9 @@
         </is>
       </c>
       <c r="K41" s="15" t="n"/>
-      <c r="L41" s="15" t="n"/>
+      <c r="L41" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M41" s="15">
         <f>SUM(H41,R41,T41,V41,X41)</f>
         <v/>
@@ -9534,7 +9602,9 @@
         </is>
       </c>
       <c r="K42" s="15" t="n"/>
-      <c r="L42" s="15" t="n"/>
+      <c r="L42" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M42" s="15">
         <f>SUM(H42,R42,T42,V42,X42)</f>
         <v/>
@@ -9605,7 +9675,9 @@
         </is>
       </c>
       <c r="K43" s="15" t="n"/>
-      <c r="L43" s="15" t="n"/>
+      <c r="L43" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M43" s="15">
         <f>SUM(H43,R43,T43,V43,X43)</f>
         <v/>
@@ -9675,8 +9747,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K44" s="15" t="n"/>
-      <c r="L44" s="15" t="n"/>
+      <c r="K44" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M44" s="15">
         <f>SUM(H44,R44,T44,V44,X44)</f>
         <v/>
@@ -9743,7 +9819,9 @@
         </is>
       </c>
       <c r="K45" s="15" t="n"/>
-      <c r="L45" s="15" t="n"/>
+      <c r="L45" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M45" s="15">
         <f>SUM(H45,R45,T45,V45,X45)</f>
         <v/>
@@ -9880,8 +9958,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K47" s="15" t="n"/>
-      <c r="L47" s="15" t="n"/>
+      <c r="K47" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M47" s="15">
         <f>SUM(H47,R47,T47,V47,X47)</f>
         <v/>
@@ -9948,7 +10030,9 @@
         </is>
       </c>
       <c r="K48" s="15" t="n"/>
-      <c r="L48" s="15" t="n"/>
+      <c r="L48" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M48" s="15">
         <f>SUM(H48,R48,T48,V48,X48)</f>
         <v/>
@@ -10018,8 +10102,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K49" s="15" t="n"/>
-      <c r="L49" s="15" t="n"/>
+      <c r="K49" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M49" s="15">
         <f>SUM(H49,R49,T49,V49,X49)</f>
         <v/>
@@ -10081,8 +10169,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K50" s="15" t="n"/>
-      <c r="L50" s="15" t="n"/>
+      <c r="K50" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M50" s="15">
         <f>SUM(H50,R50,T50,V50,X50)</f>
         <v/>
@@ -10148,7 +10240,9 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K51" s="15" t="n"/>
+      <c r="K51" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15">
         <f>SUM(H51,R51,T51,V51,X51)</f>
@@ -10215,8 +10309,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K52" s="15" t="n"/>
-      <c r="L52" s="15" t="n"/>
+      <c r="K52" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L52" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M52" s="15">
         <f>SUM(H52,R52,T52,V52,X52)</f>
         <v/>
@@ -10291,7 +10389,9 @@
         </is>
       </c>
       <c r="K53" s="15" t="n"/>
-      <c r="L53" s="15" t="n"/>
+      <c r="L53" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M53" s="15">
         <f>SUM(H53,R53,T53,V53,X53)</f>
         <v/>
@@ -10350,8 +10450,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
-        <v>9</v>
+      <c r="H54" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I54" s="15" t="n"/>
       <c r="J54" s="15" t="inlineStr">
@@ -10360,7 +10460,9 @@
         </is>
       </c>
       <c r="K54" s="15" t="n"/>
-      <c r="L54" s="15" t="n"/>
+      <c r="L54" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M54" s="15">
         <f>SUM(H54,R54,T54,V54,X54)</f>
         <v/>
@@ -10423,8 +10525,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H55" s="15" t="n">
-        <v>9</v>
+      <c r="H55" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I55" s="15" t="n"/>
       <c r="J55" s="15" t="inlineStr">
@@ -10432,8 +10534,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K55" s="15" t="n"/>
-      <c r="L55" s="15" t="n"/>
+      <c r="K55" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M55" s="15">
         <f>SUM(H55,R55,T55,V55,X55)</f>
         <v/>
@@ -10499,8 +10605,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K56" s="15" t="n"/>
-      <c r="L56" s="15" t="n"/>
+      <c r="K56" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M56" s="15">
         <f>SUM(H56,R56,T56,V56,X56)</f>
         <v/>
@@ -10563,8 +10673,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H57" s="15" t="n">
-        <v>9</v>
+      <c r="H57" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I57" s="15" t="n"/>
       <c r="J57" s="15" t="inlineStr">
@@ -10573,7 +10683,9 @@
         </is>
       </c>
       <c r="K57" s="15" t="n"/>
-      <c r="L57" s="15" t="n"/>
+      <c r="L57" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M57" s="15">
         <f>SUM(H57,R57,T57,V57,X57)</f>
         <v/>
@@ -10640,7 +10752,9 @@
         </is>
       </c>
       <c r="K58" s="15" t="n"/>
-      <c r="L58" s="15" t="n"/>
+      <c r="L58" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M58" s="15">
         <f>SUM(H58,R58,T58,V58,X58)</f>
         <v/>
@@ -10699,8 +10813,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H59" s="15" t="n">
-        <v>9</v>
+      <c r="H59" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I59" s="15" t="n"/>
       <c r="J59" s="15" t="inlineStr">
@@ -10708,8 +10822,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K59" s="15" t="n"/>
-      <c r="L59" s="15" t="n"/>
+      <c r="K59" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M59" s="15">
         <f>SUM(H59,R59,T59,V59,X59)</f>
         <v/>
@@ -10771,8 +10889,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K60" s="15" t="n"/>
-      <c r="L60" s="15" t="n"/>
+      <c r="K60" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M60" s="15">
         <f>SUM(H60,R60,T60,V60,X60)</f>
         <v/>
@@ -10831,8 +10953,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H61" s="15" t="n">
-        <v>9</v>
+      <c r="H61" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I61" s="15" t="n"/>
       <c r="J61" s="15" t="inlineStr">
@@ -10840,8 +10962,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K61" s="15" t="n"/>
-      <c r="L61" s="15" t="n"/>
+      <c r="K61" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M61" s="15">
         <f>SUM(H61,R61,T61,V61,X61)</f>
         <v/>
@@ -10907,8 +11033,12 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K62" s="15" t="n"/>
-      <c r="L62" s="15" t="n"/>
+      <c r="K62" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M62" s="15">
         <f>SUM(H62,R62,T62,V62,X62)</f>
         <v/>
@@ -10967,8 +11097,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H63" s="15" t="n">
-        <v>9</v>
+      <c r="H63" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I63" s="15" t="n"/>
       <c r="J63" s="15" t="inlineStr">
@@ -10976,8 +11106,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K63" s="15" t="n"/>
-      <c r="L63" s="15" t="n"/>
+      <c r="K63" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M63" s="15">
         <f>SUM(H63,R63,T63,V63,X63)</f>
         <v/>
@@ -11048,7 +11182,9 @@
         </is>
       </c>
       <c r="K64" s="15" t="n"/>
-      <c r="L64" s="15" t="n"/>
+      <c r="L64" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M64" s="15">
         <f>SUM(H64,R64,T64,V64,X64)</f>
         <v/>
@@ -11110,7 +11246,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K65" s="15" t="n"/>
+      <c r="K65" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="L65" s="15" t="n"/>
       <c r="M65" s="15">
         <f>SUM(H65,R65,T65,V65,X65)</f>
@@ -11304,8 +11442,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H68" s="15" t="n">
-        <v>9</v>
+      <c r="H68" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I68" s="15" t="n"/>
       <c r="J68" s="15" t="inlineStr">
@@ -11313,8 +11451,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K68" s="15" t="n"/>
-      <c r="L68" s="15" t="n"/>
+      <c r="K68" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M68" s="15">
         <f>SUM(H68,R68,T68,V68,X68)</f>
         <v/>
@@ -11373,8 +11515,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H69" s="15" t="n">
-        <v>9</v>
+      <c r="H69" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I69" s="15" t="n"/>
       <c r="J69" s="15" t="inlineStr">
@@ -11383,7 +11525,9 @@
         </is>
       </c>
       <c r="K69" s="15" t="n"/>
-      <c r="L69" s="15" t="n"/>
+      <c r="L69" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M69" s="15">
         <f>SUM(H69,R69,T69,V69,X69)</f>
         <v/>
@@ -11445,7 +11589,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K70" s="15" t="n"/>
+      <c r="K70" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="L70" s="15" t="n"/>
       <c r="M70" s="15">
         <f>SUM(H70,R70,T70,V70,X70)</f>
@@ -11505,8 +11651,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n">
-        <v>9</v>
+      <c r="H71" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I71" s="15" t="n"/>
       <c r="J71" s="15" t="inlineStr">
@@ -11514,8 +11660,12 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K71" s="15" t="n"/>
-      <c r="L71" s="15" t="n"/>
+      <c r="K71" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M71" s="15">
         <f>SUM(H71,R71,T71,V71,X71)</f>
         <v/>
@@ -11584,7 +11734,9 @@
         </is>
       </c>
       <c r="K72" s="15" t="n"/>
-      <c r="L72" s="15" t="n"/>
+      <c r="L72" s="14" t="n">
+        <v>11</v>
+      </c>
       <c r="M72" s="15">
         <f>SUM(H72,R72,T72,V72,X72)</f>
         <v/>
@@ -11653,7 +11805,9 @@
         </is>
       </c>
       <c r="K73" s="15" t="n"/>
-      <c r="L73" s="15" t="n"/>
+      <c r="L73" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="M73" s="15">
         <f>SUM(H73,R73,T73,V73,X73)</f>
         <v/>
@@ -11722,7 +11876,9 @@
         </is>
       </c>
       <c r="K74" s="15" t="n"/>
-      <c r="L74" s="15" t="n"/>
+      <c r="L74" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="M74" s="15">
         <f>SUM(H74,R74,T74,V74,X74)</f>
         <v/>
@@ -11791,7 +11947,9 @@
         </is>
       </c>
       <c r="K75" s="15" t="n"/>
-      <c r="L75" s="15" t="n"/>
+      <c r="L75" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M75" s="15">
         <f>SUM(H75,R75,T75,V75,X75)</f>
         <v/>
@@ -11860,7 +12018,9 @@
         </is>
       </c>
       <c r="K76" s="15" t="n"/>
-      <c r="L76" s="15" t="n"/>
+      <c r="L76" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M76" s="15">
         <f>SUM(H76,R76,T76,V76,X76)</f>
         <v/>
@@ -11929,7 +12089,9 @@
         </is>
       </c>
       <c r="K77" s="15" t="n"/>
-      <c r="L77" s="15" t="n"/>
+      <c r="L77" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M77" s="15">
         <f>SUM(H77,R77,T77,V77,X77)</f>
         <v/>
@@ -11998,7 +12160,9 @@
         </is>
       </c>
       <c r="K78" s="15" t="n"/>
-      <c r="L78" s="15" t="n"/>
+      <c r="L78" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M78" s="15">
         <f>SUM(H78,R78,T78,V78,X78)</f>
         <v/>
@@ -12067,7 +12231,9 @@
         </is>
       </c>
       <c r="K79" s="15" t="n"/>
-      <c r="L79" s="15" t="n"/>
+      <c r="L79" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M79" s="15">
         <f>SUM(H79,R79,T79,V79,X79)</f>
         <v/>
@@ -12136,7 +12302,9 @@
         </is>
       </c>
       <c r="K80" s="15" t="n"/>
-      <c r="L80" s="15" t="n"/>
+      <c r="L80" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M80" s="15">
         <f>SUM(H80,R80,T80,V80,X80)</f>
         <v/>
@@ -12343,7 +12511,9 @@
         </is>
       </c>
       <c r="K83" s="15" t="n"/>
-      <c r="L83" s="15" t="n"/>
+      <c r="L83" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M83" s="15">
         <f>SUM(H83,R83,T83,V83,X83)</f>
         <v/>
@@ -12485,7 +12655,9 @@
         </is>
       </c>
       <c r="K85" s="15" t="n"/>
-      <c r="L85" s="15" t="n"/>
+      <c r="L85" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M85" s="15">
         <f>SUM(H85,R85,T85,V85,X85)</f>
         <v/>
@@ -12548,8 +12720,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H86" s="15" t="n">
-        <v>9</v>
+      <c r="H86" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I86" s="15" t="n"/>
       <c r="J86" s="15" t="inlineStr">
@@ -12558,7 +12730,9 @@
         </is>
       </c>
       <c r="K86" s="15" t="n"/>
-      <c r="L86" s="15" t="n"/>
+      <c r="L86" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M86" s="15">
         <f>SUM(H86,R86,T86,V86,X86)</f>
         <v/>
@@ -12617,8 +12791,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H87" s="15" t="n">
-        <v>9</v>
+      <c r="H87" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I87" s="15" t="n"/>
       <c r="J87" s="15" t="inlineStr">
@@ -12627,7 +12801,9 @@
         </is>
       </c>
       <c r="K87" s="15" t="n"/>
-      <c r="L87" s="15" t="n"/>
+      <c r="L87" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M87" s="15">
         <f>SUM(H87,R87,T87,V87,X87)</f>
         <v/>
@@ -12694,7 +12870,9 @@
         </is>
       </c>
       <c r="K88" s="15" t="n"/>
-      <c r="L88" s="15" t="n"/>
+      <c r="L88" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M88" s="15">
         <f>SUM(H88,R88,T88,V88,X88)</f>
         <v/>
@@ -12765,7 +12943,9 @@
         </is>
       </c>
       <c r="K89" s="15" t="n"/>
-      <c r="L89" s="15" t="n"/>
+      <c r="L89" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M89" s="15">
         <f>SUM(H89,R89,T89,V89,X89)</f>
         <v/>
@@ -12836,7 +13016,9 @@
         </is>
       </c>
       <c r="K90" s="15" t="n"/>
-      <c r="L90" s="15" t="n"/>
+      <c r="L90" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M90" s="15">
         <f>SUM(H90,R90,T90,V90,X90)</f>
         <v/>
@@ -12907,7 +13089,9 @@
         </is>
       </c>
       <c r="K91" s="15" t="n"/>
-      <c r="L91" s="15" t="n"/>
+      <c r="L91" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M91" s="15">
         <f>SUM(H91,R91,T91,V91,X91)</f>
         <v/>
@@ -12970,8 +13154,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H92" s="15" t="n">
-        <v>9</v>
+      <c r="H92" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I92" s="15" t="n"/>
       <c r="J92" s="15" t="inlineStr">
@@ -12980,7 +13164,9 @@
         </is>
       </c>
       <c r="K92" s="15" t="n"/>
-      <c r="L92" s="15" t="n"/>
+      <c r="L92" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M92" s="15">
         <f>SUM(H92,R92,T92,V92,X92)</f>
         <v/>
@@ -13106,8 +13292,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H94" s="15" t="n">
-        <v>9</v>
+      <c r="H94" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I94" s="15" t="n"/>
       <c r="J94" s="15" t="inlineStr">
@@ -13116,7 +13302,9 @@
         </is>
       </c>
       <c r="K94" s="15" t="n"/>
-      <c r="L94" s="15" t="n"/>
+      <c r="L94" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M94" s="15">
         <f>SUM(H94,R94,T94,V94,X94)</f>
         <v/>
@@ -13183,7 +13371,9 @@
         </is>
       </c>
       <c r="K95" s="15" t="n"/>
-      <c r="L95" s="15" t="n"/>
+      <c r="L95" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M95" s="15">
         <f>SUM(H95,R95,T95,V95,X95)</f>
         <v/>
@@ -13242,8 +13432,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H96" s="15" t="n">
-        <v>9</v>
+      <c r="H96" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I96" s="15" t="n"/>
       <c r="J96" s="15" t="inlineStr">
@@ -13252,7 +13442,9 @@
         </is>
       </c>
       <c r="K96" s="15" t="n"/>
-      <c r="L96" s="15" t="n"/>
+      <c r="L96" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M96" s="15">
         <f>SUM(H96,R96,T96,V96,X96)</f>
         <v/>
@@ -13319,7 +13511,9 @@
         </is>
       </c>
       <c r="K97" s="15" t="n"/>
-      <c r="L97" s="15" t="n"/>
+      <c r="L97" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M97" s="15">
         <f>SUM(H97,R97,T97,V97,X97)</f>
         <v/>
@@ -13378,8 +13572,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H98" s="15" t="n">
-        <v>9</v>
+      <c r="H98" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I98" s="15" t="n"/>
       <c r="J98" s="15" t="inlineStr">
@@ -13388,7 +13582,9 @@
         </is>
       </c>
       <c r="K98" s="15" t="n"/>
-      <c r="L98" s="15" t="n"/>
+      <c r="L98" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M98" s="15">
         <f>SUM(H98,R98,T98,V98,X98)</f>
         <v/>
@@ -13455,7 +13651,9 @@
         </is>
       </c>
       <c r="K99" s="15" t="n"/>
-      <c r="L99" s="15" t="n"/>
+      <c r="L99" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M99" s="15">
         <f>SUM(H99,R99,T99,V99,X99)</f>
         <v/>
@@ -13514,8 +13712,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H100" s="15" t="n">
-        <v>9</v>
+      <c r="H100" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I100" s="15" t="n"/>
       <c r="J100" s="15" t="inlineStr">
@@ -13524,7 +13722,9 @@
         </is>
       </c>
       <c r="K100" s="15" t="n"/>
-      <c r="L100" s="15" t="n"/>
+      <c r="L100" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M100" s="15">
         <f>SUM(H100,R100,T100,V100,X100)</f>
         <v/>
@@ -13583,8 +13783,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H101" s="15" t="n">
-        <v>9</v>
+      <c r="H101" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I101" s="15" t="n"/>
       <c r="J101" s="15" t="inlineStr">
@@ -13593,7 +13793,9 @@
         </is>
       </c>
       <c r="K101" s="15" t="n"/>
-      <c r="L101" s="15" t="n"/>
+      <c r="L101" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M101" s="15">
         <f>SUM(H101,R101,T101,V101,X101)</f>
         <v/>
@@ -13733,7 +13935,9 @@
         </is>
       </c>
       <c r="K103" s="15" t="n"/>
-      <c r="L103" s="15" t="n"/>
+      <c r="L103" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M103" s="15">
         <f>SUM(H103,R103,T103,V103,X103)</f>
         <v/>
@@ -13800,7 +14004,9 @@
         </is>
       </c>
       <c r="K104" s="15" t="n"/>
-      <c r="L104" s="15" t="n"/>
+      <c r="L104" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M104" s="15">
         <f>SUM(H104,R104,T104,V104,X104)</f>
         <v/>
@@ -13876,7 +14082,9 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K105" s="15" t="n"/>
+      <c r="K105" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L105" s="15" t="n"/>
       <c r="M105" s="15">
         <f>SUM(H105,R105,T105,V105,X105)</f>
@@ -13944,7 +14152,9 @@
         </is>
       </c>
       <c r="K106" s="15" t="n"/>
-      <c r="L106" s="15" t="n"/>
+      <c r="L106" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M106" s="15">
         <f>SUM(H106,R106,T106,V106,X106)</f>
         <v/>
@@ -14011,7 +14221,9 @@
         </is>
       </c>
       <c r="K107" s="15" t="n"/>
-      <c r="L107" s="15" t="n"/>
+      <c r="L107" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M107" s="15">
         <f>SUM(H107,R107,T107,V107,X107)</f>
         <v/>
@@ -14080,7 +14292,9 @@
         </is>
       </c>
       <c r="K108" s="15" t="n"/>
-      <c r="L108" s="15" t="n"/>
+      <c r="L108" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M108" s="15">
         <f>SUM(H108,R108,T108,V108,X108)</f>
         <v/>
@@ -14149,7 +14363,9 @@
         </is>
       </c>
       <c r="K109" s="15" t="n"/>
-      <c r="L109" s="15" t="n"/>
+      <c r="L109" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M109" s="15">
         <f>SUM(H109,R109,T109,V109,X109)</f>
         <v/>
@@ -14208,8 +14424,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H110" s="15" t="n">
-        <v>6</v>
+      <c r="H110" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I110" s="15" t="n"/>
       <c r="J110" s="15" t="inlineStr">
@@ -14217,8 +14433,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K110" s="15" t="n"/>
-      <c r="L110" s="15" t="n"/>
+      <c r="K110" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M110" s="15">
         <f>SUM(H110,R110,T110,V110,X110)</f>
         <v/>
@@ -14277,8 +14497,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H111" s="15" t="n">
-        <v>6</v>
+      <c r="H111" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I111" s="15" t="n"/>
       <c r="J111" s="15" t="inlineStr">
@@ -14286,8 +14506,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K111" s="15" t="n"/>
-      <c r="L111" s="15" t="n"/>
+      <c r="K111" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M111" s="15">
         <f>SUM(H111,R111,T111,V111,X111)</f>
         <v/>
@@ -14350,7 +14574,9 @@
         </is>
       </c>
       <c r="K112" s="15" t="n"/>
-      <c r="L112" s="15" t="n"/>
+      <c r="L112" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M112" s="15">
         <f>SUM(H112,R112,T112,V112,X112)</f>
         <v/>
@@ -14413,7 +14639,9 @@
         </is>
       </c>
       <c r="K113" s="15" t="n"/>
-      <c r="L113" s="15" t="n"/>
+      <c r="L113" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M113" s="15">
         <f>SUM(H113,R113,T113,V113,X113)</f>
         <v/>
@@ -14482,7 +14710,9 @@
         </is>
       </c>
       <c r="K114" s="15" t="n"/>
-      <c r="L114" s="15" t="n"/>
+      <c r="L114" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M114" s="15">
         <f>SUM(H114,R114,T114,V114,X114)</f>
         <v/>
@@ -14551,7 +14781,9 @@
         </is>
       </c>
       <c r="K115" s="15" t="n"/>
-      <c r="L115" s="15" t="n"/>
+      <c r="L115" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M115" s="15">
         <f>SUM(H115,R115,T115,V115,X115)</f>
         <v/>
@@ -14610,8 +14842,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H116" s="15" t="n">
-        <v>6</v>
+      <c r="H116" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I116" s="15" t="n"/>
       <c r="J116" s="15" t="inlineStr">
@@ -14619,8 +14851,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K116" s="15" t="n"/>
-      <c r="L116" s="15" t="n"/>
+      <c r="K116" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M116" s="15">
         <f>SUM(H116,R116,T116,V116,X116)</f>
         <v/>
@@ -14679,8 +14915,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H117" s="15" t="n">
-        <v>6</v>
+      <c r="H117" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I117" s="15" t="n"/>
       <c r="J117" s="15" t="inlineStr">
@@ -14688,8 +14924,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K117" s="15" t="n"/>
-      <c r="L117" s="15" t="n"/>
+      <c r="K117" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L117" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M117" s="15">
         <f>SUM(H117,R117,T117,V117,X117)</f>
         <v/>
@@ -14752,7 +14992,9 @@
         </is>
       </c>
       <c r="K118" s="15" t="n"/>
-      <c r="L118" s="15" t="n"/>
+      <c r="L118" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M118" s="15">
         <f>SUM(H118,R118,T118,V118,X118)</f>
         <v/>
@@ -14811,8 +15053,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H119" s="15" t="n">
-        <v>6</v>
+      <c r="H119" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I119" s="15" t="n"/>
       <c r="J119" s="15" t="inlineStr">
@@ -14820,8 +15062,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K119" s="15" t="n"/>
-      <c r="L119" s="15" t="n"/>
+      <c r="K119" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M119" s="15">
         <f>SUM(H119,R119,T119,V119,X119)</f>
         <v/>
@@ -14884,7 +15130,9 @@
         </is>
       </c>
       <c r="K120" s="15" t="n"/>
-      <c r="L120" s="15" t="n"/>
+      <c r="L120" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M120" s="15">
         <f>SUM(H120,R120,T120,V120,X120)</f>
         <v/>
@@ -14943,8 +15191,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H121" s="15" t="n">
-        <v>6</v>
+      <c r="H121" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I121" s="15" t="n"/>
       <c r="J121" s="15" t="inlineStr">
@@ -14952,8 +15200,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K121" s="15" t="n"/>
-      <c r="L121" s="15" t="n"/>
+      <c r="K121" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L121" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M121" s="15">
         <f>SUM(H121,R121,T121,V121,X121)</f>
         <v/>
@@ -15021,7 +15273,9 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K122" s="15" t="n"/>
+      <c r="K122" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L122" s="15" t="n"/>
       <c r="M122" s="15">
         <f>SUM(H122,R122,T122,V122,X122)</f>
@@ -15150,8 +15404,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H124" s="15" t="n">
-        <v>6</v>
+      <c r="H124" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I124" s="15" t="n"/>
       <c r="J124" s="15" t="inlineStr">
@@ -15159,8 +15413,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K124" s="15" t="n"/>
-      <c r="L124" s="15" t="n"/>
+      <c r="K124" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M124" s="15">
         <f>SUM(H124,R124,T124,V124,X124)</f>
         <v/>
@@ -15228,7 +15486,9 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K125" s="15" t="n"/>
+      <c r="K125" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L125" s="15" t="n"/>
       <c r="M125" s="15">
         <f>SUM(H125,R125,T125,V125,X125)</f>
@@ -15288,8 +15548,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H126" s="15" t="n">
-        <v>6</v>
+      <c r="H126" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I126" s="15" t="n"/>
       <c r="J126" s="15" t="inlineStr">
@@ -15298,7 +15558,9 @@
         </is>
       </c>
       <c r="K126" s="15" t="n"/>
-      <c r="L126" s="15" t="n"/>
+      <c r="L126" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M126" s="15">
         <f>SUM(H126,R126,T126,V126,X126)</f>
         <v/>
@@ -15357,8 +15619,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H127" s="15" t="n">
-        <v>6</v>
+      <c r="H127" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I127" s="15" t="n"/>
       <c r="J127" s="15" t="inlineStr">
@@ -15367,7 +15629,9 @@
         </is>
       </c>
       <c r="K127" s="15" t="n"/>
-      <c r="L127" s="15" t="n"/>
+      <c r="L127" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M127" s="15">
         <f>SUM(H127,R127,T127,V127,X127)</f>
         <v/>
@@ -15426,8 +15690,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H128" s="15" t="n">
-        <v>6</v>
+      <c r="H128" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I128" s="15" t="n"/>
       <c r="J128" s="15" t="inlineStr">
@@ -15435,8 +15699,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K128" s="15" t="n"/>
-      <c r="L128" s="15" t="n"/>
+      <c r="K128" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M128" s="15">
         <f>SUM(H128,R128,T128,V128,X128)</f>
         <v/>
@@ -15495,8 +15763,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H129" s="15" t="n">
-        <v>6</v>
+      <c r="H129" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I129" s="15" t="n"/>
       <c r="J129" s="15" t="inlineStr">
@@ -15504,8 +15772,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K129" s="15" t="n"/>
-      <c r="L129" s="15" t="n"/>
+      <c r="K129" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M129" s="15">
         <f>SUM(H129,R129,T129,V129,X129)</f>
         <v/>
@@ -15564,8 +15836,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H130" s="15" t="n">
-        <v>6</v>
+      <c r="H130" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I130" s="15" t="n"/>
       <c r="J130" s="15" t="inlineStr">
@@ -15573,8 +15845,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K130" s="15" t="n"/>
-      <c r="L130" s="15" t="n"/>
+      <c r="K130" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L130" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M130" s="15">
         <f>SUM(H130,R130,T130,V130,X130)</f>
         <v/>
@@ -15633,8 +15909,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H131" s="15" t="n">
-        <v>6</v>
+      <c r="H131" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I131" s="15" t="n"/>
       <c r="J131" s="15" t="inlineStr">
@@ -15642,8 +15918,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K131" s="15" t="n"/>
-      <c r="L131" s="15" t="n"/>
+      <c r="K131" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L131" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M131" s="15">
         <f>SUM(H131,R131,T131,V131,X131)</f>
         <v/>
@@ -15702,8 +15982,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H132" s="15" t="n">
-        <v>6</v>
+      <c r="H132" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I132" s="15" t="n"/>
       <c r="J132" s="15" t="inlineStr">
@@ -15712,7 +15992,9 @@
         </is>
       </c>
       <c r="K132" s="15" t="n"/>
-      <c r="L132" s="15" t="n"/>
+      <c r="L132" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M132" s="15">
         <f>SUM(H132,R132,T132,V132,X132)</f>
         <v/>
@@ -15771,8 +16053,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H133" s="15" t="n">
-        <v>6</v>
+      <c r="H133" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I133" s="15" t="n"/>
       <c r="J133" s="15" t="inlineStr">
@@ -15780,8 +16062,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K133" s="15" t="n"/>
-      <c r="L133" s="15" t="n"/>
+      <c r="K133" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M133" s="15">
         <f>SUM(H133,R133,T133,V133,X133)</f>
         <v/>
@@ -15840,8 +16126,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H134" s="15" t="n">
-        <v>6</v>
+      <c r="H134" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I134" s="15" t="n"/>
       <c r="J134" s="15" t="inlineStr">
@@ -15850,7 +16136,9 @@
         </is>
       </c>
       <c r="K134" s="15" t="n"/>
-      <c r="L134" s="15" t="n"/>
+      <c r="L134" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M134" s="15">
         <f>SUM(H134,R134,T134,V134,X134)</f>
         <v/>
@@ -15909,8 +16197,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H135" s="15" t="n">
-        <v>6</v>
+      <c r="H135" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I135" s="15" t="n"/>
       <c r="J135" s="15" t="inlineStr">
@@ -15919,7 +16207,9 @@
         </is>
       </c>
       <c r="K135" s="15" t="n"/>
-      <c r="L135" s="15" t="n"/>
+      <c r="L135" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M135" s="15">
         <f>SUM(H135,R135,T135,V135,X135)</f>
         <v/>
@@ -15978,8 +16268,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H136" s="15" t="n">
-        <v>6</v>
+      <c r="H136" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I136" s="15" t="n"/>
       <c r="J136" s="15" t="inlineStr">
@@ -15987,8 +16277,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K136" s="15" t="n"/>
-      <c r="L136" s="15" t="n"/>
+      <c r="K136" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M136" s="15">
         <f>SUM(H136,R136,T136,V136,X136)</f>
         <v/>
@@ -16047,8 +16341,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H137" s="15" t="n">
-        <v>6</v>
+      <c r="H137" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I137" s="15" t="n"/>
       <c r="J137" s="15" t="inlineStr">
@@ -16056,8 +16350,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K137" s="15" t="n"/>
-      <c r="L137" s="15" t="n"/>
+      <c r="K137" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L137" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M137" s="15">
         <f>SUM(H137,R137,T137,V137,X137)</f>
         <v/>
@@ -16189,8 +16487,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H139" s="15" t="n">
-        <v>6</v>
+      <c r="H139" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I139" s="15" t="n"/>
       <c r="J139" s="15" t="inlineStr">
@@ -16198,8 +16496,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K139" s="15" t="n"/>
-      <c r="L139" s="15" t="n"/>
+      <c r="K139" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L139" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M139" s="15">
         <f>SUM(H139,R139,T139,V139,X139)</f>
         <v/>
@@ -16258,8 +16560,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H140" s="15" t="n">
-        <v>9</v>
+      <c r="H140" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I140" s="15" t="n"/>
       <c r="J140" s="15" t="inlineStr">
@@ -16268,7 +16570,9 @@
         </is>
       </c>
       <c r="K140" s="15" t="n"/>
-      <c r="L140" s="15" t="n"/>
+      <c r="L140" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M140" s="15">
         <f>SUM(H140,R140,T140,V140,X140)</f>
         <v/>
@@ -16341,7 +16645,9 @@
         </is>
       </c>
       <c r="K141" s="15" t="n"/>
-      <c r="L141" s="15" t="n"/>
+      <c r="L141" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="M141" s="15">
         <f>SUM(H141,R141,T141,V141,X141)</f>
         <v/>
@@ -16404,8 +16710,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H142" s="15" t="n">
-        <v>9</v>
+      <c r="H142" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I142" s="15" t="n"/>
       <c r="J142" s="15" t="inlineStr">
@@ -16414,7 +16720,9 @@
         </is>
       </c>
       <c r="K142" s="15" t="n"/>
-      <c r="L142" s="15" t="n"/>
+      <c r="L142" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M142" s="15">
         <f>SUM(H142,R142,T142,V142,X142)</f>
         <v/>
@@ -16477,8 +16785,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H143" s="15" t="n">
-        <v>9</v>
+      <c r="H143" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I143" s="15" t="n"/>
       <c r="J143" s="15" t="inlineStr">
@@ -16487,7 +16795,9 @@
         </is>
       </c>
       <c r="K143" s="15" t="n"/>
-      <c r="L143" s="15" t="n"/>
+      <c r="L143" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M143" s="15">
         <f>SUM(H143,R143,T143,V143,X143)</f>
         <v/>
@@ -16628,7 +16938,9 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K145" s="15" t="n"/>
+      <c r="K145" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L145" s="15" t="n"/>
       <c r="M145" s="15">
         <f>SUM(H145,R145,T145,V145,X145)</f>
@@ -16698,7 +17010,9 @@
         </is>
       </c>
       <c r="K146" s="15" t="n"/>
-      <c r="L146" s="15" t="n"/>
+      <c r="L146" s="14" t="n">
+        <v>11</v>
+      </c>
       <c r="M146" s="15">
         <f>SUM(H146,R146,T146,V146,X146)</f>
         <v/>
@@ -16771,7 +17085,9 @@
         </is>
       </c>
       <c r="K147" s="15" t="n"/>
-      <c r="L147" s="15" t="n"/>
+      <c r="L147" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M147" s="15">
         <f>SUM(H147,R147,T147,V147,X147)</f>
         <v/>
@@ -16840,7 +17156,9 @@
         </is>
       </c>
       <c r="K148" s="15" t="n"/>
-      <c r="L148" s="15" t="n"/>
+      <c r="L148" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M148" s="15">
         <f>SUM(H148,R148,T148,V148,X148)</f>
         <v/>
@@ -16909,7 +17227,9 @@
         </is>
       </c>
       <c r="K149" s="15" t="n"/>
-      <c r="L149" s="15" t="n"/>
+      <c r="L149" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M149" s="15">
         <f>SUM(H149,R149,T149,V149,X149)</f>
         <v/>
@@ -16978,7 +17298,9 @@
         </is>
       </c>
       <c r="K150" s="15" t="n"/>
-      <c r="L150" s="15" t="n"/>
+      <c r="L150" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M150" s="15">
         <f>SUM(H150,R150,T150,V150,X150)</f>
         <v/>
@@ -17047,7 +17369,9 @@
         </is>
       </c>
       <c r="K151" s="15" t="n"/>
-      <c r="L151" s="15" t="n"/>
+      <c r="L151" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M151" s="15">
         <f>SUM(H151,R151,T151,V151,X151)</f>
         <v/>
@@ -17116,7 +17440,9 @@
         </is>
       </c>
       <c r="K152" s="15" t="n"/>
-      <c r="L152" s="15" t="n"/>
+      <c r="L152" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M152" s="15">
         <f>SUM(H152,R152,T152,V152,X152)</f>
         <v/>
@@ -17175,8 +17501,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H153" s="15" t="n">
-        <v>9</v>
+      <c r="H153" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I153" s="15" t="n"/>
       <c r="J153" s="15" t="inlineStr">
@@ -17185,7 +17511,9 @@
         </is>
       </c>
       <c r="K153" s="15" t="n"/>
-      <c r="L153" s="15" t="n"/>
+      <c r="L153" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M153" s="15">
         <f>SUM(H153,R153,T153,V153,X153)</f>
         <v/>
@@ -17248,8 +17576,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H154" s="15" t="n">
-        <v>9</v>
+      <c r="H154" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I154" s="15" t="n"/>
       <c r="J154" s="15" t="inlineStr">
@@ -17258,7 +17586,9 @@
         </is>
       </c>
       <c r="K154" s="15" t="n"/>
-      <c r="L154" s="15" t="n"/>
+      <c r="L154" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M154" s="15">
         <f>SUM(H154,R154,T154,V154,X154)</f>
         <v/>
@@ -17317,8 +17647,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H155" s="15" t="n">
-        <v>6</v>
+      <c r="H155" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I155" s="15" t="n"/>
       <c r="J155" s="15" t="inlineStr">
@@ -17326,8 +17656,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K155" s="15" t="n"/>
-      <c r="L155" s="15" t="n"/>
+      <c r="K155" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M155" s="15">
         <f>SUM(H155,R155,T155,V155,X155)</f>
         <v/>
@@ -17396,7 +17730,9 @@
         </is>
       </c>
       <c r="K156" s="15" t="n"/>
-      <c r="L156" s="15" t="n"/>
+      <c r="L156" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="M156" s="15">
         <f>SUM(H156,R156,T156,V156,X156)</f>
         <v/>
@@ -17528,8 +17864,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H158" s="15" t="n">
-        <v>9</v>
+      <c r="H158" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I158" s="15" t="n"/>
       <c r="J158" s="15" t="inlineStr">
@@ -17538,7 +17874,9 @@
         </is>
       </c>
       <c r="K158" s="15" t="n"/>
-      <c r="L158" s="15" t="n"/>
+      <c r="L158" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M158" s="15">
         <f>SUM(H158,R158,T158,V158,X158)</f>
         <v/>
@@ -17607,7 +17945,9 @@
         </is>
       </c>
       <c r="K159" s="15" t="n"/>
-      <c r="L159" s="15" t="n"/>
+      <c r="L159" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M159" s="15">
         <f>SUM(H159,R159,T159,V159,X159)</f>
         <v/>
@@ -17670,8 +18010,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H160" s="15" t="n">
-        <v>9</v>
+      <c r="H160" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I160" s="15" t="n"/>
       <c r="J160" s="15" t="inlineStr">
@@ -17680,7 +18020,9 @@
         </is>
       </c>
       <c r="K160" s="15" t="n"/>
-      <c r="L160" s="15" t="n"/>
+      <c r="L160" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M160" s="15">
         <f>SUM(H160,R160,T160,V160,X160)</f>
         <v/>
@@ -17743,8 +18085,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H161" s="15" t="n">
-        <v>9</v>
+      <c r="H161" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I161" s="15" t="n"/>
       <c r="J161" s="15" t="inlineStr">
@@ -17753,7 +18095,9 @@
         </is>
       </c>
       <c r="K161" s="15" t="n"/>
-      <c r="L161" s="15" t="n"/>
+      <c r="L161" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M161" s="15">
         <f>SUM(H161,R161,T161,V161,X161)</f>
         <v/>
@@ -17812,8 +18156,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H162" s="15" t="n">
-        <v>6</v>
+      <c r="H162" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I162" s="15" t="n"/>
       <c r="J162" s="15" t="inlineStr">
@@ -17821,8 +18165,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K162" s="15" t="n"/>
-      <c r="L162" s="15" t="n"/>
+      <c r="K162" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L162" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M162" s="15">
         <f>SUM(H162,R162,T162,V162,X162)</f>
         <v/>
@@ -17881,8 +18229,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H163" s="15" t="n">
-        <v>9</v>
+      <c r="H163" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I163" s="15" t="n"/>
       <c r="J163" s="15" t="inlineStr">
@@ -17891,7 +18239,9 @@
         </is>
       </c>
       <c r="K163" s="15" t="n"/>
-      <c r="L163" s="15" t="n"/>
+      <c r="L163" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M163" s="15">
         <f>SUM(H163,R163,T163,V163,X163)</f>
         <v/>
@@ -18102,7 +18452,9 @@
         </is>
       </c>
       <c r="K166" s="15" t="n"/>
-      <c r="L166" s="15" t="n"/>
+      <c r="L166" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M166" s="15">
         <f>SUM(H166,R166,T166,V166,X166)</f>
         <v/>
@@ -18165,8 +18517,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H167" s="15" t="n">
-        <v>9</v>
+      <c r="H167" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I167" s="15" t="n"/>
       <c r="J167" s="15" t="inlineStr">
@@ -18175,7 +18527,9 @@
         </is>
       </c>
       <c r="K167" s="15" t="n"/>
-      <c r="L167" s="15" t="n"/>
+      <c r="L167" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M167" s="15">
         <f>SUM(H167,R167,T167,V167,X167)</f>
         <v/>
@@ -18234,8 +18588,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H168" s="15" t="n">
-        <v>6</v>
+      <c r="H168" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I168" s="15" t="n"/>
       <c r="J168" s="15" t="inlineStr">
@@ -18243,8 +18597,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K168" s="15" t="n"/>
-      <c r="L168" s="15" t="n"/>
+      <c r="K168" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L168" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M168" s="15">
         <f>SUM(H168,R168,T168,V168,X168)</f>
         <v/>
@@ -18303,8 +18661,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H169" s="15" t="n">
-        <v>9</v>
+      <c r="H169" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I169" s="15" t="n"/>
       <c r="J169" s="15" t="inlineStr">
@@ -18313,7 +18671,9 @@
         </is>
       </c>
       <c r="K169" s="15" t="n"/>
-      <c r="L169" s="15" t="n"/>
+      <c r="L169" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M169" s="15">
         <f>SUM(H169,R169,T169,V169,X169)</f>
         <v/>
@@ -18445,8 +18805,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H171" s="15" t="n">
-        <v>6</v>
+      <c r="H171" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I171" s="15" t="n"/>
       <c r="J171" s="15" t="inlineStr">
@@ -18455,7 +18815,9 @@
         </is>
       </c>
       <c r="K171" s="15" t="n"/>
-      <c r="L171" s="15" t="n"/>
+      <c r="L171" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M171" s="15">
         <f>SUM(H171,R171,T171,V171,X171)</f>
         <v/>
@@ -18524,7 +18886,9 @@
         </is>
       </c>
       <c r="K172" s="15" t="n"/>
-      <c r="L172" s="15" t="n"/>
+      <c r="L172" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M172" s="15">
         <f>SUM(H172,R172,T172,V172,X172)</f>
         <v/>
@@ -18587,8 +18951,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H173" s="15" t="n">
-        <v>9</v>
+      <c r="H173" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I173" s="15" t="n"/>
       <c r="J173" s="15" t="inlineStr">
@@ -18597,7 +18961,9 @@
         </is>
       </c>
       <c r="K173" s="15" t="n"/>
-      <c r="L173" s="15" t="n"/>
+      <c r="L173" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M173" s="15">
         <f>SUM(H173,R173,T173,V173,X173)</f>
         <v/>
@@ -18725,8 +19091,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H175" s="15" t="n">
-        <v>6</v>
+      <c r="H175" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I175" s="15" t="n"/>
       <c r="J175" s="15" t="inlineStr">
@@ -18734,8 +19100,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K175" s="15" t="n"/>
-      <c r="L175" s="15" t="n"/>
+      <c r="K175" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M175" s="15">
         <f>SUM(H175,R175,T175,V175,X175)</f>
         <v/>
@@ -18804,7 +19174,9 @@
         </is>
       </c>
       <c r="K176" s="15" t="n"/>
-      <c r="L176" s="15" t="n"/>
+      <c r="L176" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M176" s="15">
         <f>SUM(H176,R176,T176,V176,X176)</f>
         <v/>
@@ -18867,8 +19239,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H177" s="15" t="n">
-        <v>9</v>
+      <c r="H177" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I177" s="15" t="n"/>
       <c r="J177" s="15" t="inlineStr">
@@ -18877,7 +19249,9 @@
         </is>
       </c>
       <c r="K177" s="15" t="n"/>
-      <c r="L177" s="15" t="n"/>
+      <c r="L177" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M177" s="15">
         <f>SUM(H177,R177,T177,V177,X177)</f>
         <v/>
@@ -18940,8 +19314,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H178" s="15" t="n">
-        <v>6</v>
+      <c r="H178" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I178" s="15" t="n"/>
       <c r="J178" s="15" t="inlineStr">
@@ -18950,7 +19324,9 @@
         </is>
       </c>
       <c r="K178" s="15" t="n"/>
-      <c r="L178" s="15" t="n"/>
+      <c r="L178" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M178" s="15">
         <f>SUM(H178,R178,T178,V178,X178)</f>
         <v/>
@@ -19009,8 +19385,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H179" s="15" t="n">
-        <v>9</v>
+      <c r="H179" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I179" s="15" t="n"/>
       <c r="J179" s="15" t="inlineStr">
@@ -19019,7 +19395,9 @@
         </is>
       </c>
       <c r="K179" s="15" t="n"/>
-      <c r="L179" s="15" t="n"/>
+      <c r="L179" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M179" s="15">
         <f>SUM(H179,R179,T179,V179,X179)</f>
         <v/>
@@ -19078,8 +19456,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H180" s="15" t="n">
-        <v>6</v>
+      <c r="H180" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I180" s="15" t="n"/>
       <c r="J180" s="15" t="inlineStr">
@@ -19087,8 +19465,12 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K180" s="15" t="n"/>
-      <c r="L180" s="15" t="n"/>
+      <c r="K180" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L180" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M180" s="15">
         <f>SUM(H180,R180,T180,V180,X180)</f>
         <v/>
@@ -19157,7 +19539,9 @@
         </is>
       </c>
       <c r="K181" s="15" t="n"/>
-      <c r="L181" s="15" t="n"/>
+      <c r="L181" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M181" s="15">
         <f>SUM(H181,R181,T181,V181,X181)</f>
         <v/>
@@ -19226,7 +19610,9 @@
         </is>
       </c>
       <c r="K182" s="15" t="n"/>
-      <c r="L182" s="15" t="n"/>
+      <c r="L182" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M182" s="15">
         <f>SUM(H182,R182,T182,V182,X182)</f>
         <v/>
@@ -19295,7 +19681,9 @@
         </is>
       </c>
       <c r="K183" s="15" t="n"/>
-      <c r="L183" s="15" t="n"/>
+      <c r="L183" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M183" s="15">
         <f>SUM(H183,R183,T183,V183,X183)</f>
         <v/>
@@ -19354,8 +19742,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H184" s="15" t="n">
-        <v>6</v>
+      <c r="H184" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I184" s="15" t="n"/>
       <c r="J184" s="15" t="inlineStr">
@@ -19364,7 +19752,9 @@
         </is>
       </c>
       <c r="K184" s="15" t="n"/>
-      <c r="L184" s="15" t="n"/>
+      <c r="L184" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M184" s="15">
         <f>SUM(H184,R184,T184,V184,X184)</f>
         <v/>
@@ -19433,7 +19823,9 @@
         </is>
       </c>
       <c r="K185" s="15" t="n"/>
-      <c r="L185" s="15" t="n"/>
+      <c r="L185" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M185" s="15">
         <f>SUM(H185,R185,T185,V185,X185)</f>
         <v/>
@@ -19492,8 +19884,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H186" s="15" t="n">
-        <v>9</v>
+      <c r="H186" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I186" s="15" t="n"/>
       <c r="J186" s="15" t="inlineStr">
@@ -19502,7 +19894,9 @@
         </is>
       </c>
       <c r="K186" s="15" t="n"/>
-      <c r="L186" s="15" t="n"/>
+      <c r="L186" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M186" s="15">
         <f>SUM(H186,R186,T186,V186,X186)</f>
         <v/>
@@ -19561,8 +19955,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H187" s="15" t="n">
-        <v>6</v>
+      <c r="H187" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I187" s="15" t="n"/>
       <c r="J187" s="15" t="inlineStr">
@@ -19571,7 +19965,9 @@
         </is>
       </c>
       <c r="K187" s="15" t="n"/>
-      <c r="L187" s="15" t="n"/>
+      <c r="L187" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M187" s="15">
         <f>SUM(H187,R187,T187,V187,X187)</f>
         <v/>
@@ -19640,7 +20036,9 @@
         </is>
       </c>
       <c r="K188" s="15" t="n"/>
-      <c r="L188" s="15" t="n"/>
+      <c r="L188" s="14" t="n">
+        <v>11</v>
+      </c>
       <c r="M188" s="15">
         <f>SUM(H188,R188,T188,V188,X188)</f>
         <v/>
@@ -19713,7 +20111,9 @@
         </is>
       </c>
       <c r="K189" s="15" t="n"/>
-      <c r="L189" s="15" t="n"/>
+      <c r="L189" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M189" s="15">
         <f>SUM(H189,R189,T189,V189,X189)</f>
         <v/>
@@ -19772,8 +20172,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H190" s="15" t="n">
-        <v>9</v>
+      <c r="H190" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I190" s="15" t="n"/>
       <c r="J190" s="15" t="inlineStr">
@@ -19782,7 +20182,9 @@
         </is>
       </c>
       <c r="K190" s="15" t="n"/>
-      <c r="L190" s="15" t="n"/>
+      <c r="L190" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M190" s="15">
         <f>SUM(H190,R190,T190,V190,X190)</f>
         <v/>
@@ -19841,8 +20243,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H191" s="15" t="n">
-        <v>6</v>
+      <c r="H191" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I191" s="15" t="n"/>
       <c r="J191" s="15" t="inlineStr">
@@ -19851,7 +20253,9 @@
         </is>
       </c>
       <c r="K191" s="15" t="n"/>
-      <c r="L191" s="15" t="n"/>
+      <c r="L191" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M191" s="15">
         <f>SUM(H191,R191,T191,V191,X191)</f>
         <v/>
@@ -19920,7 +20324,9 @@
         </is>
       </c>
       <c r="K192" s="15" t="n"/>
-      <c r="L192" s="15" t="n"/>
+      <c r="L192" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="M192" s="15">
         <f>SUM(H192,R192,T192,V192,X192)</f>
         <v/>
@@ -19993,7 +20399,9 @@
         </is>
       </c>
       <c r="K193" s="15" t="n"/>
-      <c r="L193" s="15" t="n"/>
+      <c r="L193" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M193" s="15">
         <f>SUM(H193,R193,T193,V193,X193)</f>
         <v/>
@@ -20062,7 +20470,9 @@
         </is>
       </c>
       <c r="K194" s="15" t="n"/>
-      <c r="L194" s="15" t="n"/>
+      <c r="L194" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M194" s="15">
         <f>SUM(H194,R194,T194,V194,X194)</f>
         <v/>
@@ -20131,7 +20541,9 @@
         </is>
       </c>
       <c r="K195" s="15" t="n"/>
-      <c r="L195" s="15" t="n"/>
+      <c r="L195" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M195" s="15">
         <f>SUM(H195,R195,T195,V195,X195)</f>
         <v/>
@@ -20273,7 +20685,9 @@
         </is>
       </c>
       <c r="K197" s="15" t="n"/>
-      <c r="L197" s="15" t="n"/>
+      <c r="L197" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M197" s="15">
         <f>SUM(H197,R197,T197,V197,X197)</f>
         <v/>
@@ -20346,7 +20760,9 @@
         </is>
       </c>
       <c r="K198" s="15" t="n"/>
-      <c r="L198" s="15" t="n"/>
+      <c r="L198" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M198" s="15">
         <f>SUM(H198,R198,T198,V198,X198)</f>
         <v/>
@@ -20412,7 +20828,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K199" s="15" t="n"/>
+      <c r="K199" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="L199" s="15" t="n"/>
       <c r="M199" s="15">
         <f>SUM(H199,R199,T199,V199,X199)</f>
@@ -20544,7 +20962,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K201" s="15" t="n"/>
+      <c r="K201" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L201" s="15" t="n"/>
       <c r="M201" s="15">
         <f>SUM(H201,R201,T201,V201,X201)</f>
@@ -20614,7 +21034,9 @@
         </is>
       </c>
       <c r="K202" s="15" t="n"/>
-      <c r="L202" s="15" t="n"/>
+      <c r="L202" s="14" t="n">
+        <v>12</v>
+      </c>
       <c r="M202" s="15">
         <f>SUM(H202,R202,T202,V202,X202)</f>
         <v/>
@@ -20680,7 +21102,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K203" s="15" t="n"/>
+      <c r="K203" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="L203" s="15" t="n"/>
       <c r="M203" s="15">
         <f>SUM(H203,R203,T203,V203,X203)</f>
@@ -20750,7 +21174,9 @@
         </is>
       </c>
       <c r="K204" s="15" t="n"/>
-      <c r="L204" s="15" t="n"/>
+      <c r="L204" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M204" s="15">
         <f>SUM(H204,R204,T204,V204,X204)</f>
         <v/>
@@ -20816,7 +21242,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K205" s="15" t="n"/>
+      <c r="K205" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L205" s="15" t="n"/>
       <c r="M205" s="15">
         <f>SUM(H205,R205,T205,V205,X205)</f>
@@ -20886,7 +21314,9 @@
         </is>
       </c>
       <c r="K206" s="15" t="n"/>
-      <c r="L206" s="15" t="n"/>
+      <c r="L206" s="14" t="n">
+        <v>11</v>
+      </c>
       <c r="M206" s="15">
         <f>SUM(H206,R206,T206,V206,X206)</f>
         <v/>
@@ -21149,7 +21579,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K210" s="15" t="n"/>
+      <c r="K210" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L210" s="15" t="n"/>
       <c r="M210" s="15">
         <f>SUM(H210,R210,T210,V210,X210)</f>
@@ -21216,7 +21648,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K211" s="15" t="n"/>
+      <c r="K211" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L211" s="15" t="n"/>
       <c r="M211" s="15">
         <f>SUM(H211,R211,T211,V211,X211)</f>
@@ -21345,8 +21779,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H213" s="15" t="n">
-        <v>6</v>
+      <c r="H213" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I213" s="15" t="n"/>
       <c r="J213" s="15" t="inlineStr">
@@ -21355,7 +21789,9 @@
         </is>
       </c>
       <c r="K213" s="15" t="n"/>
-      <c r="L213" s="15" t="n"/>
+      <c r="L213" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M213" s="15">
         <f>SUM(H213,R213,T213,V213,X213)</f>
         <v/>
@@ -21424,7 +21860,9 @@
         </is>
       </c>
       <c r="K214" s="15" t="n"/>
-      <c r="L214" s="15" t="n"/>
+      <c r="L214" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M214" s="15">
         <f>SUM(H214,R214,T214,V214,X214)</f>
         <v/>
@@ -21562,7 +22000,9 @@
         </is>
       </c>
       <c r="K216" s="15" t="n"/>
-      <c r="L216" s="15" t="n"/>
+      <c r="L216" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M216" s="15">
         <f>SUM(H216,R216,T216,V216,X216)</f>
         <v/>
@@ -21696,7 +22136,9 @@
         </is>
       </c>
       <c r="K218" s="15" t="n"/>
-      <c r="L218" s="15" t="n"/>
+      <c r="L218" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M218" s="15">
         <f>SUM(H218,R218,T218,V218,X218)</f>
         <v/>
@@ -21765,7 +22207,9 @@
         </is>
       </c>
       <c r="K219" s="15" t="n"/>
-      <c r="L219" s="15" t="n"/>
+      <c r="L219" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M219" s="15">
         <f>SUM(H219,R219,T219,V219,X219)</f>
         <v/>
@@ -21824,8 +22268,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H220" s="15" t="n">
-        <v>6</v>
+      <c r="H220" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I220" s="15" t="n"/>
       <c r="J220" s="15" t="inlineStr">
@@ -21834,7 +22278,9 @@
         </is>
       </c>
       <c r="K220" s="15" t="n"/>
-      <c r="L220" s="15" t="n"/>
+      <c r="L220" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M220" s="15">
         <f>SUM(H220,R220,T220,V220,X220)</f>
         <v/>
@@ -21896,7 +22342,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K221" s="15" t="n"/>
+      <c r="K221" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="L221" s="15" t="n"/>
       <c r="M221" s="15">
         <f>SUM(H221,R221,T221,V221,X221)</f>
@@ -21956,8 +22404,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H222" s="15" t="n">
-        <v>6</v>
+      <c r="H222" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I222" s="15" t="n"/>
       <c r="J222" s="15" t="inlineStr">
@@ -21966,7 +22414,9 @@
         </is>
       </c>
       <c r="K222" s="15" t="n"/>
-      <c r="L222" s="15" t="n"/>
+      <c r="L222" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M222" s="15">
         <f>SUM(H222,R222,T222,V222,X222)</f>
         <v/>
@@ -22025,8 +22475,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H223" s="15" t="n">
-        <v>6</v>
+      <c r="H223" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I223" s="15" t="n"/>
       <c r="J223" s="15" t="inlineStr">
@@ -22035,7 +22485,9 @@
         </is>
       </c>
       <c r="K223" s="15" t="n"/>
-      <c r="L223" s="15" t="n"/>
+      <c r="L223" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M223" s="15">
         <f>SUM(H223,R223,T223,V223,X223)</f>
         <v/>
@@ -22163,8 +22615,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H225" s="15" t="n">
-        <v>6</v>
+      <c r="H225" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I225" s="15" t="n"/>
       <c r="J225" s="15" t="inlineStr">
@@ -22173,7 +22625,9 @@
         </is>
       </c>
       <c r="K225" s="15" t="n"/>
-      <c r="L225" s="15" t="n"/>
+      <c r="L225" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M225" s="15">
         <f>SUM(H225,R225,T225,V225,X225)</f>
         <v/>
@@ -22301,8 +22755,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H227" s="15" t="n">
-        <v>6</v>
+      <c r="H227" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I227" s="15" t="n"/>
       <c r="J227" s="15" t="inlineStr">
@@ -22311,7 +22765,9 @@
         </is>
       </c>
       <c r="K227" s="15" t="n"/>
-      <c r="L227" s="15" t="n"/>
+      <c r="L227" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M227" s="15">
         <f>SUM(H227,R227,T227,V227,X227)</f>
         <v/>
@@ -22373,7 +22829,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K228" s="15" t="n"/>
+      <c r="K228" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="L228" s="15" t="n"/>
       <c r="M228" s="15">
         <f>SUM(H228,R228,T228,V228,X228)</f>
@@ -22433,8 +22891,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H229" s="15" t="n">
-        <v>6</v>
+      <c r="H229" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I229" s="15" t="n"/>
       <c r="J229" s="15" t="inlineStr">
@@ -22443,7 +22901,9 @@
         </is>
       </c>
       <c r="K229" s="15" t="n"/>
-      <c r="L229" s="15" t="n"/>
+      <c r="L229" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M229" s="15">
         <f>SUM(H229,R229,T229,V229,X229)</f>
         <v/>
@@ -22512,7 +22972,9 @@
         </is>
       </c>
       <c r="K230" s="15" t="n"/>
-      <c r="L230" s="15" t="n"/>
+      <c r="L230" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M230" s="15">
         <f>SUM(H230,R230,T230,V230,X230)</f>
         <v/>
@@ -22571,8 +23033,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H231" s="15" t="n">
-        <v>6</v>
+      <c r="H231" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I231" s="15" t="n"/>
       <c r="J231" s="15" t="inlineStr">
@@ -22581,7 +23043,9 @@
         </is>
       </c>
       <c r="K231" s="15" t="n"/>
-      <c r="L231" s="15" t="n"/>
+      <c r="L231" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M231" s="15">
         <f>SUM(H231,R231,T231,V231,X231)</f>
         <v/>
@@ -22650,7 +23114,9 @@
         </is>
       </c>
       <c r="K232" s="15" t="n"/>
-      <c r="L232" s="15" t="n"/>
+      <c r="L232" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M232" s="15">
         <f>SUM(H232,R232,T232,V232,X232)</f>
         <v/>
@@ -22778,8 +23244,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H234" s="15" t="n">
-        <v>6</v>
+      <c r="H234" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I234" s="15" t="n"/>
       <c r="J234" s="15" t="inlineStr">
@@ -22788,7 +23254,9 @@
         </is>
       </c>
       <c r="K234" s="15" t="n"/>
-      <c r="L234" s="15" t="n"/>
+      <c r="L234" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M234" s="15">
         <f>SUM(H234,R234,T234,V234,X234)</f>
         <v/>
@@ -22847,8 +23315,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H235" s="15" t="n">
-        <v>6</v>
+      <c r="H235" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I235" s="15" t="n"/>
       <c r="J235" s="15" t="inlineStr">
@@ -22857,7 +23325,9 @@
         </is>
       </c>
       <c r="K235" s="15" t="n"/>
-      <c r="L235" s="15" t="n"/>
+      <c r="L235" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M235" s="15">
         <f>SUM(H235,R235,T235,V235,X235)</f>
         <v/>
@@ -23127,7 +23597,9 @@
         </is>
       </c>
       <c r="K239" s="15" t="n"/>
-      <c r="L239" s="15" t="n"/>
+      <c r="L239" s="14" t="n">
+        <v>9</v>
+      </c>
       <c r="M239" s="15">
         <f>SUM(H239,R239,T239,V239,X239)</f>
         <v/>
@@ -23334,7 +23806,9 @@
         </is>
       </c>
       <c r="K242" s="15" t="n"/>
-      <c r="L242" s="15" t="n"/>
+      <c r="L242" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M242" s="15">
         <f>SUM(H242,R242,T242,V242,X242)</f>
         <v/>
@@ -23403,7 +23877,9 @@
         </is>
       </c>
       <c r="K243" s="15" t="n"/>
-      <c r="L243" s="15" t="n"/>
+      <c r="L243" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M243" s="15">
         <f>SUM(H243,R243,T243,V243,X243)</f>
         <v/>
@@ -23602,7 +24078,9 @@
         </is>
       </c>
       <c r="K246" s="15" t="n"/>
-      <c r="L246" s="15" t="n"/>
+      <c r="L246" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M246" s="15">
         <f>SUM(H246,R246,T246,V246,X246)</f>
         <v/>
@@ -23809,7 +24287,9 @@
         </is>
       </c>
       <c r="K249" s="15" t="n"/>
-      <c r="L249" s="15" t="n"/>
+      <c r="L249" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M249" s="15">
         <f>SUM(H249,R249,T249,V249,X249)</f>
         <v/>
@@ -23875,7 +24355,9 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K250" s="15" t="n"/>
+      <c r="K250" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L250" s="15" t="n"/>
       <c r="M250" s="15">
         <f>SUM(H250,R250,T250,V250,X250)</f>
@@ -24014,7 +24496,9 @@
         </is>
       </c>
       <c r="K252" s="15" t="n"/>
-      <c r="L252" s="15" t="n"/>
+      <c r="L252" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M252" s="15">
         <f>SUM(H252,R252,T252,V252,X252)</f>
         <v/>
@@ -24152,7 +24636,9 @@
         </is>
       </c>
       <c r="K254" s="15" t="n"/>
-      <c r="L254" s="15" t="n"/>
+      <c r="L254" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M254" s="15">
         <f>SUM(H254,R254,T254,V254,X254)</f>
         <v/>
@@ -24221,7 +24707,9 @@
         </is>
       </c>
       <c r="K255" s="15" t="n"/>
-      <c r="L255" s="15" t="n"/>
+      <c r="L255" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M255" s="15">
         <f>SUM(H255,R255,T255,V255,X255)</f>
         <v/>
@@ -24352,7 +24840,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K257" s="15" t="n"/>
+      <c r="K257" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="L257" s="15" t="n"/>
       <c r="M257" s="15">
         <f>SUM(H257,R257,T257,V257,X257)</f>
@@ -24487,7 +24977,9 @@
         </is>
       </c>
       <c r="K259" s="15" t="n"/>
-      <c r="L259" s="15" t="n"/>
+      <c r="L259" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M259" s="15">
         <f>SUM(H259,R259,T259,V259,X259)</f>
         <v/>
@@ -24549,7 +25041,9 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K260" s="15" t="n"/>
+      <c r="K260" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L260" s="15" t="n"/>
       <c r="M260" s="15">
         <f>SUM(H260,R260,T260,V260,X260)</f>
@@ -24619,7 +25113,9 @@
         </is>
       </c>
       <c r="K261" s="15" t="n"/>
-      <c r="L261" s="15" t="n"/>
+      <c r="L261" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M261" s="15">
         <f>SUM(H261,R261,T261,V261,X261)</f>
         <v/>
@@ -24757,7 +25253,9 @@
         </is>
       </c>
       <c r="K263" s="15" t="n"/>
-      <c r="L263" s="15" t="n"/>
+      <c r="L263" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M263" s="15">
         <f>SUM(H263,R263,T263,V263,X263)</f>
         <v/>
@@ -24816,8 +25314,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H264" s="15" t="n">
-        <v>9</v>
+      <c r="H264" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I264" s="15" t="n"/>
       <c r="J264" s="15" t="inlineStr">
@@ -24826,7 +25324,9 @@
         </is>
       </c>
       <c r="K264" s="15" t="n"/>
-      <c r="L264" s="15" t="n"/>
+      <c r="L264" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="M264" s="15">
         <f>SUM(H264,R264,T264,V264,X264)</f>
         <v/>
@@ -24895,7 +25395,9 @@
         </is>
       </c>
       <c r="K265" s="15" t="n"/>
-      <c r="L265" s="15" t="n"/>
+      <c r="L265" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M265" s="15">
         <f>SUM(H265,R265,T265,V265,X265)</f>
         <v/>
@@ -24954,8 +25456,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H266" s="15" t="n">
-        <v>9</v>
+      <c r="H266" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I266" s="15" t="n"/>
       <c r="J266" s="15" t="inlineStr">
@@ -24964,7 +25466,9 @@
         </is>
       </c>
       <c r="K266" s="15" t="n"/>
-      <c r="L266" s="15" t="n"/>
+      <c r="L266" s="14" t="n">
+        <v>7</v>
+      </c>
       <c r="M266" s="15">
         <f>SUM(H266,R266,T266,V266,X266)</f>
         <v/>
@@ -25033,7 +25537,9 @@
         </is>
       </c>
       <c r="K267" s="15" t="n"/>
-      <c r="L267" s="15" t="n"/>
+      <c r="L267" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M267" s="15">
         <f>SUM(H267,R267,T267,V267,X267)</f>
         <v/>
@@ -25092,8 +25598,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H268" s="15" t="n">
-        <v>9</v>
+      <c r="H268" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I268" s="15" t="n"/>
       <c r="J268" s="15" t="inlineStr">
@@ -25102,7 +25608,9 @@
         </is>
       </c>
       <c r="K268" s="15" t="n"/>
-      <c r="L268" s="15" t="n"/>
+      <c r="L268" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="M268" s="15">
         <f>SUM(H268,R268,T268,V268,X268)</f>
         <v/>
@@ -25171,7 +25679,9 @@
         </is>
       </c>
       <c r="K269" s="15" t="n"/>
-      <c r="L269" s="15" t="n"/>
+      <c r="L269" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M269" s="15">
         <f>SUM(H269,R269,T269,V269,X269)</f>
         <v/>
@@ -25230,8 +25740,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H270" s="15" t="n">
-        <v>9</v>
+      <c r="H270" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I270" s="15" t="n"/>
       <c r="J270" s="15" t="inlineStr">
@@ -25240,7 +25750,9 @@
         </is>
       </c>
       <c r="K270" s="15" t="n"/>
-      <c r="L270" s="15" t="n"/>
+      <c r="L270" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M270" s="15">
         <f>SUM(H270,R270,T270,V270,X270)</f>
         <v/>
@@ -25309,7 +25821,9 @@
         </is>
       </c>
       <c r="K271" s="15" t="n"/>
-      <c r="L271" s="15" t="n"/>
+      <c r="L271" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M271" s="15">
         <f>SUM(H271,R271,T271,V271,X271)</f>
         <v/>
@@ -25368,8 +25882,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H272" s="15" t="n">
-        <v>9</v>
+      <c r="H272" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I272" s="15" t="n"/>
       <c r="J272" s="15" t="inlineStr">
@@ -25378,7 +25892,9 @@
         </is>
       </c>
       <c r="K272" s="15" t="n"/>
-      <c r="L272" s="15" t="n"/>
+      <c r="L272" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M272" s="15">
         <f>SUM(H272,R272,T272,V272,X272)</f>
         <v/>
@@ -25447,7 +25963,9 @@
         </is>
       </c>
       <c r="K273" s="15" t="n"/>
-      <c r="L273" s="15" t="n"/>
+      <c r="L273" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M273" s="15">
         <f>SUM(H273,R273,T273,V273,X273)</f>
         <v/>
@@ -25506,8 +26024,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H274" s="15" t="n">
-        <v>9</v>
+      <c r="H274" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I274" s="15" t="n"/>
       <c r="J274" s="15" t="inlineStr">
@@ -25516,7 +26034,9 @@
         </is>
       </c>
       <c r="K274" s="15" t="n"/>
-      <c r="L274" s="15" t="n"/>
+      <c r="L274" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M274" s="15">
         <f>SUM(H274,R274,T274,V274,X274)</f>
         <v/>
@@ -25585,7 +26105,9 @@
         </is>
       </c>
       <c r="K275" s="15" t="n"/>
-      <c r="L275" s="15" t="n"/>
+      <c r="L275" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M275" s="15">
         <f>SUM(H275,R275,T275,V275,X275)</f>
         <v/>
@@ -25644,8 +26166,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H276" s="15" t="n">
-        <v>9</v>
+      <c r="H276" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I276" s="15" t="n"/>
       <c r="J276" s="15" t="inlineStr">
@@ -25654,7 +26176,9 @@
         </is>
       </c>
       <c r="K276" s="15" t="n"/>
-      <c r="L276" s="15" t="n"/>
+      <c r="L276" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M276" s="15">
         <f>SUM(H276,R276,T276,V276,X276)</f>
         <v/>
@@ -25723,7 +26247,9 @@
         </is>
       </c>
       <c r="K277" s="15" t="n"/>
-      <c r="L277" s="15" t="n"/>
+      <c r="L277" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M277" s="15">
         <f>SUM(H277,R277,T277,V277,X277)</f>
         <v/>
@@ -25782,8 +26308,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H278" s="15" t="n">
-        <v>9</v>
+      <c r="H278" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="I278" s="15" t="n"/>
       <c r="J278" s="15" t="inlineStr">
@@ -25792,7 +26318,9 @@
         </is>
       </c>
       <c r="K278" s="15" t="n"/>
-      <c r="L278" s="15" t="n"/>
+      <c r="L278" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M278" s="15">
         <f>SUM(H278,R278,T278,V278,X278)</f>
         <v/>
@@ -25924,7 +26452,9 @@
         </is>
       </c>
       <c r="K280" s="15" t="n"/>
-      <c r="L280" s="15" t="n"/>
+      <c r="L280" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M280" s="15">
         <f>SUM(H280,R280,T280,V280,X280)</f>
         <v/>
@@ -26062,7 +26592,9 @@
         </is>
       </c>
       <c r="K282" s="15" t="n"/>
-      <c r="L282" s="15" t="n"/>
+      <c r="L282" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M282" s="15">
         <f>SUM(H282,R282,T282,V282,X282)</f>
         <v/>
@@ -26200,7 +26732,9 @@
         </is>
       </c>
       <c r="K284" s="15" t="n"/>
-      <c r="L284" s="15" t="n"/>
+      <c r="L284" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M284" s="15">
         <f>SUM(H284,R284,T284,V284,X284)</f>
         <v/>
@@ -26338,7 +26872,9 @@
         </is>
       </c>
       <c r="K286" s="15" t="n"/>
-      <c r="L286" s="15" t="n"/>
+      <c r="L286" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M286" s="15">
         <f>SUM(H286,R286,T286,V286,X286)</f>
         <v/>
@@ -26746,7 +27282,9 @@
         </is>
       </c>
       <c r="K292" s="15" t="n"/>
-      <c r="L292" s="15" t="n"/>
+      <c r="L292" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="M292" s="15">
         <f>SUM(H292,R292,T292,V292,X292)</f>
         <v/>
@@ -26884,7 +27422,9 @@
         </is>
       </c>
       <c r="K294" s="15" t="n"/>
-      <c r="L294" s="15" t="n"/>
+      <c r="L294" s="14" t="n">
+        <v>4</v>
+      </c>
       <c r="M294" s="15">
         <f>SUM(H294,R294,T294,V294,X294)</f>
         <v/>
@@ -27022,7 +27562,9 @@
         </is>
       </c>
       <c r="K296" s="15" t="n"/>
-      <c r="L296" s="15" t="n"/>
+      <c r="L296" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="M296" s="15">
         <f>SUM(H296,R296,T296,V296,X296)</f>
         <v/>
@@ -27160,7 +27702,9 @@
         </is>
       </c>
       <c r="K298" s="15" t="n"/>
-      <c r="L298" s="15" t="n"/>
+      <c r="L298" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="M298" s="15">
         <f>SUM(H298,R298,T298,V298,X298)</f>
         <v/>
@@ -27292,7 +27836,9 @@
         </is>
       </c>
       <c r="K300" s="15" t="n"/>
-      <c r="L300" s="15" t="n"/>
+      <c r="L300" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M300" s="15">
         <f>SUM(H300,R300,T300,V300,X300)</f>
         <v/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6690,8 +6690,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H2" s="14" t="n">
-        <v>1</v>
+      <c r="H2" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="inlineStr">
@@ -6775,9 +6775,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n"/>
-      <c r="L3" s="14" t="n">
-        <v>13</v>
-      </c>
+      <c r="L3" s="15" t="n"/>
       <c r="M3" s="15">
         <f>SUM(H3,R3,T3,V3,X3)</f>
         <v/>
@@ -6836,8 +6834,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>1</v>
+      <c r="H4" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="inlineStr">
@@ -6846,9 +6844,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n"/>
-      <c r="L4" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L4" s="15" t="n"/>
       <c r="M4" s="15">
         <f>SUM(H4,R4,T4,V4,X4)</f>
         <v/>
@@ -6917,9 +6913,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n"/>
-      <c r="L5" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L5" s="15" t="n"/>
       <c r="M5" s="15">
         <f>SUM(H5,R5,T5,V5,X5)</f>
         <v/>
@@ -6982,8 +6976,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>1</v>
+      <c r="H6" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="inlineStr">
@@ -6992,9 +6986,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n"/>
-      <c r="L6" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L6" s="15" t="n"/>
       <c r="M6" s="15">
         <f>SUM(H6,R6,T6,V6,X6)</f>
         <v/>
@@ -7063,9 +7055,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n"/>
-      <c r="L7" s="14" t="n">
-        <v>12</v>
-      </c>
+      <c r="L7" s="15" t="n"/>
       <c r="M7" s="15">
         <f>SUM(H7,R7,T7,V7,X7)</f>
         <v/>
@@ -7128,8 +7118,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>1</v>
+      <c r="H8" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="inlineStr">
@@ -7138,9 +7128,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n"/>
-      <c r="L8" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L8" s="15" t="n"/>
       <c r="M8" s="15">
         <f>SUM(H8,R8,T8,V8,X8)</f>
         <v/>
@@ -7209,9 +7197,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n"/>
-      <c r="L9" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L9" s="15" t="n"/>
       <c r="M9" s="15">
         <f>SUM(H9,R9,T9,V9,X9)</f>
         <v/>
@@ -7274,8 +7260,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>1</v>
+      <c r="H10" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="inlineStr">
@@ -7283,12 +7269,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
       <c r="M10" s="15">
         <f>SUM(H10,R10,T10,V10,X10)</f>
         <v/>
@@ -7347,8 +7329,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>1</v>
+      <c r="H11" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="inlineStr">
@@ -7357,9 +7339,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n"/>
-      <c r="L11" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L11" s="15" t="n"/>
       <c r="M11" s="15">
         <f>SUM(H11,R11,T11,V11,X11)</f>
         <v/>
@@ -7418,8 +7398,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>1</v>
+      <c r="H12" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="inlineStr">
@@ -7428,9 +7408,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n"/>
-      <c r="L12" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L12" s="15" t="n"/>
       <c r="M12" s="15">
         <f>SUM(H12,R12,T12,V12,X12)</f>
         <v/>
@@ -7503,9 +7481,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n"/>
-      <c r="L13" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L13" s="15" t="n"/>
       <c r="M13" s="15">
         <f>SUM(H13,R13,T13,V13,X13)</f>
         <v/>
@@ -7576,9 +7552,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n"/>
-      <c r="L14" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L14" s="15" t="n"/>
       <c r="M14" s="15">
         <f>SUM(H14,R14,T14,V14,X14)</f>
         <v/>
@@ -7637,8 +7611,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>1</v>
+      <c r="H15" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="15" t="inlineStr">
@@ -7647,9 +7621,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n"/>
-      <c r="L15" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L15" s="15" t="n"/>
       <c r="M15" s="15">
         <f>SUM(H15,R15,T15,V15,X15)</f>
         <v/>
@@ -7712,8 +7684,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H16" s="14" t="n">
-        <v>1</v>
+      <c r="H16" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I16" s="15" t="n"/>
       <c r="J16" s="15" t="inlineStr">
@@ -7722,9 +7694,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n"/>
-      <c r="L16" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L16" s="15" t="n"/>
       <c r="M16" s="15">
         <f>SUM(H16,R16,T16,V16,X16)</f>
         <v/>
@@ -7797,9 +7767,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n"/>
-      <c r="L17" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L17" s="15" t="n"/>
       <c r="M17" s="15">
         <f>SUM(H17,R17,T17,V17,X17)</f>
         <v/>
@@ -7870,9 +7838,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n"/>
-      <c r="L18" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L18" s="15" t="n"/>
       <c r="M18" s="15">
         <f>SUM(H18,R18,T18,V18,X18)</f>
         <v/>
@@ -7935,8 +7901,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H19" s="14" t="n">
-        <v>1</v>
+      <c r="H19" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I19" s="15" t="n"/>
       <c r="J19" s="15" t="inlineStr">
@@ -7945,9 +7911,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n"/>
-      <c r="L19" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L19" s="15" t="n"/>
       <c r="M19" s="15">
         <f>SUM(H19,R19,T19,V19,X19)</f>
         <v/>
@@ -8010,8 +7974,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>1</v>
+      <c r="H20" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="inlineStr">
@@ -8020,9 +7984,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n"/>
-      <c r="L20" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L20" s="15" t="n"/>
       <c r="M20" s="15">
         <f>SUM(H20,R20,T20,V20,X20)</f>
         <v/>
@@ -8091,9 +8053,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n"/>
-      <c r="L21" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L21" s="15" t="n"/>
       <c r="M21" s="15">
         <f>SUM(H21,R21,T21,V21,X21)</f>
         <v/>
@@ -8235,9 +8195,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n"/>
-      <c r="L23" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L23" s="15" t="n"/>
       <c r="M23" s="15">
         <f>SUM(H23,R23,T23,V23,X23)</f>
         <v/>
@@ -8367,8 +8325,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H25" s="14" t="n">
-        <v>1</v>
+      <c r="H25" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I25" s="15" t="n"/>
       <c r="J25" s="15" t="inlineStr">
@@ -8377,9 +8335,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n"/>
-      <c r="L25" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L25" s="15" t="n"/>
       <c r="M25" s="15">
         <f>SUM(H25,R25,T25,V25,X25)</f>
         <v/>
@@ -8442,8 +8398,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>1</v>
+      <c r="H26" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I26" s="15" t="n"/>
       <c r="J26" s="15" t="inlineStr">
@@ -8452,9 +8408,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n"/>
-      <c r="L26" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L26" s="15" t="n"/>
       <c r="M26" s="15">
         <f>SUM(H26,R26,T26,V26,X26)</f>
         <v/>
@@ -8523,9 +8477,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n"/>
-      <c r="L27" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L27" s="15" t="n"/>
       <c r="M27" s="15">
         <f>SUM(H27,R27,T27,V27,X27)</f>
         <v/>
@@ -8596,9 +8548,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n"/>
-      <c r="L28" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L28" s="15" t="n"/>
       <c r="M28" s="15">
         <f>SUM(H28,R28,T28,V28,X28)</f>
         <v/>
@@ -8740,9 +8690,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n"/>
-      <c r="L30" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L30" s="15" t="n"/>
       <c r="M30" s="15">
         <f>SUM(H30,R30,T30,V30,X30)</f>
         <v/>
@@ -8801,8 +8749,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
-        <v>1</v>
+      <c r="H31" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I31" s="15" t="n"/>
       <c r="J31" s="15" t="inlineStr">
@@ -8811,9 +8759,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n"/>
-      <c r="L31" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L31" s="15" t="n"/>
       <c r="M31" s="15">
         <f>SUM(H31,R31,T31,V31,X31)</f>
         <v/>
@@ -8876,8 +8822,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="14" t="n">
-        <v>1</v>
+      <c r="H32" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I32" s="15" t="n"/>
       <c r="J32" s="15" t="inlineStr">
@@ -8886,9 +8832,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n"/>
-      <c r="L32" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L32" s="15" t="n"/>
       <c r="M32" s="15">
         <f>SUM(H32,R32,T32,V32,X32)</f>
         <v/>
@@ -9024,9 +8968,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n"/>
-      <c r="L34" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L34" s="15" t="n"/>
       <c r="M34" s="15">
         <f>SUM(H34,R34,T34,V34,X34)</f>
         <v/>
@@ -9168,9 +9110,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n"/>
-      <c r="L36" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L36" s="15" t="n"/>
       <c r="M36" s="15">
         <f>SUM(H36,R36,T36,V36,X36)</f>
         <v/>
@@ -9229,8 +9169,8 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H37" s="14" t="n">
-        <v>1</v>
+      <c r="H37" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I37" s="15" t="n"/>
       <c r="J37" s="15" t="inlineStr">
@@ -9239,9 +9179,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n"/>
-      <c r="L37" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L37" s="15" t="n"/>
       <c r="M37" s="15">
         <f>SUM(H37,R37,T37,V37,X37)</f>
         <v/>
@@ -9380,12 +9318,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K39" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="15" t="n"/>
       <c r="M39" s="15">
         <f>SUM(H39,R39,T39,V39,X39)</f>
         <v/>
@@ -9529,9 +9463,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n"/>
-      <c r="L41" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L41" s="15" t="n"/>
       <c r="M41" s="15">
         <f>SUM(H41,R41,T41,V41,X41)</f>
         <v/>
@@ -9602,9 +9534,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n"/>
-      <c r="L42" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L42" s="15" t="n"/>
       <c r="M42" s="15">
         <f>SUM(H42,R42,T42,V42,X42)</f>
         <v/>
@@ -9675,9 +9605,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n"/>
-      <c r="L43" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L43" s="15" t="n"/>
       <c r="M43" s="15">
         <f>SUM(H43,R43,T43,V43,X43)</f>
         <v/>
@@ -9747,12 +9675,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K44" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K44" s="15" t="n"/>
+      <c r="L44" s="15" t="n"/>
       <c r="M44" s="15">
         <f>SUM(H44,R44,T44,V44,X44)</f>
         <v/>
@@ -9819,9 +9743,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n"/>
-      <c r="L45" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L45" s="15" t="n"/>
       <c r="M45" s="15">
         <f>SUM(H45,R45,T45,V45,X45)</f>
         <v/>
@@ -9958,12 +9880,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K47" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K47" s="15" t="n"/>
+      <c r="L47" s="15" t="n"/>
       <c r="M47" s="15">
         <f>SUM(H47,R47,T47,V47,X47)</f>
         <v/>
@@ -10030,9 +9948,7 @@
         </is>
       </c>
       <c r="K48" s="15" t="n"/>
-      <c r="L48" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L48" s="15" t="n"/>
       <c r="M48" s="15">
         <f>SUM(H48,R48,T48,V48,X48)</f>
         <v/>
@@ -10102,12 +10018,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K49" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K49" s="15" t="n"/>
+      <c r="L49" s="15" t="n"/>
       <c r="M49" s="15">
         <f>SUM(H49,R49,T49,V49,X49)</f>
         <v/>
@@ -10169,12 +10081,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K50" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="15" t="n"/>
       <c r="M50" s="15">
         <f>SUM(H50,R50,T50,V50,X50)</f>
         <v/>
@@ -10240,9 +10148,7 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K51" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15">
         <f>SUM(H51,R51,T51,V51,X51)</f>
@@ -10309,12 +10215,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K52" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
       <c r="M52" s="15">
         <f>SUM(H52,R52,T52,V52,X52)</f>
         <v/>
@@ -10389,9 +10291,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n"/>
-      <c r="L53" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L53" s="15" t="n"/>
       <c r="M53" s="15">
         <f>SUM(H53,R53,T53,V53,X53)</f>
         <v/>
@@ -10450,8 +10350,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H54" s="14" t="n">
-        <v>1</v>
+      <c r="H54" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I54" s="15" t="n"/>
       <c r="J54" s="15" t="inlineStr">
@@ -10460,9 +10360,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n"/>
-      <c r="L54" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L54" s="15" t="n"/>
       <c r="M54" s="15">
         <f>SUM(H54,R54,T54,V54,X54)</f>
         <v/>
@@ -10525,8 +10423,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H55" s="14" t="n">
-        <v>1</v>
+      <c r="H55" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I55" s="15" t="n"/>
       <c r="J55" s="15" t="inlineStr">
@@ -10534,12 +10432,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K55" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="K55" s="15" t="n"/>
+      <c r="L55" s="15" t="n"/>
       <c r="M55" s="15">
         <f>SUM(H55,R55,T55,V55,X55)</f>
         <v/>
@@ -10605,12 +10499,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K56" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K56" s="15" t="n"/>
+      <c r="L56" s="15" t="n"/>
       <c r="M56" s="15">
         <f>SUM(H56,R56,T56,V56,X56)</f>
         <v/>
@@ -10673,8 +10563,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H57" s="14" t="n">
-        <v>1</v>
+      <c r="H57" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I57" s="15" t="n"/>
       <c r="J57" s="15" t="inlineStr">
@@ -10683,9 +10573,7 @@
         </is>
       </c>
       <c r="K57" s="15" t="n"/>
-      <c r="L57" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L57" s="15" t="n"/>
       <c r="M57" s="15">
         <f>SUM(H57,R57,T57,V57,X57)</f>
         <v/>
@@ -10752,9 +10640,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n"/>
-      <c r="L58" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L58" s="15" t="n"/>
       <c r="M58" s="15">
         <f>SUM(H58,R58,T58,V58,X58)</f>
         <v/>
@@ -10813,8 +10699,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H59" s="14" t="n">
-        <v>1</v>
+      <c r="H59" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I59" s="15" t="n"/>
       <c r="J59" s="15" t="inlineStr">
@@ -10822,12 +10708,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K59" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="K59" s="15" t="n"/>
+      <c r="L59" s="15" t="n"/>
       <c r="M59" s="15">
         <f>SUM(H59,R59,T59,V59,X59)</f>
         <v/>
@@ -10889,12 +10771,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K60" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K60" s="15" t="n"/>
+      <c r="L60" s="15" t="n"/>
       <c r="M60" s="15">
         <f>SUM(H60,R60,T60,V60,X60)</f>
         <v/>
@@ -10953,8 +10831,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H61" s="14" t="n">
-        <v>1</v>
+      <c r="H61" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I61" s="15" t="n"/>
       <c r="J61" s="15" t="inlineStr">
@@ -10962,12 +10840,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K61" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L61" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K61" s="15" t="n"/>
+      <c r="L61" s="15" t="n"/>
       <c r="M61" s="15">
         <f>SUM(H61,R61,T61,V61,X61)</f>
         <v/>
@@ -11033,12 +10907,8 @@
           <t>ex Premium Collection</t>
         </is>
       </c>
-      <c r="K62" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K62" s="15" t="n"/>
+      <c r="L62" s="15" t="n"/>
       <c r="M62" s="15">
         <f>SUM(H62,R62,T62,V62,X62)</f>
         <v/>
@@ -11097,8 +10967,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H63" s="14" t="n">
-        <v>1</v>
+      <c r="H63" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I63" s="15" t="n"/>
       <c r="J63" s="15" t="inlineStr">
@@ -11106,12 +10976,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K63" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K63" s="15" t="n"/>
+      <c r="L63" s="15" t="n"/>
       <c r="M63" s="15">
         <f>SUM(H63,R63,T63,V63,X63)</f>
         <v/>
@@ -11182,9 +11048,7 @@
         </is>
       </c>
       <c r="K64" s="15" t="n"/>
-      <c r="L64" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L64" s="15" t="n"/>
       <c r="M64" s="15">
         <f>SUM(H64,R64,T64,V64,X64)</f>
         <v/>
@@ -11246,9 +11110,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K65" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="K65" s="15" t="n"/>
       <c r="L65" s="15" t="n"/>
       <c r="M65" s="15">
         <f>SUM(H65,R65,T65,V65,X65)</f>
@@ -11442,8 +11304,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H68" s="14" t="n">
-        <v>1</v>
+      <c r="H68" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I68" s="15" t="n"/>
       <c r="J68" s="15" t="inlineStr">
@@ -11451,12 +11313,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K68" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K68" s="15" t="n"/>
+      <c r="L68" s="15" t="n"/>
       <c r="M68" s="15">
         <f>SUM(H68,R68,T68,V68,X68)</f>
         <v/>
@@ -11515,8 +11373,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H69" s="14" t="n">
-        <v>1</v>
+      <c r="H69" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I69" s="15" t="n"/>
       <c r="J69" s="15" t="inlineStr">
@@ -11525,9 +11383,7 @@
         </is>
       </c>
       <c r="K69" s="15" t="n"/>
-      <c r="L69" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L69" s="15" t="n"/>
       <c r="M69" s="15">
         <f>SUM(H69,R69,T69,V69,X69)</f>
         <v/>
@@ -11589,9 +11445,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K70" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K70" s="15" t="n"/>
       <c r="L70" s="15" t="n"/>
       <c r="M70" s="15">
         <f>SUM(H70,R70,T70,V70,X70)</f>
@@ -11651,8 +11505,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H71" s="14" t="n">
-        <v>1</v>
+      <c r="H71" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I71" s="15" t="n"/>
       <c r="J71" s="15" t="inlineStr">
@@ -11660,12 +11514,8 @@
           <t>ETB (Elite Trainer Box)</t>
         </is>
       </c>
-      <c r="K71" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L71" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K71" s="15" t="n"/>
+      <c r="L71" s="15" t="n"/>
       <c r="M71" s="15">
         <f>SUM(H71,R71,T71,V71,X71)</f>
         <v/>
@@ -11734,9 +11584,7 @@
         </is>
       </c>
       <c r="K72" s="15" t="n"/>
-      <c r="L72" s="14" t="n">
-        <v>11</v>
-      </c>
+      <c r="L72" s="15" t="n"/>
       <c r="M72" s="15">
         <f>SUM(H72,R72,T72,V72,X72)</f>
         <v/>
@@ -11805,9 +11653,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n"/>
-      <c r="L73" s="14" t="n">
-        <v>10</v>
-      </c>
+      <c r="L73" s="15" t="n"/>
       <c r="M73" s="15">
         <f>SUM(H73,R73,T73,V73,X73)</f>
         <v/>
@@ -11876,9 +11722,7 @@
         </is>
       </c>
       <c r="K74" s="15" t="n"/>
-      <c r="L74" s="14" t="n">
-        <v>10</v>
-      </c>
+      <c r="L74" s="15" t="n"/>
       <c r="M74" s="15">
         <f>SUM(H74,R74,T74,V74,X74)</f>
         <v/>
@@ -11947,9 +11791,7 @@
         </is>
       </c>
       <c r="K75" s="15" t="n"/>
-      <c r="L75" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L75" s="15" t="n"/>
       <c r="M75" s="15">
         <f>SUM(H75,R75,T75,V75,X75)</f>
         <v/>
@@ -12018,9 +11860,7 @@
         </is>
       </c>
       <c r="K76" s="15" t="n"/>
-      <c r="L76" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L76" s="15" t="n"/>
       <c r="M76" s="15">
         <f>SUM(H76,R76,T76,V76,X76)</f>
         <v/>
@@ -12089,9 +11929,7 @@
         </is>
       </c>
       <c r="K77" s="15" t="n"/>
-      <c r="L77" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L77" s="15" t="n"/>
       <c r="M77" s="15">
         <f>SUM(H77,R77,T77,V77,X77)</f>
         <v/>
@@ -12160,9 +11998,7 @@
         </is>
       </c>
       <c r="K78" s="15" t="n"/>
-      <c r="L78" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L78" s="15" t="n"/>
       <c r="M78" s="15">
         <f>SUM(H78,R78,T78,V78,X78)</f>
         <v/>
@@ -12231,9 +12067,7 @@
         </is>
       </c>
       <c r="K79" s="15" t="n"/>
-      <c r="L79" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L79" s="15" t="n"/>
       <c r="M79" s="15">
         <f>SUM(H79,R79,T79,V79,X79)</f>
         <v/>
@@ -12302,9 +12136,7 @@
         </is>
       </c>
       <c r="K80" s="15" t="n"/>
-      <c r="L80" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L80" s="15" t="n"/>
       <c r="M80" s="15">
         <f>SUM(H80,R80,T80,V80,X80)</f>
         <v/>
@@ -12511,9 +12343,7 @@
         </is>
       </c>
       <c r="K83" s="15" t="n"/>
-      <c r="L83" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L83" s="15" t="n"/>
       <c r="M83" s="15">
         <f>SUM(H83,R83,T83,V83,X83)</f>
         <v/>
@@ -12655,9 +12485,7 @@
         </is>
       </c>
       <c r="K85" s="15" t="n"/>
-      <c r="L85" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L85" s="15" t="n"/>
       <c r="M85" s="15">
         <f>SUM(H85,R85,T85,V85,X85)</f>
         <v/>
@@ -12720,8 +12548,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H86" s="14" t="n">
-        <v>1</v>
+      <c r="H86" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I86" s="15" t="n"/>
       <c r="J86" s="15" t="inlineStr">
@@ -12730,9 +12558,7 @@
         </is>
       </c>
       <c r="K86" s="15" t="n"/>
-      <c r="L86" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L86" s="15" t="n"/>
       <c r="M86" s="15">
         <f>SUM(H86,R86,T86,V86,X86)</f>
         <v/>
@@ -12791,8 +12617,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H87" s="14" t="n">
-        <v>1</v>
+      <c r="H87" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I87" s="15" t="n"/>
       <c r="J87" s="15" t="inlineStr">
@@ -12801,9 +12627,7 @@
         </is>
       </c>
       <c r="K87" s="15" t="n"/>
-      <c r="L87" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L87" s="15" t="n"/>
       <c r="M87" s="15">
         <f>SUM(H87,R87,T87,V87,X87)</f>
         <v/>
@@ -12870,9 +12694,7 @@
         </is>
       </c>
       <c r="K88" s="15" t="n"/>
-      <c r="L88" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L88" s="15" t="n"/>
       <c r="M88" s="15">
         <f>SUM(H88,R88,T88,V88,X88)</f>
         <v/>
@@ -12943,9 +12765,7 @@
         </is>
       </c>
       <c r="K89" s="15" t="n"/>
-      <c r="L89" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L89" s="15" t="n"/>
       <c r="M89" s="15">
         <f>SUM(H89,R89,T89,V89,X89)</f>
         <v/>
@@ -13016,9 +12836,7 @@
         </is>
       </c>
       <c r="K90" s="15" t="n"/>
-      <c r="L90" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L90" s="15" t="n"/>
       <c r="M90" s="15">
         <f>SUM(H90,R90,T90,V90,X90)</f>
         <v/>
@@ -13089,9 +12907,7 @@
         </is>
       </c>
       <c r="K91" s="15" t="n"/>
-      <c r="L91" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L91" s="15" t="n"/>
       <c r="M91" s="15">
         <f>SUM(H91,R91,T91,V91,X91)</f>
         <v/>
@@ -13154,8 +12970,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H92" s="14" t="n">
-        <v>1</v>
+      <c r="H92" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I92" s="15" t="n"/>
       <c r="J92" s="15" t="inlineStr">
@@ -13164,9 +12980,7 @@
         </is>
       </c>
       <c r="K92" s="15" t="n"/>
-      <c r="L92" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L92" s="15" t="n"/>
       <c r="M92" s="15">
         <f>SUM(H92,R92,T92,V92,X92)</f>
         <v/>
@@ -13292,8 +13106,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H94" s="14" t="n">
-        <v>1</v>
+      <c r="H94" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I94" s="15" t="n"/>
       <c r="J94" s="15" t="inlineStr">
@@ -13302,9 +13116,7 @@
         </is>
       </c>
       <c r="K94" s="15" t="n"/>
-      <c r="L94" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L94" s="15" t="n"/>
       <c r="M94" s="15">
         <f>SUM(H94,R94,T94,V94,X94)</f>
         <v/>
@@ -13371,9 +13183,7 @@
         </is>
       </c>
       <c r="K95" s="15" t="n"/>
-      <c r="L95" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L95" s="15" t="n"/>
       <c r="M95" s="15">
         <f>SUM(H95,R95,T95,V95,X95)</f>
         <v/>
@@ -13432,8 +13242,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H96" s="14" t="n">
-        <v>1</v>
+      <c r="H96" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I96" s="15" t="n"/>
       <c r="J96" s="15" t="inlineStr">
@@ -13442,9 +13252,7 @@
         </is>
       </c>
       <c r="K96" s="15" t="n"/>
-      <c r="L96" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L96" s="15" t="n"/>
       <c r="M96" s="15">
         <f>SUM(H96,R96,T96,V96,X96)</f>
         <v/>
@@ -13511,9 +13319,7 @@
         </is>
       </c>
       <c r="K97" s="15" t="n"/>
-      <c r="L97" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L97" s="15" t="n"/>
       <c r="M97" s="15">
         <f>SUM(H97,R97,T97,V97,X97)</f>
         <v/>
@@ -13572,8 +13378,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H98" s="14" t="n">
-        <v>1</v>
+      <c r="H98" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I98" s="15" t="n"/>
       <c r="J98" s="15" t="inlineStr">
@@ -13582,9 +13388,7 @@
         </is>
       </c>
       <c r="K98" s="15" t="n"/>
-      <c r="L98" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L98" s="15" t="n"/>
       <c r="M98" s="15">
         <f>SUM(H98,R98,T98,V98,X98)</f>
         <v/>
@@ -13651,9 +13455,7 @@
         </is>
       </c>
       <c r="K99" s="15" t="n"/>
-      <c r="L99" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L99" s="15" t="n"/>
       <c r="M99" s="15">
         <f>SUM(H99,R99,T99,V99,X99)</f>
         <v/>
@@ -13712,8 +13514,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H100" s="14" t="n">
-        <v>1</v>
+      <c r="H100" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I100" s="15" t="n"/>
       <c r="J100" s="15" t="inlineStr">
@@ -13722,9 +13524,7 @@
         </is>
       </c>
       <c r="K100" s="15" t="n"/>
-      <c r="L100" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L100" s="15" t="n"/>
       <c r="M100" s="15">
         <f>SUM(H100,R100,T100,V100,X100)</f>
         <v/>
@@ -13783,8 +13583,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H101" s="14" t="n">
-        <v>1</v>
+      <c r="H101" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I101" s="15" t="n"/>
       <c r="J101" s="15" t="inlineStr">
@@ -13793,9 +13593,7 @@
         </is>
       </c>
       <c r="K101" s="15" t="n"/>
-      <c r="L101" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L101" s="15" t="n"/>
       <c r="M101" s="15">
         <f>SUM(H101,R101,T101,V101,X101)</f>
         <v/>
@@ -13935,9 +13733,7 @@
         </is>
       </c>
       <c r="K103" s="15" t="n"/>
-      <c r="L103" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L103" s="15" t="n"/>
       <c r="M103" s="15">
         <f>SUM(H103,R103,T103,V103,X103)</f>
         <v/>
@@ -14004,9 +13800,7 @@
         </is>
       </c>
       <c r="K104" s="15" t="n"/>
-      <c r="L104" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L104" s="15" t="n"/>
       <c r="M104" s="15">
         <f>SUM(H104,R104,T104,V104,X104)</f>
         <v/>
@@ -14082,9 +13876,7 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K105" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K105" s="15" t="n"/>
       <c r="L105" s="15" t="n"/>
       <c r="M105" s="15">
         <f>SUM(H105,R105,T105,V105,X105)</f>
@@ -14152,9 +13944,7 @@
         </is>
       </c>
       <c r="K106" s="15" t="n"/>
-      <c r="L106" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L106" s="15" t="n"/>
       <c r="M106" s="15">
         <f>SUM(H106,R106,T106,V106,X106)</f>
         <v/>
@@ -14221,9 +14011,7 @@
         </is>
       </c>
       <c r="K107" s="15" t="n"/>
-      <c r="L107" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L107" s="15" t="n"/>
       <c r="M107" s="15">
         <f>SUM(H107,R107,T107,V107,X107)</f>
         <v/>
@@ -14292,9 +14080,7 @@
         </is>
       </c>
       <c r="K108" s="15" t="n"/>
-      <c r="L108" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L108" s="15" t="n"/>
       <c r="M108" s="15">
         <f>SUM(H108,R108,T108,V108,X108)</f>
         <v/>
@@ -14363,9 +14149,7 @@
         </is>
       </c>
       <c r="K109" s="15" t="n"/>
-      <c r="L109" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L109" s="15" t="n"/>
       <c r="M109" s="15">
         <f>SUM(H109,R109,T109,V109,X109)</f>
         <v/>
@@ -14424,8 +14208,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H110" s="14" t="n">
-        <v>1</v>
+      <c r="H110" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I110" s="15" t="n"/>
       <c r="J110" s="15" t="inlineStr">
@@ -14433,12 +14217,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K110" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L110" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K110" s="15" t="n"/>
+      <c r="L110" s="15" t="n"/>
       <c r="M110" s="15">
         <f>SUM(H110,R110,T110,V110,X110)</f>
         <v/>
@@ -14497,8 +14277,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H111" s="14" t="n">
-        <v>1</v>
+      <c r="H111" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I111" s="15" t="n"/>
       <c r="J111" s="15" t="inlineStr">
@@ -14506,12 +14286,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K111" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L111" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K111" s="15" t="n"/>
+      <c r="L111" s="15" t="n"/>
       <c r="M111" s="15">
         <f>SUM(H111,R111,T111,V111,X111)</f>
         <v/>
@@ -14574,9 +14350,7 @@
         </is>
       </c>
       <c r="K112" s="15" t="n"/>
-      <c r="L112" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L112" s="15" t="n"/>
       <c r="M112" s="15">
         <f>SUM(H112,R112,T112,V112,X112)</f>
         <v/>
@@ -14639,9 +14413,7 @@
         </is>
       </c>
       <c r="K113" s="15" t="n"/>
-      <c r="L113" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L113" s="15" t="n"/>
       <c r="M113" s="15">
         <f>SUM(H113,R113,T113,V113,X113)</f>
         <v/>
@@ -14710,9 +14482,7 @@
         </is>
       </c>
       <c r="K114" s="15" t="n"/>
-      <c r="L114" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L114" s="15" t="n"/>
       <c r="M114" s="15">
         <f>SUM(H114,R114,T114,V114,X114)</f>
         <v/>
@@ -14781,9 +14551,7 @@
         </is>
       </c>
       <c r="K115" s="15" t="n"/>
-      <c r="L115" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L115" s="15" t="n"/>
       <c r="M115" s="15">
         <f>SUM(H115,R115,T115,V115,X115)</f>
         <v/>
@@ -14842,8 +14610,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H116" s="14" t="n">
-        <v>1</v>
+      <c r="H116" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I116" s="15" t="n"/>
       <c r="J116" s="15" t="inlineStr">
@@ -14851,12 +14619,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K116" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K116" s="15" t="n"/>
+      <c r="L116" s="15" t="n"/>
       <c r="M116" s="15">
         <f>SUM(H116,R116,T116,V116,X116)</f>
         <v/>
@@ -14915,8 +14679,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H117" s="14" t="n">
-        <v>1</v>
+      <c r="H117" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I117" s="15" t="n"/>
       <c r="J117" s="15" t="inlineStr">
@@ -14924,12 +14688,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K117" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L117" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K117" s="15" t="n"/>
+      <c r="L117" s="15" t="n"/>
       <c r="M117" s="15">
         <f>SUM(H117,R117,T117,V117,X117)</f>
         <v/>
@@ -14992,9 +14752,7 @@
         </is>
       </c>
       <c r="K118" s="15" t="n"/>
-      <c r="L118" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L118" s="15" t="n"/>
       <c r="M118" s="15">
         <f>SUM(H118,R118,T118,V118,X118)</f>
         <v/>
@@ -15053,8 +14811,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H119" s="14" t="n">
-        <v>1</v>
+      <c r="H119" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I119" s="15" t="n"/>
       <c r="J119" s="15" t="inlineStr">
@@ -15062,12 +14820,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K119" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L119" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K119" s="15" t="n"/>
+      <c r="L119" s="15" t="n"/>
       <c r="M119" s="15">
         <f>SUM(H119,R119,T119,V119,X119)</f>
         <v/>
@@ -15130,9 +14884,7 @@
         </is>
       </c>
       <c r="K120" s="15" t="n"/>
-      <c r="L120" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L120" s="15" t="n"/>
       <c r="M120" s="15">
         <f>SUM(H120,R120,T120,V120,X120)</f>
         <v/>
@@ -15191,8 +14943,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H121" s="14" t="n">
-        <v>1</v>
+      <c r="H121" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I121" s="15" t="n"/>
       <c r="J121" s="15" t="inlineStr">
@@ -15200,12 +14952,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K121" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L121" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K121" s="15" t="n"/>
+      <c r="L121" s="15" t="n"/>
       <c r="M121" s="15">
         <f>SUM(H121,R121,T121,V121,X121)</f>
         <v/>
@@ -15273,9 +15021,7 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K122" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K122" s="15" t="n"/>
       <c r="L122" s="15" t="n"/>
       <c r="M122" s="15">
         <f>SUM(H122,R122,T122,V122,X122)</f>
@@ -15404,8 +15150,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H124" s="14" t="n">
-        <v>1</v>
+      <c r="H124" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I124" s="15" t="n"/>
       <c r="J124" s="15" t="inlineStr">
@@ -15413,12 +15159,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K124" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K124" s="15" t="n"/>
+      <c r="L124" s="15" t="n"/>
       <c r="M124" s="15">
         <f>SUM(H124,R124,T124,V124,X124)</f>
         <v/>
@@ -15486,9 +15228,7 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K125" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K125" s="15" t="n"/>
       <c r="L125" s="15" t="n"/>
       <c r="M125" s="15">
         <f>SUM(H125,R125,T125,V125,X125)</f>
@@ -15548,8 +15288,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H126" s="14" t="n">
-        <v>1</v>
+      <c r="H126" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I126" s="15" t="n"/>
       <c r="J126" s="15" t="inlineStr">
@@ -15558,9 +15298,7 @@
         </is>
       </c>
       <c r="K126" s="15" t="n"/>
-      <c r="L126" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L126" s="15" t="n"/>
       <c r="M126" s="15">
         <f>SUM(H126,R126,T126,V126,X126)</f>
         <v/>
@@ -15619,8 +15357,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H127" s="14" t="n">
-        <v>1</v>
+      <c r="H127" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I127" s="15" t="n"/>
       <c r="J127" s="15" t="inlineStr">
@@ -15629,9 +15367,7 @@
         </is>
       </c>
       <c r="K127" s="15" t="n"/>
-      <c r="L127" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L127" s="15" t="n"/>
       <c r="M127" s="15">
         <f>SUM(H127,R127,T127,V127,X127)</f>
         <v/>
@@ -15690,8 +15426,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H128" s="14" t="n">
-        <v>1</v>
+      <c r="H128" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I128" s="15" t="n"/>
       <c r="J128" s="15" t="inlineStr">
@@ -15699,12 +15435,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K128" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K128" s="15" t="n"/>
+      <c r="L128" s="15" t="n"/>
       <c r="M128" s="15">
         <f>SUM(H128,R128,T128,V128,X128)</f>
         <v/>
@@ -15763,8 +15495,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H129" s="14" t="n">
-        <v>1</v>
+      <c r="H129" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I129" s="15" t="n"/>
       <c r="J129" s="15" t="inlineStr">
@@ -15772,12 +15504,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K129" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L129" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K129" s="15" t="n"/>
+      <c r="L129" s="15" t="n"/>
       <c r="M129" s="15">
         <f>SUM(H129,R129,T129,V129,X129)</f>
         <v/>
@@ -15836,8 +15564,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H130" s="14" t="n">
-        <v>1</v>
+      <c r="H130" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I130" s="15" t="n"/>
       <c r="J130" s="15" t="inlineStr">
@@ -15845,12 +15573,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K130" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K130" s="15" t="n"/>
+      <c r="L130" s="15" t="n"/>
       <c r="M130" s="15">
         <f>SUM(H130,R130,T130,V130,X130)</f>
         <v/>
@@ -15909,8 +15633,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H131" s="14" t="n">
-        <v>1</v>
+      <c r="H131" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I131" s="15" t="n"/>
       <c r="J131" s="15" t="inlineStr">
@@ -15918,12 +15642,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K131" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K131" s="15" t="n"/>
+      <c r="L131" s="15" t="n"/>
       <c r="M131" s="15">
         <f>SUM(H131,R131,T131,V131,X131)</f>
         <v/>
@@ -15982,8 +15702,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H132" s="14" t="n">
-        <v>1</v>
+      <c r="H132" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I132" s="15" t="n"/>
       <c r="J132" s="15" t="inlineStr">
@@ -15992,9 +15712,7 @@
         </is>
       </c>
       <c r="K132" s="15" t="n"/>
-      <c r="L132" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L132" s="15" t="n"/>
       <c r="M132" s="15">
         <f>SUM(H132,R132,T132,V132,X132)</f>
         <v/>
@@ -16053,8 +15771,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H133" s="14" t="n">
-        <v>1</v>
+      <c r="H133" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I133" s="15" t="n"/>
       <c r="J133" s="15" t="inlineStr">
@@ -16062,12 +15780,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K133" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L133" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K133" s="15" t="n"/>
+      <c r="L133" s="15" t="n"/>
       <c r="M133" s="15">
         <f>SUM(H133,R133,T133,V133,X133)</f>
         <v/>
@@ -16126,8 +15840,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H134" s="14" t="n">
-        <v>1</v>
+      <c r="H134" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I134" s="15" t="n"/>
       <c r="J134" s="15" t="inlineStr">
@@ -16136,9 +15850,7 @@
         </is>
       </c>
       <c r="K134" s="15" t="n"/>
-      <c r="L134" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L134" s="15" t="n"/>
       <c r="M134" s="15">
         <f>SUM(H134,R134,T134,V134,X134)</f>
         <v/>
@@ -16197,8 +15909,8 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H135" s="14" t="n">
-        <v>1</v>
+      <c r="H135" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I135" s="15" t="n"/>
       <c r="J135" s="15" t="inlineStr">
@@ -16207,9 +15919,7 @@
         </is>
       </c>
       <c r="K135" s="15" t="n"/>
-      <c r="L135" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L135" s="15" t="n"/>
       <c r="M135" s="15">
         <f>SUM(H135,R135,T135,V135,X135)</f>
         <v/>
@@ -16268,8 +15978,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H136" s="14" t="n">
-        <v>1</v>
+      <c r="H136" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I136" s="15" t="n"/>
       <c r="J136" s="15" t="inlineStr">
@@ -16277,12 +15987,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K136" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K136" s="15" t="n"/>
+      <c r="L136" s="15" t="n"/>
       <c r="M136" s="15">
         <f>SUM(H136,R136,T136,V136,X136)</f>
         <v/>
@@ -16341,8 +16047,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H137" s="14" t="n">
-        <v>1</v>
+      <c r="H137" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I137" s="15" t="n"/>
       <c r="J137" s="15" t="inlineStr">
@@ -16350,12 +16056,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K137" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K137" s="15" t="n"/>
+      <c r="L137" s="15" t="n"/>
       <c r="M137" s="15">
         <f>SUM(H137,R137,T137,V137,X137)</f>
         <v/>
@@ -16487,8 +16189,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H139" s="14" t="n">
-        <v>1</v>
+      <c r="H139" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I139" s="15" t="n"/>
       <c r="J139" s="15" t="inlineStr">
@@ -16496,12 +16198,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K139" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L139" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K139" s="15" t="n"/>
+      <c r="L139" s="15" t="n"/>
       <c r="M139" s="15">
         <f>SUM(H139,R139,T139,V139,X139)</f>
         <v/>
@@ -16560,8 +16258,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H140" s="14" t="n">
-        <v>1</v>
+      <c r="H140" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I140" s="15" t="n"/>
       <c r="J140" s="15" t="inlineStr">
@@ -16570,9 +16268,7 @@
         </is>
       </c>
       <c r="K140" s="15" t="n"/>
-      <c r="L140" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L140" s="15" t="n"/>
       <c r="M140" s="15">
         <f>SUM(H140,R140,T140,V140,X140)</f>
         <v/>
@@ -16645,9 +16341,7 @@
         </is>
       </c>
       <c r="K141" s="15" t="n"/>
-      <c r="L141" s="14" t="n">
-        <v>12</v>
-      </c>
+      <c r="L141" s="15" t="n"/>
       <c r="M141" s="15">
         <f>SUM(H141,R141,T141,V141,X141)</f>
         <v/>
@@ -16710,8 +16404,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H142" s="14" t="n">
-        <v>1</v>
+      <c r="H142" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I142" s="15" t="n"/>
       <c r="J142" s="15" t="inlineStr">
@@ -16720,9 +16414,7 @@
         </is>
       </c>
       <c r="K142" s="15" t="n"/>
-      <c r="L142" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L142" s="15" t="n"/>
       <c r="M142" s="15">
         <f>SUM(H142,R142,T142,V142,X142)</f>
         <v/>
@@ -16785,8 +16477,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H143" s="14" t="n">
-        <v>1</v>
+      <c r="H143" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I143" s="15" t="n"/>
       <c r="J143" s="15" t="inlineStr">
@@ -16795,9 +16487,7 @@
         </is>
       </c>
       <c r="K143" s="15" t="n"/>
-      <c r="L143" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L143" s="15" t="n"/>
       <c r="M143" s="15">
         <f>SUM(H143,R143,T143,V143,X143)</f>
         <v/>
@@ -16938,9 +16628,7 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K145" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K145" s="15" t="n"/>
       <c r="L145" s="15" t="n"/>
       <c r="M145" s="15">
         <f>SUM(H145,R145,T145,V145,X145)</f>
@@ -17010,9 +16698,7 @@
         </is>
       </c>
       <c r="K146" s="15" t="n"/>
-      <c r="L146" s="14" t="n">
-        <v>11</v>
-      </c>
+      <c r="L146" s="15" t="n"/>
       <c r="M146" s="15">
         <f>SUM(H146,R146,T146,V146,X146)</f>
         <v/>
@@ -17085,9 +16771,7 @@
         </is>
       </c>
       <c r="K147" s="15" t="n"/>
-      <c r="L147" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L147" s="15" t="n"/>
       <c r="M147" s="15">
         <f>SUM(H147,R147,T147,V147,X147)</f>
         <v/>
@@ -17156,9 +16840,7 @@
         </is>
       </c>
       <c r="K148" s="15" t="n"/>
-      <c r="L148" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L148" s="15" t="n"/>
       <c r="M148" s="15">
         <f>SUM(H148,R148,T148,V148,X148)</f>
         <v/>
@@ -17227,9 +16909,7 @@
         </is>
       </c>
       <c r="K149" s="15" t="n"/>
-      <c r="L149" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L149" s="15" t="n"/>
       <c r="M149" s="15">
         <f>SUM(H149,R149,T149,V149,X149)</f>
         <v/>
@@ -17298,9 +16978,7 @@
         </is>
       </c>
       <c r="K150" s="15" t="n"/>
-      <c r="L150" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L150" s="15" t="n"/>
       <c r="M150" s="15">
         <f>SUM(H150,R150,T150,V150,X150)</f>
         <v/>
@@ -17369,9 +17047,7 @@
         </is>
       </c>
       <c r="K151" s="15" t="n"/>
-      <c r="L151" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L151" s="15" t="n"/>
       <c r="M151" s="15">
         <f>SUM(H151,R151,T151,V151,X151)</f>
         <v/>
@@ -17440,9 +17116,7 @@
         </is>
       </c>
       <c r="K152" s="15" t="n"/>
-      <c r="L152" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L152" s="15" t="n"/>
       <c r="M152" s="15">
         <f>SUM(H152,R152,T152,V152,X152)</f>
         <v/>
@@ -17501,8 +17175,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H153" s="14" t="n">
-        <v>1</v>
+      <c r="H153" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I153" s="15" t="n"/>
       <c r="J153" s="15" t="inlineStr">
@@ -17511,9 +17185,7 @@
         </is>
       </c>
       <c r="K153" s="15" t="n"/>
-      <c r="L153" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L153" s="15" t="n"/>
       <c r="M153" s="15">
         <f>SUM(H153,R153,T153,V153,X153)</f>
         <v/>
@@ -17576,8 +17248,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H154" s="14" t="n">
-        <v>1</v>
+      <c r="H154" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I154" s="15" t="n"/>
       <c r="J154" s="15" t="inlineStr">
@@ -17586,9 +17258,7 @@
         </is>
       </c>
       <c r="K154" s="15" t="n"/>
-      <c r="L154" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L154" s="15" t="n"/>
       <c r="M154" s="15">
         <f>SUM(H154,R154,T154,V154,X154)</f>
         <v/>
@@ -17647,8 +17317,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H155" s="14" t="n">
-        <v>1</v>
+      <c r="H155" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I155" s="15" t="n"/>
       <c r="J155" s="15" t="inlineStr">
@@ -17656,12 +17326,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K155" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L155" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="K155" s="15" t="n"/>
+      <c r="L155" s="15" t="n"/>
       <c r="M155" s="15">
         <f>SUM(H155,R155,T155,V155,X155)</f>
         <v/>
@@ -17730,9 +17396,7 @@
         </is>
       </c>
       <c r="K156" s="15" t="n"/>
-      <c r="L156" s="14" t="n">
-        <v>10</v>
-      </c>
+      <c r="L156" s="15" t="n"/>
       <c r="M156" s="15">
         <f>SUM(H156,R156,T156,V156,X156)</f>
         <v/>
@@ -17864,8 +17528,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H158" s="14" t="n">
-        <v>1</v>
+      <c r="H158" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I158" s="15" t="n"/>
       <c r="J158" s="15" t="inlineStr">
@@ -17874,9 +17538,7 @@
         </is>
       </c>
       <c r="K158" s="15" t="n"/>
-      <c r="L158" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L158" s="15" t="n"/>
       <c r="M158" s="15">
         <f>SUM(H158,R158,T158,V158,X158)</f>
         <v/>
@@ -17945,9 +17607,7 @@
         </is>
       </c>
       <c r="K159" s="15" t="n"/>
-      <c r="L159" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L159" s="15" t="n"/>
       <c r="M159" s="15">
         <f>SUM(H159,R159,T159,V159,X159)</f>
         <v/>
@@ -18010,8 +17670,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H160" s="14" t="n">
-        <v>1</v>
+      <c r="H160" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I160" s="15" t="n"/>
       <c r="J160" s="15" t="inlineStr">
@@ -18020,9 +17680,7 @@
         </is>
       </c>
       <c r="K160" s="15" t="n"/>
-      <c r="L160" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L160" s="15" t="n"/>
       <c r="M160" s="15">
         <f>SUM(H160,R160,T160,V160,X160)</f>
         <v/>
@@ -18085,8 +17743,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H161" s="14" t="n">
-        <v>1</v>
+      <c r="H161" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I161" s="15" t="n"/>
       <c r="J161" s="15" t="inlineStr">
@@ -18095,9 +17753,7 @@
         </is>
       </c>
       <c r="K161" s="15" t="n"/>
-      <c r="L161" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L161" s="15" t="n"/>
       <c r="M161" s="15">
         <f>SUM(H161,R161,T161,V161,X161)</f>
         <v/>
@@ -18156,8 +17812,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H162" s="14" t="n">
-        <v>1</v>
+      <c r="H162" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I162" s="15" t="n"/>
       <c r="J162" s="15" t="inlineStr">
@@ -18165,12 +17821,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K162" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L162" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K162" s="15" t="n"/>
+      <c r="L162" s="15" t="n"/>
       <c r="M162" s="15">
         <f>SUM(H162,R162,T162,V162,X162)</f>
         <v/>
@@ -18229,8 +17881,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H163" s="14" t="n">
-        <v>1</v>
+      <c r="H163" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I163" s="15" t="n"/>
       <c r="J163" s="15" t="inlineStr">
@@ -18239,9 +17891,7 @@
         </is>
       </c>
       <c r="K163" s="15" t="n"/>
-      <c r="L163" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L163" s="15" t="n"/>
       <c r="M163" s="15">
         <f>SUM(H163,R163,T163,V163,X163)</f>
         <v/>
@@ -18452,9 +18102,7 @@
         </is>
       </c>
       <c r="K166" s="15" t="n"/>
-      <c r="L166" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L166" s="15" t="n"/>
       <c r="M166" s="15">
         <f>SUM(H166,R166,T166,V166,X166)</f>
         <v/>
@@ -18517,8 +18165,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H167" s="14" t="n">
-        <v>1</v>
+      <c r="H167" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I167" s="15" t="n"/>
       <c r="J167" s="15" t="inlineStr">
@@ -18527,9 +18175,7 @@
         </is>
       </c>
       <c r="K167" s="15" t="n"/>
-      <c r="L167" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L167" s="15" t="n"/>
       <c r="M167" s="15">
         <f>SUM(H167,R167,T167,V167,X167)</f>
         <v/>
@@ -18588,8 +18234,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H168" s="14" t="n">
-        <v>1</v>
+      <c r="H168" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I168" s="15" t="n"/>
       <c r="J168" s="15" t="inlineStr">
@@ -18597,12 +18243,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K168" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L168" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K168" s="15" t="n"/>
+      <c r="L168" s="15" t="n"/>
       <c r="M168" s="15">
         <f>SUM(H168,R168,T168,V168,X168)</f>
         <v/>
@@ -18661,8 +18303,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H169" s="14" t="n">
-        <v>1</v>
+      <c r="H169" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I169" s="15" t="n"/>
       <c r="J169" s="15" t="inlineStr">
@@ -18671,9 +18313,7 @@
         </is>
       </c>
       <c r="K169" s="15" t="n"/>
-      <c r="L169" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L169" s="15" t="n"/>
       <c r="M169" s="15">
         <f>SUM(H169,R169,T169,V169,X169)</f>
         <v/>
@@ -18805,8 +18445,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H171" s="14" t="n">
-        <v>1</v>
+      <c r="H171" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I171" s="15" t="n"/>
       <c r="J171" s="15" t="inlineStr">
@@ -18815,9 +18455,7 @@
         </is>
       </c>
       <c r="K171" s="15" t="n"/>
-      <c r="L171" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L171" s="15" t="n"/>
       <c r="M171" s="15">
         <f>SUM(H171,R171,T171,V171,X171)</f>
         <v/>
@@ -18886,9 +18524,7 @@
         </is>
       </c>
       <c r="K172" s="15" t="n"/>
-      <c r="L172" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L172" s="15" t="n"/>
       <c r="M172" s="15">
         <f>SUM(H172,R172,T172,V172,X172)</f>
         <v/>
@@ -18951,8 +18587,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H173" s="14" t="n">
-        <v>1</v>
+      <c r="H173" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I173" s="15" t="n"/>
       <c r="J173" s="15" t="inlineStr">
@@ -18961,9 +18597,7 @@
         </is>
       </c>
       <c r="K173" s="15" t="n"/>
-      <c r="L173" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L173" s="15" t="n"/>
       <c r="M173" s="15">
         <f>SUM(H173,R173,T173,V173,X173)</f>
         <v/>
@@ -19091,8 +18725,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H175" s="14" t="n">
-        <v>1</v>
+      <c r="H175" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I175" s="15" t="n"/>
       <c r="J175" s="15" t="inlineStr">
@@ -19100,12 +18734,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K175" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L175" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K175" s="15" t="n"/>
+      <c r="L175" s="15" t="n"/>
       <c r="M175" s="15">
         <f>SUM(H175,R175,T175,V175,X175)</f>
         <v/>
@@ -19174,9 +18804,7 @@
         </is>
       </c>
       <c r="K176" s="15" t="n"/>
-      <c r="L176" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L176" s="15" t="n"/>
       <c r="M176" s="15">
         <f>SUM(H176,R176,T176,V176,X176)</f>
         <v/>
@@ -19239,8 +18867,8 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H177" s="14" t="n">
-        <v>1</v>
+      <c r="H177" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I177" s="15" t="n"/>
       <c r="J177" s="15" t="inlineStr">
@@ -19249,9 +18877,7 @@
         </is>
       </c>
       <c r="K177" s="15" t="n"/>
-      <c r="L177" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L177" s="15" t="n"/>
       <c r="M177" s="15">
         <f>SUM(H177,R177,T177,V177,X177)</f>
         <v/>
@@ -19314,8 +18940,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H178" s="14" t="n">
-        <v>1</v>
+      <c r="H178" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I178" s="15" t="n"/>
       <c r="J178" s="15" t="inlineStr">
@@ -19324,9 +18950,7 @@
         </is>
       </c>
       <c r="K178" s="15" t="n"/>
-      <c r="L178" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L178" s="15" t="n"/>
       <c r="M178" s="15">
         <f>SUM(H178,R178,T178,V178,X178)</f>
         <v/>
@@ -19385,8 +19009,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H179" s="14" t="n">
-        <v>1</v>
+      <c r="H179" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I179" s="15" t="n"/>
       <c r="J179" s="15" t="inlineStr">
@@ -19395,9 +19019,7 @@
         </is>
       </c>
       <c r="K179" s="15" t="n"/>
-      <c r="L179" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L179" s="15" t="n"/>
       <c r="M179" s="15">
         <f>SUM(H179,R179,T179,V179,X179)</f>
         <v/>
@@ -19456,8 +19078,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H180" s="14" t="n">
-        <v>1</v>
+      <c r="H180" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I180" s="15" t="n"/>
       <c r="J180" s="15" t="inlineStr">
@@ -19465,12 +19087,8 @@
           <t>Booster Bundle</t>
         </is>
       </c>
-      <c r="K180" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L180" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K180" s="15" t="n"/>
+      <c r="L180" s="15" t="n"/>
       <c r="M180" s="15">
         <f>SUM(H180,R180,T180,V180,X180)</f>
         <v/>
@@ -19539,9 +19157,7 @@
         </is>
       </c>
       <c r="K181" s="15" t="n"/>
-      <c r="L181" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L181" s="15" t="n"/>
       <c r="M181" s="15">
         <f>SUM(H181,R181,T181,V181,X181)</f>
         <v/>
@@ -19610,9 +19226,7 @@
         </is>
       </c>
       <c r="K182" s="15" t="n"/>
-      <c r="L182" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L182" s="15" t="n"/>
       <c r="M182" s="15">
         <f>SUM(H182,R182,T182,V182,X182)</f>
         <v/>
@@ -19681,9 +19295,7 @@
         </is>
       </c>
       <c r="K183" s="15" t="n"/>
-      <c r="L183" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L183" s="15" t="n"/>
       <c r="M183" s="15">
         <f>SUM(H183,R183,T183,V183,X183)</f>
         <v/>
@@ -19742,8 +19354,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H184" s="14" t="n">
-        <v>1</v>
+      <c r="H184" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I184" s="15" t="n"/>
       <c r="J184" s="15" t="inlineStr">
@@ -19752,9 +19364,7 @@
         </is>
       </c>
       <c r="K184" s="15" t="n"/>
-      <c r="L184" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L184" s="15" t="n"/>
       <c r="M184" s="15">
         <f>SUM(H184,R184,T184,V184,X184)</f>
         <v/>
@@ -19823,9 +19433,7 @@
         </is>
       </c>
       <c r="K185" s="15" t="n"/>
-      <c r="L185" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L185" s="15" t="n"/>
       <c r="M185" s="15">
         <f>SUM(H185,R185,T185,V185,X185)</f>
         <v/>
@@ -19884,8 +19492,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H186" s="14" t="n">
-        <v>1</v>
+      <c r="H186" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I186" s="15" t="n"/>
       <c r="J186" s="15" t="inlineStr">
@@ -19894,9 +19502,7 @@
         </is>
       </c>
       <c r="K186" s="15" t="n"/>
-      <c r="L186" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L186" s="15" t="n"/>
       <c r="M186" s="15">
         <f>SUM(H186,R186,T186,V186,X186)</f>
         <v/>
@@ -19955,8 +19561,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H187" s="14" t="n">
-        <v>1</v>
+      <c r="H187" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I187" s="15" t="n"/>
       <c r="J187" s="15" t="inlineStr">
@@ -19965,9 +19571,7 @@
         </is>
       </c>
       <c r="K187" s="15" t="n"/>
-      <c r="L187" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L187" s="15" t="n"/>
       <c r="M187" s="15">
         <f>SUM(H187,R187,T187,V187,X187)</f>
         <v/>
@@ -20036,9 +19640,7 @@
         </is>
       </c>
       <c r="K188" s="15" t="n"/>
-      <c r="L188" s="14" t="n">
-        <v>11</v>
-      </c>
+      <c r="L188" s="15" t="n"/>
       <c r="M188" s="15">
         <f>SUM(H188,R188,T188,V188,X188)</f>
         <v/>
@@ -20111,9 +19713,7 @@
         </is>
       </c>
       <c r="K189" s="15" t="n"/>
-      <c r="L189" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L189" s="15" t="n"/>
       <c r="M189" s="15">
         <f>SUM(H189,R189,T189,V189,X189)</f>
         <v/>
@@ -20172,8 +19772,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H190" s="14" t="n">
-        <v>1</v>
+      <c r="H190" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I190" s="15" t="n"/>
       <c r="J190" s="15" t="inlineStr">
@@ -20182,9 +19782,7 @@
         </is>
       </c>
       <c r="K190" s="15" t="n"/>
-      <c r="L190" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L190" s="15" t="n"/>
       <c r="M190" s="15">
         <f>SUM(H190,R190,T190,V190,X190)</f>
         <v/>
@@ -20243,8 +19841,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H191" s="14" t="n">
-        <v>1</v>
+      <c r="H191" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I191" s="15" t="n"/>
       <c r="J191" s="15" t="inlineStr">
@@ -20253,9 +19851,7 @@
         </is>
       </c>
       <c r="K191" s="15" t="n"/>
-      <c r="L191" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L191" s="15" t="n"/>
       <c r="M191" s="15">
         <f>SUM(H191,R191,T191,V191,X191)</f>
         <v/>
@@ -20324,9 +19920,7 @@
         </is>
       </c>
       <c r="K192" s="15" t="n"/>
-      <c r="L192" s="14" t="n">
-        <v>10</v>
-      </c>
+      <c r="L192" s="15" t="n"/>
       <c r="M192" s="15">
         <f>SUM(H192,R192,T192,V192,X192)</f>
         <v/>
@@ -20399,9 +19993,7 @@
         </is>
       </c>
       <c r="K193" s="15" t="n"/>
-      <c r="L193" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L193" s="15" t="n"/>
       <c r="M193" s="15">
         <f>SUM(H193,R193,T193,V193,X193)</f>
         <v/>
@@ -20470,9 +20062,7 @@
         </is>
       </c>
       <c r="K194" s="15" t="n"/>
-      <c r="L194" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L194" s="15" t="n"/>
       <c r="M194" s="15">
         <f>SUM(H194,R194,T194,V194,X194)</f>
         <v/>
@@ -20541,9 +20131,7 @@
         </is>
       </c>
       <c r="K195" s="15" t="n"/>
-      <c r="L195" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L195" s="15" t="n"/>
       <c r="M195" s="15">
         <f>SUM(H195,R195,T195,V195,X195)</f>
         <v/>
@@ -20685,9 +20273,7 @@
         </is>
       </c>
       <c r="K197" s="15" t="n"/>
-      <c r="L197" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L197" s="15" t="n"/>
       <c r="M197" s="15">
         <f>SUM(H197,R197,T197,V197,X197)</f>
         <v/>
@@ -20760,9 +20346,7 @@
         </is>
       </c>
       <c r="K198" s="15" t="n"/>
-      <c r="L198" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L198" s="15" t="n"/>
       <c r="M198" s="15">
         <f>SUM(H198,R198,T198,V198,X198)</f>
         <v/>
@@ -20828,9 +20412,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K199" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K199" s="15" t="n"/>
       <c r="L199" s="15" t="n"/>
       <c r="M199" s="15">
         <f>SUM(H199,R199,T199,V199,X199)</f>
@@ -20962,9 +20544,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K201" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K201" s="15" t="n"/>
       <c r="L201" s="15" t="n"/>
       <c r="M201" s="15">
         <f>SUM(H201,R201,T201,V201,X201)</f>
@@ -21034,9 +20614,7 @@
         </is>
       </c>
       <c r="K202" s="15" t="n"/>
-      <c r="L202" s="14" t="n">
-        <v>12</v>
-      </c>
+      <c r="L202" s="15" t="n"/>
       <c r="M202" s="15">
         <f>SUM(H202,R202,T202,V202,X202)</f>
         <v/>
@@ -21102,9 +20680,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K203" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K203" s="15" t="n"/>
       <c r="L203" s="15" t="n"/>
       <c r="M203" s="15">
         <f>SUM(H203,R203,T203,V203,X203)</f>
@@ -21174,9 +20750,7 @@
         </is>
       </c>
       <c r="K204" s="15" t="n"/>
-      <c r="L204" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L204" s="15" t="n"/>
       <c r="M204" s="15">
         <f>SUM(H204,R204,T204,V204,X204)</f>
         <v/>
@@ -21242,9 +20816,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K205" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K205" s="15" t="n"/>
       <c r="L205" s="15" t="n"/>
       <c r="M205" s="15">
         <f>SUM(H205,R205,T205,V205,X205)</f>
@@ -21314,9 +20886,7 @@
         </is>
       </c>
       <c r="K206" s="15" t="n"/>
-      <c r="L206" s="14" t="n">
-        <v>11</v>
-      </c>
+      <c r="L206" s="15" t="n"/>
       <c r="M206" s="15">
         <f>SUM(H206,R206,T206,V206,X206)</f>
         <v/>
@@ -21579,9 +21149,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K210" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K210" s="15" t="n"/>
       <c r="L210" s="15" t="n"/>
       <c r="M210" s="15">
         <f>SUM(H210,R210,T210,V210,X210)</f>
@@ -21648,9 +21216,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K211" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K211" s="15" t="n"/>
       <c r="L211" s="15" t="n"/>
       <c r="M211" s="15">
         <f>SUM(H211,R211,T211,V211,X211)</f>
@@ -21779,8 +21345,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H213" s="14" t="n">
-        <v>1</v>
+      <c r="H213" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I213" s="15" t="n"/>
       <c r="J213" s="15" t="inlineStr">
@@ -21789,9 +21355,7 @@
         </is>
       </c>
       <c r="K213" s="15" t="n"/>
-      <c r="L213" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L213" s="15" t="n"/>
       <c r="M213" s="15">
         <f>SUM(H213,R213,T213,V213,X213)</f>
         <v/>
@@ -21860,9 +21424,7 @@
         </is>
       </c>
       <c r="K214" s="15" t="n"/>
-      <c r="L214" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L214" s="15" t="n"/>
       <c r="M214" s="15">
         <f>SUM(H214,R214,T214,V214,X214)</f>
         <v/>
@@ -22000,9 +21562,7 @@
         </is>
       </c>
       <c r="K216" s="15" t="n"/>
-      <c r="L216" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L216" s="15" t="n"/>
       <c r="M216" s="15">
         <f>SUM(H216,R216,T216,V216,X216)</f>
         <v/>
@@ -22136,9 +21696,7 @@
         </is>
       </c>
       <c r="K218" s="15" t="n"/>
-      <c r="L218" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L218" s="15" t="n"/>
       <c r="M218" s="15">
         <f>SUM(H218,R218,T218,V218,X218)</f>
         <v/>
@@ -22207,9 +21765,7 @@
         </is>
       </c>
       <c r="K219" s="15" t="n"/>
-      <c r="L219" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L219" s="15" t="n"/>
       <c r="M219" s="15">
         <f>SUM(H219,R219,T219,V219,X219)</f>
         <v/>
@@ -22268,8 +21824,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H220" s="14" t="n">
-        <v>1</v>
+      <c r="H220" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I220" s="15" t="n"/>
       <c r="J220" s="15" t="inlineStr">
@@ -22278,9 +21834,7 @@
         </is>
       </c>
       <c r="K220" s="15" t="n"/>
-      <c r="L220" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L220" s="15" t="n"/>
       <c r="M220" s="15">
         <f>SUM(H220,R220,T220,V220,X220)</f>
         <v/>
@@ -22342,9 +21896,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K221" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="K221" s="15" t="n"/>
       <c r="L221" s="15" t="n"/>
       <c r="M221" s="15">
         <f>SUM(H221,R221,T221,V221,X221)</f>
@@ -22404,8 +21956,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H222" s="14" t="n">
-        <v>1</v>
+      <c r="H222" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I222" s="15" t="n"/>
       <c r="J222" s="15" t="inlineStr">
@@ -22414,9 +21966,7 @@
         </is>
       </c>
       <c r="K222" s="15" t="n"/>
-      <c r="L222" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L222" s="15" t="n"/>
       <c r="M222" s="15">
         <f>SUM(H222,R222,T222,V222,X222)</f>
         <v/>
@@ -22475,8 +22025,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H223" s="14" t="n">
-        <v>1</v>
+      <c r="H223" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I223" s="15" t="n"/>
       <c r="J223" s="15" t="inlineStr">
@@ -22485,9 +22035,7 @@
         </is>
       </c>
       <c r="K223" s="15" t="n"/>
-      <c r="L223" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L223" s="15" t="n"/>
       <c r="M223" s="15">
         <f>SUM(H223,R223,T223,V223,X223)</f>
         <v/>
@@ -22615,8 +22163,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H225" s="14" t="n">
-        <v>1</v>
+      <c r="H225" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I225" s="15" t="n"/>
       <c r="J225" s="15" t="inlineStr">
@@ -22625,9 +22173,7 @@
         </is>
       </c>
       <c r="K225" s="15" t="n"/>
-      <c r="L225" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L225" s="15" t="n"/>
       <c r="M225" s="15">
         <f>SUM(H225,R225,T225,V225,X225)</f>
         <v/>
@@ -22755,8 +22301,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H227" s="14" t="n">
-        <v>1</v>
+      <c r="H227" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I227" s="15" t="n"/>
       <c r="J227" s="15" t="inlineStr">
@@ -22765,9 +22311,7 @@
         </is>
       </c>
       <c r="K227" s="15" t="n"/>
-      <c r="L227" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L227" s="15" t="n"/>
       <c r="M227" s="15">
         <f>SUM(H227,R227,T227,V227,X227)</f>
         <v/>
@@ -22829,9 +22373,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K228" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="K228" s="15" t="n"/>
       <c r="L228" s="15" t="n"/>
       <c r="M228" s="15">
         <f>SUM(H228,R228,T228,V228,X228)</f>
@@ -22891,8 +22433,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H229" s="14" t="n">
-        <v>1</v>
+      <c r="H229" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I229" s="15" t="n"/>
       <c r="J229" s="15" t="inlineStr">
@@ -22901,9 +22443,7 @@
         </is>
       </c>
       <c r="K229" s="15" t="n"/>
-      <c r="L229" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L229" s="15" t="n"/>
       <c r="M229" s="15">
         <f>SUM(H229,R229,T229,V229,X229)</f>
         <v/>
@@ -22972,9 +22512,7 @@
         </is>
       </c>
       <c r="K230" s="15" t="n"/>
-      <c r="L230" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L230" s="15" t="n"/>
       <c r="M230" s="15">
         <f>SUM(H230,R230,T230,V230,X230)</f>
         <v/>
@@ -23033,8 +22571,8 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H231" s="14" t="n">
-        <v>1</v>
+      <c r="H231" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I231" s="15" t="n"/>
       <c r="J231" s="15" t="inlineStr">
@@ -23043,9 +22581,7 @@
         </is>
       </c>
       <c r="K231" s="15" t="n"/>
-      <c r="L231" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L231" s="15" t="n"/>
       <c r="M231" s="15">
         <f>SUM(H231,R231,T231,V231,X231)</f>
         <v/>
@@ -23114,9 +22650,7 @@
         </is>
       </c>
       <c r="K232" s="15" t="n"/>
-      <c r="L232" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L232" s="15" t="n"/>
       <c r="M232" s="15">
         <f>SUM(H232,R232,T232,V232,X232)</f>
         <v/>
@@ -23244,8 +22778,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H234" s="14" t="n">
-        <v>1</v>
+      <c r="H234" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I234" s="15" t="n"/>
       <c r="J234" s="15" t="inlineStr">
@@ -23254,9 +22788,7 @@
         </is>
       </c>
       <c r="K234" s="15" t="n"/>
-      <c r="L234" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L234" s="15" t="n"/>
       <c r="M234" s="15">
         <f>SUM(H234,R234,T234,V234,X234)</f>
         <v/>
@@ -23315,8 +22847,8 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H235" s="14" t="n">
-        <v>1</v>
+      <c r="H235" s="15" t="n">
+        <v>6</v>
       </c>
       <c r="I235" s="15" t="n"/>
       <c r="J235" s="15" t="inlineStr">
@@ -23325,9 +22857,7 @@
         </is>
       </c>
       <c r="K235" s="15" t="n"/>
-      <c r="L235" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L235" s="15" t="n"/>
       <c r="M235" s="15">
         <f>SUM(H235,R235,T235,V235,X235)</f>
         <v/>
@@ -23597,9 +23127,7 @@
         </is>
       </c>
       <c r="K239" s="15" t="n"/>
-      <c r="L239" s="14" t="n">
-        <v>9</v>
-      </c>
+      <c r="L239" s="15" t="n"/>
       <c r="M239" s="15">
         <f>SUM(H239,R239,T239,V239,X239)</f>
         <v/>
@@ -23806,9 +23334,7 @@
         </is>
       </c>
       <c r="K242" s="15" t="n"/>
-      <c r="L242" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L242" s="15" t="n"/>
       <c r="M242" s="15">
         <f>SUM(H242,R242,T242,V242,X242)</f>
         <v/>
@@ -23877,9 +23403,7 @@
         </is>
       </c>
       <c r="K243" s="15" t="n"/>
-      <c r="L243" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L243" s="15" t="n"/>
       <c r="M243" s="15">
         <f>SUM(H243,R243,T243,V243,X243)</f>
         <v/>
@@ -24078,9 +23602,7 @@
         </is>
       </c>
       <c r="K246" s="15" t="n"/>
-      <c r="L246" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L246" s="15" t="n"/>
       <c r="M246" s="15">
         <f>SUM(H246,R246,T246,V246,X246)</f>
         <v/>
@@ -24287,9 +23809,7 @@
         </is>
       </c>
       <c r="K249" s="15" t="n"/>
-      <c r="L249" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L249" s="15" t="n"/>
       <c r="M249" s="15">
         <f>SUM(H249,R249,T249,V249,X249)</f>
         <v/>
@@ -24355,9 +23875,7 @@
           <t>Tin</t>
         </is>
       </c>
-      <c r="K250" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K250" s="15" t="n"/>
       <c r="L250" s="15" t="n"/>
       <c r="M250" s="15">
         <f>SUM(H250,R250,T250,V250,X250)</f>
@@ -24496,9 +24014,7 @@
         </is>
       </c>
       <c r="K252" s="15" t="n"/>
-      <c r="L252" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L252" s="15" t="n"/>
       <c r="M252" s="15">
         <f>SUM(H252,R252,T252,V252,X252)</f>
         <v/>
@@ -24636,9 +24152,7 @@
         </is>
       </c>
       <c r="K254" s="15" t="n"/>
-      <c r="L254" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L254" s="15" t="n"/>
       <c r="M254" s="15">
         <f>SUM(H254,R254,T254,V254,X254)</f>
         <v/>
@@ -24707,9 +24221,7 @@
         </is>
       </c>
       <c r="K255" s="15" t="n"/>
-      <c r="L255" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L255" s="15" t="n"/>
       <c r="M255" s="15">
         <f>SUM(H255,R255,T255,V255,X255)</f>
         <v/>
@@ -24840,9 +24352,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K257" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="K257" s="15" t="n"/>
       <c r="L257" s="15" t="n"/>
       <c r="M257" s="15">
         <f>SUM(H257,R257,T257,V257,X257)</f>
@@ -24977,9 +24487,7 @@
         </is>
       </c>
       <c r="K259" s="15" t="n"/>
-      <c r="L259" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L259" s="15" t="n"/>
       <c r="M259" s="15">
         <f>SUM(H259,R259,T259,V259,X259)</f>
         <v/>
@@ -25041,9 +24549,7 @@
           <t>Collection Box</t>
         </is>
       </c>
-      <c r="K260" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="K260" s="15" t="n"/>
       <c r="L260" s="15" t="n"/>
       <c r="M260" s="15">
         <f>SUM(H260,R260,T260,V260,X260)</f>
@@ -25113,9 +24619,7 @@
         </is>
       </c>
       <c r="K261" s="15" t="n"/>
-      <c r="L261" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L261" s="15" t="n"/>
       <c r="M261" s="15">
         <f>SUM(H261,R261,T261,V261,X261)</f>
         <v/>
@@ -25253,9 +24757,7 @@
         </is>
       </c>
       <c r="K263" s="15" t="n"/>
-      <c r="L263" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L263" s="15" t="n"/>
       <c r="M263" s="15">
         <f>SUM(H263,R263,T263,V263,X263)</f>
         <v/>
@@ -25314,8 +24816,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H264" s="14" t="n">
-        <v>1</v>
+      <c r="H264" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I264" s="15" t="n"/>
       <c r="J264" s="15" t="inlineStr">
@@ -25324,9 +24826,7 @@
         </is>
       </c>
       <c r="K264" s="15" t="n"/>
-      <c r="L264" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="L264" s="15" t="n"/>
       <c r="M264" s="15">
         <f>SUM(H264,R264,T264,V264,X264)</f>
         <v/>
@@ -25395,9 +24895,7 @@
         </is>
       </c>
       <c r="K265" s="15" t="n"/>
-      <c r="L265" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L265" s="15" t="n"/>
       <c r="M265" s="15">
         <f>SUM(H265,R265,T265,V265,X265)</f>
         <v/>
@@ -25456,8 +24954,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H266" s="14" t="n">
-        <v>1</v>
+      <c r="H266" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I266" s="15" t="n"/>
       <c r="J266" s="15" t="inlineStr">
@@ -25466,9 +24964,7 @@
         </is>
       </c>
       <c r="K266" s="15" t="n"/>
-      <c r="L266" s="14" t="n">
-        <v>7</v>
-      </c>
+      <c r="L266" s="15" t="n"/>
       <c r="M266" s="15">
         <f>SUM(H266,R266,T266,V266,X266)</f>
         <v/>
@@ -25537,9 +25033,7 @@
         </is>
       </c>
       <c r="K267" s="15" t="n"/>
-      <c r="L267" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L267" s="15" t="n"/>
       <c r="M267" s="15">
         <f>SUM(H267,R267,T267,V267,X267)</f>
         <v/>
@@ -25598,8 +25092,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H268" s="14" t="n">
-        <v>1</v>
+      <c r="H268" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I268" s="15" t="n"/>
       <c r="J268" s="15" t="inlineStr">
@@ -25608,9 +25102,7 @@
         </is>
       </c>
       <c r="K268" s="15" t="n"/>
-      <c r="L268" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="L268" s="15" t="n"/>
       <c r="M268" s="15">
         <f>SUM(H268,R268,T268,V268,X268)</f>
         <v/>
@@ -25679,9 +25171,7 @@
         </is>
       </c>
       <c r="K269" s="15" t="n"/>
-      <c r="L269" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L269" s="15" t="n"/>
       <c r="M269" s="15">
         <f>SUM(H269,R269,T269,V269,X269)</f>
         <v/>
@@ -25740,8 +25230,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H270" s="14" t="n">
-        <v>1</v>
+      <c r="H270" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I270" s="15" t="n"/>
       <c r="J270" s="15" t="inlineStr">
@@ -25750,9 +25240,7 @@
         </is>
       </c>
       <c r="K270" s="15" t="n"/>
-      <c r="L270" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L270" s="15" t="n"/>
       <c r="M270" s="15">
         <f>SUM(H270,R270,T270,V270,X270)</f>
         <v/>
@@ -25821,9 +25309,7 @@
         </is>
       </c>
       <c r="K271" s="15" t="n"/>
-      <c r="L271" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L271" s="15" t="n"/>
       <c r="M271" s="15">
         <f>SUM(H271,R271,T271,V271,X271)</f>
         <v/>
@@ -25882,8 +25368,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H272" s="14" t="n">
-        <v>1</v>
+      <c r="H272" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I272" s="15" t="n"/>
       <c r="J272" s="15" t="inlineStr">
@@ -25892,9 +25378,7 @@
         </is>
       </c>
       <c r="K272" s="15" t="n"/>
-      <c r="L272" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L272" s="15" t="n"/>
       <c r="M272" s="15">
         <f>SUM(H272,R272,T272,V272,X272)</f>
         <v/>
@@ -25963,9 +25447,7 @@
         </is>
       </c>
       <c r="K273" s="15" t="n"/>
-      <c r="L273" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L273" s="15" t="n"/>
       <c r="M273" s="15">
         <f>SUM(H273,R273,T273,V273,X273)</f>
         <v/>
@@ -26024,8 +25506,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H274" s="14" t="n">
-        <v>1</v>
+      <c r="H274" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I274" s="15" t="n"/>
       <c r="J274" s="15" t="inlineStr">
@@ -26034,9 +25516,7 @@
         </is>
       </c>
       <c r="K274" s="15" t="n"/>
-      <c r="L274" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L274" s="15" t="n"/>
       <c r="M274" s="15">
         <f>SUM(H274,R274,T274,V274,X274)</f>
         <v/>
@@ -26105,9 +25585,7 @@
         </is>
       </c>
       <c r="K275" s="15" t="n"/>
-      <c r="L275" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L275" s="15" t="n"/>
       <c r="M275" s="15">
         <f>SUM(H275,R275,T275,V275,X275)</f>
         <v/>
@@ -26166,8 +25644,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H276" s="14" t="n">
-        <v>1</v>
+      <c r="H276" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I276" s="15" t="n"/>
       <c r="J276" s="15" t="inlineStr">
@@ -26176,9 +25654,7 @@
         </is>
       </c>
       <c r="K276" s="15" t="n"/>
-      <c r="L276" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L276" s="15" t="n"/>
       <c r="M276" s="15">
         <f>SUM(H276,R276,T276,V276,X276)</f>
         <v/>
@@ -26247,9 +25723,7 @@
         </is>
       </c>
       <c r="K277" s="15" t="n"/>
-      <c r="L277" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L277" s="15" t="n"/>
       <c r="M277" s="15">
         <f>SUM(H277,R277,T277,V277,X277)</f>
         <v/>
@@ -26308,8 +25782,8 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H278" s="14" t="n">
-        <v>1</v>
+      <c r="H278" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="I278" s="15" t="n"/>
       <c r="J278" s="15" t="inlineStr">
@@ -26318,9 +25792,7 @@
         </is>
       </c>
       <c r="K278" s="15" t="n"/>
-      <c r="L278" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L278" s="15" t="n"/>
       <c r="M278" s="15">
         <f>SUM(H278,R278,T278,V278,X278)</f>
         <v/>
@@ -26452,9 +25924,7 @@
         </is>
       </c>
       <c r="K280" s="15" t="n"/>
-      <c r="L280" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L280" s="15" t="n"/>
       <c r="M280" s="15">
         <f>SUM(H280,R280,T280,V280,X280)</f>
         <v/>
@@ -26592,9 +26062,7 @@
         </is>
       </c>
       <c r="K282" s="15" t="n"/>
-      <c r="L282" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L282" s="15" t="n"/>
       <c r="M282" s="15">
         <f>SUM(H282,R282,T282,V282,X282)</f>
         <v/>
@@ -26732,9 +26200,7 @@
         </is>
       </c>
       <c r="K284" s="15" t="n"/>
-      <c r="L284" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L284" s="15" t="n"/>
       <c r="M284" s="15">
         <f>SUM(H284,R284,T284,V284,X284)</f>
         <v/>
@@ -26872,9 +26338,7 @@
         </is>
       </c>
       <c r="K286" s="15" t="n"/>
-      <c r="L286" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L286" s="15" t="n"/>
       <c r="M286" s="15">
         <f>SUM(H286,R286,T286,V286,X286)</f>
         <v/>
@@ -27282,9 +26746,7 @@
         </is>
       </c>
       <c r="K292" s="15" t="n"/>
-      <c r="L292" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="L292" s="15" t="n"/>
       <c r="M292" s="15">
         <f>SUM(H292,R292,T292,V292,X292)</f>
         <v/>
@@ -27422,9 +26884,7 @@
         </is>
       </c>
       <c r="K294" s="15" t="n"/>
-      <c r="L294" s="14" t="n">
-        <v>4</v>
-      </c>
+      <c r="L294" s="15" t="n"/>
       <c r="M294" s="15">
         <f>SUM(H294,R294,T294,V294,X294)</f>
         <v/>
@@ -27562,9 +27022,7 @@
         </is>
       </c>
       <c r="K296" s="15" t="n"/>
-      <c r="L296" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="L296" s="15" t="n"/>
       <c r="M296" s="15">
         <f>SUM(H296,R296,T296,V296,X296)</f>
         <v/>
@@ -27702,9 +27160,7 @@
         </is>
       </c>
       <c r="K298" s="15" t="n"/>
-      <c r="L298" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="L298" s="15" t="n"/>
       <c r="M298" s="15">
         <f>SUM(H298,R298,T298,V298,X298)</f>
         <v/>
@@ -27836,9 +27292,7 @@
         </is>
       </c>
       <c r="K300" s="15" t="n"/>
-      <c r="L300" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="L300" s="15" t="n"/>
       <c r="M300" s="15">
         <f>SUM(H300,R300,T300,V300,X300)</f>
         <v/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -271,7 +271,17 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>How many packs from the set in the Set column, not the whole rip.</t>
+        <t>HOW MANY PACKS OF THE SET IN THE Set COLUMN you opened in THIS video.
+Not how many the box holds. If you opened one pack out of a Chaos
+Rising ETB, this is 1, not 9. The 9 belongs to the box, and Box #
+and Pack # are where you say which box and which pack.
+A whole box opened in one video IS the full number: if you opened an
+entire ETB on camera, put 9 and leave Pack # empty.
+MIXED VIDEOS USE THE EXTRA PAIRS. A UPC holding 6 Journey Together
+and 6 Pitch Black packs is Set=Journey Together Packs=6 and
+Set 2=Pitch Black Packs 2=6. Packs Opened adds them to 12 for you.
+This is what makes 'how many Pitch Black packs have we opened'
+answerable at all: a single total cannot be split back apart.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
@@ -307,7 +317,17 @@
         <t>COMPUTED. Do not type here.
 It adds up Packs, Packs 2, Packs 3, Packs 4 and Packs 5.
 Put the count for each set in that set's own Packs column and this
-adds itself up. Typing over it deletes the sum for that row.</t>
+adds itself up. Typing over it deletes the sum for that row.
+WHAT THE FILLED COLUMNS BUY, once this sheet comes back:
+  Opening Type + Box #  -&gt;  exactly how many ETBs, Booster Bundles
+                            and single packs we have opened, per set
+                            and overall.
+  Set + Packs           -&gt;  exactly how many packs of each set we
+                            have opened, including the ones that came
+                            out of a mixed box.
+  Pack #                -&gt;  which pack of that box the video is, so a
+                            label reads 'Chaos Rising ETB 3 - Pack 3'.
+Nothing on the site prints any of these until you have typed them.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
@@ -6690,15 +6710,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H2" s="15" t="n"/>
       <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J2" s="15" t="n"/>
       <c r="K2" s="15" t="n">
         <v>3</v>
       </c>
@@ -6765,15 +6779,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H3" s="15" t="n"/>
       <c r="I3" s="15" t="n"/>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
       <c r="M3" s="15">
@@ -6834,15 +6842,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H4" s="15" t="n"/>
       <c r="I4" s="15" t="n"/>
-      <c r="J4" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
       <c r="M4" s="15">
@@ -6903,15 +6905,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H5" s="15" t="n"/>
       <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15">
@@ -6976,15 +6972,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15">
@@ -7045,15 +7035,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H7" s="15" t="n"/>
       <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15">
@@ -7118,15 +7102,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H8" s="15" t="n"/>
       <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15">
@@ -7187,15 +7165,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H9" s="15" t="n"/>
       <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15">
@@ -7260,15 +7232,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H10" s="15" t="n"/>
       <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15">
@@ -7329,15 +7295,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H11" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H11" s="15" t="n"/>
       <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15">
@@ -7398,15 +7358,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H12" s="15" t="n"/>
       <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15">
@@ -7471,15 +7425,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H13" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H13" s="15" t="n"/>
       <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15">
@@ -7546,11 +7494,7 @@
       </c>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15">
@@ -7611,15 +7555,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J15" s="15" t="n"/>
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15">
@@ -7684,15 +7622,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H16" s="15" t="n"/>
       <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15">
@@ -7757,15 +7689,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H17" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H17" s="15" t="n"/>
       <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15">
@@ -7832,11 +7758,7 @@
       </c>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J18" s="15" t="n"/>
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15">
@@ -7901,15 +7823,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H19" s="15" t="n"/>
       <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J19" s="15" t="n"/>
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15">
@@ -7974,15 +7890,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H20" s="15" t="n"/>
       <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15">
@@ -8043,15 +7953,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H21" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H21" s="15" t="n"/>
       <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J21" s="15" t="n"/>
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15">
@@ -8118,11 +8022,7 @@
       </c>
       <c r="H22" s="15" t="n"/>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15">
@@ -8189,11 +8089,7 @@
       </c>
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J23" s="15" t="n"/>
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15">
@@ -8260,11 +8156,7 @@
       </c>
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J24" s="15" t="n"/>
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15">
@@ -8325,15 +8217,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J25" s="15" t="n"/>
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15">
@@ -8398,15 +8284,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H26" s="15" t="n"/>
       <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15">
@@ -8467,15 +8347,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H27" s="15" t="n"/>
       <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J27" s="15" t="n"/>
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15">
@@ -8542,11 +8416,7 @@
       </c>
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J28" s="15" t="n"/>
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15">
@@ -8613,11 +8483,7 @@
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J29" s="15" t="n"/>
       <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15">
@@ -8684,11 +8550,7 @@
       </c>
       <c r="H30" s="15" t="n"/>
       <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J30" s="15" t="n"/>
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
       <c r="M30" s="15">
@@ -8749,15 +8611,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H31" s="15" t="n"/>
       <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J31" s="15" t="n"/>
       <c r="K31" s="15" t="n"/>
       <c r="L31" s="15" t="n"/>
       <c r="M31" s="15">
@@ -8822,15 +8678,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H32" s="15" t="n"/>
       <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J32" s="15" t="n"/>
       <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15">
@@ -8891,15 +8741,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H33" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H33" s="15" t="n"/>
       <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J33" s="15" t="n"/>
       <c r="K33" s="15" t="n"/>
       <c r="L33" s="15" t="n"/>
       <c r="M33" s="15">
@@ -8962,11 +8806,7 @@
       </c>
       <c r="H34" s="15" t="n"/>
       <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J34" s="15" t="n"/>
       <c r="K34" s="15" t="n"/>
       <c r="L34" s="15" t="n"/>
       <c r="M34" s="15">
@@ -9037,11 +8877,7 @@
       </c>
       <c r="H35" s="15" t="n"/>
       <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J35" s="15" t="n"/>
       <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15">
@@ -9104,11 +8940,7 @@
       </c>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J36" s="15" t="n"/>
       <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
       <c r="M36" s="15">
@@ -9169,15 +9001,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H37" s="15" t="n"/>
       <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J37" s="15" t="n"/>
       <c r="K37" s="15" t="n"/>
       <c r="L37" s="15" t="n"/>
       <c r="M37" s="15">
@@ -9242,15 +9068,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H38" s="15" t="n"/>
       <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J38" s="15" t="n"/>
       <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15">
@@ -9313,11 +9133,7 @@
       </c>
       <c r="H39" s="15" t="n"/>
       <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J39" s="15" t="n"/>
       <c r="K39" s="15" t="n"/>
       <c r="L39" s="15" t="n"/>
       <c r="M39" s="15">
@@ -9382,15 +9198,9 @@
           <t>Pitch Black</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H40" s="15" t="n"/>
       <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J40" s="15" t="n"/>
       <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15">
@@ -9457,11 +9267,7 @@
       </c>
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J41" s="15" t="n"/>
       <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15">
@@ -9528,11 +9334,7 @@
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J42" s="15" t="n"/>
       <c r="K42" s="15" t="n"/>
       <c r="L42" s="15" t="n"/>
       <c r="M42" s="15">
@@ -9599,11 +9401,7 @@
       </c>
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J43" s="15" t="n"/>
       <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15">
@@ -9670,11 +9468,7 @@
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J44" s="15" t="n"/>
       <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15">
@@ -9737,11 +9531,7 @@
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J45" s="15" t="n"/>
       <c r="K45" s="15" t="n"/>
       <c r="L45" s="15" t="n"/>
       <c r="M45" s="15">
@@ -9808,11 +9598,7 @@
       </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J46" s="15" t="n"/>
       <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15">
@@ -9875,11 +9661,7 @@
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J47" s="15" t="n"/>
       <c r="K47" s="15" t="n"/>
       <c r="L47" s="15" t="n"/>
       <c r="M47" s="15">
@@ -9942,11 +9724,7 @@
       </c>
       <c r="H48" s="15" t="n"/>
       <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="n"/>
       <c r="L48" s="15" t="n"/>
       <c r="M48" s="15">
@@ -10013,11 +9791,7 @@
       </c>
       <c r="H49" s="15" t="n"/>
       <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J49" s="15" t="n"/>
       <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15">
@@ -10076,11 +9850,7 @@
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="15" t="n"/>
       <c r="I50" s="15" t="n"/>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="n"/>
       <c r="L50" s="15" t="n"/>
       <c r="M50" s="15">
@@ -10143,11 +9913,7 @@
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="15" t="n"/>
-      <c r="J51" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J51" s="15" t="n"/>
       <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15">
@@ -10210,11 +9976,7 @@
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="15" t="n"/>
-      <c r="J52" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J52" s="15" t="n"/>
       <c r="K52" s="15" t="n"/>
       <c r="L52" s="15" t="n"/>
       <c r="M52" s="15">
@@ -10285,11 +10047,7 @@
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="15" t="n"/>
-      <c r="J53" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J53" s="15" t="n"/>
       <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15">
@@ -10350,15 +10108,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H54" s="15" t="n"/>
       <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J54" s="15" t="n"/>
       <c r="K54" s="15" t="n"/>
       <c r="L54" s="15" t="n"/>
       <c r="M54" s="15">
@@ -10423,15 +10175,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H55" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H55" s="15" t="n"/>
       <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15">
@@ -10494,11 +10240,7 @@
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="15" t="n"/>
-      <c r="J56" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J56" s="15" t="n"/>
       <c r="K56" s="15" t="n"/>
       <c r="L56" s="15" t="n"/>
       <c r="M56" s="15">
@@ -10563,15 +10305,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H57" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H57" s="15" t="n"/>
       <c r="I57" s="15" t="n"/>
-      <c r="J57" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15">
@@ -10634,11 +10370,7 @@
       </c>
       <c r="H58" s="15" t="n"/>
       <c r="I58" s="15" t="n"/>
-      <c r="J58" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J58" s="15" t="n"/>
       <c r="K58" s="15" t="n"/>
       <c r="L58" s="15" t="n"/>
       <c r="M58" s="15">
@@ -10699,15 +10431,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H59" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H59" s="15" t="n"/>
       <c r="I59" s="15" t="n"/>
-      <c r="J59" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J59" s="15" t="n"/>
       <c r="K59" s="15" t="n"/>
       <c r="L59" s="15" t="n"/>
       <c r="M59" s="15">
@@ -10766,11 +10492,7 @@
       <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="15" t="n"/>
-      <c r="J60" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J60" s="15" t="n"/>
       <c r="K60" s="15" t="n"/>
       <c r="L60" s="15" t="n"/>
       <c r="M60" s="15">
@@ -10831,15 +10553,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H61" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H61" s="15" t="n"/>
       <c r="I61" s="15" t="n"/>
-      <c r="J61" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J61" s="15" t="n"/>
       <c r="K61" s="15" t="n"/>
       <c r="L61" s="15" t="n"/>
       <c r="M61" s="15">
@@ -10902,11 +10618,7 @@
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="15" t="n"/>
-      <c r="J62" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J62" s="15" t="n"/>
       <c r="K62" s="15" t="n"/>
       <c r="L62" s="15" t="n"/>
       <c r="M62" s="15">
@@ -10967,15 +10679,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H63" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H63" s="15" t="n"/>
       <c r="I63" s="15" t="n"/>
-      <c r="J63" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J63" s="15" t="n"/>
       <c r="K63" s="15" t="n"/>
       <c r="L63" s="15" t="n"/>
       <c r="M63" s="15">
@@ -11042,11 +10748,7 @@
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="15" t="n"/>
-      <c r="J64" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J64" s="15" t="n"/>
       <c r="K64" s="15" t="n"/>
       <c r="L64" s="15" t="n"/>
       <c r="M64" s="15">
@@ -11105,11 +10807,7 @@
       <c r="G65" s="15" t="n"/>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="15" t="n"/>
-      <c r="J65" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J65" s="15" t="n"/>
       <c r="K65" s="15" t="n"/>
       <c r="L65" s="15" t="n"/>
       <c r="M65" s="15">
@@ -11172,11 +10870,7 @@
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="15" t="n"/>
-      <c r="J66" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J66" s="15" t="n"/>
       <c r="K66" s="15" t="n"/>
       <c r="L66" s="15" t="n"/>
       <c r="M66" s="15">
@@ -11239,11 +10933,7 @@
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="15" t="n"/>
-      <c r="J67" s="15" t="inlineStr">
-        <is>
-          <t>Poke Ball Tin</t>
-        </is>
-      </c>
+      <c r="J67" s="15" t="n"/>
       <c r="K67" s="15" t="n"/>
       <c r="L67" s="15" t="n"/>
       <c r="M67" s="15">
@@ -11304,15 +10994,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H68" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H68" s="15" t="n"/>
       <c r="I68" s="15" t="n"/>
-      <c r="J68" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J68" s="15" t="n"/>
       <c r="K68" s="15" t="n"/>
       <c r="L68" s="15" t="n"/>
       <c r="M68" s="15">
@@ -11373,15 +11057,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H69" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H69" s="15" t="n"/>
       <c r="I69" s="15" t="n"/>
-      <c r="J69" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J69" s="15" t="n"/>
       <c r="K69" s="15" t="n"/>
       <c r="L69" s="15" t="n"/>
       <c r="M69" s="15">
@@ -11440,11 +11118,7 @@
       <c r="G70" s="15" t="n"/>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="15" t="n"/>
-      <c r="J70" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J70" s="15" t="n"/>
       <c r="K70" s="15" t="n"/>
       <c r="L70" s="15" t="n"/>
       <c r="M70" s="15">
@@ -11505,15 +11179,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H71" s="15" t="n"/>
       <c r="I71" s="15" t="n"/>
-      <c r="J71" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J71" s="15" t="n"/>
       <c r="K71" s="15" t="n"/>
       <c r="L71" s="15" t="n"/>
       <c r="M71" s="15">
@@ -11574,15 +11242,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H72" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H72" s="15" t="n"/>
       <c r="I72" s="15" t="n"/>
-      <c r="J72" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J72" s="15" t="n"/>
       <c r="K72" s="15" t="n"/>
       <c r="L72" s="15" t="n"/>
       <c r="M72" s="15">
@@ -11643,15 +11305,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H73" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H73" s="15" t="n"/>
       <c r="I73" s="15" t="n"/>
-      <c r="J73" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J73" s="15" t="n"/>
       <c r="K73" s="15" t="n"/>
       <c r="L73" s="15" t="n"/>
       <c r="M73" s="15">
@@ -11712,15 +11368,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H74" s="15" t="n"/>
       <c r="I74" s="15" t="n"/>
-      <c r="J74" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n"/>
       <c r="L74" s="15" t="n"/>
       <c r="M74" s="15">
@@ -11781,15 +11431,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H75" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H75" s="15" t="n"/>
       <c r="I75" s="15" t="n"/>
-      <c r="J75" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J75" s="15" t="n"/>
       <c r="K75" s="15" t="n"/>
       <c r="L75" s="15" t="n"/>
       <c r="M75" s="15">
@@ -11850,15 +11494,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H76" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H76" s="15" t="n"/>
       <c r="I76" s="15" t="n"/>
-      <c r="J76" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J76" s="15" t="n"/>
       <c r="K76" s="15" t="n"/>
       <c r="L76" s="15" t="n"/>
       <c r="M76" s="15">
@@ -11919,15 +11557,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H77" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H77" s="15" t="n"/>
       <c r="I77" s="15" t="n"/>
-      <c r="J77" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J77" s="15" t="n"/>
       <c r="K77" s="15" t="n"/>
       <c r="L77" s="15" t="n"/>
       <c r="M77" s="15">
@@ -11988,15 +11620,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H78" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H78" s="15" t="n"/>
       <c r="I78" s="15" t="n"/>
-      <c r="J78" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J78" s="15" t="n"/>
       <c r="K78" s="15" t="n"/>
       <c r="L78" s="15" t="n"/>
       <c r="M78" s="15">
@@ -12057,15 +11683,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H79" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H79" s="15" t="n"/>
       <c r="I79" s="15" t="n"/>
-      <c r="J79" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J79" s="15" t="n"/>
       <c r="K79" s="15" t="n"/>
       <c r="L79" s="15" t="n"/>
       <c r="M79" s="15">
@@ -12126,15 +11746,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H80" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H80" s="15" t="n"/>
       <c r="I80" s="15" t="n"/>
-      <c r="J80" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J80" s="15" t="n"/>
       <c r="K80" s="15" t="n"/>
       <c r="L80" s="15" t="n"/>
       <c r="M80" s="15">
@@ -12195,15 +11809,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H81" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H81" s="15" t="n"/>
       <c r="I81" s="15" t="n"/>
-      <c r="J81" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J81" s="15" t="n"/>
       <c r="K81" s="15" t="n"/>
       <c r="L81" s="15" t="n"/>
       <c r="M81" s="15">
@@ -12266,11 +11874,7 @@
       </c>
       <c r="H82" s="15" t="n"/>
       <c r="I82" s="15" t="n"/>
-      <c r="J82" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J82" s="15" t="n"/>
       <c r="K82" s="15" t="n"/>
       <c r="L82" s="15" t="n"/>
       <c r="M82" s="15">
@@ -12337,11 +11941,7 @@
       </c>
       <c r="H83" s="15" t="n"/>
       <c r="I83" s="15" t="n"/>
-      <c r="J83" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J83" s="15" t="n"/>
       <c r="K83" s="15" t="n"/>
       <c r="L83" s="15" t="n"/>
       <c r="M83" s="15">
@@ -12408,11 +12008,7 @@
       </c>
       <c r="H84" s="15" t="n"/>
       <c r="I84" s="15" t="n"/>
-      <c r="J84" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J84" s="15" t="n"/>
       <c r="K84" s="15" t="n"/>
       <c r="L84" s="15" t="n"/>
       <c r="M84" s="15">
@@ -12479,11 +12075,7 @@
       </c>
       <c r="H85" s="15" t="n"/>
       <c r="I85" s="15" t="n"/>
-      <c r="J85" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J85" s="15" t="n"/>
       <c r="K85" s="15" t="n"/>
       <c r="L85" s="15" t="n"/>
       <c r="M85" s="15">
@@ -12548,15 +12140,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H86" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H86" s="15" t="n"/>
       <c r="I86" s="15" t="n"/>
-      <c r="J86" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J86" s="15" t="n"/>
       <c r="K86" s="15" t="n"/>
       <c r="L86" s="15" t="n"/>
       <c r="M86" s="15">
@@ -12617,15 +12203,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H87" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H87" s="15" t="n"/>
       <c r="I87" s="15" t="n"/>
-      <c r="J87" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J87" s="15" t="n"/>
       <c r="K87" s="15" t="n"/>
       <c r="L87" s="15" t="n"/>
       <c r="M87" s="15">
@@ -12688,11 +12268,7 @@
       </c>
       <c r="H88" s="15" t="n"/>
       <c r="I88" s="15" t="n"/>
-      <c r="J88" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J88" s="15" t="n"/>
       <c r="K88" s="15" t="n"/>
       <c r="L88" s="15" t="n"/>
       <c r="M88" s="15">
@@ -12759,11 +12335,7 @@
       </c>
       <c r="H89" s="15" t="n"/>
       <c r="I89" s="15" t="n"/>
-      <c r="J89" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J89" s="15" t="n"/>
       <c r="K89" s="15" t="n"/>
       <c r="L89" s="15" t="n"/>
       <c r="M89" s="15">
@@ -12830,11 +12402,7 @@
       </c>
       <c r="H90" s="15" t="n"/>
       <c r="I90" s="15" t="n"/>
-      <c r="J90" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J90" s="15" t="n"/>
       <c r="K90" s="15" t="n"/>
       <c r="L90" s="15" t="n"/>
       <c r="M90" s="15">
@@ -12901,11 +12469,7 @@
       </c>
       <c r="H91" s="15" t="n"/>
       <c r="I91" s="15" t="n"/>
-      <c r="J91" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J91" s="15" t="n"/>
       <c r="K91" s="15" t="n"/>
       <c r="L91" s="15" t="n"/>
       <c r="M91" s="15">
@@ -12970,15 +12534,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H92" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H92" s="15" t="n"/>
       <c r="I92" s="15" t="n"/>
-      <c r="J92" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J92" s="15" t="n"/>
       <c r="K92" s="15" t="n"/>
       <c r="L92" s="15" t="n"/>
       <c r="M92" s="15">
@@ -13041,11 +12599,7 @@
       </c>
       <c r="H93" s="15" t="n"/>
       <c r="I93" s="15" t="n"/>
-      <c r="J93" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J93" s="15" t="n"/>
       <c r="K93" s="15" t="n"/>
       <c r="L93" s="15" t="n"/>
       <c r="M93" s="15">
@@ -13106,15 +12660,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H94" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H94" s="15" t="n"/>
       <c r="I94" s="15" t="n"/>
-      <c r="J94" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J94" s="15" t="n"/>
       <c r="K94" s="15" t="n"/>
       <c r="L94" s="15" t="n"/>
       <c r="M94" s="15">
@@ -13177,11 +12725,7 @@
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="15" t="n"/>
-      <c r="J95" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J95" s="15" t="n"/>
       <c r="K95" s="15" t="n"/>
       <c r="L95" s="15" t="n"/>
       <c r="M95" s="15">
@@ -13242,15 +12786,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H96" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H96" s="15" t="n"/>
       <c r="I96" s="15" t="n"/>
-      <c r="J96" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J96" s="15" t="n"/>
       <c r="K96" s="15" t="n"/>
       <c r="L96" s="15" t="n"/>
       <c r="M96" s="15">
@@ -13313,11 +12851,7 @@
       </c>
       <c r="H97" s="15" t="n"/>
       <c r="I97" s="15" t="n"/>
-      <c r="J97" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J97" s="15" t="n"/>
       <c r="K97" s="15" t="n"/>
       <c r="L97" s="15" t="n"/>
       <c r="M97" s="15">
@@ -13378,15 +12912,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H98" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H98" s="15" t="n"/>
       <c r="I98" s="15" t="n"/>
-      <c r="J98" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J98" s="15" t="n"/>
       <c r="K98" s="15" t="n"/>
       <c r="L98" s="15" t="n"/>
       <c r="M98" s="15">
@@ -13449,11 +12977,7 @@
       </c>
       <c r="H99" s="15" t="n"/>
       <c r="I99" s="15" t="n"/>
-      <c r="J99" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J99" s="15" t="n"/>
       <c r="K99" s="15" t="n"/>
       <c r="L99" s="15" t="n"/>
       <c r="M99" s="15">
@@ -13514,15 +13038,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H100" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H100" s="15" t="n"/>
       <c r="I100" s="15" t="n"/>
-      <c r="J100" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J100" s="15" t="n"/>
       <c r="K100" s="15" t="n"/>
       <c r="L100" s="15" t="n"/>
       <c r="M100" s="15">
@@ -13583,15 +13101,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H101" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H101" s="15" t="n"/>
       <c r="I101" s="15" t="n"/>
-      <c r="J101" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J101" s="15" t="n"/>
       <c r="K101" s="15" t="n"/>
       <c r="L101" s="15" t="n"/>
       <c r="M101" s="15">
@@ -13654,11 +13166,7 @@
       </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="15" t="n"/>
-      <c r="J102" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J102" s="15" t="n"/>
       <c r="K102" s="15" t="n"/>
       <c r="L102" s="15" t="n"/>
       <c r="M102" s="15">
@@ -13723,15 +13231,9 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H103" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H103" s="15" t="n"/>
       <c r="I103" s="15" t="n"/>
-      <c r="J103" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J103" s="15" t="n"/>
       <c r="K103" s="15" t="n"/>
       <c r="L103" s="15" t="n"/>
       <c r="M103" s="15">
@@ -13794,11 +13296,7 @@
       </c>
       <c r="H104" s="15" t="n"/>
       <c r="I104" s="15" t="n"/>
-      <c r="J104" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J104" s="15" t="n"/>
       <c r="K104" s="15" t="n"/>
       <c r="L104" s="15" t="n"/>
       <c r="M104" s="15">
@@ -13867,15 +13365,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H105" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H105" s="15" t="n"/>
       <c r="I105" s="15" t="n"/>
-      <c r="J105" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J105" s="15" t="n"/>
       <c r="K105" s="15" t="n"/>
       <c r="L105" s="15" t="n"/>
       <c r="M105" s="15">
@@ -13938,11 +13430,7 @@
       </c>
       <c r="H106" s="15" t="n"/>
       <c r="I106" s="15" t="n"/>
-      <c r="J106" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J106" s="15" t="n"/>
       <c r="K106" s="15" t="n"/>
       <c r="L106" s="15" t="n"/>
       <c r="M106" s="15">
@@ -14005,11 +13493,7 @@
       <c r="G107" s="15" t="n"/>
       <c r="H107" s="15" t="n"/>
       <c r="I107" s="15" t="n"/>
-      <c r="J107" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J107" s="15" t="n"/>
       <c r="K107" s="15" t="n"/>
       <c r="L107" s="15" t="n"/>
       <c r="M107" s="15">
@@ -14070,15 +13554,9 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H108" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H108" s="15" t="n"/>
       <c r="I108" s="15" t="n"/>
-      <c r="J108" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J108" s="15" t="n"/>
       <c r="K108" s="15" t="n"/>
       <c r="L108" s="15" t="n"/>
       <c r="M108" s="15">
@@ -14139,15 +13617,9 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H109" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H109" s="15" t="n"/>
       <c r="I109" s="15" t="n"/>
-      <c r="J109" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J109" s="15" t="n"/>
       <c r="K109" s="15" t="n"/>
       <c r="L109" s="15" t="n"/>
       <c r="M109" s="15">
@@ -14208,15 +13680,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H110" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H110" s="15" t="n"/>
       <c r="I110" s="15" t="n"/>
-      <c r="J110" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J110" s="15" t="n"/>
       <c r="K110" s="15" t="n"/>
       <c r="L110" s="15" t="n"/>
       <c r="M110" s="15">
@@ -14277,15 +13743,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H111" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H111" s="15" t="n"/>
       <c r="I111" s="15" t="n"/>
-      <c r="J111" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J111" s="15" t="n"/>
       <c r="K111" s="15" t="n"/>
       <c r="L111" s="15" t="n"/>
       <c r="M111" s="15">
@@ -14344,11 +13804,7 @@
       <c r="G112" s="15" t="n"/>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="15" t="n"/>
-      <c r="J112" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J112" s="15" t="n"/>
       <c r="K112" s="15" t="n"/>
       <c r="L112" s="15" t="n"/>
       <c r="M112" s="15">
@@ -14407,11 +13863,7 @@
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="15" t="n"/>
       <c r="I113" s="15" t="n"/>
-      <c r="J113" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J113" s="15" t="n"/>
       <c r="K113" s="15" t="n"/>
       <c r="L113" s="15" t="n"/>
       <c r="M113" s="15">
@@ -14472,15 +13924,9 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H114" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H114" s="15" t="n"/>
       <c r="I114" s="15" t="n"/>
-      <c r="J114" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J114" s="15" t="n"/>
       <c r="K114" s="15" t="n"/>
       <c r="L114" s="15" t="n"/>
       <c r="M114" s="15">
@@ -14541,15 +13987,9 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="H115" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H115" s="15" t="n"/>
       <c r="I115" s="15" t="n"/>
-      <c r="J115" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J115" s="15" t="n"/>
       <c r="K115" s="15" t="n"/>
       <c r="L115" s="15" t="n"/>
       <c r="M115" s="15">
@@ -14610,15 +14050,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H116" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H116" s="15" t="n"/>
       <c r="I116" s="15" t="n"/>
-      <c r="J116" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J116" s="15" t="n"/>
       <c r="K116" s="15" t="n"/>
       <c r="L116" s="15" t="n"/>
       <c r="M116" s="15">
@@ -14679,15 +14113,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H117" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H117" s="15" t="n"/>
       <c r="I117" s="15" t="n"/>
-      <c r="J117" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J117" s="15" t="n"/>
       <c r="K117" s="15" t="n"/>
       <c r="L117" s="15" t="n"/>
       <c r="M117" s="15">
@@ -14746,11 +14174,7 @@
       <c r="G118" s="15" t="n"/>
       <c r="H118" s="15" t="n"/>
       <c r="I118" s="15" t="n"/>
-      <c r="J118" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J118" s="15" t="n"/>
       <c r="K118" s="15" t="n"/>
       <c r="L118" s="15" t="n"/>
       <c r="M118" s="15">
@@ -14811,15 +14235,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H119" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H119" s="15" t="n"/>
       <c r="I119" s="15" t="n"/>
-      <c r="J119" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J119" s="15" t="n"/>
       <c r="K119" s="15" t="n"/>
       <c r="L119" s="15" t="n"/>
       <c r="M119" s="15">
@@ -14878,11 +14296,7 @@
       <c r="G120" s="15" t="n"/>
       <c r="H120" s="15" t="n"/>
       <c r="I120" s="15" t="n"/>
-      <c r="J120" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J120" s="15" t="n"/>
       <c r="K120" s="15" t="n"/>
       <c r="L120" s="15" t="n"/>
       <c r="M120" s="15">
@@ -14943,15 +14357,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H121" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H121" s="15" t="n"/>
       <c r="I121" s="15" t="n"/>
-      <c r="J121" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J121" s="15" t="n"/>
       <c r="K121" s="15" t="n"/>
       <c r="L121" s="15" t="n"/>
       <c r="M121" s="15">
@@ -15012,15 +14420,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H122" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H122" s="15" t="n"/>
       <c r="I122" s="15" t="n"/>
-      <c r="J122" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J122" s="15" t="n"/>
       <c r="K122" s="15" t="n"/>
       <c r="L122" s="15" t="n"/>
       <c r="M122" s="15">
@@ -15081,15 +14483,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H123" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H123" s="15" t="n"/>
       <c r="I123" s="15" t="n"/>
-      <c r="J123" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J123" s="15" t="n"/>
       <c r="K123" s="15" t="n"/>
       <c r="L123" s="15" t="n"/>
       <c r="M123" s="15">
@@ -15150,15 +14546,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H124" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H124" s="15" t="n"/>
       <c r="I124" s="15" t="n"/>
-      <c r="J124" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J124" s="15" t="n"/>
       <c r="K124" s="15" t="n"/>
       <c r="L124" s="15" t="n"/>
       <c r="M124" s="15">
@@ -15219,15 +14609,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H125" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H125" s="15" t="n"/>
       <c r="I125" s="15" t="n"/>
-      <c r="J125" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J125" s="15" t="n"/>
       <c r="K125" s="15" t="n"/>
       <c r="L125" s="15" t="n"/>
       <c r="M125" s="15">
@@ -15288,15 +14672,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H126" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H126" s="15" t="n"/>
       <c r="I126" s="15" t="n"/>
-      <c r="J126" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J126" s="15" t="n"/>
       <c r="K126" s="15" t="n"/>
       <c r="L126" s="15" t="n"/>
       <c r="M126" s="15">
@@ -15357,15 +14735,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H127" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H127" s="15" t="n"/>
       <c r="I127" s="15" t="n"/>
-      <c r="J127" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J127" s="15" t="n"/>
       <c r="K127" s="15" t="n"/>
       <c r="L127" s="15" t="n"/>
       <c r="M127" s="15">
@@ -15426,15 +14798,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H128" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H128" s="15" t="n"/>
       <c r="I128" s="15" t="n"/>
-      <c r="J128" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J128" s="15" t="n"/>
       <c r="K128" s="15" t="n"/>
       <c r="L128" s="15" t="n"/>
       <c r="M128" s="15">
@@ -15495,15 +14861,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H129" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H129" s="15" t="n"/>
       <c r="I129" s="15" t="n"/>
-      <c r="J129" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J129" s="15" t="n"/>
       <c r="K129" s="15" t="n"/>
       <c r="L129" s="15" t="n"/>
       <c r="M129" s="15">
@@ -15564,15 +14924,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H130" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H130" s="15" t="n"/>
       <c r="I130" s="15" t="n"/>
-      <c r="J130" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J130" s="15" t="n"/>
       <c r="K130" s="15" t="n"/>
       <c r="L130" s="15" t="n"/>
       <c r="M130" s="15">
@@ -15633,15 +14987,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H131" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H131" s="15" t="n"/>
       <c r="I131" s="15" t="n"/>
-      <c r="J131" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J131" s="15" t="n"/>
       <c r="K131" s="15" t="n"/>
       <c r="L131" s="15" t="n"/>
       <c r="M131" s="15">
@@ -15702,15 +15050,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H132" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H132" s="15" t="n"/>
       <c r="I132" s="15" t="n"/>
-      <c r="J132" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J132" s="15" t="n"/>
       <c r="K132" s="15" t="n"/>
       <c r="L132" s="15" t="n"/>
       <c r="M132" s="15">
@@ -15771,15 +15113,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H133" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H133" s="15" t="n"/>
       <c r="I133" s="15" t="n"/>
-      <c r="J133" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J133" s="15" t="n"/>
       <c r="K133" s="15" t="n"/>
       <c r="L133" s="15" t="n"/>
       <c r="M133" s="15">
@@ -15840,15 +15176,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H134" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H134" s="15" t="n"/>
       <c r="I134" s="15" t="n"/>
-      <c r="J134" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J134" s="15" t="n"/>
       <c r="K134" s="15" t="n"/>
       <c r="L134" s="15" t="n"/>
       <c r="M134" s="15">
@@ -15909,15 +15239,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H135" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H135" s="15" t="n"/>
       <c r="I135" s="15" t="n"/>
-      <c r="J135" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J135" s="15" t="n"/>
       <c r="K135" s="15" t="n"/>
       <c r="L135" s="15" t="n"/>
       <c r="M135" s="15">
@@ -15978,15 +15302,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H136" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H136" s="15" t="n"/>
       <c r="I136" s="15" t="n"/>
-      <c r="J136" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J136" s="15" t="n"/>
       <c r="K136" s="15" t="n"/>
       <c r="L136" s="15" t="n"/>
       <c r="M136" s="15">
@@ -16047,15 +15365,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H137" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H137" s="15" t="n"/>
       <c r="I137" s="15" t="n"/>
-      <c r="J137" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J137" s="15" t="n"/>
       <c r="K137" s="15" t="n"/>
       <c r="L137" s="15" t="n"/>
       <c r="M137" s="15">
@@ -16116,15 +15428,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H138" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H138" s="15" t="n"/>
       <c r="I138" s="15" t="n"/>
-      <c r="J138" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J138" s="15" t="n"/>
       <c r="K138" s="15" t="n"/>
       <c r="L138" s="15" t="n"/>
       <c r="M138" s="15">
@@ -16189,15 +15495,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H139" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H139" s="15" t="n"/>
       <c r="I139" s="15" t="n"/>
-      <c r="J139" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J139" s="15" t="n"/>
       <c r="K139" s="15" t="n"/>
       <c r="L139" s="15" t="n"/>
       <c r="M139" s="15">
@@ -16258,15 +15558,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H140" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H140" s="15" t="n"/>
       <c r="I140" s="15" t="n"/>
-      <c r="J140" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J140" s="15" t="n"/>
       <c r="K140" s="15" t="n"/>
       <c r="L140" s="15" t="n"/>
       <c r="M140" s="15">
@@ -16331,15 +15625,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H141" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H141" s="15" t="n"/>
       <c r="I141" s="15" t="n"/>
-      <c r="J141" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J141" s="15" t="n"/>
       <c r="K141" s="15" t="n"/>
       <c r="L141" s="15" t="n"/>
       <c r="M141" s="15">
@@ -16404,15 +15692,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H142" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H142" s="15" t="n"/>
       <c r="I142" s="15" t="n"/>
-      <c r="J142" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J142" s="15" t="n"/>
       <c r="K142" s="15" t="n"/>
       <c r="L142" s="15" t="n"/>
       <c r="M142" s="15">
@@ -16477,15 +15759,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H143" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H143" s="15" t="n"/>
       <c r="I143" s="15" t="n"/>
-      <c r="J143" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J143" s="15" t="n"/>
       <c r="K143" s="15" t="n"/>
       <c r="L143" s="15" t="n"/>
       <c r="M143" s="15">
@@ -16550,15 +15826,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H144" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H144" s="15" t="n"/>
       <c r="I144" s="15" t="n"/>
-      <c r="J144" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J144" s="15" t="n"/>
       <c r="K144" s="15" t="n"/>
       <c r="L144" s="15" t="n"/>
       <c r="M144" s="15">
@@ -16619,15 +15889,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H145" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H145" s="15" t="n"/>
       <c r="I145" s="15" t="n"/>
-      <c r="J145" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J145" s="15" t="n"/>
       <c r="K145" s="15" t="n"/>
       <c r="L145" s="15" t="n"/>
       <c r="M145" s="15">
@@ -16688,15 +15952,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H146" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H146" s="15" t="n"/>
       <c r="I146" s="15" t="n"/>
-      <c r="J146" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J146" s="15" t="n"/>
       <c r="K146" s="15" t="n"/>
       <c r="L146" s="15" t="n"/>
       <c r="M146" s="15">
@@ -16761,15 +16019,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H147" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H147" s="15" t="n"/>
       <c r="I147" s="15" t="n"/>
-      <c r="J147" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J147" s="15" t="n"/>
       <c r="K147" s="15" t="n"/>
       <c r="L147" s="15" t="n"/>
       <c r="M147" s="15">
@@ -16830,15 +16082,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H148" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H148" s="15" t="n"/>
       <c r="I148" s="15" t="n"/>
-      <c r="J148" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J148" s="15" t="n"/>
       <c r="K148" s="15" t="n"/>
       <c r="L148" s="15" t="n"/>
       <c r="M148" s="15">
@@ -16899,15 +16145,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H149" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H149" s="15" t="n"/>
       <c r="I149" s="15" t="n"/>
-      <c r="J149" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J149" s="15" t="n"/>
       <c r="K149" s="15" t="n"/>
       <c r="L149" s="15" t="n"/>
       <c r="M149" s="15">
@@ -16968,15 +16208,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H150" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H150" s="15" t="n"/>
       <c r="I150" s="15" t="n"/>
-      <c r="J150" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J150" s="15" t="n"/>
       <c r="K150" s="15" t="n"/>
       <c r="L150" s="15" t="n"/>
       <c r="M150" s="15">
@@ -17037,15 +16271,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H151" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H151" s="15" t="n"/>
       <c r="I151" s="15" t="n"/>
-      <c r="J151" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J151" s="15" t="n"/>
       <c r="K151" s="15" t="n"/>
       <c r="L151" s="15" t="n"/>
       <c r="M151" s="15">
@@ -17106,15 +16334,9 @@
           <t>Chaos Rising</t>
         </is>
       </c>
-      <c r="H152" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H152" s="15" t="n"/>
       <c r="I152" s="15" t="n"/>
-      <c r="J152" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J152" s="15" t="n"/>
       <c r="K152" s="15" t="n"/>
       <c r="L152" s="15" t="n"/>
       <c r="M152" s="15">
@@ -17175,15 +16397,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H153" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H153" s="15" t="n"/>
       <c r="I153" s="15" t="n"/>
-      <c r="J153" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J153" s="15" t="n"/>
       <c r="K153" s="15" t="n"/>
       <c r="L153" s="15" t="n"/>
       <c r="M153" s="15">
@@ -17248,15 +16464,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H154" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H154" s="15" t="n"/>
       <c r="I154" s="15" t="n"/>
-      <c r="J154" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J154" s="15" t="n"/>
       <c r="K154" s="15" t="n"/>
       <c r="L154" s="15" t="n"/>
       <c r="M154" s="15">
@@ -17317,15 +16527,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H155" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H155" s="15" t="n"/>
       <c r="I155" s="15" t="n"/>
-      <c r="J155" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J155" s="15" t="n"/>
       <c r="K155" s="15" t="n"/>
       <c r="L155" s="15" t="n"/>
       <c r="M155" s="15">
@@ -17386,15 +16590,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H156" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H156" s="15" t="n"/>
       <c r="I156" s="15" t="n"/>
-      <c r="J156" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J156" s="15" t="n"/>
       <c r="K156" s="15" t="n"/>
       <c r="L156" s="15" t="n"/>
       <c r="M156" s="15">
@@ -17459,15 +16657,9 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H157" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H157" s="15" t="n"/>
       <c r="I157" s="15" t="n"/>
-      <c r="J157" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J157" s="15" t="n"/>
       <c r="K157" s="15" t="n"/>
       <c r="L157" s="15" t="n"/>
       <c r="M157" s="15">
@@ -17528,15 +16720,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H158" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H158" s="15" t="n"/>
       <c r="I158" s="15" t="n"/>
-      <c r="J158" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J158" s="15" t="n"/>
       <c r="K158" s="15" t="n"/>
       <c r="L158" s="15" t="n"/>
       <c r="M158" s="15">
@@ -17597,15 +16783,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H159" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H159" s="15" t="n"/>
       <c r="I159" s="15" t="n"/>
-      <c r="J159" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J159" s="15" t="n"/>
       <c r="K159" s="15" t="n"/>
       <c r="L159" s="15" t="n"/>
       <c r="M159" s="15">
@@ -17670,15 +16850,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H160" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H160" s="15" t="n"/>
       <c r="I160" s="15" t="n"/>
-      <c r="J160" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J160" s="15" t="n"/>
       <c r="K160" s="15" t="n"/>
       <c r="L160" s="15" t="n"/>
       <c r="M160" s="15">
@@ -17743,15 +16917,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H161" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H161" s="15" t="n"/>
       <c r="I161" s="15" t="n"/>
-      <c r="J161" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J161" s="15" t="n"/>
       <c r="K161" s="15" t="n"/>
       <c r="L161" s="15" t="n"/>
       <c r="M161" s="15">
@@ -17812,15 +16980,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H162" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H162" s="15" t="n"/>
       <c r="I162" s="15" t="n"/>
-      <c r="J162" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J162" s="15" t="n"/>
       <c r="K162" s="15" t="n"/>
       <c r="L162" s="15" t="n"/>
       <c r="M162" s="15">
@@ -17881,15 +17043,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H163" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H163" s="15" t="n"/>
       <c r="I163" s="15" t="n"/>
-      <c r="J163" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J163" s="15" t="n"/>
       <c r="K163" s="15" t="n"/>
       <c r="L163" s="15" t="n"/>
       <c r="M163" s="15">
@@ -17954,15 +17110,9 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H164" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H164" s="15" t="n"/>
       <c r="I164" s="15" t="n"/>
-      <c r="J164" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J164" s="15" t="n"/>
       <c r="K164" s="15" t="n"/>
       <c r="L164" s="15" t="n"/>
       <c r="M164" s="15">
@@ -18023,15 +17173,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H165" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H165" s="15" t="n"/>
       <c r="I165" s="15" t="n"/>
-      <c r="J165" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J165" s="15" t="n"/>
       <c r="K165" s="15" t="n"/>
       <c r="L165" s="15" t="n"/>
       <c r="M165" s="15">
@@ -18092,15 +17236,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H166" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H166" s="15" t="n"/>
       <c r="I166" s="15" t="n"/>
-      <c r="J166" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J166" s="15" t="n"/>
       <c r="K166" s="15" t="n"/>
       <c r="L166" s="15" t="n"/>
       <c r="M166" s="15">
@@ -18165,15 +17303,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H167" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H167" s="15" t="n"/>
       <c r="I167" s="15" t="n"/>
-      <c r="J167" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J167" s="15" t="n"/>
       <c r="K167" s="15" t="n"/>
       <c r="L167" s="15" t="n"/>
       <c r="M167" s="15">
@@ -18234,15 +17366,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H168" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H168" s="15" t="n"/>
       <c r="I168" s="15" t="n"/>
-      <c r="J168" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J168" s="15" t="n"/>
       <c r="K168" s="15" t="n"/>
       <c r="L168" s="15" t="n"/>
       <c r="M168" s="15">
@@ -18303,15 +17429,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H169" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H169" s="15" t="n"/>
       <c r="I169" s="15" t="n"/>
-      <c r="J169" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J169" s="15" t="n"/>
       <c r="K169" s="15" t="n"/>
       <c r="L169" s="15" t="n"/>
       <c r="M169" s="15">
@@ -18376,15 +17496,9 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H170" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H170" s="15" t="n"/>
       <c r="I170" s="15" t="n"/>
-      <c r="J170" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J170" s="15" t="n"/>
       <c r="K170" s="15" t="n"/>
       <c r="L170" s="15" t="n"/>
       <c r="M170" s="15">
@@ -18445,15 +17559,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H171" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H171" s="15" t="n"/>
       <c r="I171" s="15" t="n"/>
-      <c r="J171" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J171" s="15" t="n"/>
       <c r="K171" s="15" t="n"/>
       <c r="L171" s="15" t="n"/>
       <c r="M171" s="15">
@@ -18514,15 +17622,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H172" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H172" s="15" t="n"/>
       <c r="I172" s="15" t="n"/>
-      <c r="J172" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J172" s="15" t="n"/>
       <c r="K172" s="15" t="n"/>
       <c r="L172" s="15" t="n"/>
       <c r="M172" s="15">
@@ -18587,15 +17689,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H173" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H173" s="15" t="n"/>
       <c r="I173" s="15" t="n"/>
-      <c r="J173" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J173" s="15" t="n"/>
       <c r="K173" s="15" t="n"/>
       <c r="L173" s="15" t="n"/>
       <c r="M173" s="15">
@@ -18656,15 +17752,9 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="H174" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H174" s="15" t="n"/>
       <c r="I174" s="15" t="n"/>
-      <c r="J174" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J174" s="15" t="n"/>
       <c r="K174" s="15" t="n"/>
       <c r="L174" s="15" t="n"/>
       <c r="M174" s="15">
@@ -18725,15 +17815,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H175" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H175" s="15" t="n"/>
       <c r="I175" s="15" t="n"/>
-      <c r="J175" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J175" s="15" t="n"/>
       <c r="K175" s="15" t="n"/>
       <c r="L175" s="15" t="n"/>
       <c r="M175" s="15">
@@ -18794,15 +17878,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H176" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H176" s="15" t="n"/>
       <c r="I176" s="15" t="n"/>
-      <c r="J176" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J176" s="15" t="n"/>
       <c r="K176" s="15" t="n"/>
       <c r="L176" s="15" t="n"/>
       <c r="M176" s="15">
@@ -18867,15 +17945,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H177" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H177" s="15" t="n"/>
       <c r="I177" s="15" t="n"/>
-      <c r="J177" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J177" s="15" t="n"/>
       <c r="K177" s="15" t="n"/>
       <c r="L177" s="15" t="n"/>
       <c r="M177" s="15">
@@ -18940,15 +18012,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H178" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H178" s="15" t="n"/>
       <c r="I178" s="15" t="n"/>
-      <c r="J178" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J178" s="15" t="n"/>
       <c r="K178" s="15" t="n"/>
       <c r="L178" s="15" t="n"/>
       <c r="M178" s="15">
@@ -19009,15 +18075,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H179" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H179" s="15" t="n"/>
       <c r="I179" s="15" t="n"/>
-      <c r="J179" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J179" s="15" t="n"/>
       <c r="K179" s="15" t="n"/>
       <c r="L179" s="15" t="n"/>
       <c r="M179" s="15">
@@ -19078,15 +18138,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H180" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H180" s="15" t="n"/>
       <c r="I180" s="15" t="n"/>
-      <c r="J180" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J180" s="15" t="n"/>
       <c r="K180" s="15" t="n"/>
       <c r="L180" s="15" t="n"/>
       <c r="M180" s="15">
@@ -19147,15 +18201,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H181" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H181" s="15" t="n"/>
       <c r="I181" s="15" t="n"/>
-      <c r="J181" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J181" s="15" t="n"/>
       <c r="K181" s="15" t="n"/>
       <c r="L181" s="15" t="n"/>
       <c r="M181" s="15">
@@ -19216,15 +18264,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H182" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H182" s="15" t="n"/>
       <c r="I182" s="15" t="n"/>
-      <c r="J182" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J182" s="15" t="n"/>
       <c r="K182" s="15" t="n"/>
       <c r="L182" s="15" t="n"/>
       <c r="M182" s="15">
@@ -19285,15 +18327,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H183" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H183" s="15" t="n"/>
       <c r="I183" s="15" t="n"/>
-      <c r="J183" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J183" s="15" t="n"/>
       <c r="K183" s="15" t="n"/>
       <c r="L183" s="15" t="n"/>
       <c r="M183" s="15">
@@ -19354,15 +18390,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H184" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H184" s="15" t="n"/>
       <c r="I184" s="15" t="n"/>
-      <c r="J184" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J184" s="15" t="n"/>
       <c r="K184" s="15" t="n"/>
       <c r="L184" s="15" t="n"/>
       <c r="M184" s="15">
@@ -19423,15 +18453,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H185" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H185" s="15" t="n"/>
       <c r="I185" s="15" t="n"/>
-      <c r="J185" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J185" s="15" t="n"/>
       <c r="K185" s="15" t="n"/>
       <c r="L185" s="15" t="n"/>
       <c r="M185" s="15">
@@ -19492,15 +18516,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H186" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H186" s="15" t="n"/>
       <c r="I186" s="15" t="n"/>
-      <c r="J186" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J186" s="15" t="n"/>
       <c r="K186" s="15" t="n"/>
       <c r="L186" s="15" t="n"/>
       <c r="M186" s="15">
@@ -19561,15 +18579,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H187" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H187" s="15" t="n"/>
       <c r="I187" s="15" t="n"/>
-      <c r="J187" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J187" s="15" t="n"/>
       <c r="K187" s="15" t="n"/>
       <c r="L187" s="15" t="n"/>
       <c r="M187" s="15">
@@ -19630,15 +18642,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H188" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H188" s="15" t="n"/>
       <c r="I188" s="15" t="n"/>
-      <c r="J188" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J188" s="15" t="n"/>
       <c r="K188" s="15" t="n"/>
       <c r="L188" s="15" t="n"/>
       <c r="M188" s="15">
@@ -19703,15 +18709,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H189" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H189" s="15" t="n"/>
       <c r="I189" s="15" t="n"/>
-      <c r="J189" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J189" s="15" t="n"/>
       <c r="K189" s="15" t="n"/>
       <c r="L189" s="15" t="n"/>
       <c r="M189" s="15">
@@ -19772,15 +18772,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H190" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H190" s="15" t="n"/>
       <c r="I190" s="15" t="n"/>
-      <c r="J190" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J190" s="15" t="n"/>
       <c r="K190" s="15" t="n"/>
       <c r="L190" s="15" t="n"/>
       <c r="M190" s="15">
@@ -19841,15 +18835,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H191" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H191" s="15" t="n"/>
       <c r="I191" s="15" t="n"/>
-      <c r="J191" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J191" s="15" t="n"/>
       <c r="K191" s="15" t="n"/>
       <c r="L191" s="15" t="n"/>
       <c r="M191" s="15">
@@ -19910,15 +18898,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H192" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H192" s="15" t="n"/>
       <c r="I192" s="15" t="n"/>
-      <c r="J192" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J192" s="15" t="n"/>
       <c r="K192" s="15" t="n"/>
       <c r="L192" s="15" t="n"/>
       <c r="M192" s="15">
@@ -19983,15 +18965,9 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H193" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H193" s="15" t="n"/>
       <c r="I193" s="15" t="n"/>
-      <c r="J193" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J193" s="15" t="n"/>
       <c r="K193" s="15" t="n"/>
       <c r="L193" s="15" t="n"/>
       <c r="M193" s="15">
@@ -20052,15 +19028,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H194" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H194" s="15" t="n"/>
       <c r="I194" s="15" t="n"/>
-      <c r="J194" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J194" s="15" t="n"/>
       <c r="K194" s="15" t="n"/>
       <c r="L194" s="15" t="n"/>
       <c r="M194" s="15">
@@ -20121,15 +19091,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H195" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H195" s="15" t="n"/>
       <c r="I195" s="15" t="n"/>
-      <c r="J195" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J195" s="15" t="n"/>
       <c r="K195" s="15" t="n"/>
       <c r="L195" s="15" t="n"/>
       <c r="M195" s="15">
@@ -20190,15 +19154,9 @@
           <t>Obsidian Flames</t>
         </is>
       </c>
-      <c r="H196" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H196" s="15" t="n"/>
       <c r="I196" s="15" t="n"/>
-      <c r="J196" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J196" s="15" t="n"/>
       <c r="K196" s="15" t="n"/>
       <c r="L196" s="15" t="n"/>
       <c r="M196" s="15">
@@ -20263,15 +19221,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H197" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H197" s="15" t="n"/>
       <c r="I197" s="15" t="n"/>
-      <c r="J197" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J197" s="15" t="n"/>
       <c r="K197" s="15" t="n"/>
       <c r="L197" s="15" t="n"/>
       <c r="M197" s="15">
@@ -20336,15 +19288,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H198" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H198" s="15" t="n"/>
       <c r="I198" s="15" t="n"/>
-      <c r="J198" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J198" s="15" t="n"/>
       <c r="K198" s="15" t="n"/>
       <c r="L198" s="15" t="n"/>
       <c r="M198" s="15">
@@ -20407,11 +19353,7 @@
       </c>
       <c r="H199" s="15" t="n"/>
       <c r="I199" s="15" t="n"/>
-      <c r="J199" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J199" s="15" t="n"/>
       <c r="K199" s="15" t="n"/>
       <c r="L199" s="15" t="n"/>
       <c r="M199" s="15">
@@ -20472,15 +19414,9 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H200" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H200" s="15" t="n"/>
       <c r="I200" s="15" t="n"/>
-      <c r="J200" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J200" s="15" t="n"/>
       <c r="K200" s="15" t="n"/>
       <c r="L200" s="15" t="n"/>
       <c r="M200" s="15">
@@ -20539,11 +19475,7 @@
       <c r="G201" s="15" t="n"/>
       <c r="H201" s="15" t="n"/>
       <c r="I201" s="15" t="n"/>
-      <c r="J201" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J201" s="15" t="n"/>
       <c r="K201" s="15" t="n"/>
       <c r="L201" s="15" t="n"/>
       <c r="M201" s="15">
@@ -20604,15 +19536,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H202" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H202" s="15" t="n"/>
       <c r="I202" s="15" t="n"/>
-      <c r="J202" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J202" s="15" t="n"/>
       <c r="K202" s="15" t="n"/>
       <c r="L202" s="15" t="n"/>
       <c r="M202" s="15">
@@ -20675,11 +19601,7 @@
       </c>
       <c r="H203" s="15" t="n"/>
       <c r="I203" s="15" t="n"/>
-      <c r="J203" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J203" s="15" t="n"/>
       <c r="K203" s="15" t="n"/>
       <c r="L203" s="15" t="n"/>
       <c r="M203" s="15">
@@ -20740,15 +19662,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H204" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H204" s="15" t="n"/>
       <c r="I204" s="15" t="n"/>
-      <c r="J204" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J204" s="15" t="n"/>
       <c r="K204" s="15" t="n"/>
       <c r="L204" s="15" t="n"/>
       <c r="M204" s="15">
@@ -20811,11 +19727,7 @@
       </c>
       <c r="H205" s="15" t="n"/>
       <c r="I205" s="15" t="n"/>
-      <c r="J205" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J205" s="15" t="n"/>
       <c r="K205" s="15" t="n"/>
       <c r="L205" s="15" t="n"/>
       <c r="M205" s="15">
@@ -20876,15 +19788,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H206" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H206" s="15" t="n"/>
       <c r="I206" s="15" t="n"/>
-      <c r="J206" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J206" s="15" t="n"/>
       <c r="K206" s="15" t="n"/>
       <c r="L206" s="15" t="n"/>
       <c r="M206" s="15">
@@ -20943,11 +19849,7 @@
       <c r="G207" s="15" t="n"/>
       <c r="H207" s="15" t="n"/>
       <c r="I207" s="15" t="n"/>
-      <c r="J207" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J207" s="15" t="n"/>
       <c r="K207" s="15" t="n"/>
       <c r="L207" s="15" t="n"/>
       <c r="M207" s="15">
@@ -21008,15 +19910,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H208" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H208" s="15" t="n"/>
       <c r="I208" s="15" t="n"/>
-      <c r="J208" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J208" s="15" t="n"/>
       <c r="K208" s="15" t="n"/>
       <c r="L208" s="15" t="n"/>
       <c r="M208" s="15">
@@ -21077,15 +19973,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H209" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H209" s="15" t="n"/>
       <c r="I209" s="15" t="n"/>
-      <c r="J209" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J209" s="15" t="n"/>
       <c r="K209" s="15" t="n"/>
       <c r="L209" s="15" t="n"/>
       <c r="M209" s="15">
@@ -21144,11 +20034,7 @@
       <c r="G210" s="15" t="n"/>
       <c r="H210" s="15" t="n"/>
       <c r="I210" s="15" t="n"/>
-      <c r="J210" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J210" s="15" t="n"/>
       <c r="K210" s="15" t="n"/>
       <c r="L210" s="15" t="n"/>
       <c r="M210" s="15">
@@ -21211,11 +20097,7 @@
       </c>
       <c r="H211" s="15" t="n"/>
       <c r="I211" s="15" t="n"/>
-      <c r="J211" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J211" s="15" t="n"/>
       <c r="K211" s="15" t="n"/>
       <c r="L211" s="15" t="n"/>
       <c r="M211" s="15">
@@ -21276,15 +20158,9 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="H212" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H212" s="15" t="n"/>
       <c r="I212" s="15" t="n"/>
-      <c r="J212" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J212" s="15" t="n"/>
       <c r="K212" s="15" t="n"/>
       <c r="L212" s="15" t="n"/>
       <c r="M212" s="15">
@@ -21345,15 +20221,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H213" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H213" s="15" t="n"/>
       <c r="I213" s="15" t="n"/>
-      <c r="J213" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J213" s="15" t="n"/>
       <c r="K213" s="15" t="n"/>
       <c r="L213" s="15" t="n"/>
       <c r="M213" s="15">
@@ -21414,15 +20284,9 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H214" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H214" s="15" t="n"/>
       <c r="I214" s="15" t="n"/>
-      <c r="J214" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J214" s="15" t="n"/>
       <c r="K214" s="15" t="n"/>
       <c r="L214" s="15" t="n"/>
       <c r="M214" s="15">
@@ -21483,15 +20347,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H215" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H215" s="15" t="n"/>
       <c r="I215" s="15" t="n"/>
-      <c r="J215" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J215" s="15" t="n"/>
       <c r="K215" s="15" t="n"/>
       <c r="L215" s="15" t="n"/>
       <c r="M215" s="15">
@@ -21552,15 +20410,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H216" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H216" s="15" t="n"/>
       <c r="I216" s="15" t="n"/>
-      <c r="J216" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J216" s="15" t="n"/>
       <c r="K216" s="15" t="n"/>
       <c r="L216" s="15" t="n"/>
       <c r="M216" s="15">
@@ -21617,15 +20469,9 @@
         <v/>
       </c>
       <c r="G217" s="15" t="n"/>
-      <c r="H217" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H217" s="15" t="n"/>
       <c r="I217" s="15" t="n"/>
-      <c r="J217" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J217" s="15" t="n"/>
       <c r="K217" s="15" t="n"/>
       <c r="L217" s="15" t="n"/>
       <c r="M217" s="15">
@@ -21686,15 +20532,9 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H218" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H218" s="15" t="n"/>
       <c r="I218" s="15" t="n"/>
-      <c r="J218" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J218" s="15" t="n"/>
       <c r="K218" s="15" t="n"/>
       <c r="L218" s="15" t="n"/>
       <c r="M218" s="15">
@@ -21755,15 +20595,9 @@
           <t>Crown Zenith</t>
         </is>
       </c>
-      <c r="H219" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H219" s="15" t="n"/>
       <c r="I219" s="15" t="n"/>
-      <c r="J219" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J219" s="15" t="n"/>
       <c r="K219" s="15" t="n"/>
       <c r="L219" s="15" t="n"/>
       <c r="M219" s="15">
@@ -21824,15 +20658,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H220" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H220" s="15" t="n"/>
       <c r="I220" s="15" t="n"/>
-      <c r="J220" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J220" s="15" t="n"/>
       <c r="K220" s="15" t="n"/>
       <c r="L220" s="15" t="n"/>
       <c r="M220" s="15">
@@ -21891,11 +20719,7 @@
       <c r="G221" s="15" t="n"/>
       <c r="H221" s="15" t="n"/>
       <c r="I221" s="15" t="n"/>
-      <c r="J221" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J221" s="15" t="n"/>
       <c r="K221" s="15" t="n"/>
       <c r="L221" s="15" t="n"/>
       <c r="M221" s="15">
@@ -21956,15 +20780,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H222" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H222" s="15" t="n"/>
       <c r="I222" s="15" t="n"/>
-      <c r="J222" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J222" s="15" t="n"/>
       <c r="K222" s="15" t="n"/>
       <c r="L222" s="15" t="n"/>
       <c r="M222" s="15">
@@ -22025,15 +20843,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H223" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H223" s="15" t="n"/>
       <c r="I223" s="15" t="n"/>
-      <c r="J223" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J223" s="15" t="n"/>
       <c r="K223" s="15" t="n"/>
       <c r="L223" s="15" t="n"/>
       <c r="M223" s="15">
@@ -22094,15 +20906,9 @@
           <t>Mega Brave (JP)</t>
         </is>
       </c>
-      <c r="H224" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H224" s="15" t="n"/>
       <c r="I224" s="15" t="n"/>
-      <c r="J224" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J224" s="15" t="n"/>
       <c r="K224" s="15" t="n"/>
       <c r="L224" s="15" t="n"/>
       <c r="M224" s="15">
@@ -22163,15 +20969,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H225" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H225" s="15" t="n"/>
       <c r="I225" s="15" t="n"/>
-      <c r="J225" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J225" s="15" t="n"/>
       <c r="K225" s="15" t="n"/>
       <c r="L225" s="15" t="n"/>
       <c r="M225" s="15">
@@ -22232,15 +21032,9 @@
           <t>Chilling Reign</t>
         </is>
       </c>
-      <c r="H226" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H226" s="15" t="n"/>
       <c r="I226" s="15" t="n"/>
-      <c r="J226" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J226" s="15" t="n"/>
       <c r="K226" s="15" t="n"/>
       <c r="L226" s="15" t="n"/>
       <c r="M226" s="15">
@@ -22301,15 +21095,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H227" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H227" s="15" t="n"/>
       <c r="I227" s="15" t="n"/>
-      <c r="J227" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J227" s="15" t="n"/>
       <c r="K227" s="15" t="n"/>
       <c r="L227" s="15" t="n"/>
       <c r="M227" s="15">
@@ -22368,11 +21156,7 @@
       <c r="G228" s="15" t="n"/>
       <c r="H228" s="15" t="n"/>
       <c r="I228" s="15" t="n"/>
-      <c r="J228" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J228" s="15" t="n"/>
       <c r="K228" s="15" t="n"/>
       <c r="L228" s="15" t="n"/>
       <c r="M228" s="15">
@@ -22433,15 +21217,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H229" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H229" s="15" t="n"/>
       <c r="I229" s="15" t="n"/>
-      <c r="J229" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J229" s="15" t="n"/>
       <c r="K229" s="15" t="n"/>
       <c r="L229" s="15" t="n"/>
       <c r="M229" s="15">
@@ -22502,15 +21280,9 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H230" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H230" s="15" t="n"/>
       <c r="I230" s="15" t="n"/>
-      <c r="J230" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J230" s="15" t="n"/>
       <c r="K230" s="15" t="n"/>
       <c r="L230" s="15" t="n"/>
       <c r="M230" s="15">
@@ -22571,15 +21343,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H231" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H231" s="15" t="n"/>
       <c r="I231" s="15" t="n"/>
-      <c r="J231" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J231" s="15" t="n"/>
       <c r="K231" s="15" t="n"/>
       <c r="L231" s="15" t="n"/>
       <c r="M231" s="15">
@@ -22640,15 +21406,9 @@
           <t>Rebel Clash</t>
         </is>
       </c>
-      <c r="H232" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H232" s="15" t="n"/>
       <c r="I232" s="15" t="n"/>
-      <c r="J232" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J232" s="15" t="n"/>
       <c r="K232" s="15" t="n"/>
       <c r="L232" s="15" t="n"/>
       <c r="M232" s="15">
@@ -22709,15 +21469,9 @@
           <t>Rebel Clash</t>
         </is>
       </c>
-      <c r="H233" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H233" s="15" t="n"/>
       <c r="I233" s="15" t="n"/>
-      <c r="J233" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J233" s="15" t="n"/>
       <c r="K233" s="15" t="n"/>
       <c r="L233" s="15" t="n"/>
       <c r="M233" s="15">
@@ -22778,15 +21532,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H234" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H234" s="15" t="n"/>
       <c r="I234" s="15" t="n"/>
-      <c r="J234" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J234" s="15" t="n"/>
       <c r="K234" s="15" t="n"/>
       <c r="L234" s="15" t="n"/>
       <c r="M234" s="15">
@@ -22847,15 +21595,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H235" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H235" s="15" t="n"/>
       <c r="I235" s="15" t="n"/>
-      <c r="J235" s="15" t="inlineStr">
-        <is>
-          <t>Booster Bundle</t>
-        </is>
-      </c>
+      <c r="J235" s="15" t="n"/>
       <c r="K235" s="15" t="n"/>
       <c r="L235" s="15" t="n"/>
       <c r="M235" s="15">
@@ -22916,15 +21658,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H236" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H236" s="15" t="n"/>
       <c r="I236" s="15" t="n"/>
-      <c r="J236" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J236" s="15" t="n"/>
       <c r="K236" s="15" t="n"/>
       <c r="L236" s="15" t="n"/>
       <c r="M236" s="15">
@@ -22983,11 +21719,7 @@
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="15" t="n"/>
       <c r="I237" s="15" t="n"/>
-      <c r="J237" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J237" s="15" t="n"/>
       <c r="K237" s="15" t="n"/>
       <c r="L237" s="15" t="n"/>
       <c r="M237" s="15">
@@ -23048,15 +21780,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H238" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H238" s="15" t="n"/>
       <c r="I238" s="15" t="n"/>
-      <c r="J238" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J238" s="15" t="n"/>
       <c r="K238" s="15" t="n"/>
       <c r="L238" s="15" t="n"/>
       <c r="M238" s="15">
@@ -23117,15 +21843,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H239" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H239" s="15" t="n"/>
       <c r="I239" s="15" t="n"/>
-      <c r="J239" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J239" s="15" t="n"/>
       <c r="K239" s="15" t="n"/>
       <c r="L239" s="15" t="n"/>
       <c r="M239" s="15">
@@ -23186,15 +21906,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H240" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H240" s="15" t="n"/>
       <c r="I240" s="15" t="n"/>
-      <c r="J240" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J240" s="15" t="n"/>
       <c r="K240" s="15" t="n"/>
       <c r="L240" s="15" t="n"/>
       <c r="M240" s="15">
@@ -23255,15 +21969,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H241" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H241" s="15" t="n"/>
       <c r="I241" s="15" t="n"/>
-      <c r="J241" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J241" s="15" t="n"/>
       <c r="K241" s="15" t="n"/>
       <c r="L241" s="15" t="n"/>
       <c r="M241" s="15">
@@ -23324,15 +22032,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H242" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H242" s="15" t="n"/>
       <c r="I242" s="15" t="n"/>
-      <c r="J242" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J242" s="15" t="n"/>
       <c r="K242" s="15" t="n"/>
       <c r="L242" s="15" t="n"/>
       <c r="M242" s="15">
@@ -23393,15 +22095,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H243" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H243" s="15" t="n"/>
       <c r="I243" s="15" t="n"/>
-      <c r="J243" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J243" s="15" t="n"/>
       <c r="K243" s="15" t="n"/>
       <c r="L243" s="15" t="n"/>
       <c r="M243" s="15">
@@ -23460,11 +22156,7 @@
       <c r="G244" s="15" t="n"/>
       <c r="H244" s="15" t="n"/>
       <c r="I244" s="15" t="n"/>
-      <c r="J244" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J244" s="15" t="n"/>
       <c r="K244" s="15" t="n"/>
       <c r="L244" s="15" t="n"/>
       <c r="M244" s="15">
@@ -23523,11 +22215,7 @@
       <c r="G245" s="15" t="n"/>
       <c r="H245" s="15" t="n"/>
       <c r="I245" s="15" t="n"/>
-      <c r="J245" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J245" s="15" t="n"/>
       <c r="K245" s="15" t="n"/>
       <c r="L245" s="15" t="n"/>
       <c r="M245" s="15">
@@ -23592,15 +22280,9 @@
           <t>Celebrations</t>
         </is>
       </c>
-      <c r="H246" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H246" s="15" t="n"/>
       <c r="I246" s="15" t="n"/>
-      <c r="J246" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J246" s="15" t="n"/>
       <c r="K246" s="15" t="n"/>
       <c r="L246" s="15" t="n"/>
       <c r="M246" s="15">
@@ -23661,15 +22343,9 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="H247" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H247" s="15" t="n"/>
       <c r="I247" s="15" t="n"/>
-      <c r="J247" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J247" s="15" t="n"/>
       <c r="K247" s="15" t="n"/>
       <c r="L247" s="15" t="n"/>
       <c r="M247" s="15">
@@ -23730,15 +22406,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H248" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H248" s="15" t="n"/>
       <c r="I248" s="15" t="n"/>
-      <c r="J248" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J248" s="15" t="n"/>
       <c r="K248" s="15" t="n"/>
       <c r="L248" s="15" t="n"/>
       <c r="M248" s="15">
@@ -23799,15 +22469,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H249" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H249" s="15" t="n"/>
       <c r="I249" s="15" t="n"/>
-      <c r="J249" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J249" s="15" t="n"/>
       <c r="K249" s="15" t="n"/>
       <c r="L249" s="15" t="n"/>
       <c r="M249" s="15">
@@ -23870,11 +22534,7 @@
       </c>
       <c r="H250" s="15" t="n"/>
       <c r="I250" s="15" t="n"/>
-      <c r="J250" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J250" s="15" t="n"/>
       <c r="K250" s="15" t="n"/>
       <c r="L250" s="15" t="n"/>
       <c r="M250" s="15">
@@ -23935,15 +22595,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H251" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H251" s="15" t="n"/>
       <c r="I251" s="15" t="n"/>
-      <c r="J251" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J251" s="15" t="n"/>
       <c r="K251" s="15" t="n"/>
       <c r="L251" s="15" t="n"/>
       <c r="M251" s="15">
@@ -24004,15 +22658,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H252" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H252" s="15" t="n"/>
       <c r="I252" s="15" t="n"/>
-      <c r="J252" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J252" s="15" t="n"/>
       <c r="K252" s="15" t="n"/>
       <c r="L252" s="15" t="n"/>
       <c r="M252" s="15">
@@ -24073,15 +22721,9 @@
           <t>Ninja Spinner (JP)</t>
         </is>
       </c>
-      <c r="H253" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H253" s="15" t="n"/>
       <c r="I253" s="15" t="n"/>
-      <c r="J253" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J253" s="15" t="n"/>
       <c r="K253" s="15" t="n"/>
       <c r="L253" s="15" t="n"/>
       <c r="M253" s="15">
@@ -24142,15 +22784,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H254" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H254" s="15" t="n"/>
       <c r="I254" s="15" t="n"/>
-      <c r="J254" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J254" s="15" t="n"/>
       <c r="K254" s="15" t="n"/>
       <c r="L254" s="15" t="n"/>
       <c r="M254" s="15">
@@ -24211,15 +22847,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H255" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H255" s="15" t="n"/>
       <c r="I255" s="15" t="n"/>
-      <c r="J255" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J255" s="15" t="n"/>
       <c r="K255" s="15" t="n"/>
       <c r="L255" s="15" t="n"/>
       <c r="M255" s="15">
@@ -24280,15 +22910,9 @@
           <t>Clay Burst (KR)</t>
         </is>
       </c>
-      <c r="H256" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H256" s="15" t="n"/>
       <c r="I256" s="15" t="n"/>
-      <c r="J256" s="15" t="inlineStr">
-        <is>
-          <t>Korean Booster Pack</t>
-        </is>
-      </c>
+      <c r="J256" s="15" t="n"/>
       <c r="K256" s="15" t="n"/>
       <c r="L256" s="15" t="n"/>
       <c r="M256" s="15">
@@ -24347,11 +22971,7 @@
       <c r="G257" s="15" t="n"/>
       <c r="H257" s="15" t="n"/>
       <c r="I257" s="15" t="n"/>
-      <c r="J257" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J257" s="15" t="n"/>
       <c r="K257" s="15" t="n"/>
       <c r="L257" s="15" t="n"/>
       <c r="M257" s="15">
@@ -24408,15 +23028,9 @@
         <v/>
       </c>
       <c r="G258" s="15" t="n"/>
-      <c r="H258" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H258" s="15" t="n"/>
       <c r="I258" s="15" t="n"/>
-      <c r="J258" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J258" s="15" t="n"/>
       <c r="K258" s="15" t="n"/>
       <c r="L258" s="15" t="n"/>
       <c r="M258" s="15">
@@ -24477,15 +23091,9 @@
           <t>Perfect Order</t>
         </is>
       </c>
-      <c r="H259" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H259" s="15" t="n"/>
       <c r="I259" s="15" t="n"/>
-      <c r="J259" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J259" s="15" t="n"/>
       <c r="K259" s="15" t="n"/>
       <c r="L259" s="15" t="n"/>
       <c r="M259" s="15">
@@ -24544,11 +23152,7 @@
       <c r="G260" s="15" t="n"/>
       <c r="H260" s="15" t="n"/>
       <c r="I260" s="15" t="n"/>
-      <c r="J260" s="15" t="inlineStr">
-        <is>
-          <t>Collection Box</t>
-        </is>
-      </c>
+      <c r="J260" s="15" t="n"/>
       <c r="K260" s="15" t="n"/>
       <c r="L260" s="15" t="n"/>
       <c r="M260" s="15">
@@ -24609,15 +23213,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H261" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H261" s="15" t="n"/>
       <c r="I261" s="15" t="n"/>
-      <c r="J261" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J261" s="15" t="n"/>
       <c r="K261" s="15" t="n"/>
       <c r="L261" s="15" t="n"/>
       <c r="M261" s="15">
@@ -24678,15 +23276,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H262" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H262" s="15" t="n"/>
       <c r="I262" s="15" t="n"/>
-      <c r="J262" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J262" s="15" t="n"/>
       <c r="K262" s="15" t="n"/>
       <c r="L262" s="15" t="n"/>
       <c r="M262" s="15">
@@ -24747,15 +23339,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H263" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H263" s="15" t="n"/>
       <c r="I263" s="15" t="n"/>
-      <c r="J263" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J263" s="15" t="n"/>
       <c r="K263" s="15" t="n"/>
       <c r="L263" s="15" t="n"/>
       <c r="M263" s="15">
@@ -24816,15 +23402,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H264" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H264" s="15" t="n"/>
       <c r="I264" s="15" t="n"/>
-      <c r="J264" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J264" s="15" t="n"/>
       <c r="K264" s="15" t="n"/>
       <c r="L264" s="15" t="n"/>
       <c r="M264" s="15">
@@ -24885,15 +23465,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H265" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H265" s="15" t="n"/>
       <c r="I265" s="15" t="n"/>
-      <c r="J265" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J265" s="15" t="n"/>
       <c r="K265" s="15" t="n"/>
       <c r="L265" s="15" t="n"/>
       <c r="M265" s="15">
@@ -24954,15 +23528,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H266" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H266" s="15" t="n"/>
       <c r="I266" s="15" t="n"/>
-      <c r="J266" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J266" s="15" t="n"/>
       <c r="K266" s="15" t="n"/>
       <c r="L266" s="15" t="n"/>
       <c r="M266" s="15">
@@ -25023,15 +23591,9 @@
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H267" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H267" s="15" t="n"/>
       <c r="I267" s="15" t="n"/>
-      <c r="J267" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J267" s="15" t="n"/>
       <c r="K267" s="15" t="n"/>
       <c r="L267" s="15" t="n"/>
       <c r="M267" s="15">
@@ -25092,15 +23654,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H268" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H268" s="15" t="n"/>
       <c r="I268" s="15" t="n"/>
-      <c r="J268" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J268" s="15" t="n"/>
       <c r="K268" s="15" t="n"/>
       <c r="L268" s="15" t="n"/>
       <c r="M268" s="15">
@@ -25161,15 +23717,9 @@
           <t>Temporal Forces</t>
         </is>
       </c>
-      <c r="H269" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H269" s="15" t="n"/>
       <c r="I269" s="15" t="n"/>
-      <c r="J269" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J269" s="15" t="n"/>
       <c r="K269" s="15" t="n"/>
       <c r="L269" s="15" t="n"/>
       <c r="M269" s="15">
@@ -25230,15 +23780,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H270" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H270" s="15" t="n"/>
       <c r="I270" s="15" t="n"/>
-      <c r="J270" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J270" s="15" t="n"/>
       <c r="K270" s="15" t="n"/>
       <c r="L270" s="15" t="n"/>
       <c r="M270" s="15">
@@ -25299,15 +23843,9 @@
           <t>Shining Fates</t>
         </is>
       </c>
-      <c r="H271" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H271" s="15" t="n"/>
       <c r="I271" s="15" t="n"/>
-      <c r="J271" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J271" s="15" t="n"/>
       <c r="K271" s="15" t="n"/>
       <c r="L271" s="15" t="n"/>
       <c r="M271" s="15">
@@ -25368,15 +23906,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H272" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H272" s="15" t="n"/>
       <c r="I272" s="15" t="n"/>
-      <c r="J272" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J272" s="15" t="n"/>
       <c r="K272" s="15" t="n"/>
       <c r="L272" s="15" t="n"/>
       <c r="M272" s="15">
@@ -25437,15 +23969,9 @@
           <t>Shining Fates</t>
         </is>
       </c>
-      <c r="H273" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H273" s="15" t="n"/>
       <c r="I273" s="15" t="n"/>
-      <c r="J273" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J273" s="15" t="n"/>
       <c r="K273" s="15" t="n"/>
       <c r="L273" s="15" t="n"/>
       <c r="M273" s="15">
@@ -25506,15 +24032,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H274" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H274" s="15" t="n"/>
       <c r="I274" s="15" t="n"/>
-      <c r="J274" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J274" s="15" t="n"/>
       <c r="K274" s="15" t="n"/>
       <c r="L274" s="15" t="n"/>
       <c r="M274" s="15">
@@ -25575,15 +24095,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H275" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H275" s="15" t="n"/>
       <c r="I275" s="15" t="n"/>
-      <c r="J275" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J275" s="15" t="n"/>
       <c r="K275" s="15" t="n"/>
       <c r="L275" s="15" t="n"/>
       <c r="M275" s="15">
@@ -25644,15 +24158,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H276" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H276" s="15" t="n"/>
       <c r="I276" s="15" t="n"/>
-      <c r="J276" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J276" s="15" t="n"/>
       <c r="K276" s="15" t="n"/>
       <c r="L276" s="15" t="n"/>
       <c r="M276" s="15">
@@ -25713,15 +24221,9 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="H277" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H277" s="15" t="n"/>
       <c r="I277" s="15" t="n"/>
-      <c r="J277" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J277" s="15" t="n"/>
       <c r="K277" s="15" t="n"/>
       <c r="L277" s="15" t="n"/>
       <c r="M277" s="15">
@@ -25782,15 +24284,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H278" s="15" t="n">
-        <v>9</v>
-      </c>
+      <c r="H278" s="15" t="n"/>
       <c r="I278" s="15" t="n"/>
-      <c r="J278" s="15" t="inlineStr">
-        <is>
-          <t>ETB (Elite Trainer Box)</t>
-        </is>
-      </c>
+      <c r="J278" s="15" t="n"/>
       <c r="K278" s="15" t="n"/>
       <c r="L278" s="15" t="n"/>
       <c r="M278" s="15">
@@ -25849,11 +24345,7 @@
       <c r="G279" s="15" t="n"/>
       <c r="H279" s="15" t="n"/>
       <c r="I279" s="15" t="n"/>
-      <c r="J279" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J279" s="15" t="n"/>
       <c r="K279" s="15" t="n"/>
       <c r="L279" s="15" t="n"/>
       <c r="M279" s="15">
@@ -25914,15 +24406,9 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H280" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H280" s="15" t="n"/>
       <c r="I280" s="15" t="n"/>
-      <c r="J280" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J280" s="15" t="n"/>
       <c r="K280" s="15" t="n"/>
       <c r="L280" s="15" t="n"/>
       <c r="M280" s="15">
@@ -25983,15 +24469,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H281" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H281" s="15" t="n"/>
       <c r="I281" s="15" t="n"/>
-      <c r="J281" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J281" s="15" t="n"/>
       <c r="K281" s="15" t="n"/>
       <c r="L281" s="15" t="n"/>
       <c r="M281" s="15">
@@ -26052,15 +24532,9 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H282" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H282" s="15" t="n"/>
       <c r="I282" s="15" t="n"/>
-      <c r="J282" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J282" s="15" t="n"/>
       <c r="K282" s="15" t="n"/>
       <c r="L282" s="15" t="n"/>
       <c r="M282" s="15">
@@ -26121,15 +24595,9 @@
           <t>Battle Partners (KR)</t>
         </is>
       </c>
-      <c r="H283" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H283" s="15" t="n"/>
       <c r="I283" s="15" t="n"/>
-      <c r="J283" s="15" t="inlineStr">
-        <is>
-          <t>Korean Booster Pack</t>
-        </is>
-      </c>
+      <c r="J283" s="15" t="n"/>
       <c r="K283" s="15" t="n"/>
       <c r="L283" s="15" t="n"/>
       <c r="M283" s="15">
@@ -26190,15 +24658,9 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H284" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H284" s="15" t="n"/>
       <c r="I284" s="15" t="n"/>
-      <c r="J284" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J284" s="15" t="n"/>
       <c r="K284" s="15" t="n"/>
       <c r="L284" s="15" t="n"/>
       <c r="M284" s="15">
@@ -26259,15 +24721,9 @@
           <t>Crimson Haze (KR)</t>
         </is>
       </c>
-      <c r="H285" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H285" s="15" t="n"/>
       <c r="I285" s="15" t="n"/>
-      <c r="J285" s="15" t="inlineStr">
-        <is>
-          <t>Korean Booster Pack</t>
-        </is>
-      </c>
+      <c r="J285" s="15" t="n"/>
       <c r="K285" s="15" t="n"/>
       <c r="L285" s="15" t="n"/>
       <c r="M285" s="15">
@@ -26328,15 +24784,9 @@
           <t>Surging Sparks</t>
         </is>
       </c>
-      <c r="H286" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H286" s="15" t="n"/>
       <c r="I286" s="15" t="n"/>
-      <c r="J286" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J286" s="15" t="n"/>
       <c r="K286" s="15" t="n"/>
       <c r="L286" s="15" t="n"/>
       <c r="M286" s="15">
@@ -26397,15 +24847,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H287" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H287" s="15" t="n"/>
       <c r="I287" s="15" t="n"/>
-      <c r="J287" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J287" s="15" t="n"/>
       <c r="K287" s="15" t="n"/>
       <c r="L287" s="15" t="n"/>
       <c r="M287" s="15">
@@ -26464,11 +24908,7 @@
       <c r="G288" s="15" t="n"/>
       <c r="H288" s="15" t="n"/>
       <c r="I288" s="15" t="n"/>
-      <c r="J288" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J288" s="15" t="n"/>
       <c r="K288" s="15" t="n"/>
       <c r="L288" s="15" t="n"/>
       <c r="M288" s="15">
@@ -26533,15 +24973,9 @@
           <t>151</t>
         </is>
       </c>
-      <c r="H289" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H289" s="15" t="n"/>
       <c r="I289" s="15" t="n"/>
-      <c r="J289" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J289" s="15" t="n"/>
       <c r="K289" s="15" t="n"/>
       <c r="L289" s="15" t="n"/>
       <c r="M289" s="15">
@@ -26598,15 +25032,9 @@
         <v/>
       </c>
       <c r="G290" s="15" t="n"/>
-      <c r="H290" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H290" s="15" t="n"/>
       <c r="I290" s="15" t="n"/>
-      <c r="J290" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J290" s="15" t="n"/>
       <c r="K290" s="15" t="n"/>
       <c r="L290" s="15" t="n"/>
       <c r="M290" s="15">
@@ -26667,15 +25095,9 @@
           <t>Prismatic Evolutions</t>
         </is>
       </c>
-      <c r="H291" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H291" s="15" t="n"/>
       <c r="I291" s="15" t="n"/>
-      <c r="J291" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J291" s="15" t="n"/>
       <c r="K291" s="15" t="n"/>
       <c r="L291" s="15" t="n"/>
       <c r="M291" s="15">
@@ -26736,15 +25158,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H292" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H292" s="15" t="n"/>
       <c r="I292" s="15" t="n"/>
-      <c r="J292" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J292" s="15" t="n"/>
       <c r="K292" s="15" t="n"/>
       <c r="L292" s="15" t="n"/>
       <c r="M292" s="15">
@@ -26805,15 +25221,9 @@
           <t>Destined Rivals</t>
         </is>
       </c>
-      <c r="H293" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H293" s="15" t="n"/>
       <c r="I293" s="15" t="n"/>
-      <c r="J293" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J293" s="15" t="n"/>
       <c r="K293" s="15" t="n"/>
       <c r="L293" s="15" t="n"/>
       <c r="M293" s="15">
@@ -26874,15 +25284,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H294" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H294" s="15" t="n"/>
       <c r="I294" s="15" t="n"/>
-      <c r="J294" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J294" s="15" t="n"/>
       <c r="K294" s="15" t="n"/>
       <c r="L294" s="15" t="n"/>
       <c r="M294" s="15">
@@ -26943,15 +25347,9 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H295" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H295" s="15" t="n"/>
       <c r="I295" s="15" t="n"/>
-      <c r="J295" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J295" s="15" t="n"/>
       <c r="K295" s="15" t="n"/>
       <c r="L295" s="15" t="n"/>
       <c r="M295" s="15">
@@ -27012,15 +25410,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H296" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H296" s="15" t="n"/>
       <c r="I296" s="15" t="n"/>
-      <c r="J296" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J296" s="15" t="n"/>
       <c r="K296" s="15" t="n"/>
       <c r="L296" s="15" t="n"/>
       <c r="M296" s="15">
@@ -27081,15 +25473,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H297" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H297" s="15" t="n"/>
       <c r="I297" s="15" t="n"/>
-      <c r="J297" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J297" s="15" t="n"/>
       <c r="K297" s="15" t="n"/>
       <c r="L297" s="15" t="n"/>
       <c r="M297" s="15">
@@ -27150,15 +25536,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H298" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H298" s="15" t="n"/>
       <c r="I298" s="15" t="n"/>
-      <c r="J298" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J298" s="15" t="n"/>
       <c r="K298" s="15" t="n"/>
       <c r="L298" s="15" t="n"/>
       <c r="M298" s="15">
@@ -27217,11 +25597,7 @@
       <c r="G299" s="15" t="n"/>
       <c r="H299" s="15" t="n"/>
       <c r="I299" s="15" t="n"/>
-      <c r="J299" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J299" s="15" t="n"/>
       <c r="K299" s="15" t="n"/>
       <c r="L299" s="15" t="n"/>
       <c r="M299" s="15">
@@ -27282,15 +25658,9 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="H300" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H300" s="15" t="n"/>
       <c r="I300" s="15" t="n"/>
-      <c r="J300" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J300" s="15" t="n"/>
       <c r="K300" s="15" t="n"/>
       <c r="L300" s="15" t="n"/>
       <c r="M300" s="15">
@@ -27355,15 +25725,9 @@
         <v/>
       </c>
       <c r="G301" s="15" t="n"/>
-      <c r="H301" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H301" s="15" t="n"/>
       <c r="I301" s="15" t="n"/>
-      <c r="J301" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J301" s="15" t="n"/>
       <c r="K301" s="15" t="n"/>
       <c r="L301" s="15" t="n"/>
       <c r="M301" s="15">
@@ -27428,15 +25792,9 @@
           <t>Mask of Change (KR)</t>
         </is>
       </c>
-      <c r="H302" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H302" s="15" t="n"/>
       <c r="I302" s="15" t="n"/>
-      <c r="J302" s="15" t="inlineStr">
-        <is>
-          <t>Korean Booster Pack</t>
-        </is>
-      </c>
+      <c r="J302" s="15" t="n"/>
       <c r="K302" s="15" t="n"/>
       <c r="L302" s="15" t="n"/>
       <c r="M302" s="15">
@@ -27501,15 +25859,9 @@
           <t>Violet ex (JP)</t>
         </is>
       </c>
-      <c r="H303" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H303" s="15" t="n"/>
       <c r="I303" s="15" t="n"/>
-      <c r="J303" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J303" s="15" t="n"/>
       <c r="K303" s="15" t="n"/>
       <c r="L303" s="15" t="n"/>
       <c r="M303" s="15">
@@ -27574,15 +25926,9 @@
           <t>Gem Pack Vol. 2 (CN)</t>
         </is>
       </c>
-      <c r="H304" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H304" s="15" t="n"/>
       <c r="I304" s="15" t="n"/>
-      <c r="J304" s="15" t="inlineStr">
-        <is>
-          <t>Chinese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J304" s="15" t="n"/>
       <c r="K304" s="15" t="n"/>
       <c r="L304" s="15" t="n"/>
       <c r="M304" s="15">
@@ -27647,15 +25993,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H305" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H305" s="15" t="n"/>
       <c r="I305" s="15" t="n"/>
-      <c r="J305" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J305" s="15" t="n"/>
       <c r="K305" s="15" t="n"/>
       <c r="L305" s="15" t="n"/>
       <c r="M305" s="15">
@@ -27724,15 +26064,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H306" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H306" s="15" t="n"/>
       <c r="I306" s="15" t="n"/>
-      <c r="J306" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J306" s="15" t="n"/>
       <c r="K306" s="15" t="n"/>
       <c r="L306" s="15" t="n"/>
       <c r="M306" s="15">
@@ -27809,15 +26143,9 @@
           <t>Journey Together</t>
         </is>
       </c>
-      <c r="H307" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="H307" s="15" t="n"/>
       <c r="I307" s="15" t="n"/>
-      <c r="J307" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J307" s="15" t="n"/>
       <c r="K307" s="15" t="n"/>
       <c r="L307" s="15" t="n"/>
       <c r="M307" s="15">
@@ -27886,15 +26214,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H308" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H308" s="15" t="n"/>
       <c r="I308" s="15" t="n"/>
-      <c r="J308" s="15" t="inlineStr">
-        <is>
-          <t>Single Booster Pack</t>
-        </is>
-      </c>
+      <c r="J308" s="15" t="n"/>
       <c r="K308" s="15" t="n"/>
       <c r="L308" s="15" t="n"/>
       <c r="M308" s="15">
@@ -27963,15 +26285,9 @@
           <t>Cyber Judge (JP)</t>
         </is>
       </c>
-      <c r="H309" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H309" s="15" t="n"/>
       <c r="I309" s="15" t="n"/>
-      <c r="J309" s="15" t="inlineStr">
-        <is>
-          <t>Japanese Booster Pack</t>
-        </is>
-      </c>
+      <c r="J309" s="15" t="n"/>
       <c r="K309" s="15" t="n"/>
       <c r="L309" s="15" t="n"/>
       <c r="M309" s="15">
@@ -28040,15 +26356,9 @@
           <t>Paldea Evolved</t>
         </is>
       </c>
-      <c r="H310" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="H310" s="15" t="n"/>
       <c r="I310" s="15" t="n"/>
-      <c r="J310" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J310" s="15" t="n"/>
       <c r="K310" s="15" t="n"/>
       <c r="L310" s="15" t="n"/>
       <c r="M310" s="15">
@@ -28113,15 +26423,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H311" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H311" s="15" t="n"/>
       <c r="I311" s="15" t="n"/>
-      <c r="J311" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J311" s="15" t="n"/>
       <c r="K311" s="15" t="n"/>
       <c r="L311" s="15" t="n"/>
       <c r="M311" s="15">
@@ -28194,15 +26498,9 @@
           <t>Twilight Masquerade</t>
         </is>
       </c>
-      <c r="H312" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H312" s="15" t="n"/>
       <c r="I312" s="15" t="n"/>
-      <c r="J312" s="15" t="inlineStr">
-        <is>
-          <t>Knock Out Collection</t>
-        </is>
-      </c>
+      <c r="J312" s="15" t="n"/>
       <c r="K312" s="15" t="n"/>
       <c r="L312" s="15" t="n"/>
       <c r="M312" s="15">
@@ -28279,15 +26577,9 @@
           <t>Twilight Masquerade</t>
         </is>
       </c>
-      <c r="H313" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H313" s="15" t="n"/>
       <c r="I313" s="15" t="n"/>
-      <c r="J313" s="15" t="inlineStr">
-        <is>
-          <t>Knock Out Collection</t>
-        </is>
-      </c>
+      <c r="J313" s="15" t="n"/>
       <c r="K313" s="15" t="n"/>
       <c r="L313" s="15" t="n"/>
       <c r="M313" s="15">
@@ -28364,15 +26656,9 @@
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="H314" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="H314" s="15" t="n"/>
       <c r="I314" s="15" t="n"/>
-      <c r="J314" s="15" t="inlineStr">
-        <is>
-          <t>Blister</t>
-        </is>
-      </c>
+      <c r="J314" s="15" t="n"/>
       <c r="K314" s="15" t="n"/>
       <c r="L314" s="15" t="n"/>
       <c r="M314" s="15">
@@ -28441,15 +26727,9 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H315" s="15" t="n">
-        <v>4</v>
-      </c>
+      <c r="H315" s="15" t="n"/>
       <c r="I315" s="15" t="n"/>
-      <c r="J315" s="15" t="inlineStr">
-        <is>
-          <t>ex Premium Collection</t>
-        </is>
-      </c>
+      <c r="J315" s="15" t="n"/>
       <c r="K315" s="15" t="n"/>
       <c r="L315" s="15" t="n"/>
       <c r="M315" s="15">
@@ -28530,15 +26810,9 @@
           <t>Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H316" s="15" t="n">
-        <v>18</v>
-      </c>
+      <c r="H316" s="15" t="n"/>
       <c r="I316" s="15" t="n"/>
-      <c r="J316" s="15" t="inlineStr">
-        <is>
-          <t>UPC (Ultra Premium Collection)</t>
-        </is>
-      </c>
+      <c r="J316" s="15" t="n"/>
       <c r="K316" s="15" t="n"/>
       <c r="L316" s="15" t="n"/>
       <c r="M316" s="15">
@@ -28631,19 +26905,13 @@
           <t>Mega Evolution</t>
         </is>
       </c>
-      <c r="H317" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="H317" s="15" t="n"/>
       <c r="I317" s="15" t="inlineStr">
         <is>
           <t>Fall 2025 Collector Chest</t>
         </is>
       </c>
-      <c r="J317" s="15" t="inlineStr">
-        <is>
-          <t>Tin</t>
-        </is>
-      </c>
+      <c r="J317" s="15" t="n"/>
       <c r="K317" s="15" t="n"/>
       <c r="L317" s="15" t="n"/>
       <c r="M317" s="15">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -298,6 +298,20 @@
 Set 2=Pitch Black Packs 2=6. Packs Opened adds them to 12 for you.
 This is what makes 'how many Pitch Black packs have we opened'
 answerable at all: a single total cannot be split back apart.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>FREE TEXT. Type it however you say it out loud.
+  Pitch Black Booster Bundle #3 Pack#5
+  Chaos Rising ETB 3 - pack 3
+  Journey Together Booster Bundle 2, pack 6
+This one cell can fill Opening Type, Set, Box # and Pack # for you, so
+if you write it here you do not have to fill those four as well.
+Anything you DO type in those columns wins over what is read here.
+There is no dropdown any more, on purpose: the old list could only
+offer products already in the log, so it could never contain the one
+you were recording for the first time.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
@@ -6500,7 +6514,7 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -27058,7 +27072,7 @@
       <formula>AND($N2="Yes",$O2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="16">
+  <dataValidations count="15">
     <dataValidation sqref="H2:H318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>gr_list_A</formula1>
     </dataValidation>
@@ -27104,9 +27118,6 @@
     <dataValidation sqref="L2:L318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>gr_list_M</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_F</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -362,24 +362,16 @@
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
-FREE TEXT. There is no dropdown on this column and there should not be
-one. If Sheets offers to turn what you have typed into a dropdown, say
-no; if one appears, select the column and use Data, Data validation,
-Remove rule. A dropdown here means retyping a card you already wrote.
-One line per card, in this shape:
-   Set - Card name - Rarity
-For example:
-   Surging Sparks - Feebas - Illustration Rare
-Several cards from one rip go in the SAME cell, separated by commas,
-and they can be from different sets and different rarities:
-   Journey Together - Noibat - Illustration Rare,
-   Mega Evolution - Marshadow - Illustration Rare
-The site reads the rarity out of these words, so spell the rarity out.
-The star description is welcome and ignored: write it if it helps you.
-Leave it EMPTY when there was no hit. An empty cell means the video
-shows no rarity badge anywhere on the site, which is correct: we only
-claim a pull where you have said what the card was.</t>
+        <t>FREE TEXT. Type it the way you say it: set, card, rarity.
+  Chaos Rising Mega Greninja ex Hyper Rare
+MORE THAN ONE HIT? Separate them with a comma:
+  Chaos Rising Mega Greninja ex Hyper Rare,
+  Pitch Black Umbreon ex Special Illustration Rare
+The comma separates HITS, not the parts of one hit.
+The set and the rarity are matched against the real lists, so what is
+left over is the card name. Leave the rarity off if you do not know it
+and the card is still recorded. Nothing you type is ever discarded:
+the whole line is kept exactly as written whatever gets recognised.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -27072,7 +27064,7 @@
       <formula>AND($N2="Yes",$O2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="5">
     <dataValidation sqref="H2:H318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>gr_list_A</formula1>
     </dataValidation>
@@ -27087,36 +27079,6 @@
     </dataValidation>
     <dataValidation sqref="W2:W318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>gr_list_A</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_B</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_C</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_D</formula1>
-    </dataValidation>
-    <dataValidation sqref="Y2:Y318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_D</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE2:AE318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_D</formula1>
-    </dataValidation>
-    <dataValidation sqref="AF2:AF318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_D</formula1>
-    </dataValidation>
-    <dataValidation sqref="AA2:AA318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_E</formula1>
-    </dataValidation>
-    <dataValidation sqref="Z2:Z318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_K</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_L</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_M</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="gr_list_A">Lists!$A$2:$A$190</definedName>
+    <definedName name="gr_list_AA">Lists!$A$2:$A$190</definedName>
     <definedName name="gr_list_B">Lists!$B$2:$B$19</definedName>
     <definedName name="gr_list_C">Lists!$C$2:$C$13</definedName>
     <definedName name="gr_list_D">Lists!$D$2:$D$3</definedName>
@@ -26736,16 +26737,30 @@
         <f>HYPERLINK("https://youtu.be/EOFAhFwJKqw","watch")</f>
         <v/>
       </c>
-      <c r="G315" s="14" t="n"/>
+      <c r="G315" s="14" t="inlineStr">
+        <is>
+          <t>Blister Pack</t>
+        </is>
+      </c>
       <c r="H315" s="15" t="inlineStr">
         <is>
           <t>Paradox Rift</t>
         </is>
       </c>
-      <c r="I315" s="14" t="n"/>
-      <c r="J315" s="14" t="n"/>
-      <c r="K315" s="14" t="n"/>
-      <c r="L315" s="14" t="n"/>
+      <c r="I315" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J315" s="14" t="inlineStr">
+        <is>
+          <t>Paradox Rift Blister Pack</t>
+        </is>
+      </c>
+      <c r="K315" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L315" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="M315" s="14">
         <f>SUM(I315,R315,T315,V315,X315)</f>
         <v/>
@@ -26807,15 +26822,25 @@
         <f>HYPERLINK("https://youtu.be/l6RPdGNs7uE","watch")</f>
         <v/>
       </c>
-      <c r="G316" s="14" t="n"/>
+      <c r="G316" s="14" t="inlineStr">
+        <is>
+          <t>ex Box</t>
+        </is>
+      </c>
       <c r="H316" s="15" t="inlineStr">
         <is>
           <t>Mega Evolution</t>
         </is>
       </c>
       <c r="I316" s="14" t="n"/>
-      <c r="J316" s="14" t="n"/>
-      <c r="K316" s="14" t="n"/>
+      <c r="J316" s="14" t="inlineStr">
+        <is>
+          <t>Mega Kangaskhan ex Box</t>
+        </is>
+      </c>
+      <c r="K316" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L316" s="14" t="n"/>
       <c r="M316" s="14">
         <f>SUM(I316,R316,T316,V316,X316)</f>
@@ -26890,15 +26915,25 @@
         <f>HYPERLINK("https://youtu.be/kj7532tb0_I","watch")</f>
         <v/>
       </c>
-      <c r="G317" s="14" t="n"/>
+      <c r="G317" s="14" t="inlineStr">
+        <is>
+          <t>UPC</t>
+        </is>
+      </c>
       <c r="H317" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="I317" s="14" t="n"/>
-      <c r="J317" s="14" t="n"/>
-      <c r="K317" s="14" t="n"/>
+      <c r="J317" s="14" t="inlineStr">
+        <is>
+          <t>Mega Charizard X ex Ultra Premium Collection</t>
+        </is>
+      </c>
+      <c r="K317" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L317" s="14" t="n"/>
       <c r="M317" s="14">
         <f>SUM(I317,R317,T317,V317,X317)</f>
@@ -26985,7 +27020,11 @@
         <f>HYPERLINK("https://youtu.be/TN7_ZsuRQSI","watch")</f>
         <v/>
       </c>
-      <c r="G318" s="14" t="n"/>
+      <c r="G318" s="14" t="inlineStr">
+        <is>
+          <t>Collector Chest</t>
+        </is>
+      </c>
       <c r="H318" s="15" t="inlineStr">
         <is>
           <t>Mega Evolution</t>
@@ -26997,7 +27036,9 @@
           <t>Fall 2025 Collector Chest</t>
         </is>
       </c>
-      <c r="K318" s="14" t="n"/>
+      <c r="K318" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="L318" s="14" t="n"/>
       <c r="M318" s="14">
         <f>SUM(I318,R318,T318,V318,X318)</f>
@@ -27066,7 +27107,7 @@
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="H2:H318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>gr_list_A</formula1>
+      <formula1>gr_list_AA</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>gr_list_A</formula1>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -26708,22 +26708,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation sqref="G2:G318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_B</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_AA</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_A</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_A</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_A</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V318" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_A</formula1>
     </dataValidation>
   </dataValidations>
@@ -27530,7 +27530,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_D</formula1>
     </dataValidation>
   </dataValidations>
@@ -36484,13 +36484,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_D</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_D</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_H</formula1>
     </dataValidation>
   </dataValidations>
@@ -41266,16 +41266,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="No such video id" error="That id is not in the Video Log. Keep it if you are sure." type="list" errorStyle="warning">
       <formula1>='Video Log'!$A$2:$A$318</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_A</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_C</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_D</formula1>
     </dataValidation>
   </dataValidations>
@@ -41533,13 +41533,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="F2:F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_D</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_I</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
       <formula1>gr_list_J</formula1>
     </dataValidation>
   </dataValidations>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -31,7 +31,7 @@
     <definedName name="gr_list_K">Lists!$K$2:$K$21</definedName>
     <definedName name="gr_list_L">Lists!$L$2:$L$31</definedName>
     <definedName name="gr_list_M">Lists!$M$2:$M$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$U$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$T$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -274,7 +274,20 @@
     <author>Garbage Rips</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>WRITE IT THE WAY YOU SAY IT, all in this one cell:
+   Pitch Black ETB #3
+   Journey Together Booster Bundle #2
+   Paradox Rift Blister Pack
+Set, product, and which one of that product. Three columns used to ask
+you to take that sentence apart before typing it. Now you type the
+sentence and the import takes it apart.
+The Lists tab has every set name and product type if you want to copy
+one exactly. Anything not recognised is reported back, never guessed.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>WHICH PACK OUT OF THAT BOX this video opens. Pack 3 of the 9 in an
 ETB is 3.
@@ -287,23 +300,6 @@
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>WHAT CAME OUT OF THIS VIDEO. Set name, then how many packs of it.
-Comma between sets. Same grammar as Hit Info.
-ONE PACK:   Pitch Black 1
-WHOLE ETB:  Pitch Black 9
-MULTI SET:  Phantasmal Flames 6, Mega Evolution 4, Destined Rivals 4
-This replaces Set, Packs and the four Set 2-5 pairs. A UPC across five
-sets used to need ten columns spread across the sheet. Now it is one
-cell, and the rare case costs no more than the common one.
-It is what THIS VIDEO opened, not what the box holds. One pack out of
-a nine-pack ETB is 1, not 9. Nothing else on the row asks for a pack
-count, so there is no second number to disagree with this one.
-The Lists tab has all 174 set names to copy from. Anything not
-recognised is reported back rather than silently dropped.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
 FREE TEXT. There is no dropdown on this column and there should not be
@@ -325,7 +321,17 @@
 claim a pull where you have said what the card was.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>LEAVE THIS BLANK unless the video opened packs from MORE THAN ONE SET.
+Nearly every video is one pack from one set, and for those the Product
+and Pack # cells already say everything. Do those first.
+For a UPC or a chest that spans sets, write set and count:
+   Phantasmal Flames 6, Mega Evolution 4, Destined Rivals 4
+We can rework this column once the single-set rows are done.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>The Hall of Fame band on the home page.
 Separate from the Hits playlist: this is the shortlist, that is a
@@ -6426,7 +6432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U318"/>
+  <dimension ref="A1:T318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6435,21 +6441,20 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="54" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6490,70 +6495,65 @@
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>Product #</t>
+          <t>Pack #</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>Pack #</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
+          <t>Hit Info</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
           <t>Sets &amp; Packs</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>Hit</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>Hit Info</t>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>Greatest Hits</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>Greatest Hits</t>
-        </is>
-      </c>
-      <c r="N1" s="10" t="inlineStr">
-        <is>
           <t>Greatest Hits Rank</t>
         </is>
       </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Playlist To Add</t>
+        </is>
+      </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>Playlist To Add</t>
+          <t>Affiliate Link</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>Affiliate Link</t>
+          <t>Site Title</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>Site Title</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Hide</t>
         </is>
       </c>
       <c r="T1" s="9" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6601,7 +6601,6 @@
       <c r="R2" s="14" t="n"/>
       <c r="S2" s="14" t="n"/>
       <c r="T2" s="14" t="n"/>
-      <c r="U2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -6635,23 +6634,20 @@
       <c r="H3" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="I3" s="14" t="n"/>
       <c r="J3" s="14" t="n"/>
       <c r="K3" s="14" t="n"/>
       <c r="L3" s="14" t="n"/>
-      <c r="M3" s="14" t="n"/>
-      <c r="N3" s="14" t="n">
+      <c r="M3" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="N3" s="14" t="n"/>
       <c r="O3" s="14" t="n"/>
       <c r="P3" s="14" t="n"/>
       <c r="Q3" s="14" t="n"/>
       <c r="R3" s="14" t="n"/>
       <c r="S3" s="14" t="n"/>
       <c r="T3" s="14" t="n"/>
-      <c r="U3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -6695,7 +6691,6 @@
       <c r="R4" s="14" t="n"/>
       <c r="S4" s="14" t="n"/>
       <c r="T4" s="14" t="n"/>
-      <c r="U4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -6739,7 +6734,6 @@
       <c r="R5" s="14" t="n"/>
       <c r="S5" s="14" t="n"/>
       <c r="T5" s="14" t="n"/>
-      <c r="U5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -6771,13 +6765,13 @@
       </c>
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
@@ -6787,7 +6781,6 @@
       <c r="R6" s="14" t="n"/>
       <c r="S6" s="14" t="n"/>
       <c r="T6" s="14" t="n"/>
-      <c r="U6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -6831,7 +6824,6 @@
       <c r="R7" s="14" t="n"/>
       <c r="S7" s="14" t="n"/>
       <c r="T7" s="14" t="n"/>
-      <c r="U7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6863,13 +6855,13 @@
       </c>
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K8" s="14" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
@@ -6879,7 +6871,6 @@
       <c r="R8" s="14" t="n"/>
       <c r="S8" s="14" t="n"/>
       <c r="T8" s="14" t="n"/>
-      <c r="U8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -6923,7 +6914,6 @@
       <c r="R9" s="14" t="n"/>
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="14" t="n"/>
-      <c r="U9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -6955,13 +6945,13 @@
       </c>
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="14" t="n"/>
@@ -6971,7 +6961,6 @@
       <c r="R10" s="14" t="n"/>
       <c r="S10" s="14" t="n"/>
       <c r="T10" s="14" t="n"/>
-      <c r="U10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -7015,7 +7004,6 @@
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="14" t="n"/>
       <c r="T11" s="14" t="n"/>
-      <c r="U11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -7059,7 +7047,6 @@
       <c r="R12" s="14" t="n"/>
       <c r="S12" s="14" t="n"/>
       <c r="T12" s="14" t="n"/>
-      <c r="U12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -7091,13 +7078,13 @@
       </c>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K13" s="14" t="n"/>
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="14" t="n"/>
@@ -7107,7 +7094,6 @@
       <c r="R13" s="14" t="n"/>
       <c r="S13" s="14" t="n"/>
       <c r="T13" s="14" t="n"/>
-      <c r="U13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -7139,13 +7125,13 @@
       </c>
       <c r="G14" s="14" t="n"/>
       <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
@@ -7155,7 +7141,6 @@
       <c r="R14" s="14" t="n"/>
       <c r="S14" s="14" t="n"/>
       <c r="T14" s="14" t="n"/>
-      <c r="U14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -7199,7 +7184,6 @@
       <c r="R15" s="14" t="n"/>
       <c r="S15" s="14" t="n"/>
       <c r="T15" s="14" t="n"/>
-      <c r="U15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -7231,13 +7215,13 @@
       </c>
       <c r="G16" s="14" t="n"/>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K16" s="14" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
@@ -7247,7 +7231,6 @@
       <c r="R16" s="14" t="n"/>
       <c r="S16" s="14" t="n"/>
       <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -7279,13 +7262,13 @@
       </c>
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="14" t="n"/>
@@ -7295,7 +7278,6 @@
       <c r="R17" s="14" t="n"/>
       <c r="S17" s="14" t="n"/>
       <c r="T17" s="14" t="n"/>
-      <c r="U17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -7327,13 +7309,13 @@
       </c>
       <c r="G18" s="14" t="n"/>
       <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
@@ -7343,7 +7325,6 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="n"/>
       <c r="T18" s="14" t="n"/>
-      <c r="U18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -7375,13 +7356,13 @@
       </c>
       <c r="G19" s="14" t="n"/>
       <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="14" t="n"/>
@@ -7391,7 +7372,6 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="n"/>
       <c r="T19" s="14" t="n"/>
-      <c r="U19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -7423,13 +7403,13 @@
       </c>
       <c r="G20" s="14" t="n"/>
       <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J20" s="14" t="n"/>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
@@ -7439,7 +7419,6 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="n"/>
       <c r="T20" s="14" t="n"/>
-      <c r="U20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -7483,7 +7462,6 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="14" t="n"/>
       <c r="T21" s="14" t="n"/>
-      <c r="U21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -7515,13 +7493,13 @@
       </c>
       <c r="G22" s="14" t="n"/>
       <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="n"/>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J22" s="14" t="n"/>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
@@ -7531,7 +7509,6 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="n"/>
       <c r="T22" s="14" t="n"/>
-      <c r="U22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -7563,13 +7540,13 @@
       </c>
       <c r="G23" s="14" t="n"/>
       <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J23" s="14" t="n"/>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K23" s="14" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="14" t="n"/>
       <c r="N23" s="14" t="n"/>
@@ -7579,7 +7556,6 @@
       <c r="R23" s="14" t="n"/>
       <c r="S23" s="14" t="n"/>
       <c r="T23" s="14" t="n"/>
-      <c r="U23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -7611,13 +7587,13 @@
       </c>
       <c r="G24" s="14" t="n"/>
       <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K24" s="14" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
@@ -7627,7 +7603,6 @@
       <c r="R24" s="14" t="n"/>
       <c r="S24" s="14" t="n"/>
       <c r="T24" s="14" t="n"/>
-      <c r="U24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -7671,7 +7646,6 @@
       <c r="R25" s="14" t="n"/>
       <c r="S25" s="14" t="n"/>
       <c r="T25" s="14" t="n"/>
-      <c r="U25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -7703,13 +7677,13 @@
       </c>
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K26" s="14" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
@@ -7719,7 +7693,6 @@
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="14" t="n"/>
       <c r="T26" s="14" t="n"/>
-      <c r="U26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -7763,7 +7736,6 @@
       <c r="R27" s="14" t="n"/>
       <c r="S27" s="14" t="n"/>
       <c r="T27" s="14" t="n"/>
-      <c r="U27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -7795,13 +7767,13 @@
       </c>
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K28" s="14" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
@@ -7811,7 +7783,6 @@
       <c r="R28" s="14" t="n"/>
       <c r="S28" s="14" t="n"/>
       <c r="T28" s="14" t="n"/>
-      <c r="U28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -7843,13 +7814,13 @@
       </c>
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K29" s="14" t="n"/>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="14" t="n"/>
       <c r="N29" s="14" t="n"/>
@@ -7859,7 +7830,6 @@
       <c r="R29" s="14" t="n"/>
       <c r="S29" s="14" t="n"/>
       <c r="T29" s="14" t="n"/>
-      <c r="U29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -7903,7 +7873,6 @@
       <c r="R30" s="14" t="n"/>
       <c r="S30" s="14" t="n"/>
       <c r="T30" s="14" t="n"/>
-      <c r="U30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -7947,7 +7916,6 @@
       <c r="R31" s="14" t="n"/>
       <c r="S31" s="14" t="n"/>
       <c r="T31" s="14" t="n"/>
-      <c r="U31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -7979,13 +7947,13 @@
       </c>
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K32" s="14" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
@@ -7995,7 +7963,6 @@
       <c r="R32" s="14" t="n"/>
       <c r="S32" s="14" t="n"/>
       <c r="T32" s="14" t="n"/>
-      <c r="U32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -8039,7 +8006,6 @@
       <c r="R33" s="14" t="n"/>
       <c r="S33" s="14" t="n"/>
       <c r="T33" s="14" t="n"/>
-      <c r="U33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -8083,7 +8049,6 @@
       <c r="R34" s="14" t="n"/>
       <c r="S34" s="14" t="n"/>
       <c r="T34" s="14" t="n"/>
-      <c r="U34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -8115,13 +8080,13 @@
       </c>
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="n"/>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J35" s="14" t="n"/>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K35" s="14" t="n"/>
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="14" t="n"/>
       <c r="N35" s="14" t="n"/>
@@ -8131,7 +8096,6 @@
       <c r="R35" s="14" t="n"/>
       <c r="S35" s="14" t="n"/>
       <c r="T35" s="14" t="n"/>
-      <c r="U35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -8175,7 +8139,6 @@
       <c r="R36" s="14" t="n"/>
       <c r="S36" s="14" t="n"/>
       <c r="T36" s="14" t="n"/>
-      <c r="U36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -8219,7 +8182,6 @@
       <c r="R37" s="14" t="n"/>
       <c r="S37" s="14" t="n"/>
       <c r="T37" s="14" t="n"/>
-      <c r="U37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -8251,13 +8213,13 @@
       </c>
       <c r="G38" s="14" t="n"/>
       <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K38" s="14" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
@@ -8267,7 +8229,6 @@
       <c r="R38" s="14" t="n"/>
       <c r="S38" s="14" t="n"/>
       <c r="T38" s="14" t="n"/>
-      <c r="U38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -8311,7 +8272,6 @@
       <c r="R39" s="14" t="n"/>
       <c r="S39" s="14" t="n"/>
       <c r="T39" s="14" t="n"/>
-      <c r="U39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -8343,13 +8303,13 @@
       </c>
       <c r="G40" s="14" t="n"/>
       <c r="H40" s="14" t="n"/>
-      <c r="I40" s="14" t="n"/>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J40" s="14" t="n"/>
-      <c r="K40" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K40" s="14" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
@@ -8359,7 +8319,6 @@
       <c r="R40" s="14" t="n"/>
       <c r="S40" s="14" t="n"/>
       <c r="T40" s="14" t="n"/>
-      <c r="U40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -8391,13 +8350,13 @@
       </c>
       <c r="G41" s="14" t="n"/>
       <c r="H41" s="14" t="n"/>
-      <c r="I41" s="14" t="n"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J41" s="14" t="n"/>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K41" s="14" t="n"/>
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="14" t="n"/>
       <c r="N41" s="14" t="n"/>
@@ -8407,7 +8366,6 @@
       <c r="R41" s="14" t="n"/>
       <c r="S41" s="14" t="n"/>
       <c r="T41" s="14" t="n"/>
-      <c r="U41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -8451,7 +8409,6 @@
       <c r="R42" s="14" t="n"/>
       <c r="S42" s="14" t="n"/>
       <c r="T42" s="14" t="n"/>
-      <c r="U42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -8483,13 +8440,13 @@
       </c>
       <c r="G43" s="14" t="n"/>
       <c r="H43" s="14" t="n"/>
-      <c r="I43" s="14" t="n"/>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J43" s="14" t="n"/>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K43" s="14" t="n"/>
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="14" t="n"/>
@@ -8499,7 +8456,6 @@
       <c r="R43" s="14" t="n"/>
       <c r="S43" s="14" t="n"/>
       <c r="T43" s="14" t="n"/>
-      <c r="U43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -8531,13 +8487,13 @@
       </c>
       <c r="G44" s="14" t="n"/>
       <c r="H44" s="14" t="n"/>
-      <c r="I44" s="14" t="n"/>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J44" s="14" t="n"/>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="14" t="n"/>
@@ -8547,7 +8503,6 @@
       <c r="R44" s="14" t="n"/>
       <c r="S44" s="14" t="n"/>
       <c r="T44" s="14" t="n"/>
-      <c r="U44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -8591,7 +8546,6 @@
       <c r="R45" s="14" t="n"/>
       <c r="S45" s="14" t="n"/>
       <c r="T45" s="14" t="n"/>
-      <c r="U45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -8623,13 +8577,13 @@
       </c>
       <c r="G46" s="14" t="n"/>
       <c r="H46" s="14" t="n"/>
-      <c r="I46" s="14" t="n"/>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J46" s="14" t="n"/>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="14" t="n"/>
@@ -8639,7 +8593,6 @@
       <c r="R46" s="14" t="n"/>
       <c r="S46" s="14" t="n"/>
       <c r="T46" s="14" t="n"/>
-      <c r="U46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -8683,7 +8636,6 @@
       <c r="R47" s="14" t="n"/>
       <c r="S47" s="14" t="n"/>
       <c r="T47" s="14" t="n"/>
-      <c r="U47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -8727,7 +8679,6 @@
       <c r="R48" s="14" t="n"/>
       <c r="S48" s="14" t="n"/>
       <c r="T48" s="14" t="n"/>
-      <c r="U48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -8759,13 +8710,13 @@
       </c>
       <c r="G49" s="14" t="n"/>
       <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J49" s="14" t="n"/>
-      <c r="K49" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K49" s="14" t="n"/>
       <c r="L49" s="14" t="n"/>
       <c r="M49" s="14" t="n"/>
       <c r="N49" s="14" t="n"/>
@@ -8775,7 +8726,6 @@
       <c r="R49" s="14" t="n"/>
       <c r="S49" s="14" t="n"/>
       <c r="T49" s="14" t="n"/>
-      <c r="U49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -8819,7 +8769,6 @@
       <c r="R50" s="14" t="n"/>
       <c r="S50" s="14" t="n"/>
       <c r="T50" s="14" t="n"/>
-      <c r="U50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -8851,13 +8800,13 @@
       </c>
       <c r="G51" s="14" t="n"/>
       <c r="H51" s="14" t="n"/>
-      <c r="I51" s="14" t="n"/>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J51" s="14" t="n"/>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K51" s="14" t="n"/>
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="14" t="n"/>
       <c r="N51" s="14" t="n"/>
@@ -8867,7 +8816,6 @@
       <c r="R51" s="14" t="n"/>
       <c r="S51" s="14" t="n"/>
       <c r="T51" s="14" t="n"/>
-      <c r="U51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -8911,7 +8859,6 @@
       <c r="R52" s="14" t="n"/>
       <c r="S52" s="14" t="n"/>
       <c r="T52" s="14" t="n"/>
-      <c r="U52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -8943,13 +8890,13 @@
       </c>
       <c r="G53" s="14" t="n"/>
       <c r="H53" s="14" t="n"/>
-      <c r="I53" s="14" t="n"/>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J53" s="14" t="n"/>
-      <c r="K53" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K53" s="14" t="n"/>
       <c r="L53" s="14" t="n"/>
       <c r="M53" s="14" t="n"/>
       <c r="N53" s="14" t="n"/>
@@ -8959,7 +8906,6 @@
       <c r="R53" s="14" t="n"/>
       <c r="S53" s="14" t="n"/>
       <c r="T53" s="14" t="n"/>
-      <c r="U53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -9003,7 +8949,6 @@
       <c r="R54" s="14" t="n"/>
       <c r="S54" s="14" t="n"/>
       <c r="T54" s="14" t="n"/>
-      <c r="U54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -9035,13 +8980,13 @@
       </c>
       <c r="G55" s="14" t="n"/>
       <c r="H55" s="14" t="n"/>
-      <c r="I55" s="14" t="n"/>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J55" s="14" t="n"/>
-      <c r="K55" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K55" s="14" t="n"/>
       <c r="L55" s="14" t="n"/>
       <c r="M55" s="14" t="n"/>
       <c r="N55" s="14" t="n"/>
@@ -9051,7 +8996,6 @@
       <c r="R55" s="14" t="n"/>
       <c r="S55" s="14" t="n"/>
       <c r="T55" s="14" t="n"/>
-      <c r="U55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -9095,7 +9039,6 @@
       <c r="R56" s="14" t="n"/>
       <c r="S56" s="14" t="n"/>
       <c r="T56" s="14" t="n"/>
-      <c r="U56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -9127,13 +9070,13 @@
       </c>
       <c r="G57" s="14" t="n"/>
       <c r="H57" s="14" t="n"/>
-      <c r="I57" s="14" t="n"/>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J57" s="14" t="n"/>
-      <c r="K57" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K57" s="14" t="n"/>
       <c r="L57" s="14" t="n"/>
       <c r="M57" s="14" t="n"/>
       <c r="N57" s="14" t="n"/>
@@ -9143,7 +9086,6 @@
       <c r="R57" s="14" t="n"/>
       <c r="S57" s="14" t="n"/>
       <c r="T57" s="14" t="n"/>
-      <c r="U57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -9187,7 +9129,6 @@
       <c r="R58" s="14" t="n"/>
       <c r="S58" s="14" t="n"/>
       <c r="T58" s="14" t="n"/>
-      <c r="U58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -9231,7 +9172,6 @@
       <c r="R59" s="14" t="n"/>
       <c r="S59" s="14" t="n"/>
       <c r="T59" s="14" t="n"/>
-      <c r="U59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -9275,7 +9215,6 @@
       <c r="R60" s="14" t="n"/>
       <c r="S60" s="14" t="n"/>
       <c r="T60" s="14" t="n"/>
-      <c r="U60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -9319,7 +9258,6 @@
       <c r="R61" s="14" t="n"/>
       <c r="S61" s="14" t="n"/>
       <c r="T61" s="14" t="n"/>
-      <c r="U61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -9363,7 +9301,6 @@
       <c r="R62" s="14" t="n"/>
       <c r="S62" s="14" t="n"/>
       <c r="T62" s="14" t="n"/>
-      <c r="U62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -9407,7 +9344,6 @@
       <c r="R63" s="14" t="n"/>
       <c r="S63" s="14" t="n"/>
       <c r="T63" s="14" t="n"/>
-      <c r="U63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -9439,13 +9375,13 @@
       </c>
       <c r="G64" s="14" t="n"/>
       <c r="H64" s="14" t="n"/>
-      <c r="I64" s="14" t="n"/>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J64" s="14" t="n"/>
-      <c r="K64" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K64" s="14" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
@@ -9455,7 +9391,6 @@
       <c r="R64" s="14" t="n"/>
       <c r="S64" s="14" t="n"/>
       <c r="T64" s="14" t="n"/>
-      <c r="U64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -9499,7 +9434,6 @@
       <c r="R65" s="14" t="n"/>
       <c r="S65" s="14" t="n"/>
       <c r="T65" s="14" t="n"/>
-      <c r="U65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -9543,7 +9477,6 @@
       <c r="R66" s="14" t="n"/>
       <c r="S66" s="14" t="n"/>
       <c r="T66" s="14" t="n"/>
-      <c r="U66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -9587,7 +9520,6 @@
       <c r="R67" s="14" t="n"/>
       <c r="S67" s="14" t="n"/>
       <c r="T67" s="14" t="n"/>
-      <c r="U67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -9631,7 +9563,6 @@
       <c r="R68" s="14" t="n"/>
       <c r="S68" s="14" t="n"/>
       <c r="T68" s="14" t="n"/>
-      <c r="U68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -9675,7 +9606,6 @@
       <c r="R69" s="14" t="n"/>
       <c r="S69" s="14" t="n"/>
       <c r="T69" s="14" t="n"/>
-      <c r="U69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -9719,7 +9649,6 @@
       <c r="R70" s="14" t="n"/>
       <c r="S70" s="14" t="n"/>
       <c r="T70" s="14" t="n"/>
-      <c r="U70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -9763,7 +9692,6 @@
       <c r="R71" s="14" t="n"/>
       <c r="S71" s="14" t="n"/>
       <c r="T71" s="14" t="n"/>
-      <c r="U71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -9807,7 +9735,6 @@
       <c r="R72" s="14" t="n"/>
       <c r="S72" s="14" t="n"/>
       <c r="T72" s="14" t="n"/>
-      <c r="U72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -9851,7 +9778,6 @@
       <c r="R73" s="14" t="n"/>
       <c r="S73" s="14" t="n"/>
       <c r="T73" s="14" t="n"/>
-      <c r="U73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -9895,7 +9821,6 @@
       <c r="R74" s="14" t="n"/>
       <c r="S74" s="14" t="n"/>
       <c r="T74" s="14" t="n"/>
-      <c r="U74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -9939,7 +9864,6 @@
       <c r="R75" s="14" t="n"/>
       <c r="S75" s="14" t="n"/>
       <c r="T75" s="14" t="n"/>
-      <c r="U75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -9983,7 +9907,6 @@
       <c r="R76" s="14" t="n"/>
       <c r="S76" s="14" t="n"/>
       <c r="T76" s="14" t="n"/>
-      <c r="U76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -10027,7 +9950,6 @@
       <c r="R77" s="14" t="n"/>
       <c r="S77" s="14" t="n"/>
       <c r="T77" s="14" t="n"/>
-      <c r="U77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -10071,7 +9993,6 @@
       <c r="R78" s="14" t="n"/>
       <c r="S78" s="14" t="n"/>
       <c r="T78" s="14" t="n"/>
-      <c r="U78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -10115,7 +10036,6 @@
       <c r="R79" s="14" t="n"/>
       <c r="S79" s="14" t="n"/>
       <c r="T79" s="14" t="n"/>
-      <c r="U79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -10159,7 +10079,6 @@
       <c r="R80" s="14" t="n"/>
       <c r="S80" s="14" t="n"/>
       <c r="T80" s="14" t="n"/>
-      <c r="U80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -10203,7 +10122,6 @@
       <c r="R81" s="14" t="n"/>
       <c r="S81" s="14" t="n"/>
       <c r="T81" s="14" t="n"/>
-      <c r="U81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -10247,7 +10165,6 @@
       <c r="R82" s="14" t="n"/>
       <c r="S82" s="14" t="n"/>
       <c r="T82" s="14" t="n"/>
-      <c r="U82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -10279,13 +10196,13 @@
       </c>
       <c r="G83" s="14" t="n"/>
       <c r="H83" s="14" t="n"/>
-      <c r="I83" s="14" t="n"/>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J83" s="14" t="n"/>
-      <c r="K83" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K83" s="14" t="n"/>
       <c r="L83" s="14" t="n"/>
       <c r="M83" s="14" t="n"/>
       <c r="N83" s="14" t="n"/>
@@ -10295,7 +10212,6 @@
       <c r="R83" s="14" t="n"/>
       <c r="S83" s="14" t="n"/>
       <c r="T83" s="14" t="n"/>
-      <c r="U83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -10327,13 +10243,13 @@
       </c>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
-      <c r="I84" s="14" t="n"/>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J84" s="14" t="n"/>
-      <c r="K84" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
@@ -10343,7 +10259,6 @@
       <c r="R84" s="14" t="n"/>
       <c r="S84" s="14" t="n"/>
       <c r="T84" s="14" t="n"/>
-      <c r="U84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -10375,13 +10290,13 @@
       </c>
       <c r="G85" s="14" t="n"/>
       <c r="H85" s="14" t="n"/>
-      <c r="I85" s="14" t="n"/>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J85" s="14" t="n"/>
-      <c r="K85" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K85" s="14" t="n"/>
       <c r="L85" s="14" t="n"/>
       <c r="M85" s="14" t="n"/>
       <c r="N85" s="14" t="n"/>
@@ -10391,7 +10306,6 @@
       <c r="R85" s="14" t="n"/>
       <c r="S85" s="14" t="n"/>
       <c r="T85" s="14" t="n"/>
-      <c r="U85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -10423,13 +10337,13 @@
       </c>
       <c r="G86" s="14" t="n"/>
       <c r="H86" s="14" t="n"/>
-      <c r="I86" s="14" t="n"/>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J86" s="14" t="n"/>
-      <c r="K86" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K86" s="14" t="n"/>
       <c r="L86" s="14" t="n"/>
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
@@ -10439,7 +10353,6 @@
       <c r="R86" s="14" t="n"/>
       <c r="S86" s="14" t="n"/>
       <c r="T86" s="14" t="n"/>
-      <c r="U86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -10483,7 +10396,6 @@
       <c r="R87" s="14" t="n"/>
       <c r="S87" s="14" t="n"/>
       <c r="T87" s="14" t="n"/>
-      <c r="U87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -10527,7 +10439,6 @@
       <c r="R88" s="14" t="n"/>
       <c r="S88" s="14" t="n"/>
       <c r="T88" s="14" t="n"/>
-      <c r="U88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
@@ -10559,13 +10470,13 @@
       </c>
       <c r="G89" s="14" t="n"/>
       <c r="H89" s="14" t="n"/>
-      <c r="I89" s="14" t="n"/>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J89" s="14" t="n"/>
-      <c r="K89" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K89" s="14" t="n"/>
       <c r="L89" s="14" t="n"/>
       <c r="M89" s="14" t="n"/>
       <c r="N89" s="14" t="n"/>
@@ -10575,7 +10486,6 @@
       <c r="R89" s="14" t="n"/>
       <c r="S89" s="14" t="n"/>
       <c r="T89" s="14" t="n"/>
-      <c r="U89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -10607,13 +10517,13 @@
       </c>
       <c r="G90" s="14" t="n"/>
       <c r="H90" s="14" t="n"/>
-      <c r="I90" s="14" t="n"/>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J90" s="14" t="n"/>
-      <c r="K90" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K90" s="14" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
@@ -10623,7 +10533,6 @@
       <c r="R90" s="14" t="n"/>
       <c r="S90" s="14" t="n"/>
       <c r="T90" s="14" t="n"/>
-      <c r="U90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -10655,13 +10564,13 @@
       </c>
       <c r="G91" s="14" t="n"/>
       <c r="H91" s="14" t="n"/>
-      <c r="I91" s="14" t="n"/>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J91" s="14" t="n"/>
-      <c r="K91" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K91" s="14" t="n"/>
       <c r="L91" s="14" t="n"/>
       <c r="M91" s="14" t="n"/>
       <c r="N91" s="14" t="n"/>
@@ -10671,7 +10580,6 @@
       <c r="R91" s="14" t="n"/>
       <c r="S91" s="14" t="n"/>
       <c r="T91" s="14" t="n"/>
-      <c r="U91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
@@ -10703,13 +10611,13 @@
       </c>
       <c r="G92" s="14" t="n"/>
       <c r="H92" s="14" t="n"/>
-      <c r="I92" s="14" t="n"/>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J92" s="14" t="n"/>
-      <c r="K92" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K92" s="14" t="n"/>
       <c r="L92" s="14" t="n"/>
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
@@ -10719,7 +10627,6 @@
       <c r="R92" s="14" t="n"/>
       <c r="S92" s="14" t="n"/>
       <c r="T92" s="14" t="n"/>
-      <c r="U92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -10763,7 +10670,6 @@
       <c r="R93" s="14" t="n"/>
       <c r="S93" s="14" t="n"/>
       <c r="T93" s="14" t="n"/>
-      <c r="U93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -10807,7 +10713,6 @@
       <c r="R94" s="14" t="n"/>
       <c r="S94" s="14" t="n"/>
       <c r="T94" s="14" t="n"/>
-      <c r="U94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -10851,7 +10756,6 @@
       <c r="R95" s="14" t="n"/>
       <c r="S95" s="14" t="n"/>
       <c r="T95" s="14" t="n"/>
-      <c r="U95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -10895,7 +10799,6 @@
       <c r="R96" s="14" t="n"/>
       <c r="S96" s="14" t="n"/>
       <c r="T96" s="14" t="n"/>
-      <c r="U96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -10939,7 +10842,6 @@
       <c r="R97" s="14" t="n"/>
       <c r="S97" s="14" t="n"/>
       <c r="T97" s="14" t="n"/>
-      <c r="U97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -10983,7 +10885,6 @@
       <c r="R98" s="14" t="n"/>
       <c r="S98" s="14" t="n"/>
       <c r="T98" s="14" t="n"/>
-      <c r="U98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -11027,7 +10928,6 @@
       <c r="R99" s="14" t="n"/>
       <c r="S99" s="14" t="n"/>
       <c r="T99" s="14" t="n"/>
-      <c r="U99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -11071,7 +10971,6 @@
       <c r="R100" s="14" t="n"/>
       <c r="S100" s="14" t="n"/>
       <c r="T100" s="14" t="n"/>
-      <c r="U100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
@@ -11115,7 +11014,6 @@
       <c r="R101" s="14" t="n"/>
       <c r="S101" s="14" t="n"/>
       <c r="T101" s="14" t="n"/>
-      <c r="U101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -11159,7 +11057,6 @@
       <c r="R102" s="14" t="n"/>
       <c r="S102" s="14" t="n"/>
       <c r="T102" s="14" t="n"/>
-      <c r="U102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -11191,13 +11088,13 @@
       </c>
       <c r="G103" s="14" t="n"/>
       <c r="H103" s="14" t="n"/>
-      <c r="I103" s="14" t="n"/>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J103" s="14" t="n"/>
-      <c r="K103" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K103" s="14" t="n"/>
       <c r="L103" s="14" t="n"/>
       <c r="M103" s="14" t="n"/>
       <c r="N103" s="14" t="n"/>
@@ -11207,7 +11104,6 @@
       <c r="R103" s="14" t="n"/>
       <c r="S103" s="14" t="n"/>
       <c r="T103" s="14" t="n"/>
-      <c r="U103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -11251,7 +11147,6 @@
       <c r="R104" s="14" t="n"/>
       <c r="S104" s="14" t="n"/>
       <c r="T104" s="14" t="n"/>
-      <c r="U104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -11283,13 +11178,13 @@
       </c>
       <c r="G105" s="14" t="n"/>
       <c r="H105" s="14" t="n"/>
-      <c r="I105" s="14" t="n"/>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J105" s="14" t="n"/>
-      <c r="K105" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K105" s="14" t="n"/>
       <c r="L105" s="14" t="n"/>
       <c r="M105" s="14" t="n"/>
       <c r="N105" s="14" t="n"/>
@@ -11299,7 +11194,6 @@
       <c r="R105" s="14" t="n"/>
       <c r="S105" s="14" t="n"/>
       <c r="T105" s="14" t="n"/>
-      <c r="U105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -11343,7 +11237,6 @@
       <c r="R106" s="14" t="n"/>
       <c r="S106" s="14" t="n"/>
       <c r="T106" s="14" t="n"/>
-      <c r="U106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -11387,7 +11280,6 @@
       <c r="R107" s="14" t="n"/>
       <c r="S107" s="14" t="n"/>
       <c r="T107" s="14" t="n"/>
-      <c r="U107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -11431,7 +11323,6 @@
       <c r="R108" s="14" t="n"/>
       <c r="S108" s="14" t="n"/>
       <c r="T108" s="14" t="n"/>
-      <c r="U108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -11475,7 +11366,6 @@
       <c r="R109" s="14" t="n"/>
       <c r="S109" s="14" t="n"/>
       <c r="T109" s="14" t="n"/>
-      <c r="U109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -11519,7 +11409,6 @@
       <c r="R110" s="14" t="n"/>
       <c r="S110" s="14" t="n"/>
       <c r="T110" s="14" t="n"/>
-      <c r="U110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -11563,7 +11452,6 @@
       <c r="R111" s="14" t="n"/>
       <c r="S111" s="14" t="n"/>
       <c r="T111" s="14" t="n"/>
-      <c r="U111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -11607,7 +11495,6 @@
       <c r="R112" s="14" t="n"/>
       <c r="S112" s="14" t="n"/>
       <c r="T112" s="14" t="n"/>
-      <c r="U112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -11651,7 +11538,6 @@
       <c r="R113" s="14" t="n"/>
       <c r="S113" s="14" t="n"/>
       <c r="T113" s="14" t="n"/>
-      <c r="U113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
@@ -11695,7 +11581,6 @@
       <c r="R114" s="14" t="n"/>
       <c r="S114" s="14" t="n"/>
       <c r="T114" s="14" t="n"/>
-      <c r="U114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -11739,7 +11624,6 @@
       <c r="R115" s="14" t="n"/>
       <c r="S115" s="14" t="n"/>
       <c r="T115" s="14" t="n"/>
-      <c r="U115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
@@ -11783,7 +11667,6 @@
       <c r="R116" s="14" t="n"/>
       <c r="S116" s="14" t="n"/>
       <c r="T116" s="14" t="n"/>
-      <c r="U116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -11827,7 +11710,6 @@
       <c r="R117" s="14" t="n"/>
       <c r="S117" s="14" t="n"/>
       <c r="T117" s="14" t="n"/>
-      <c r="U117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
@@ -11871,7 +11753,6 @@
       <c r="R118" s="14" t="n"/>
       <c r="S118" s="14" t="n"/>
       <c r="T118" s="14" t="n"/>
-      <c r="U118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
@@ -11915,7 +11796,6 @@
       <c r="R119" s="14" t="n"/>
       <c r="S119" s="14" t="n"/>
       <c r="T119" s="14" t="n"/>
-      <c r="U119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -11959,7 +11839,6 @@
       <c r="R120" s="14" t="n"/>
       <c r="S120" s="14" t="n"/>
       <c r="T120" s="14" t="n"/>
-      <c r="U120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -12003,7 +11882,6 @@
       <c r="R121" s="14" t="n"/>
       <c r="S121" s="14" t="n"/>
       <c r="T121" s="14" t="n"/>
-      <c r="U121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -12047,7 +11925,6 @@
       <c r="R122" s="14" t="n"/>
       <c r="S122" s="14" t="n"/>
       <c r="T122" s="14" t="n"/>
-      <c r="U122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -12091,7 +11968,6 @@
       <c r="R123" s="14" t="n"/>
       <c r="S123" s="14" t="n"/>
       <c r="T123" s="14" t="n"/>
-      <c r="U123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -12135,7 +12011,6 @@
       <c r="R124" s="14" t="n"/>
       <c r="S124" s="14" t="n"/>
       <c r="T124" s="14" t="n"/>
-      <c r="U124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -12179,7 +12054,6 @@
       <c r="R125" s="14" t="n"/>
       <c r="S125" s="14" t="n"/>
       <c r="T125" s="14" t="n"/>
-      <c r="U125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -12223,7 +12097,6 @@
       <c r="R126" s="14" t="n"/>
       <c r="S126" s="14" t="n"/>
       <c r="T126" s="14" t="n"/>
-      <c r="U126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -12267,7 +12140,6 @@
       <c r="R127" s="14" t="n"/>
       <c r="S127" s="14" t="n"/>
       <c r="T127" s="14" t="n"/>
-      <c r="U127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -12311,7 +12183,6 @@
       <c r="R128" s="14" t="n"/>
       <c r="S128" s="14" t="n"/>
       <c r="T128" s="14" t="n"/>
-      <c r="U128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -12355,7 +12226,6 @@
       <c r="R129" s="14" t="n"/>
       <c r="S129" s="14" t="n"/>
       <c r="T129" s="14" t="n"/>
-      <c r="U129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
@@ -12399,7 +12269,6 @@
       <c r="R130" s="14" t="n"/>
       <c r="S130" s="14" t="n"/>
       <c r="T130" s="14" t="n"/>
-      <c r="U130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -12443,7 +12312,6 @@
       <c r="R131" s="14" t="n"/>
       <c r="S131" s="14" t="n"/>
       <c r="T131" s="14" t="n"/>
-      <c r="U131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -12487,7 +12355,6 @@
       <c r="R132" s="14" t="n"/>
       <c r="S132" s="14" t="n"/>
       <c r="T132" s="14" t="n"/>
-      <c r="U132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -12531,7 +12398,6 @@
       <c r="R133" s="14" t="n"/>
       <c r="S133" s="14" t="n"/>
       <c r="T133" s="14" t="n"/>
-      <c r="U133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -12575,7 +12441,6 @@
       <c r="R134" s="14" t="n"/>
       <c r="S134" s="14" t="n"/>
       <c r="T134" s="14" t="n"/>
-      <c r="U134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -12619,7 +12484,6 @@
       <c r="R135" s="14" t="n"/>
       <c r="S135" s="14" t="n"/>
       <c r="T135" s="14" t="n"/>
-      <c r="U135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
@@ -12663,7 +12527,6 @@
       <c r="R136" s="14" t="n"/>
       <c r="S136" s="14" t="n"/>
       <c r="T136" s="14" t="n"/>
-      <c r="U136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -12707,7 +12570,6 @@
       <c r="R137" s="14" t="n"/>
       <c r="S137" s="14" t="n"/>
       <c r="T137" s="14" t="n"/>
-      <c r="U137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -12751,7 +12613,6 @@
       <c r="R138" s="14" t="n"/>
       <c r="S138" s="14" t="n"/>
       <c r="T138" s="14" t="n"/>
-      <c r="U138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -12783,13 +12644,13 @@
       </c>
       <c r="G139" s="14" t="n"/>
       <c r="H139" s="14" t="n"/>
-      <c r="I139" s="14" t="n"/>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J139" s="14" t="n"/>
-      <c r="K139" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K139" s="14" t="n"/>
       <c r="L139" s="14" t="n"/>
       <c r="M139" s="14" t="n"/>
       <c r="N139" s="14" t="n"/>
@@ -12799,7 +12660,6 @@
       <c r="R139" s="14" t="n"/>
       <c r="S139" s="14" t="n"/>
       <c r="T139" s="14" t="n"/>
-      <c r="U139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -12843,7 +12703,6 @@
       <c r="R140" s="14" t="n"/>
       <c r="S140" s="14" t="n"/>
       <c r="T140" s="14" t="n"/>
-      <c r="U140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
@@ -12875,13 +12734,13 @@
       </c>
       <c r="G141" s="14" t="n"/>
       <c r="H141" s="14" t="n"/>
-      <c r="I141" s="14" t="n"/>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J141" s="14" t="n"/>
-      <c r="K141" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K141" s="14" t="n"/>
       <c r="L141" s="14" t="n"/>
       <c r="M141" s="14" t="n"/>
       <c r="N141" s="14" t="n"/>
@@ -12891,7 +12750,6 @@
       <c r="R141" s="14" t="n"/>
       <c r="S141" s="14" t="n"/>
       <c r="T141" s="14" t="n"/>
-      <c r="U141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
@@ -12923,13 +12781,13 @@
       </c>
       <c r="G142" s="14" t="n"/>
       <c r="H142" s="14" t="n"/>
-      <c r="I142" s="14" t="n"/>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J142" s="14" t="n"/>
-      <c r="K142" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K142" s="14" t="n"/>
       <c r="L142" s="14" t="n"/>
       <c r="M142" s="14" t="n"/>
       <c r="N142" s="14" t="n"/>
@@ -12939,7 +12797,6 @@
       <c r="R142" s="14" t="n"/>
       <c r="S142" s="14" t="n"/>
       <c r="T142" s="14" t="n"/>
-      <c r="U142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -12971,13 +12828,13 @@
       </c>
       <c r="G143" s="14" t="n"/>
       <c r="H143" s="14" t="n"/>
-      <c r="I143" s="14" t="n"/>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J143" s="14" t="n"/>
-      <c r="K143" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K143" s="14" t="n"/>
       <c r="L143" s="14" t="n"/>
       <c r="M143" s="14" t="n"/>
       <c r="N143" s="14" t="n"/>
@@ -12987,7 +12844,6 @@
       <c r="R143" s="14" t="n"/>
       <c r="S143" s="14" t="n"/>
       <c r="T143" s="14" t="n"/>
-      <c r="U143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -13019,13 +12875,13 @@
       </c>
       <c r="G144" s="14" t="n"/>
       <c r="H144" s="14" t="n"/>
-      <c r="I144" s="14" t="n"/>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J144" s="14" t="n"/>
-      <c r="K144" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K144" s="14" t="n"/>
       <c r="L144" s="14" t="n"/>
       <c r="M144" s="14" t="n"/>
       <c r="N144" s="14" t="n"/>
@@ -13035,7 +12891,6 @@
       <c r="R144" s="14" t="n"/>
       <c r="S144" s="14" t="n"/>
       <c r="T144" s="14" t="n"/>
-      <c r="U144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -13079,7 +12934,6 @@
       <c r="R145" s="14" t="n"/>
       <c r="S145" s="14" t="n"/>
       <c r="T145" s="14" t="n"/>
-      <c r="U145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
@@ -13123,7 +12977,6 @@
       <c r="R146" s="14" t="n"/>
       <c r="S146" s="14" t="n"/>
       <c r="T146" s="14" t="n"/>
-      <c r="U146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -13155,13 +13008,13 @@
       </c>
       <c r="G147" s="14" t="n"/>
       <c r="H147" s="14" t="n"/>
-      <c r="I147" s="14" t="n"/>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J147" s="14" t="n"/>
-      <c r="K147" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K147" s="14" t="n"/>
       <c r="L147" s="14" t="n"/>
       <c r="M147" s="14" t="n"/>
       <c r="N147" s="14" t="n"/>
@@ -13171,7 +13024,6 @@
       <c r="R147" s="14" t="n"/>
       <c r="S147" s="14" t="n"/>
       <c r="T147" s="14" t="n"/>
-      <c r="U147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -13215,7 +13067,6 @@
       <c r="R148" s="14" t="n"/>
       <c r="S148" s="14" t="n"/>
       <c r="T148" s="14" t="n"/>
-      <c r="U148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -13259,7 +13110,6 @@
       <c r="R149" s="14" t="n"/>
       <c r="S149" s="14" t="n"/>
       <c r="T149" s="14" t="n"/>
-      <c r="U149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
@@ -13303,7 +13153,6 @@
       <c r="R150" s="14" t="n"/>
       <c r="S150" s="14" t="n"/>
       <c r="T150" s="14" t="n"/>
-      <c r="U150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -13347,7 +13196,6 @@
       <c r="R151" s="14" t="n"/>
       <c r="S151" s="14" t="n"/>
       <c r="T151" s="14" t="n"/>
-      <c r="U151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -13391,7 +13239,6 @@
       <c r="R152" s="14" t="n"/>
       <c r="S152" s="14" t="n"/>
       <c r="T152" s="14" t="n"/>
-      <c r="U152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -13435,7 +13282,6 @@
       <c r="R153" s="14" t="n"/>
       <c r="S153" s="14" t="n"/>
       <c r="T153" s="14" t="n"/>
-      <c r="U153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -13467,13 +13313,13 @@
       </c>
       <c r="G154" s="14" t="n"/>
       <c r="H154" s="14" t="n"/>
-      <c r="I154" s="14" t="n"/>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J154" s="14" t="n"/>
-      <c r="K154" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K154" s="14" t="n"/>
       <c r="L154" s="14" t="n"/>
       <c r="M154" s="14" t="n"/>
       <c r="N154" s="14" t="n"/>
@@ -13483,7 +13329,6 @@
       <c r="R154" s="14" t="n"/>
       <c r="S154" s="14" t="n"/>
       <c r="T154" s="14" t="n"/>
-      <c r="U154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
@@ -13527,7 +13372,6 @@
       <c r="R155" s="14" t="n"/>
       <c r="S155" s="14" t="n"/>
       <c r="T155" s="14" t="n"/>
-      <c r="U155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
@@ -13571,7 +13415,6 @@
       <c r="R156" s="14" t="n"/>
       <c r="S156" s="14" t="n"/>
       <c r="T156" s="14" t="n"/>
-      <c r="U156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
@@ -13603,13 +13446,13 @@
       </c>
       <c r="G157" s="14" t="n"/>
       <c r="H157" s="14" t="n"/>
-      <c r="I157" s="14" t="n"/>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J157" s="14" t="n"/>
-      <c r="K157" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K157" s="14" t="n"/>
       <c r="L157" s="14" t="n"/>
       <c r="M157" s="14" t="n"/>
       <c r="N157" s="14" t="n"/>
@@ -13619,7 +13462,6 @@
       <c r="R157" s="14" t="n"/>
       <c r="S157" s="14" t="n"/>
       <c r="T157" s="14" t="n"/>
-      <c r="U157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
@@ -13663,7 +13505,6 @@
       <c r="R158" s="14" t="n"/>
       <c r="S158" s="14" t="n"/>
       <c r="T158" s="14" t="n"/>
-      <c r="U158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
@@ -13707,7 +13548,6 @@
       <c r="R159" s="14" t="n"/>
       <c r="S159" s="14" t="n"/>
       <c r="T159" s="14" t="n"/>
-      <c r="U159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
@@ -13739,13 +13579,13 @@
       </c>
       <c r="G160" s="14" t="n"/>
       <c r="H160" s="14" t="n"/>
-      <c r="I160" s="14" t="n"/>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J160" s="14" t="n"/>
-      <c r="K160" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K160" s="14" t="n"/>
       <c r="L160" s="14" t="n"/>
       <c r="M160" s="14" t="n"/>
       <c r="N160" s="14" t="n"/>
@@ -13755,7 +13595,6 @@
       <c r="R160" s="14" t="n"/>
       <c r="S160" s="14" t="n"/>
       <c r="T160" s="14" t="n"/>
-      <c r="U160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
@@ -13787,13 +13626,13 @@
       </c>
       <c r="G161" s="14" t="n"/>
       <c r="H161" s="14" t="n"/>
-      <c r="I161" s="14" t="n"/>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J161" s="14" t="n"/>
-      <c r="K161" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K161" s="14" t="n"/>
       <c r="L161" s="14" t="n"/>
       <c r="M161" s="14" t="n"/>
       <c r="N161" s="14" t="n"/>
@@ -13803,7 +13642,6 @@
       <c r="R161" s="14" t="n"/>
       <c r="S161" s="14" t="n"/>
       <c r="T161" s="14" t="n"/>
-      <c r="U161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
@@ -13847,7 +13685,6 @@
       <c r="R162" s="14" t="n"/>
       <c r="S162" s="14" t="n"/>
       <c r="T162" s="14" t="n"/>
-      <c r="U162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
@@ -13891,7 +13728,6 @@
       <c r="R163" s="14" t="n"/>
       <c r="S163" s="14" t="n"/>
       <c r="T163" s="14" t="n"/>
-      <c r="U163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
@@ -13923,13 +13759,13 @@
       </c>
       <c r="G164" s="14" t="n"/>
       <c r="H164" s="14" t="n"/>
-      <c r="I164" s="14" t="n"/>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J164" s="14" t="n"/>
-      <c r="K164" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K164" s="14" t="n"/>
       <c r="L164" s="14" t="n"/>
       <c r="M164" s="14" t="n"/>
       <c r="N164" s="14" t="n"/>
@@ -13939,7 +13775,6 @@
       <c r="R164" s="14" t="n"/>
       <c r="S164" s="14" t="n"/>
       <c r="T164" s="14" t="n"/>
-      <c r="U164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
@@ -13983,7 +13818,6 @@
       <c r="R165" s="14" t="n"/>
       <c r="S165" s="14" t="n"/>
       <c r="T165" s="14" t="n"/>
-      <c r="U165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
@@ -14027,7 +13861,6 @@
       <c r="R166" s="14" t="n"/>
       <c r="S166" s="14" t="n"/>
       <c r="T166" s="14" t="n"/>
-      <c r="U166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
@@ -14059,13 +13892,13 @@
       </c>
       <c r="G167" s="14" t="n"/>
       <c r="H167" s="14" t="n"/>
-      <c r="I167" s="14" t="n"/>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J167" s="14" t="n"/>
-      <c r="K167" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K167" s="14" t="n"/>
       <c r="L167" s="14" t="n"/>
       <c r="M167" s="14" t="n"/>
       <c r="N167" s="14" t="n"/>
@@ -14075,7 +13908,6 @@
       <c r="R167" s="14" t="n"/>
       <c r="S167" s="14" t="n"/>
       <c r="T167" s="14" t="n"/>
-      <c r="U167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -14119,7 +13951,6 @@
       <c r="R168" s="14" t="n"/>
       <c r="S168" s="14" t="n"/>
       <c r="T168" s="14" t="n"/>
-      <c r="U168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
@@ -14163,7 +13994,6 @@
       <c r="R169" s="14" t="n"/>
       <c r="S169" s="14" t="n"/>
       <c r="T169" s="14" t="n"/>
-      <c r="U169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -14195,13 +14025,13 @@
       </c>
       <c r="G170" s="14" t="n"/>
       <c r="H170" s="14" t="n"/>
-      <c r="I170" s="14" t="n"/>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J170" s="14" t="n"/>
-      <c r="K170" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K170" s="14" t="n"/>
       <c r="L170" s="14" t="n"/>
       <c r="M170" s="14" t="n"/>
       <c r="N170" s="14" t="n"/>
@@ -14211,7 +14041,6 @@
       <c r="R170" s="14" t="n"/>
       <c r="S170" s="14" t="n"/>
       <c r="T170" s="14" t="n"/>
-      <c r="U170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
@@ -14255,7 +14084,6 @@
       <c r="R171" s="14" t="n"/>
       <c r="S171" s="14" t="n"/>
       <c r="T171" s="14" t="n"/>
-      <c r="U171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -14299,7 +14127,6 @@
       <c r="R172" s="14" t="n"/>
       <c r="S172" s="14" t="n"/>
       <c r="T172" s="14" t="n"/>
-      <c r="U172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -14331,13 +14158,13 @@
       </c>
       <c r="G173" s="14" t="n"/>
       <c r="H173" s="14" t="n"/>
-      <c r="I173" s="14" t="n"/>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J173" s="14" t="n"/>
-      <c r="K173" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K173" s="14" t="n"/>
       <c r="L173" s="14" t="n"/>
       <c r="M173" s="14" t="n"/>
       <c r="N173" s="14" t="n"/>
@@ -14347,7 +14174,6 @@
       <c r="R173" s="14" t="n"/>
       <c r="S173" s="14" t="n"/>
       <c r="T173" s="14" t="n"/>
-      <c r="U173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
@@ -14391,7 +14217,6 @@
       <c r="R174" s="14" t="n"/>
       <c r="S174" s="14" t="n"/>
       <c r="T174" s="14" t="n"/>
-      <c r="U174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -14435,7 +14260,6 @@
       <c r="R175" s="14" t="n"/>
       <c r="S175" s="14" t="n"/>
       <c r="T175" s="14" t="n"/>
-      <c r="U175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
@@ -14479,7 +14303,6 @@
       <c r="R176" s="14" t="n"/>
       <c r="S176" s="14" t="n"/>
       <c r="T176" s="14" t="n"/>
-      <c r="U176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -14511,13 +14334,13 @@
       </c>
       <c r="G177" s="14" t="n"/>
       <c r="H177" s="14" t="n"/>
-      <c r="I177" s="14" t="n"/>
+      <c r="I177" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J177" s="14" t="n"/>
-      <c r="K177" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K177" s="14" t="n"/>
       <c r="L177" s="14" t="n"/>
       <c r="M177" s="14" t="n"/>
       <c r="N177" s="14" t="n"/>
@@ -14527,7 +14350,6 @@
       <c r="R177" s="14" t="n"/>
       <c r="S177" s="14" t="n"/>
       <c r="T177" s="14" t="n"/>
-      <c r="U177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -14559,13 +14381,13 @@
       </c>
       <c r="G178" s="14" t="n"/>
       <c r="H178" s="14" t="n"/>
-      <c r="I178" s="14" t="n"/>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J178" s="14" t="n"/>
-      <c r="K178" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K178" s="14" t="n"/>
       <c r="L178" s="14" t="n"/>
       <c r="M178" s="14" t="n"/>
       <c r="N178" s="14" t="n"/>
@@ -14575,7 +14397,6 @@
       <c r="R178" s="14" t="n"/>
       <c r="S178" s="14" t="n"/>
       <c r="T178" s="14" t="n"/>
-      <c r="U178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -14619,7 +14440,6 @@
       <c r="R179" s="14" t="n"/>
       <c r="S179" s="14" t="n"/>
       <c r="T179" s="14" t="n"/>
-      <c r="U179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
@@ -14663,7 +14483,6 @@
       <c r="R180" s="14" t="n"/>
       <c r="S180" s="14" t="n"/>
       <c r="T180" s="14" t="n"/>
-      <c r="U180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
@@ -14707,7 +14526,6 @@
       <c r="R181" s="14" t="n"/>
       <c r="S181" s="14" t="n"/>
       <c r="T181" s="14" t="n"/>
-      <c r="U181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
@@ -14751,7 +14569,6 @@
       <c r="R182" s="14" t="n"/>
       <c r="S182" s="14" t="n"/>
       <c r="T182" s="14" t="n"/>
-      <c r="U182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
@@ -14795,7 +14612,6 @@
       <c r="R183" s="14" t="n"/>
       <c r="S183" s="14" t="n"/>
       <c r="T183" s="14" t="n"/>
-      <c r="U183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
@@ -14839,7 +14655,6 @@
       <c r="R184" s="14" t="n"/>
       <c r="S184" s="14" t="n"/>
       <c r="T184" s="14" t="n"/>
-      <c r="U184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
@@ -14883,7 +14698,6 @@
       <c r="R185" s="14" t="n"/>
       <c r="S185" s="14" t="n"/>
       <c r="T185" s="14" t="n"/>
-      <c r="U185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
@@ -14927,7 +14741,6 @@
       <c r="R186" s="14" t="n"/>
       <c r="S186" s="14" t="n"/>
       <c r="T186" s="14" t="n"/>
-      <c r="U186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
@@ -14971,7 +14784,6 @@
       <c r="R187" s="14" t="n"/>
       <c r="S187" s="14" t="n"/>
       <c r="T187" s="14" t="n"/>
-      <c r="U187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -15015,7 +14827,6 @@
       <c r="R188" s="14" t="n"/>
       <c r="S188" s="14" t="n"/>
       <c r="T188" s="14" t="n"/>
-      <c r="U188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -15047,13 +14858,13 @@
       </c>
       <c r="G189" s="14" t="n"/>
       <c r="H189" s="14" t="n"/>
-      <c r="I189" s="14" t="n"/>
+      <c r="I189" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J189" s="14" t="n"/>
-      <c r="K189" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K189" s="14" t="n"/>
       <c r="L189" s="14" t="n"/>
       <c r="M189" s="14" t="n"/>
       <c r="N189" s="14" t="n"/>
@@ -15063,7 +14874,6 @@
       <c r="R189" s="14" t="n"/>
       <c r="S189" s="14" t="n"/>
       <c r="T189" s="14" t="n"/>
-      <c r="U189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
@@ -15107,7 +14917,6 @@
       <c r="R190" s="14" t="n"/>
       <c r="S190" s="14" t="n"/>
       <c r="T190" s="14" t="n"/>
-      <c r="U190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -15151,7 +14960,6 @@
       <c r="R191" s="14" t="n"/>
       <c r="S191" s="14" t="n"/>
       <c r="T191" s="14" t="n"/>
-      <c r="U191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -15195,7 +15003,6 @@
       <c r="R192" s="14" t="n"/>
       <c r="S192" s="14" t="n"/>
       <c r="T192" s="14" t="n"/>
-      <c r="U192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -15227,13 +15034,13 @@
       </c>
       <c r="G193" s="14" t="n"/>
       <c r="H193" s="14" t="n"/>
-      <c r="I193" s="14" t="n"/>
+      <c r="I193" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J193" s="14" t="n"/>
-      <c r="K193" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K193" s="14" t="n"/>
       <c r="L193" s="14" t="n"/>
       <c r="M193" s="14" t="n"/>
       <c r="N193" s="14" t="n"/>
@@ -15243,7 +15050,6 @@
       <c r="R193" s="14" t="n"/>
       <c r="S193" s="14" t="n"/>
       <c r="T193" s="14" t="n"/>
-      <c r="U193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -15287,7 +15093,6 @@
       <c r="R194" s="14" t="n"/>
       <c r="S194" s="14" t="n"/>
       <c r="T194" s="14" t="n"/>
-      <c r="U194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
@@ -15331,7 +15136,6 @@
       <c r="R195" s="14" t="n"/>
       <c r="S195" s="14" t="n"/>
       <c r="T195" s="14" t="n"/>
-      <c r="U195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
@@ -15375,7 +15179,6 @@
       <c r="R196" s="14" t="n"/>
       <c r="S196" s="14" t="n"/>
       <c r="T196" s="14" t="n"/>
-      <c r="U196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
@@ -15407,13 +15210,13 @@
       </c>
       <c r="G197" s="14" t="n"/>
       <c r="H197" s="14" t="n"/>
-      <c r="I197" s="14" t="n"/>
+      <c r="I197" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J197" s="14" t="n"/>
-      <c r="K197" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K197" s="14" t="n"/>
       <c r="L197" s="14" t="n"/>
       <c r="M197" s="14" t="n"/>
       <c r="N197" s="14" t="n"/>
@@ -15423,7 +15226,6 @@
       <c r="R197" s="14" t="n"/>
       <c r="S197" s="14" t="n"/>
       <c r="T197" s="14" t="n"/>
-      <c r="U197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
@@ -15455,13 +15257,13 @@
       </c>
       <c r="G198" s="14" t="n"/>
       <c r="H198" s="14" t="n"/>
-      <c r="I198" s="14" t="n"/>
+      <c r="I198" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J198" s="14" t="n"/>
-      <c r="K198" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K198" s="14" t="n"/>
       <c r="L198" s="14" t="n"/>
       <c r="M198" s="14" t="n"/>
       <c r="N198" s="14" t="n"/>
@@ -15471,7 +15273,6 @@
       <c r="R198" s="14" t="n"/>
       <c r="S198" s="14" t="n"/>
       <c r="T198" s="14" t="n"/>
-      <c r="U198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
@@ -15515,7 +15316,6 @@
       <c r="R199" s="14" t="n"/>
       <c r="S199" s="14" t="n"/>
       <c r="T199" s="14" t="n"/>
-      <c r="U199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
@@ -15559,7 +15359,6 @@
       <c r="R200" s="14" t="n"/>
       <c r="S200" s="14" t="n"/>
       <c r="T200" s="14" t="n"/>
-      <c r="U200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
@@ -15603,7 +15402,6 @@
       <c r="R201" s="14" t="n"/>
       <c r="S201" s="14" t="n"/>
       <c r="T201" s="14" t="n"/>
-      <c r="U201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
@@ -15647,7 +15445,6 @@
       <c r="R202" s="14" t="n"/>
       <c r="S202" s="14" t="n"/>
       <c r="T202" s="14" t="n"/>
-      <c r="U202" s="14" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
@@ -15691,7 +15488,6 @@
       <c r="R203" s="14" t="n"/>
       <c r="S203" s="14" t="n"/>
       <c r="T203" s="14" t="n"/>
-      <c r="U203" s="14" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
@@ -15735,7 +15531,6 @@
       <c r="R204" s="14" t="n"/>
       <c r="S204" s="14" t="n"/>
       <c r="T204" s="14" t="n"/>
-      <c r="U204" s="14" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
@@ -15779,7 +15574,6 @@
       <c r="R205" s="14" t="n"/>
       <c r="S205" s="14" t="n"/>
       <c r="T205" s="14" t="n"/>
-      <c r="U205" s="14" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -15823,7 +15617,6 @@
       <c r="R206" s="14" t="n"/>
       <c r="S206" s="14" t="n"/>
       <c r="T206" s="14" t="n"/>
-      <c r="U206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -15867,7 +15660,6 @@
       <c r="R207" s="14" t="n"/>
       <c r="S207" s="14" t="n"/>
       <c r="T207" s="14" t="n"/>
-      <c r="U207" s="14" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -15911,7 +15703,6 @@
       <c r="R208" s="14" t="n"/>
       <c r="S208" s="14" t="n"/>
       <c r="T208" s="14" t="n"/>
-      <c r="U208" s="14" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -15955,7 +15746,6 @@
       <c r="R209" s="14" t="n"/>
       <c r="S209" s="14" t="n"/>
       <c r="T209" s="14" t="n"/>
-      <c r="U209" s="14" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
@@ -15999,7 +15789,6 @@
       <c r="R210" s="14" t="n"/>
       <c r="S210" s="14" t="n"/>
       <c r="T210" s="14" t="n"/>
-      <c r="U210" s="14" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
@@ -16043,7 +15832,6 @@
       <c r="R211" s="14" t="n"/>
       <c r="S211" s="14" t="n"/>
       <c r="T211" s="14" t="n"/>
-      <c r="U211" s="14" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
@@ -16087,7 +15875,6 @@
       <c r="R212" s="14" t="n"/>
       <c r="S212" s="14" t="n"/>
       <c r="T212" s="14" t="n"/>
-      <c r="U212" s="14" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -16131,7 +15918,6 @@
       <c r="R213" s="14" t="n"/>
       <c r="S213" s="14" t="n"/>
       <c r="T213" s="14" t="n"/>
-      <c r="U213" s="14" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -16175,7 +15961,6 @@
       <c r="R214" s="14" t="n"/>
       <c r="S214" s="14" t="n"/>
       <c r="T214" s="14" t="n"/>
-      <c r="U214" s="14" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
@@ -16219,7 +16004,6 @@
       <c r="R215" s="14" t="n"/>
       <c r="S215" s="14" t="n"/>
       <c r="T215" s="14" t="n"/>
-      <c r="U215" s="14" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
@@ -16263,7 +16047,6 @@
       <c r="R216" s="14" t="n"/>
       <c r="S216" s="14" t="n"/>
       <c r="T216" s="14" t="n"/>
-      <c r="U216" s="14" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -16307,7 +16090,6 @@
       <c r="R217" s="14" t="n"/>
       <c r="S217" s="14" t="n"/>
       <c r="T217" s="14" t="n"/>
-      <c r="U217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
@@ -16351,7 +16133,6 @@
       <c r="R218" s="14" t="n"/>
       <c r="S218" s="14" t="n"/>
       <c r="T218" s="14" t="n"/>
-      <c r="U218" s="14" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
@@ -16395,7 +16176,6 @@
       <c r="R219" s="14" t="n"/>
       <c r="S219" s="14" t="n"/>
       <c r="T219" s="14" t="n"/>
-      <c r="U219" s="14" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
@@ -16439,7 +16219,6 @@
       <c r="R220" s="14" t="n"/>
       <c r="S220" s="14" t="n"/>
       <c r="T220" s="14" t="n"/>
-      <c r="U220" s="14" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
@@ -16483,7 +16262,6 @@
       <c r="R221" s="14" t="n"/>
       <c r="S221" s="14" t="n"/>
       <c r="T221" s="14" t="n"/>
-      <c r="U221" s="14" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
@@ -16527,7 +16305,6 @@
       <c r="R222" s="14" t="n"/>
       <c r="S222" s="14" t="n"/>
       <c r="T222" s="14" t="n"/>
-      <c r="U222" s="14" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
@@ -16571,7 +16348,6 @@
       <c r="R223" s="14" t="n"/>
       <c r="S223" s="14" t="n"/>
       <c r="T223" s="14" t="n"/>
-      <c r="U223" s="14" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
@@ -16615,7 +16391,6 @@
       <c r="R224" s="14" t="n"/>
       <c r="S224" s="14" t="n"/>
       <c r="T224" s="14" t="n"/>
-      <c r="U224" s="14" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
@@ -16659,7 +16434,6 @@
       <c r="R225" s="14" t="n"/>
       <c r="S225" s="14" t="n"/>
       <c r="T225" s="14" t="n"/>
-      <c r="U225" s="14" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
@@ -16703,7 +16477,6 @@
       <c r="R226" s="14" t="n"/>
       <c r="S226" s="14" t="n"/>
       <c r="T226" s="14" t="n"/>
-      <c r="U226" s="14" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
@@ -16747,7 +16520,6 @@
       <c r="R227" s="14" t="n"/>
       <c r="S227" s="14" t="n"/>
       <c r="T227" s="14" t="n"/>
-      <c r="U227" s="14" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
@@ -16791,7 +16563,6 @@
       <c r="R228" s="14" t="n"/>
       <c r="S228" s="14" t="n"/>
       <c r="T228" s="14" t="n"/>
-      <c r="U228" s="14" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
@@ -16835,7 +16606,6 @@
       <c r="R229" s="14" t="n"/>
       <c r="S229" s="14" t="n"/>
       <c r="T229" s="14" t="n"/>
-      <c r="U229" s="14" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
@@ -16879,7 +16649,6 @@
       <c r="R230" s="14" t="n"/>
       <c r="S230" s="14" t="n"/>
       <c r="T230" s="14" t="n"/>
-      <c r="U230" s="14" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
@@ -16923,7 +16692,6 @@
       <c r="R231" s="14" t="n"/>
       <c r="S231" s="14" t="n"/>
       <c r="T231" s="14" t="n"/>
-      <c r="U231" s="14" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
@@ -16967,7 +16735,6 @@
       <c r="R232" s="14" t="n"/>
       <c r="S232" s="14" t="n"/>
       <c r="T232" s="14" t="n"/>
-      <c r="U232" s="14" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
@@ -17011,7 +16778,6 @@
       <c r="R233" s="14" t="n"/>
       <c r="S233" s="14" t="n"/>
       <c r="T233" s="14" t="n"/>
-      <c r="U233" s="14" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
@@ -17055,7 +16821,6 @@
       <c r="R234" s="14" t="n"/>
       <c r="S234" s="14" t="n"/>
       <c r="T234" s="14" t="n"/>
-      <c r="U234" s="14" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
@@ -17099,7 +16864,6 @@
       <c r="R235" s="14" t="n"/>
       <c r="S235" s="14" t="n"/>
       <c r="T235" s="14" t="n"/>
-      <c r="U235" s="14" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
@@ -17143,7 +16907,6 @@
       <c r="R236" s="14" t="n"/>
       <c r="S236" s="14" t="n"/>
       <c r="T236" s="14" t="n"/>
-      <c r="U236" s="14" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
@@ -17187,7 +16950,6 @@
       <c r="R237" s="14" t="n"/>
       <c r="S237" s="14" t="n"/>
       <c r="T237" s="14" t="n"/>
-      <c r="U237" s="14" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
@@ -17231,7 +16993,6 @@
       <c r="R238" s="14" t="n"/>
       <c r="S238" s="14" t="n"/>
       <c r="T238" s="14" t="n"/>
-      <c r="U238" s="14" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
@@ -17275,7 +17036,6 @@
       <c r="R239" s="14" t="n"/>
       <c r="S239" s="14" t="n"/>
       <c r="T239" s="14" t="n"/>
-      <c r="U239" s="14" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
@@ -17319,7 +17079,6 @@
       <c r="R240" s="14" t="n"/>
       <c r="S240" s="14" t="n"/>
       <c r="T240" s="14" t="n"/>
-      <c r="U240" s="14" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
@@ -17363,7 +17122,6 @@
       <c r="R241" s="14" t="n"/>
       <c r="S241" s="14" t="n"/>
       <c r="T241" s="14" t="n"/>
-      <c r="U241" s="14" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
@@ -17407,7 +17165,6 @@
       <c r="R242" s="14" t="n"/>
       <c r="S242" s="14" t="n"/>
       <c r="T242" s="14" t="n"/>
-      <c r="U242" s="14" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
@@ -17451,7 +17208,6 @@
       <c r="R243" s="14" t="n"/>
       <c r="S243" s="14" t="n"/>
       <c r="T243" s="14" t="n"/>
-      <c r="U243" s="14" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
@@ -17495,7 +17251,6 @@
       <c r="R244" s="14" t="n"/>
       <c r="S244" s="14" t="n"/>
       <c r="T244" s="14" t="n"/>
-      <c r="U244" s="14" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
@@ -17539,7 +17294,6 @@
       <c r="R245" s="14" t="n"/>
       <c r="S245" s="14" t="n"/>
       <c r="T245" s="14" t="n"/>
-      <c r="U245" s="14" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
@@ -17571,13 +17325,13 @@
       </c>
       <c r="G246" s="14" t="n"/>
       <c r="H246" s="14" t="n"/>
-      <c r="I246" s="14" t="n"/>
+      <c r="I246" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J246" s="14" t="n"/>
-      <c r="K246" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K246" s="14" t="n"/>
       <c r="L246" s="14" t="n"/>
       <c r="M246" s="14" t="n"/>
       <c r="N246" s="14" t="n"/>
@@ -17587,7 +17341,6 @@
       <c r="R246" s="14" t="n"/>
       <c r="S246" s="14" t="n"/>
       <c r="T246" s="14" t="n"/>
-      <c r="U246" s="14" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
@@ -17631,7 +17384,6 @@
       <c r="R247" s="14" t="n"/>
       <c r="S247" s="14" t="n"/>
       <c r="T247" s="14" t="n"/>
-      <c r="U247" s="14" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
@@ -17675,7 +17427,6 @@
       <c r="R248" s="14" t="n"/>
       <c r="S248" s="14" t="n"/>
       <c r="T248" s="14" t="n"/>
-      <c r="U248" s="14" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
@@ -17719,7 +17470,6 @@
       <c r="R249" s="14" t="n"/>
       <c r="S249" s="14" t="n"/>
       <c r="T249" s="14" t="n"/>
-      <c r="U249" s="14" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
@@ -17763,7 +17513,6 @@
       <c r="R250" s="14" t="n"/>
       <c r="S250" s="14" t="n"/>
       <c r="T250" s="14" t="n"/>
-      <c r="U250" s="14" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
@@ -17807,7 +17556,6 @@
       <c r="R251" s="14" t="n"/>
       <c r="S251" s="14" t="n"/>
       <c r="T251" s="14" t="n"/>
-      <c r="U251" s="14" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
@@ -17851,7 +17599,6 @@
       <c r="R252" s="14" t="n"/>
       <c r="S252" s="14" t="n"/>
       <c r="T252" s="14" t="n"/>
-      <c r="U252" s="14" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
@@ -17895,7 +17642,6 @@
       <c r="R253" s="14" t="n"/>
       <c r="S253" s="14" t="n"/>
       <c r="T253" s="14" t="n"/>
-      <c r="U253" s="14" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
@@ -17939,7 +17685,6 @@
       <c r="R254" s="14" t="n"/>
       <c r="S254" s="14" t="n"/>
       <c r="T254" s="14" t="n"/>
-      <c r="U254" s="14" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
@@ -17983,7 +17728,6 @@
       <c r="R255" s="14" t="n"/>
       <c r="S255" s="14" t="n"/>
       <c r="T255" s="14" t="n"/>
-      <c r="U255" s="14" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
@@ -18027,7 +17771,6 @@
       <c r="R256" s="14" t="n"/>
       <c r="S256" s="14" t="n"/>
       <c r="T256" s="14" t="n"/>
-      <c r="U256" s="14" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
@@ -18071,7 +17814,6 @@
       <c r="R257" s="14" t="n"/>
       <c r="S257" s="14" t="n"/>
       <c r="T257" s="14" t="n"/>
-      <c r="U257" s="14" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
@@ -18115,7 +17857,6 @@
       <c r="R258" s="14" t="n"/>
       <c r="S258" s="14" t="n"/>
       <c r="T258" s="14" t="n"/>
-      <c r="U258" s="14" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
@@ -18159,7 +17900,6 @@
       <c r="R259" s="14" t="n"/>
       <c r="S259" s="14" t="n"/>
       <c r="T259" s="14" t="n"/>
-      <c r="U259" s="14" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
@@ -18203,7 +17943,6 @@
       <c r="R260" s="14" t="n"/>
       <c r="S260" s="14" t="n"/>
       <c r="T260" s="14" t="n"/>
-      <c r="U260" s="14" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
@@ -18247,7 +17986,6 @@
       <c r="R261" s="14" t="n"/>
       <c r="S261" s="14" t="n"/>
       <c r="T261" s="14" t="n"/>
-      <c r="U261" s="14" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
@@ -18291,7 +18029,6 @@
       <c r="R262" s="14" t="n"/>
       <c r="S262" s="14" t="n"/>
       <c r="T262" s="14" t="n"/>
-      <c r="U262" s="14" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
@@ -18335,7 +18072,6 @@
       <c r="R263" s="14" t="n"/>
       <c r="S263" s="14" t="n"/>
       <c r="T263" s="14" t="n"/>
-      <c r="U263" s="14" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
@@ -18379,7 +18115,6 @@
       <c r="R264" s="14" t="n"/>
       <c r="S264" s="14" t="n"/>
       <c r="T264" s="14" t="n"/>
-      <c r="U264" s="14" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
@@ -18423,7 +18158,6 @@
       <c r="R265" s="14" t="n"/>
       <c r="S265" s="14" t="n"/>
       <c r="T265" s="14" t="n"/>
-      <c r="U265" s="14" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
@@ -18467,7 +18201,6 @@
       <c r="R266" s="14" t="n"/>
       <c r="S266" s="14" t="n"/>
       <c r="T266" s="14" t="n"/>
-      <c r="U266" s="14" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
@@ -18511,7 +18244,6 @@
       <c r="R267" s="14" t="n"/>
       <c r="S267" s="14" t="n"/>
       <c r="T267" s="14" t="n"/>
-      <c r="U267" s="14" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
@@ -18555,7 +18287,6 @@
       <c r="R268" s="14" t="n"/>
       <c r="S268" s="14" t="n"/>
       <c r="T268" s="14" t="n"/>
-      <c r="U268" s="14" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
@@ -18599,7 +18330,6 @@
       <c r="R269" s="14" t="n"/>
       <c r="S269" s="14" t="n"/>
       <c r="T269" s="14" t="n"/>
-      <c r="U269" s="14" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
@@ -18643,7 +18373,6 @@
       <c r="R270" s="14" t="n"/>
       <c r="S270" s="14" t="n"/>
       <c r="T270" s="14" t="n"/>
-      <c r="U270" s="14" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
@@ -18687,7 +18416,6 @@
       <c r="R271" s="14" t="n"/>
       <c r="S271" s="14" t="n"/>
       <c r="T271" s="14" t="n"/>
-      <c r="U271" s="14" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
@@ -18731,7 +18459,6 @@
       <c r="R272" s="14" t="n"/>
       <c r="S272" s="14" t="n"/>
       <c r="T272" s="14" t="n"/>
-      <c r="U272" s="14" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
@@ -18775,7 +18502,6 @@
       <c r="R273" s="14" t="n"/>
       <c r="S273" s="14" t="n"/>
       <c r="T273" s="14" t="n"/>
-      <c r="U273" s="14" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
@@ -18819,7 +18545,6 @@
       <c r="R274" s="14" t="n"/>
       <c r="S274" s="14" t="n"/>
       <c r="T274" s="14" t="n"/>
-      <c r="U274" s="14" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
@@ -18863,7 +18588,6 @@
       <c r="R275" s="14" t="n"/>
       <c r="S275" s="14" t="n"/>
       <c r="T275" s="14" t="n"/>
-      <c r="U275" s="14" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
@@ -18907,7 +18631,6 @@
       <c r="R276" s="14" t="n"/>
       <c r="S276" s="14" t="n"/>
       <c r="T276" s="14" t="n"/>
-      <c r="U276" s="14" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
@@ -18951,7 +18674,6 @@
       <c r="R277" s="14" t="n"/>
       <c r="S277" s="14" t="n"/>
       <c r="T277" s="14" t="n"/>
-      <c r="U277" s="14" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
@@ -18995,7 +18717,6 @@
       <c r="R278" s="14" t="n"/>
       <c r="S278" s="14" t="n"/>
       <c r="T278" s="14" t="n"/>
-      <c r="U278" s="14" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
@@ -19039,7 +18760,6 @@
       <c r="R279" s="14" t="n"/>
       <c r="S279" s="14" t="n"/>
       <c r="T279" s="14" t="n"/>
-      <c r="U279" s="14" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
@@ -19083,7 +18803,6 @@
       <c r="R280" s="14" t="n"/>
       <c r="S280" s="14" t="n"/>
       <c r="T280" s="14" t="n"/>
-      <c r="U280" s="14" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
@@ -19127,7 +18846,6 @@
       <c r="R281" s="14" t="n"/>
       <c r="S281" s="14" t="n"/>
       <c r="T281" s="14" t="n"/>
-      <c r="U281" s="14" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
@@ -19171,7 +18889,6 @@
       <c r="R282" s="14" t="n"/>
       <c r="S282" s="14" t="n"/>
       <c r="T282" s="14" t="n"/>
-      <c r="U282" s="14" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
@@ -19215,7 +18932,6 @@
       <c r="R283" s="14" t="n"/>
       <c r="S283" s="14" t="n"/>
       <c r="T283" s="14" t="n"/>
-      <c r="U283" s="14" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
@@ -19259,7 +18975,6 @@
       <c r="R284" s="14" t="n"/>
       <c r="S284" s="14" t="n"/>
       <c r="T284" s="14" t="n"/>
-      <c r="U284" s="14" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
@@ -19303,7 +19018,6 @@
       <c r="R285" s="14" t="n"/>
       <c r="S285" s="14" t="n"/>
       <c r="T285" s="14" t="n"/>
-      <c r="U285" s="14" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
@@ -19347,7 +19061,6 @@
       <c r="R286" s="14" t="n"/>
       <c r="S286" s="14" t="n"/>
       <c r="T286" s="14" t="n"/>
-      <c r="U286" s="14" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
@@ -19391,7 +19104,6 @@
       <c r="R287" s="14" t="n"/>
       <c r="S287" s="14" t="n"/>
       <c r="T287" s="14" t="n"/>
-      <c r="U287" s="14" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
@@ -19435,7 +19147,6 @@
       <c r="R288" s="14" t="n"/>
       <c r="S288" s="14" t="n"/>
       <c r="T288" s="14" t="n"/>
-      <c r="U288" s="14" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
@@ -19467,13 +19178,13 @@
       </c>
       <c r="G289" s="14" t="n"/>
       <c r="H289" s="14" t="n"/>
-      <c r="I289" s="14" t="n"/>
+      <c r="I289" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J289" s="14" t="n"/>
-      <c r="K289" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="K289" s="14" t="n"/>
       <c r="L289" s="14" t="n"/>
       <c r="M289" s="14" t="n"/>
       <c r="N289" s="14" t="n"/>
@@ -19483,7 +19194,6 @@
       <c r="R289" s="14" t="n"/>
       <c r="S289" s="14" t="n"/>
       <c r="T289" s="14" t="n"/>
-      <c r="U289" s="14" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
@@ -19527,7 +19237,6 @@
       <c r="R290" s="14" t="n"/>
       <c r="S290" s="14" t="n"/>
       <c r="T290" s="14" t="n"/>
-      <c r="U290" s="14" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
@@ -19571,7 +19280,6 @@
       <c r="R291" s="14" t="n"/>
       <c r="S291" s="14" t="n"/>
       <c r="T291" s="14" t="n"/>
-      <c r="U291" s="14" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
@@ -19615,7 +19323,6 @@
       <c r="R292" s="14" t="n"/>
       <c r="S292" s="14" t="n"/>
       <c r="T292" s="14" t="n"/>
-      <c r="U292" s="14" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
@@ -19659,7 +19366,6 @@
       <c r="R293" s="14" t="n"/>
       <c r="S293" s="14" t="n"/>
       <c r="T293" s="14" t="n"/>
-      <c r="U293" s="14" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
@@ -19703,7 +19409,6 @@
       <c r="R294" s="14" t="n"/>
       <c r="S294" s="14" t="n"/>
       <c r="T294" s="14" t="n"/>
-      <c r="U294" s="14" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
@@ -19747,7 +19452,6 @@
       <c r="R295" s="14" t="n"/>
       <c r="S295" s="14" t="n"/>
       <c r="T295" s="14" t="n"/>
-      <c r="U295" s="14" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
@@ -19791,7 +19495,6 @@
       <c r="R296" s="14" t="n"/>
       <c r="S296" s="14" t="n"/>
       <c r="T296" s="14" t="n"/>
-      <c r="U296" s="14" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
@@ -19835,7 +19538,6 @@
       <c r="R297" s="14" t="n"/>
       <c r="S297" s="14" t="n"/>
       <c r="T297" s="14" t="n"/>
-      <c r="U297" s="14" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
@@ -19879,7 +19581,6 @@
       <c r="R298" s="14" t="n"/>
       <c r="S298" s="14" t="n"/>
       <c r="T298" s="14" t="n"/>
-      <c r="U298" s="14" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
@@ -19923,7 +19624,6 @@
       <c r="R299" s="14" t="n"/>
       <c r="S299" s="14" t="n"/>
       <c r="T299" s="14" t="n"/>
-      <c r="U299" s="14" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
@@ -19967,7 +19667,6 @@
       <c r="R300" s="14" t="n"/>
       <c r="S300" s="14" t="n"/>
       <c r="T300" s="14" t="n"/>
-      <c r="U300" s="14" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
@@ -19999,18 +19698,18 @@
       </c>
       <c r="G301" s="14" t="n"/>
       <c r="H301" s="14" t="n"/>
-      <c r="I301" s="14" t="n"/>
-      <c r="J301" s="14" t="n"/>
-      <c r="K301" s="14" t="inlineStr">
+      <c r="I301" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L301" s="14" t="inlineStr">
+      <c r="J301" s="14" t="inlineStr">
         <is>
           <t>Ascended Heroes - Stunfisk ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
+      <c r="K301" s="14" t="n"/>
+      <c r="L301" s="14" t="n"/>
       <c r="M301" s="14" t="n"/>
       <c r="N301" s="14" t="n"/>
       <c r="O301" s="14" t="n"/>
@@ -20019,7 +19718,6 @@
       <c r="R301" s="14" t="n"/>
       <c r="S301" s="14" t="n"/>
       <c r="T301" s="14" t="n"/>
-      <c r="U301" s="14" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
@@ -20051,13 +19749,13 @@
       </c>
       <c r="G302" s="14" t="n"/>
       <c r="H302" s="14" t="n"/>
-      <c r="I302" s="14" t="n"/>
+      <c r="I302" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J302" s="14" t="n"/>
-      <c r="K302" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K302" s="14" t="n"/>
       <c r="L302" s="14" t="n"/>
       <c r="M302" s="14" t="n"/>
       <c r="N302" s="14" t="n"/>
@@ -20067,7 +19765,6 @@
       <c r="R302" s="14" t="n"/>
       <c r="S302" s="14" t="n"/>
       <c r="T302" s="14" t="n"/>
-      <c r="U302" s="14" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
@@ -20099,13 +19796,13 @@
       </c>
       <c r="G303" s="14" t="n"/>
       <c r="H303" s="14" t="n"/>
-      <c r="I303" s="14" t="n"/>
+      <c r="I303" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J303" s="14" t="n"/>
-      <c r="K303" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K303" s="14" t="n"/>
       <c r="L303" s="14" t="n"/>
       <c r="M303" s="14" t="n"/>
       <c r="N303" s="14" t="n"/>
@@ -20115,7 +19812,6 @@
       <c r="R303" s="14" t="n"/>
       <c r="S303" s="14" t="n"/>
       <c r="T303" s="14" t="n"/>
-      <c r="U303" s="14" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
@@ -20147,13 +19843,13 @@
       </c>
       <c r="G304" s="14" t="n"/>
       <c r="H304" s="14" t="n"/>
-      <c r="I304" s="14" t="n"/>
+      <c r="I304" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J304" s="14" t="n"/>
-      <c r="K304" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K304" s="14" t="n"/>
       <c r="L304" s="14" t="n"/>
       <c r="M304" s="14" t="n"/>
       <c r="N304" s="14" t="n"/>
@@ -20163,7 +19859,6 @@
       <c r="R304" s="14" t="n"/>
       <c r="S304" s="14" t="n"/>
       <c r="T304" s="14" t="n"/>
-      <c r="U304" s="14" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
@@ -20195,13 +19890,13 @@
       </c>
       <c r="G305" s="14" t="n"/>
       <c r="H305" s="14" t="n"/>
-      <c r="I305" s="14" t="n"/>
+      <c r="I305" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J305" s="14" t="n"/>
-      <c r="K305" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K305" s="14" t="n"/>
       <c r="L305" s="14" t="n"/>
       <c r="M305" s="14" t="n"/>
       <c r="N305" s="14" t="n"/>
@@ -20211,7 +19906,6 @@
       <c r="R305" s="14" t="n"/>
       <c r="S305" s="14" t="n"/>
       <c r="T305" s="14" t="n"/>
-      <c r="U305" s="14" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
@@ -20243,18 +19937,18 @@
       </c>
       <c r="G306" s="14" t="n"/>
       <c r="H306" s="14" t="n"/>
-      <c r="I306" s="14" t="n"/>
-      <c r="J306" s="14" t="n"/>
-      <c r="K306" s="14" t="inlineStr">
+      <c r="I306" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L306" s="14" t="inlineStr">
+      <c r="J306" s="14" t="inlineStr">
         <is>
           <t>Journey Together - Volcanion ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="K306" s="14" t="n"/>
+      <c r="L306" s="14" t="n"/>
       <c r="M306" s="14" t="n"/>
       <c r="N306" s="14" t="n"/>
       <c r="O306" s="14" t="n"/>
@@ -20263,7 +19957,6 @@
       <c r="R306" s="14" t="n"/>
       <c r="S306" s="14" t="n"/>
       <c r="T306" s="14" t="n"/>
-      <c r="U306" s="14" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
@@ -20295,18 +19988,18 @@
       </c>
       <c r="G307" s="14" t="n"/>
       <c r="H307" s="14" t="n"/>
-      <c r="I307" s="14" t="n"/>
-      <c r="J307" s="14" t="n"/>
-      <c r="K307" s="14" t="inlineStr">
+      <c r="I307" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L307" s="14" t="inlineStr">
+      <c r="J307" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Rotom ex - Double Black Star- Double Rare</t>
         </is>
       </c>
+      <c r="K307" s="14" t="n"/>
+      <c r="L307" s="14" t="n"/>
       <c r="M307" s="14" t="n"/>
       <c r="N307" s="14" t="n"/>
       <c r="O307" s="14" t="n"/>
@@ -20314,8 +20007,7 @@
       <c r="Q307" s="14" t="n"/>
       <c r="R307" s="14" t="n"/>
       <c r="S307" s="14" t="n"/>
-      <c r="T307" s="14" t="n"/>
-      <c r="U307" s="14" t="inlineStr">
+      <c r="T307" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -20351,18 +20043,18 @@
       </c>
       <c r="G308" s="14" t="n"/>
       <c r="H308" s="14" t="n"/>
-      <c r="I308" s="14" t="n"/>
-      <c r="J308" s="14" t="n"/>
-      <c r="K308" s="14" t="inlineStr">
+      <c r="I308" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L308" s="14" t="inlineStr">
+      <c r="J308" s="14" t="inlineStr">
         <is>
           <t>Journey Together - Trainer - Ruffian - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
+      <c r="K308" s="14" t="n"/>
+      <c r="L308" s="14" t="n"/>
       <c r="M308" s="14" t="n"/>
       <c r="N308" s="14" t="n"/>
       <c r="O308" s="14" t="n"/>
@@ -20371,7 +20063,6 @@
       <c r="R308" s="14" t="n"/>
       <c r="S308" s="14" t="n"/>
       <c r="T308" s="14" t="n"/>
-      <c r="U308" s="14" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
@@ -20403,18 +20094,18 @@
       </c>
       <c r="G309" s="14" t="n"/>
       <c r="H309" s="14" t="n"/>
-      <c r="I309" s="14" t="n"/>
-      <c r="J309" s="14" t="n"/>
-      <c r="K309" s="14" t="inlineStr">
+      <c r="I309" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L309" s="14" t="inlineStr">
+      <c r="J309" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Mismagius ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="K309" s="14" t="n"/>
+      <c r="L309" s="14" t="n"/>
       <c r="M309" s="14" t="n"/>
       <c r="N309" s="14" t="n"/>
       <c r="O309" s="14" t="n"/>
@@ -20423,7 +20114,6 @@
       <c r="R309" s="14" t="n"/>
       <c r="S309" s="14" t="n"/>
       <c r="T309" s="14" t="n"/>
-      <c r="U309" s="14" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
@@ -20455,18 +20145,18 @@
       </c>
       <c r="G310" s="14" t="n"/>
       <c r="H310" s="14" t="n"/>
-      <c r="I310" s="14" t="n"/>
-      <c r="J310" s="14" t="n"/>
-      <c r="K310" s="14" t="inlineStr">
+      <c r="I310" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L310" s="14" t="inlineStr">
+      <c r="J310" s="14" t="inlineStr">
         <is>
           <t>Cyber Judge - Incineroar ex - SR - Super Rare</t>
         </is>
       </c>
+      <c r="K310" s="14" t="n"/>
+      <c r="L310" s="14" t="n"/>
       <c r="M310" s="14" t="n"/>
       <c r="N310" s="14" t="n"/>
       <c r="O310" s="14" t="n"/>
@@ -20475,7 +20165,6 @@
       <c r="R310" s="14" t="n"/>
       <c r="S310" s="14" t="n"/>
       <c r="T310" s="14" t="n"/>
-      <c r="U310" s="14" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
@@ -20507,13 +20196,13 @@
       </c>
       <c r="G311" s="14" t="n"/>
       <c r="H311" s="14" t="n"/>
-      <c r="I311" s="14" t="n"/>
+      <c r="I311" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J311" s="14" t="n"/>
-      <c r="K311" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K311" s="14" t="n"/>
       <c r="L311" s="14" t="n"/>
       <c r="M311" s="14" t="n"/>
       <c r="N311" s="14" t="n"/>
@@ -20523,7 +20212,6 @@
       <c r="R311" s="14" t="n"/>
       <c r="S311" s="14" t="n"/>
       <c r="T311" s="14" t="n"/>
-      <c r="U311" s="14" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
@@ -20555,31 +20243,30 @@
       </c>
       <c r="G312" s="14" t="n"/>
       <c r="H312" s="14" t="n"/>
-      <c r="I312" s="14" t="n"/>
-      <c r="J312" s="14" t="n"/>
-      <c r="K312" s="14" t="inlineStr">
+      <c r="I312" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L312" s="14" t="inlineStr">
+      <c r="J312" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Mega Lopunny ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="K312" s="14" t="n"/>
+      <c r="L312" s="14" t="n"/>
       <c r="M312" s="14" t="n"/>
-      <c r="N312" s="14" t="n"/>
-      <c r="O312" s="14" t="inlineStr">
+      <c r="N312" s="14" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
+      <c r="O312" s="14" t="n"/>
       <c r="P312" s="14" t="n"/>
       <c r="Q312" s="14" t="n"/>
       <c r="R312" s="14" t="n"/>
       <c r="S312" s="14" t="n"/>
       <c r="T312" s="14" t="n"/>
-      <c r="U312" s="14" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
@@ -20611,18 +20298,18 @@
       </c>
       <c r="G313" s="14" t="n"/>
       <c r="H313" s="14" t="n"/>
-      <c r="I313" s="14" t="n"/>
-      <c r="J313" s="14" t="n"/>
-      <c r="K313" s="14" t="inlineStr">
+      <c r="I313" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L313" s="14" t="inlineStr">
+      <c r="J313" s="14" t="inlineStr">
         <is>
           <t>Surging Sparks - Feebas - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
+      <c r="K313" s="14" t="n"/>
+      <c r="L313" s="14" t="n"/>
       <c r="M313" s="14" t="n"/>
       <c r="N313" s="14" t="n"/>
       <c r="O313" s="14" t="n"/>
@@ -20630,8 +20317,7 @@
       <c r="Q313" s="14" t="n"/>
       <c r="R313" s="14" t="n"/>
       <c r="S313" s="14" t="n"/>
-      <c r="T313" s="14" t="n"/>
-      <c r="U313" s="14" t="inlineStr">
+      <c r="T313" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -20667,27 +20353,26 @@
       </c>
       <c r="G314" s="14" t="n"/>
       <c r="H314" s="14" t="n"/>
-      <c r="I314" s="14" t="n"/>
+      <c r="I314" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J314" s="14" t="n"/>
-      <c r="K314" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="K314" s="14" t="n"/>
       <c r="L314" s="14" t="n"/>
       <c r="M314" s="14" t="n"/>
-      <c r="N314" s="14" t="n"/>
-      <c r="O314" s="14" t="inlineStr">
+      <c r="N314" s="14" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
+      <c r="O314" s="14" t="n"/>
       <c r="P314" s="14" t="n"/>
       <c r="Q314" s="14" t="n"/>
       <c r="R314" s="14" t="n"/>
       <c r="S314" s="14" t="n"/>
-      <c r="T314" s="14" t="n"/>
-      <c r="U314" s="14" t="inlineStr">
+      <c r="T314" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -20729,20 +20414,18 @@
       <c r="H315" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I315" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J315" s="14" t="n"/>
-      <c r="K315" s="14" t="inlineStr">
+      <c r="I315" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L315" s="14" t="inlineStr">
+      <c r="J315" s="14" t="inlineStr">
         <is>
           <t>Paradox Rift - Tsareena ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="K315" s="14" t="n"/>
+      <c r="L315" s="14" t="n"/>
       <c r="M315" s="14" t="n"/>
       <c r="N315" s="14" t="n"/>
       <c r="O315" s="14" t="n"/>
@@ -20751,7 +20434,6 @@
       <c r="R315" s="14" t="n"/>
       <c r="S315" s="14" t="n"/>
       <c r="T315" s="14" t="n"/>
-      <c r="U315" s="14" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
@@ -20786,34 +20468,31 @@
           <t>ex Box</t>
         </is>
       </c>
-      <c r="H316" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I316" s="14" t="n"/>
-      <c r="J316" s="14" t="n"/>
-      <c r="K316" s="14" t="inlineStr">
+      <c r="H316" s="14" t="n"/>
+      <c r="I316" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L316" s="14" t="inlineStr">
+      <c r="J316" s="14" t="inlineStr">
         <is>
           <t>Mega Kangakhan ex - Black Star Promo , Mega Evolution - Spearow - Single Gold Star - Illustration Rare,</t>
         </is>
       </c>
+      <c r="K316" s="14" t="n"/>
+      <c r="L316" s="14" t="n"/>
       <c r="M316" s="14" t="n"/>
-      <c r="N316" s="14" t="n"/>
-      <c r="O316" s="14" t="inlineStr">
+      <c r="N316" s="14" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
+      <c r="O316" s="14" t="n"/>
       <c r="P316" s="14" t="n"/>
       <c r="Q316" s="14" t="n"/>
       <c r="R316" s="14" t="n"/>
       <c r="S316" s="14" t="n"/>
-      <c r="T316" s="14" t="n"/>
-      <c r="U316" s="14" t="inlineStr">
+      <c r="T316" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -20852,34 +20531,31 @@
           <t>UPC</t>
         </is>
       </c>
-      <c r="H317" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I317" s="14" t="n"/>
-      <c r="J317" s="14" t="n"/>
-      <c r="K317" s="14" t="inlineStr">
+      <c r="H317" s="14" t="n"/>
+      <c r="I317" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L317" s="14" t="inlineStr">
+      <c r="J317" s="14" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Trainer - Dawn - Double Silver Star - Ultra Rare, Phantasmal Flames - Mega Gengar ex - Double Black Star - Double Rare , Mega Evolution - Mega Gardevoir ex - Double Silver Star - Ultra Rare , Mega Evolution - Mega Venusaur ex - Double Black Star - Double Rare , Mega Evolution - Marshadow - Single Gold Star - Illustration Rare ,  Destined Rivals - Cetitan ex - Double Black Star , Destined Rivals - Rotom - Single Gold Star - Illustration Rare, Journey Together - Noibat - Single Gold Star - Illustration Rare, Journey Together - Trainer - Brock's Scouting - Double Silver Star - Ultra Rare , Journey Together - Blaziken ex - Double Black Star - Double Rare, Surging Sparks - Trainer - Scramble Switch - Single Pink Star -  ACE SPEC Rare , Surging Sparks - Trainer - Cyrano - Double Silver Star - Ultra Rare, Phantasmal Falmes - Charizard X ex - Black Star Promo Card , Phantasmal Flames - Oricorio ex - Black Star Promo Card</t>
         </is>
       </c>
+      <c r="K317" s="14" t="n"/>
+      <c r="L317" s="14" t="n"/>
       <c r="M317" s="14" t="n"/>
-      <c r="N317" s="14" t="n"/>
-      <c r="O317" s="14" t="inlineStr">
+      <c r="N317" s="14" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
+      <c r="O317" s="14" t="n"/>
       <c r="P317" s="14" t="n"/>
       <c r="Q317" s="14" t="n"/>
       <c r="R317" s="14" t="n"/>
       <c r="S317" s="14" t="n"/>
-      <c r="T317" s="14" t="n"/>
-      <c r="U317" s="14" t="inlineStr">
+      <c r="T317" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -20918,56 +20594,48 @@
           <t>Collector Chest</t>
         </is>
       </c>
-      <c r="H318" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I318" s="14" t="n"/>
-      <c r="J318" s="14" t="n"/>
-      <c r="K318" s="14" t="inlineStr">
+      <c r="H318" s="14" t="n"/>
+      <c r="I318" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L318" s="14" t="inlineStr">
+      <c r="J318" s="14" t="inlineStr">
         <is>
           <t>Mega Evolution - Stufful - Single Gold star - Illustration Rare , Destined Rivals - Marnie's Grimmsnarl ex , Double Black Star - Double Rare , Journey Together - Wailord - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
+      <c r="K318" s="14" t="n"/>
+      <c r="L318" s="14" t="n"/>
       <c r="M318" s="14" t="n"/>
-      <c r="N318" s="14" t="n"/>
-      <c r="O318" s="14" t="inlineStr">
+      <c r="N318" s="14" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
+      <c r="O318" s="14" t="n"/>
       <c r="P318" s="14" t="n"/>
       <c r="Q318" s="14" t="n"/>
       <c r="R318" s="14" t="n"/>
       <c r="S318" s="14" t="n"/>
-      <c r="T318" s="14" t="n"/>
-      <c r="U318" s="14" t="inlineStr">
+      <c r="T318" s="14" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U318"/>
-  <conditionalFormatting sqref="G2:K318">
+  <autoFilter ref="A1:T318"/>
+  <conditionalFormatting sqref="G2:I318">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>OR($G2="",$J2="",$K2="")</formula>
+      <formula>OR($G2="",$I2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L318">
+  <conditionalFormatting sqref="I2:J318">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND($K2="Yes",$L2="")</formula>
+      <formula>AND($I2="Yes",$J2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G318" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not on the list" error="Not on the list. Keep it if that is what you mean." type="list" errorStyle="warning">
-      <formula1>gr_list_B</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -21785,7 +21453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -21839,7 +21507,7 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>COUNTA('Video Log'!J2:J318)</f>
+        <f>COUNTA('Video Log'!K2:K318)</f>
         <v/>
       </c>
     </row>
@@ -21850,14 +21518,14 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>COUNTA('Video Log'!A2:A318)-COUNTA('Video Log'!J2:J318)</f>
+        <f>COUNTA('Video Log'!A2:A318)-COUNTA('Video Log'!K2:K318)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Product number filled in</t>
+          <t>Pack number filled in</t>
         </is>
       </c>
       <c r="B8" s="17">
@@ -21868,60 +21536,49 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Pack number filled in</t>
+          <t>Marked as a hit</t>
         </is>
       </c>
       <c r="B9" s="17">
-        <f>COUNTA('Video Log'!I2:I318)</f>
+        <f>COUNTIF('Video Log'!I2:I318,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Marked as a hit</t>
+          <t>Hit info written</t>
         </is>
       </c>
       <c r="B10" s="17">
-        <f>COUNTIF('Video Log'!K2:K318,"Yes")</f>
+        <f>COUNTA('Video Log'!J2:J318)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Hit info written</t>
+          <t>In Greatest Hits</t>
         </is>
       </c>
       <c r="B11" s="17">
-        <f>COUNTA('Video Log'!L2:L318)</f>
+        <f>COUNTIF('Video Log'!L2:L318,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>In Greatest Hits</t>
+          <t>Given a rank</t>
         </is>
       </c>
       <c r="B12" s="17">
-        <f>COUNTIF('Video Log'!M2:M318,"Yes")</f>
+        <f>COUNTA('Video Log'!M2:M318)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Given a rank</t>
-        </is>
-      </c>
-      <c r="B13" s="17">
-        <f>COUNTA('Video Log'!N2:N318)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Counts update as you type. Blank cells are skipped by the import, so a half-filled sheet is fine.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -31,7 +31,7 @@
     <definedName name="gr_list_K">Lists!$K$2:$K$21</definedName>
     <definedName name="gr_list_L">Lists!$L$2:$L$31</definedName>
     <definedName name="gr_list_M">Lists!$M$2:$M$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$U$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$V$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -290,7 +290,7 @@
 one exactly. Anything not recognised is reported back, never guessed.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>WHICH PACK OUT OF THAT BOX this video opens. Pack 3 of the 9 in an
 ETB is 3.
@@ -302,7 +302,7 @@
 you did not keep count.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
 FREE TEXT. There is no dropdown on this column and there should not be
@@ -324,7 +324,7 @@
 claim a pull where you have said what the card was.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>LEAVE THIS BLANK unless the video opened packs from MORE THAN ONE SET.
 Nearly every video is one pack from one set, and for those the Product
@@ -334,7 +334,7 @@
 We can rework this column once the single-set rows are done.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>The Hall of Fame band on the home page.
 Separate from the Hits playlist: this is the shortlist, that is a
@@ -6435,7 +6435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U318"/>
+  <dimension ref="A1:V318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6445,20 +6445,21 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="54" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="54" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6504,65 +6505,70 @@
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
+          <t>Product #</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
           <t>Pack #</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Hit</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Hit Info</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Sets &amp; Packs</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Greatest Hits</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Greatest Hits Rank</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Playlist To Add</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Affiliate Link</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>Site Title</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="T1" s="9" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Hide</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6601,10 +6607,20 @@
           <t>desc: pack 9  Pitch Black</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>Sleeved Booster Pack</t>
+        </is>
+      </c>
       <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
-      <c r="K2" s="15" t="n"/>
+      <c r="J2" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L2" s="15" t="n"/>
       <c r="M2" s="15" t="n"/>
       <c r="N2" s="15" t="n"/>
@@ -6615,6 +6631,7 @@
       <c r="S2" s="15" t="n"/>
       <c r="T2" s="15" t="n"/>
       <c r="U2" s="15" t="n"/>
+      <c r="V2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -6649,24 +6666,41 @@
           <t>desc: #3 pack 3  Chaos Rising</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n">
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="15" t="n"/>
-      <c r="K3" s="15" t="n"/>
-      <c r="L3" s="15" t="n"/>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>Mega Greninja ex - Hyper Rare - Gold Card</t>
+        </is>
+      </c>
       <c r="M3" s="15" t="n"/>
-      <c r="N3" s="15" t="n">
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="O3" s="15" t="n"/>
       <c r="P3" s="15" t="n"/>
       <c r="Q3" s="15" t="n"/>
       <c r="R3" s="15" t="n"/>
       <c r="S3" s="15" t="n"/>
       <c r="T3" s="15" t="n"/>
       <c r="U3" s="15" t="n"/>
+      <c r="V3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -6701,10 +6735,20 @@
           <t>title: pack 13  Chaos Rising</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I4" s="15" t="n"/>
-      <c r="J4" s="15" t="n"/>
-      <c r="K4" s="15" t="n"/>
+      <c r="J4" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L4" s="15" t="n"/>
       <c r="M4" s="15" t="n"/>
       <c r="N4" s="15" t="n"/>
@@ -6715,6 +6759,7 @@
       <c r="S4" s="15" t="n"/>
       <c r="T4" s="15" t="n"/>
       <c r="U4" s="15" t="n"/>
+      <c r="V4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -6749,10 +6794,20 @@
           <t>title: pack 8  Pitch Black</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n"/>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
       <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="15" t="n"/>
+      <c r="J5" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
       <c r="N5" s="15" t="n"/>
@@ -6763,6 +6818,7 @@
       <c r="S5" s="15" t="n"/>
       <c r="T5" s="15" t="n"/>
       <c r="U5" s="15" t="n"/>
+      <c r="V5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -6797,14 +6853,20 @@
           <t>desc: pack 8  Pitch Black</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n"/>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Sleeved Booster Pack</t>
+        </is>
+      </c>
       <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="n"/>
+      <c r="J6" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
@@ -6815,6 +6877,7 @@
       <c r="S6" s="15" t="n"/>
       <c r="T6" s="15" t="n"/>
       <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -6849,10 +6912,20 @@
           <t>desc: pack 2  Chaos Rising</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n"/>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
       <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
+      <c r="J7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
       <c r="N7" s="15" t="n"/>
@@ -6863,6 +6936,7 @@
       <c r="S7" s="15" t="n"/>
       <c r="T7" s="15" t="n"/>
       <c r="U7" s="15" t="n"/>
+      <c r="V7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6897,15 +6971,25 @@
           <t>desc: pack 12  Chaos Rising</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n"/>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="J8" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Cinccino ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
@@ -6915,6 +6999,7 @@
       <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n"/>
       <c r="U8" s="15" t="n"/>
+      <c r="V8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -6949,10 +7034,20 @@
           <t>desc: pack 7  Pitch Black</t>
         </is>
       </c>
-      <c r="H9" s="15" t="n"/>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
       <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="15" t="n"/>
+      <c r="J9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
       <c r="N9" s="15" t="n"/>
@@ -6963,6 +7058,7 @@
       <c r="S9" s="15" t="n"/>
       <c r="T9" s="15" t="n"/>
       <c r="U9" s="15" t="n"/>
+      <c r="V9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -6997,14 +7093,20 @@
           <t>desc: pack 7  Pitch Black</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n"/>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="n"/>
+      <c r="J10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
@@ -7015,6 +7117,7 @@
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n"/>
       <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -7049,10 +7152,20 @@
           <t>title: #3  Chaos Rising</t>
         </is>
       </c>
-      <c r="H11" s="15" t="n"/>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
       <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="15" t="n"/>
+      <c r="J11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
       <c r="N11" s="15" t="n"/>
@@ -7063,6 +7176,7 @@
       <c r="S11" s="15" t="n"/>
       <c r="T11" s="15" t="n"/>
       <c r="U11" s="15" t="n"/>
+      <c r="V11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -7111,6 +7225,7 @@
       <c r="S12" s="15" t="n"/>
       <c r="T12" s="15" t="n"/>
       <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -7147,12 +7262,12 @@
       </c>
       <c r="H13" s="15" t="n"/>
       <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
       <c r="N13" s="15" t="n"/>
@@ -7163,6 +7278,7 @@
       <c r="S13" s="15" t="n"/>
       <c r="T13" s="15" t="n"/>
       <c r="U13" s="15" t="n"/>
+      <c r="V13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -7199,12 +7315,12 @@
       </c>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
@@ -7215,6 +7331,7 @@
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
       <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -7263,6 +7380,7 @@
       <c r="S15" s="15" t="n"/>
       <c r="T15" s="15" t="n"/>
       <c r="U15" s="15" t="n"/>
+      <c r="V15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -7299,12 +7417,12 @@
       </c>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
@@ -7315,6 +7433,7 @@
       <c r="S16" s="15" t="n"/>
       <c r="T16" s="15" t="n"/>
       <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -7351,12 +7470,12 @@
       </c>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
@@ -7367,6 +7486,7 @@
       <c r="S17" s="15" t="n"/>
       <c r="T17" s="15" t="n"/>
       <c r="U17" s="15" t="n"/>
+      <c r="V17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -7403,12 +7523,12 @@
       </c>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -7419,6 +7539,7 @@
       <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n"/>
       <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -7455,12 +7576,12 @@
       </c>
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
@@ -7471,6 +7592,7 @@
       <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="15" t="n"/>
+      <c r="V19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -7507,12 +7629,12 @@
       </c>
       <c r="H20" s="15" t="n"/>
       <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
@@ -7523,6 +7645,7 @@
       <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -7571,6 +7694,7 @@
       <c r="S21" s="15" t="n"/>
       <c r="T21" s="15" t="n"/>
       <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -7607,12 +7731,12 @@
       </c>
       <c r="H22" s="15" t="n"/>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="inlineStr">
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -7623,6 +7747,7 @@
       <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -7659,12 +7784,12 @@
       </c>
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
@@ -7675,6 +7800,7 @@
       <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n"/>
       <c r="U23" s="15" t="n"/>
+      <c r="V23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -7711,12 +7837,12 @@
       </c>
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="inlineStr">
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
@@ -7727,6 +7853,7 @@
       <c r="S24" s="15" t="n"/>
       <c r="T24" s="15" t="n"/>
       <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -7775,6 +7902,7 @@
       <c r="S25" s="15" t="n"/>
       <c r="T25" s="15" t="n"/>
       <c r="U25" s="15" t="n"/>
+      <c r="V25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -7811,12 +7939,12 @@
       </c>
       <c r="H26" s="15" t="n"/>
       <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
@@ -7827,6 +7955,7 @@
       <c r="S26" s="15" t="n"/>
       <c r="T26" s="15" t="n"/>
       <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -7875,6 +8004,7 @@
       <c r="S27" s="15" t="n"/>
       <c r="T27" s="15" t="n"/>
       <c r="U27" s="15" t="n"/>
+      <c r="V27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -7911,12 +8041,12 @@
       </c>
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="inlineStr">
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
       <c r="N28" s="15" t="n"/>
@@ -7927,6 +8057,7 @@
       <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n"/>
       <c r="U28" s="15" t="n"/>
+      <c r="V28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -7963,12 +8094,12 @@
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="inlineStr">
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
       <c r="M29" s="15" t="n"/>
       <c r="N29" s="15" t="n"/>
@@ -7979,6 +8110,7 @@
       <c r="S29" s="15" t="n"/>
       <c r="T29" s="15" t="n"/>
       <c r="U29" s="15" t="n"/>
+      <c r="V29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -8027,6 +8159,7 @@
       <c r="S30" s="15" t="n"/>
       <c r="T30" s="15" t="n"/>
       <c r="U30" s="15" t="n"/>
+      <c r="V30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -8075,6 +8208,7 @@
       <c r="S31" s="15" t="n"/>
       <c r="T31" s="15" t="n"/>
       <c r="U31" s="15" t="n"/>
+      <c r="V31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -8111,12 +8245,12 @@
       </c>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="inlineStr">
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K32" s="15" t="n"/>
       <c r="L32" s="15" t="n"/>
       <c r="M32" s="15" t="n"/>
       <c r="N32" s="15" t="n"/>
@@ -8127,6 +8261,7 @@
       <c r="S32" s="15" t="n"/>
       <c r="T32" s="15" t="n"/>
       <c r="U32" s="15" t="n"/>
+      <c r="V32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -8175,6 +8310,7 @@
       <c r="S33" s="15" t="n"/>
       <c r="T33" s="15" t="n"/>
       <c r="U33" s="15" t="n"/>
+      <c r="V33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -8223,6 +8359,7 @@
       <c r="S34" s="15" t="n"/>
       <c r="T34" s="15" t="n"/>
       <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -8259,12 +8396,12 @@
       </c>
       <c r="H35" s="15" t="n"/>
       <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K35" s="15" t="n"/>
       <c r="L35" s="15" t="n"/>
       <c r="M35" s="15" t="n"/>
       <c r="N35" s="15" t="n"/>
@@ -8275,6 +8412,7 @@
       <c r="S35" s="15" t="n"/>
       <c r="T35" s="15" t="n"/>
       <c r="U35" s="15" t="n"/>
+      <c r="V35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -8323,6 +8461,7 @@
       <c r="S36" s="15" t="n"/>
       <c r="T36" s="15" t="n"/>
       <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -8371,6 +8510,7 @@
       <c r="S37" s="15" t="n"/>
       <c r="T37" s="15" t="n"/>
       <c r="U37" s="15" t="n"/>
+      <c r="V37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -8407,12 +8547,12 @@
       </c>
       <c r="H38" s="15" t="n"/>
       <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="inlineStr">
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K38" s="15" t="n"/>
       <c r="L38" s="15" t="n"/>
       <c r="M38" s="15" t="n"/>
       <c r="N38" s="15" t="n"/>
@@ -8423,6 +8563,7 @@
       <c r="S38" s="15" t="n"/>
       <c r="T38" s="15" t="n"/>
       <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -8471,6 +8612,7 @@
       <c r="S39" s="15" t="n"/>
       <c r="T39" s="15" t="n"/>
       <c r="U39" s="15" t="n"/>
+      <c r="V39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -8507,12 +8649,12 @@
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="inlineStr">
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K40" s="15" t="n"/>
       <c r="L40" s="15" t="n"/>
       <c r="M40" s="15" t="n"/>
       <c r="N40" s="15" t="n"/>
@@ -8523,6 +8665,7 @@
       <c r="S40" s="15" t="n"/>
       <c r="T40" s="15" t="n"/>
       <c r="U40" s="15" t="n"/>
+      <c r="V40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -8559,12 +8702,12 @@
       </c>
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K41" s="15" t="n"/>
       <c r="L41" s="15" t="n"/>
       <c r="M41" s="15" t="n"/>
       <c r="N41" s="15" t="n"/>
@@ -8575,6 +8718,7 @@
       <c r="S41" s="15" t="n"/>
       <c r="T41" s="15" t="n"/>
       <c r="U41" s="15" t="n"/>
+      <c r="V41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -8623,6 +8767,7 @@
       <c r="S42" s="15" t="n"/>
       <c r="T42" s="15" t="n"/>
       <c r="U42" s="15" t="n"/>
+      <c r="V42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -8659,12 +8804,12 @@
       </c>
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="J43" s="15" t="n"/>
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K43" s="15" t="n"/>
       <c r="L43" s="15" t="n"/>
       <c r="M43" s="15" t="n"/>
       <c r="N43" s="15" t="n"/>
@@ -8675,6 +8820,7 @@
       <c r="S43" s="15" t="n"/>
       <c r="T43" s="15" t="n"/>
       <c r="U43" s="15" t="n"/>
+      <c r="V43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -8711,12 +8857,12 @@
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" s="15" t="n"/>
+      <c r="K44" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K44" s="15" t="n"/>
       <c r="L44" s="15" t="n"/>
       <c r="M44" s="15" t="n"/>
       <c r="N44" s="15" t="n"/>
@@ -8727,6 +8873,7 @@
       <c r="S44" s="15" t="n"/>
       <c r="T44" s="15" t="n"/>
       <c r="U44" s="15" t="n"/>
+      <c r="V44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -8775,6 +8922,7 @@
       <c r="S45" s="15" t="n"/>
       <c r="T45" s="15" t="n"/>
       <c r="U45" s="15" t="n"/>
+      <c r="V45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -8811,12 +8959,12 @@
       </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K46" s="15" t="n"/>
       <c r="L46" s="15" t="n"/>
       <c r="M46" s="15" t="n"/>
       <c r="N46" s="15" t="n"/>
@@ -8827,6 +8975,7 @@
       <c r="S46" s="15" t="n"/>
       <c r="T46" s="15" t="n"/>
       <c r="U46" s="15" t="n"/>
+      <c r="V46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -8875,6 +9024,7 @@
       <c r="S47" s="15" t="n"/>
       <c r="T47" s="15" t="n"/>
       <c r="U47" s="15" t="n"/>
+      <c r="V47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -8923,6 +9073,7 @@
       <c r="S48" s="15" t="n"/>
       <c r="T48" s="15" t="n"/>
       <c r="U48" s="15" t="n"/>
+      <c r="V48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -8959,12 +9110,12 @@
       </c>
       <c r="H49" s="15" t="n"/>
       <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="J49" s="15" t="n"/>
+      <c r="K49" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K49" s="15" t="n"/>
       <c r="L49" s="15" t="n"/>
       <c r="M49" s="15" t="n"/>
       <c r="N49" s="15" t="n"/>
@@ -8975,6 +9126,7 @@
       <c r="S49" s="15" t="n"/>
       <c r="T49" s="15" t="n"/>
       <c r="U49" s="15" t="n"/>
+      <c r="V49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -9023,6 +9175,7 @@
       <c r="S50" s="15" t="n"/>
       <c r="T50" s="15" t="n"/>
       <c r="U50" s="15" t="n"/>
+      <c r="V50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -9059,12 +9212,12 @@
       </c>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="15" t="n"/>
-      <c r="J51" s="15" t="inlineStr">
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K51" s="15" t="n"/>
       <c r="L51" s="15" t="n"/>
       <c r="M51" s="15" t="n"/>
       <c r="N51" s="15" t="n"/>
@@ -9075,6 +9228,7 @@
       <c r="S51" s="15" t="n"/>
       <c r="T51" s="15" t="n"/>
       <c r="U51" s="15" t="n"/>
+      <c r="V51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -9123,6 +9277,7 @@
       <c r="S52" s="15" t="n"/>
       <c r="T52" s="15" t="n"/>
       <c r="U52" s="15" t="n"/>
+      <c r="V52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -9159,12 +9314,12 @@
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="15" t="n"/>
-      <c r="J53" s="15" t="inlineStr">
+      <c r="J53" s="15" t="n"/>
+      <c r="K53" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K53" s="15" t="n"/>
       <c r="L53" s="15" t="n"/>
       <c r="M53" s="15" t="n"/>
       <c r="N53" s="15" t="n"/>
@@ -9175,6 +9330,7 @@
       <c r="S53" s="15" t="n"/>
       <c r="T53" s="15" t="n"/>
       <c r="U53" s="15" t="n"/>
+      <c r="V53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -9223,6 +9379,7 @@
       <c r="S54" s="15" t="n"/>
       <c r="T54" s="15" t="n"/>
       <c r="U54" s="15" t="n"/>
+      <c r="V54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -9259,12 +9416,12 @@
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="inlineStr">
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K55" s="15" t="n"/>
       <c r="L55" s="15" t="n"/>
       <c r="M55" s="15" t="n"/>
       <c r="N55" s="15" t="n"/>
@@ -9275,6 +9432,7 @@
       <c r="S55" s="15" t="n"/>
       <c r="T55" s="15" t="n"/>
       <c r="U55" s="15" t="n"/>
+      <c r="V55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -9323,6 +9481,7 @@
       <c r="S56" s="15" t="n"/>
       <c r="T56" s="15" t="n"/>
       <c r="U56" s="15" t="n"/>
+      <c r="V56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -9359,12 +9518,12 @@
       </c>
       <c r="H57" s="15" t="n"/>
       <c r="I57" s="15" t="n"/>
-      <c r="J57" s="15" t="inlineStr">
+      <c r="J57" s="15" t="n"/>
+      <c r="K57" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K57" s="15" t="n"/>
       <c r="L57" s="15" t="n"/>
       <c r="M57" s="15" t="n"/>
       <c r="N57" s="15" t="n"/>
@@ -9375,6 +9534,7 @@
       <c r="S57" s="15" t="n"/>
       <c r="T57" s="15" t="n"/>
       <c r="U57" s="15" t="n"/>
+      <c r="V57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -9423,6 +9583,7 @@
       <c r="S58" s="15" t="n"/>
       <c r="T58" s="15" t="n"/>
       <c r="U58" s="15" t="n"/>
+      <c r="V58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -9471,6 +9632,7 @@
       <c r="S59" s="15" t="n"/>
       <c r="T59" s="15" t="n"/>
       <c r="U59" s="15" t="n"/>
+      <c r="V59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -9519,6 +9681,7 @@
       <c r="S60" s="15" t="n"/>
       <c r="T60" s="15" t="n"/>
       <c r="U60" s="15" t="n"/>
+      <c r="V60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -9567,6 +9730,7 @@
       <c r="S61" s="15" t="n"/>
       <c r="T61" s="15" t="n"/>
       <c r="U61" s="15" t="n"/>
+      <c r="V61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -9615,6 +9779,7 @@
       <c r="S62" s="15" t="n"/>
       <c r="T62" s="15" t="n"/>
       <c r="U62" s="15" t="n"/>
+      <c r="V62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -9663,6 +9828,7 @@
       <c r="S63" s="15" t="n"/>
       <c r="T63" s="15" t="n"/>
       <c r="U63" s="15" t="n"/>
+      <c r="V63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -9699,12 +9865,12 @@
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="15" t="n"/>
-      <c r="J64" s="15" t="inlineStr">
+      <c r="J64" s="15" t="n"/>
+      <c r="K64" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K64" s="15" t="n"/>
       <c r="L64" s="15" t="n"/>
       <c r="M64" s="15" t="n"/>
       <c r="N64" s="15" t="n"/>
@@ -9715,6 +9881,7 @@
       <c r="S64" s="15" t="n"/>
       <c r="T64" s="15" t="n"/>
       <c r="U64" s="15" t="n"/>
+      <c r="V64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -9763,6 +9930,7 @@
       <c r="S65" s="15" t="n"/>
       <c r="T65" s="15" t="n"/>
       <c r="U65" s="15" t="n"/>
+      <c r="V65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -9811,6 +9979,7 @@
       <c r="S66" s="15" t="n"/>
       <c r="T66" s="15" t="n"/>
       <c r="U66" s="15" t="n"/>
+      <c r="V66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -9859,6 +10028,7 @@
       <c r="S67" s="15" t="n"/>
       <c r="T67" s="15" t="n"/>
       <c r="U67" s="15" t="n"/>
+      <c r="V67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -9907,6 +10077,7 @@
       <c r="S68" s="15" t="n"/>
       <c r="T68" s="15" t="n"/>
       <c r="U68" s="15" t="n"/>
+      <c r="V68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -9955,6 +10126,7 @@
       <c r="S69" s="15" t="n"/>
       <c r="T69" s="15" t="n"/>
       <c r="U69" s="15" t="n"/>
+      <c r="V69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -10003,6 +10175,7 @@
       <c r="S70" s="15" t="n"/>
       <c r="T70" s="15" t="n"/>
       <c r="U70" s="15" t="n"/>
+      <c r="V70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -10051,6 +10224,7 @@
       <c r="S71" s="15" t="n"/>
       <c r="T71" s="15" t="n"/>
       <c r="U71" s="15" t="n"/>
+      <c r="V71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -10099,6 +10273,7 @@
       <c r="S72" s="15" t="n"/>
       <c r="T72" s="15" t="n"/>
       <c r="U72" s="15" t="n"/>
+      <c r="V72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -10147,6 +10322,7 @@
       <c r="S73" s="15" t="n"/>
       <c r="T73" s="15" t="n"/>
       <c r="U73" s="15" t="n"/>
+      <c r="V73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -10195,6 +10371,7 @@
       <c r="S74" s="15" t="n"/>
       <c r="T74" s="15" t="n"/>
       <c r="U74" s="15" t="n"/>
+      <c r="V74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -10243,6 +10420,7 @@
       <c r="S75" s="15" t="n"/>
       <c r="T75" s="15" t="n"/>
       <c r="U75" s="15" t="n"/>
+      <c r="V75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -10291,6 +10469,7 @@
       <c r="S76" s="15" t="n"/>
       <c r="T76" s="15" t="n"/>
       <c r="U76" s="15" t="n"/>
+      <c r="V76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -10339,6 +10518,7 @@
       <c r="S77" s="15" t="n"/>
       <c r="T77" s="15" t="n"/>
       <c r="U77" s="15" t="n"/>
+      <c r="V77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -10387,6 +10567,7 @@
       <c r="S78" s="15" t="n"/>
       <c r="T78" s="15" t="n"/>
       <c r="U78" s="15" t="n"/>
+      <c r="V78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -10435,6 +10616,7 @@
       <c r="S79" s="15" t="n"/>
       <c r="T79" s="15" t="n"/>
       <c r="U79" s="15" t="n"/>
+      <c r="V79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -10483,6 +10665,7 @@
       <c r="S80" s="15" t="n"/>
       <c r="T80" s="15" t="n"/>
       <c r="U80" s="15" t="n"/>
+      <c r="V80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -10531,6 +10714,7 @@
       <c r="S81" s="15" t="n"/>
       <c r="T81" s="15" t="n"/>
       <c r="U81" s="15" t="n"/>
+      <c r="V81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -10579,6 +10763,7 @@
       <c r="S82" s="15" t="n"/>
       <c r="T82" s="15" t="n"/>
       <c r="U82" s="15" t="n"/>
+      <c r="V82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -10615,12 +10800,12 @@
       </c>
       <c r="H83" s="15" t="n"/>
       <c r="I83" s="15" t="n"/>
-      <c r="J83" s="15" t="inlineStr">
+      <c r="J83" s="15" t="n"/>
+      <c r="K83" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K83" s="15" t="n"/>
       <c r="L83" s="15" t="n"/>
       <c r="M83" s="15" t="n"/>
       <c r="N83" s="15" t="n"/>
@@ -10631,6 +10816,7 @@
       <c r="S83" s="15" t="n"/>
       <c r="T83" s="15" t="n"/>
       <c r="U83" s="15" t="n"/>
+      <c r="V83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -10667,12 +10853,12 @@
       </c>
       <c r="H84" s="15" t="n"/>
       <c r="I84" s="15" t="n"/>
-      <c r="J84" s="15" t="inlineStr">
+      <c r="J84" s="15" t="n"/>
+      <c r="K84" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K84" s="15" t="n"/>
       <c r="L84" s="15" t="n"/>
       <c r="M84" s="15" t="n"/>
       <c r="N84" s="15" t="n"/>
@@ -10683,6 +10869,7 @@
       <c r="S84" s="15" t="n"/>
       <c r="T84" s="15" t="n"/>
       <c r="U84" s="15" t="n"/>
+      <c r="V84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -10719,12 +10906,12 @@
       </c>
       <c r="H85" s="15" t="n"/>
       <c r="I85" s="15" t="n"/>
-      <c r="J85" s="15" t="inlineStr">
+      <c r="J85" s="15" t="n"/>
+      <c r="K85" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K85" s="15" t="n"/>
       <c r="L85" s="15" t="n"/>
       <c r="M85" s="15" t="n"/>
       <c r="N85" s="15" t="n"/>
@@ -10735,6 +10922,7 @@
       <c r="S85" s="15" t="n"/>
       <c r="T85" s="15" t="n"/>
       <c r="U85" s="15" t="n"/>
+      <c r="V85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -10771,12 +10959,12 @@
       </c>
       <c r="H86" s="15" t="n"/>
       <c r="I86" s="15" t="n"/>
-      <c r="J86" s="15" t="inlineStr">
+      <c r="J86" s="15" t="n"/>
+      <c r="K86" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K86" s="15" t="n"/>
       <c r="L86" s="15" t="n"/>
       <c r="M86" s="15" t="n"/>
       <c r="N86" s="15" t="n"/>
@@ -10787,6 +10975,7 @@
       <c r="S86" s="15" t="n"/>
       <c r="T86" s="15" t="n"/>
       <c r="U86" s="15" t="n"/>
+      <c r="V86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -10835,6 +11024,7 @@
       <c r="S87" s="15" t="n"/>
       <c r="T87" s="15" t="n"/>
       <c r="U87" s="15" t="n"/>
+      <c r="V87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -10883,6 +11073,7 @@
       <c r="S88" s="15" t="n"/>
       <c r="T88" s="15" t="n"/>
       <c r="U88" s="15" t="n"/>
+      <c r="V88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
@@ -10919,12 +11110,12 @@
       </c>
       <c r="H89" s="15" t="n"/>
       <c r="I89" s="15" t="n"/>
-      <c r="J89" s="15" t="inlineStr">
+      <c r="J89" s="15" t="n"/>
+      <c r="K89" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K89" s="15" t="n"/>
       <c r="L89" s="15" t="n"/>
       <c r="M89" s="15" t="n"/>
       <c r="N89" s="15" t="n"/>
@@ -10935,6 +11126,7 @@
       <c r="S89" s="15" t="n"/>
       <c r="T89" s="15" t="n"/>
       <c r="U89" s="15" t="n"/>
+      <c r="V89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -10971,12 +11163,12 @@
       </c>
       <c r="H90" s="15" t="n"/>
       <c r="I90" s="15" t="n"/>
-      <c r="J90" s="15" t="inlineStr">
+      <c r="J90" s="15" t="n"/>
+      <c r="K90" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K90" s="15" t="n"/>
       <c r="L90" s="15" t="n"/>
       <c r="M90" s="15" t="n"/>
       <c r="N90" s="15" t="n"/>
@@ -10987,6 +11179,7 @@
       <c r="S90" s="15" t="n"/>
       <c r="T90" s="15" t="n"/>
       <c r="U90" s="15" t="n"/>
+      <c r="V90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -11023,12 +11216,12 @@
       </c>
       <c r="H91" s="15" t="n"/>
       <c r="I91" s="15" t="n"/>
-      <c r="J91" s="15" t="inlineStr">
+      <c r="J91" s="15" t="n"/>
+      <c r="K91" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K91" s="15" t="n"/>
       <c r="L91" s="15" t="n"/>
       <c r="M91" s="15" t="n"/>
       <c r="N91" s="15" t="n"/>
@@ -11039,6 +11232,7 @@
       <c r="S91" s="15" t="n"/>
       <c r="T91" s="15" t="n"/>
       <c r="U91" s="15" t="n"/>
+      <c r="V91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
@@ -11075,12 +11269,12 @@
       </c>
       <c r="H92" s="15" t="n"/>
       <c r="I92" s="15" t="n"/>
-      <c r="J92" s="15" t="inlineStr">
+      <c r="J92" s="15" t="n"/>
+      <c r="K92" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K92" s="15" t="n"/>
       <c r="L92" s="15" t="n"/>
       <c r="M92" s="15" t="n"/>
       <c r="N92" s="15" t="n"/>
@@ -11091,6 +11285,7 @@
       <c r="S92" s="15" t="n"/>
       <c r="T92" s="15" t="n"/>
       <c r="U92" s="15" t="n"/>
+      <c r="V92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -11139,6 +11334,7 @@
       <c r="S93" s="15" t="n"/>
       <c r="T93" s="15" t="n"/>
       <c r="U93" s="15" t="n"/>
+      <c r="V93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -11187,6 +11383,7 @@
       <c r="S94" s="15" t="n"/>
       <c r="T94" s="15" t="n"/>
       <c r="U94" s="15" t="n"/>
+      <c r="V94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -11235,6 +11432,7 @@
       <c r="S95" s="15" t="n"/>
       <c r="T95" s="15" t="n"/>
       <c r="U95" s="15" t="n"/>
+      <c r="V95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -11283,6 +11481,7 @@
       <c r="S96" s="15" t="n"/>
       <c r="T96" s="15" t="n"/>
       <c r="U96" s="15" t="n"/>
+      <c r="V96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -11331,6 +11530,7 @@
       <c r="S97" s="15" t="n"/>
       <c r="T97" s="15" t="n"/>
       <c r="U97" s="15" t="n"/>
+      <c r="V97" s="15" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -11379,6 +11579,7 @@
       <c r="S98" s="15" t="n"/>
       <c r="T98" s="15" t="n"/>
       <c r="U98" s="15" t="n"/>
+      <c r="V98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -11427,6 +11628,7 @@
       <c r="S99" s="15" t="n"/>
       <c r="T99" s="15" t="n"/>
       <c r="U99" s="15" t="n"/>
+      <c r="V99" s="15" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -11475,6 +11677,7 @@
       <c r="S100" s="15" t="n"/>
       <c r="T100" s="15" t="n"/>
       <c r="U100" s="15" t="n"/>
+      <c r="V100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
@@ -11523,6 +11726,7 @@
       <c r="S101" s="15" t="n"/>
       <c r="T101" s="15" t="n"/>
       <c r="U101" s="15" t="n"/>
+      <c r="V101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -11571,6 +11775,7 @@
       <c r="S102" s="15" t="n"/>
       <c r="T102" s="15" t="n"/>
       <c r="U102" s="15" t="n"/>
+      <c r="V102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -11607,12 +11812,12 @@
       </c>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="15" t="n"/>
-      <c r="J103" s="15" t="inlineStr">
+      <c r="J103" s="15" t="n"/>
+      <c r="K103" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K103" s="15" t="n"/>
       <c r="L103" s="15" t="n"/>
       <c r="M103" s="15" t="n"/>
       <c r="N103" s="15" t="n"/>
@@ -11623,6 +11828,7 @@
       <c r="S103" s="15" t="n"/>
       <c r="T103" s="15" t="n"/>
       <c r="U103" s="15" t="n"/>
+      <c r="V103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -11671,6 +11877,7 @@
       <c r="S104" s="15" t="n"/>
       <c r="T104" s="15" t="n"/>
       <c r="U104" s="15" t="n"/>
+      <c r="V104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -11707,12 +11914,12 @@
       </c>
       <c r="H105" s="15" t="n"/>
       <c r="I105" s="15" t="n"/>
-      <c r="J105" s="15" t="inlineStr">
+      <c r="J105" s="15" t="n"/>
+      <c r="K105" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K105" s="15" t="n"/>
       <c r="L105" s="15" t="n"/>
       <c r="M105" s="15" t="n"/>
       <c r="N105" s="15" t="n"/>
@@ -11723,6 +11930,7 @@
       <c r="S105" s="15" t="n"/>
       <c r="T105" s="15" t="n"/>
       <c r="U105" s="15" t="n"/>
+      <c r="V105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -11771,6 +11979,7 @@
       <c r="S106" s="15" t="n"/>
       <c r="T106" s="15" t="n"/>
       <c r="U106" s="15" t="n"/>
+      <c r="V106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -11819,6 +12028,7 @@
       <c r="S107" s="15" t="n"/>
       <c r="T107" s="15" t="n"/>
       <c r="U107" s="15" t="n"/>
+      <c r="V107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -11867,6 +12077,7 @@
       <c r="S108" s="15" t="n"/>
       <c r="T108" s="15" t="n"/>
       <c r="U108" s="15" t="n"/>
+      <c r="V108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -11915,6 +12126,7 @@
       <c r="S109" s="15" t="n"/>
       <c r="T109" s="15" t="n"/>
       <c r="U109" s="15" t="n"/>
+      <c r="V109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -11963,6 +12175,7 @@
       <c r="S110" s="15" t="n"/>
       <c r="T110" s="15" t="n"/>
       <c r="U110" s="15" t="n"/>
+      <c r="V110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -12011,6 +12224,7 @@
       <c r="S111" s="15" t="n"/>
       <c r="T111" s="15" t="n"/>
       <c r="U111" s="15" t="n"/>
+      <c r="V111" s="15" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -12059,6 +12273,7 @@
       <c r="S112" s="15" t="n"/>
       <c r="T112" s="15" t="n"/>
       <c r="U112" s="15" t="n"/>
+      <c r="V112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -12107,6 +12322,7 @@
       <c r="S113" s="15" t="n"/>
       <c r="T113" s="15" t="n"/>
       <c r="U113" s="15" t="n"/>
+      <c r="V113" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
@@ -12155,6 +12371,7 @@
       <c r="S114" s="15" t="n"/>
       <c r="T114" s="15" t="n"/>
       <c r="U114" s="15" t="n"/>
+      <c r="V114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -12203,6 +12420,7 @@
       <c r="S115" s="15" t="n"/>
       <c r="T115" s="15" t="n"/>
       <c r="U115" s="15" t="n"/>
+      <c r="V115" s="15" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
@@ -12251,6 +12469,7 @@
       <c r="S116" s="15" t="n"/>
       <c r="T116" s="15" t="n"/>
       <c r="U116" s="15" t="n"/>
+      <c r="V116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -12299,6 +12518,7 @@
       <c r="S117" s="15" t="n"/>
       <c r="T117" s="15" t="n"/>
       <c r="U117" s="15" t="n"/>
+      <c r="V117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
@@ -12347,6 +12567,7 @@
       <c r="S118" s="15" t="n"/>
       <c r="T118" s="15" t="n"/>
       <c r="U118" s="15" t="n"/>
+      <c r="V118" s="15" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
@@ -12395,6 +12616,7 @@
       <c r="S119" s="15" t="n"/>
       <c r="T119" s="15" t="n"/>
       <c r="U119" s="15" t="n"/>
+      <c r="V119" s="15" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -12443,6 +12665,7 @@
       <c r="S120" s="15" t="n"/>
       <c r="T120" s="15" t="n"/>
       <c r="U120" s="15" t="n"/>
+      <c r="V120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -12491,6 +12714,7 @@
       <c r="S121" s="15" t="n"/>
       <c r="T121" s="15" t="n"/>
       <c r="U121" s="15" t="n"/>
+      <c r="V121" s="15" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -12539,6 +12763,7 @@
       <c r="S122" s="15" t="n"/>
       <c r="T122" s="15" t="n"/>
       <c r="U122" s="15" t="n"/>
+      <c r="V122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -12587,6 +12812,7 @@
       <c r="S123" s="15" t="n"/>
       <c r="T123" s="15" t="n"/>
       <c r="U123" s="15" t="n"/>
+      <c r="V123" s="15" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -12635,6 +12861,7 @@
       <c r="S124" s="15" t="n"/>
       <c r="T124" s="15" t="n"/>
       <c r="U124" s="15" t="n"/>
+      <c r="V124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -12683,6 +12910,7 @@
       <c r="S125" s="15" t="n"/>
       <c r="T125" s="15" t="n"/>
       <c r="U125" s="15" t="n"/>
+      <c r="V125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -12731,6 +12959,7 @@
       <c r="S126" s="15" t="n"/>
       <c r="T126" s="15" t="n"/>
       <c r="U126" s="15" t="n"/>
+      <c r="V126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -12779,6 +13008,7 @@
       <c r="S127" s="15" t="n"/>
       <c r="T127" s="15" t="n"/>
       <c r="U127" s="15" t="n"/>
+      <c r="V127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -12827,6 +13057,7 @@
       <c r="S128" s="15" t="n"/>
       <c r="T128" s="15" t="n"/>
       <c r="U128" s="15" t="n"/>
+      <c r="V128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -12875,6 +13106,7 @@
       <c r="S129" s="15" t="n"/>
       <c r="T129" s="15" t="n"/>
       <c r="U129" s="15" t="n"/>
+      <c r="V129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
@@ -12923,6 +13155,7 @@
       <c r="S130" s="15" t="n"/>
       <c r="T130" s="15" t="n"/>
       <c r="U130" s="15" t="n"/>
+      <c r="V130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -12971,6 +13204,7 @@
       <c r="S131" s="15" t="n"/>
       <c r="T131" s="15" t="n"/>
       <c r="U131" s="15" t="n"/>
+      <c r="V131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -13019,6 +13253,7 @@
       <c r="S132" s="15" t="n"/>
       <c r="T132" s="15" t="n"/>
       <c r="U132" s="15" t="n"/>
+      <c r="V132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -13067,6 +13302,7 @@
       <c r="S133" s="15" t="n"/>
       <c r="T133" s="15" t="n"/>
       <c r="U133" s="15" t="n"/>
+      <c r="V133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -13115,6 +13351,7 @@
       <c r="S134" s="15" t="n"/>
       <c r="T134" s="15" t="n"/>
       <c r="U134" s="15" t="n"/>
+      <c r="V134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -13163,6 +13400,7 @@
       <c r="S135" s="15" t="n"/>
       <c r="T135" s="15" t="n"/>
       <c r="U135" s="15" t="n"/>
+      <c r="V135" s="15" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
@@ -13211,6 +13449,7 @@
       <c r="S136" s="15" t="n"/>
       <c r="T136" s="15" t="n"/>
       <c r="U136" s="15" t="n"/>
+      <c r="V136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -13259,6 +13498,7 @@
       <c r="S137" s="15" t="n"/>
       <c r="T137" s="15" t="n"/>
       <c r="U137" s="15" t="n"/>
+      <c r="V137" s="15" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -13307,6 +13547,7 @@
       <c r="S138" s="15" t="n"/>
       <c r="T138" s="15" t="n"/>
       <c r="U138" s="15" t="n"/>
+      <c r="V138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -13343,12 +13584,12 @@
       </c>
       <c r="H139" s="15" t="n"/>
       <c r="I139" s="15" t="n"/>
-      <c r="J139" s="15" t="inlineStr">
+      <c r="J139" s="15" t="n"/>
+      <c r="K139" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K139" s="15" t="n"/>
       <c r="L139" s="15" t="n"/>
       <c r="M139" s="15" t="n"/>
       <c r="N139" s="15" t="n"/>
@@ -13359,6 +13600,7 @@
       <c r="S139" s="15" t="n"/>
       <c r="T139" s="15" t="n"/>
       <c r="U139" s="15" t="n"/>
+      <c r="V139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -13407,6 +13649,7 @@
       <c r="S140" s="15" t="n"/>
       <c r="T140" s="15" t="n"/>
       <c r="U140" s="15" t="n"/>
+      <c r="V140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
@@ -13443,12 +13686,12 @@
       </c>
       <c r="H141" s="15" t="n"/>
       <c r="I141" s="15" t="n"/>
-      <c r="J141" s="15" t="inlineStr">
+      <c r="J141" s="15" t="n"/>
+      <c r="K141" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K141" s="15" t="n"/>
       <c r="L141" s="15" t="n"/>
       <c r="M141" s="15" t="n"/>
       <c r="N141" s="15" t="n"/>
@@ -13459,6 +13702,7 @@
       <c r="S141" s="15" t="n"/>
       <c r="T141" s="15" t="n"/>
       <c r="U141" s="15" t="n"/>
+      <c r="V141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
@@ -13495,12 +13739,12 @@
       </c>
       <c r="H142" s="15" t="n"/>
       <c r="I142" s="15" t="n"/>
-      <c r="J142" s="15" t="inlineStr">
+      <c r="J142" s="15" t="n"/>
+      <c r="K142" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K142" s="15" t="n"/>
       <c r="L142" s="15" t="n"/>
       <c r="M142" s="15" t="n"/>
       <c r="N142" s="15" t="n"/>
@@ -13511,6 +13755,7 @@
       <c r="S142" s="15" t="n"/>
       <c r="T142" s="15" t="n"/>
       <c r="U142" s="15" t="n"/>
+      <c r="V142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -13547,12 +13792,12 @@
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="15" t="n"/>
-      <c r="J143" s="15" t="inlineStr">
+      <c r="J143" s="15" t="n"/>
+      <c r="K143" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K143" s="15" t="n"/>
       <c r="L143" s="15" t="n"/>
       <c r="M143" s="15" t="n"/>
       <c r="N143" s="15" t="n"/>
@@ -13563,6 +13808,7 @@
       <c r="S143" s="15" t="n"/>
       <c r="T143" s="15" t="n"/>
       <c r="U143" s="15" t="n"/>
+      <c r="V143" s="15" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -13599,12 +13845,12 @@
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="15" t="n"/>
-      <c r="J144" s="15" t="inlineStr">
+      <c r="J144" s="15" t="n"/>
+      <c r="K144" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K144" s="15" t="n"/>
       <c r="L144" s="15" t="n"/>
       <c r="M144" s="15" t="n"/>
       <c r="N144" s="15" t="n"/>
@@ -13615,6 +13861,7 @@
       <c r="S144" s="15" t="n"/>
       <c r="T144" s="15" t="n"/>
       <c r="U144" s="15" t="n"/>
+      <c r="V144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -13663,6 +13910,7 @@
       <c r="S145" s="15" t="n"/>
       <c r="T145" s="15" t="n"/>
       <c r="U145" s="15" t="n"/>
+      <c r="V145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
@@ -13711,6 +13959,7 @@
       <c r="S146" s="15" t="n"/>
       <c r="T146" s="15" t="n"/>
       <c r="U146" s="15" t="n"/>
+      <c r="V146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -13747,12 +13996,12 @@
       </c>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="15" t="n"/>
-      <c r="J147" s="15" t="inlineStr">
+      <c r="J147" s="15" t="n"/>
+      <c r="K147" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K147" s="15" t="n"/>
       <c r="L147" s="15" t="n"/>
       <c r="M147" s="15" t="n"/>
       <c r="N147" s="15" t="n"/>
@@ -13763,6 +14012,7 @@
       <c r="S147" s="15" t="n"/>
       <c r="T147" s="15" t="n"/>
       <c r="U147" s="15" t="n"/>
+      <c r="V147" s="15" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -13811,6 +14061,7 @@
       <c r="S148" s="15" t="n"/>
       <c r="T148" s="15" t="n"/>
       <c r="U148" s="15" t="n"/>
+      <c r="V148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -13859,6 +14110,7 @@
       <c r="S149" s="15" t="n"/>
       <c r="T149" s="15" t="n"/>
       <c r="U149" s="15" t="n"/>
+      <c r="V149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
@@ -13907,6 +14159,7 @@
       <c r="S150" s="15" t="n"/>
       <c r="T150" s="15" t="n"/>
       <c r="U150" s="15" t="n"/>
+      <c r="V150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -13955,6 +14208,7 @@
       <c r="S151" s="15" t="n"/>
       <c r="T151" s="15" t="n"/>
       <c r="U151" s="15" t="n"/>
+      <c r="V151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -14003,6 +14257,7 @@
       <c r="S152" s="15" t="n"/>
       <c r="T152" s="15" t="n"/>
       <c r="U152" s="15" t="n"/>
+      <c r="V152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -14051,6 +14306,7 @@
       <c r="S153" s="15" t="n"/>
       <c r="T153" s="15" t="n"/>
       <c r="U153" s="15" t="n"/>
+      <c r="V153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -14087,12 +14343,12 @@
       </c>
       <c r="H154" s="15" t="n"/>
       <c r="I154" s="15" t="n"/>
-      <c r="J154" s="15" t="inlineStr">
+      <c r="J154" s="15" t="n"/>
+      <c r="K154" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K154" s="15" t="n"/>
       <c r="L154" s="15" t="n"/>
       <c r="M154" s="15" t="n"/>
       <c r="N154" s="15" t="n"/>
@@ -14103,6 +14359,7 @@
       <c r="S154" s="15" t="n"/>
       <c r="T154" s="15" t="n"/>
       <c r="U154" s="15" t="n"/>
+      <c r="V154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
@@ -14151,6 +14408,7 @@
       <c r="S155" s="15" t="n"/>
       <c r="T155" s="15" t="n"/>
       <c r="U155" s="15" t="n"/>
+      <c r="V155" s="15" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
@@ -14199,6 +14457,7 @@
       <c r="S156" s="15" t="n"/>
       <c r="T156" s="15" t="n"/>
       <c r="U156" s="15" t="n"/>
+      <c r="V156" s="15" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
@@ -14235,12 +14494,12 @@
       </c>
       <c r="H157" s="15" t="n"/>
       <c r="I157" s="15" t="n"/>
-      <c r="J157" s="15" t="inlineStr">
+      <c r="J157" s="15" t="n"/>
+      <c r="K157" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K157" s="15" t="n"/>
       <c r="L157" s="15" t="n"/>
       <c r="M157" s="15" t="n"/>
       <c r="N157" s="15" t="n"/>
@@ -14251,6 +14510,7 @@
       <c r="S157" s="15" t="n"/>
       <c r="T157" s="15" t="n"/>
       <c r="U157" s="15" t="n"/>
+      <c r="V157" s="15" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
@@ -14295,6 +14555,7 @@
       <c r="S158" s="15" t="n"/>
       <c r="T158" s="15" t="n"/>
       <c r="U158" s="15" t="n"/>
+      <c r="V158" s="15" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
@@ -14343,6 +14604,7 @@
       <c r="S159" s="15" t="n"/>
       <c r="T159" s="15" t="n"/>
       <c r="U159" s="15" t="n"/>
+      <c r="V159" s="15" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
@@ -14379,12 +14641,12 @@
       </c>
       <c r="H160" s="15" t="n"/>
       <c r="I160" s="15" t="n"/>
-      <c r="J160" s="15" t="inlineStr">
+      <c r="J160" s="15" t="n"/>
+      <c r="K160" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K160" s="15" t="n"/>
       <c r="L160" s="15" t="n"/>
       <c r="M160" s="15" t="n"/>
       <c r="N160" s="15" t="n"/>
@@ -14395,6 +14657,7 @@
       <c r="S160" s="15" t="n"/>
       <c r="T160" s="15" t="n"/>
       <c r="U160" s="15" t="n"/>
+      <c r="V160" s="15" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
@@ -14431,12 +14694,12 @@
       </c>
       <c r="H161" s="15" t="n"/>
       <c r="I161" s="15" t="n"/>
-      <c r="J161" s="15" t="inlineStr">
+      <c r="J161" s="15" t="n"/>
+      <c r="K161" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K161" s="15" t="n"/>
       <c r="L161" s="15" t="n"/>
       <c r="M161" s="15" t="n"/>
       <c r="N161" s="15" t="n"/>
@@ -14447,6 +14710,7 @@
       <c r="S161" s="15" t="n"/>
       <c r="T161" s="15" t="n"/>
       <c r="U161" s="15" t="n"/>
+      <c r="V161" s="15" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
@@ -14495,6 +14759,7 @@
       <c r="S162" s="15" t="n"/>
       <c r="T162" s="15" t="n"/>
       <c r="U162" s="15" t="n"/>
+      <c r="V162" s="15" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
@@ -14543,6 +14808,7 @@
       <c r="S163" s="15" t="n"/>
       <c r="T163" s="15" t="n"/>
       <c r="U163" s="15" t="n"/>
+      <c r="V163" s="15" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
@@ -14579,12 +14845,12 @@
       </c>
       <c r="H164" s="15" t="n"/>
       <c r="I164" s="15" t="n"/>
-      <c r="J164" s="15" t="inlineStr">
+      <c r="J164" s="15" t="n"/>
+      <c r="K164" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K164" s="15" t="n"/>
       <c r="L164" s="15" t="n"/>
       <c r="M164" s="15" t="n"/>
       <c r="N164" s="15" t="n"/>
@@ -14595,6 +14861,7 @@
       <c r="S164" s="15" t="n"/>
       <c r="T164" s="15" t="n"/>
       <c r="U164" s="15" t="n"/>
+      <c r="V164" s="15" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
@@ -14639,6 +14906,7 @@
       <c r="S165" s="15" t="n"/>
       <c r="T165" s="15" t="n"/>
       <c r="U165" s="15" t="n"/>
+      <c r="V165" s="15" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
@@ -14687,6 +14955,7 @@
       <c r="S166" s="15" t="n"/>
       <c r="T166" s="15" t="n"/>
       <c r="U166" s="15" t="n"/>
+      <c r="V166" s="15" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
@@ -14723,12 +14992,12 @@
       </c>
       <c r="H167" s="15" t="n"/>
       <c r="I167" s="15" t="n"/>
-      <c r="J167" s="15" t="inlineStr">
+      <c r="J167" s="15" t="n"/>
+      <c r="K167" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K167" s="15" t="n"/>
       <c r="L167" s="15" t="n"/>
       <c r="M167" s="15" t="n"/>
       <c r="N167" s="15" t="n"/>
@@ -14739,6 +15008,7 @@
       <c r="S167" s="15" t="n"/>
       <c r="T167" s="15" t="n"/>
       <c r="U167" s="15" t="n"/>
+      <c r="V167" s="15" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -14787,6 +15057,7 @@
       <c r="S168" s="15" t="n"/>
       <c r="T168" s="15" t="n"/>
       <c r="U168" s="15" t="n"/>
+      <c r="V168" s="15" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
@@ -14835,6 +15106,7 @@
       <c r="S169" s="15" t="n"/>
       <c r="T169" s="15" t="n"/>
       <c r="U169" s="15" t="n"/>
+      <c r="V169" s="15" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -14871,12 +15143,12 @@
       </c>
       <c r="H170" s="15" t="n"/>
       <c r="I170" s="15" t="n"/>
-      <c r="J170" s="15" t="inlineStr">
+      <c r="J170" s="15" t="n"/>
+      <c r="K170" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K170" s="15" t="n"/>
       <c r="L170" s="15" t="n"/>
       <c r="M170" s="15" t="n"/>
       <c r="N170" s="15" t="n"/>
@@ -14887,6 +15159,7 @@
       <c r="S170" s="15" t="n"/>
       <c r="T170" s="15" t="n"/>
       <c r="U170" s="15" t="n"/>
+      <c r="V170" s="15" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
@@ -14931,6 +15204,7 @@
       <c r="S171" s="15" t="n"/>
       <c r="T171" s="15" t="n"/>
       <c r="U171" s="15" t="n"/>
+      <c r="V171" s="15" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -14979,6 +15253,7 @@
       <c r="S172" s="15" t="n"/>
       <c r="T172" s="15" t="n"/>
       <c r="U172" s="15" t="n"/>
+      <c r="V172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -15015,12 +15290,12 @@
       </c>
       <c r="H173" s="15" t="n"/>
       <c r="I173" s="15" t="n"/>
-      <c r="J173" s="15" t="inlineStr">
+      <c r="J173" s="15" t="n"/>
+      <c r="K173" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K173" s="15" t="n"/>
       <c r="L173" s="15" t="n"/>
       <c r="M173" s="15" t="n"/>
       <c r="N173" s="15" t="n"/>
@@ -15031,6 +15306,7 @@
       <c r="S173" s="15" t="n"/>
       <c r="T173" s="15" t="n"/>
       <c r="U173" s="15" t="n"/>
+      <c r="V173" s="15" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
@@ -15079,6 +15355,7 @@
       <c r="S174" s="15" t="n"/>
       <c r="T174" s="15" t="n"/>
       <c r="U174" s="15" t="n"/>
+      <c r="V174" s="15" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -15123,6 +15400,7 @@
       <c r="S175" s="15" t="n"/>
       <c r="T175" s="15" t="n"/>
       <c r="U175" s="15" t="n"/>
+      <c r="V175" s="15" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
@@ -15171,6 +15449,7 @@
       <c r="S176" s="15" t="n"/>
       <c r="T176" s="15" t="n"/>
       <c r="U176" s="15" t="n"/>
+      <c r="V176" s="15" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -15207,12 +15486,12 @@
       </c>
       <c r="H177" s="15" t="n"/>
       <c r="I177" s="15" t="n"/>
-      <c r="J177" s="15" t="inlineStr">
+      <c r="J177" s="15" t="n"/>
+      <c r="K177" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K177" s="15" t="n"/>
       <c r="L177" s="15" t="n"/>
       <c r="M177" s="15" t="n"/>
       <c r="N177" s="15" t="n"/>
@@ -15223,6 +15502,7 @@
       <c r="S177" s="15" t="n"/>
       <c r="T177" s="15" t="n"/>
       <c r="U177" s="15" t="n"/>
+      <c r="V177" s="15" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -15259,12 +15539,12 @@
       </c>
       <c r="H178" s="15" t="n"/>
       <c r="I178" s="15" t="n"/>
-      <c r="J178" s="15" t="inlineStr">
+      <c r="J178" s="15" t="n"/>
+      <c r="K178" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K178" s="15" t="n"/>
       <c r="L178" s="15" t="n"/>
       <c r="M178" s="15" t="n"/>
       <c r="N178" s="15" t="n"/>
@@ -15275,6 +15555,7 @@
       <c r="S178" s="15" t="n"/>
       <c r="T178" s="15" t="n"/>
       <c r="U178" s="15" t="n"/>
+      <c r="V178" s="15" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -15323,6 +15604,7 @@
       <c r="S179" s="15" t="n"/>
       <c r="T179" s="15" t="n"/>
       <c r="U179" s="15" t="n"/>
+      <c r="V179" s="15" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
@@ -15371,6 +15653,7 @@
       <c r="S180" s="15" t="n"/>
       <c r="T180" s="15" t="n"/>
       <c r="U180" s="15" t="n"/>
+      <c r="V180" s="15" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
@@ -15419,6 +15702,7 @@
       <c r="S181" s="15" t="n"/>
       <c r="T181" s="15" t="n"/>
       <c r="U181" s="15" t="n"/>
+      <c r="V181" s="15" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
@@ -15467,6 +15751,7 @@
       <c r="S182" s="15" t="n"/>
       <c r="T182" s="15" t="n"/>
       <c r="U182" s="15" t="n"/>
+      <c r="V182" s="15" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
@@ -15515,6 +15800,7 @@
       <c r="S183" s="15" t="n"/>
       <c r="T183" s="15" t="n"/>
       <c r="U183" s="15" t="n"/>
+      <c r="V183" s="15" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
@@ -15563,6 +15849,7 @@
       <c r="S184" s="15" t="n"/>
       <c r="T184" s="15" t="n"/>
       <c r="U184" s="15" t="n"/>
+      <c r="V184" s="15" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
@@ -15611,6 +15898,7 @@
       <c r="S185" s="15" t="n"/>
       <c r="T185" s="15" t="n"/>
       <c r="U185" s="15" t="n"/>
+      <c r="V185" s="15" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
@@ -15659,6 +15947,7 @@
       <c r="S186" s="15" t="n"/>
       <c r="T186" s="15" t="n"/>
       <c r="U186" s="15" t="n"/>
+      <c r="V186" s="15" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
@@ -15707,6 +15996,7 @@
       <c r="S187" s="15" t="n"/>
       <c r="T187" s="15" t="n"/>
       <c r="U187" s="15" t="n"/>
+      <c r="V187" s="15" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -15755,6 +16045,7 @@
       <c r="S188" s="15" t="n"/>
       <c r="T188" s="15" t="n"/>
       <c r="U188" s="15" t="n"/>
+      <c r="V188" s="15" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -15791,12 +16082,12 @@
       </c>
       <c r="H189" s="15" t="n"/>
       <c r="I189" s="15" t="n"/>
-      <c r="J189" s="15" t="inlineStr">
+      <c r="J189" s="15" t="n"/>
+      <c r="K189" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K189" s="15" t="n"/>
       <c r="L189" s="15" t="n"/>
       <c r="M189" s="15" t="n"/>
       <c r="N189" s="15" t="n"/>
@@ -15807,6 +16098,7 @@
       <c r="S189" s="15" t="n"/>
       <c r="T189" s="15" t="n"/>
       <c r="U189" s="15" t="n"/>
+      <c r="V189" s="15" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
@@ -15855,6 +16147,7 @@
       <c r="S190" s="15" t="n"/>
       <c r="T190" s="15" t="n"/>
       <c r="U190" s="15" t="n"/>
+      <c r="V190" s="15" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -15903,6 +16196,7 @@
       <c r="S191" s="15" t="n"/>
       <c r="T191" s="15" t="n"/>
       <c r="U191" s="15" t="n"/>
+      <c r="V191" s="15" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -15951,6 +16245,7 @@
       <c r="S192" s="15" t="n"/>
       <c r="T192" s="15" t="n"/>
       <c r="U192" s="15" t="n"/>
+      <c r="V192" s="15" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -15987,12 +16282,12 @@
       </c>
       <c r="H193" s="15" t="n"/>
       <c r="I193" s="15" t="n"/>
-      <c r="J193" s="15" t="inlineStr">
+      <c r="J193" s="15" t="n"/>
+      <c r="K193" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K193" s="15" t="n"/>
       <c r="L193" s="15" t="n"/>
       <c r="M193" s="15" t="n"/>
       <c r="N193" s="15" t="n"/>
@@ -16003,6 +16298,7 @@
       <c r="S193" s="15" t="n"/>
       <c r="T193" s="15" t="n"/>
       <c r="U193" s="15" t="n"/>
+      <c r="V193" s="15" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -16051,6 +16347,7 @@
       <c r="S194" s="15" t="n"/>
       <c r="T194" s="15" t="n"/>
       <c r="U194" s="15" t="n"/>
+      <c r="V194" s="15" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
@@ -16099,6 +16396,7 @@
       <c r="S195" s="15" t="n"/>
       <c r="T195" s="15" t="n"/>
       <c r="U195" s="15" t="n"/>
+      <c r="V195" s="15" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
@@ -16147,6 +16445,7 @@
       <c r="S196" s="15" t="n"/>
       <c r="T196" s="15" t="n"/>
       <c r="U196" s="15" t="n"/>
+      <c r="V196" s="15" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
@@ -16183,12 +16482,12 @@
       </c>
       <c r="H197" s="15" t="n"/>
       <c r="I197" s="15" t="n"/>
-      <c r="J197" s="15" t="inlineStr">
+      <c r="J197" s="15" t="n"/>
+      <c r="K197" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K197" s="15" t="n"/>
       <c r="L197" s="15" t="n"/>
       <c r="M197" s="15" t="n"/>
       <c r="N197" s="15" t="n"/>
@@ -16199,6 +16498,7 @@
       <c r="S197" s="15" t="n"/>
       <c r="T197" s="15" t="n"/>
       <c r="U197" s="15" t="n"/>
+      <c r="V197" s="15" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
@@ -16235,12 +16535,12 @@
       </c>
       <c r="H198" s="15" t="n"/>
       <c r="I198" s="15" t="n"/>
-      <c r="J198" s="15" t="inlineStr">
+      <c r="J198" s="15" t="n"/>
+      <c r="K198" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K198" s="15" t="n"/>
       <c r="L198" s="15" t="n"/>
       <c r="M198" s="15" t="n"/>
       <c r="N198" s="15" t="n"/>
@@ -16251,6 +16551,7 @@
       <c r="S198" s="15" t="n"/>
       <c r="T198" s="15" t="n"/>
       <c r="U198" s="15" t="n"/>
+      <c r="V198" s="15" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
@@ -16299,6 +16600,7 @@
       <c r="S199" s="15" t="n"/>
       <c r="T199" s="15" t="n"/>
       <c r="U199" s="15" t="n"/>
+      <c r="V199" s="15" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
@@ -16347,6 +16649,7 @@
       <c r="S200" s="15" t="n"/>
       <c r="T200" s="15" t="n"/>
       <c r="U200" s="15" t="n"/>
+      <c r="V200" s="15" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
@@ -16391,6 +16694,7 @@
       <c r="S201" s="15" t="n"/>
       <c r="T201" s="15" t="n"/>
       <c r="U201" s="15" t="n"/>
+      <c r="V201" s="15" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
@@ -16439,6 +16743,7 @@
       <c r="S202" s="15" t="n"/>
       <c r="T202" s="15" t="n"/>
       <c r="U202" s="15" t="n"/>
+      <c r="V202" s="15" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
@@ -16487,6 +16792,7 @@
       <c r="S203" s="15" t="n"/>
       <c r="T203" s="15" t="n"/>
       <c r="U203" s="15" t="n"/>
+      <c r="V203" s="15" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
@@ -16535,6 +16841,7 @@
       <c r="S204" s="15" t="n"/>
       <c r="T204" s="15" t="n"/>
       <c r="U204" s="15" t="n"/>
+      <c r="V204" s="15" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
@@ -16583,6 +16890,7 @@
       <c r="S205" s="15" t="n"/>
       <c r="T205" s="15" t="n"/>
       <c r="U205" s="15" t="n"/>
+      <c r="V205" s="15" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -16631,6 +16939,7 @@
       <c r="S206" s="15" t="n"/>
       <c r="T206" s="15" t="n"/>
       <c r="U206" s="15" t="n"/>
+      <c r="V206" s="15" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -16679,6 +16988,7 @@
       <c r="S207" s="15" t="n"/>
       <c r="T207" s="15" t="n"/>
       <c r="U207" s="15" t="n"/>
+      <c r="V207" s="15" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -16723,6 +17033,7 @@
       <c r="S208" s="15" t="n"/>
       <c r="T208" s="15" t="n"/>
       <c r="U208" s="15" t="n"/>
+      <c r="V208" s="15" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -16771,6 +17082,7 @@
       <c r="S209" s="15" t="n"/>
       <c r="T209" s="15" t="n"/>
       <c r="U209" s="15" t="n"/>
+      <c r="V209" s="15" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
@@ -16819,6 +17131,7 @@
       <c r="S210" s="15" t="n"/>
       <c r="T210" s="15" t="n"/>
       <c r="U210" s="15" t="n"/>
+      <c r="V210" s="15" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
@@ -16867,6 +17180,7 @@
       <c r="S211" s="15" t="n"/>
       <c r="T211" s="15" t="n"/>
       <c r="U211" s="15" t="n"/>
+      <c r="V211" s="15" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
@@ -16915,6 +17229,7 @@
       <c r="S212" s="15" t="n"/>
       <c r="T212" s="15" t="n"/>
       <c r="U212" s="15" t="n"/>
+      <c r="V212" s="15" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -16959,6 +17274,7 @@
       <c r="S213" s="15" t="n"/>
       <c r="T213" s="15" t="n"/>
       <c r="U213" s="15" t="n"/>
+      <c r="V213" s="15" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -17007,6 +17323,7 @@
       <c r="S214" s="15" t="n"/>
       <c r="T214" s="15" t="n"/>
       <c r="U214" s="15" t="n"/>
+      <c r="V214" s="15" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
@@ -17055,6 +17372,7 @@
       <c r="S215" s="15" t="n"/>
       <c r="T215" s="15" t="n"/>
       <c r="U215" s="15" t="n"/>
+      <c r="V215" s="15" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
@@ -17103,6 +17421,7 @@
       <c r="S216" s="15" t="n"/>
       <c r="T216" s="15" t="n"/>
       <c r="U216" s="15" t="n"/>
+      <c r="V216" s="15" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -17151,6 +17470,7 @@
       <c r="S217" s="15" t="n"/>
       <c r="T217" s="15" t="n"/>
       <c r="U217" s="15" t="n"/>
+      <c r="V217" s="15" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
@@ -17199,6 +17519,7 @@
       <c r="S218" s="15" t="n"/>
       <c r="T218" s="15" t="n"/>
       <c r="U218" s="15" t="n"/>
+      <c r="V218" s="15" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
@@ -17247,6 +17568,7 @@
       <c r="S219" s="15" t="n"/>
       <c r="T219" s="15" t="n"/>
       <c r="U219" s="15" t="n"/>
+      <c r="V219" s="15" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
@@ -17295,6 +17617,7 @@
       <c r="S220" s="15" t="n"/>
       <c r="T220" s="15" t="n"/>
       <c r="U220" s="15" t="n"/>
+      <c r="V220" s="15" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
@@ -17343,6 +17666,7 @@
       <c r="S221" s="15" t="n"/>
       <c r="T221" s="15" t="n"/>
       <c r="U221" s="15" t="n"/>
+      <c r="V221" s="15" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
@@ -17391,6 +17715,7 @@
       <c r="S222" s="15" t="n"/>
       <c r="T222" s="15" t="n"/>
       <c r="U222" s="15" t="n"/>
+      <c r="V222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
@@ -17439,6 +17764,7 @@
       <c r="S223" s="15" t="n"/>
       <c r="T223" s="15" t="n"/>
       <c r="U223" s="15" t="n"/>
+      <c r="V223" s="15" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
@@ -17487,6 +17813,7 @@
       <c r="S224" s="15" t="n"/>
       <c r="T224" s="15" t="n"/>
       <c r="U224" s="15" t="n"/>
+      <c r="V224" s="15" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
@@ -17531,6 +17858,7 @@
       <c r="S225" s="15" t="n"/>
       <c r="T225" s="15" t="n"/>
       <c r="U225" s="15" t="n"/>
+      <c r="V225" s="15" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
@@ -17579,6 +17907,7 @@
       <c r="S226" s="15" t="n"/>
       <c r="T226" s="15" t="n"/>
       <c r="U226" s="15" t="n"/>
+      <c r="V226" s="15" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
@@ -17627,6 +17956,7 @@
       <c r="S227" s="15" t="n"/>
       <c r="T227" s="15" t="n"/>
       <c r="U227" s="15" t="n"/>
+      <c r="V227" s="15" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
@@ -17675,6 +18005,7 @@
       <c r="S228" s="15" t="n"/>
       <c r="T228" s="15" t="n"/>
       <c r="U228" s="15" t="n"/>
+      <c r="V228" s="15" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
@@ -17723,6 +18054,7 @@
       <c r="S229" s="15" t="n"/>
       <c r="T229" s="15" t="n"/>
       <c r="U229" s="15" t="n"/>
+      <c r="V229" s="15" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
@@ -17771,6 +18103,7 @@
       <c r="S230" s="15" t="n"/>
       <c r="T230" s="15" t="n"/>
       <c r="U230" s="15" t="n"/>
+      <c r="V230" s="15" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
@@ -17819,6 +18152,7 @@
       <c r="S231" s="15" t="n"/>
       <c r="T231" s="15" t="n"/>
       <c r="U231" s="15" t="n"/>
+      <c r="V231" s="15" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
@@ -17867,6 +18201,7 @@
       <c r="S232" s="15" t="n"/>
       <c r="T232" s="15" t="n"/>
       <c r="U232" s="15" t="n"/>
+      <c r="V232" s="15" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
@@ -17915,6 +18250,7 @@
       <c r="S233" s="15" t="n"/>
       <c r="T233" s="15" t="n"/>
       <c r="U233" s="15" t="n"/>
+      <c r="V233" s="15" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
@@ -17963,6 +18299,7 @@
       <c r="S234" s="15" t="n"/>
       <c r="T234" s="15" t="n"/>
       <c r="U234" s="15" t="n"/>
+      <c r="V234" s="15" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
@@ -18011,6 +18348,7 @@
       <c r="S235" s="15" t="n"/>
       <c r="T235" s="15" t="n"/>
       <c r="U235" s="15" t="n"/>
+      <c r="V235" s="15" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
@@ -18059,6 +18397,7 @@
       <c r="S236" s="15" t="n"/>
       <c r="T236" s="15" t="n"/>
       <c r="U236" s="15" t="n"/>
+      <c r="V236" s="15" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
@@ -18107,6 +18446,7 @@
       <c r="S237" s="15" t="n"/>
       <c r="T237" s="15" t="n"/>
       <c r="U237" s="15" t="n"/>
+      <c r="V237" s="15" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
@@ -18151,6 +18491,7 @@
       <c r="S238" s="15" t="n"/>
       <c r="T238" s="15" t="n"/>
       <c r="U238" s="15" t="n"/>
+      <c r="V238" s="15" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
@@ -18199,6 +18540,7 @@
       <c r="S239" s="15" t="n"/>
       <c r="T239" s="15" t="n"/>
       <c r="U239" s="15" t="n"/>
+      <c r="V239" s="15" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
@@ -18247,6 +18589,7 @@
       <c r="S240" s="15" t="n"/>
       <c r="T240" s="15" t="n"/>
       <c r="U240" s="15" t="n"/>
+      <c r="V240" s="15" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
@@ -18295,6 +18638,7 @@
       <c r="S241" s="15" t="n"/>
       <c r="T241" s="15" t="n"/>
       <c r="U241" s="15" t="n"/>
+      <c r="V241" s="15" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
@@ -18343,6 +18687,7 @@
       <c r="S242" s="15" t="n"/>
       <c r="T242" s="15" t="n"/>
       <c r="U242" s="15" t="n"/>
+      <c r="V242" s="15" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
@@ -18391,6 +18736,7 @@
       <c r="S243" s="15" t="n"/>
       <c r="T243" s="15" t="n"/>
       <c r="U243" s="15" t="n"/>
+      <c r="V243" s="15" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
@@ -18439,6 +18785,7 @@
       <c r="S244" s="15" t="n"/>
       <c r="T244" s="15" t="n"/>
       <c r="U244" s="15" t="n"/>
+      <c r="V244" s="15" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
@@ -18483,6 +18830,7 @@
       <c r="S245" s="15" t="n"/>
       <c r="T245" s="15" t="n"/>
       <c r="U245" s="15" t="n"/>
+      <c r="V245" s="15" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
@@ -18519,12 +18867,12 @@
       </c>
       <c r="H246" s="15" t="n"/>
       <c r="I246" s="15" t="n"/>
-      <c r="J246" s="15" t="inlineStr">
+      <c r="J246" s="15" t="n"/>
+      <c r="K246" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K246" s="15" t="n"/>
       <c r="L246" s="15" t="n"/>
       <c r="M246" s="15" t="n"/>
       <c r="N246" s="15" t="n"/>
@@ -18535,6 +18883,7 @@
       <c r="S246" s="15" t="n"/>
       <c r="T246" s="15" t="n"/>
       <c r="U246" s="15" t="n"/>
+      <c r="V246" s="15" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
@@ -18583,6 +18932,7 @@
       <c r="S247" s="15" t="n"/>
       <c r="T247" s="15" t="n"/>
       <c r="U247" s="15" t="n"/>
+      <c r="V247" s="15" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
@@ -18627,6 +18977,7 @@
       <c r="S248" s="15" t="n"/>
       <c r="T248" s="15" t="n"/>
       <c r="U248" s="15" t="n"/>
+      <c r="V248" s="15" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
@@ -18675,6 +19026,7 @@
       <c r="S249" s="15" t="n"/>
       <c r="T249" s="15" t="n"/>
       <c r="U249" s="15" t="n"/>
+      <c r="V249" s="15" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
@@ -18723,6 +19075,7 @@
       <c r="S250" s="15" t="n"/>
       <c r="T250" s="15" t="n"/>
       <c r="U250" s="15" t="n"/>
+      <c r="V250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
@@ -18771,6 +19124,7 @@
       <c r="S251" s="15" t="n"/>
       <c r="T251" s="15" t="n"/>
       <c r="U251" s="15" t="n"/>
+      <c r="V251" s="15" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
@@ -18819,6 +19173,7 @@
       <c r="S252" s="15" t="n"/>
       <c r="T252" s="15" t="n"/>
       <c r="U252" s="15" t="n"/>
+      <c r="V252" s="15" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
@@ -18867,6 +19222,7 @@
       <c r="S253" s="15" t="n"/>
       <c r="T253" s="15" t="n"/>
       <c r="U253" s="15" t="n"/>
+      <c r="V253" s="15" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
@@ -18911,6 +19267,7 @@
       <c r="S254" s="15" t="n"/>
       <c r="T254" s="15" t="n"/>
       <c r="U254" s="15" t="n"/>
+      <c r="V254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
@@ -18959,6 +19316,7 @@
       <c r="S255" s="15" t="n"/>
       <c r="T255" s="15" t="n"/>
       <c r="U255" s="15" t="n"/>
+      <c r="V255" s="15" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
@@ -19007,6 +19365,7 @@
       <c r="S256" s="15" t="n"/>
       <c r="T256" s="15" t="n"/>
       <c r="U256" s="15" t="n"/>
+      <c r="V256" s="15" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
@@ -19051,6 +19410,7 @@
       <c r="S257" s="15" t="n"/>
       <c r="T257" s="15" t="n"/>
       <c r="U257" s="15" t="n"/>
+      <c r="V257" s="15" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
@@ -19099,6 +19459,7 @@
       <c r="S258" s="15" t="n"/>
       <c r="T258" s="15" t="n"/>
       <c r="U258" s="15" t="n"/>
+      <c r="V258" s="15" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
@@ -19147,6 +19508,7 @@
       <c r="S259" s="15" t="n"/>
       <c r="T259" s="15" t="n"/>
       <c r="U259" s="15" t="n"/>
+      <c r="V259" s="15" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
@@ -19195,6 +19557,7 @@
       <c r="S260" s="15" t="n"/>
       <c r="T260" s="15" t="n"/>
       <c r="U260" s="15" t="n"/>
+      <c r="V260" s="15" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
@@ -19243,6 +19606,7 @@
       <c r="S261" s="15" t="n"/>
       <c r="T261" s="15" t="n"/>
       <c r="U261" s="15" t="n"/>
+      <c r="V261" s="15" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
@@ -19291,6 +19655,7 @@
       <c r="S262" s="15" t="n"/>
       <c r="T262" s="15" t="n"/>
       <c r="U262" s="15" t="n"/>
+      <c r="V262" s="15" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
@@ -19339,6 +19704,7 @@
       <c r="S263" s="15" t="n"/>
       <c r="T263" s="15" t="n"/>
       <c r="U263" s="15" t="n"/>
+      <c r="V263" s="15" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
@@ -19387,6 +19753,7 @@
       <c r="S264" s="15" t="n"/>
       <c r="T264" s="15" t="n"/>
       <c r="U264" s="15" t="n"/>
+      <c r="V264" s="15" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
@@ -19435,6 +19802,7 @@
       <c r="S265" s="15" t="n"/>
       <c r="T265" s="15" t="n"/>
       <c r="U265" s="15" t="n"/>
+      <c r="V265" s="15" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
@@ -19483,6 +19851,7 @@
       <c r="S266" s="15" t="n"/>
       <c r="T266" s="15" t="n"/>
       <c r="U266" s="15" t="n"/>
+      <c r="V266" s="15" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
@@ -19531,6 +19900,7 @@
       <c r="S267" s="15" t="n"/>
       <c r="T267" s="15" t="n"/>
       <c r="U267" s="15" t="n"/>
+      <c r="V267" s="15" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
@@ -19579,6 +19949,7 @@
       <c r="S268" s="15" t="n"/>
       <c r="T268" s="15" t="n"/>
       <c r="U268" s="15" t="n"/>
+      <c r="V268" s="15" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
@@ -19627,6 +19998,7 @@
       <c r="S269" s="15" t="n"/>
       <c r="T269" s="15" t="n"/>
       <c r="U269" s="15" t="n"/>
+      <c r="V269" s="15" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
@@ -19675,6 +20047,7 @@
       <c r="S270" s="15" t="n"/>
       <c r="T270" s="15" t="n"/>
       <c r="U270" s="15" t="n"/>
+      <c r="V270" s="15" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
@@ -19723,6 +20096,7 @@
       <c r="S271" s="15" t="n"/>
       <c r="T271" s="15" t="n"/>
       <c r="U271" s="15" t="n"/>
+      <c r="V271" s="15" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
@@ -19771,6 +20145,7 @@
       <c r="S272" s="15" t="n"/>
       <c r="T272" s="15" t="n"/>
       <c r="U272" s="15" t="n"/>
+      <c r="V272" s="15" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
@@ -19819,6 +20194,7 @@
       <c r="S273" s="15" t="n"/>
       <c r="T273" s="15" t="n"/>
       <c r="U273" s="15" t="n"/>
+      <c r="V273" s="15" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
@@ -19867,6 +20243,7 @@
       <c r="S274" s="15" t="n"/>
       <c r="T274" s="15" t="n"/>
       <c r="U274" s="15" t="n"/>
+      <c r="V274" s="15" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
@@ -19915,6 +20292,7 @@
       <c r="S275" s="15" t="n"/>
       <c r="T275" s="15" t="n"/>
       <c r="U275" s="15" t="n"/>
+      <c r="V275" s="15" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
@@ -19963,6 +20341,7 @@
       <c r="S276" s="15" t="n"/>
       <c r="T276" s="15" t="n"/>
       <c r="U276" s="15" t="n"/>
+      <c r="V276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
@@ -20011,6 +20390,7 @@
       <c r="S277" s="15" t="n"/>
       <c r="T277" s="15" t="n"/>
       <c r="U277" s="15" t="n"/>
+      <c r="V277" s="15" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
@@ -20059,6 +20439,7 @@
       <c r="S278" s="15" t="n"/>
       <c r="T278" s="15" t="n"/>
       <c r="U278" s="15" t="n"/>
+      <c r="V278" s="15" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
@@ -20107,6 +20488,7 @@
       <c r="S279" s="15" t="n"/>
       <c r="T279" s="15" t="n"/>
       <c r="U279" s="15" t="n"/>
+      <c r="V279" s="15" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
@@ -20155,6 +20537,7 @@
       <c r="S280" s="15" t="n"/>
       <c r="T280" s="15" t="n"/>
       <c r="U280" s="15" t="n"/>
+      <c r="V280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
@@ -20203,6 +20586,7 @@
       <c r="S281" s="15" t="n"/>
       <c r="T281" s="15" t="n"/>
       <c r="U281" s="15" t="n"/>
+      <c r="V281" s="15" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
@@ -20251,6 +20635,7 @@
       <c r="S282" s="15" t="n"/>
       <c r="T282" s="15" t="n"/>
       <c r="U282" s="15" t="n"/>
+      <c r="V282" s="15" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
@@ -20299,6 +20684,7 @@
       <c r="S283" s="15" t="n"/>
       <c r="T283" s="15" t="n"/>
       <c r="U283" s="15" t="n"/>
+      <c r="V283" s="15" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
@@ -20343,6 +20729,7 @@
       <c r="S284" s="15" t="n"/>
       <c r="T284" s="15" t="n"/>
       <c r="U284" s="15" t="n"/>
+      <c r="V284" s="15" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
@@ -20391,6 +20778,7 @@
       <c r="S285" s="15" t="n"/>
       <c r="T285" s="15" t="n"/>
       <c r="U285" s="15" t="n"/>
+      <c r="V285" s="15" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
@@ -20435,6 +20823,7 @@
       <c r="S286" s="15" t="n"/>
       <c r="T286" s="15" t="n"/>
       <c r="U286" s="15" t="n"/>
+      <c r="V286" s="15" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
@@ -20483,6 +20872,7 @@
       <c r="S287" s="15" t="n"/>
       <c r="T287" s="15" t="n"/>
       <c r="U287" s="15" t="n"/>
+      <c r="V287" s="15" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
@@ -20531,6 +20921,7 @@
       <c r="S288" s="15" t="n"/>
       <c r="T288" s="15" t="n"/>
       <c r="U288" s="15" t="n"/>
+      <c r="V288" s="15" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
@@ -20567,12 +20958,12 @@
       </c>
       <c r="H289" s="15" t="n"/>
       <c r="I289" s="15" t="n"/>
-      <c r="J289" s="15" t="inlineStr">
+      <c r="J289" s="15" t="n"/>
+      <c r="K289" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K289" s="15" t="n"/>
       <c r="L289" s="15" t="n"/>
       <c r="M289" s="15" t="n"/>
       <c r="N289" s="15" t="n"/>
@@ -20583,6 +20974,7 @@
       <c r="S289" s="15" t="n"/>
       <c r="T289" s="15" t="n"/>
       <c r="U289" s="15" t="n"/>
+      <c r="V289" s="15" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
@@ -20631,6 +21023,7 @@
       <c r="S290" s="15" t="n"/>
       <c r="T290" s="15" t="n"/>
       <c r="U290" s="15" t="n"/>
+      <c r="V290" s="15" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
@@ -20675,6 +21068,7 @@
       <c r="S291" s="15" t="n"/>
       <c r="T291" s="15" t="n"/>
       <c r="U291" s="15" t="n"/>
+      <c r="V291" s="15" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
@@ -20723,6 +21117,7 @@
       <c r="S292" s="15" t="n"/>
       <c r="T292" s="15" t="n"/>
       <c r="U292" s="15" t="n"/>
+      <c r="V292" s="15" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
@@ -20771,6 +21166,7 @@
       <c r="S293" s="15" t="n"/>
       <c r="T293" s="15" t="n"/>
       <c r="U293" s="15" t="n"/>
+      <c r="V293" s="15" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
@@ -20819,6 +21215,7 @@
       <c r="S294" s="15" t="n"/>
       <c r="T294" s="15" t="n"/>
       <c r="U294" s="15" t="n"/>
+      <c r="V294" s="15" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
@@ -20867,6 +21264,7 @@
       <c r="S295" s="15" t="n"/>
       <c r="T295" s="15" t="n"/>
       <c r="U295" s="15" t="n"/>
+      <c r="V295" s="15" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
@@ -20915,6 +21313,7 @@
       <c r="S296" s="15" t="n"/>
       <c r="T296" s="15" t="n"/>
       <c r="U296" s="15" t="n"/>
+      <c r="V296" s="15" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
@@ -20963,6 +21362,7 @@
       <c r="S297" s="15" t="n"/>
       <c r="T297" s="15" t="n"/>
       <c r="U297" s="15" t="n"/>
+      <c r="V297" s="15" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
@@ -21011,6 +21411,7 @@
       <c r="S298" s="15" t="n"/>
       <c r="T298" s="15" t="n"/>
       <c r="U298" s="15" t="n"/>
+      <c r="V298" s="15" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
@@ -21059,6 +21460,7 @@
       <c r="S299" s="15" t="n"/>
       <c r="T299" s="15" t="n"/>
       <c r="U299" s="15" t="n"/>
+      <c r="V299" s="15" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
@@ -21107,6 +21509,7 @@
       <c r="S300" s="15" t="n"/>
       <c r="T300" s="15" t="n"/>
       <c r="U300" s="15" t="n"/>
+      <c r="V300" s="15" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
@@ -21143,17 +21546,17 @@
       </c>
       <c r="H301" s="15" t="n"/>
       <c r="I301" s="15" t="n"/>
-      <c r="J301" s="15" t="inlineStr">
+      <c r="J301" s="15" t="n"/>
+      <c r="K301" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K301" s="15" t="inlineStr">
+      <c r="L301" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes - Stunfisk ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
-      <c r="L301" s="15" t="n"/>
       <c r="M301" s="15" t="n"/>
       <c r="N301" s="15" t="n"/>
       <c r="O301" s="15" t="n"/>
@@ -21163,6 +21566,7 @@
       <c r="S301" s="15" t="n"/>
       <c r="T301" s="15" t="n"/>
       <c r="U301" s="15" t="n"/>
+      <c r="V301" s="15" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
@@ -21195,12 +21599,12 @@
       <c r="G302" s="15" t="n"/>
       <c r="H302" s="15" t="n"/>
       <c r="I302" s="15" t="n"/>
-      <c r="J302" s="15" t="inlineStr">
+      <c r="J302" s="15" t="n"/>
+      <c r="K302" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K302" s="15" t="n"/>
       <c r="L302" s="15" t="n"/>
       <c r="M302" s="15" t="n"/>
       <c r="N302" s="15" t="n"/>
@@ -21211,6 +21615,7 @@
       <c r="S302" s="15" t="n"/>
       <c r="T302" s="15" t="n"/>
       <c r="U302" s="15" t="n"/>
+      <c r="V302" s="15" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
@@ -21243,12 +21648,12 @@
       <c r="G303" s="15" t="n"/>
       <c r="H303" s="15" t="n"/>
       <c r="I303" s="15" t="n"/>
-      <c r="J303" s="15" t="inlineStr">
+      <c r="J303" s="15" t="n"/>
+      <c r="K303" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K303" s="15" t="n"/>
       <c r="L303" s="15" t="n"/>
       <c r="M303" s="15" t="n"/>
       <c r="N303" s="15" t="n"/>
@@ -21259,6 +21664,7 @@
       <c r="S303" s="15" t="n"/>
       <c r="T303" s="15" t="n"/>
       <c r="U303" s="15" t="n"/>
+      <c r="V303" s="15" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
@@ -21295,12 +21701,12 @@
       </c>
       <c r="H304" s="15" t="n"/>
       <c r="I304" s="15" t="n"/>
-      <c r="J304" s="15" t="inlineStr">
+      <c r="J304" s="15" t="n"/>
+      <c r="K304" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K304" s="15" t="n"/>
       <c r="L304" s="15" t="n"/>
       <c r="M304" s="15" t="n"/>
       <c r="N304" s="15" t="n"/>
@@ -21311,6 +21717,7 @@
       <c r="S304" s="15" t="n"/>
       <c r="T304" s="15" t="n"/>
       <c r="U304" s="15" t="n"/>
+      <c r="V304" s="15" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
@@ -21347,12 +21754,12 @@
       </c>
       <c r="H305" s="15" t="n"/>
       <c r="I305" s="15" t="n"/>
-      <c r="J305" s="15" t="inlineStr">
+      <c r="J305" s="15" t="n"/>
+      <c r="K305" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K305" s="15" t="n"/>
       <c r="L305" s="15" t="n"/>
       <c r="M305" s="15" t="n"/>
       <c r="N305" s="15" t="n"/>
@@ -21363,6 +21770,7 @@
       <c r="S305" s="15" t="n"/>
       <c r="T305" s="15" t="n"/>
       <c r="U305" s="15" t="n"/>
+      <c r="V305" s="15" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
@@ -21399,17 +21807,17 @@
       </c>
       <c r="H306" s="15" t="n"/>
       <c r="I306" s="15" t="n"/>
-      <c r="J306" s="15" t="inlineStr">
+      <c r="J306" s="15" t="n"/>
+      <c r="K306" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K306" s="15" t="inlineStr">
+      <c r="L306" s="15" t="inlineStr">
         <is>
           <t>Journey Together - Volcanion ex - Double Black Star - Double Rare</t>
         </is>
       </c>
-      <c r="L306" s="15" t="n"/>
       <c r="M306" s="15" t="n"/>
       <c r="N306" s="15" t="n"/>
       <c r="O306" s="15" t="n"/>
@@ -21419,6 +21827,7 @@
       <c r="S306" s="15" t="n"/>
       <c r="T306" s="15" t="n"/>
       <c r="U306" s="15" t="n"/>
+      <c r="V306" s="15" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
@@ -21455,17 +21864,17 @@
       </c>
       <c r="H307" s="15" t="n"/>
       <c r="I307" s="15" t="n"/>
-      <c r="J307" s="15" t="inlineStr">
+      <c r="J307" s="15" t="n"/>
+      <c r="K307" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K307" s="15" t="inlineStr">
+      <c r="L307" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Rotom ex - Double Black Star- Double Rare</t>
         </is>
       </c>
-      <c r="L307" s="15" t="n"/>
       <c r="M307" s="15" t="n"/>
       <c r="N307" s="15" t="n"/>
       <c r="O307" s="15" t="n"/>
@@ -21474,7 +21883,8 @@
       <c r="R307" s="15" t="n"/>
       <c r="S307" s="15" t="n"/>
       <c r="T307" s="15" t="n"/>
-      <c r="U307" s="15" t="inlineStr">
+      <c r="U307" s="15" t="n"/>
+      <c r="V307" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -21515,17 +21925,17 @@
       </c>
       <c r="H308" s="15" t="n"/>
       <c r="I308" s="15" t="n"/>
-      <c r="J308" s="15" t="inlineStr">
+      <c r="J308" s="15" t="n"/>
+      <c r="K308" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K308" s="15" t="inlineStr">
+      <c r="L308" s="15" t="inlineStr">
         <is>
           <t>Journey Together - Trainer - Ruffian - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
-      <c r="L308" s="15" t="n"/>
       <c r="M308" s="15" t="n"/>
       <c r="N308" s="15" t="n"/>
       <c r="O308" s="15" t="n"/>
@@ -21535,6 +21945,7 @@
       <c r="S308" s="15" t="n"/>
       <c r="T308" s="15" t="n"/>
       <c r="U308" s="15" t="n"/>
+      <c r="V308" s="15" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
@@ -21571,17 +21982,17 @@
       </c>
       <c r="H309" s="15" t="n"/>
       <c r="I309" s="15" t="n"/>
-      <c r="J309" s="15" t="inlineStr">
+      <c r="J309" s="15" t="n"/>
+      <c r="K309" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K309" s="15" t="inlineStr">
+      <c r="L309" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Mismagius ex - Double Black Star - Double Rare</t>
         </is>
       </c>
-      <c r="L309" s="15" t="n"/>
       <c r="M309" s="15" t="n"/>
       <c r="N309" s="15" t="n"/>
       <c r="O309" s="15" t="n"/>
@@ -21591,6 +22002,7 @@
       <c r="S309" s="15" t="n"/>
       <c r="T309" s="15" t="n"/>
       <c r="U309" s="15" t="n"/>
+      <c r="V309" s="15" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
@@ -21623,17 +22035,17 @@
       <c r="G310" s="15" t="n"/>
       <c r="H310" s="15" t="n"/>
       <c r="I310" s="15" t="n"/>
-      <c r="J310" s="15" t="inlineStr">
+      <c r="J310" s="15" t="n"/>
+      <c r="K310" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K310" s="15" t="inlineStr">
+      <c r="L310" s="15" t="inlineStr">
         <is>
           <t>Cyber Judge - Incineroar ex - SR - Super Rare</t>
         </is>
       </c>
-      <c r="L310" s="15" t="n"/>
       <c r="M310" s="15" t="n"/>
       <c r="N310" s="15" t="n"/>
       <c r="O310" s="15" t="n"/>
@@ -21643,6 +22055,7 @@
       <c r="S310" s="15" t="n"/>
       <c r="T310" s="15" t="n"/>
       <c r="U310" s="15" t="n"/>
+      <c r="V310" s="15" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
@@ -21679,12 +22092,12 @@
       </c>
       <c r="H311" s="15" t="n"/>
       <c r="I311" s="15" t="n"/>
-      <c r="J311" s="15" t="inlineStr">
+      <c r="J311" s="15" t="n"/>
+      <c r="K311" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K311" s="15" t="n"/>
       <c r="L311" s="15" t="n"/>
       <c r="M311" s="15" t="n"/>
       <c r="N311" s="15" t="n"/>
@@ -21695,6 +22108,7 @@
       <c r="S311" s="15" t="n"/>
       <c r="T311" s="15" t="n"/>
       <c r="U311" s="15" t="n"/>
+      <c r="V311" s="15" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
@@ -21731,30 +22145,31 @@
       </c>
       <c r="H312" s="15" t="n"/>
       <c r="I312" s="15" t="n"/>
-      <c r="J312" s="15" t="inlineStr">
+      <c r="J312" s="15" t="n"/>
+      <c r="K312" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K312" s="15" t="inlineStr">
+      <c r="L312" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Mega Lopunny ex - Double Black Star - Double Rare</t>
         </is>
       </c>
-      <c r="L312" s="15" t="n"/>
       <c r="M312" s="15" t="n"/>
       <c r="N312" s="15" t="n"/>
-      <c r="O312" s="15" t="inlineStr">
+      <c r="O312" s="15" t="n"/>
+      <c r="P312" s="15" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="P312" s="15" t="n"/>
       <c r="Q312" s="15" t="n"/>
       <c r="R312" s="15" t="n"/>
       <c r="S312" s="15" t="n"/>
       <c r="T312" s="15" t="n"/>
       <c r="U312" s="15" t="n"/>
+      <c r="V312" s="15" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
@@ -21791,17 +22206,17 @@
       </c>
       <c r="H313" s="15" t="n"/>
       <c r="I313" s="15" t="n"/>
-      <c r="J313" s="15" t="inlineStr">
+      <c r="J313" s="15" t="n"/>
+      <c r="K313" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K313" s="15" t="inlineStr">
+      <c r="L313" s="15" t="inlineStr">
         <is>
           <t>Surging Sparks - Feebas - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
-      <c r="L313" s="15" t="n"/>
       <c r="M313" s="15" t="n"/>
       <c r="N313" s="15" t="n"/>
       <c r="O313" s="15" t="n"/>
@@ -21810,7 +22225,8 @@
       <c r="R313" s="15" t="n"/>
       <c r="S313" s="15" t="n"/>
       <c r="T313" s="15" t="n"/>
-      <c r="U313" s="15" t="inlineStr">
+      <c r="U313" s="15" t="n"/>
+      <c r="V313" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -21851,26 +22267,27 @@
       </c>
       <c r="H314" s="15" t="n"/>
       <c r="I314" s="15" t="n"/>
-      <c r="J314" s="15" t="inlineStr">
+      <c r="J314" s="15" t="n"/>
+      <c r="K314" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K314" s="15" t="n"/>
       <c r="L314" s="15" t="n"/>
       <c r="M314" s="15" t="n"/>
       <c r="N314" s="15" t="n"/>
-      <c r="O314" s="15" t="inlineStr">
+      <c r="O314" s="15" t="n"/>
+      <c r="P314" s="15" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="P314" s="15" t="n"/>
       <c r="Q314" s="15" t="n"/>
       <c r="R314" s="15" t="n"/>
       <c r="S314" s="15" t="n"/>
       <c r="T314" s="15" t="n"/>
-      <c r="U314" s="15" t="inlineStr">
+      <c r="U314" s="15" t="n"/>
+      <c r="V314" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -21914,20 +22331,20 @@
           <t>Blister Pack</t>
         </is>
       </c>
-      <c r="I315" s="15" t="n">
+      <c r="I315" s="15" t="n"/>
+      <c r="J315" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J315" s="15" t="inlineStr">
+      <c r="K315" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K315" s="15" t="inlineStr">
+      <c r="L315" s="15" t="inlineStr">
         <is>
           <t>Paradox Rift - Tsareena ex - Double Black Star - Double Rare</t>
         </is>
       </c>
-      <c r="L315" s="15" t="n"/>
       <c r="M315" s="15" t="n"/>
       <c r="N315" s="15" t="n"/>
       <c r="O315" s="15" t="n"/>
@@ -21937,6 +22354,7 @@
       <c r="S315" s="15" t="n"/>
       <c r="T315" s="15" t="n"/>
       <c r="U315" s="15" t="n"/>
+      <c r="V315" s="15" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="11" t="inlineStr">
@@ -21973,30 +22391,31 @@
         </is>
       </c>
       <c r="I316" s="15" t="n"/>
-      <c r="J316" s="15" t="inlineStr">
+      <c r="J316" s="15" t="n"/>
+      <c r="K316" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K316" s="15" t="inlineStr">
+      <c r="L316" s="15" t="inlineStr">
         <is>
           <t>Mega Kangakhan ex - Black Star Promo , Mega Evolution - Spearow - Single Gold Star - Illustration Rare,</t>
         </is>
       </c>
-      <c r="L316" s="15" t="n"/>
       <c r="M316" s="15" t="n"/>
       <c r="N316" s="15" t="n"/>
-      <c r="O316" s="15" t="inlineStr">
+      <c r="O316" s="15" t="n"/>
+      <c r="P316" s="15" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="P316" s="15" t="n"/>
       <c r="Q316" s="15" t="n"/>
       <c r="R316" s="15" t="n"/>
       <c r="S316" s="15" t="n"/>
       <c r="T316" s="15" t="n"/>
-      <c r="U316" s="15" t="inlineStr">
+      <c r="U316" s="15" t="n"/>
+      <c r="V316" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -22037,30 +22456,31 @@
         </is>
       </c>
       <c r="I317" s="15" t="n"/>
-      <c r="J317" s="15" t="inlineStr">
+      <c r="J317" s="15" t="n"/>
+      <c r="K317" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K317" s="15" t="inlineStr">
+      <c r="L317" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames - Trainer - Dawn - Double Silver Star - Ultra Rare, Phantasmal Flames - Mega Gengar ex - Double Black Star - Double Rare , Mega Evolution - Mega Gardevoir ex - Double Silver Star - Ultra Rare , Mega Evolution - Mega Venusaur ex - Double Black Star - Double Rare , Mega Evolution - Marshadow - Single Gold Star - Illustration Rare ,  Destined Rivals - Cetitan ex - Double Black Star , Destined Rivals - Rotom - Single Gold Star - Illustration Rare, Journey Together - Noibat - Single Gold Star - Illustration Rare, Journey Together - Trainer - Brock's Scouting - Double Silver Star - Ultra Rare , Journey Together - Blaziken ex - Double Black Star - Double Rare, Surging Sparks - Trainer - Scramble Switch - Single Pink Star -  ACE SPEC Rare , Surging Sparks - Trainer - Cyrano - Double Silver Star - Ultra Rare, Phantasmal Falmes - Charizard X ex - Black Star Promo Card , Phantasmal Flames - Oricorio ex - Black Star Promo Card</t>
         </is>
       </c>
-      <c r="L317" s="15" t="n"/>
       <c r="M317" s="15" t="n"/>
       <c r="N317" s="15" t="n"/>
-      <c r="O317" s="15" t="inlineStr">
+      <c r="O317" s="15" t="n"/>
+      <c r="P317" s="15" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="P317" s="15" t="n"/>
       <c r="Q317" s="15" t="n"/>
       <c r="R317" s="15" t="n"/>
       <c r="S317" s="15" t="n"/>
       <c r="T317" s="15" t="n"/>
-      <c r="U317" s="15" t="inlineStr">
+      <c r="U317" s="15" t="n"/>
+      <c r="V317" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -22101,45 +22521,46 @@
         </is>
       </c>
       <c r="I318" s="15" t="n"/>
-      <c r="J318" s="15" t="inlineStr">
+      <c r="J318" s="15" t="n"/>
+      <c r="K318" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K318" s="15" t="inlineStr">
+      <c r="L318" s="15" t="inlineStr">
         <is>
           <t>Mega Evolution - Stufful - Single Gold star - Illustration Rare , Destined Rivals - Marnie's Grimmsnarl ex , Double Black Star - Double Rare , Journey Together - Wailord - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
-      <c r="L318" s="15" t="n"/>
       <c r="M318" s="15" t="n"/>
       <c r="N318" s="15" t="n"/>
-      <c r="O318" s="15" t="inlineStr">
+      <c r="O318" s="15" t="n"/>
+      <c r="P318" s="15" t="inlineStr">
         <is>
           <t>Hits</t>
         </is>
       </c>
-      <c r="P318" s="15" t="n"/>
       <c r="Q318" s="15" t="n"/>
       <c r="R318" s="15" t="n"/>
       <c r="S318" s="15" t="n"/>
       <c r="T318" s="15" t="n"/>
-      <c r="U318" s="15" t="inlineStr">
+      <c r="U318" s="15" t="n"/>
+      <c r="V318" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U318"/>
-  <conditionalFormatting sqref="H2:J318">
+  <autoFilter ref="A1:V318"/>
+  <conditionalFormatting sqref="H2:K318">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>OR($H2="",$J2="")</formula>
+      <formula>OR($H2="",$K2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K318">
+  <conditionalFormatting sqref="K2:L318">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND($J2="Yes",$K2="")</formula>
+      <formula>AND($K2="Yes",$L2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23013,54 +23434,54 @@
         </is>
       </c>
       <c r="B6" s="18">
+        <f>COUNTA('Video Log'!M2:M318)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Still missing Sets &amp; Packs</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>COUNTA('Video Log'!A2:A318)-COUNTA('Video Log'!M2:M318)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Pack number filled in</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>COUNTA('Video Log'!J2:J318)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Marked as a hit</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>COUNTIF('Video Log'!K2:K318,"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Hit info written</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
         <f>COUNTA('Video Log'!L2:L318)</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Still missing Sets &amp; Packs</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A318)-COUNTA('Video Log'!L2:L318)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Pack number filled in</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I318)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Marked as a hit</t>
-        </is>
-      </c>
-      <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J318,"Yes")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Hit info written</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K318)</f>
-        <v/>
-      </c>
-    </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -23068,7 +23489,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M318,"Yes")</f>
+        <f>COUNTIF('Video Log'!N2:N318,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -23079,7 +23500,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N318)</f>
+        <f>COUNTA('Video Log'!O2:O318)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>26</v>
+        <v>488</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -6622,7 +6622,11 @@
         </is>
       </c>
       <c r="L2" s="15" t="n"/>
-      <c r="M2" s="15" t="n"/>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N2" s="15" t="n"/>
       <c r="O2" s="15" t="n"/>
       <c r="P2" s="15" t="n"/>
@@ -6650,7 +6654,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -6671,7 +6675,9 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="I3" s="15" t="n"/>
+      <c r="I3" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="J3" s="15" t="n">
         <v>3</v>
       </c>
@@ -6685,7 +6691,11 @@
           <t>Mega Greninja ex - Hyper Rare - Gold Card</t>
         </is>
       </c>
-      <c r="M3" s="15" t="n"/>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N3" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6719,7 +6729,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
@@ -6750,7 +6760,11 @@
         </is>
       </c>
       <c r="L4" s="15" t="n"/>
-      <c r="M4" s="15" t="n"/>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N4" s="15" t="n"/>
       <c r="O4" s="15" t="n"/>
       <c r="P4" s="15" t="n"/>
@@ -6778,7 +6792,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -6799,7 +6813,9 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="I5" s="15" t="n"/>
+      <c r="I5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" s="15" t="n">
         <v>8</v>
       </c>
@@ -6809,7 +6825,11 @@
         </is>
       </c>
       <c r="L5" s="15" t="n"/>
-      <c r="M5" s="15" t="n"/>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N5" s="15" t="n"/>
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
@@ -6868,7 +6888,11 @@
         </is>
       </c>
       <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
@@ -6917,7 +6941,9 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="I7" s="15" t="n"/>
+      <c r="I7" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="J7" s="15" t="n">
         <v>2</v>
       </c>
@@ -6927,7 +6953,11 @@
         </is>
       </c>
       <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N7" s="15" t="n"/>
       <c r="O7" s="15" t="n"/>
       <c r="P7" s="15" t="n"/>
@@ -6955,7 +6985,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -6990,7 +7020,11 @@
           <t>Cinccino ex - Double Black Star - Double Rare</t>
         </is>
       </c>
-      <c r="M8" s="15" t="n"/>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="15" t="n"/>
@@ -7039,7 +7073,9 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
+      <c r="I9" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="J9" s="15" t="n">
         <v>7</v>
       </c>
@@ -7049,7 +7085,11 @@
         </is>
       </c>
       <c r="L9" s="15" t="n"/>
-      <c r="M9" s="15" t="n"/>
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N9" s="15" t="n"/>
       <c r="O9" s="15" t="n"/>
       <c r="P9" s="15" t="n"/>
@@ -7108,7 +7148,11 @@
         </is>
       </c>
       <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="n"/>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
@@ -7157,7 +7201,9 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="I11" s="15" t="n"/>
+      <c r="I11" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="J11" s="15" t="n">
         <v>1</v>
       </c>
@@ -7167,7 +7213,11 @@
         </is>
       </c>
       <c r="L11" s="15" t="n"/>
-      <c r="M11" s="15" t="n"/>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="15" t="n"/>
       <c r="P11" s="15" t="n"/>
@@ -7211,12 +7261,32 @@
           <t>desc: pack 6  Pitch Black</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="15" t="n"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>Rampardos ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
@@ -7260,16 +7330,28 @@
           <t>desc: pack 6  Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" s="15" t="n"/>
-      <c r="M13" s="15" t="n"/>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="15" t="n"/>
       <c r="P13" s="15" t="n"/>
@@ -7313,16 +7395,26 @@
           <t>desc: pack 6  Pitch Black</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n"/>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
+      <c r="J14" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="15" t="n"/>
@@ -7366,12 +7458,28 @@
           <t>desc: pack 8  ex Premium Collection  Perfect Order</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L15" s="15" t="n"/>
-      <c r="M15" s="15" t="n"/>
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t>Perfect Order</t>
+        </is>
+      </c>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="15" t="n"/>
       <c r="P15" s="15" t="n"/>
@@ -7415,16 +7523,28 @@
           <t>desc: pack 5  Pitch Black</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="15" t="n"/>
@@ -7468,16 +7588,28 @@
           <t>desc: pack 5  Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
       <c r="P17" s="15" t="n"/>
@@ -7521,16 +7653,30 @@
           <t>desc: pack 5  Pitch Black</t>
         </is>
       </c>
-      <c r="H18" s="15" t="n"/>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
+      <c r="J18" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>Bastiodon - Single Gold Star - Illustration Rare</t>
+        </is>
+      </c>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
@@ -7574,16 +7720,32 @@
           <t>desc: pack 7  ex Premium Collection  Perfect Order</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>Mega Skarmory ex - Double Silver Star - Ultra Rare</t>
+        </is>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>Perfect Order</t>
+        </is>
+      </c>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
       <c r="P19" s="15" t="n"/>
@@ -7627,16 +7789,32 @@
           <t>desc: pack 4  Pitch Black</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>Toucannon - Single Gold Star - Illustration Rare</t>
+        </is>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
@@ -7680,12 +7858,28 @@
           <t>desc: pack 4  Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="15" t="n"/>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L21" s="15" t="n"/>
-      <c r="M21" s="15" t="n"/>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
       <c r="P21" s="15" t="n"/>
@@ -7729,16 +7923,26 @@
           <t>desc: pack 4  Pitch Black</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n"/>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
+      <c r="J22" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
@@ -7782,16 +7986,32 @@
           <t>ex Premium Collection  Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L23" s="15" t="n"/>
-      <c r="M23" s="15" t="n"/>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <t>Trainer - Dawn - Double Silver Star - Ultra Rare</t>
+        </is>
+      </c>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
       <c r="P23" s="15" t="n"/>
@@ -7835,16 +8055,32 @@
           <t>desc: pack 6  ex Premium Collection</t>
         </is>
       </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>Mega Floette ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
@@ -7888,12 +8124,26 @@
           <t>Tin  Chaos Rising</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n"/>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Mini Tin</t>
+        </is>
+      </c>
       <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="15" t="n"/>
+      <c r="J25" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L25" s="15" t="n"/>
-      <c r="M25" s="15" t="n"/>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N25" s="15" t="n"/>
       <c r="O25" s="15" t="n"/>
       <c r="P25" s="15" t="n"/>
@@ -7937,16 +8187,32 @@
           <t>desc: pack 3  Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="K26" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>Rampardos ex - Double Silver Star - Ultra Rare</t>
+        </is>
+      </c>
+      <c r="M26" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
@@ -7990,12 +8256,28 @@
           <t>desc: pack 3  Pitch Black</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="n"/>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L27" s="15" t="n"/>
-      <c r="M27" s="15" t="n"/>
+      <c r="M27" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N27" s="15" t="n"/>
       <c r="O27" s="15" t="n"/>
       <c r="P27" s="15" t="n"/>
@@ -8039,16 +8321,26 @@
           <t>title: pack 3  Pitch Black</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n"/>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
+      <c r="J28" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="K28" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="15" t="n"/>
@@ -8092,16 +8384,32 @@
           <t>desc: pack 7  ex Premium Collection  Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>Trainer - Dawn - Double Gold Star - Special Illustration Rare</t>
+        </is>
+      </c>
+      <c r="M29" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="N29" s="15" t="n"/>
       <c r="O29" s="15" t="n"/>
       <c r="P29" s="15" t="n"/>
@@ -8145,12 +8453,30 @@
           <t>Tin  Perfect Order</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n"/>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Mini Tin</t>
+        </is>
+      </c>
       <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
+      <c r="J30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" s="15" t="inlineStr">
+        <is>
+          <t>Mega Starmie ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M30" s="15" t="inlineStr">
+        <is>
+          <t>Perfect Order</t>
+        </is>
+      </c>
       <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="15" t="n"/>
@@ -8194,12 +8520,28 @@
           <t>desc: pack 5  ex Premium Collection</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
-      <c r="K31" s="15" t="n"/>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L31" s="15" t="n"/>
-      <c r="M31" s="15" t="n"/>
+      <c r="M31" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N31" s="15" t="n"/>
       <c r="O31" s="15" t="n"/>
       <c r="P31" s="15" t="n"/>
@@ -8243,16 +8585,26 @@
           <t>title: pack 2  Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n"/>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Sleeved Booster Pack</t>
+        </is>
+      </c>
       <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
+      <c r="J32" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
+      <c r="M32" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N32" s="15" t="n"/>
       <c r="O32" s="15" t="n"/>
       <c r="P32" s="15" t="n"/>
@@ -8296,12 +8648,28 @@
           <t>desc: pack 2  Pitch Black</t>
         </is>
       </c>
-      <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
-      <c r="K33" s="15" t="n"/>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L33" s="15" t="n"/>
-      <c r="M33" s="15" t="n"/>
+      <c r="M33" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N33" s="15" t="n"/>
       <c r="O33" s="15" t="n"/>
       <c r="P33" s="15" t="n"/>
@@ -8345,12 +8713,28 @@
           <t>Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
-      <c r="K34" s="15" t="n"/>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
+      <c r="M34" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N34" s="15" t="n"/>
       <c r="O34" s="15" t="n"/>
       <c r="P34" s="15" t="n"/>
@@ -8394,16 +8778,28 @@
           <t>desc: pack 6  ex Premium Collection  Phantasmal Flames</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L35" s="15" t="n"/>
-      <c r="M35" s="15" t="n"/>
+      <c r="M35" s="15" t="inlineStr">
+        <is>
+          <t>Perfect Order</t>
+        </is>
+      </c>
       <c r="N35" s="15" t="n"/>
       <c r="O35" s="15" t="n"/>
       <c r="P35" s="15" t="n"/>
@@ -8447,12 +8843,26 @@
           <t>Tin  Twilight Masquerade</t>
         </is>
       </c>
-      <c r="H36" s="15" t="n"/>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Poke Ball Tin</t>
+        </is>
+      </c>
       <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
-      <c r="K36" s="15" t="n"/>
+      <c r="J36" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
+      <c r="M36" s="15" t="inlineStr">
+        <is>
+          <t>Twilight Masquerade</t>
+        </is>
+      </c>
       <c r="N36" s="15" t="n"/>
       <c r="O36" s="15" t="n"/>
       <c r="P36" s="15" t="n"/>
@@ -8496,12 +8906,28 @@
           <t>desc: pack 4  ex Premium Collection  Chaos Rising</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
-      <c r="K37" s="15" t="n"/>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="L37" s="15" t="n"/>
-      <c r="M37" s="15" t="n"/>
+      <c r="M37" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="N37" s="15" t="n"/>
       <c r="O37" s="15" t="n"/>
       <c r="P37" s="15" t="n"/>
@@ -8545,16 +8971,32 @@
           <t>desc: pack 1  Pitch Black</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
+          <t>Mega Chandelure ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="15" t="n"/>
@@ -8598,12 +9040,32 @@
           <t>Booster Bundle  Pitch Black</t>
         </is>
       </c>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
-      <c r="M39" s="15" t="n"/>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Booster Bundle</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
+          <t>Mega Excadrill ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M39" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="N39" s="15" t="n"/>
       <c r="O39" s="15" t="n"/>
       <c r="P39" s="15" t="n"/>
@@ -8647,16 +9109,32 @@
           <t>title: #2 pack 5  ex Premium Collection</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>ex Premium Collection Box</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>Salazzle ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>Perfect Order</t>
+        </is>
+      </c>
       <c r="N40" s="15" t="n"/>
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="15" t="n"/>
@@ -18608,7 +19086,7 @@
         </is>
       </c>
       <c r="D241" s="12" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E241" s="11" t="inlineStr">
         <is>
@@ -22310,7 +22788,7 @@
         </is>
       </c>
       <c r="D315" s="12" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E315" s="11" t="inlineStr">
         <is>
@@ -22373,7 +22851,7 @@
         </is>
       </c>
       <c r="D316" s="12" t="n">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E316" s="11" t="inlineStr">
         <is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -664,7 +664,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -677,7 +676,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -762,7 +760,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -842,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -898,7 +894,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -911,7 +906,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -924,7 +918,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -937,7 +930,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -950,7 +942,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -963,7 +954,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -976,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -989,7 +978,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -11352,7 +11340,7 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio  - Phantasmal Flames - Trainer - Punk Helmet - Double Silver Star - Ultra Rare</t>
+          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio ; Phantasmal Flames - Trainer - Punk Helmet - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -664,6 +664,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -676,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -760,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -839,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -894,6 +898,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -906,6 +911,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -918,6 +924,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -930,6 +937,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -942,6 +950,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -954,6 +963,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -966,6 +976,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -978,6 +989,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -6614,7 +6626,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>480</v>
+        <v>611</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -6664,7 +6676,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
@@ -6728,7 +6740,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
@@ -8268,7 +8280,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
@@ -11034,7 +11046,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
@@ -11102,7 +11114,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
@@ -11170,7 +11182,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
@@ -11240,7 +11252,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
@@ -11306,7 +11318,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
@@ -11376,7 +11388,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
@@ -11442,7 +11454,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
@@ -11506,7 +11518,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
@@ -11570,7 +11582,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
@@ -11634,7 +11646,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
@@ -11698,7 +11710,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
@@ -11766,7 +11778,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
@@ -11834,7 +11846,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
@@ -11902,7 +11914,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
@@ -11966,7 +11978,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
@@ -12030,7 +12042,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
@@ -12096,7 +12108,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
@@ -12162,7 +12174,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
@@ -12232,7 +12244,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
@@ -12298,7 +12310,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
@@ -12364,7 +12376,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
@@ -12434,7 +12446,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
@@ -12500,7 +12512,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
@@ -12570,7 +12582,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
@@ -12636,7 +12648,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
@@ -12702,7 +12714,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
@@ -12772,7 +12784,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
@@ -12842,7 +12854,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
@@ -12908,7 +12920,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
@@ -12974,7 +12986,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
@@ -13044,7 +13056,7 @@
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
@@ -13114,7 +13126,7 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
@@ -13180,7 +13192,7 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
@@ -13246,7 +13258,7 @@
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
@@ -13312,7 +13324,7 @@
         </is>
       </c>
       <c r="D102" s="12" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
@@ -13378,7 +13390,7 @@
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
@@ -13448,7 +13460,7 @@
         </is>
       </c>
       <c r="D104" s="12" t="n">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
@@ -13512,7 +13524,7 @@
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
@@ -35873,20 +35885,12 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Popplio Trainer Punk Helmet</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
+          <t>Popplio</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr"/>
       <c r="D64" s="15" t="n"/>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>Ultra Rare</t>
-        </is>
-      </c>
+      <c r="E64" s="15" t="n"/>
       <c r="F64" s="22" t="n"/>
       <c r="G64" s="22" t="n"/>
       <c r="H64" s="15" t="n"/>
@@ -35895,23 +35899,23 @@
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>EifpW6bQhPE</t>
+          <t>xNGxOuMpSiw</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Mega Dragalge ex</t>
+          <t>Punk Helmet</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Chaos Rising</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D65" s="15" t="n"/>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F65" s="22" t="n"/>
@@ -35922,23 +35926,23 @@
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>6bMl7VF_ov0</t>
+          <t>EifpW6bQhPE</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Dedenne</t>
+          <t>Mega Dragalge ex</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Perfect Order</t>
+          <t>Chaos Rising</t>
         </is>
       </c>
       <c r="D66" s="15" t="n"/>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F66" s="22" t="n"/>
@@ -35949,17 +35953,17 @@
     <row r="67">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>HHjdWa5tfXY</t>
+          <t>6bMl7VF_ov0</t>
         </is>
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Xerneas</t>
+          <t>Dedenne</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Chaos Rising</t>
+          <t>Perfect Order</t>
         </is>
       </c>
       <c r="D67" s="15" t="n"/>
@@ -35976,23 +35980,23 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>w3dQBhumsug</t>
+          <t>HHjdWa5tfXY</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Larry's Dudunsparce ex</t>
+          <t>Xerneas</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Ascended Heroes</t>
+          <t>Chaos Rising</t>
         </is>
       </c>
       <c r="D68" s="15" t="n"/>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F68" s="22" t="n"/>
@@ -36003,17 +36007,17 @@
     <row r="69">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>Mhz1-_ppwJA</t>
+          <t>w3dQBhumsug</t>
         </is>
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Krookodile ex</t>
+          <t>Larry's Dudunsparce ex</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Chaos Rising</t>
+          <t>Ascended Heroes</t>
         </is>
       </c>
       <c r="D69" s="15" t="n"/>
@@ -36030,17 +36034,17 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>n4iGQVPBtfE</t>
+          <t>Mhz1-_ppwJA</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Larry's Dudunsparce ex</t>
+          <t>Krookodile ex</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Ascended Heroes</t>
+          <t>Chaos Rising</t>
         </is>
       </c>
       <c r="D70" s="15" t="n"/>
@@ -36057,12 +36061,12 @@
     <row r="71">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>qKiLbaLhdp8</t>
+          <t>n4iGQVPBtfE</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Slurpuff</t>
+          <t>Larry's Dudunsparce ex</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
@@ -36073,7 +36077,7 @@
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F71" s="22" t="n"/>
@@ -36084,23 +36088,23 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>QKYrh9l8BYA</t>
+          <t>qKiLbaLhdp8</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Mega Greninja ex</t>
+          <t>Slurpuff</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Chaos Rising</t>
+          <t>Ascended Heroes</t>
         </is>
       </c>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F72" s="22" t="n"/>
@@ -36111,17 +36115,17 @@
     <row r="73">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>hOBpKIl2lX4</t>
+          <t>QKYrh9l8BYA</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Mega Hawlucha ex</t>
+          <t>Mega Greninja ex</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Ascended Heroes</t>
+          <t>Chaos Rising</t>
         </is>
       </c>
       <c r="D73" s="15" t="n"/>
@@ -36138,17 +36142,17 @@
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>4gBo585VhEI</t>
+          <t>hOBpKIl2lX4</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Cobalion ex</t>
+          <t>Mega Hawlucha ex</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Chaos Rising</t>
+          <t>Ascended Heroes</t>
         </is>
       </c>
       <c r="D74" s="15" t="n"/>
@@ -36165,12 +36169,12 @@
     <row r="75">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>bpm7cSVXNiM</t>
+          <t>4gBo585VhEI</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Chespin</t>
+          <t>Cobalion ex</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -36181,7 +36185,7 @@
       <c r="D75" s="15" t="n"/>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F75" s="22" t="n"/>
@@ -36190,11 +36194,27 @@
       <c r="I75" s="15" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="15" t="n"/>
-      <c r="B76" s="15" t="n"/>
-      <c r="C76" s="15" t="n"/>
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>bpm7cSVXNiM</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Chespin</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="D76" s="15" t="n"/>
-      <c r="E76" s="15" t="n"/>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F76" s="22" t="n"/>
       <c r="G76" s="22" t="n"/>
       <c r="H76" s="15" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -31,7 +31,7 @@
     <definedName name="gr_list_K">Lists!$K$2:$K$21</definedName>
     <definedName name="gr_list_L">Lists!$L$2:$L$31</definedName>
     <definedName name="gr_list_M">Lists!$M$2:$M$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$W$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Video Log'!$A$1:$U$319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -290,7 +290,7 @@
 one exactly. Anything not recognised is reported back, never guessed.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>WHICH PACK OUT OF THAT BOX this video opens. Pack 3 of the 9 in an
 ETB is 3.
@@ -302,7 +302,7 @@
 you did not keep count.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>THIS IS THE COLUMN THAT DRIVES THE SITE. Nothing else claims a hit.
 FREE TEXT. There is no dropdown on this column and there should not be
@@ -324,7 +324,7 @@
 claim a pull where you have said what the card was.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>LEAVE THIS BLANK unless the video opened packs from MORE THAN ONE SET.
 Nearly every video is one pack from one set, and for those the Product
@@ -334,23 +334,7 @@
 We can rework this column once the single-set rows are done.</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>HOW MANY PACKS OF THAT SET THIS VIDEO OPENED. Blank means one, so
-nearly every row stays empty and you only touch this when a video
-opened more than one pack of the same set.
-   (blank)   one pack, the normal case
-   2         two packs of the one set named next door
-   6, 4, 4   Sets &amp; Packs names three sets, in that same order
-ONE NUMBER PER SET, IN THE SAME ORDER AS Sets &amp; Packs. If the counts
-and the sets do not line up the import says so and changes nothing,
-rather than guessing which set the number belonged to.
-This is NOT how many packs the box holds, and it is not Pack #.
-Pack # is WHICH pack. This is HOW MANY. A video opening pack 3 of an
-ETB is Pack # 3 and blank here, because it opened one pack.</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>The Hall of Fame band on the home page.
 Separate from the Hits playlist: this is the shortlist, that is a
@@ -920,7 +904,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A tin with two packs, or a box with ten packs from four sets, belongs to every set it contains. Name them all in Sets &amp; Packs, commas between them, the set the video is really about first. Then say how many packs of each in Packs of Each Set, one number per set in the same order: Sets &amp; Packs 'Journey Together, Pitch Black' with Packs of Each Set '6, 6' is a UPC reading 12 packs that still knows six of them were Journey Together. That is what makes a per-set pack count possible.</t>
+          <t>A tin with two packs, or a box with ten packs from four sets, belongs to every set it contains. Name them all in Sets &amp; Packs, commas between them, the set the video is really about first, and put the count next to the set it counts: 'First Partner Illustration Collection (Series 1) - 1 Pack, Phantasmal Flames - 1 Pack, Mega Evolution - 1 Pack'. The count belongs beside the name because that is the only place it cannot come adrift when you insert a set into the middle of the list later.</t>
         </is>
       </c>
     </row>
@@ -933,7 +917,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Packs of Each Set is HOW MANY, Pack # is WHICH ONE, and they answer different questions. A video opening pack 3 of a nine-pack ETB is Pack # 3 with Packs of Each Set left blank, because it opened one pack. Blank means one, so nearly every row stays empty: you only type here when a video opened more than one pack, like the Abyss Eye video that ripped packs 9 and 10 back to back. That one is a 2. Neither column is ever how many packs the box holds.</t>
+          <t>The count in Sets &amp; Packs is HOW MANY, Pack # is WHICH ONE, and they answer different questions. A video opening pack 3 of a nine-pack ETB is Pack # 3, and its Sets &amp; Packs cell just names the set, because it opened one pack. Leaving the count off means one, so most rows never need it: you only write '- 2 Pack' when a video opened two of the same set, like the Abyss Eye video that ripped packs 9 and 10 back to back. Neither number is ever how many packs the box holds.</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W319"/>
+  <dimension ref="A1:U319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6475,21 +6459,19 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="54" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6535,75 +6517,65 @@
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>Product #</t>
+          <t>Pack #</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>Pack #</t>
+          <t>Hit</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Hit Info</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Hit Info</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
-        <is>
           <t>Sets &amp; Packs</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
-        <is>
-          <t>Packs of Each Set</t>
-        </is>
-      </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Greatest Hits</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Greatest Hits Rank</t>
         </is>
       </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Playlist To Add</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>Affiliate Link</t>
+        </is>
+      </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>Playlist To Add</t>
+          <t>Site Title</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>Affiliate Link</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
         <is>
-          <t>Site Title</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="T1" s="9" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Hide</t>
         </is>
       </c>
       <c r="U1" s="9" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="V1" s="9" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6656,8 +6628,6 @@
       <c r="S2" s="15" t="n"/>
       <c r="T2" s="15" t="n"/>
       <c r="U2" s="15" t="n"/>
-      <c r="V2" s="15" t="n"/>
-      <c r="W2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -6697,21 +6667,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="15" t="n">
+      <c r="I3" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" s="15" t="n"/>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M3" s="15" t="n"/>
       <c r="N3" s="15" t="n"/>
       <c r="O3" s="15" t="n"/>
       <c r="P3" s="15" t="n"/>
@@ -6720,8 +6690,6 @@
       <c r="S3" s="15" t="n"/>
       <c r="T3" s="15" t="n"/>
       <c r="U3" s="15" t="n"/>
-      <c r="V3" s="15" t="n"/>
-      <c r="W3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -6764,40 +6732,36 @@
       <c r="I4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>3</v>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
+          <t>Mega Greninja ex - Hyper Rare - Gold Card</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr">
-        <is>
-          <t>Mega Greninja ex - Hyper Rare - Gold Card</t>
-        </is>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>Chaos Rising</t>
-        </is>
-      </c>
-      <c r="N4" s="15" t="n"/>
-      <c r="O4" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P4" s="15" t="n">
+      <c r="N4" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="O4" s="15" t="n"/>
+      <c r="P4" s="15" t="n"/>
       <c r="Q4" s="15" t="n"/>
       <c r="R4" s="15" t="n"/>
       <c r="S4" s="15" t="n"/>
       <c r="T4" s="15" t="n"/>
       <c r="U4" s="15" t="n"/>
-      <c r="V4" s="15" t="n"/>
-      <c r="W4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -6837,21 +6801,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n">
+      <c r="I5" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" s="15" t="n"/>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M5" s="15" t="n"/>
       <c r="N5" s="15" t="n"/>
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
@@ -6860,8 +6824,6 @@
       <c r="S5" s="15" t="n"/>
       <c r="T5" s="15" t="n"/>
       <c r="U5" s="15" t="n"/>
-      <c r="V5" s="15" t="n"/>
-      <c r="W5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -6902,22 +6864,20 @@
         </is>
       </c>
       <c r="I6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M6" s="15" t="n"/>
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
@@ -6926,8 +6886,6 @@
       <c r="S6" s="15" t="n"/>
       <c r="T6" s="15" t="n"/>
       <c r="U6" s="15" t="n"/>
-      <c r="V6" s="15" t="n"/>
-      <c r="W6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -6967,21 +6925,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n">
+      <c r="I7" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M7" s="15" t="n"/>
       <c r="N7" s="15" t="n"/>
       <c r="O7" s="15" t="n"/>
       <c r="P7" s="15" t="n"/>
@@ -6990,8 +6948,6 @@
       <c r="S7" s="15" t="n"/>
       <c r="T7" s="15" t="n"/>
       <c r="U7" s="15" t="n"/>
-      <c r="V7" s="15" t="n"/>
-      <c r="W7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7032,22 +6988,20 @@
         </is>
       </c>
       <c r="I8" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="15" t="n"/>
@@ -7056,8 +7010,6 @@
       <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n"/>
       <c r="U8" s="15" t="n"/>
-      <c r="V8" s="15" t="n"/>
-      <c r="W8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -7097,25 +7049,25 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n">
+      <c r="I9" s="15" t="n">
         <v>12</v>
       </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cinccino ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>Cinccino ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M9" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M9" s="15" t="n"/>
       <c r="N9" s="15" t="n"/>
       <c r="O9" s="15" t="n"/>
       <c r="P9" s="15" t="n"/>
@@ -7124,8 +7076,6 @@
       <c r="S9" s="15" t="n"/>
       <c r="T9" s="15" t="n"/>
       <c r="U9" s="15" t="n"/>
-      <c r="V9" s="15" t="n"/>
-      <c r="W9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -7166,22 +7116,20 @@
         </is>
       </c>
       <c r="I10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
@@ -7190,8 +7138,6 @@
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n"/>
       <c r="U10" s="15" t="n"/>
-      <c r="V10" s="15" t="n"/>
-      <c r="W10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -7231,21 +7177,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n">
+      <c r="I11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" s="15" t="n"/>
-      <c r="M11" s="15" t="inlineStr">
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M11" s="15" t="n"/>
       <c r="N11" s="15" t="n"/>
       <c r="O11" s="15" t="n"/>
       <c r="P11" s="15" t="n"/>
@@ -7254,8 +7200,6 @@
       <c r="S11" s="15" t="n"/>
       <c r="T11" s="15" t="n"/>
       <c r="U11" s="15" t="n"/>
-      <c r="V11" s="15" t="n"/>
-      <c r="W11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -7296,22 +7240,20 @@
         </is>
       </c>
       <c r="I12" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
@@ -7320,8 +7262,6 @@
       <c r="S12" s="15" t="n"/>
       <c r="T12" s="15" t="n"/>
       <c r="U12" s="15" t="n"/>
-      <c r="V12" s="15" t="n"/>
-      <c r="W12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -7362,26 +7302,24 @@
         </is>
       </c>
       <c r="I13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="15" t="n">
         <v>6</v>
       </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rampardos ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
         <is>
-          <t>Rampardos ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M13" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M13" s="15" t="n"/>
       <c r="N13" s="15" t="n"/>
       <c r="O13" s="15" t="n"/>
       <c r="P13" s="15" t="n"/>
@@ -7390,8 +7328,6 @@
       <c r="S13" s="15" t="n"/>
       <c r="T13" s="15" t="n"/>
       <c r="U13" s="15" t="n"/>
-      <c r="V13" s="15" t="n"/>
-      <c r="W13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -7432,22 +7368,20 @@
         </is>
       </c>
       <c r="I14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="15" t="n"/>
@@ -7456,8 +7390,6 @@
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
       <c r="U14" s="15" t="n"/>
-      <c r="V14" s="15" t="n"/>
-      <c r="W14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -7497,21 +7429,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n">
+      <c r="I15" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" s="15" t="n"/>
-      <c r="M15" s="15" t="inlineStr">
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M15" s="15" t="n"/>
       <c r="N15" s="15" t="n"/>
       <c r="O15" s="15" t="n"/>
       <c r="P15" s="15" t="n"/>
@@ -7520,8 +7452,6 @@
       <c r="S15" s="15" t="n"/>
       <c r="T15" s="15" t="n"/>
       <c r="U15" s="15" t="n"/>
-      <c r="V15" s="15" t="n"/>
-      <c r="W15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -7562,22 +7492,20 @@
         </is>
       </c>
       <c r="I16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="inlineStr">
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="15" t="n"/>
@@ -7586,8 +7514,6 @@
       <c r="S16" s="15" t="n"/>
       <c r="T16" s="15" t="n"/>
       <c r="U16" s="15" t="n"/>
-      <c r="V16" s="15" t="n"/>
-      <c r="W16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -7628,22 +7554,20 @@
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="inlineStr">
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
       <c r="P17" s="15" t="n"/>
@@ -7652,8 +7576,6 @@
       <c r="S17" s="15" t="n"/>
       <c r="T17" s="15" t="n"/>
       <c r="U17" s="15" t="n"/>
-      <c r="V17" s="15" t="n"/>
-      <c r="W17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -7694,22 +7616,20 @@
         </is>
       </c>
       <c r="I18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="inlineStr">
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
@@ -7718,8 +7638,6 @@
       <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n"/>
       <c r="U18" s="15" t="n"/>
-      <c r="V18" s="15" t="n"/>
-      <c r="W18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -7759,25 +7677,25 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n">
+      <c r="I19" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bastiodon - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>Bastiodon - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
       <c r="P19" s="15" t="n"/>
@@ -7786,8 +7704,6 @@
       <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="15" t="n"/>
-      <c r="V19" s="15" t="n"/>
-      <c r="W19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -7828,26 +7744,24 @@
         </is>
       </c>
       <c r="I20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="15" t="n">
         <v>7</v>
       </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Skarmory ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>Mega Skarmory ex - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
@@ -7856,8 +7770,6 @@
       <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
-      <c r="V20" s="15" t="n"/>
-      <c r="W20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -7898,26 +7810,24 @@
         </is>
       </c>
       <c r="I21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Toucannon - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>Toucannon - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M21" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
       <c r="P21" s="15" t="n"/>
@@ -7926,8 +7836,6 @@
       <c r="S21" s="15" t="n"/>
       <c r="T21" s="15" t="n"/>
       <c r="U21" s="15" t="n"/>
-      <c r="V21" s="15" t="n"/>
-      <c r="W21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -7968,22 +7876,20 @@
         </is>
       </c>
       <c r="I22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="inlineStr">
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
@@ -7992,8 +7898,6 @@
       <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="15" t="n"/>
-      <c r="V22" s="15" t="n"/>
-      <c r="W22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -8033,21 +7937,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n">
+      <c r="I23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" s="15" t="n"/>
-      <c r="M23" s="15" t="inlineStr">
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
       <c r="P23" s="15" t="n"/>
@@ -8056,8 +7960,6 @@
       <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n"/>
       <c r="U23" s="15" t="n"/>
-      <c r="V23" s="15" t="n"/>
-      <c r="W23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -8098,26 +8000,24 @@
         </is>
       </c>
       <c r="I24" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Dawn - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Dawn - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M24" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
+      <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
@@ -8126,8 +8026,6 @@
       <c r="S24" s="15" t="n"/>
       <c r="T24" s="15" t="n"/>
       <c r="U24" s="15" t="n"/>
-      <c r="V24" s="15" t="n"/>
-      <c r="W24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -8168,26 +8066,24 @@
         </is>
       </c>
       <c r="I25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="15" t="n">
         <v>6</v>
       </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Floette ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L25" s="15" t="inlineStr">
         <is>
-          <t>Mega Floette ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M25" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M25" s="15" t="n"/>
       <c r="N25" s="15" t="n"/>
       <c r="O25" s="15" t="n"/>
       <c r="P25" s="15" t="n"/>
@@ -8196,8 +8092,6 @@
       <c r="S25" s="15" t="n"/>
       <c r="T25" s="15" t="n"/>
       <c r="U25" s="15" t="n"/>
-      <c r="V25" s="15" t="n"/>
-      <c r="W25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -8237,21 +8131,21 @@
           <t>Mini Tin</t>
         </is>
       </c>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n">
+      <c r="I26" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="J26" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="inlineStr">
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
@@ -8260,8 +8154,6 @@
       <c r="S26" s="15" t="n"/>
       <c r="T26" s="15" t="n"/>
       <c r="U26" s="15" t="n"/>
-      <c r="V26" s="15" t="n"/>
-      <c r="W26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -8302,26 +8194,24 @@
         </is>
       </c>
       <c r="I27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rampardos ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
-          <t>Rampardos ex - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M27" s="15" t="n"/>
       <c r="N27" s="15" t="n"/>
       <c r="O27" s="15" t="n"/>
       <c r="P27" s="15" t="n"/>
@@ -8330,8 +8220,6 @@
       <c r="S27" s="15" t="n"/>
       <c r="T27" s="15" t="n"/>
       <c r="U27" s="15" t="n"/>
-      <c r="V27" s="15" t="n"/>
-      <c r="W27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -8372,22 +8260,20 @@
         </is>
       </c>
       <c r="I28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="inlineStr">
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M28" s="15" t="n"/>
       <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="15" t="n"/>
@@ -8396,8 +8282,6 @@
       <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n"/>
       <c r="U28" s="15" t="n"/>
-      <c r="V28" s="15" t="n"/>
-      <c r="W28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -8437,21 +8321,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n">
+      <c r="I29" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="J29" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="inlineStr">
+      <c r="K29" s="15" t="n"/>
+      <c r="L29" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M29" s="15" t="n"/>
       <c r="N29" s="15" t="n"/>
       <c r="O29" s="15" t="n"/>
       <c r="P29" s="15" t="n"/>
@@ -8460,8 +8344,6 @@
       <c r="S29" s="15" t="n"/>
       <c r="T29" s="15" t="n"/>
       <c r="U29" s="15" t="n"/>
-      <c r="V29" s="15" t="n"/>
-      <c r="W29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -8502,26 +8384,24 @@
         </is>
       </c>
       <c r="I30" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="15" t="n">
         <v>7</v>
       </c>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Dawn - Double Gold Star - Special Illustration Rare</t>
         </is>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Dawn - Double Gold Star - Special Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M30" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
+      <c r="M30" s="15" t="n"/>
       <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="15" t="n"/>
@@ -8530,8 +8410,6 @@
       <c r="S30" s="15" t="n"/>
       <c r="T30" s="15" t="n"/>
       <c r="U30" s="15" t="n"/>
-      <c r="V30" s="15" t="n"/>
-      <c r="W30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -8571,25 +8449,25 @@
           <t>Mini Tin</t>
         </is>
       </c>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n">
+      <c r="I31" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Starmie ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
-          <t>Mega Starmie ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M31" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M31" s="15" t="n"/>
       <c r="N31" s="15" t="n"/>
       <c r="O31" s="15" t="n"/>
       <c r="P31" s="15" t="n"/>
@@ -8598,8 +8476,6 @@
       <c r="S31" s="15" t="n"/>
       <c r="T31" s="15" t="n"/>
       <c r="U31" s="15" t="n"/>
-      <c r="V31" s="15" t="n"/>
-      <c r="W31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -8640,22 +8516,20 @@
         </is>
       </c>
       <c r="I32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="inlineStr">
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M32" s="15" t="n"/>
       <c r="N32" s="15" t="n"/>
       <c r="O32" s="15" t="n"/>
       <c r="P32" s="15" t="n"/>
@@ -8664,8 +8538,6 @@
       <c r="S32" s="15" t="n"/>
       <c r="T32" s="15" t="n"/>
       <c r="U32" s="15" t="n"/>
-      <c r="V32" s="15" t="n"/>
-      <c r="W32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -8705,21 +8577,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n">
+      <c r="I33" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="J33" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L33" s="15" t="n"/>
-      <c r="M33" s="15" t="inlineStr">
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M33" s="15" t="n"/>
       <c r="N33" s="15" t="n"/>
       <c r="O33" s="15" t="n"/>
       <c r="P33" s="15" t="n"/>
@@ -8728,8 +8600,6 @@
       <c r="S33" s="15" t="n"/>
       <c r="T33" s="15" t="n"/>
       <c r="U33" s="15" t="n"/>
-      <c r="V33" s="15" t="n"/>
-      <c r="W33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -8770,22 +8640,20 @@
         </is>
       </c>
       <c r="I34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M34" s="15" t="n"/>
       <c r="N34" s="15" t="n"/>
       <c r="O34" s="15" t="n"/>
       <c r="P34" s="15" t="n"/>
@@ -8794,8 +8662,6 @@
       <c r="S34" s="15" t="n"/>
       <c r="T34" s="15" t="n"/>
       <c r="U34" s="15" t="n"/>
-      <c r="V34" s="15" t="n"/>
-      <c r="W34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -8836,22 +8702,20 @@
         </is>
       </c>
       <c r="I35" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="J35" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L35" s="15" t="n"/>
-      <c r="M35" s="15" t="inlineStr">
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="inlineStr">
         <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M35" s="15" t="n"/>
       <c r="N35" s="15" t="n"/>
       <c r="O35" s="15" t="n"/>
       <c r="P35" s="15" t="n"/>
@@ -8860,8 +8724,6 @@
       <c r="S35" s="15" t="n"/>
       <c r="T35" s="15" t="n"/>
       <c r="U35" s="15" t="n"/>
-      <c r="V35" s="15" t="n"/>
-      <c r="W35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -8902,22 +8764,20 @@
         </is>
       </c>
       <c r="I36" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="15" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="inlineStr">
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M36" s="15" t="n"/>
       <c r="N36" s="15" t="n"/>
       <c r="O36" s="15" t="n"/>
       <c r="P36" s="15" t="n"/>
@@ -8926,8 +8786,6 @@
       <c r="S36" s="15" t="n"/>
       <c r="T36" s="15" t="n"/>
       <c r="U36" s="15" t="n"/>
-      <c r="V36" s="15" t="n"/>
-      <c r="W36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -8967,21 +8825,21 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n">
+      <c r="I37" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="J37" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L37" s="15" t="n"/>
-      <c r="M37" s="15" t="inlineStr">
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="inlineStr">
         <is>
           <t>Twilight Masquerade</t>
         </is>
       </c>
+      <c r="M37" s="15" t="n"/>
       <c r="N37" s="15" t="n"/>
       <c r="O37" s="15" t="n"/>
       <c r="P37" s="15" t="n"/>
@@ -8990,8 +8848,6 @@
       <c r="S37" s="15" t="n"/>
       <c r="T37" s="15" t="n"/>
       <c r="U37" s="15" t="n"/>
-      <c r="V37" s="15" t="n"/>
-      <c r="W37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -9032,22 +8888,20 @@
         </is>
       </c>
       <c r="I38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="inlineStr">
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M38" s="15" t="n"/>
       <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="15" t="n"/>
@@ -9056,8 +8910,6 @@
       <c r="S38" s="15" t="n"/>
       <c r="T38" s="15" t="n"/>
       <c r="U38" s="15" t="n"/>
-      <c r="V38" s="15" t="n"/>
-      <c r="W38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -9100,24 +8952,22 @@
       <c r="I39" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="15" t="n">
-        <v>1</v>
+      <c r="J39" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Chandelure ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L39" s="15" t="inlineStr">
         <is>
-          <t>Mega Chandelure ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M39" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M39" s="15" t="n"/>
       <c r="N39" s="15" t="n"/>
       <c r="O39" s="15" t="n"/>
       <c r="P39" s="15" t="n"/>
@@ -9126,8 +8976,6 @@
       <c r="S39" s="15" t="n"/>
       <c r="T39" s="15" t="n"/>
       <c r="U39" s="15" t="n"/>
-      <c r="V39" s="15" t="n"/>
-      <c r="W39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -9170,24 +9018,22 @@
       <c r="I40" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="15" t="n">
-        <v>1</v>
+      <c r="J40" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Excadrill ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>Mega Excadrill ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M40" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M40" s="15" t="n"/>
       <c r="N40" s="15" t="n"/>
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="15" t="n"/>
@@ -9196,8 +9042,6 @@
       <c r="S40" s="15" t="n"/>
       <c r="T40" s="15" t="n"/>
       <c r="U40" s="15" t="n"/>
-      <c r="V40" s="15" t="n"/>
-      <c r="W40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -9238,26 +9082,24 @@
         </is>
       </c>
       <c r="I41" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="15" t="n">
         <v>5</v>
       </c>
+      <c r="J41" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Salazzle ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L41" s="15" t="inlineStr">
         <is>
-          <t>Salazzle ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M41" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M41" s="15" t="n"/>
       <c r="N41" s="15" t="n"/>
       <c r="O41" s="15" t="n"/>
       <c r="P41" s="15" t="n"/>
@@ -9266,8 +9108,6 @@
       <c r="S41" s="15" t="n"/>
       <c r="T41" s="15" t="n"/>
       <c r="U41" s="15" t="n"/>
-      <c r="V41" s="15" t="n"/>
-      <c r="W41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -9307,25 +9147,25 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n">
+      <c r="I42" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Thievul - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>Thievul - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M42" s="15" t="inlineStr">
-        <is>
           <t>Pitch Black</t>
         </is>
       </c>
+      <c r="M42" s="15" t="n"/>
       <c r="N42" s="15" t="n"/>
       <c r="O42" s="15" t="n"/>
       <c r="P42" s="15" t="n"/>
@@ -9334,8 +9174,6 @@
       <c r="S42" s="15" t="n"/>
       <c r="T42" s="15" t="n"/>
       <c r="U42" s="15" t="n"/>
-      <c r="V42" s="15" t="n"/>
-      <c r="W42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -9375,21 +9213,21 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n">
+      <c r="I43" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="J43" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L43" s="15" t="n"/>
-      <c r="M43" s="15" t="inlineStr">
+      <c r="K43" s="15" t="n"/>
+      <c r="L43" s="15" t="inlineStr">
         <is>
           <t>Surging Sparks</t>
         </is>
       </c>
+      <c r="M43" s="15" t="n"/>
       <c r="N43" s="15" t="n"/>
       <c r="O43" s="15" t="n"/>
       <c r="P43" s="15" t="n"/>
@@ -9398,8 +9236,6 @@
       <c r="S43" s="15" t="n"/>
       <c r="T43" s="15" t="n"/>
       <c r="U43" s="15" t="n"/>
-      <c r="V43" s="15" t="n"/>
-      <c r="W43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -9440,22 +9276,20 @@
         </is>
       </c>
       <c r="I44" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K44" s="15" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="inlineStr">
+      <c r="K44" s="15" t="n"/>
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M44" s="15" t="n"/>
       <c r="N44" s="15" t="n"/>
       <c r="O44" s="15" t="n"/>
       <c r="P44" s="15" t="n"/>
@@ -9464,8 +9298,6 @@
       <c r="S44" s="15" t="n"/>
       <c r="T44" s="15" t="n"/>
       <c r="U44" s="15" t="n"/>
-      <c r="V44" s="15" t="n"/>
-      <c r="W44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -9506,26 +9338,24 @@
         </is>
       </c>
       <c r="I45" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="J45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chespin - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L45" s="15" t="inlineStr">
         <is>
-          <t>Chespin - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M45" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M45" s="15" t="n"/>
       <c r="N45" s="15" t="n"/>
       <c r="O45" s="15" t="n"/>
       <c r="P45" s="15" t="n"/>
@@ -9534,8 +9364,6 @@
       <c r="S45" s="15" t="n"/>
       <c r="T45" s="15" t="n"/>
       <c r="U45" s="15" t="n"/>
-      <c r="V45" s="15" t="n"/>
-      <c r="W45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -9576,26 +9404,24 @@
         </is>
       </c>
       <c r="I46" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="J46" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K46" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Sacred Ash - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Sacred Ash - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M46" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M46" s="15" t="n"/>
       <c r="N46" s="15" t="n"/>
       <c r="O46" s="15" t="n"/>
       <c r="P46" s="15" t="n"/>
@@ -9604,8 +9430,6 @@
       <c r="S46" s="15" t="n"/>
       <c r="T46" s="15" t="n"/>
       <c r="U46" s="15" t="n"/>
-      <c r="V46" s="15" t="n"/>
-      <c r="W46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -9646,22 +9470,20 @@
         </is>
       </c>
       <c r="I47" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L47" s="15" t="n"/>
-      <c r="M47" s="15" t="inlineStr">
+      <c r="K47" s="15" t="n"/>
+      <c r="L47" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M47" s="15" t="n"/>
       <c r="N47" s="15" t="n"/>
       <c r="O47" s="15" t="n"/>
       <c r="P47" s="15" t="n"/>
@@ -9670,8 +9492,6 @@
       <c r="S47" s="15" t="n"/>
       <c r="T47" s="15" t="n"/>
       <c r="U47" s="15" t="n"/>
-      <c r="V47" s="15" t="n"/>
-      <c r="W47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -9711,25 +9531,25 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="n">
+      <c r="I48" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Lumiose City - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Lumiose City - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M48" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M48" s="15" t="n"/>
       <c r="N48" s="15" t="n"/>
       <c r="O48" s="15" t="n"/>
       <c r="P48" s="15" t="n"/>
@@ -9738,8 +9558,6 @@
       <c r="S48" s="15" t="n"/>
       <c r="T48" s="15" t="n"/>
       <c r="U48" s="15" t="n"/>
-      <c r="V48" s="15" t="n"/>
-      <c r="W48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -9780,22 +9598,20 @@
         </is>
       </c>
       <c r="I49" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K49" s="15" t="inlineStr">
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L49" s="15" t="n"/>
-      <c r="M49" s="15" t="inlineStr">
+      <c r="K49" s="15" t="n"/>
+      <c r="L49" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M49" s="15" t="n"/>
       <c r="N49" s="15" t="n"/>
       <c r="O49" s="15" t="n"/>
       <c r="P49" s="15" t="n"/>
@@ -9804,8 +9620,6 @@
       <c r="S49" s="15" t="n"/>
       <c r="T49" s="15" t="n"/>
       <c r="U49" s="15" t="n"/>
-      <c r="V49" s="15" t="n"/>
-      <c r="W49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -9848,24 +9662,22 @@
       <c r="I50" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="15" t="n">
-        <v>1</v>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ampharos - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>Ampharos - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M50" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M50" s="15" t="n"/>
       <c r="N50" s="15" t="n"/>
       <c r="O50" s="15" t="n"/>
       <c r="P50" s="15" t="n"/>
@@ -9874,8 +9686,6 @@
       <c r="S50" s="15" t="n"/>
       <c r="T50" s="15" t="n"/>
       <c r="U50" s="15" t="n"/>
-      <c r="V50" s="15" t="n"/>
-      <c r="W50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -9916,26 +9726,24 @@
         </is>
       </c>
       <c r="I51" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J51" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Scrafty ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L51" s="15" t="inlineStr">
         <is>
-          <t>Mega Scrafty ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M51" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M51" s="15" t="n"/>
       <c r="N51" s="15" t="n"/>
       <c r="O51" s="15" t="n"/>
       <c r="P51" s="15" t="n"/>
@@ -9944,8 +9752,6 @@
       <c r="S51" s="15" t="n"/>
       <c r="T51" s="15" t="n"/>
       <c r="U51" s="15" t="n"/>
-      <c r="V51" s="15" t="n"/>
-      <c r="W51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -9988,24 +9794,22 @@
       <c r="I52" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="15" t="n">
-        <v>2</v>
+      <c r="J52" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Energy Recycler - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Energy Recycler - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M52" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M52" s="15" t="n"/>
       <c r="N52" s="15" t="n"/>
       <c r="O52" s="15" t="n"/>
       <c r="P52" s="15" t="n"/>
@@ -10014,8 +9818,6 @@
       <c r="S52" s="15" t="n"/>
       <c r="T52" s="15" t="n"/>
       <c r="U52" s="15" t="n"/>
-      <c r="V52" s="15" t="n"/>
-      <c r="W52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -10056,26 +9858,24 @@
         </is>
       </c>
       <c r="I53" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Trainer - Team Rocket's Transceiver - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L53" s="15" t="inlineStr">
         <is>
-          <t>Trainer - Team Rocket's Transceiver - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M53" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M53" s="15" t="n"/>
       <c r="N53" s="15" t="n"/>
       <c r="O53" s="15" t="n"/>
       <c r="P53" s="15" t="n"/>
@@ -10084,8 +9884,6 @@
       <c r="S53" s="15" t="n"/>
       <c r="T53" s="15" t="n"/>
       <c r="U53" s="15" t="n"/>
-      <c r="V53" s="15" t="n"/>
-      <c r="W53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -10126,22 +9924,20 @@
         </is>
       </c>
       <c r="I54" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="15" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="K54" s="15" t="n"/>
+      <c r="L54" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M54" s="15" t="n"/>
       <c r="N54" s="15" t="n"/>
       <c r="O54" s="15" t="n"/>
       <c r="P54" s="15" t="n"/>
@@ -10150,8 +9946,6 @@
       <c r="S54" s="15" t="n"/>
       <c r="T54" s="15" t="n"/>
       <c r="U54" s="15" t="n"/>
-      <c r="V54" s="15" t="n"/>
-      <c r="W54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -10194,20 +9988,18 @@
       <c r="I55" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" s="15" t="inlineStr">
+      <c r="J55" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L55" s="15" t="n"/>
-      <c r="M55" s="15" t="inlineStr">
+      <c r="K55" s="15" t="n"/>
+      <c r="L55" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M55" s="15" t="n"/>
       <c r="N55" s="15" t="n"/>
       <c r="O55" s="15" t="n"/>
       <c r="P55" s="15" t="n"/>
@@ -10216,8 +10008,6 @@
       <c r="S55" s="15" t="n"/>
       <c r="T55" s="15" t="n"/>
       <c r="U55" s="15" t="n"/>
-      <c r="V55" s="15" t="n"/>
-      <c r="W55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -10258,22 +10048,20 @@
         </is>
       </c>
       <c r="I56" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L56" s="15" t="n"/>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="K56" s="15" t="n"/>
+      <c r="L56" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M56" s="15" t="n"/>
       <c r="N56" s="15" t="n"/>
       <c r="O56" s="15" t="n"/>
       <c r="P56" s="15" t="n"/>
@@ -10282,8 +10070,6 @@
       <c r="S56" s="15" t="n"/>
       <c r="T56" s="15" t="n"/>
       <c r="U56" s="15" t="n"/>
-      <c r="V56" s="15" t="n"/>
-      <c r="W56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -10324,22 +10110,20 @@
         </is>
       </c>
       <c r="I57" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="K57" s="15" t="inlineStr">
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L57" s="15" t="n"/>
-      <c r="M57" s="15" t="inlineStr">
+      <c r="K57" s="15" t="n"/>
+      <c r="L57" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M57" s="15" t="n"/>
       <c r="N57" s="15" t="n"/>
       <c r="O57" s="15" t="n"/>
       <c r="P57" s="15" t="n"/>
@@ -10348,8 +10132,6 @@
       <c r="S57" s="15" t="n"/>
       <c r="T57" s="15" t="n"/>
       <c r="U57" s="15" t="n"/>
-      <c r="V57" s="15" t="n"/>
-      <c r="W57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -10390,26 +10172,24 @@
         </is>
       </c>
       <c r="I58" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J58" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Scorbunny - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>Scorbunny - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M58" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M58" s="15" t="n"/>
       <c r="N58" s="15" t="n"/>
       <c r="O58" s="15" t="n"/>
       <c r="P58" s="15" t="n"/>
@@ -10418,8 +10198,6 @@
       <c r="S58" s="15" t="n"/>
       <c r="T58" s="15" t="n"/>
       <c r="U58" s="15" t="n"/>
-      <c r="V58" s="15" t="n"/>
-      <c r="W58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -10460,22 +10238,20 @@
         </is>
       </c>
       <c r="I59" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K59" s="15" t="inlineStr">
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L59" s="15" t="n"/>
-      <c r="M59" s="15" t="inlineStr">
+      <c r="K59" s="15" t="n"/>
+      <c r="L59" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M59" s="15" t="n"/>
       <c r="N59" s="15" t="n"/>
       <c r="O59" s="15" t="n"/>
       <c r="P59" s="15" t="n"/>
@@ -10484,8 +10260,6 @@
       <c r="S59" s="15" t="n"/>
       <c r="T59" s="15" t="n"/>
       <c r="U59" s="15" t="n"/>
-      <c r="V59" s="15" t="n"/>
-      <c r="W59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -10526,22 +10300,20 @@
         </is>
       </c>
       <c r="I60" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K60" s="15" t="inlineStr">
+      <c r="J60" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="K60" s="15" t="n"/>
+      <c r="L60" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M60" s="15" t="n"/>
       <c r="N60" s="15" t="n"/>
       <c r="O60" s="15" t="n"/>
       <c r="P60" s="15" t="n"/>
@@ -10550,8 +10322,6 @@
       <c r="S60" s="15" t="n"/>
       <c r="T60" s="15" t="n"/>
       <c r="U60" s="15" t="n"/>
-      <c r="V60" s="15" t="n"/>
-      <c r="W60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -10592,26 +10362,24 @@
         </is>
       </c>
       <c r="I61" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="15" t="n">
         <v>6</v>
       </c>
+      <c r="J61" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K61" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Beedrill ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L61" s="15" t="inlineStr">
         <is>
-          <t>Beedrill ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M61" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M61" s="15" t="n"/>
       <c r="N61" s="15" t="n"/>
       <c r="O61" s="15" t="n"/>
       <c r="P61" s="15" t="n"/>
@@ -10620,8 +10388,6 @@
       <c r="S61" s="15" t="n"/>
       <c r="T61" s="15" t="n"/>
       <c r="U61" s="15" t="n"/>
-      <c r="V61" s="15" t="n"/>
-      <c r="W61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -10664,24 +10430,22 @@
       <c r="I62" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="15" t="n">
-        <v>2</v>
+      <c r="J62" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Scrafty ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>Mega Scrafty ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M62" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M62" s="15" t="n"/>
       <c r="N62" s="15" t="n"/>
       <c r="O62" s="15" t="n"/>
       <c r="P62" s="15" t="n"/>
@@ -10690,8 +10454,6 @@
       <c r="S62" s="15" t="n"/>
       <c r="T62" s="15" t="n"/>
       <c r="U62" s="15" t="n"/>
-      <c r="V62" s="15" t="n"/>
-      <c r="W62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -10732,22 +10494,20 @@
         </is>
       </c>
       <c r="I63" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K63" s="15" t="inlineStr">
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L63" s="15" t="n"/>
-      <c r="M63" s="15" t="inlineStr">
+      <c r="K63" s="15" t="n"/>
+      <c r="L63" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M63" s="15" t="n"/>
       <c r="N63" s="15" t="n"/>
       <c r="O63" s="15" t="n"/>
       <c r="P63" s="15" t="n"/>
@@ -10756,8 +10516,6 @@
       <c r="S63" s="15" t="n"/>
       <c r="T63" s="15" t="n"/>
       <c r="U63" s="15" t="n"/>
-      <c r="V63" s="15" t="n"/>
-      <c r="W63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -10798,22 +10556,20 @@
         </is>
       </c>
       <c r="I64" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="15" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="K64" s="15" t="n"/>
+      <c r="L64" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M64" s="15" t="n"/>
       <c r="N64" s="15" t="n"/>
       <c r="O64" s="15" t="n"/>
       <c r="P64" s="15" t="n"/>
@@ -10822,8 +10578,6 @@
       <c r="S64" s="15" t="n"/>
       <c r="T64" s="15" t="n"/>
       <c r="U64" s="15" t="n"/>
-      <c r="V64" s="15" t="n"/>
-      <c r="W64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -10864,26 +10618,24 @@
         </is>
       </c>
       <c r="I65" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="J65" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chespin - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>Chespin - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M65" s="15" t="n"/>
       <c r="N65" s="15" t="n"/>
       <c r="O65" s="15" t="n"/>
       <c r="P65" s="15" t="n"/>
@@ -10892,8 +10644,6 @@
       <c r="S65" s="15" t="n"/>
       <c r="T65" s="15" t="n"/>
       <c r="U65" s="15" t="n"/>
-      <c r="V65" s="15" t="n"/>
-      <c r="W65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -10933,21 +10683,21 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I66" s="15" t="n"/>
-      <c r="J66" s="15" t="n">
+      <c r="I66" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K66" s="15" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="inlineStr">
+      <c r="K66" s="15" t="n"/>
+      <c r="L66" s="15" t="inlineStr">
         <is>
           <t>Twilight Masquerade</t>
         </is>
       </c>
+      <c r="M66" s="15" t="n"/>
       <c r="N66" s="15" t="n"/>
       <c r="O66" s="15" t="n"/>
       <c r="P66" s="15" t="n"/>
@@ -10956,8 +10706,6 @@
       <c r="S66" s="15" t="n"/>
       <c r="T66" s="15" t="n"/>
       <c r="U66" s="15" t="n"/>
-      <c r="V66" s="15" t="n"/>
-      <c r="W66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -10998,26 +10746,24 @@
         </is>
       </c>
       <c r="I67" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J67" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
-          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="inlineStr">
-        <is>
           <t>First Partner Illustration Collection (Series 1) , Phantasmal Flames, Mega Evolution</t>
         </is>
       </c>
+      <c r="M67" s="15" t="n"/>
       <c r="N67" s="15" t="n"/>
       <c r="O67" s="15" t="n"/>
       <c r="P67" s="15" t="n"/>
@@ -11026,8 +10772,6 @@
       <c r="S67" s="15" t="n"/>
       <c r="T67" s="15" t="n"/>
       <c r="U67" s="15" t="n"/>
-      <c r="V67" s="15" t="n"/>
-      <c r="W67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
@@ -11067,25 +10811,25 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I68" s="15" t="n"/>
-      <c r="J68" s="15" t="n">
+      <c r="I68" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="J68" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Shiinotic - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>Shiinotic - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="inlineStr">
-        <is>
           <t>Surging Sparks</t>
         </is>
       </c>
+      <c r="M68" s="15" t="n"/>
       <c r="N68" s="15" t="n"/>
       <c r="O68" s="15" t="n"/>
       <c r="P68" s="15" t="n"/>
@@ -11094,8 +10838,6 @@
       <c r="S68" s="15" t="n"/>
       <c r="T68" s="15" t="n"/>
       <c r="U68" s="15" t="n"/>
-      <c r="V68" s="15" t="n"/>
-      <c r="W68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -11135,25 +10877,25 @@
           <t>Poke Ball Tin</t>
         </is>
       </c>
-      <c r="I69" s="15" t="n"/>
-      <c r="J69" s="15" t="n">
+      <c r="I69" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J69" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Salazzle ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
         <is>
-          <t>Salazzle ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M69" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M69" s="15" t="n"/>
       <c r="N69" s="15" t="n"/>
       <c r="O69" s="15" t="n"/>
       <c r="P69" s="15" t="n"/>
@@ -11162,8 +10904,6 @@
       <c r="S69" s="15" t="n"/>
       <c r="T69" s="15" t="n"/>
       <c r="U69" s="15" t="n"/>
-      <c r="V69" s="15" t="n"/>
-      <c r="W69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -11204,26 +10944,24 @@
         </is>
       </c>
       <c r="I70" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J70" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Floette ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>Mega Floette ex - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M70" s="15" t="n"/>
       <c r="N70" s="15" t="n"/>
       <c r="O70" s="15" t="n"/>
       <c r="P70" s="15" t="n"/>
@@ -11232,8 +10970,6 @@
       <c r="S70" s="15" t="n"/>
       <c r="T70" s="15" t="n"/>
       <c r="U70" s="15" t="n"/>
-      <c r="V70" s="15" t="n"/>
-      <c r="W70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -11274,22 +11010,20 @@
         </is>
       </c>
       <c r="I71" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K71" s="15" t="inlineStr">
+      <c r="J71" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L71" s="15" t="n"/>
-      <c r="M71" s="15" t="inlineStr">
+      <c r="K71" s="15" t="n"/>
+      <c r="L71" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M71" s="15" t="n"/>
       <c r="N71" s="15" t="n"/>
       <c r="O71" s="15" t="n"/>
       <c r="P71" s="15" t="n"/>
@@ -11298,8 +11032,6 @@
       <c r="S71" s="15" t="n"/>
       <c r="T71" s="15" t="n"/>
       <c r="U71" s="15" t="n"/>
-      <c r="V71" s="15" t="n"/>
-      <c r="W71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -11340,26 +11072,24 @@
         </is>
       </c>
       <c r="I72" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J72" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio ; Phantasmal Flames - Trainer - Punk Helmet - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>First Partner Illustration Collection (Series 1) Alola Region Promo : Rowlet, Litten, Popplio ; Phantasmal Flames - Trainer - Punk Helmet - Double Silver Star - Ultra Rare</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
           <t>First Partner Illustration Collection (Series 1) , Phantasmal Flames, Mega Evolution</t>
         </is>
       </c>
+      <c r="M72" s="15" t="n"/>
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
       <c r="P72" s="15" t="n"/>
@@ -11368,8 +11098,6 @@
       <c r="S72" s="15" t="n"/>
       <c r="T72" s="15" t="n"/>
       <c r="U72" s="15" t="n"/>
-      <c r="V72" s="15" t="n"/>
-      <c r="W72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -11410,22 +11138,20 @@
         </is>
       </c>
       <c r="I73" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K73" s="15" t="inlineStr">
+      <c r="J73" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L73" s="15" t="n"/>
-      <c r="M73" s="15" t="inlineStr">
+      <c r="K73" s="15" t="n"/>
+      <c r="L73" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M73" s="15" t="n"/>
       <c r="N73" s="15" t="n"/>
       <c r="O73" s="15" t="n"/>
       <c r="P73" s="15" t="n"/>
@@ -11434,8 +11160,6 @@
       <c r="S73" s="15" t="n"/>
       <c r="T73" s="15" t="n"/>
       <c r="U73" s="15" t="n"/>
-      <c r="V73" s="15" t="n"/>
-      <c r="W73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -11475,21 +11199,21 @@
           <t>Single Booster Pack</t>
         </is>
       </c>
-      <c r="I74" s="15" t="n"/>
-      <c r="J74" s="15" t="n">
+      <c r="I74" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="K74" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="K74" s="15" t="n"/>
+      <c r="L74" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M74" s="15" t="n"/>
       <c r="N74" s="15" t="n"/>
       <c r="O74" s="15" t="n"/>
       <c r="P74" s="15" t="n"/>
@@ -11498,8 +11222,6 @@
       <c r="S74" s="15" t="n"/>
       <c r="T74" s="15" t="n"/>
       <c r="U74" s="15" t="n"/>
-      <c r="V74" s="15" t="n"/>
-      <c r="W74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
@@ -11539,21 +11261,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I75" s="15" t="n"/>
-      <c r="J75" s="15" t="n">
+      <c r="I75" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="K75" s="15" t="inlineStr">
+      <c r="J75" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L75" s="15" t="n"/>
-      <c r="M75" s="15" t="inlineStr">
+      <c r="K75" s="15" t="n"/>
+      <c r="L75" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M75" s="15" t="n"/>
       <c r="N75" s="15" t="n"/>
       <c r="O75" s="15" t="n"/>
       <c r="P75" s="15" t="n"/>
@@ -11562,8 +11284,6 @@
       <c r="S75" s="15" t="n"/>
       <c r="T75" s="15" t="n"/>
       <c r="U75" s="15" t="n"/>
-      <c r="V75" s="15" t="n"/>
-      <c r="W75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
@@ -11603,21 +11323,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I76" s="15" t="n"/>
-      <c r="J76" s="15" t="n">
+      <c r="I76" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="K76" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="K76" s="15" t="n"/>
+      <c r="L76" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M76" s="15" t="n"/>
       <c r="N76" s="15" t="n"/>
       <c r="O76" s="15" t="n"/>
       <c r="P76" s="15" t="n"/>
@@ -11626,8 +11346,6 @@
       <c r="S76" s="15" t="n"/>
       <c r="T76" s="15" t="n"/>
       <c r="U76" s="15" t="n"/>
-      <c r="V76" s="15" t="n"/>
-      <c r="W76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -11667,21 +11385,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I77" s="15" t="n"/>
-      <c r="J77" s="15" t="n">
+      <c r="I77" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="K77" s="15" t="inlineStr">
+      <c r="J77" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L77" s="15" t="n"/>
-      <c r="M77" s="15" t="inlineStr">
+      <c r="K77" s="15" t="n"/>
+      <c r="L77" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M77" s="15" t="n"/>
       <c r="N77" s="15" t="n"/>
       <c r="O77" s="15" t="n"/>
       <c r="P77" s="15" t="n"/>
@@ -11690,8 +11408,6 @@
       <c r="S77" s="15" t="n"/>
       <c r="T77" s="15" t="n"/>
       <c r="U77" s="15" t="n"/>
-      <c r="V77" s="15" t="n"/>
-      <c r="W77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -11731,25 +11447,25 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I78" s="15" t="n"/>
-      <c r="J78" s="15" t="n">
+      <c r="I78" s="15" t="n">
         <v>9</v>
       </c>
+      <c r="J78" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Dragalge ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>Mega Dragalge ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M78" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M78" s="15" t="n"/>
       <c r="N78" s="15" t="n"/>
       <c r="O78" s="15" t="n"/>
       <c r="P78" s="15" t="n"/>
@@ -11758,8 +11474,6 @@
       <c r="S78" s="15" t="n"/>
       <c r="T78" s="15" t="n"/>
       <c r="U78" s="15" t="n"/>
-      <c r="V78" s="15" t="n"/>
-      <c r="W78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -11799,25 +11513,25 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I79" s="15" t="n"/>
-      <c r="J79" s="15" t="n">
+      <c r="I79" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="J79" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dedenne - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
         <is>
-          <t>Dedenne - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M79" s="15" t="inlineStr">
-        <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M79" s="15" t="n"/>
       <c r="N79" s="15" t="n"/>
       <c r="O79" s="15" t="n"/>
       <c r="P79" s="15" t="n"/>
@@ -11826,8 +11540,6 @@
       <c r="S79" s="15" t="n"/>
       <c r="T79" s="15" t="n"/>
       <c r="U79" s="15" t="n"/>
-      <c r="V79" s="15" t="n"/>
-      <c r="W79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -11867,25 +11579,25 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I80" s="15" t="n"/>
-      <c r="J80" s="15" t="n">
+      <c r="I80" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="J80" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Xerneas - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>Xerneas - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M80" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M80" s="15" t="n"/>
       <c r="N80" s="15" t="n"/>
       <c r="O80" s="15" t="n"/>
       <c r="P80" s="15" t="n"/>
@@ -11894,8 +11606,6 @@
       <c r="S80" s="15" t="n"/>
       <c r="T80" s="15" t="n"/>
       <c r="U80" s="15" t="n"/>
-      <c r="V80" s="15" t="n"/>
-      <c r="W80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -11935,21 +11645,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I81" s="15" t="n"/>
-      <c r="J81" s="15" t="n">
+      <c r="I81" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K81" s="15" t="inlineStr">
+      <c r="J81" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L81" s="15" t="n"/>
-      <c r="M81" s="15" t="inlineStr">
+      <c r="K81" s="15" t="n"/>
+      <c r="L81" s="15" t="inlineStr">
         <is>
           <t>Perfect Order</t>
         </is>
       </c>
+      <c r="M81" s="15" t="n"/>
       <c r="N81" s="15" t="n"/>
       <c r="O81" s="15" t="n"/>
       <c r="P81" s="15" t="n"/>
@@ -11958,8 +11668,6 @@
       <c r="S81" s="15" t="n"/>
       <c r="T81" s="15" t="n"/>
       <c r="U81" s="15" t="n"/>
-      <c r="V81" s="15" t="n"/>
-      <c r="W81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -11999,21 +11707,21 @@
           <t>Sleeved Booster Pack</t>
         </is>
       </c>
-      <c r="I82" s="15" t="n"/>
-      <c r="J82" s="15" t="n">
+      <c r="I82" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K82" s="15" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L82" s="15" t="n"/>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="K82" s="15" t="n"/>
+      <c r="L82" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M82" s="15" t="n"/>
       <c r="N82" s="15" t="n"/>
       <c r="O82" s="15" t="n"/>
       <c r="P82" s="15" t="n"/>
@@ -12022,8 +11730,6 @@
       <c r="S82" s="15" t="n"/>
       <c r="T82" s="15" t="n"/>
       <c r="U82" s="15" t="n"/>
-      <c r="V82" s="15" t="n"/>
-      <c r="W82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
@@ -12064,22 +11770,20 @@
         </is>
       </c>
       <c r="I83" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="K83" s="15" t="inlineStr">
+      <c r="J83" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L83" s="15" t="n"/>
-      <c r="M83" s="15" t="inlineStr">
+      <c r="K83" s="15" t="n"/>
+      <c r="L83" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M83" s="15" t="n"/>
       <c r="N83" s="15" t="n"/>
       <c r="O83" s="15" t="n"/>
       <c r="P83" s="15" t="n"/>
@@ -12088,8 +11792,6 @@
       <c r="S83" s="15" t="n"/>
       <c r="T83" s="15" t="n"/>
       <c r="U83" s="15" t="n"/>
-      <c r="V83" s="15" t="n"/>
-      <c r="W83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
@@ -12130,22 +11832,20 @@
         </is>
       </c>
       <c r="I84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K84" s="15" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L84" s="15" t="n"/>
-      <c r="M84" s="15" t="inlineStr">
+      <c r="K84" s="15" t="n"/>
+      <c r="L84" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M84" s="15" t="n"/>
       <c r="N84" s="15" t="n"/>
       <c r="O84" s="15" t="n"/>
       <c r="P84" s="15" t="n"/>
@@ -12154,8 +11854,6 @@
       <c r="S84" s="15" t="n"/>
       <c r="T84" s="15" t="n"/>
       <c r="U84" s="15" t="n"/>
-      <c r="V84" s="15" t="n"/>
-      <c r="W84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
@@ -12196,26 +11894,24 @@
         </is>
       </c>
       <c r="I85" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J85" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K85" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Larry's Dudunsparce ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L85" s="15" t="inlineStr">
         <is>
-          <t>Larry's Dudunsparce ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M85" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M85" s="15" t="n"/>
       <c r="N85" s="15" t="n"/>
       <c r="O85" s="15" t="n"/>
       <c r="P85" s="15" t="n"/>
@@ -12224,8 +11920,6 @@
       <c r="S85" s="15" t="n"/>
       <c r="T85" s="15" t="n"/>
       <c r="U85" s="15" t="n"/>
-      <c r="V85" s="15" t="n"/>
-      <c r="W85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -12266,22 +11960,20 @@
         </is>
       </c>
       <c r="I86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K86" s="15" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L86" s="15" t="n"/>
-      <c r="M86" s="15" t="inlineStr">
+      <c r="K86" s="15" t="n"/>
+      <c r="L86" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M86" s="15" t="n"/>
       <c r="N86" s="15" t="n"/>
       <c r="O86" s="15" t="n"/>
       <c r="P86" s="15" t="n"/>
@@ -12290,8 +11982,6 @@
       <c r="S86" s="15" t="n"/>
       <c r="T86" s="15" t="n"/>
       <c r="U86" s="15" t="n"/>
-      <c r="V86" s="15" t="n"/>
-      <c r="W86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -12332,22 +12022,20 @@
         </is>
       </c>
       <c r="I87" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="15" t="inlineStr">
+      <c r="J87" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L87" s="15" t="n"/>
-      <c r="M87" s="15" t="inlineStr">
+      <c r="K87" s="15" t="n"/>
+      <c r="L87" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M87" s="15" t="n"/>
       <c r="N87" s="15" t="n"/>
       <c r="O87" s="15" t="n"/>
       <c r="P87" s="15" t="n"/>
@@ -12356,8 +12044,6 @@
       <c r="S87" s="15" t="n"/>
       <c r="T87" s="15" t="n"/>
       <c r="U87" s="15" t="n"/>
-      <c r="V87" s="15" t="n"/>
-      <c r="W87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
@@ -12398,26 +12084,24 @@
         </is>
       </c>
       <c r="I88" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="15" t="n">
         <v>8</v>
       </c>
+      <c r="J88" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Krookodile ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>Krookodile ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M88" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M88" s="15" t="n"/>
       <c r="N88" s="15" t="n"/>
       <c r="O88" s="15" t="n"/>
       <c r="P88" s="15" t="n"/>
@@ -12426,8 +12110,6 @@
       <c r="S88" s="15" t="n"/>
       <c r="T88" s="15" t="n"/>
       <c r="U88" s="15" t="n"/>
-      <c r="V88" s="15" t="n"/>
-      <c r="W88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
@@ -12468,22 +12150,20 @@
         </is>
       </c>
       <c r="I89" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="K89" s="15" t="inlineStr">
+      <c r="J89" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L89" s="15" t="n"/>
-      <c r="M89" s="15" t="inlineStr">
+      <c r="K89" s="15" t="n"/>
+      <c r="L89" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M89" s="15" t="n"/>
       <c r="N89" s="15" t="n"/>
       <c r="O89" s="15" t="n"/>
       <c r="P89" s="15" t="n"/>
@@ -12492,8 +12172,6 @@
       <c r="S89" s="15" t="n"/>
       <c r="T89" s="15" t="n"/>
       <c r="U89" s="15" t="n"/>
-      <c r="V89" s="15" t="n"/>
-      <c r="W89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
@@ -12534,26 +12212,24 @@
         </is>
       </c>
       <c r="I90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="J90" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Larry's Dudunsparce ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>Larry's Dudunsparce ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M90" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M90" s="15" t="n"/>
       <c r="N90" s="15" t="n"/>
       <c r="O90" s="15" t="n"/>
       <c r="P90" s="15" t="n"/>
@@ -12562,8 +12238,6 @@
       <c r="S90" s="15" t="n"/>
       <c r="T90" s="15" t="n"/>
       <c r="U90" s="15" t="n"/>
-      <c r="V90" s="15" t="n"/>
-      <c r="W90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
@@ -12606,20 +12280,18 @@
       <c r="I91" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" s="15" t="inlineStr">
+      <c r="J91" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L91" s="15" t="n"/>
-      <c r="M91" s="15" t="inlineStr">
+      <c r="K91" s="15" t="n"/>
+      <c r="L91" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M91" s="15" t="n"/>
       <c r="N91" s="15" t="n"/>
       <c r="O91" s="15" t="n"/>
       <c r="P91" s="15" t="n"/>
@@ -12628,8 +12300,6 @@
       <c r="S91" s="15" t="n"/>
       <c r="T91" s="15" t="n"/>
       <c r="U91" s="15" t="n"/>
-      <c r="V91" s="15" t="n"/>
-      <c r="W91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
@@ -12670,22 +12340,20 @@
         </is>
       </c>
       <c r="I92" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K92" s="15" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L92" s="15" t="n"/>
-      <c r="M92" s="15" t="inlineStr">
+      <c r="K92" s="15" t="n"/>
+      <c r="L92" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M92" s="15" t="n"/>
       <c r="N92" s="15" t="n"/>
       <c r="O92" s="15" t="n"/>
       <c r="P92" s="15" t="n"/>
@@ -12694,8 +12362,6 @@
       <c r="S92" s="15" t="n"/>
       <c r="T92" s="15" t="n"/>
       <c r="U92" s="15" t="n"/>
-      <c r="V92" s="15" t="n"/>
-      <c r="W92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -12738,24 +12404,22 @@
       <c r="I93" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J93" s="15" t="n">
-        <v>1</v>
+      <c r="J93" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K93" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Slurpuff - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L93" s="15" t="inlineStr">
         <is>
-          <t>Slurpuff - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M93" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M93" s="15" t="n"/>
       <c r="N93" s="15" t="n"/>
       <c r="O93" s="15" t="n"/>
       <c r="P93" s="15" t="n"/>
@@ -12764,8 +12428,6 @@
       <c r="S93" s="15" t="n"/>
       <c r="T93" s="15" t="n"/>
       <c r="U93" s="15" t="n"/>
-      <c r="V93" s="15" t="n"/>
-      <c r="W93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
@@ -12806,26 +12468,24 @@
         </is>
       </c>
       <c r="I94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="15" t="n">
         <v>6</v>
       </c>
+      <c r="J94" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Greninja ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>Mega Greninja ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M94" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M94" s="15" t="n"/>
       <c r="N94" s="15" t="n"/>
       <c r="O94" s="15" t="n"/>
       <c r="P94" s="15" t="n"/>
@@ -12834,8 +12494,6 @@
       <c r="S94" s="15" t="n"/>
       <c r="T94" s="15" t="n"/>
       <c r="U94" s="15" t="n"/>
-      <c r="V94" s="15" t="n"/>
-      <c r="W94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
@@ -12876,22 +12534,20 @@
         </is>
       </c>
       <c r="I95" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K95" s="15" t="inlineStr">
+      <c r="J95" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L95" s="15" t="n"/>
-      <c r="M95" s="15" t="inlineStr">
+      <c r="K95" s="15" t="n"/>
+      <c r="L95" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M95" s="15" t="n"/>
       <c r="N95" s="15" t="n"/>
       <c r="O95" s="15" t="n"/>
       <c r="P95" s="15" t="n"/>
@@ -12900,8 +12556,6 @@
       <c r="S95" s="15" t="n"/>
       <c r="T95" s="15" t="n"/>
       <c r="U95" s="15" t="n"/>
-      <c r="V95" s="15" t="n"/>
-      <c r="W95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
@@ -12942,22 +12596,20 @@
         </is>
       </c>
       <c r="I96" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="K96" s="15" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L96" s="15" t="n"/>
-      <c r="M96" s="15" t="inlineStr">
+      <c r="K96" s="15" t="n"/>
+      <c r="L96" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M96" s="15" t="n"/>
       <c r="N96" s="15" t="n"/>
       <c r="O96" s="15" t="n"/>
       <c r="P96" s="15" t="n"/>
@@ -12966,8 +12618,6 @@
       <c r="S96" s="15" t="n"/>
       <c r="T96" s="15" t="n"/>
       <c r="U96" s="15" t="n"/>
-      <c r="V96" s="15" t="n"/>
-      <c r="W96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
@@ -13008,26 +12658,24 @@
         </is>
       </c>
       <c r="I97" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="15" t="n">
         <v>3</v>
       </c>
+      <c r="J97" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mega Hawlucha ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L97" s="15" t="inlineStr">
         <is>
-          <t>Mega Hawlucha ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M97" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M97" s="15" t="n"/>
       <c r="N97" s="15" t="n"/>
       <c r="O97" s="15" t="n"/>
       <c r="P97" s="15" t="n"/>
@@ -13036,8 +12684,6 @@
       <c r="S97" s="15" t="n"/>
       <c r="T97" s="15" t="n"/>
       <c r="U97" s="15" t="n"/>
-      <c r="V97" s="15" t="n"/>
-      <c r="W97" s="15" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
@@ -13078,26 +12724,24 @@
         </is>
       </c>
       <c r="I98" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="15" t="n">
         <v>4</v>
       </c>
+      <c r="J98" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cobalion ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>Cobalion ex - Double Black Star - Double Rare</t>
-        </is>
-      </c>
-      <c r="M98" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M98" s="15" t="n"/>
       <c r="N98" s="15" t="n"/>
       <c r="O98" s="15" t="n"/>
       <c r="P98" s="15" t="n"/>
@@ -13106,8 +12750,6 @@
       <c r="S98" s="15" t="n"/>
       <c r="T98" s="15" t="n"/>
       <c r="U98" s="15" t="n"/>
-      <c r="V98" s="15" t="n"/>
-      <c r="W98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -13150,20 +12792,18 @@
       <c r="I99" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J99" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K99" s="15" t="inlineStr">
+      <c r="J99" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L99" s="15" t="n"/>
-      <c r="M99" s="15" t="inlineStr">
+      <c r="K99" s="15" t="n"/>
+      <c r="L99" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M99" s="15" t="n"/>
       <c r="N99" s="15" t="n"/>
       <c r="O99" s="15" t="n"/>
       <c r="P99" s="15" t="n"/>
@@ -13172,8 +12812,6 @@
       <c r="S99" s="15" t="n"/>
       <c r="T99" s="15" t="n"/>
       <c r="U99" s="15" t="n"/>
-      <c r="V99" s="15" t="n"/>
-      <c r="W99" s="15" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -13214,22 +12852,20 @@
         </is>
       </c>
       <c r="I100" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K100" s="15" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L100" s="15" t="n"/>
-      <c r="M100" s="15" t="inlineStr">
+      <c r="K100" s="15" t="n"/>
+      <c r="L100" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M100" s="15" t="n"/>
       <c r="N100" s="15" t="n"/>
       <c r="O100" s="15" t="n"/>
       <c r="P100" s="15" t="n"/>
@@ -13238,8 +12874,6 @@
       <c r="S100" s="15" t="n"/>
       <c r="T100" s="15" t="n"/>
       <c r="U100" s="15" t="n"/>
-      <c r="V100" s="15" t="n"/>
-      <c r="W100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
@@ -13280,22 +12914,20 @@
         </is>
       </c>
       <c r="I101" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K101" s="15" t="inlineStr">
+      <c r="J101" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L101" s="15" t="n"/>
-      <c r="M101" s="15" t="inlineStr">
+      <c r="K101" s="15" t="n"/>
+      <c r="L101" s="15" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
         </is>
       </c>
+      <c r="M101" s="15" t="n"/>
       <c r="N101" s="15" t="n"/>
       <c r="O101" s="15" t="n"/>
       <c r="P101" s="15" t="n"/>
@@ -13304,8 +12936,6 @@
       <c r="S101" s="15" t="n"/>
       <c r="T101" s="15" t="n"/>
       <c r="U101" s="15" t="n"/>
-      <c r="V101" s="15" t="n"/>
-      <c r="W101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
@@ -13346,22 +12976,20 @@
         </is>
       </c>
       <c r="I102" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K102" s="15" t="inlineStr">
+      <c r="J102" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="inlineStr">
+      <c r="K102" s="15" t="n"/>
+      <c r="L102" s="15" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M102" s="15" t="n"/>
       <c r="N102" s="15" t="n"/>
       <c r="O102" s="15" t="n"/>
       <c r="P102" s="15" t="n"/>
@@ -13370,8 +12998,6 @@
       <c r="S102" s="15" t="n"/>
       <c r="T102" s="15" t="n"/>
       <c r="U102" s="15" t="n"/>
-      <c r="V102" s="15" t="n"/>
-      <c r="W102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
@@ -13414,24 +13040,22 @@
       <c r="I103" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J103" s="15" t="n">
-        <v>1</v>
+      <c r="J103" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="K103" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chespin - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
         <is>
-          <t>Chespin - Single Gold Star - Illustration Rare</t>
-        </is>
-      </c>
-      <c r="M103" s="15" t="inlineStr">
-        <is>
           <t>Chaos Rising</t>
         </is>
       </c>
+      <c r="M103" s="15" t="n"/>
       <c r="N103" s="15" t="n"/>
       <c r="O103" s="15" t="n"/>
       <c r="P103" s="15" t="n"/>
@@ -13440,8 +13064,6 @@
       <c r="S103" s="15" t="n"/>
       <c r="T103" s="15" t="n"/>
       <c r="U103" s="15" t="n"/>
-      <c r="V103" s="15" t="n"/>
-      <c r="W103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
@@ -13481,21 +13103,21 @@
           <t>ex Premium Collection Box</t>
         </is>
       </c>
-      <c r="I104" s="15" t="n"/>
-      <c r="J104" s="15" t="n">
+      <c r="I104" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="K104" s="15" t="inlineStr">
+      <c r="J104" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L104" s="15" t="n"/>
-      <c r="M104" s="15" t="inlineStr">
+      <c r="K104" s="15" t="n"/>
+      <c r="L104" s="15" t="inlineStr">
         <is>
           <t>Phantasmal Flames</t>
         </is>
       </c>
+      <c r="M104" s="15" t="n"/>
       <c r="N104" s="15" t="n"/>
       <c r="O104" s="15" t="n"/>
       <c r="P104" s="15" t="n"/>
@@ -13504,8 +13126,6 @@
       <c r="S104" s="15" t="n"/>
       <c r="T104" s="15" t="n"/>
       <c r="U104" s="15" t="n"/>
-      <c r="V104" s="15" t="n"/>
-      <c r="W104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -13546,18 +13166,18 @@
         </is>
       </c>
       <c r="I105" s="15" t="n"/>
-      <c r="J105" s="15" t="n"/>
-      <c r="K105" s="15" t="inlineStr">
+      <c r="J105" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L105" s="15" t="n"/>
-      <c r="M105" s="15" t="inlineStr">
+      <c r="K105" s="15" t="n"/>
+      <c r="L105" s="15" t="inlineStr">
         <is>
           <t>Abyss Eye</t>
         </is>
       </c>
+      <c r="M105" s="15" t="n"/>
       <c r="N105" s="15" t="n"/>
       <c r="O105" s="15" t="n"/>
       <c r="P105" s="15" t="n"/>
@@ -13566,8 +13186,6 @@
       <c r="S105" s="15" t="n"/>
       <c r="T105" s="15" t="n"/>
       <c r="U105" s="15" t="n"/>
-      <c r="V105" s="15" t="n"/>
-      <c r="W105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -13616,8 +13234,6 @@
       <c r="S106" s="15" t="n"/>
       <c r="T106" s="15" t="n"/>
       <c r="U106" s="15" t="n"/>
-      <c r="V106" s="15" t="n"/>
-      <c r="W106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
@@ -13666,8 +13282,6 @@
       <c r="S107" s="15" t="n"/>
       <c r="T107" s="15" t="n"/>
       <c r="U107" s="15" t="n"/>
-      <c r="V107" s="15" t="n"/>
-      <c r="W107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
@@ -13716,8 +13330,6 @@
       <c r="S108" s="15" t="n"/>
       <c r="T108" s="15" t="n"/>
       <c r="U108" s="15" t="n"/>
-      <c r="V108" s="15" t="n"/>
-      <c r="W108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
@@ -13766,8 +13378,6 @@
       <c r="S109" s="15" t="n"/>
       <c r="T109" s="15" t="n"/>
       <c r="U109" s="15" t="n"/>
-      <c r="V109" s="15" t="n"/>
-      <c r="W109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -13816,8 +13426,6 @@
       <c r="S110" s="15" t="n"/>
       <c r="T110" s="15" t="n"/>
       <c r="U110" s="15" t="n"/>
-      <c r="V110" s="15" t="n"/>
-      <c r="W110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -13866,8 +13474,6 @@
       <c r="S111" s="15" t="n"/>
       <c r="T111" s="15" t="n"/>
       <c r="U111" s="15" t="n"/>
-      <c r="V111" s="15" t="n"/>
-      <c r="W111" s="15" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -13916,8 +13522,6 @@
       <c r="S112" s="15" t="n"/>
       <c r="T112" s="15" t="n"/>
       <c r="U112" s="15" t="n"/>
-      <c r="V112" s="15" t="n"/>
-      <c r="W112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
@@ -13966,8 +13570,6 @@
       <c r="S113" s="15" t="n"/>
       <c r="T113" s="15" t="n"/>
       <c r="U113" s="15" t="n"/>
-      <c r="V113" s="15" t="n"/>
-      <c r="W113" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
@@ -14016,8 +13618,6 @@
       <c r="S114" s="15" t="n"/>
       <c r="T114" s="15" t="n"/>
       <c r="U114" s="15" t="n"/>
-      <c r="V114" s="15" t="n"/>
-      <c r="W114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
@@ -14066,8 +13666,6 @@
       <c r="S115" s="15" t="n"/>
       <c r="T115" s="15" t="n"/>
       <c r="U115" s="15" t="n"/>
-      <c r="V115" s="15" t="n"/>
-      <c r="W115" s="15" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
@@ -14116,8 +13714,6 @@
       <c r="S116" s="15" t="n"/>
       <c r="T116" s="15" t="n"/>
       <c r="U116" s="15" t="n"/>
-      <c r="V116" s="15" t="n"/>
-      <c r="W116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -14166,8 +13762,6 @@
       <c r="S117" s="15" t="n"/>
       <c r="T117" s="15" t="n"/>
       <c r="U117" s="15" t="n"/>
-      <c r="V117" s="15" t="n"/>
-      <c r="W117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
@@ -14216,8 +13810,6 @@
       <c r="S118" s="15" t="n"/>
       <c r="T118" s="15" t="n"/>
       <c r="U118" s="15" t="n"/>
-      <c r="V118" s="15" t="n"/>
-      <c r="W118" s="15" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
@@ -14266,8 +13858,6 @@
       <c r="S119" s="15" t="n"/>
       <c r="T119" s="15" t="n"/>
       <c r="U119" s="15" t="n"/>
-      <c r="V119" s="15" t="n"/>
-      <c r="W119" s="15" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -14316,8 +13906,6 @@
       <c r="S120" s="15" t="n"/>
       <c r="T120" s="15" t="n"/>
       <c r="U120" s="15" t="n"/>
-      <c r="V120" s="15" t="n"/>
-      <c r="W120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
@@ -14366,8 +13954,6 @@
       <c r="S121" s="15" t="n"/>
       <c r="T121" s="15" t="n"/>
       <c r="U121" s="15" t="n"/>
-      <c r="V121" s="15" t="n"/>
-      <c r="W121" s="15" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
@@ -14416,8 +14002,6 @@
       <c r="S122" s="15" t="n"/>
       <c r="T122" s="15" t="n"/>
       <c r="U122" s="15" t="n"/>
-      <c r="V122" s="15" t="n"/>
-      <c r="W122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
@@ -14466,8 +14050,6 @@
       <c r="S123" s="15" t="n"/>
       <c r="T123" s="15" t="n"/>
       <c r="U123" s="15" t="n"/>
-      <c r="V123" s="15" t="n"/>
-      <c r="W123" s="15" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
@@ -14516,8 +14098,6 @@
       <c r="S124" s="15" t="n"/>
       <c r="T124" s="15" t="n"/>
       <c r="U124" s="15" t="n"/>
-      <c r="V124" s="15" t="n"/>
-      <c r="W124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
@@ -14566,8 +14146,6 @@
       <c r="S125" s="15" t="n"/>
       <c r="T125" s="15" t="n"/>
       <c r="U125" s="15" t="n"/>
-      <c r="V125" s="15" t="n"/>
-      <c r="W125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
@@ -14616,8 +14194,6 @@
       <c r="S126" s="15" t="n"/>
       <c r="T126" s="15" t="n"/>
       <c r="U126" s="15" t="n"/>
-      <c r="V126" s="15" t="n"/>
-      <c r="W126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -14666,8 +14242,6 @@
       <c r="S127" s="15" t="n"/>
       <c r="T127" s="15" t="n"/>
       <c r="U127" s="15" t="n"/>
-      <c r="V127" s="15" t="n"/>
-      <c r="W127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -14716,8 +14290,6 @@
       <c r="S128" s="15" t="n"/>
       <c r="T128" s="15" t="n"/>
       <c r="U128" s="15" t="n"/>
-      <c r="V128" s="15" t="n"/>
-      <c r="W128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
@@ -14766,8 +14338,6 @@
       <c r="S129" s="15" t="n"/>
       <c r="T129" s="15" t="n"/>
       <c r="U129" s="15" t="n"/>
-      <c r="V129" s="15" t="n"/>
-      <c r="W129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
@@ -14816,8 +14386,6 @@
       <c r="S130" s="15" t="n"/>
       <c r="T130" s="15" t="n"/>
       <c r="U130" s="15" t="n"/>
-      <c r="V130" s="15" t="n"/>
-      <c r="W130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -14866,8 +14434,6 @@
       <c r="S131" s="15" t="n"/>
       <c r="T131" s="15" t="n"/>
       <c r="U131" s="15" t="n"/>
-      <c r="V131" s="15" t="n"/>
-      <c r="W131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
@@ -14916,8 +14482,6 @@
       <c r="S132" s="15" t="n"/>
       <c r="T132" s="15" t="n"/>
       <c r="U132" s="15" t="n"/>
-      <c r="V132" s="15" t="n"/>
-      <c r="W132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
@@ -14966,8 +14530,6 @@
       <c r="S133" s="15" t="n"/>
       <c r="T133" s="15" t="n"/>
       <c r="U133" s="15" t="n"/>
-      <c r="V133" s="15" t="n"/>
-      <c r="W133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
@@ -15016,8 +14578,6 @@
       <c r="S134" s="15" t="n"/>
       <c r="T134" s="15" t="n"/>
       <c r="U134" s="15" t="n"/>
-      <c r="V134" s="15" t="n"/>
-      <c r="W134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -15066,8 +14626,6 @@
       <c r="S135" s="15" t="n"/>
       <c r="T135" s="15" t="n"/>
       <c r="U135" s="15" t="n"/>
-      <c r="V135" s="15" t="n"/>
-      <c r="W135" s="15" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
@@ -15116,8 +14674,6 @@
       <c r="S136" s="15" t="n"/>
       <c r="T136" s="15" t="n"/>
       <c r="U136" s="15" t="n"/>
-      <c r="V136" s="15" t="n"/>
-      <c r="W136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -15166,8 +14722,6 @@
       <c r="S137" s="15" t="n"/>
       <c r="T137" s="15" t="n"/>
       <c r="U137" s="15" t="n"/>
-      <c r="V137" s="15" t="n"/>
-      <c r="W137" s="15" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -15216,8 +14770,6 @@
       <c r="S138" s="15" t="n"/>
       <c r="T138" s="15" t="n"/>
       <c r="U138" s="15" t="n"/>
-      <c r="V138" s="15" t="n"/>
-      <c r="W138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -15266,8 +14818,6 @@
       <c r="S139" s="15" t="n"/>
       <c r="T139" s="15" t="n"/>
       <c r="U139" s="15" t="n"/>
-      <c r="V139" s="15" t="n"/>
-      <c r="W139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -15304,12 +14854,12 @@
       </c>
       <c r="H140" s="15" t="n"/>
       <c r="I140" s="15" t="n"/>
-      <c r="J140" s="15" t="n"/>
-      <c r="K140" s="15" t="inlineStr">
+      <c r="J140" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K140" s="15" t="n"/>
       <c r="L140" s="15" t="n"/>
       <c r="M140" s="15" t="n"/>
       <c r="N140" s="15" t="n"/>
@@ -15320,8 +14870,6 @@
       <c r="S140" s="15" t="n"/>
       <c r="T140" s="15" t="n"/>
       <c r="U140" s="15" t="n"/>
-      <c r="V140" s="15" t="n"/>
-      <c r="W140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
@@ -15370,8 +14918,6 @@
       <c r="S141" s="15" t="n"/>
       <c r="T141" s="15" t="n"/>
       <c r="U141" s="15" t="n"/>
-      <c r="V141" s="15" t="n"/>
-      <c r="W141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
@@ -15408,12 +14954,12 @@
       </c>
       <c r="H142" s="15" t="n"/>
       <c r="I142" s="15" t="n"/>
-      <c r="J142" s="15" t="n"/>
-      <c r="K142" s="15" t="inlineStr">
+      <c r="J142" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K142" s="15" t="n"/>
       <c r="L142" s="15" t="n"/>
       <c r="M142" s="15" t="n"/>
       <c r="N142" s="15" t="n"/>
@@ -15424,8 +14970,6 @@
       <c r="S142" s="15" t="n"/>
       <c r="T142" s="15" t="n"/>
       <c r="U142" s="15" t="n"/>
-      <c r="V142" s="15" t="n"/>
-      <c r="W142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -15462,12 +15006,12 @@
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="15" t="n"/>
-      <c r="J143" s="15" t="n"/>
-      <c r="K143" s="15" t="inlineStr">
+      <c r="J143" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K143" s="15" t="n"/>
       <c r="L143" s="15" t="n"/>
       <c r="M143" s="15" t="n"/>
       <c r="N143" s="15" t="n"/>
@@ -15478,8 +15022,6 @@
       <c r="S143" s="15" t="n"/>
       <c r="T143" s="15" t="n"/>
       <c r="U143" s="15" t="n"/>
-      <c r="V143" s="15" t="n"/>
-      <c r="W143" s="15" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -15516,12 +15058,12 @@
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="15" t="n"/>
-      <c r="J144" s="15" t="n"/>
-      <c r="K144" s="15" t="inlineStr">
+      <c r="J144" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K144" s="15" t="n"/>
       <c r="L144" s="15" t="n"/>
       <c r="M144" s="15" t="n"/>
       <c r="N144" s="15" t="n"/>
@@ -15532,8 +15074,6 @@
       <c r="S144" s="15" t="n"/>
       <c r="T144" s="15" t="n"/>
       <c r="U144" s="15" t="n"/>
-      <c r="V144" s="15" t="n"/>
-      <c r="W144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -15570,12 +15110,12 @@
       </c>
       <c r="H145" s="15" t="n"/>
       <c r="I145" s="15" t="n"/>
-      <c r="J145" s="15" t="n"/>
-      <c r="K145" s="15" t="inlineStr">
+      <c r="J145" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K145" s="15" t="n"/>
       <c r="L145" s="15" t="n"/>
       <c r="M145" s="15" t="n"/>
       <c r="N145" s="15" t="n"/>
@@ -15586,8 +15126,6 @@
       <c r="S145" s="15" t="n"/>
       <c r="T145" s="15" t="n"/>
       <c r="U145" s="15" t="n"/>
-      <c r="V145" s="15" t="n"/>
-      <c r="W145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
@@ -15636,8 +15174,6 @@
       <c r="S146" s="15" t="n"/>
       <c r="T146" s="15" t="n"/>
       <c r="U146" s="15" t="n"/>
-      <c r="V146" s="15" t="n"/>
-      <c r="W146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -15686,8 +15222,6 @@
       <c r="S147" s="15" t="n"/>
       <c r="T147" s="15" t="n"/>
       <c r="U147" s="15" t="n"/>
-      <c r="V147" s="15" t="n"/>
-      <c r="W147" s="15" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -15724,12 +15258,12 @@
       </c>
       <c r="H148" s="15" t="n"/>
       <c r="I148" s="15" t="n"/>
-      <c r="J148" s="15" t="n"/>
-      <c r="K148" s="15" t="inlineStr">
+      <c r="J148" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K148" s="15" t="n"/>
       <c r="L148" s="15" t="n"/>
       <c r="M148" s="15" t="n"/>
       <c r="N148" s="15" t="n"/>
@@ -15740,8 +15274,6 @@
       <c r="S148" s="15" t="n"/>
       <c r="T148" s="15" t="n"/>
       <c r="U148" s="15" t="n"/>
-      <c r="V148" s="15" t="n"/>
-      <c r="W148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -15790,8 +15322,6 @@
       <c r="S149" s="15" t="n"/>
       <c r="T149" s="15" t="n"/>
       <c r="U149" s="15" t="n"/>
-      <c r="V149" s="15" t="n"/>
-      <c r="W149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
@@ -15840,8 +15370,6 @@
       <c r="S150" s="15" t="n"/>
       <c r="T150" s="15" t="n"/>
       <c r="U150" s="15" t="n"/>
-      <c r="V150" s="15" t="n"/>
-      <c r="W150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -15890,8 +15418,6 @@
       <c r="S151" s="15" t="n"/>
       <c r="T151" s="15" t="n"/>
       <c r="U151" s="15" t="n"/>
-      <c r="V151" s="15" t="n"/>
-      <c r="W151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -15940,8 +15466,6 @@
       <c r="S152" s="15" t="n"/>
       <c r="T152" s="15" t="n"/>
       <c r="U152" s="15" t="n"/>
-      <c r="V152" s="15" t="n"/>
-      <c r="W152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -15990,8 +15514,6 @@
       <c r="S153" s="15" t="n"/>
       <c r="T153" s="15" t="n"/>
       <c r="U153" s="15" t="n"/>
-      <c r="V153" s="15" t="n"/>
-      <c r="W153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
@@ -16040,8 +15562,6 @@
       <c r="S154" s="15" t="n"/>
       <c r="T154" s="15" t="n"/>
       <c r="U154" s="15" t="n"/>
-      <c r="V154" s="15" t="n"/>
-      <c r="W154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
@@ -16078,12 +15598,12 @@
       </c>
       <c r="H155" s="15" t="n"/>
       <c r="I155" s="15" t="n"/>
-      <c r="J155" s="15" t="n"/>
-      <c r="K155" s="15" t="inlineStr">
+      <c r="J155" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K155" s="15" t="n"/>
       <c r="L155" s="15" t="n"/>
       <c r="M155" s="15" t="n"/>
       <c r="N155" s="15" t="n"/>
@@ -16094,8 +15614,6 @@
       <c r="S155" s="15" t="n"/>
       <c r="T155" s="15" t="n"/>
       <c r="U155" s="15" t="n"/>
-      <c r="V155" s="15" t="n"/>
-      <c r="W155" s="15" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
@@ -16144,8 +15662,6 @@
       <c r="S156" s="15" t="n"/>
       <c r="T156" s="15" t="n"/>
       <c r="U156" s="15" t="n"/>
-      <c r="V156" s="15" t="n"/>
-      <c r="W156" s="15" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
@@ -16194,8 +15710,6 @@
       <c r="S157" s="15" t="n"/>
       <c r="T157" s="15" t="n"/>
       <c r="U157" s="15" t="n"/>
-      <c r="V157" s="15" t="n"/>
-      <c r="W157" s="15" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="inlineStr">
@@ -16232,12 +15746,12 @@
       </c>
       <c r="H158" s="15" t="n"/>
       <c r="I158" s="15" t="n"/>
-      <c r="J158" s="15" t="n"/>
-      <c r="K158" s="15" t="inlineStr">
+      <c r="J158" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K158" s="15" t="n"/>
       <c r="L158" s="15" t="n"/>
       <c r="M158" s="15" t="n"/>
       <c r="N158" s="15" t="n"/>
@@ -16248,8 +15762,6 @@
       <c r="S158" s="15" t="n"/>
       <c r="T158" s="15" t="n"/>
       <c r="U158" s="15" t="n"/>
-      <c r="V158" s="15" t="n"/>
-      <c r="W158" s="15" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
@@ -16294,8 +15806,6 @@
       <c r="S159" s="15" t="n"/>
       <c r="T159" s="15" t="n"/>
       <c r="U159" s="15" t="n"/>
-      <c r="V159" s="15" t="n"/>
-      <c r="W159" s="15" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
@@ -16344,8 +15854,6 @@
       <c r="S160" s="15" t="n"/>
       <c r="T160" s="15" t="n"/>
       <c r="U160" s="15" t="n"/>
-      <c r="V160" s="15" t="n"/>
-      <c r="W160" s="15" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
@@ -16382,12 +15890,12 @@
       </c>
       <c r="H161" s="15" t="n"/>
       <c r="I161" s="15" t="n"/>
-      <c r="J161" s="15" t="n"/>
-      <c r="K161" s="15" t="inlineStr">
+      <c r="J161" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K161" s="15" t="n"/>
       <c r="L161" s="15" t="n"/>
       <c r="M161" s="15" t="n"/>
       <c r="N161" s="15" t="n"/>
@@ -16398,8 +15906,6 @@
       <c r="S161" s="15" t="n"/>
       <c r="T161" s="15" t="n"/>
       <c r="U161" s="15" t="n"/>
-      <c r="V161" s="15" t="n"/>
-      <c r="W161" s="15" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="inlineStr">
@@ -16436,12 +15942,12 @@
       </c>
       <c r="H162" s="15" t="n"/>
       <c r="I162" s="15" t="n"/>
-      <c r="J162" s="15" t="n"/>
-      <c r="K162" s="15" t="inlineStr">
+      <c r="J162" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K162" s="15" t="n"/>
       <c r="L162" s="15" t="n"/>
       <c r="M162" s="15" t="n"/>
       <c r="N162" s="15" t="n"/>
@@ -16452,8 +15958,6 @@
       <c r="S162" s="15" t="n"/>
       <c r="T162" s="15" t="n"/>
       <c r="U162" s="15" t="n"/>
-      <c r="V162" s="15" t="n"/>
-      <c r="W162" s="15" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
@@ -16502,8 +16006,6 @@
       <c r="S163" s="15" t="n"/>
       <c r="T163" s="15" t="n"/>
       <c r="U163" s="15" t="n"/>
-      <c r="V163" s="15" t="n"/>
-      <c r="W163" s="15" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
@@ -16552,8 +16054,6 @@
       <c r="S164" s="15" t="n"/>
       <c r="T164" s="15" t="n"/>
       <c r="U164" s="15" t="n"/>
-      <c r="V164" s="15" t="n"/>
-      <c r="W164" s="15" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
@@ -16590,12 +16090,12 @@
       </c>
       <c r="H165" s="15" t="n"/>
       <c r="I165" s="15" t="n"/>
-      <c r="J165" s="15" t="n"/>
-      <c r="K165" s="15" t="inlineStr">
+      <c r="J165" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K165" s="15" t="n"/>
       <c r="L165" s="15" t="n"/>
       <c r="M165" s="15" t="n"/>
       <c r="N165" s="15" t="n"/>
@@ -16606,8 +16106,6 @@
       <c r="S165" s="15" t="n"/>
       <c r="T165" s="15" t="n"/>
       <c r="U165" s="15" t="n"/>
-      <c r="V165" s="15" t="n"/>
-      <c r="W165" s="15" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
@@ -16652,8 +16150,6 @@
       <c r="S166" s="15" t="n"/>
       <c r="T166" s="15" t="n"/>
       <c r="U166" s="15" t="n"/>
-      <c r="V166" s="15" t="n"/>
-      <c r="W166" s="15" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
@@ -16702,8 +16198,6 @@
       <c r="S167" s="15" t="n"/>
       <c r="T167" s="15" t="n"/>
       <c r="U167" s="15" t="n"/>
-      <c r="V167" s="15" t="n"/>
-      <c r="W167" s="15" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -16740,12 +16234,12 @@
       </c>
       <c r="H168" s="15" t="n"/>
       <c r="I168" s="15" t="n"/>
-      <c r="J168" s="15" t="n"/>
-      <c r="K168" s="15" t="inlineStr">
+      <c r="J168" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K168" s="15" t="n"/>
       <c r="L168" s="15" t="n"/>
       <c r="M168" s="15" t="n"/>
       <c r="N168" s="15" t="n"/>
@@ -16756,8 +16250,6 @@
       <c r="S168" s="15" t="n"/>
       <c r="T168" s="15" t="n"/>
       <c r="U168" s="15" t="n"/>
-      <c r="V168" s="15" t="n"/>
-      <c r="W168" s="15" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
@@ -16806,8 +16298,6 @@
       <c r="S169" s="15" t="n"/>
       <c r="T169" s="15" t="n"/>
       <c r="U169" s="15" t="n"/>
-      <c r="V169" s="15" t="n"/>
-      <c r="W169" s="15" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -16856,8 +16346,6 @@
       <c r="S170" s="15" t="n"/>
       <c r="T170" s="15" t="n"/>
       <c r="U170" s="15" t="n"/>
-      <c r="V170" s="15" t="n"/>
-      <c r="W170" s="15" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
@@ -16894,12 +16382,12 @@
       </c>
       <c r="H171" s="15" t="n"/>
       <c r="I171" s="15" t="n"/>
-      <c r="J171" s="15" t="n"/>
-      <c r="K171" s="15" t="inlineStr">
+      <c r="J171" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K171" s="15" t="n"/>
       <c r="L171" s="15" t="n"/>
       <c r="M171" s="15" t="n"/>
       <c r="N171" s="15" t="n"/>
@@ -16910,8 +16398,6 @@
       <c r="S171" s="15" t="n"/>
       <c r="T171" s="15" t="n"/>
       <c r="U171" s="15" t="n"/>
-      <c r="V171" s="15" t="n"/>
-      <c r="W171" s="15" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -16956,8 +16442,6 @@
       <c r="S172" s="15" t="n"/>
       <c r="T172" s="15" t="n"/>
       <c r="U172" s="15" t="n"/>
-      <c r="V172" s="15" t="n"/>
-      <c r="W172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -17006,8 +16490,6 @@
       <c r="S173" s="15" t="n"/>
       <c r="T173" s="15" t="n"/>
       <c r="U173" s="15" t="n"/>
-      <c r="V173" s="15" t="n"/>
-      <c r="W173" s="15" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
@@ -17044,12 +16526,12 @@
       </c>
       <c r="H174" s="15" t="n"/>
       <c r="I174" s="15" t="n"/>
-      <c r="J174" s="15" t="n"/>
-      <c r="K174" s="15" t="inlineStr">
+      <c r="J174" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K174" s="15" t="n"/>
       <c r="L174" s="15" t="n"/>
       <c r="M174" s="15" t="n"/>
       <c r="N174" s="15" t="n"/>
@@ -17060,8 +16542,6 @@
       <c r="S174" s="15" t="n"/>
       <c r="T174" s="15" t="n"/>
       <c r="U174" s="15" t="n"/>
-      <c r="V174" s="15" t="n"/>
-      <c r="W174" s="15" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -17110,8 +16590,6 @@
       <c r="S175" s="15" t="n"/>
       <c r="T175" s="15" t="n"/>
       <c r="U175" s="15" t="n"/>
-      <c r="V175" s="15" t="n"/>
-      <c r="W175" s="15" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
@@ -17156,8 +16634,6 @@
       <c r="S176" s="15" t="n"/>
       <c r="T176" s="15" t="n"/>
       <c r="U176" s="15" t="n"/>
-      <c r="V176" s="15" t="n"/>
-      <c r="W176" s="15" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -17206,8 +16682,6 @@
       <c r="S177" s="15" t="n"/>
       <c r="T177" s="15" t="n"/>
       <c r="U177" s="15" t="n"/>
-      <c r="V177" s="15" t="n"/>
-      <c r="W177" s="15" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -17244,12 +16718,12 @@
       </c>
       <c r="H178" s="15" t="n"/>
       <c r="I178" s="15" t="n"/>
-      <c r="J178" s="15" t="n"/>
-      <c r="K178" s="15" t="inlineStr">
+      <c r="J178" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K178" s="15" t="n"/>
       <c r="L178" s="15" t="n"/>
       <c r="M178" s="15" t="n"/>
       <c r="N178" s="15" t="n"/>
@@ -17260,8 +16734,6 @@
       <c r="S178" s="15" t="n"/>
       <c r="T178" s="15" t="n"/>
       <c r="U178" s="15" t="n"/>
-      <c r="V178" s="15" t="n"/>
-      <c r="W178" s="15" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -17298,12 +16770,12 @@
       </c>
       <c r="H179" s="15" t="n"/>
       <c r="I179" s="15" t="n"/>
-      <c r="J179" s="15" t="n"/>
-      <c r="K179" s="15" t="inlineStr">
+      <c r="J179" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K179" s="15" t="n"/>
       <c r="L179" s="15" t="n"/>
       <c r="M179" s="15" t="n"/>
       <c r="N179" s="15" t="n"/>
@@ -17314,8 +16786,6 @@
       <c r="S179" s="15" t="n"/>
       <c r="T179" s="15" t="n"/>
       <c r="U179" s="15" t="n"/>
-      <c r="V179" s="15" t="n"/>
-      <c r="W179" s="15" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="inlineStr">
@@ -17364,8 +16834,6 @@
       <c r="S180" s="15" t="n"/>
       <c r="T180" s="15" t="n"/>
       <c r="U180" s="15" t="n"/>
-      <c r="V180" s="15" t="n"/>
-      <c r="W180" s="15" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
@@ -17414,8 +16882,6 @@
       <c r="S181" s="15" t="n"/>
       <c r="T181" s="15" t="n"/>
       <c r="U181" s="15" t="n"/>
-      <c r="V181" s="15" t="n"/>
-      <c r="W181" s="15" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
@@ -17464,8 +16930,6 @@
       <c r="S182" s="15" t="n"/>
       <c r="T182" s="15" t="n"/>
       <c r="U182" s="15" t="n"/>
-      <c r="V182" s="15" t="n"/>
-      <c r="W182" s="15" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
@@ -17514,8 +16978,6 @@
       <c r="S183" s="15" t="n"/>
       <c r="T183" s="15" t="n"/>
       <c r="U183" s="15" t="n"/>
-      <c r="V183" s="15" t="n"/>
-      <c r="W183" s="15" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
@@ -17564,8 +17026,6 @@
       <c r="S184" s="15" t="n"/>
       <c r="T184" s="15" t="n"/>
       <c r="U184" s="15" t="n"/>
-      <c r="V184" s="15" t="n"/>
-      <c r="W184" s="15" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
@@ -17614,8 +17074,6 @@
       <c r="S185" s="15" t="n"/>
       <c r="T185" s="15" t="n"/>
       <c r="U185" s="15" t="n"/>
-      <c r="V185" s="15" t="n"/>
-      <c r="W185" s="15" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
@@ -17664,8 +17122,6 @@
       <c r="S186" s="15" t="n"/>
       <c r="T186" s="15" t="n"/>
       <c r="U186" s="15" t="n"/>
-      <c r="V186" s="15" t="n"/>
-      <c r="W186" s="15" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
@@ -17714,8 +17170,6 @@
       <c r="S187" s="15" t="n"/>
       <c r="T187" s="15" t="n"/>
       <c r="U187" s="15" t="n"/>
-      <c r="V187" s="15" t="n"/>
-      <c r="W187" s="15" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -17764,8 +17218,6 @@
       <c r="S188" s="15" t="n"/>
       <c r="T188" s="15" t="n"/>
       <c r="U188" s="15" t="n"/>
-      <c r="V188" s="15" t="n"/>
-      <c r="W188" s="15" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -17814,8 +17266,6 @@
       <c r="S189" s="15" t="n"/>
       <c r="T189" s="15" t="n"/>
       <c r="U189" s="15" t="n"/>
-      <c r="V189" s="15" t="n"/>
-      <c r="W189" s="15" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
@@ -17852,12 +17302,12 @@
       </c>
       <c r="H190" s="15" t="n"/>
       <c r="I190" s="15" t="n"/>
-      <c r="J190" s="15" t="n"/>
-      <c r="K190" s="15" t="inlineStr">
+      <c r="J190" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K190" s="15" t="n"/>
       <c r="L190" s="15" t="n"/>
       <c r="M190" s="15" t="n"/>
       <c r="N190" s="15" t="n"/>
@@ -17868,8 +17318,6 @@
       <c r="S190" s="15" t="n"/>
       <c r="T190" s="15" t="n"/>
       <c r="U190" s="15" t="n"/>
-      <c r="V190" s="15" t="n"/>
-      <c r="W190" s="15" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -17918,8 +17366,6 @@
       <c r="S191" s="15" t="n"/>
       <c r="T191" s="15" t="n"/>
       <c r="U191" s="15" t="n"/>
-      <c r="V191" s="15" t="n"/>
-      <c r="W191" s="15" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -17968,8 +17414,6 @@
       <c r="S192" s="15" t="n"/>
       <c r="T192" s="15" t="n"/>
       <c r="U192" s="15" t="n"/>
-      <c r="V192" s="15" t="n"/>
-      <c r="W192" s="15" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -18018,8 +17462,6 @@
       <c r="S193" s="15" t="n"/>
       <c r="T193" s="15" t="n"/>
       <c r="U193" s="15" t="n"/>
-      <c r="V193" s="15" t="n"/>
-      <c r="W193" s="15" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -18056,12 +17498,12 @@
       </c>
       <c r="H194" s="15" t="n"/>
       <c r="I194" s="15" t="n"/>
-      <c r="J194" s="15" t="n"/>
-      <c r="K194" s="15" t="inlineStr">
+      <c r="J194" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K194" s="15" t="n"/>
       <c r="L194" s="15" t="n"/>
       <c r="M194" s="15" t="n"/>
       <c r="N194" s="15" t="n"/>
@@ -18072,8 +17514,6 @@
       <c r="S194" s="15" t="n"/>
       <c r="T194" s="15" t="n"/>
       <c r="U194" s="15" t="n"/>
-      <c r="V194" s="15" t="n"/>
-      <c r="W194" s="15" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
@@ -18122,8 +17562,6 @@
       <c r="S195" s="15" t="n"/>
       <c r="T195" s="15" t="n"/>
       <c r="U195" s="15" t="n"/>
-      <c r="V195" s="15" t="n"/>
-      <c r="W195" s="15" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
@@ -18172,8 +17610,6 @@
       <c r="S196" s="15" t="n"/>
       <c r="T196" s="15" t="n"/>
       <c r="U196" s="15" t="n"/>
-      <c r="V196" s="15" t="n"/>
-      <c r="W196" s="15" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
@@ -18222,8 +17658,6 @@
       <c r="S197" s="15" t="n"/>
       <c r="T197" s="15" t="n"/>
       <c r="U197" s="15" t="n"/>
-      <c r="V197" s="15" t="n"/>
-      <c r="W197" s="15" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
@@ -18260,12 +17694,12 @@
       </c>
       <c r="H198" s="15" t="n"/>
       <c r="I198" s="15" t="n"/>
-      <c r="J198" s="15" t="n"/>
-      <c r="K198" s="15" t="inlineStr">
+      <c r="J198" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K198" s="15" t="n"/>
       <c r="L198" s="15" t="n"/>
       <c r="M198" s="15" t="n"/>
       <c r="N198" s="15" t="n"/>
@@ -18276,8 +17710,6 @@
       <c r="S198" s="15" t="n"/>
       <c r="T198" s="15" t="n"/>
       <c r="U198" s="15" t="n"/>
-      <c r="V198" s="15" t="n"/>
-      <c r="W198" s="15" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
@@ -18314,12 +17746,12 @@
       </c>
       <c r="H199" s="15" t="n"/>
       <c r="I199" s="15" t="n"/>
-      <c r="J199" s="15" t="n"/>
-      <c r="K199" s="15" t="inlineStr">
+      <c r="J199" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K199" s="15" t="n"/>
       <c r="L199" s="15" t="n"/>
       <c r="M199" s="15" t="n"/>
       <c r="N199" s="15" t="n"/>
@@ -18330,8 +17762,6 @@
       <c r="S199" s="15" t="n"/>
       <c r="T199" s="15" t="n"/>
       <c r="U199" s="15" t="n"/>
-      <c r="V199" s="15" t="n"/>
-      <c r="W199" s="15" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
@@ -18380,8 +17810,6 @@
       <c r="S200" s="15" t="n"/>
       <c r="T200" s="15" t="n"/>
       <c r="U200" s="15" t="n"/>
-      <c r="V200" s="15" t="n"/>
-      <c r="W200" s="15" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
@@ -18430,8 +17858,6 @@
       <c r="S201" s="15" t="n"/>
       <c r="T201" s="15" t="n"/>
       <c r="U201" s="15" t="n"/>
-      <c r="V201" s="15" t="n"/>
-      <c r="W201" s="15" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
@@ -18476,8 +17902,6 @@
       <c r="S202" s="15" t="n"/>
       <c r="T202" s="15" t="n"/>
       <c r="U202" s="15" t="n"/>
-      <c r="V202" s="15" t="n"/>
-      <c r="W202" s="15" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
@@ -18526,8 +17950,6 @@
       <c r="S203" s="15" t="n"/>
       <c r="T203" s="15" t="n"/>
       <c r="U203" s="15" t="n"/>
-      <c r="V203" s="15" t="n"/>
-      <c r="W203" s="15" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
@@ -18576,8 +17998,6 @@
       <c r="S204" s="15" t="n"/>
       <c r="T204" s="15" t="n"/>
       <c r="U204" s="15" t="n"/>
-      <c r="V204" s="15" t="n"/>
-      <c r="W204" s="15" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
@@ -18626,8 +18046,6 @@
       <c r="S205" s="15" t="n"/>
       <c r="T205" s="15" t="n"/>
       <c r="U205" s="15" t="n"/>
-      <c r="V205" s="15" t="n"/>
-      <c r="W205" s="15" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -18676,8 +18094,6 @@
       <c r="S206" s="15" t="n"/>
       <c r="T206" s="15" t="n"/>
       <c r="U206" s="15" t="n"/>
-      <c r="V206" s="15" t="n"/>
-      <c r="W206" s="15" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -18726,8 +18142,6 @@
       <c r="S207" s="15" t="n"/>
       <c r="T207" s="15" t="n"/>
       <c r="U207" s="15" t="n"/>
-      <c r="V207" s="15" t="n"/>
-      <c r="W207" s="15" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -18776,8 +18190,6 @@
       <c r="S208" s="15" t="n"/>
       <c r="T208" s="15" t="n"/>
       <c r="U208" s="15" t="n"/>
-      <c r="V208" s="15" t="n"/>
-      <c r="W208" s="15" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -18822,8 +18234,6 @@
       <c r="S209" s="15" t="n"/>
       <c r="T209" s="15" t="n"/>
       <c r="U209" s="15" t="n"/>
-      <c r="V209" s="15" t="n"/>
-      <c r="W209" s="15" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
@@ -18872,8 +18282,6 @@
       <c r="S210" s="15" t="n"/>
       <c r="T210" s="15" t="n"/>
       <c r="U210" s="15" t="n"/>
-      <c r="V210" s="15" t="n"/>
-      <c r="W210" s="15" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
@@ -18922,8 +18330,6 @@
       <c r="S211" s="15" t="n"/>
       <c r="T211" s="15" t="n"/>
       <c r="U211" s="15" t="n"/>
-      <c r="V211" s="15" t="n"/>
-      <c r="W211" s="15" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
@@ -18972,8 +18378,6 @@
       <c r="S212" s="15" t="n"/>
       <c r="T212" s="15" t="n"/>
       <c r="U212" s="15" t="n"/>
-      <c r="V212" s="15" t="n"/>
-      <c r="W212" s="15" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -19022,8 +18426,6 @@
       <c r="S213" s="15" t="n"/>
       <c r="T213" s="15" t="n"/>
       <c r="U213" s="15" t="n"/>
-      <c r="V213" s="15" t="n"/>
-      <c r="W213" s="15" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -19068,8 +18470,6 @@
       <c r="S214" s="15" t="n"/>
       <c r="T214" s="15" t="n"/>
       <c r="U214" s="15" t="n"/>
-      <c r="V214" s="15" t="n"/>
-      <c r="W214" s="15" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
@@ -19118,8 +18518,6 @@
       <c r="S215" s="15" t="n"/>
       <c r="T215" s="15" t="n"/>
       <c r="U215" s="15" t="n"/>
-      <c r="V215" s="15" t="n"/>
-      <c r="W215" s="15" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
@@ -19168,8 +18566,6 @@
       <c r="S216" s="15" t="n"/>
       <c r="T216" s="15" t="n"/>
       <c r="U216" s="15" t="n"/>
-      <c r="V216" s="15" t="n"/>
-      <c r="W216" s="15" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -19218,8 +18614,6 @@
       <c r="S217" s="15" t="n"/>
       <c r="T217" s="15" t="n"/>
       <c r="U217" s="15" t="n"/>
-      <c r="V217" s="15" t="n"/>
-      <c r="W217" s="15" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
@@ -19268,8 +18662,6 @@
       <c r="S218" s="15" t="n"/>
       <c r="T218" s="15" t="n"/>
       <c r="U218" s="15" t="n"/>
-      <c r="V218" s="15" t="n"/>
-      <c r="W218" s="15" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
@@ -19318,8 +18710,6 @@
       <c r="S219" s="15" t="n"/>
       <c r="T219" s="15" t="n"/>
       <c r="U219" s="15" t="n"/>
-      <c r="V219" s="15" t="n"/>
-      <c r="W219" s="15" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
@@ -19368,8 +18758,6 @@
       <c r="S220" s="15" t="n"/>
       <c r="T220" s="15" t="n"/>
       <c r="U220" s="15" t="n"/>
-      <c r="V220" s="15" t="n"/>
-      <c r="W220" s="15" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
@@ -19418,8 +18806,6 @@
       <c r="S221" s="15" t="n"/>
       <c r="T221" s="15" t="n"/>
       <c r="U221" s="15" t="n"/>
-      <c r="V221" s="15" t="n"/>
-      <c r="W221" s="15" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
@@ -19468,8 +18854,6 @@
       <c r="S222" s="15" t="n"/>
       <c r="T222" s="15" t="n"/>
       <c r="U222" s="15" t="n"/>
-      <c r="V222" s="15" t="n"/>
-      <c r="W222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
@@ -19518,8 +18902,6 @@
       <c r="S223" s="15" t="n"/>
       <c r="T223" s="15" t="n"/>
       <c r="U223" s="15" t="n"/>
-      <c r="V223" s="15" t="n"/>
-      <c r="W223" s="15" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
@@ -19568,8 +18950,6 @@
       <c r="S224" s="15" t="n"/>
       <c r="T224" s="15" t="n"/>
       <c r="U224" s="15" t="n"/>
-      <c r="V224" s="15" t="n"/>
-      <c r="W224" s="15" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
@@ -19618,8 +18998,6 @@
       <c r="S225" s="15" t="n"/>
       <c r="T225" s="15" t="n"/>
       <c r="U225" s="15" t="n"/>
-      <c r="V225" s="15" t="n"/>
-      <c r="W225" s="15" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
@@ -19664,8 +19042,6 @@
       <c r="S226" s="15" t="n"/>
       <c r="T226" s="15" t="n"/>
       <c r="U226" s="15" t="n"/>
-      <c r="V226" s="15" t="n"/>
-      <c r="W226" s="15" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
@@ -19714,8 +19090,6 @@
       <c r="S227" s="15" t="n"/>
       <c r="T227" s="15" t="n"/>
       <c r="U227" s="15" t="n"/>
-      <c r="V227" s="15" t="n"/>
-      <c r="W227" s="15" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
@@ -19764,8 +19138,6 @@
       <c r="S228" s="15" t="n"/>
       <c r="T228" s="15" t="n"/>
       <c r="U228" s="15" t="n"/>
-      <c r="V228" s="15" t="n"/>
-      <c r="W228" s="15" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="inlineStr">
@@ -19814,8 +19186,6 @@
       <c r="S229" s="15" t="n"/>
       <c r="T229" s="15" t="n"/>
       <c r="U229" s="15" t="n"/>
-      <c r="V229" s="15" t="n"/>
-      <c r="W229" s="15" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
@@ -19864,8 +19234,6 @@
       <c r="S230" s="15" t="n"/>
       <c r="T230" s="15" t="n"/>
       <c r="U230" s="15" t="n"/>
-      <c r="V230" s="15" t="n"/>
-      <c r="W230" s="15" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
@@ -19914,8 +19282,6 @@
       <c r="S231" s="15" t="n"/>
       <c r="T231" s="15" t="n"/>
       <c r="U231" s="15" t="n"/>
-      <c r="V231" s="15" t="n"/>
-      <c r="W231" s="15" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
@@ -19964,8 +19330,6 @@
       <c r="S232" s="15" t="n"/>
       <c r="T232" s="15" t="n"/>
       <c r="U232" s="15" t="n"/>
-      <c r="V232" s="15" t="n"/>
-      <c r="W232" s="15" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="inlineStr">
@@ -20014,8 +19378,6 @@
       <c r="S233" s="15" t="n"/>
       <c r="T233" s="15" t="n"/>
       <c r="U233" s="15" t="n"/>
-      <c r="V233" s="15" t="n"/>
-      <c r="W233" s="15" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
@@ -20064,8 +19426,6 @@
       <c r="S234" s="15" t="n"/>
       <c r="T234" s="15" t="n"/>
       <c r="U234" s="15" t="n"/>
-      <c r="V234" s="15" t="n"/>
-      <c r="W234" s="15" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
@@ -20114,8 +19474,6 @@
       <c r="S235" s="15" t="n"/>
       <c r="T235" s="15" t="n"/>
       <c r="U235" s="15" t="n"/>
-      <c r="V235" s="15" t="n"/>
-      <c r="W235" s="15" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
@@ -20164,8 +19522,6 @@
       <c r="S236" s="15" t="n"/>
       <c r="T236" s="15" t="n"/>
       <c r="U236" s="15" t="n"/>
-      <c r="V236" s="15" t="n"/>
-      <c r="W236" s="15" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
@@ -20214,8 +19570,6 @@
       <c r="S237" s="15" t="n"/>
       <c r="T237" s="15" t="n"/>
       <c r="U237" s="15" t="n"/>
-      <c r="V237" s="15" t="n"/>
-      <c r="W237" s="15" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
@@ -20264,8 +19618,6 @@
       <c r="S238" s="15" t="n"/>
       <c r="T238" s="15" t="n"/>
       <c r="U238" s="15" t="n"/>
-      <c r="V238" s="15" t="n"/>
-      <c r="W238" s="15" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
@@ -20310,8 +19662,6 @@
       <c r="S239" s="15" t="n"/>
       <c r="T239" s="15" t="n"/>
       <c r="U239" s="15" t="n"/>
-      <c r="V239" s="15" t="n"/>
-      <c r="W239" s="15" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
@@ -20360,8 +19710,6 @@
       <c r="S240" s="15" t="n"/>
       <c r="T240" s="15" t="n"/>
       <c r="U240" s="15" t="n"/>
-      <c r="V240" s="15" t="n"/>
-      <c r="W240" s="15" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
@@ -20410,8 +19758,6 @@
       <c r="S241" s="15" t="n"/>
       <c r="T241" s="15" t="n"/>
       <c r="U241" s="15" t="n"/>
-      <c r="V241" s="15" t="n"/>
-      <c r="W241" s="15" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
@@ -20460,8 +19806,6 @@
       <c r="S242" s="15" t="n"/>
       <c r="T242" s="15" t="n"/>
       <c r="U242" s="15" t="n"/>
-      <c r="V242" s="15" t="n"/>
-      <c r="W242" s="15" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
@@ -20510,8 +19854,6 @@
       <c r="S243" s="15" t="n"/>
       <c r="T243" s="15" t="n"/>
       <c r="U243" s="15" t="n"/>
-      <c r="V243" s="15" t="n"/>
-      <c r="W243" s="15" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
@@ -20560,8 +19902,6 @@
       <c r="S244" s="15" t="n"/>
       <c r="T244" s="15" t="n"/>
       <c r="U244" s="15" t="n"/>
-      <c r="V244" s="15" t="n"/>
-      <c r="W244" s="15" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
@@ -20610,8 +19950,6 @@
       <c r="S245" s="15" t="n"/>
       <c r="T245" s="15" t="n"/>
       <c r="U245" s="15" t="n"/>
-      <c r="V245" s="15" t="n"/>
-      <c r="W245" s="15" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
@@ -20656,8 +19994,6 @@
       <c r="S246" s="15" t="n"/>
       <c r="T246" s="15" t="n"/>
       <c r="U246" s="15" t="n"/>
-      <c r="V246" s="15" t="n"/>
-      <c r="W246" s="15" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
@@ -20694,12 +20030,12 @@
       </c>
       <c r="H247" s="15" t="n"/>
       <c r="I247" s="15" t="n"/>
-      <c r="J247" s="15" t="n"/>
-      <c r="K247" s="15" t="inlineStr">
+      <c r="J247" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K247" s="15" t="n"/>
       <c r="L247" s="15" t="n"/>
       <c r="M247" s="15" t="n"/>
       <c r="N247" s="15" t="n"/>
@@ -20710,8 +20046,6 @@
       <c r="S247" s="15" t="n"/>
       <c r="T247" s="15" t="n"/>
       <c r="U247" s="15" t="n"/>
-      <c r="V247" s="15" t="n"/>
-      <c r="W247" s="15" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
@@ -20760,8 +20094,6 @@
       <c r="S248" s="15" t="n"/>
       <c r="T248" s="15" t="n"/>
       <c r="U248" s="15" t="n"/>
-      <c r="V248" s="15" t="n"/>
-      <c r="W248" s="15" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
@@ -20806,8 +20138,6 @@
       <c r="S249" s="15" t="n"/>
       <c r="T249" s="15" t="n"/>
       <c r="U249" s="15" t="n"/>
-      <c r="V249" s="15" t="n"/>
-      <c r="W249" s="15" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
@@ -20856,8 +20186,6 @@
       <c r="S250" s="15" t="n"/>
       <c r="T250" s="15" t="n"/>
       <c r="U250" s="15" t="n"/>
-      <c r="V250" s="15" t="n"/>
-      <c r="W250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
@@ -20906,8 +20234,6 @@
       <c r="S251" s="15" t="n"/>
       <c r="T251" s="15" t="n"/>
       <c r="U251" s="15" t="n"/>
-      <c r="V251" s="15" t="n"/>
-      <c r="W251" s="15" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
@@ -20956,8 +20282,6 @@
       <c r="S252" s="15" t="n"/>
       <c r="T252" s="15" t="n"/>
       <c r="U252" s="15" t="n"/>
-      <c r="V252" s="15" t="n"/>
-      <c r="W252" s="15" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
@@ -21006,8 +20330,6 @@
       <c r="S253" s="15" t="n"/>
       <c r="T253" s="15" t="n"/>
       <c r="U253" s="15" t="n"/>
-      <c r="V253" s="15" t="n"/>
-      <c r="W253" s="15" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="inlineStr">
@@ -21056,8 +20378,6 @@
       <c r="S254" s="15" t="n"/>
       <c r="T254" s="15" t="n"/>
       <c r="U254" s="15" t="n"/>
-      <c r="V254" s="15" t="n"/>
-      <c r="W254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
@@ -21102,8 +20422,6 @@
       <c r="S255" s="15" t="n"/>
       <c r="T255" s="15" t="n"/>
       <c r="U255" s="15" t="n"/>
-      <c r="V255" s="15" t="n"/>
-      <c r="W255" s="15" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
@@ -21152,8 +20470,6 @@
       <c r="S256" s="15" t="n"/>
       <c r="T256" s="15" t="n"/>
       <c r="U256" s="15" t="n"/>
-      <c r="V256" s="15" t="n"/>
-      <c r="W256" s="15" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
@@ -21202,8 +20518,6 @@
       <c r="S257" s="15" t="n"/>
       <c r="T257" s="15" t="n"/>
       <c r="U257" s="15" t="n"/>
-      <c r="V257" s="15" t="n"/>
-      <c r="W257" s="15" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
@@ -21248,8 +20562,6 @@
       <c r="S258" s="15" t="n"/>
       <c r="T258" s="15" t="n"/>
       <c r="U258" s="15" t="n"/>
-      <c r="V258" s="15" t="n"/>
-      <c r="W258" s="15" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
@@ -21298,8 +20610,6 @@
       <c r="S259" s="15" t="n"/>
       <c r="T259" s="15" t="n"/>
       <c r="U259" s="15" t="n"/>
-      <c r="V259" s="15" t="n"/>
-      <c r="W259" s="15" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="inlineStr">
@@ -21348,8 +20658,6 @@
       <c r="S260" s="15" t="n"/>
       <c r="T260" s="15" t="n"/>
       <c r="U260" s="15" t="n"/>
-      <c r="V260" s="15" t="n"/>
-      <c r="W260" s="15" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
@@ -21398,8 +20706,6 @@
       <c r="S261" s="15" t="n"/>
       <c r="T261" s="15" t="n"/>
       <c r="U261" s="15" t="n"/>
-      <c r="V261" s="15" t="n"/>
-      <c r="W261" s="15" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
@@ -21448,8 +20754,6 @@
       <c r="S262" s="15" t="n"/>
       <c r="T262" s="15" t="n"/>
       <c r="U262" s="15" t="n"/>
-      <c r="V262" s="15" t="n"/>
-      <c r="W262" s="15" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="inlineStr">
@@ -21498,8 +20802,6 @@
       <c r="S263" s="15" t="n"/>
       <c r="T263" s="15" t="n"/>
       <c r="U263" s="15" t="n"/>
-      <c r="V263" s="15" t="n"/>
-      <c r="W263" s="15" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
@@ -21548,8 +20850,6 @@
       <c r="S264" s="15" t="n"/>
       <c r="T264" s="15" t="n"/>
       <c r="U264" s="15" t="n"/>
-      <c r="V264" s="15" t="n"/>
-      <c r="W264" s="15" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
@@ -21598,8 +20898,6 @@
       <c r="S265" s="15" t="n"/>
       <c r="T265" s="15" t="n"/>
       <c r="U265" s="15" t="n"/>
-      <c r="V265" s="15" t="n"/>
-      <c r="W265" s="15" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
@@ -21648,8 +20946,6 @@
       <c r="S266" s="15" t="n"/>
       <c r="T266" s="15" t="n"/>
       <c r="U266" s="15" t="n"/>
-      <c r="V266" s="15" t="n"/>
-      <c r="W266" s="15" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
@@ -21698,8 +20994,6 @@
       <c r="S267" s="15" t="n"/>
       <c r="T267" s="15" t="n"/>
       <c r="U267" s="15" t="n"/>
-      <c r="V267" s="15" t="n"/>
-      <c r="W267" s="15" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
@@ -21748,8 +21042,6 @@
       <c r="S268" s="15" t="n"/>
       <c r="T268" s="15" t="n"/>
       <c r="U268" s="15" t="n"/>
-      <c r="V268" s="15" t="n"/>
-      <c r="W268" s="15" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
@@ -21798,8 +21090,6 @@
       <c r="S269" s="15" t="n"/>
       <c r="T269" s="15" t="n"/>
       <c r="U269" s="15" t="n"/>
-      <c r="V269" s="15" t="n"/>
-      <c r="W269" s="15" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
@@ -21848,8 +21138,6 @@
       <c r="S270" s="15" t="n"/>
       <c r="T270" s="15" t="n"/>
       <c r="U270" s="15" t="n"/>
-      <c r="V270" s="15" t="n"/>
-      <c r="W270" s="15" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
@@ -21898,8 +21186,6 @@
       <c r="S271" s="15" t="n"/>
       <c r="T271" s="15" t="n"/>
       <c r="U271" s="15" t="n"/>
-      <c r="V271" s="15" t="n"/>
-      <c r="W271" s="15" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
@@ -21948,8 +21234,6 @@
       <c r="S272" s="15" t="n"/>
       <c r="T272" s="15" t="n"/>
       <c r="U272" s="15" t="n"/>
-      <c r="V272" s="15" t="n"/>
-      <c r="W272" s="15" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
@@ -21998,8 +21282,6 @@
       <c r="S273" s="15" t="n"/>
       <c r="T273" s="15" t="n"/>
       <c r="U273" s="15" t="n"/>
-      <c r="V273" s="15" t="n"/>
-      <c r="W273" s="15" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="inlineStr">
@@ -22048,8 +21330,6 @@
       <c r="S274" s="15" t="n"/>
       <c r="T274" s="15" t="n"/>
       <c r="U274" s="15" t="n"/>
-      <c r="V274" s="15" t="n"/>
-      <c r="W274" s="15" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="inlineStr">
@@ -22098,8 +21378,6 @@
       <c r="S275" s="15" t="n"/>
       <c r="T275" s="15" t="n"/>
       <c r="U275" s="15" t="n"/>
-      <c r="V275" s="15" t="n"/>
-      <c r="W275" s="15" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
@@ -22148,8 +21426,6 @@
       <c r="S276" s="15" t="n"/>
       <c r="T276" s="15" t="n"/>
       <c r="U276" s="15" t="n"/>
-      <c r="V276" s="15" t="n"/>
-      <c r="W276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
@@ -22198,8 +21474,6 @@
       <c r="S277" s="15" t="n"/>
       <c r="T277" s="15" t="n"/>
       <c r="U277" s="15" t="n"/>
-      <c r="V277" s="15" t="n"/>
-      <c r="W277" s="15" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
@@ -22248,8 +21522,6 @@
       <c r="S278" s="15" t="n"/>
       <c r="T278" s="15" t="n"/>
       <c r="U278" s="15" t="n"/>
-      <c r="V278" s="15" t="n"/>
-      <c r="W278" s="15" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
@@ -22298,8 +21570,6 @@
       <c r="S279" s="15" t="n"/>
       <c r="T279" s="15" t="n"/>
       <c r="U279" s="15" t="n"/>
-      <c r="V279" s="15" t="n"/>
-      <c r="W279" s="15" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
@@ -22348,8 +21618,6 @@
       <c r="S280" s="15" t="n"/>
       <c r="T280" s="15" t="n"/>
       <c r="U280" s="15" t="n"/>
-      <c r="V280" s="15" t="n"/>
-      <c r="W280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
@@ -22398,8 +21666,6 @@
       <c r="S281" s="15" t="n"/>
       <c r="T281" s="15" t="n"/>
       <c r="U281" s="15" t="n"/>
-      <c r="V281" s="15" t="n"/>
-      <c r="W281" s="15" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
@@ -22448,8 +21714,6 @@
       <c r="S282" s="15" t="n"/>
       <c r="T282" s="15" t="n"/>
       <c r="U282" s="15" t="n"/>
-      <c r="V282" s="15" t="n"/>
-      <c r="W282" s="15" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
@@ -22498,8 +21762,6 @@
       <c r="S283" s="15" t="n"/>
       <c r="T283" s="15" t="n"/>
       <c r="U283" s="15" t="n"/>
-      <c r="V283" s="15" t="n"/>
-      <c r="W283" s="15" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
@@ -22548,8 +21810,6 @@
       <c r="S284" s="15" t="n"/>
       <c r="T284" s="15" t="n"/>
       <c r="U284" s="15" t="n"/>
-      <c r="V284" s="15" t="n"/>
-      <c r="W284" s="15" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="inlineStr">
@@ -22594,8 +21854,6 @@
       <c r="S285" s="15" t="n"/>
       <c r="T285" s="15" t="n"/>
       <c r="U285" s="15" t="n"/>
-      <c r="V285" s="15" t="n"/>
-      <c r="W285" s="15" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
@@ -22644,8 +21902,6 @@
       <c r="S286" s="15" t="n"/>
       <c r="T286" s="15" t="n"/>
       <c r="U286" s="15" t="n"/>
-      <c r="V286" s="15" t="n"/>
-      <c r="W286" s="15" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
@@ -22690,8 +21946,6 @@
       <c r="S287" s="15" t="n"/>
       <c r="T287" s="15" t="n"/>
       <c r="U287" s="15" t="n"/>
-      <c r="V287" s="15" t="n"/>
-      <c r="W287" s="15" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
@@ -22740,8 +21994,6 @@
       <c r="S288" s="15" t="n"/>
       <c r="T288" s="15" t="n"/>
       <c r="U288" s="15" t="n"/>
-      <c r="V288" s="15" t="n"/>
-      <c r="W288" s="15" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
@@ -22790,8 +22042,6 @@
       <c r="S289" s="15" t="n"/>
       <c r="T289" s="15" t="n"/>
       <c r="U289" s="15" t="n"/>
-      <c r="V289" s="15" t="n"/>
-      <c r="W289" s="15" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
@@ -22828,12 +22078,12 @@
       </c>
       <c r="H290" s="15" t="n"/>
       <c r="I290" s="15" t="n"/>
-      <c r="J290" s="15" t="n"/>
-      <c r="K290" s="15" t="inlineStr">
+      <c r="J290" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="K290" s="15" t="n"/>
       <c r="L290" s="15" t="n"/>
       <c r="M290" s="15" t="n"/>
       <c r="N290" s="15" t="n"/>
@@ -22844,8 +22094,6 @@
       <c r="S290" s="15" t="n"/>
       <c r="T290" s="15" t="n"/>
       <c r="U290" s="15" t="n"/>
-      <c r="V290" s="15" t="n"/>
-      <c r="W290" s="15" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="inlineStr">
@@ -22894,8 +22142,6 @@
       <c r="S291" s="15" t="n"/>
       <c r="T291" s="15" t="n"/>
       <c r="U291" s="15" t="n"/>
-      <c r="V291" s="15" t="n"/>
-      <c r="W291" s="15" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
@@ -22940,8 +22186,6 @@
       <c r="S292" s="15" t="n"/>
       <c r="T292" s="15" t="n"/>
       <c r="U292" s="15" t="n"/>
-      <c r="V292" s="15" t="n"/>
-      <c r="W292" s="15" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
@@ -22990,8 +22234,6 @@
       <c r="S293" s="15" t="n"/>
       <c r="T293" s="15" t="n"/>
       <c r="U293" s="15" t="n"/>
-      <c r="V293" s="15" t="n"/>
-      <c r="W293" s="15" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
@@ -23040,8 +22282,6 @@
       <c r="S294" s="15" t="n"/>
       <c r="T294" s="15" t="n"/>
       <c r="U294" s="15" t="n"/>
-      <c r="V294" s="15" t="n"/>
-      <c r="W294" s="15" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
@@ -23090,8 +22330,6 @@
       <c r="S295" s="15" t="n"/>
       <c r="T295" s="15" t="n"/>
       <c r="U295" s="15" t="n"/>
-      <c r="V295" s="15" t="n"/>
-      <c r="W295" s="15" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
@@ -23140,8 +22378,6 @@
       <c r="S296" s="15" t="n"/>
       <c r="T296" s="15" t="n"/>
       <c r="U296" s="15" t="n"/>
-      <c r="V296" s="15" t="n"/>
-      <c r="W296" s="15" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="inlineStr">
@@ -23190,8 +22426,6 @@
       <c r="S297" s="15" t="n"/>
       <c r="T297" s="15" t="n"/>
       <c r="U297" s="15" t="n"/>
-      <c r="V297" s="15" t="n"/>
-      <c r="W297" s="15" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
@@ -23240,8 +22474,6 @@
       <c r="S298" s="15" t="n"/>
       <c r="T298" s="15" t="n"/>
       <c r="U298" s="15" t="n"/>
-      <c r="V298" s="15" t="n"/>
-      <c r="W298" s="15" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
@@ -23290,8 +22522,6 @@
       <c r="S299" s="15" t="n"/>
       <c r="T299" s="15" t="n"/>
       <c r="U299" s="15" t="n"/>
-      <c r="V299" s="15" t="n"/>
-      <c r="W299" s="15" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
@@ -23340,8 +22570,6 @@
       <c r="S300" s="15" t="n"/>
       <c r="T300" s="15" t="n"/>
       <c r="U300" s="15" t="n"/>
-      <c r="V300" s="15" t="n"/>
-      <c r="W300" s="15" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
@@ -23390,8 +22618,6 @@
       <c r="S301" s="15" t="n"/>
       <c r="T301" s="15" t="n"/>
       <c r="U301" s="15" t="n"/>
-      <c r="V301" s="15" t="n"/>
-      <c r="W301" s="15" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
@@ -23428,17 +22654,17 @@
       </c>
       <c r="H302" s="15" t="n"/>
       <c r="I302" s="15" t="n"/>
-      <c r="J302" s="15" t="n"/>
+      <c r="J302" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K302" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L302" s="15" t="inlineStr">
-        <is>
           <t>Ascended Heroes - Stunfisk ex - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
+      <c r="L302" s="15" t="n"/>
       <c r="M302" s="15" t="n"/>
       <c r="N302" s="15" t="n"/>
       <c r="O302" s="15" t="n"/>
@@ -23448,8 +22674,6 @@
       <c r="S302" s="15" t="n"/>
       <c r="T302" s="15" t="n"/>
       <c r="U302" s="15" t="n"/>
-      <c r="V302" s="15" t="n"/>
-      <c r="W302" s="15" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
@@ -23482,12 +22706,12 @@
       <c r="G303" s="15" t="n"/>
       <c r="H303" s="15" t="n"/>
       <c r="I303" s="15" t="n"/>
-      <c r="J303" s="15" t="n"/>
-      <c r="K303" s="15" t="inlineStr">
+      <c r="J303" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K303" s="15" t="n"/>
       <c r="L303" s="15" t="n"/>
       <c r="M303" s="15" t="n"/>
       <c r="N303" s="15" t="n"/>
@@ -23498,8 +22722,6 @@
       <c r="S303" s="15" t="n"/>
       <c r="T303" s="15" t="n"/>
       <c r="U303" s="15" t="n"/>
-      <c r="V303" s="15" t="n"/>
-      <c r="W303" s="15" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
@@ -23532,12 +22754,12 @@
       <c r="G304" s="15" t="n"/>
       <c r="H304" s="15" t="n"/>
       <c r="I304" s="15" t="n"/>
-      <c r="J304" s="15" t="n"/>
-      <c r="K304" s="15" t="inlineStr">
+      <c r="J304" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K304" s="15" t="n"/>
       <c r="L304" s="15" t="n"/>
       <c r="M304" s="15" t="n"/>
       <c r="N304" s="15" t="n"/>
@@ -23548,8 +22770,6 @@
       <c r="S304" s="15" t="n"/>
       <c r="T304" s="15" t="n"/>
       <c r="U304" s="15" t="n"/>
-      <c r="V304" s="15" t="n"/>
-      <c r="W304" s="15" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
@@ -23586,12 +22806,12 @@
       </c>
       <c r="H305" s="15" t="n"/>
       <c r="I305" s="15" t="n"/>
-      <c r="J305" s="15" t="n"/>
-      <c r="K305" s="15" t="inlineStr">
+      <c r="J305" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K305" s="15" t="n"/>
       <c r="L305" s="15" t="n"/>
       <c r="M305" s="15" t="n"/>
       <c r="N305" s="15" t="n"/>
@@ -23602,8 +22822,6 @@
       <c r="S305" s="15" t="n"/>
       <c r="T305" s="15" t="n"/>
       <c r="U305" s="15" t="n"/>
-      <c r="V305" s="15" t="n"/>
-      <c r="W305" s="15" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
@@ -23640,12 +22858,12 @@
       </c>
       <c r="H306" s="15" t="n"/>
       <c r="I306" s="15" t="n"/>
-      <c r="J306" s="15" t="n"/>
-      <c r="K306" s="15" t="inlineStr">
+      <c r="J306" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K306" s="15" t="n"/>
       <c r="L306" s="15" t="n"/>
       <c r="M306" s="15" t="n"/>
       <c r="N306" s="15" t="n"/>
@@ -23656,8 +22874,6 @@
       <c r="S306" s="15" t="n"/>
       <c r="T306" s="15" t="n"/>
       <c r="U306" s="15" t="n"/>
-      <c r="V306" s="15" t="n"/>
-      <c r="W306" s="15" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
@@ -23694,17 +22910,17 @@
       </c>
       <c r="H307" s="15" t="n"/>
       <c r="I307" s="15" t="n"/>
-      <c r="J307" s="15" t="n"/>
+      <c r="J307" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K307" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L307" s="15" t="inlineStr">
-        <is>
           <t>Journey Together - Volcanion ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="L307" s="15" t="n"/>
       <c r="M307" s="15" t="n"/>
       <c r="N307" s="15" t="n"/>
       <c r="O307" s="15" t="n"/>
@@ -23714,8 +22930,6 @@
       <c r="S307" s="15" t="n"/>
       <c r="T307" s="15" t="n"/>
       <c r="U307" s="15" t="n"/>
-      <c r="V307" s="15" t="n"/>
-      <c r="W307" s="15" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
@@ -23752,17 +22966,17 @@
       </c>
       <c r="H308" s="15" t="n"/>
       <c r="I308" s="15" t="n"/>
-      <c r="J308" s="15" t="n"/>
+      <c r="J308" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K308" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L308" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames - Rotom ex - Double Black Star- Double Rare</t>
         </is>
       </c>
+      <c r="L308" s="15" t="n"/>
       <c r="M308" s="15" t="n"/>
       <c r="N308" s="15" t="n"/>
       <c r="O308" s="15" t="n"/>
@@ -23771,9 +22985,7 @@
       <c r="R308" s="15" t="n"/>
       <c r="S308" s="15" t="n"/>
       <c r="T308" s="15" t="n"/>
-      <c r="U308" s="15" t="n"/>
-      <c r="V308" s="15" t="n"/>
-      <c r="W308" s="15" t="inlineStr">
+      <c r="U308" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -23814,17 +23026,17 @@
       </c>
       <c r="H309" s="15" t="n"/>
       <c r="I309" s="15" t="n"/>
-      <c r="J309" s="15" t="n"/>
+      <c r="J309" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K309" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L309" s="15" t="inlineStr">
-        <is>
           <t>Journey Together - Trainer - Ruffian - Double Silver Star - Ultra Rare</t>
         </is>
       </c>
+      <c r="L309" s="15" t="n"/>
       <c r="M309" s="15" t="n"/>
       <c r="N309" s="15" t="n"/>
       <c r="O309" s="15" t="n"/>
@@ -23834,8 +23046,6 @@
       <c r="S309" s="15" t="n"/>
       <c r="T309" s="15" t="n"/>
       <c r="U309" s="15" t="n"/>
-      <c r="V309" s="15" t="n"/>
-      <c r="W309" s="15" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
@@ -23872,17 +23082,17 @@
       </c>
       <c r="H310" s="15" t="n"/>
       <c r="I310" s="15" t="n"/>
-      <c r="J310" s="15" t="n"/>
+      <c r="J310" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K310" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L310" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames - Mismagius ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="L310" s="15" t="n"/>
       <c r="M310" s="15" t="n"/>
       <c r="N310" s="15" t="n"/>
       <c r="O310" s="15" t="n"/>
@@ -23892,8 +23102,6 @@
       <c r="S310" s="15" t="n"/>
       <c r="T310" s="15" t="n"/>
       <c r="U310" s="15" t="n"/>
-      <c r="V310" s="15" t="n"/>
-      <c r="W310" s="15" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
@@ -23926,17 +23134,17 @@
       <c r="G311" s="15" t="n"/>
       <c r="H311" s="15" t="n"/>
       <c r="I311" s="15" t="n"/>
-      <c r="J311" s="15" t="n"/>
+      <c r="J311" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K311" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L311" s="15" t="inlineStr">
-        <is>
           <t>Cyber Judge - Incineroar ex - SR - Super Rare</t>
         </is>
       </c>
+      <c r="L311" s="15" t="n"/>
       <c r="M311" s="15" t="n"/>
       <c r="N311" s="15" t="n"/>
       <c r="O311" s="15" t="n"/>
@@ -23946,8 +23154,6 @@
       <c r="S311" s="15" t="n"/>
       <c r="T311" s="15" t="n"/>
       <c r="U311" s="15" t="n"/>
-      <c r="V311" s="15" t="n"/>
-      <c r="W311" s="15" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
@@ -23984,12 +23190,12 @@
       </c>
       <c r="H312" s="15" t="n"/>
       <c r="I312" s="15" t="n"/>
-      <c r="J312" s="15" t="n"/>
-      <c r="K312" s="15" t="inlineStr">
+      <c r="J312" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K312" s="15" t="n"/>
       <c r="L312" s="15" t="n"/>
       <c r="M312" s="15" t="n"/>
       <c r="N312" s="15" t="n"/>
@@ -24000,8 +23206,6 @@
       <c r="S312" s="15" t="n"/>
       <c r="T312" s="15" t="n"/>
       <c r="U312" s="15" t="n"/>
-      <c r="V312" s="15" t="n"/>
-      <c r="W312" s="15" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
@@ -24038,32 +23242,30 @@
       </c>
       <c r="H313" s="15" t="n"/>
       <c r="I313" s="15" t="n"/>
-      <c r="J313" s="15" t="n"/>
+      <c r="J313" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K313" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L313" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames - Mega Lopunny ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="L313" s="15" t="n"/>
       <c r="M313" s="15" t="n"/>
       <c r="N313" s="15" t="n"/>
-      <c r="O313" s="15" t="n"/>
+      <c r="O313" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="P313" s="15" t="n"/>
-      <c r="Q313" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Q313" s="15" t="n"/>
       <c r="R313" s="15" t="n"/>
       <c r="S313" s="15" t="n"/>
       <c r="T313" s="15" t="n"/>
       <c r="U313" s="15" t="n"/>
-      <c r="V313" s="15" t="n"/>
-      <c r="W313" s="15" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
@@ -24100,17 +23302,17 @@
       </c>
       <c r="H314" s="15" t="n"/>
       <c r="I314" s="15" t="n"/>
-      <c r="J314" s="15" t="n"/>
+      <c r="J314" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K314" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L314" s="15" t="inlineStr">
-        <is>
           <t>Surging Sparks - Feebas - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
+      <c r="L314" s="15" t="n"/>
       <c r="M314" s="15" t="n"/>
       <c r="N314" s="15" t="n"/>
       <c r="O314" s="15" t="n"/>
@@ -24119,9 +23321,7 @@
       <c r="R314" s="15" t="n"/>
       <c r="S314" s="15" t="n"/>
       <c r="T314" s="15" t="n"/>
-      <c r="U314" s="15" t="n"/>
-      <c r="V314" s="15" t="n"/>
-      <c r="W314" s="15" t="inlineStr">
+      <c r="U314" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -24162,28 +23362,26 @@
       </c>
       <c r="H315" s="15" t="n"/>
       <c r="I315" s="15" t="n"/>
-      <c r="J315" s="15" t="n"/>
-      <c r="K315" s="15" t="inlineStr">
+      <c r="J315" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
+      <c r="K315" s="15" t="n"/>
       <c r="L315" s="15" t="n"/>
       <c r="M315" s="15" t="n"/>
       <c r="N315" s="15" t="n"/>
-      <c r="O315" s="15" t="n"/>
+      <c r="O315" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="P315" s="15" t="n"/>
-      <c r="Q315" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Q315" s="15" t="n"/>
       <c r="R315" s="15" t="n"/>
       <c r="S315" s="15" t="n"/>
       <c r="T315" s="15" t="n"/>
-      <c r="U315" s="15" t="n"/>
-      <c r="V315" s="15" t="n"/>
-      <c r="W315" s="15" t="inlineStr">
+      <c r="U315" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -24227,20 +23425,20 @@
           <t>Blister Pack</t>
         </is>
       </c>
-      <c r="I316" s="15" t="n"/>
-      <c r="J316" s="15" t="n">
+      <c r="I316" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="J316" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K316" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L316" s="15" t="inlineStr">
-        <is>
           <t>Paradox Rift - Tsareena ex - Double Black Star - Double Rare</t>
         </is>
       </c>
+      <c r="L316" s="15" t="n"/>
       <c r="M316" s="15" t="n"/>
       <c r="N316" s="15" t="n"/>
       <c r="O316" s="15" t="n"/>
@@ -24250,8 +23448,6 @@
       <c r="S316" s="15" t="n"/>
       <c r="T316" s="15" t="n"/>
       <c r="U316" s="15" t="n"/>
-      <c r="V316" s="15" t="n"/>
-      <c r="W316" s="15" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
@@ -24288,32 +23484,30 @@
         </is>
       </c>
       <c r="I317" s="15" t="n"/>
-      <c r="J317" s="15" t="n"/>
+      <c r="J317" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K317" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L317" s="15" t="inlineStr">
-        <is>
           <t>Mega Kangakhan ex - Black Star Promo , Mega Evolution - Spearow - Single Gold Star - Illustration Rare,</t>
         </is>
       </c>
+      <c r="L317" s="15" t="n"/>
       <c r="M317" s="15" t="n"/>
       <c r="N317" s="15" t="n"/>
-      <c r="O317" s="15" t="n"/>
+      <c r="O317" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="P317" s="15" t="n"/>
-      <c r="Q317" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Q317" s="15" t="n"/>
       <c r="R317" s="15" t="n"/>
       <c r="S317" s="15" t="n"/>
       <c r="T317" s="15" t="n"/>
-      <c r="U317" s="15" t="n"/>
-      <c r="V317" s="15" t="n"/>
-      <c r="W317" s="15" t="inlineStr">
+      <c r="U317" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -24354,32 +23548,30 @@
         </is>
       </c>
       <c r="I318" s="15" t="n"/>
-      <c r="J318" s="15" t="n"/>
+      <c r="J318" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K318" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L318" s="15" t="inlineStr">
-        <is>
           <t>Phantasmal Flames - Trainer - Dawn - Double Silver Star - Ultra Rare, Phantasmal Flames - Mega Gengar ex - Double Black Star - Double Rare , Mega Evolution - Mega Gardevoir ex - Double Silver Star - Ultra Rare , Mega Evolution - Mega Venusaur ex - Double Black Star - Double Rare , Mega Evolution - Marshadow - Single Gold Star - Illustration Rare ,  Destined Rivals - Cetitan ex - Double Black Star , Destined Rivals - Rotom - Single Gold Star - Illustration Rare, Journey Together - Noibat - Single Gold Star - Illustration Rare, Journey Together - Trainer - Brock's Scouting - Double Silver Star - Ultra Rare , Journey Together - Blaziken ex - Double Black Star - Double Rare, Surging Sparks - Trainer - Scramble Switch - Single Pink Star -  ACE SPEC Rare , Surging Sparks - Trainer - Cyrano - Double Silver Star - Ultra Rare, Phantasmal Falmes - Charizard X ex - Black Star Promo Card , Phantasmal Flames - Oricorio ex - Black Star Promo Card</t>
         </is>
       </c>
+      <c r="L318" s="15" t="n"/>
       <c r="M318" s="15" t="n"/>
       <c r="N318" s="15" t="n"/>
-      <c r="O318" s="15" t="n"/>
+      <c r="O318" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="P318" s="15" t="n"/>
-      <c r="Q318" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Q318" s="15" t="n"/>
       <c r="R318" s="15" t="n"/>
       <c r="S318" s="15" t="n"/>
       <c r="T318" s="15" t="n"/>
-      <c r="U318" s="15" t="n"/>
-      <c r="V318" s="15" t="n"/>
-      <c r="W318" s="15" t="inlineStr">
+      <c r="U318" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
@@ -24420,47 +23612,45 @@
         </is>
       </c>
       <c r="I319" s="15" t="n"/>
-      <c r="J319" s="15" t="n"/>
+      <c r="J319" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K319" s="15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L319" s="15" t="inlineStr">
-        <is>
           <t>Mega Evolution - Stufful - Single Gold star - Illustration Rare , Destined Rivals - Marnie's Grimmsnarl ex , Double Black Star - Double Rare , Journey Together - Wailord - Single Gold Star - Illustration Rare</t>
         </is>
       </c>
+      <c r="L319" s="15" t="n"/>
       <c r="M319" s="15" t="n"/>
       <c r="N319" s="15" t="n"/>
-      <c r="O319" s="15" t="n"/>
+      <c r="O319" s="15" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
       <c r="P319" s="15" t="n"/>
-      <c r="Q319" s="15" t="inlineStr">
-        <is>
-          <t>Hits</t>
-        </is>
-      </c>
+      <c r="Q319" s="15" t="n"/>
       <c r="R319" s="15" t="n"/>
       <c r="S319" s="15" t="n"/>
       <c r="T319" s="15" t="n"/>
-      <c r="U319" s="15" t="n"/>
-      <c r="V319" s="15" t="n"/>
-      <c r="W319" s="15" t="inlineStr">
+      <c r="U319" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W319"/>
-  <conditionalFormatting sqref="H2:K319">
+  <autoFilter ref="A1:U319"/>
+  <conditionalFormatting sqref="H2:J319">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>OR($H2="",$K2="")</formula>
+      <formula>OR($H2="",$J2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:L319">
+  <conditionalFormatting sqref="J2:K319">
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>AND($K2="Yes",$L2="")</formula>
+      <formula>AND($J2="Yes",$K2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25334,7 +24524,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!M2:M319)</f>
+        <f>COUNTA('Video Log'!L2:L319)</f>
         <v/>
       </c>
     </row>
@@ -25345,7 +24535,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A319)-COUNTA('Video Log'!M2:M319)</f>
+        <f>COUNTA('Video Log'!A2:A319)-COUNTA('Video Log'!L2:L319)</f>
         <v/>
       </c>
     </row>
@@ -25356,7 +24546,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!J2:J319)</f>
+        <f>COUNTA('Video Log'!I2:I319)</f>
         <v/>
       </c>
     </row>
@@ -25367,7 +24557,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!K2:K319,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J319,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -25378,7 +24568,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!L2:L319)</f>
+        <f>COUNTA('Video Log'!K2:K319)</f>
         <v/>
       </c>
     </row>
@@ -25389,7 +24579,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!O2:O319,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M319,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -25400,7 +24590,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!P2:P319)</f>
+        <f>COUNTA('Video Log'!N2:N319)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -367,13 +367,6 @@
       <text>
         <t>The last build could not resolve this hit:
   "Manectric" (Abyss Eye (JP)) -- the checklist holds it and carries no scan and no price
-Not always a typo -- check the reason first.</t>
-      </text>
-    </comment>
-    <comment ref="K169" authorId="1" shapeId="0">
-      <text>
-        <t>The last build could not resolve this hit:
-  "Trainer Rare Candy" (Mega Symphonia (JP)) -- that name is not on the checklist we hold for that set
 Not always a typo -- check the reason first.</t>
       </text>
     </comment>
@@ -6751,7 +6744,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -6815,11 +6808,25 @@
           <t>desc: #3 pack 4  Chaos Rising</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n"/>
-      <c r="J3" s="15" t="n"/>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="K3" s="15" t="n"/>
-      <c r="L3" s="15" t="n"/>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="M3" s="15" t="n"/>
       <c r="N3" s="15" t="n"/>
       <c r="O3" s="15" t="n"/>
@@ -6863,11 +6870,25 @@
           <t>desc: pack 14  Chaos Rising</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
-      <c r="J4" s="15" t="n"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="K4" s="15" t="n"/>
-      <c r="L4" s="15" t="n"/>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="M4" s="15" t="n"/>
       <c r="N4" s="15" t="n"/>
       <c r="O4" s="15" t="n"/>
@@ -17329,64 +17350,64 @@
       <c r="U168" s="15" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="16" t="inlineStr">
+      <c r="A169" s="11" t="inlineStr">
         <is>
           <t>auKzs0g2LL8</t>
         </is>
       </c>
-      <c r="B169" s="16" t="inlineStr">
+      <c r="B169" s="11" t="inlineStr">
         <is>
           <t>Do Mega Symphonia Packs Actually Hit?! 🇯🇵✨</t>
         </is>
       </c>
-      <c r="C169" s="16" t="inlineStr">
+      <c r="C169" s="11" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="D169" s="17" t="n">
+      <c r="D169" s="12" t="n">
         <v>934</v>
       </c>
-      <c r="E169" s="16" t="inlineStr">
+      <c r="E169" s="11" t="inlineStr">
         <is>
           <t>0:42</t>
         </is>
       </c>
-      <c r="F169" s="18">
+      <c r="F169" s="13">
         <f>HYPERLINK("https://youtu.be/auKzs0g2LL8","watch")</f>
         <v/>
       </c>
-      <c r="G169" s="20" t="n"/>
-      <c r="H169" s="20" t="inlineStr">
+      <c r="G169" s="15" t="n"/>
+      <c r="H169" s="15" t="inlineStr">
         <is>
           <t>Japanese Single Booster Pack</t>
         </is>
       </c>
-      <c r="I169" s="20" t="n"/>
-      <c r="J169" s="20" t="inlineStr">
+      <c r="I169" s="15" t="n"/>
+      <c r="J169" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K169" s="20" t="inlineStr">
+      <c r="K169" s="15" t="inlineStr">
         <is>
           <t>Mega Abomasnow ex - RR - Double Rare , Trainer - Rare Candy - SR - Full Art</t>
         </is>
       </c>
-      <c r="L169" s="20" t="inlineStr">
+      <c r="L169" s="15" t="inlineStr">
         <is>
           <t>Mega Symphonia - 5 Packs</t>
         </is>
       </c>
-      <c r="M169" s="20" t="n"/>
-      <c r="N169" s="20" t="n"/>
-      <c r="O169" s="20" t="n"/>
-      <c r="P169" s="20" t="n"/>
-      <c r="Q169" s="20" t="n"/>
-      <c r="R169" s="20" t="n"/>
-      <c r="S169" s="20" t="n"/>
-      <c r="T169" s="20" t="n"/>
-      <c r="U169" s="20" t="n"/>
+      <c r="M169" s="15" t="n"/>
+      <c r="N169" s="15" t="n"/>
+      <c r="O169" s="15" t="n"/>
+      <c r="P169" s="15" t="n"/>
+      <c r="Q169" s="15" t="n"/>
+      <c r="R169" s="15" t="n"/>
+      <c r="S169" s="15" t="n"/>
+      <c r="T169" s="15" t="n"/>
+      <c r="U169" s="15" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -39672,7 +39693,7 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Trainer Rare Candy</t>
+          <t>Rare Candy</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -21976,7 +21976,11 @@
       <c r="I242" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J242" s="15" t="n"/>
+      <c r="J242" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="K242" s="15" t="inlineStr">
         <is>
           <t>Surging Sparks - Palossand ex - Double Black Star - Double Rare ; Twilight Masquerade - Bloodmoon Ursaluna ex - Double Black Star - Double Rare</t>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -41250,11 +41250,7 @@
           <t>Mabosstiff ex</t>
         </is>
       </c>
-      <c r="C170" s="15" t="inlineStr">
-        <is>
-          <t>Paradox Rift</t>
-        </is>
-      </c>
+      <c r="C170" s="15" t="n"/>
       <c r="D170" s="15" t="n"/>
       <c r="E170" s="15" t="inlineStr">
         <is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -21669,7 +21669,7 @@
       </c>
       <c r="K237" s="15" t="inlineStr">
         <is>
-          <t>Cinderace V Max</t>
+          <t>Cinderace VMAX</t>
         </is>
       </c>
       <c r="L237" s="15" t="inlineStr">
@@ -41035,7 +41035,7 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Cinderace V Max</t>
+          <t>Cinderace VMAX</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
@@ -41043,8 +41043,16 @@
           <t>Rebel Clash</t>
         </is>
       </c>
-      <c r="D162" s="15" t="n"/>
-      <c r="E162" s="15" t="n"/>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>Holo Rare VMAX</t>
+        </is>
+      </c>
       <c r="F162" s="27" t="n"/>
       <c r="G162" s="27" t="n"/>
       <c r="H162" s="15" t="n"/>
@@ -41621,8 +41629,16 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="D184" s="15" t="n"/>
-      <c r="E184" s="15" t="n"/>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr">
+        <is>
+          <t>Holo Rare V</t>
+        </is>
+      </c>
       <c r="F184" s="27" t="n"/>
       <c r="G184" s="27" t="n"/>
       <c r="H184" s="15" t="n"/>
@@ -41839,8 +41855,16 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="D194" s="15" t="n"/>
-      <c r="E194" s="15" t="n"/>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>Holo Rare V</t>
+        </is>
+      </c>
       <c r="F194" s="27" t="n"/>
       <c r="G194" s="27" t="n"/>
       <c r="H194" s="15" t="n"/>
@@ -41862,8 +41886,16 @@
           <t>Pokémon GO</t>
         </is>
       </c>
-      <c r="D195" s="15" t="n"/>
-      <c r="E195" s="15" t="n"/>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="E195" s="15" t="inlineStr">
+        <is>
+          <t>Holo Rare V</t>
+        </is>
+      </c>
       <c r="F195" s="27" t="n"/>
       <c r="G195" s="27" t="n"/>
       <c r="H195" s="15" t="n"/>
@@ -44384,6 +44416,7 @@
       <c r="H400" s="15" t="n"/>
       <c r="I400" s="15" t="n"/>
     </row>
+    <row r="401"/>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
         <is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -40139,7 +40139,7 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Bidoof PEELABLE DITTO 059/078 Reverse Holo</t>
+          <t>Bidoof</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -40148,7 +40148,11 @@
         </is>
       </c>
       <c r="D126" s="15" t="n"/>
-      <c r="E126" s="15" t="n"/>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
       <c r="F126" s="27" t="n"/>
       <c r="G126" s="27" t="n"/>
       <c r="H126" s="15" t="n"/>
@@ -40162,7 +40166,7 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Mega Froslass ex Pink and Green Star Mega Attack Rare</t>
+          <t>Mega Froslass ex</t>
         </is>
       </c>
       <c r="C127" s="15" t="inlineStr">
@@ -40171,7 +40175,11 @@
         </is>
       </c>
       <c r="D127" s="15" t="n"/>
-      <c r="E127" s="15" t="n"/>
+      <c r="E127" s="15" t="inlineStr">
+        <is>
+          <t>Mega Attack Rare</t>
+        </is>
+      </c>
       <c r="F127" s="27" t="n"/>
       <c r="G127" s="27" t="n"/>
       <c r="H127" s="15" t="n"/>
@@ -40682,7 +40690,7 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Paras Galarian Gallery</t>
+          <t>Paras</t>
         </is>
       </c>
       <c r="C147" s="15" t="inlineStr">
@@ -40691,7 +40699,11 @@
         </is>
       </c>
       <c r="D147" s="15" t="n"/>
-      <c r="E147" s="15" t="n"/>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
       <c r="F147" s="27" t="n"/>
       <c r="G147" s="27" t="n"/>
       <c r="H147" s="15" t="n"/>
@@ -44416,7 +44428,6 @@
       <c r="H400" s="15" t="n"/>
       <c r="I400" s="15" t="n"/>
     </row>
-    <row r="401"/>
     <row r="402">
       <c r="A402" s="5" t="inlineStr">
         <is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -36762,7 +36762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I403"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37823,13 +37823,19 @@
           <t>Cyber Judge (JP)</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n"/>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>085</t>
+        </is>
+      </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Super Rare</t>
         </is>
       </c>
-      <c r="F38" s="27" t="n"/>
+      <c r="F38" s="27" t="n">
+        <v>1.74</v>
+      </c>
       <c r="G38" s="27" t="n"/>
       <c r="H38" s="15" t="n"/>
       <c r="I38" s="15" t="n"/>
@@ -37927,13 +37933,19 @@
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr"/>
-      <c r="D42" s="15" t="n"/>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>025</t>
+        </is>
+      </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Black Star Promo</t>
         </is>
       </c>
-      <c r="F42" s="27" t="n"/>
+      <c r="F42" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="G42" s="27" t="n"/>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="15" t="n"/>
@@ -38878,13 +38890,19 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="D79" s="15" t="n"/>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>084</t>
+        </is>
+      </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F79" s="27" t="n"/>
+      <c r="F79" s="27" t="n">
+        <v>5.87</v>
+      </c>
       <c r="G79" s="27" t="n"/>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="15" t="n"/>
@@ -38905,13 +38923,19 @@
           <t>Abyss Eye (JP)</t>
         </is>
       </c>
-      <c r="D80" s="15" t="n"/>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>086</t>
+        </is>
+      </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F80" s="27" t="n"/>
+      <c r="F80" s="27" t="n">
+        <v>2.48</v>
+      </c>
       <c r="G80" s="27" t="n"/>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="15" t="n"/>
@@ -39526,13 +39550,19 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="D103" s="15" t="n"/>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F103" s="27" t="n"/>
+      <c r="F103" s="27" t="n">
+        <v>1.3</v>
+      </c>
       <c r="G103" s="27" t="n"/>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="15" t="n"/>
@@ -39634,13 +39664,19 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="D107" s="15" t="n"/>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
       <c r="E107" s="15" t="inlineStr">
         <is>
           <t>Double Rare</t>
         </is>
       </c>
-      <c r="F107" s="27" t="n"/>
+      <c r="F107" s="27" t="n">
+        <v>0.35</v>
+      </c>
       <c r="G107" s="27" t="n"/>
       <c r="H107" s="15" t="n"/>
       <c r="I107" s="15" t="n"/>
@@ -39661,13 +39697,19 @@
           <t>Mega Symphonia (JP)</t>
         </is>
       </c>
-      <c r="D108" s="15" t="n"/>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>082</t>
+        </is>
+      </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
           <t>Super Rare</t>
         </is>
       </c>
-      <c r="F108" s="27" t="n"/>
+      <c r="F108" s="27" t="n">
+        <v>0.88</v>
+      </c>
       <c r="G108" s="27" t="n"/>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="15" t="n"/>
@@ -39769,13 +39811,19 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="D112" s="15" t="n"/>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F112" s="27" t="n"/>
+      <c r="F112" s="27" t="n">
+        <v>2.6</v>
+      </c>
       <c r="G112" s="27" t="n"/>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="15" t="n"/>
@@ -39796,13 +39844,19 @@
           <t>Stellar Miracle (JP)</t>
         </is>
       </c>
-      <c r="D113" s="15" t="n"/>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
       <c r="E113" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F113" s="27" t="n"/>
+      <c r="F113" s="27" t="n">
+        <v>2.71</v>
+      </c>
       <c r="G113" s="27" t="n"/>
       <c r="H113" s="15" t="n"/>
       <c r="I113" s="15" t="n"/>
@@ -40093,13 +40147,19 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="D124" s="15" t="n"/>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="E124" s="15" t="inlineStr">
         <is>
           <t>Super Rare</t>
         </is>
       </c>
-      <c r="F124" s="27" t="n"/>
+      <c r="F124" s="27" t="n">
+        <v>2.02</v>
+      </c>
       <c r="G124" s="27" t="n"/>
       <c r="H124" s="15" t="n"/>
       <c r="I124" s="15" t="n"/>
@@ -40255,9 +40315,15 @@
           <t>Scarlet &amp; Violet Black Star Promos</t>
         </is>
       </c>
-      <c r="D130" s="15" t="n"/>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
       <c r="E130" s="15" t="n"/>
-      <c r="F130" s="27" t="n"/>
+      <c r="F130" s="27" t="n">
+        <v>13.96</v>
+      </c>
       <c r="G130" s="27" t="n"/>
       <c r="H130" s="15" t="n"/>
       <c r="I130" s="15" t="n"/>
@@ -40494,13 +40560,19 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="D139" s="15" t="n"/>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>092</t>
+        </is>
+      </c>
       <c r="E139" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F139" s="27" t="n"/>
+      <c r="F139" s="27" t="n">
+        <v>1.76</v>
+      </c>
       <c r="G139" s="27" t="n"/>
       <c r="H139" s="15" t="n"/>
       <c r="I139" s="15" t="n"/>
@@ -40521,13 +40593,19 @@
           <t>Nihil Zero (JP)</t>
         </is>
       </c>
-      <c r="D140" s="15" t="n"/>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>084</t>
+        </is>
+      </c>
       <c r="E140" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F140" s="27" t="n"/>
+      <c r="F140" s="27" t="n">
+        <v>2.46</v>
+      </c>
       <c r="G140" s="27" t="n"/>
       <c r="H140" s="15" t="n"/>
       <c r="I140" s="15" t="n"/>
@@ -40629,9 +40707,15 @@
           <t>Silver Tempest</t>
         </is>
       </c>
-      <c r="D144" s="15" t="n"/>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>TG18</t>
+        </is>
+      </c>
       <c r="E144" s="15" t="n"/>
-      <c r="F144" s="27" t="n"/>
+      <c r="F144" s="27" t="n">
+        <v>15.49</v>
+      </c>
       <c r="G144" s="27" t="n"/>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="15" t="n"/>
@@ -40652,9 +40736,15 @@
           <t>Silver Tempest</t>
         </is>
       </c>
-      <c r="D145" s="15" t="n"/>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
       <c r="E145" s="15" t="n"/>
-      <c r="F145" s="27" t="n"/>
+      <c r="F145" s="27" t="n">
+        <v>1.21</v>
+      </c>
       <c r="G145" s="27" t="n"/>
       <c r="H145" s="15" t="n"/>
       <c r="I145" s="15" t="n"/>
@@ -40675,9 +40765,15 @@
           <t>Lost Origin</t>
         </is>
       </c>
-      <c r="D146" s="15" t="n"/>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="E146" s="15" t="n"/>
-      <c r="F146" s="27" t="n"/>
+      <c r="F146" s="27" t="n">
+        <v>0.75</v>
+      </c>
       <c r="G146" s="27" t="n"/>
       <c r="H146" s="15" t="n"/>
       <c r="I146" s="15" t="n"/>
@@ -40698,13 +40794,19 @@
           <t>Crown Zenith</t>
         </is>
       </c>
-      <c r="D147" s="15" t="n"/>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>GG32</t>
+        </is>
+      </c>
       <c r="E147" s="15" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="F147" s="27" t="n"/>
+      <c r="F147" s="27" t="n">
+        <v>9.26</v>
+      </c>
       <c r="G147" s="27" t="n"/>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="15" t="n"/>
@@ -40836,13 +40938,19 @@
           <t>Mega Brave (JP)</t>
         </is>
       </c>
-      <c r="D153" s="15" t="n"/>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>074</t>
+        </is>
+      </c>
       <c r="E153" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F153" s="27" t="n"/>
+      <c r="F153" s="27" t="n">
+        <v>2.26</v>
+      </c>
       <c r="G153" s="27" t="n"/>
       <c r="H153" s="15" t="n"/>
       <c r="I153" s="15" t="n"/>
@@ -41271,13 +41379,19 @@
         </is>
       </c>
       <c r="C170" s="15" t="n"/>
-      <c r="D170" s="15" t="n"/>
+      <c r="D170" s="15" t="inlineStr">
+        <is>
+          <t>086</t>
+        </is>
+      </c>
       <c r="E170" s="15" t="inlineStr">
         <is>
           <t>Black Star Promo</t>
         </is>
       </c>
-      <c r="F170" s="27" t="n"/>
+      <c r="F170" s="27" t="n">
+        <v>0.45</v>
+      </c>
       <c r="G170" s="27" t="n"/>
       <c r="H170" s="15" t="n"/>
       <c r="I170" s="15" t="n"/>
@@ -41325,9 +41439,15 @@
           <t>Silver Tempest</t>
         </is>
       </c>
-      <c r="D172" s="15" t="n"/>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
+          <t>033</t>
+        </is>
+      </c>
       <c r="E172" s="15" t="n"/>
-      <c r="F172" s="27" t="n"/>
+      <c r="F172" s="27" t="n">
+        <v>2.09</v>
+      </c>
       <c r="G172" s="27" t="n"/>
       <c r="H172" s="15" t="n"/>
       <c r="I172" s="15" t="n"/>
@@ -41344,13 +41464,19 @@
         </is>
       </c>
       <c r="C173" s="15" t="inlineStr"/>
-      <c r="D173" s="15" t="n"/>
+      <c r="D173" s="15" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
       <c r="E173" s="15" t="inlineStr">
         <is>
           <t>Black Star Promo</t>
         </is>
       </c>
-      <c r="F173" s="27" t="n"/>
+      <c r="F173" s="27" t="n">
+        <v>5.98</v>
+      </c>
       <c r="G173" s="27" t="n"/>
       <c r="H173" s="15" t="n"/>
       <c r="I173" s="15" t="n"/>
@@ -41614,13 +41740,19 @@
           <t>Ninja Spinner (JP)</t>
         </is>
       </c>
-      <c r="D183" s="15" t="n"/>
+      <c r="D183" s="15" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
       <c r="E183" s="15" t="inlineStr">
         <is>
           <t>Art Rare</t>
         </is>
       </c>
-      <c r="F183" s="27" t="n"/>
+      <c r="F183" s="27" t="n">
+        <v>3.91</v>
+      </c>
       <c r="G183" s="27" t="n"/>
       <c r="H183" s="15" t="n"/>
       <c r="I183" s="15" t="n"/>
@@ -41979,7 +42111,11 @@
           <t>Ascended Heroes</t>
         </is>
       </c>
-      <c r="D198" s="15" t="n"/>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
       <c r="E198" s="15" t="inlineStr">
         <is>
           <t>Double Rare</t>
@@ -42029,13 +42165,19 @@
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr"/>
-      <c r="D200" s="15" t="n"/>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
       <c r="E200" s="15" t="inlineStr">
         <is>
           <t>Black Star Promo</t>
         </is>
       </c>
-      <c r="F200" s="27" t="n"/>
+      <c r="F200" s="27" t="n">
+        <v>0.89</v>
+      </c>
       <c r="G200" s="27" t="n"/>
       <c r="H200" s="15" t="n"/>
       <c r="I200" s="15" t="n"/>
@@ -42160,13 +42302,19 @@
         </is>
       </c>
       <c r="C205" s="15" t="inlineStr"/>
-      <c r="D205" s="15" t="n"/>
+      <c r="D205" s="15" t="inlineStr">
+        <is>
+          <t>030</t>
+        </is>
+      </c>
       <c r="E205" s="15" t="inlineStr">
         <is>
           <t>Black Star Promo</t>
         </is>
       </c>
-      <c r="F205" s="27" t="n"/>
+      <c r="F205" s="27" t="n">
+        <v>5.98</v>
+      </c>
       <c r="G205" s="27" t="n"/>
       <c r="H205" s="15" t="n"/>
       <c r="I205" s="15" t="n"/>
@@ -42179,21 +42327,23 @@
       </c>
       <c r="B206" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="D206" s="15" t="n"/>
+          <t>Mega Charizard X ex</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="n"/>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>029</t>
+        </is>
+      </c>
       <c r="E206" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
-        </is>
-      </c>
-      <c r="F206" s="27" t="n"/>
+          <t>Black Star Promo</t>
+        </is>
+      </c>
+      <c r="F206" s="27" t="n">
+        <v>5.68</v>
+      </c>
       <c r="G206" s="27" t="n"/>
       <c r="H206" s="15" t="n"/>
       <c r="I206" s="15" t="n"/>
@@ -42201,17 +42351,17 @@
     <row r="207">
       <c r="A207" s="15" t="inlineStr">
         <is>
-          <t>zIn3mWKwkyg</t>
+          <t>F9mAQqKd6r8</t>
         </is>
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
+          <t>Empoleon ex</t>
         </is>
       </c>
       <c r="C207" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D207" s="15" t="n"/>
@@ -42233,18 +42383,18 @@
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
+          <t>Mega Venusaur ex</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D208" s="15" t="n"/>
       <c r="E208" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F208" s="27" t="n"/>
@@ -42255,23 +42405,23 @@
     <row r="209">
       <c r="A209" s="15" t="inlineStr">
         <is>
-          <t>AqZBxDu2wkc</t>
+          <t>zIn3mWKwkyg</t>
         </is>
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Jolteon ex</t>
+          <t>Empoleon ex</t>
         </is>
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>Prismatic Evolutions</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D209" s="15" t="n"/>
       <c r="E209" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F209" s="27" t="n"/>
@@ -42282,17 +42432,17 @@
     <row r="210">
       <c r="A210" s="15" t="inlineStr">
         <is>
-          <t>LROQ-vFl4Hs</t>
+          <t>AqZBxDu2wkc</t>
         </is>
       </c>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Cinderace ex</t>
+          <t>Jolteon ex</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>Ascended Heroes</t>
+          <t>Prismatic Evolutions</t>
         </is>
       </c>
       <c r="D210" s="15" t="n"/>
@@ -42309,23 +42459,23 @@
     <row r="211">
       <c r="A211" s="15" t="inlineStr">
         <is>
-          <t>Ab81MNFnDLw</t>
+          <t>LROQ-vFl4Hs</t>
         </is>
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Cinderace ex</t>
         </is>
       </c>
       <c r="C211" s="15" t="inlineStr">
         <is>
-          <t>Black Bolt</t>
+          <t>Ascended Heroes</t>
         </is>
       </c>
       <c r="D211" s="15" t="n"/>
       <c r="E211" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F211" s="27" t="n"/>
@@ -42336,23 +42486,23 @@
     <row r="212">
       <c r="A212" s="15" t="inlineStr">
         <is>
-          <t>b1B3Vbpsrh8</t>
+          <t>Ab81MNFnDLw</t>
         </is>
       </c>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>Gladion’s Final Battle</t>
+          <t>Panpour</t>
         </is>
       </c>
       <c r="C212" s="15" t="inlineStr">
         <is>
-          <t>Pitch Black</t>
+          <t>Black Bolt</t>
         </is>
       </c>
       <c r="D212" s="15" t="n"/>
       <c r="E212" s="15" t="inlineStr">
         <is>
-          <t>Special Illustration Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F212" s="27" t="n"/>
@@ -42361,11 +42511,27 @@
       <c r="I212" s="15" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="15" t="n"/>
-      <c r="B213" s="15" t="n"/>
-      <c r="C213" s="15" t="n"/>
+      <c r="A213" s="15" t="inlineStr">
+        <is>
+          <t>b1B3Vbpsrh8</t>
+        </is>
+      </c>
+      <c r="B213" s="15" t="inlineStr">
+        <is>
+          <t>Gladion’s Final Battle</t>
+        </is>
+      </c>
+      <c r="C213" s="15" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
       <c r="D213" s="15" t="n"/>
-      <c r="E213" s="15" t="n"/>
+      <c r="E213" s="15" t="inlineStr">
+        <is>
+          <t>Special Illustration Rare</t>
+        </is>
+      </c>
       <c r="F213" s="27" t="n"/>
       <c r="G213" s="27" t="n"/>
       <c r="H213" s="15" t="n"/>
@@ -44428,15 +44594,27 @@
       <c r="H400" s="15" t="n"/>
       <c r="I400" s="15" t="n"/>
     </row>
-    <row r="402">
-      <c r="A402" s="5" t="inlineStr">
-        <is>
-          <t>One row per card pulled. Several rows can share a Video ID.</t>
-        </is>
-      </c>
-    </row>
+    <row r="401">
+      <c r="A401" s="15" t="n"/>
+      <c r="B401" s="15" t="n"/>
+      <c r="C401" s="15" t="n"/>
+      <c r="D401" s="15" t="n"/>
+      <c r="E401" s="15" t="n"/>
+      <c r="F401" s="27" t="n"/>
+      <c r="G401" s="27" t="n"/>
+      <c r="H401" s="15" t="n"/>
+      <c r="I401" s="15" t="n"/>
+    </row>
+    <row r="402"/>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t>One row per card pulled. Several rows can share a Video ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="inlineStr">
         <is>
           <t>Hall of Fame = Yes marks the all-time best, which get their own page.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -20839,7 +20839,7 @@
       </c>
       <c r="K224" s="20" t="inlineStr">
         <is>
-          <t>Paras - Galarian Gallery</t>
+          <t>Crown Zenith - Paras - Galarian Gallery - Rare</t>
         </is>
       </c>
       <c r="L224" s="20" t="inlineStr">
@@ -25191,7 +25191,7 @@
       </c>
       <c r="K293" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard Y ex - Black Star Promo ; Phantasmal Flames - Empoleon ex - Double Black Star - Double Rare</t>
+          <t>Mega Charizard X ex - Black Star Promo ; Phantasmal Flames - Empoleon ex - Double Black Star - Double Rare</t>
         </is>
       </c>
       <c r="L293" s="15" t="inlineStr">
@@ -36762,7 +36762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I404"/>
+  <dimension ref="A1:I403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42298,13 +42298,13 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard Y ex</t>
-        </is>
-      </c>
-      <c r="C205" s="15" t="inlineStr"/>
+          <t>Mega Charizard X ex</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="n"/>
       <c r="D205" s="15" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>029</t>
         </is>
       </c>
       <c r="E205" s="15" t="inlineStr">
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="F205" s="27" t="n">
-        <v>5.98</v>
+        <v>5.68</v>
       </c>
       <c r="G205" s="27" t="n"/>
       <c r="H205" s="15" t="n"/>
@@ -42327,23 +42327,21 @@
       </c>
       <c r="B206" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard X ex</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="n"/>
-      <c r="D206" s="15" t="inlineStr">
-        <is>
-          <t>029</t>
-        </is>
-      </c>
+          <t>Empoleon ex</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="n"/>
       <c r="E206" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
-        </is>
-      </c>
-      <c r="F206" s="27" t="n">
-        <v>5.68</v>
-      </c>
+          <t>Double Rare</t>
+        </is>
+      </c>
+      <c r="F206" s="27" t="n"/>
       <c r="G206" s="27" t="n"/>
       <c r="H206" s="15" t="n"/>
       <c r="I206" s="15" t="n"/>
@@ -42351,17 +42349,17 @@
     <row r="207">
       <c r="A207" s="15" t="inlineStr">
         <is>
-          <t>F9mAQqKd6r8</t>
+          <t>zIn3mWKwkyg</t>
         </is>
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
+          <t>Mega Venusaur ex</t>
         </is>
       </c>
       <c r="C207" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D207" s="15" t="n"/>
@@ -42383,18 +42381,18 @@
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
+          <t>Empoleon ex</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D208" s="15" t="n"/>
       <c r="E208" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F208" s="27" t="n"/>
@@ -42405,23 +42403,23 @@
     <row r="209">
       <c r="A209" s="15" t="inlineStr">
         <is>
-          <t>zIn3mWKwkyg</t>
+          <t>AqZBxDu2wkc</t>
         </is>
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
+          <t>Jolteon ex</t>
         </is>
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Prismatic Evolutions</t>
         </is>
       </c>
       <c r="D209" s="15" t="n"/>
       <c r="E209" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F209" s="27" t="n"/>
@@ -42432,17 +42430,17 @@
     <row r="210">
       <c r="A210" s="15" t="inlineStr">
         <is>
-          <t>AqZBxDu2wkc</t>
+          <t>LROQ-vFl4Hs</t>
         </is>
       </c>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Jolteon ex</t>
+          <t>Cinderace ex</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>Prismatic Evolutions</t>
+          <t>Ascended Heroes</t>
         </is>
       </c>
       <c r="D210" s="15" t="n"/>
@@ -42459,23 +42457,23 @@
     <row r="211">
       <c r="A211" s="15" t="inlineStr">
         <is>
-          <t>LROQ-vFl4Hs</t>
+          <t>Ab81MNFnDLw</t>
         </is>
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>Cinderace ex</t>
+          <t>Panpour</t>
         </is>
       </c>
       <c r="C211" s="15" t="inlineStr">
         <is>
-          <t>Ascended Heroes</t>
+          <t>Black Bolt</t>
         </is>
       </c>
       <c r="D211" s="15" t="n"/>
       <c r="E211" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F211" s="27" t="n"/>
@@ -42486,23 +42484,23 @@
     <row r="212">
       <c r="A212" s="15" t="inlineStr">
         <is>
-          <t>Ab81MNFnDLw</t>
+          <t>b1B3Vbpsrh8</t>
         </is>
       </c>
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>Panpour</t>
+          <t>Gladion’s Final Battle</t>
         </is>
       </c>
       <c r="C212" s="15" t="inlineStr">
         <is>
-          <t>Black Bolt</t>
+          <t>Pitch Black</t>
         </is>
       </c>
       <c r="D212" s="15" t="n"/>
       <c r="E212" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Special Illustration Rare</t>
         </is>
       </c>
       <c r="F212" s="27" t="n"/>
@@ -42511,27 +42509,11 @@
       <c r="I212" s="15" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="15" t="inlineStr">
-        <is>
-          <t>b1B3Vbpsrh8</t>
-        </is>
-      </c>
-      <c r="B213" s="15" t="inlineStr">
-        <is>
-          <t>Gladion’s Final Battle</t>
-        </is>
-      </c>
-      <c r="C213" s="15" t="inlineStr">
-        <is>
-          <t>Pitch Black</t>
-        </is>
-      </c>
+      <c r="A213" s="15" t="n"/>
+      <c r="B213" s="15" t="n"/>
+      <c r="C213" s="15" t="n"/>
       <c r="D213" s="15" t="n"/>
-      <c r="E213" s="15" t="inlineStr">
-        <is>
-          <t>Special Illustration Rare</t>
-        </is>
-      </c>
+      <c r="E213" s="15" t="n"/>
       <c r="F213" s="27" t="n"/>
       <c r="G213" s="27" t="n"/>
       <c r="H213" s="15" t="n"/>
@@ -44594,27 +44576,15 @@
       <c r="H400" s="15" t="n"/>
       <c r="I400" s="15" t="n"/>
     </row>
-    <row r="401">
-      <c r="A401" s="15" t="n"/>
-      <c r="B401" s="15" t="n"/>
-      <c r="C401" s="15" t="n"/>
-      <c r="D401" s="15" t="n"/>
-      <c r="E401" s="15" t="n"/>
-      <c r="F401" s="27" t="n"/>
-      <c r="G401" s="27" t="n"/>
-      <c r="H401" s="15" t="n"/>
-      <c r="I401" s="15" t="n"/>
-    </row>
-    <row r="402"/>
+    <row r="402">
+      <c r="A402" s="5" t="inlineStr">
+        <is>
+          <t>One row per card pulled. Several rows can share a Video ID.</t>
+        </is>
+      </c>
+    </row>
     <row r="403">
       <c r="A403" s="5" t="inlineStr">
-        <is>
-          <t>One row per card pulled. Several rows can share a Video ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="5" t="inlineStr">
         <is>
           <t>Hall of Fame = Yes marks the all-time best, which get their own page.</t>
         </is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="D2" s="12" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
@@ -6614,11 +6614,25 @@
           <t>desc: #3 pack 5  Chaos Rising</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="K2" s="15" t="n"/>
-      <c r="L2" s="15" t="n"/>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
+        </is>
+      </c>
       <c r="M2" s="15" t="n"/>
       <c r="N2" s="15" t="n"/>
       <c r="O2" s="15" t="n"/>
@@ -37153,28 +37167,26 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard X ex</t>
+          <t>Dawn</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>MEP Black Star Promos</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>023</t>
+          <t>118</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n">
-        <v>176.57</v>
-      </c>
+      <c r="G2" s="22" t="n"/>
       <c r="H2" s="15" t="n"/>
       <c r="I2" s="15" t="n"/>
     </row>
@@ -37186,28 +37198,26 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Oricorio ex</t>
+          <t>Mega Gengar ex</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>MEP Black Star Promos</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>056</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F3" s="22" t="n"/>
-      <c r="G3" s="22" t="n">
-        <v>99.78</v>
-      </c>
+      <c r="G3" s="22" t="n"/>
       <c r="H3" s="15" t="n"/>
       <c r="I3" s="15" t="n"/>
     </row>
@@ -37219,7 +37229,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Marshadow</t>
+          <t>Mega Gardevoir ex</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -37229,12 +37239,12 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F4" s="22" t="n"/>
@@ -37250,22 +37260,22 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Mega Venusaur ex</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>003</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F5" s="22" t="n"/>
@@ -37281,17 +37291,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Noibat</t>
+          <t>Marshadow</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Journey Together</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>146</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -37312,22 +37322,22 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Mega Gardevoir ex</t>
+          <t>Cetitan ex</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>Destined Rivals</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>065</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F7" s="22" t="n"/>
@@ -37374,22 +37384,22 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Mega Gengar ex</t>
+          <t>Noibat</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Journey Together</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F9" s="22" t="n"/>
@@ -37405,17 +37415,17 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Cyrano</t>
+          <t>Brock's Scouting</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Surging Sparks</t>
+          <t>Journey Together</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>179</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -37436,7 +37446,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Brock's Scouting</t>
+          <t>Blaziken ex</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -37446,12 +37456,12 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>024</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F11" s="22" t="n"/>
@@ -37467,22 +37477,22 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Blaziken ex</t>
+          <t>Scramble Switch</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Journey Together</t>
+          <t>Surging Sparks</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>ACE SPEC Rare</t>
         </is>
       </c>
       <c r="F12" s="22" t="n"/>
@@ -37498,22 +37508,22 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Cetitan ex</t>
+          <t>Cyrano</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Destined Rivals</t>
+          <t>Surging Sparks</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>065</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
@@ -37529,26 +37539,28 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
+          <t>Mega Charizard X ex</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>MEP Black Star Promos</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>023</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="G14" s="22" t="n">
+        <v>176.57</v>
+      </c>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
     </row>
@@ -37560,26 +37572,28 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Scramble Switch</t>
+          <t>Oricorio ex</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Surging Sparks</t>
+          <t>MEP Black Star Promos</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>024</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>ACE SPEC Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
+      <c r="G15" s="22" t="n">
+        <v>99.78</v>
+      </c>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
     </row>
@@ -37591,17 +37605,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Wailord</t>
+          <t>Stufful</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Journey Together</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -37622,22 +37636,22 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Stufful</t>
+          <t>Marnie's Grimmsnarl ex</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>Destined Rivals</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>136</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F17" s="22" t="n"/>
@@ -37653,22 +37667,22 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Marnie's Grimmsnarl ex</t>
+          <t>Wailord</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Destined Rivals</t>
+          <t>Journey Together</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F18" s="22" t="n"/>
@@ -38397,22 +38411,18 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Spearow</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Mega Evolution</t>
-        </is>
-      </c>
+          <t>Mega Kangaskhan ex</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr"/>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>025</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F42" s="22" t="n"/>
@@ -38428,18 +38438,22 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Mega Kangaskhan ex</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr"/>
+          <t>Spearow</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F43" s="22" t="n"/>
@@ -38977,24 +38991,12 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Punk Helmet</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>Ultra Rare</t>
-        </is>
-      </c>
+          <t>Rowlet</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
       <c r="F62" s="22" t="n"/>
       <c r="G62" s="22" t="n"/>
       <c r="H62" s="15" t="n"/>
@@ -39008,7 +39010,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Rowlet</t>
+          <t>Litten</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr"/>
@@ -39027,7 +39029,7 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Litten</t>
+          <t>Popplio</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr"/>
@@ -39046,12 +39048,24 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Popplio</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr"/>
-      <c r="D65" s="15" t="n"/>
-      <c r="E65" s="15" t="n"/>
+          <t>Punk Helmet</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F65" s="22" t="n"/>
       <c r="G65" s="22" t="n"/>
       <c r="H65" s="15" t="n"/>
@@ -41049,24 +41063,20 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Servine</t>
+          <t>Victini</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Black Bolt</t>
+          <t>Scarlet &amp; Violet Black Star Promos</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>088</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n"/>
       <c r="F130" s="22" t="n"/>
       <c r="G130" s="22" t="n"/>
       <c r="H130" s="15" t="n"/>
@@ -41080,7 +41090,7 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Musharna</t>
+          <t>Servine</t>
         </is>
       </c>
       <c r="C131" s="15" t="inlineStr">
@@ -41090,7 +41100,7 @@
       </c>
       <c r="D131" s="15" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>088</t>
         </is>
       </c>
       <c r="E131" s="15" t="inlineStr">
@@ -41111,17 +41121,17 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Mienshao</t>
+          <t>Musharna</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>White Flare</t>
+          <t>Black Bolt</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr">
@@ -41173,20 +41183,24 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Victini</t>
+          <t>Mienshao</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Scarlet &amp; Violet Black Star Promos</t>
+          <t>White Flare</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="E134" s="15" t="n"/>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E134" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F134" s="22" t="n"/>
       <c r="G134" s="22" t="n"/>
       <c r="H134" s="15" t="n"/>
@@ -41622,24 +41636,12 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Mismagius ex</t>
-        </is>
-      </c>
-      <c r="C149" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="D149" s="15" t="inlineStr">
-        <is>
-          <t>036</t>
-        </is>
-      </c>
-      <c r="E149" s="15" t="inlineStr">
-        <is>
-          <t>Double Rare</t>
-        </is>
-      </c>
+          <t>Turtwig</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr"/>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
       <c r="F149" s="22" t="n"/>
       <c r="G149" s="22" t="n"/>
       <c r="H149" s="15" t="n"/>
@@ -41653,7 +41655,7 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Turtwig</t>
+          <t>Chimchar</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr"/>
@@ -41672,7 +41674,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Chimchar</t>
+          <t>Piplup</t>
         </is>
       </c>
       <c r="C151" s="15" t="inlineStr"/>
@@ -41691,12 +41693,24 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Piplup</t>
-        </is>
-      </c>
-      <c r="C152" s="15" t="inlineStr"/>
-      <c r="D152" s="15" t="n"/>
-      <c r="E152" s="15" t="n"/>
+          <t>Mismagius ex</t>
+        </is>
+      </c>
+      <c r="C152" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="E152" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F152" s="22" t="n"/>
       <c r="G152" s="22" t="n"/>
       <c r="H152" s="15" t="n"/>
@@ -41834,24 +41848,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
-        </is>
-      </c>
-      <c r="C157" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="D157" s="15" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E157" s="15" t="inlineStr">
-        <is>
-          <t>Ultra Rare</t>
-        </is>
-      </c>
+          <t>Rowlet</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr"/>
+      <c r="D157" s="15" t="n"/>
+      <c r="E157" s="15" t="n"/>
       <c r="F157" s="22" t="n"/>
       <c r="G157" s="22" t="n"/>
       <c r="H157" s="15" t="n"/>
@@ -41865,24 +41867,12 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr">
-        <is>
-          <t>Mega Evolution</t>
-        </is>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr">
-        <is>
-          <t>Double Rare</t>
-        </is>
-      </c>
+          <t>Litten</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr"/>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
       <c r="F158" s="22" t="n"/>
       <c r="G158" s="22" t="n"/>
       <c r="H158" s="15" t="n"/>
@@ -41896,7 +41886,7 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Rowlet</t>
+          <t>Popplio</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr"/>
@@ -41915,12 +41905,24 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Litten</t>
-        </is>
-      </c>
-      <c r="C160" s="15" t="inlineStr"/>
-      <c r="D160" s="15" t="n"/>
-      <c r="E160" s="15" t="n"/>
+          <t>Mega Venusaur ex</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr">
+        <is>
+          <t>Mega Evolution</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>Double Rare</t>
+        </is>
+      </c>
       <c r="F160" s="22" t="n"/>
       <c r="G160" s="22" t="n"/>
       <c r="H160" s="15" t="n"/>
@@ -41934,12 +41936,24 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Popplio</t>
-        </is>
-      </c>
-      <c r="C161" s="15" t="inlineStr"/>
-      <c r="D161" s="15" t="n"/>
-      <c r="E161" s="15" t="n"/>
+          <t>Empoleon ex</t>
+        </is>
+      </c>
+      <c r="C161" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E161" s="15" t="inlineStr">
+        <is>
+          <t>Ultra Rare</t>
+        </is>
+      </c>
       <c r="F161" s="22" t="n"/>
       <c r="G161" s="22" t="n"/>
       <c r="H161" s="15" t="n"/>
@@ -42015,7 +42029,7 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Togekiss</t>
+          <t>Anthea &amp; Concordia</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -42025,12 +42039,12 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E164" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F164" s="22" t="n"/>
@@ -42046,7 +42060,7 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Anthea &amp; Concordia</t>
+          <t>Togekiss</t>
         </is>
       </c>
       <c r="C165" s="15" t="inlineStr">
@@ -42056,12 +42070,12 @@
       </c>
       <c r="D165" s="15" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E165" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F165" s="22" t="n"/>
@@ -42077,17 +42091,17 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Bloodmoon Ursaluna ex</t>
+          <t>Palossand ex</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Twilight Masquerade</t>
+          <t>Surging Sparks</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>091</t>
         </is>
       </c>
       <c r="E166" s="15" t="inlineStr">
@@ -42108,17 +42122,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Palossand ex</t>
+          <t>Bloodmoon Ursaluna ex</t>
         </is>
       </c>
       <c r="C167" s="15" t="inlineStr">
         <is>
-          <t>Surging Sparks</t>
+          <t>Twilight Masquerade</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E167" s="15" t="inlineStr">
@@ -42170,7 +42184,7 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Dragapult ex</t>
+          <t>Larry's Dudunsparce ex</t>
         </is>
       </c>
       <c r="C169" s="15" t="inlineStr">
@@ -42180,7 +42194,7 @@
       </c>
       <c r="D169" s="15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>164</t>
         </is>
       </c>
       <c r="E169" s="15" t="inlineStr">
@@ -42201,7 +42215,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Larry's Dudunsparce ex</t>
+          <t>Dragapult ex</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -42211,7 +42225,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>160</t>
         </is>
       </c>
       <c r="E170" s="15" t="inlineStr">
@@ -42232,22 +42246,18 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Golisopod ex</t>
-        </is>
-      </c>
-      <c r="C171" s="15" t="inlineStr">
-        <is>
-          <t>Paradox Rift</t>
-        </is>
-      </c>
+          <t>Mabosstiff ex</t>
+        </is>
+      </c>
+      <c r="C171" s="15" t="inlineStr"/>
       <c r="D171" s="15" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>086</t>
         </is>
       </c>
       <c r="E171" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F171" s="22" t="n"/>
@@ -42263,18 +42273,22 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Mabosstiff ex</t>
-        </is>
-      </c>
-      <c r="C172" s="15" t="inlineStr"/>
+          <t>Golisopod ex</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>Paradox Rift</t>
+        </is>
+      </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>050</t>
         </is>
       </c>
       <c r="E172" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F172" s="22" t="n"/>
@@ -42317,22 +42331,18 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Marshadow</t>
-        </is>
-      </c>
-      <c r="C174" s="15" t="inlineStr">
-        <is>
-          <t>Mega Evolution</t>
-        </is>
-      </c>
+          <t>Mega Charizard Y ex</t>
+        </is>
+      </c>
+      <c r="C174" s="15" t="inlineStr"/>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>030</t>
         </is>
       </c>
       <c r="E174" s="15" t="inlineStr">
         <is>
-          <t>Illustration Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F174" s="22" t="n"/>
@@ -42379,22 +42389,22 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Mega Lopunny ex</t>
+          <t>Marshadow</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>084</t>
+          <t>146</t>
         </is>
       </c>
       <c r="E176" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Illustration Rare</t>
         </is>
       </c>
       <c r="F176" s="22" t="n"/>
@@ -42410,18 +42420,22 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard Y ex</t>
-        </is>
-      </c>
-      <c r="C177" s="15" t="inlineStr"/>
+          <t>Mega Lopunny ex</t>
+        </is>
+      </c>
+      <c r="C177" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="D177" s="15" t="inlineStr">
         <is>
-          <t>030</t>
+          <t>084</t>
         </is>
       </c>
       <c r="E177" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F177" s="22" t="n"/>
@@ -42804,24 +42818,12 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Dewgong</t>
-        </is>
-      </c>
-      <c r="C191" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
-      <c r="D191" s="15" t="inlineStr">
-        <is>
-          <t>097</t>
-        </is>
-      </c>
-      <c r="E191" s="15" t="inlineStr">
-        <is>
-          <t>Illustration Rare</t>
-        </is>
-      </c>
+          <t>Rowlet</t>
+        </is>
+      </c>
+      <c r="C191" s="15" t="inlineStr"/>
+      <c r="D191" s="15" t="n"/>
+      <c r="E191" s="15" t="n"/>
       <c r="F191" s="22" t="n"/>
       <c r="G191" s="22" t="n"/>
       <c r="H191" s="15" t="n"/>
@@ -42835,7 +42837,7 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Rowlet</t>
+          <t>Litten</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
@@ -42854,7 +42856,7 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Litten</t>
+          <t>Popplio</t>
         </is>
       </c>
       <c r="C193" s="15" t="inlineStr"/>
@@ -42873,12 +42875,24 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Popplio</t>
-        </is>
-      </c>
-      <c r="C194" s="15" t="inlineStr"/>
-      <c r="D194" s="15" t="n"/>
-      <c r="E194" s="15" t="n"/>
+          <t>Dewgong</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>097</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>Illustration Rare</t>
+        </is>
+      </c>
       <c r="F194" s="22" t="n"/>
       <c r="G194" s="22" t="n"/>
       <c r="H194" s="15" t="n"/>
@@ -43229,22 +43243,18 @@
       </c>
       <c r="B206" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>Phantasmal Flames</t>
-        </is>
-      </c>
+          <t>Mega Charizard X ex</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr"/>
       <c r="D206" s="15" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>029</t>
         </is>
       </c>
       <c r="E206" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Black Star Promo</t>
         </is>
       </c>
       <c r="F206" s="22" t="n"/>
@@ -43260,18 +43270,22 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Mega Charizard X ex</t>
-        </is>
-      </c>
-      <c r="C207" s="15" t="inlineStr"/>
+          <t>Empoleon ex</t>
+        </is>
+      </c>
+      <c r="C207" s="15" t="inlineStr">
+        <is>
+          <t>Phantasmal Flames</t>
+        </is>
+      </c>
       <c r="D207" s="15" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>070</t>
         </is>
       </c>
       <c r="E207" s="15" t="inlineStr">
         <is>
-          <t>Black Star Promo</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F207" s="22" t="n"/>
@@ -43287,22 +43301,22 @@
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Empoleon ex</t>
+          <t>Mega Venusaur ex</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>Phantasmal Flames</t>
+          <t>Mega Evolution</t>
         </is>
       </c>
       <c r="D208" s="15" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>003</t>
         </is>
       </c>
       <c r="E208" s="15" t="inlineStr">
         <is>
-          <t>Ultra Rare</t>
+          <t>Double Rare</t>
         </is>
       </c>
       <c r="F208" s="22" t="n"/>
@@ -43318,22 +43332,22 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Mega Venusaur ex</t>
+          <t>Empoleon ex</t>
         </is>
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>Mega Evolution</t>
+          <t>Phantasmal Flames</t>
         </is>
       </c>
       <c r="D209" s="15" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E209" s="15" t="inlineStr">
         <is>
-          <t>Double Rare</t>
+          <t>Ultra Rare</t>
         </is>
       </c>
       <c r="F209" s="22" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -648,7 +648,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -661,7 +660,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -746,7 +744,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -826,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -882,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -895,7 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -908,7 +902,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -921,7 +914,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -934,7 +926,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -947,7 +938,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -960,7 +950,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -973,7 +962,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -6448,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U324"/>
+  <dimension ref="A1:U325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27076,6 +27064,58 @@
       <c r="U324" s="15" t="inlineStr">
         <is>
           <t>All the packs are on the first set. Move some across the Packs columns if they came from different sets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>rPElm7KrH_E</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>The Single Pack Streak is REAL! ⚡😱</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>193</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>0:20</t>
+        </is>
+      </c>
+      <c r="F325">
+        <f>HYPERLINK("https://youtu.be/rPElm7KrH_E","watch")</f>
+        <v/>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>16</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Ampharos - Single Gold Star - Illustration Rare</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
         </is>
       </c>
     </row>
@@ -27922,6 +27962,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -27929,7 +27970,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A324)</f>
+        <f>COUNTA('Video Log'!A2:A325)</f>
         <v/>
       </c>
     </row>
@@ -27940,7 +27981,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H324)</f>
+        <f>COUNTA('Video Log'!H2:H325)</f>
         <v/>
       </c>
     </row>
@@ -27951,7 +27992,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A324)-COUNTA('Video Log'!H2:H324)</f>
+        <f>COUNTA('Video Log'!A2:A325)-COUNTA('Video Log'!H2:H325)</f>
         <v/>
       </c>
     </row>
@@ -27962,7 +28003,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L324)</f>
+        <f>COUNTA('Video Log'!L2:L325)</f>
         <v/>
       </c>
     </row>
@@ -27973,7 +28014,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A324)-COUNTA('Video Log'!L2:L324)</f>
+        <f>COUNTA('Video Log'!A2:A325)-COUNTA('Video Log'!L2:L325)</f>
         <v/>
       </c>
     </row>
@@ -27984,7 +28025,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I324)</f>
+        <f>COUNTA('Video Log'!I2:I325)</f>
         <v/>
       </c>
     </row>
@@ -27995,7 +28036,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J324,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J325,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28006,7 +28047,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K324)</f>
+        <f>COUNTA('Video Log'!K2:K325)</f>
         <v/>
       </c>
     </row>
@@ -28017,7 +28058,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M324,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M325,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28028,10 +28069,12 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N324)</f>
+        <f>COUNTA('Video Log'!N2:N325)</f>
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6436,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U325"/>
+  <dimension ref="A1:U327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27116,6 +27116,105 @@
       <c r="L325" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>VSf9bxl_siE</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Mega Darkrai ex is INSANE! 😱🤘</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>1098</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0:20</t>
+        </is>
+      </c>
+      <c r="F326">
+        <f>HYPERLINK("https://youtu.be/VSf9bxl_siE","watch")</f>
+        <v/>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I326" t="n">
+        <v>11</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Mega Darkrai ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>8Cmsa2BycMc</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Where is the Pikachu SIR?? ⚡😱</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>996</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0:21</t>
+        </is>
+      </c>
+      <c r="F327">
+        <f>HYPERLINK("https://youtu.be/8Cmsa2BycMc","watch")</f>
+        <v/>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>8</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Ascended Heroes</t>
         </is>
       </c>
     </row>
@@ -27970,7 +28069,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A325)</f>
+        <f>COUNTA('Video Log'!A2:A327)</f>
         <v/>
       </c>
     </row>
@@ -27981,7 +28080,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H325)</f>
+        <f>COUNTA('Video Log'!H2:H327)</f>
         <v/>
       </c>
     </row>
@@ -27992,7 +28091,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A325)-COUNTA('Video Log'!H2:H325)</f>
+        <f>COUNTA('Video Log'!A2:A327)-COUNTA('Video Log'!H2:H327)</f>
         <v/>
       </c>
     </row>
@@ -28003,7 +28102,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L325)</f>
+        <f>COUNTA('Video Log'!L2:L327)</f>
         <v/>
       </c>
     </row>
@@ -28014,7 +28113,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A325)-COUNTA('Video Log'!L2:L325)</f>
+        <f>COUNTA('Video Log'!A2:A327)-COUNTA('Video Log'!L2:L327)</f>
         <v/>
       </c>
     </row>
@@ -28025,7 +28124,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I325)</f>
+        <f>COUNTA('Video Log'!I2:I327)</f>
         <v/>
       </c>
     </row>
@@ -28036,7 +28135,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J325,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J327,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28047,7 +28146,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K325)</f>
+        <f>COUNTA('Video Log'!K2:K327)</f>
         <v/>
       </c>
     </row>
@@ -28058,7 +28157,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M325,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M327,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28069,7 +28168,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N325)</f>
+        <f>COUNTA('Video Log'!N2:N327)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6436,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U327"/>
+  <dimension ref="A1:U328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27215,6 +27215,58 @@
       <c r="L327" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>0mtM71JvFkc</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Mega Dragalge ex is STUNNING! 🐲✨</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>94</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0:22</t>
+        </is>
+      </c>
+      <c r="F328">
+        <f>HYPERLINK("https://youtu.be/0mtM71JvFkc","watch")</f>
+        <v/>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>ETB</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>6</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Mega Dragalge ex - Double Black Star - Double Rare</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Chaos Rising</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28121,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A327)</f>
+        <f>COUNTA('Video Log'!A2:A328)</f>
         <v/>
       </c>
     </row>
@@ -28080,7 +28132,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H327)</f>
+        <f>COUNTA('Video Log'!H2:H328)</f>
         <v/>
       </c>
     </row>
@@ -28091,7 +28143,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A327)-COUNTA('Video Log'!H2:H327)</f>
+        <f>COUNTA('Video Log'!A2:A328)-COUNTA('Video Log'!H2:H328)</f>
         <v/>
       </c>
     </row>
@@ -28102,7 +28154,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L327)</f>
+        <f>COUNTA('Video Log'!L2:L328)</f>
         <v/>
       </c>
     </row>
@@ -28113,7 +28165,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A327)-COUNTA('Video Log'!L2:L327)</f>
+        <f>COUNTA('Video Log'!A2:A328)-COUNTA('Video Log'!L2:L328)</f>
         <v/>
       </c>
     </row>
@@ -28124,7 +28176,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I327)</f>
+        <f>COUNTA('Video Log'!I2:I328)</f>
         <v/>
       </c>
     </row>
@@ -28135,7 +28187,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J327,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J328,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28146,7 +28198,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K327)</f>
+        <f>COUNTA('Video Log'!K2:K328)</f>
         <v/>
       </c>
     </row>
@@ -28157,7 +28209,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M327,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M328,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28168,7 +28220,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N327)</f>
+        <f>COUNTA('Video Log'!N2:N328)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6436,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U328"/>
+  <dimension ref="A1:U329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27267,6 +27267,53 @@
       <c r="L328" t="inlineStr">
         <is>
           <t>Chaos Rising</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>zrI6oaxBct8</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Ascended Heroes is TOUGH 💀🤘</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>106</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0:21</t>
+        </is>
+      </c>
+      <c r="F329">
+        <f>HYPERLINK("https://youtu.be/zrI6oaxBct8","watch")</f>
+        <v/>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I329" t="n">
+        <v>9</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Ascended Heroes</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28168,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A328)</f>
+        <f>COUNTA('Video Log'!A2:A329)</f>
         <v/>
       </c>
     </row>
@@ -28132,7 +28179,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H328)</f>
+        <f>COUNTA('Video Log'!H2:H329)</f>
         <v/>
       </c>
     </row>
@@ -28143,7 +28190,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A328)-COUNTA('Video Log'!H2:H328)</f>
+        <f>COUNTA('Video Log'!A2:A329)-COUNTA('Video Log'!H2:H329)</f>
         <v/>
       </c>
     </row>
@@ -28154,7 +28201,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L328)</f>
+        <f>COUNTA('Video Log'!L2:L329)</f>
         <v/>
       </c>
     </row>
@@ -28165,7 +28212,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A328)-COUNTA('Video Log'!L2:L328)</f>
+        <f>COUNTA('Video Log'!A2:A329)-COUNTA('Video Log'!L2:L329)</f>
         <v/>
       </c>
     </row>
@@ -28176,7 +28223,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I328)</f>
+        <f>COUNTA('Video Log'!I2:I329)</f>
         <v/>
       </c>
     </row>
@@ -28187,7 +28234,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J328,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J329,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28198,7 +28245,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K328)</f>
+        <f>COUNTA('Video Log'!K2:K329)</f>
         <v/>
       </c>
     </row>
@@ -28209,7 +28256,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M328,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M329,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28220,7 +28267,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N328)</f>
+        <f>COUNTA('Video Log'!N2:N329)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6436,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U329"/>
+  <dimension ref="A1:U330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27314,6 +27314,53 @@
       <c r="L329" t="inlineStr">
         <is>
           <t>Ascended Heroes</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>nTnwXiQzsW0</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Pitch Black vs. Garbage Rips 🗑️🤘</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>105</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0:18</t>
+        </is>
+      </c>
+      <c r="F330">
+        <f>HYPERLINK("https://youtu.be/nTnwXiQzsW0","watch")</f>
+        <v/>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I330" t="n">
+        <v>12</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Pitch Black</t>
         </is>
       </c>
     </row>
@@ -28168,7 +28215,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A329)</f>
+        <f>COUNTA('Video Log'!A2:A330)</f>
         <v/>
       </c>
     </row>
@@ -28179,7 +28226,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H329)</f>
+        <f>COUNTA('Video Log'!H2:H330)</f>
         <v/>
       </c>
     </row>
@@ -28190,7 +28237,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A329)-COUNTA('Video Log'!H2:H329)</f>
+        <f>COUNTA('Video Log'!A2:A330)-COUNTA('Video Log'!H2:H330)</f>
         <v/>
       </c>
     </row>
@@ -28201,7 +28248,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L329)</f>
+        <f>COUNTA('Video Log'!L2:L330)</f>
         <v/>
       </c>
     </row>
@@ -28212,7 +28259,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A329)-COUNTA('Video Log'!L2:L329)</f>
+        <f>COUNTA('Video Log'!A2:A330)-COUNTA('Video Log'!L2:L330)</f>
         <v/>
       </c>
     </row>
@@ -28223,7 +28270,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I329)</f>
+        <f>COUNTA('Video Log'!I2:I330)</f>
         <v/>
       </c>
     </row>
@@ -28234,7 +28281,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J329,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J330,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28245,7 +28292,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K329)</f>
+        <f>COUNTA('Video Log'!K2:K330)</f>
         <v/>
       </c>
     </row>
@@ -28256,7 +28303,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M329,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M330,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28267,7 +28314,7 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N329)</f>
+        <f>COUNTA('Video Log'!N2:N330)</f>
         <v/>
       </c>
     </row>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -28207,7 +28207,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -28318,8 +28317,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -41821,7 +41818,11 @@
           <t>024</t>
         </is>
       </c>
-      <c r="E145" s="15" t="n"/>
+      <c r="E145" s="15" t="inlineStr">
+        <is>
+          <t>Holo Rare V</t>
+        </is>
+      </c>
       <c r="F145" s="22" t="n"/>
       <c r="G145" s="22" t="n"/>
       <c r="H145" s="15" t="n"/>

--- a/Garbage-Rips-585-Video-Log.xlsx
+++ b/Garbage-Rips-585-Video-Log.xlsx
@@ -6436,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U330"/>
+  <dimension ref="A1:U331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27361,6 +27361,53 @@
       <c r="L330" t="inlineStr">
         <is>
           <t>Pitch Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>vdsGni1AMtQ</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>My First Silver Tempest Pack was TRASH 🗑️</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>69</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0:21</t>
+        </is>
+      </c>
+      <c r="F331">
+        <f>HYPERLINK("https://youtu.be/vdsGni1AMtQ","watch")</f>
+        <v/>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Single Booster Pack</t>
+        </is>
+      </c>
+      <c r="I331" t="n">
+        <v>1</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Silver Tempest</t>
         </is>
       </c>
     </row>
@@ -28207,6 +28254,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -28214,7 +28262,7 @@
         </is>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA('Video Log'!A2:A330)</f>
+        <f>COUNTA('Video Log'!A2:A331)</f>
         <v/>
       </c>
     </row>
@@ -28225,7 +28273,7 @@
         </is>
       </c>
       <c r="B4" s="18">
-        <f>COUNTA('Video Log'!H2:H330)</f>
+        <f>COUNTA('Video Log'!H2:H331)</f>
         <v/>
       </c>
     </row>
@@ -28236,7 +28284,7 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>COUNTA('Video Log'!A2:A330)-COUNTA('Video Log'!H2:H330)</f>
+        <f>COUNTA('Video Log'!A2:A331)-COUNTA('Video Log'!H2:H331)</f>
         <v/>
       </c>
     </row>
@@ -28247,7 +28295,7 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>COUNTA('Video Log'!L2:L330)</f>
+        <f>COUNTA('Video Log'!L2:L331)</f>
         <v/>
       </c>
     </row>
@@ -28258,7 +28306,7 @@
         </is>
       </c>
       <c r="B7" s="18">
-        <f>COUNTA('Video Log'!A2:A330)-COUNTA('Video Log'!L2:L330)</f>
+        <f>COUNTA('Video Log'!A2:A331)-COUNTA('Video Log'!L2:L331)</f>
         <v/>
       </c>
     </row>
@@ -28269,7 +28317,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>COUNTA('Video Log'!I2:I330)</f>
+        <f>COUNTA('Video Log'!I2:I331)</f>
         <v/>
       </c>
     </row>
@@ -28280,7 +28328,7 @@
         </is>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIF('Video Log'!J2:J330,"Yes")</f>
+        <f>COUNTIF('Video Log'!J2:J331,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28291,7 +28339,7 @@
         </is>
       </c>
       <c r="B10" s="18">
-        <f>COUNTA('Video Log'!K2:K330)</f>
+        <f>COUNTA('Video Log'!K2:K331)</f>
         <v/>
       </c>
     </row>
@@ -28302,7 +28350,7 @@
         </is>
       </c>
       <c r="B11" s="18">
-        <f>COUNTIF('Video Log'!M2:M330,"Yes")</f>
+        <f>COUNTIF('Video Log'!M2:M331,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -28313,10 +28361,12 @@
         </is>
       </c>
       <c r="B12" s="18">
-        <f>COUNTA('Video Log'!N2:N330)</f>
+        <f>COUNTA('Video Log'!N2:N331)</f>
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
